--- a/practice_excel.xlsx
+++ b/practice_excel.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4bff1f7f1b08cbf8/Documents/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="8_{13A36251-90CA-4812-B750-A4E5E3B4B7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{782BCF83-1FB2-4683-AE58-03D9B9CBF214}"/>
+  <xr:revisionPtr revIDLastSave="237" documentId="8_{13A36251-90CA-4812-B750-A4E5E3B4B7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6840E249-DE90-4DF8-95E6-FC28C42EC0A2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{8833C839-1A56-48AD-BAD5-E70EFDA34D12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="2" xr2:uid="{8833C839-1A56-48AD-BAD5-E70EFDA34D12}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
   <si>
     <t>sr.no</t>
   </si>
@@ -184,13 +185,49 @@
   </si>
   <si>
     <t>rank</t>
+  </si>
+  <si>
+    <t>amar</t>
+  </si>
+  <si>
+    <t>suman</t>
+  </si>
+  <si>
+    <t>kiran</t>
+  </si>
+  <si>
+    <t>ajit</t>
+  </si>
+  <si>
+    <t>Email Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>am.1000@gmail.com</t>
+  </si>
+  <si>
+    <t>su.1001@gmail.com</t>
+  </si>
+  <si>
+    <t>ki.1002@gmail.com</t>
+  </si>
+  <si>
+    <t>aj.1003@gmail.com</t>
+  </si>
+  <si>
+    <t>value</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,6 +241,30 @@
       <color theme="1"/>
       <name val="Arial Rounded MT Bold"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -238,10 +299,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -251,11 +313,65 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -266,6 +382,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2086,4 +2206,173 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2994953-FFE3-4C8D-AE6A-122C63BE2058}">
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="5"/>
+    <col min="3" max="3" width="25.5703125" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D6" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D7" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D8" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D9" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D10" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D11" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D12" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D13" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D14" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D15" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D16" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D18" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D20" s="5">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D20">
+    <cfRule type="top10" dxfId="0" priority="1" percent="1" rank="9"/>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{192AD57E-0404-4B54-B137-2F347467D6E8}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{6E8F9312-9215-4DB2-A69B-034FD780EEDA}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{EDE7F99D-476A-4EBF-A4AB-05B71E2C4332}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{A3DC91E8-1C21-4799-9A7B-C6A027214250}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/practice_excel.xlsx
+++ b/practice_excel.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4bff1f7f1b08cbf8/Documents/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="237" documentId="8_{13A36251-90CA-4812-B750-A4E5E3B4B7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6840E249-DE90-4DF8-95E6-FC28C42EC0A2}"/>
+  <xr:revisionPtr revIDLastSave="368" documentId="8_{13A36251-90CA-4812-B750-A4E5E3B4B7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF8F7B1A-D399-4FF6-93D5-A8594F864A93}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="2" xr2:uid="{8833C839-1A56-48AD-BAD5-E70EFDA34D12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{8833C839-1A56-48AD-BAD5-E70EFDA34D12}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
   <si>
     <t>sr.no</t>
   </si>
@@ -220,7 +222,31 @@
     <t>aj.1003@gmail.com</t>
   </si>
   <si>
-    <t>value</t>
+    <t>id</t>
+  </si>
+  <si>
+    <t>marks</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>Timeline</t>
+  </si>
+  <si>
+    <t>Values</t>
+  </si>
+  <si>
+    <t>Forecast</t>
+  </si>
+  <si>
+    <t>Lower Confidence Bound</t>
+  </si>
+  <si>
+    <t>Upper Confidence Bound</t>
   </si>
 </sst>
 </file>
@@ -267,15 +293,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -298,12 +330,108 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -312,8 +440,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
@@ -322,15 +449,392 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="27">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -338,6 +842,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -353,21 +867,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -384,8 +898,1147 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Values</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>208.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>209.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>208.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5662-4397-B264-F59C4A22043F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Forecast</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet4!$A$2:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>d\-mmm\-yy</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46054</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46082</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46110</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$C$2:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="2">
+                  <c:v>208.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>208.9583990000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5662-4397-B264-F59C4A22043F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Lower Confidence Bound</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="E97132"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet4!$A$2:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>d\-mmm\-yy</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46054</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46082</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46110</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$D$2:$D$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="2" formatCode="0.00">
+                  <c:v>208.5</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.00">
+                  <c:v>207.80462484078024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5662-4397-B264-F59C4A22043F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Upper Confidence Bound</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="E97132"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet4!$A$2:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>d\-mmm\-yy</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46054</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46082</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46110</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$E$2:$E$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="2" formatCode="0.00">
+                  <c:v>208.5</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.00">
+                  <c:v>210.11217315922036</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-5662-4397-B264-F59C4A22043F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1821290464"/>
+        <c:axId val="1785167248"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1821290464"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1785167248"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1785167248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1821290464"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1504950</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6D01150-D76C-CF95-06D2-7397A1712169}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F5150032-0159-4CA8-893D-099E996638F2}" name="Table5" displayName="Table5" ref="A1:P21" totalsRowShown="0" headerRowDxfId="0" dataDxfId="2" headerRowBorderDxfId="20" tableBorderDxfId="21" totalsRowBorderDxfId="19">
+  <autoFilter ref="A1:P21" xr:uid="{F5150032-0159-4CA8-893D-099E996638F2}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{C5CBFC98-8E7D-4C21-89E4-FAF15EA36526}" name="roll no" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{90E1E575-36AE-4B57-9554-F810D22C4069}" name="name" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{41CE8180-A4B3-4981-A46A-5797578CAEBC}" name="class" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{4F43BF84-4F85-45AF-A5B7-BFD0B0B34915}" name="age" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{723CA5DE-548C-4380-AD3E-C06E34485EB9}" name="math" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{37F8BA1F-733A-4691-BF51-B91D7018745E}" name="science" dataDxfId="13">
+      <calculatedColumnFormula>E2-5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{CDC30C63-68AB-41E4-A290-A45A3E040F06}" name="marathi" dataDxfId="12">
+      <calculatedColumnFormula>F2+10</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{BEE1DACA-0144-458E-B4DB-2E8FA27BD48F}" name="hindi" dataDxfId="11">
+      <calculatedColumnFormula>G2-15</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{BBBCAECC-4D66-4109-B234-FD85295AFE78}" name="english" dataDxfId="10">
+      <calculatedColumnFormula>E2+10</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{B96932F1-5DF6-40E6-82DD-186EBF3F6BDB}" name="total " dataDxfId="9">
+      <calculatedColumnFormula>E2+F2+G2+H2+I2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{ACBC5DBF-7793-4B03-BAEE-DA459C59102B}" name="percentage" dataDxfId="8">
+      <calculatedColumnFormula>J2/5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{86B97156-9599-4332-9136-4948BFDC7CA4}" name="max mark" dataDxfId="7">
+      <calculatedColumnFormula>MAX(E2:I2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{59256C59-67E2-4019-929E-7A2B13AA2E2D}" name="min mark" dataDxfId="6">
+      <calculatedColumnFormula>MIN(E2:I2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{87E2380E-FA60-4C28-B452-18BA6BEEB07B}" name="grade" dataDxfId="5">
+      <calculatedColumnFormula>IF(K2&gt;=75,"A grade",IF(K2&gt;=60,"B grade",IF(K2&gt;=50,"C grade","Fail")))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{AC83FF28-CE7B-48BB-BB92-5021D9540420}" name="pass/fail" dataDxfId="4">
+      <calculatedColumnFormula>IF(K2&gt;=35,"pass","fail")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{D4F53D51-E319-4A77-BCBF-62DC45AD5BB4}" name="rank" dataDxfId="3">
+      <calculatedColumnFormula>RANK(K2,$K$2:$K$20,0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C9B4D063-B7D8-4E47-8C86-D164EA8A7EDA}" name="Table6" displayName="Table6" ref="A1:E5" totalsRowShown="0">
+  <autoFilter ref="A1:E5" xr:uid="{C9B4D063-B7D8-4E47-8C86-D164EA8A7EDA}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{49C51BA5-B62E-40F7-85F4-4331E95A2AC7}" name="Timeline" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{B8340230-C8E7-4489-9FB7-8C38F220FDCA}" name="Values"/>
+    <tableColumn id="3" xr3:uid="{CA2197FD-54B9-44BE-ABAB-9BCC80299CC5}" name="Forecast"/>
+    <tableColumn id="4" xr3:uid="{BE0ED526-ABE0-4DA3-B130-5A3417BAF8EE}" name="Lower Confidence Bound"/>
+    <tableColumn id="5" xr3:uid="{6F90FA9C-79B9-4964-B299-CAEBB276AB66}" name="Upper Confidence Bound"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -929,61 +2582,73 @@
   <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="11" max="13" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1038,13 +2703,13 @@
         <f>IF(K2&gt;=35,"pass","fail")</f>
         <v>pass</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="9">
         <f>RANK(K2,$K$2:$K$20,0)</f>
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1084,7 +2749,7 @@
         <v>35</v>
       </c>
       <c r="L3" s="2">
-        <f t="shared" ref="L3:L21" si="6">MAX(E3:I3)</f>
+        <f t="shared" ref="L3:M21" si="6">MAX(E3:I3)</f>
         <v>45</v>
       </c>
       <c r="M3" s="2">
@@ -1099,13 +2764,13 @@
         <f t="shared" ref="O3:O21" si="9">IF(K3&gt;=35,"pass","fail")</f>
         <v>pass</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="9">
         <f>RANK(K3,$K$2:$K$20,0)</f>
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1160,13 +2825,13 @@
         <f t="shared" si="9"/>
         <v>pass</v>
       </c>
-      <c r="P4" s="4">
-        <f t="shared" ref="P4:P21" si="10">RANK(K4,$K$2:$K$20,0)</f>
+      <c r="P4" s="9">
+        <f>RANK(K4,$K$2:$K$20,0)</f>
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1221,13 +2886,13 @@
         <f t="shared" si="9"/>
         <v>pass</v>
       </c>
-      <c r="P5" s="4">
-        <f t="shared" si="10"/>
+      <c r="P5" s="9">
+        <f>RANK(K5,$K$2:$K$20,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1282,13 +2947,13 @@
         <f t="shared" si="9"/>
         <v>fail</v>
       </c>
-      <c r="P6" s="4">
-        <f t="shared" si="10"/>
+      <c r="P6" s="9">
+        <f>RANK(K6,$K$2:$K$20,0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1343,13 +3008,13 @@
         <f t="shared" si="9"/>
         <v>fail</v>
       </c>
-      <c r="P7" s="4">
-        <f t="shared" si="10"/>
+      <c r="P7" s="9">
+        <f>RANK(K7,$K$2:$K$20,0)</f>
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8" s="8">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1404,13 +3069,13 @@
         <f t="shared" si="9"/>
         <v>pass</v>
       </c>
-      <c r="P8" s="4">
-        <f t="shared" si="10"/>
+      <c r="P8" s="9">
+        <f>RANK(K8,$K$2:$K$20,0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9" s="8">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1465,13 +3130,13 @@
         <f t="shared" si="9"/>
         <v>fail</v>
       </c>
-      <c r="P9" s="4">
-        <f t="shared" si="10"/>
+      <c r="P9" s="9">
+        <f>RANK(K9,$K$2:$K$20,0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="8">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1526,13 +3191,13 @@
         <f t="shared" si="9"/>
         <v>pass</v>
       </c>
-      <c r="P10" s="4">
-        <f t="shared" si="10"/>
+      <c r="P10" s="9">
+        <f>RANK(K10,$K$2:$K$20,0)</f>
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="8">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1587,13 +3252,13 @@
         <f t="shared" si="9"/>
         <v>fail</v>
       </c>
-      <c r="P11" s="4">
-        <f t="shared" si="10"/>
+      <c r="P11" s="9">
+        <f>RANK(K11,$K$2:$K$20,0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="A12" s="8">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1648,13 +3313,13 @@
         <f t="shared" si="9"/>
         <v>pass</v>
       </c>
-      <c r="P12" s="4">
-        <f t="shared" si="10"/>
+      <c r="P12" s="9">
+        <f>RANK(K12,$K$2:$K$20,0)</f>
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="A13" s="8">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1709,13 +3374,13 @@
         <f t="shared" si="9"/>
         <v>pass</v>
       </c>
-      <c r="P13" s="4">
-        <f t="shared" si="10"/>
+      <c r="P13" s="9">
+        <f>RANK(K13,$K$2:$K$20,0)</f>
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="A14" s="8">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1770,13 +3435,13 @@
         <f t="shared" si="9"/>
         <v>pass</v>
       </c>
-      <c r="P14" s="4">
-        <f t="shared" si="10"/>
+      <c r="P14" s="9">
+        <f>RANK(K14,$K$2:$K$20,0)</f>
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="A15" s="8">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1831,13 +3496,13 @@
         <f t="shared" si="9"/>
         <v>pass</v>
       </c>
-      <c r="P15" s="4">
-        <f t="shared" si="10"/>
+      <c r="P15" s="9">
+        <f>RANK(K15,$K$2:$K$20,0)</f>
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="A16" s="8">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1892,13 +3557,13 @@
         <f t="shared" si="9"/>
         <v>pass</v>
       </c>
-      <c r="P16" s="4">
-        <f t="shared" si="10"/>
+      <c r="P16" s="9">
+        <f>RANK(K16,$K$2:$K$20,0)</f>
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17" s="8">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1953,13 +3618,13 @@
         <f t="shared" si="9"/>
         <v>fail</v>
       </c>
-      <c r="P17" s="4">
-        <f t="shared" si="10"/>
+      <c r="P17" s="9">
+        <f>RANK(K17,$K$2:$K$20,0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="A18" s="8">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -2014,13 +3679,13 @@
         <f t="shared" si="9"/>
         <v>pass</v>
       </c>
-      <c r="P18" s="4">
-        <f t="shared" si="10"/>
+      <c r="P18" s="9">
+        <f>RANK(K18,$K$2:$K$20,0)</f>
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19" s="8">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -2075,13 +3740,13 @@
         <f t="shared" si="9"/>
         <v>pass</v>
       </c>
-      <c r="P19" s="4">
-        <f t="shared" si="10"/>
+      <c r="P19" s="9">
+        <f>RANK(K19,$K$2:$K$20,0)</f>
         <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20" s="8">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -2136,237 +3801,392 @@
         <f t="shared" si="9"/>
         <v>pass</v>
       </c>
-      <c r="P20" s="4">
-        <f t="shared" si="10"/>
+      <c r="P20" s="9">
+        <f>RANK(K20,$K$2:$K$20,0)</f>
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="A21" s="10">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="11">
         <v>10</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="11">
         <v>16</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="11">
         <v>87</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="11">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="11">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="11">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="11">
         <f t="shared" si="3"/>
         <v>97</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="11">
         <f>E21+F21+G21+H21+I21</f>
         <v>435</v>
       </c>
-      <c r="K21" s="2">
+      <c r="K21" s="11">
         <f t="shared" si="5"/>
         <v>87</v>
       </c>
-      <c r="L21" s="2">
+      <c r="L21" s="11">
         <f t="shared" si="6"/>
         <v>97</v>
       </c>
-      <c r="M21" s="2">
+      <c r="M21" s="11">
         <f>MIN(E21:I21)</f>
         <v>77</v>
       </c>
-      <c r="N21" s="2" t="str">
+      <c r="N21" s="11" t="str">
         <f t="shared" si="8"/>
         <v>A grade</v>
       </c>
-      <c r="O21" s="2" t="str">
+      <c r="O21" s="11" t="str">
         <f t="shared" si="9"/>
         <v>pass</v>
       </c>
-      <c r="P21" s="4" t="e">
-        <f t="shared" si="10"/>
+      <c r="P21" s="12" t="e">
+        <f>RANK(K21,$K$2:$K$20,0)</f>
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="J2:J21">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{A58A8664-BC14-43AB-8977-5378E8CAEBCD}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P21">
+    <cfRule type="top10" dxfId="23" priority="3" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P1:P23">
+    <cfRule type="top10" dxfId="22" priority="2" bottom="1" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K21">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Symbols">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{A58A8664-BC14-43AB-8977-5378E8CAEBCD}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF008AEF"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>J2:J21</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2994953-FFE3-4C8D-AE6A-122C63BE2058}">
-  <dimension ref="A1:D20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{112AB862-3F45-4735-AE31-D12B2AC2B233}">
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="5"/>
-    <col min="3" max="3" width="25.5703125" style="5" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="4" max="5" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="14">
+        <v>46023</v>
+      </c>
+      <c r="B2">
+        <v>208.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="14">
+        <v>46054</v>
+      </c>
+      <c r="B3">
+        <v>209.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="14">
+        <v>46082</v>
+      </c>
+      <c r="B4">
+        <v>208.5</v>
+      </c>
+      <c r="C4">
+        <v>208.5</v>
+      </c>
+      <c r="D4" s="15">
+        <v>208.5</v>
+      </c>
+      <c r="E4" s="15">
+        <v>208.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="14">
+        <v>46110</v>
+      </c>
+      <c r="C5">
+        <f>_xlfn.FORECAST.ETS(A5,$B$2:$B$4,$A$2:$A$4,1,1)</f>
+        <v>208.9583990000003</v>
+      </c>
+      <c r="D5" s="15">
+        <f>C5-_xlfn.FORECAST.ETS.CONFINT(A5,$B$2:$B$4,$A$2:$A$4,0.95,1,1)</f>
+        <v>207.80462484078024</v>
+      </c>
+      <c r="E5" s="15">
+        <f>C5+_xlfn.FORECAST.ETS.CONFINT(A5,$B$2:$B$4,$A$2:$A$4,0.95,1,1)</f>
+        <v>210.11217315922036</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2994953-FFE3-4C8D-AE6A-122C63BE2058}">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="4"/>
+    <col min="3" max="3" width="25.5703125" style="4" customWidth="1"/>
+    <col min="4" max="8" width="9.140625" style="4"/>
+    <col min="9" max="9" width="9.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7"/>
+      <c r="E1" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1000</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="5">
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="4">
+        <v>52</v>
+      </c>
+      <c r="I2" s="13">
+        <v>46023</v>
+      </c>
+      <c r="J2" s="4">
+        <v>208.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1001</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="4">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="4">
+        <v>79</v>
+      </c>
+      <c r="I3" s="13">
+        <v>46054</v>
+      </c>
+      <c r="J3" s="4">
+        <v>208.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1002</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="4">
+        <v>4</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="4">
+        <v>95</v>
+      </c>
+      <c r="I4" s="13">
+        <v>46082</v>
+      </c>
+      <c r="J4" s="4">
+        <v>208.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1003</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D6" s="5">
+      <c r="E5" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D8" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D9" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D10" s="5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D11" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D12" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D13" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D14" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D15" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D16" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D17" s="5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D18" s="5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D19" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D20" s="5">
-        <v>19</v>
+      <c r="F5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="4">
+        <v>54</v>
+      </c>
+      <c r="I5" s="13">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="I6" s="13">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="4">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E12" s="4">
+        <f>B9+B11+B13</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E15" s="4">
+        <f>600+100</f>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D20">
-    <cfRule type="top10" dxfId="0" priority="1" percent="1" rank="9"/>
-  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{192AD57E-0404-4B54-B137-2F347467D6E8}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{6E8F9312-9215-4DB2-A69B-034FD780EEDA}"/>
@@ -2375,4 +4195,13 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0695BAEB-1CFB-4118-AB7D-51B52EBDE8A5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/practice_excel.xlsx
+++ b/practice_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4bff1f7f1b08cbf8/Documents/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="368" documentId="8_{13A36251-90CA-4812-B750-A4E5E3B4B7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF8F7B1A-D399-4FF6-93D5-A8594F864A93}"/>
+  <xr:revisionPtr revIDLastSave="673" documentId="8_{13A36251-90CA-4812-B750-A4E5E3B4B7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20245839-6C5B-4916-B5F4-B2363672321F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{8833C839-1A56-48AD-BAD5-E70EFDA34D12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="3" xr2:uid="{8833C839-1A56-48AD-BAD5-E70EFDA34D12}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,25 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v5.0" hidden="1">Sheet5!$A$1</definedName>
+    <definedName name="_xlchart.v5.1" hidden="1">Sheet5!$A$2:$A$9</definedName>
+    <definedName name="_xlchart.v5.2" hidden="1">Sheet5!$B$1</definedName>
+    <definedName name="_xlchart.v5.3" hidden="1">Sheet5!$B$2:$B$9</definedName>
+    <definedName name="Slicer_state">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
+      <x15:slicerCaches xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+        <x14:slicerCache r:id="rId7"/>
+      </x15:slicerCaches>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -40,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="90">
   <si>
     <t>sr.no</t>
   </si>
@@ -248,6 +264,69 @@
   <si>
     <t>Upper Confidence Bound</t>
   </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>maharashtra</t>
+  </si>
+  <si>
+    <t>delhi</t>
+  </si>
+  <si>
+    <t>punjab</t>
+  </si>
+  <si>
+    <t>rajasthan</t>
+  </si>
+  <si>
+    <t>goa</t>
+  </si>
+  <si>
+    <t>gujrat</t>
+  </si>
+  <si>
+    <t>up</t>
+  </si>
+  <si>
+    <t>mp</t>
+  </si>
+  <si>
+    <t>population</t>
+  </si>
+  <si>
+    <t>order id</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>clothing</t>
+  </si>
+  <si>
+    <t>electronics</t>
+  </si>
+  <si>
+    <t>home care</t>
+  </si>
+  <si>
+    <t>grocery</t>
+  </si>
+  <si>
+    <t>personal care</t>
+  </si>
+  <si>
+    <t>payment mode</t>
+  </si>
+  <si>
+    <t>UPI</t>
+  </si>
+  <si>
+    <t>remark</t>
+  </si>
+  <si>
+    <t>dollar sign</t>
+  </si>
 </sst>
 </file>
 
@@ -431,7 +510,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -475,20 +554,102 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="30">
     <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.39997558519241921"/>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -502,9 +663,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -814,13 +972,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -836,54 +987,33 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1379,6 +1509,3010 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="0"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="60"/>
+      <c:rAngAx val="0"/>
+      <c:perspective val="100"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:bar3DChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>population</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d contourW="9525">
+              <a:contourClr>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:contourClr>
+            </a:sp3d>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet5!$A$2:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>punjab</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>rajasthan</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>up</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>mp</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$2:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>750000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>820000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>54820000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5486555</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-38DB-4128-91C7-CC589EC1EFF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="65"/>
+        <c:shape val="box"/>
+        <c:axId val="776765424"/>
+        <c:axId val="617834480"/>
+        <c:axId val="0"/>
+      </c:bar3DChart>
+      <c:catAx>
+        <c:axId val="776765424"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="617834480"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="617834480"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="776765424"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="7000"/>
+            <a:lumOff val="93000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="74000">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="45000"/>
+            <a:lumOff val="55000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="83000">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="45000"/>
+            <a:lumOff val="55000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="30000"/>
+            <a:lumOff val="70000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:lin ang="5400000" scaled="1"/>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:srgbClr val="00B050"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v5.1</cx:f>
+        <cx:nf>_xlchart.v5.0</cx:nf>
+      </cx:strDim>
+      <cx:numDim type="colorVal">
+        <cx:f>_xlchart.v5.3</cx:f>
+        <cx:nf>_xlchart.v5.2</cx:nf>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0"/>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:plotSurface>
+          <cx:spPr>
+            <a:solidFill>
+              <a:srgbClr val="002060"/>
+            </a:solidFill>
+          </cx:spPr>
+        </cx:plotSurface>
+        <cx:series layoutId="regionMap" uniqueId="{00000001-EF53-414A-B3A4-37F34D5CFE48}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v5.2</cx:f>
+              <cx:v>population</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:geography cultureLanguage="en-US" cultureRegion="IN" attribution="Powered by Bing">
+              <cx:geoCache provider="{E9337A44-BEBE-4D9F-B70C-5C5E7DAFC167}">
+                <cx:binary>1Htbc9y2su5fSfl508GFuK1aWQ/gcEaSJUuW735hybIMEgQJkiB4+/W7FTuJPCt2dnT2ObWOKyl7
+yCHQ7EZ3f/11zz9vl3/curub4aelcW34x+3yy5NyHLt//PxzuC3vmpvwtKluBx/85/HprW9+9p8/
+V7d3P38abuaqNT8ThNOfb8ubYbxbnvzrn7CaufPn/vZmrHz7It4N6/VdiG4MP7j3p7d+uvnUVO2u
+CuNQ3Y74lyddbO3Nxyc/3bVjNa6v1u7ulyfffOfJTz8fr/Rvu/7kQLAxfoJnKXoqUyKVSMmTn5xv
+zdfrgj1NMUsFVVT9+kf+tufzmwaeu/pLOX6V4ubTp+EuBHiNX//+47lvZIbL+slPtz62472mDCjt
+lyen7afq5slPVfDZlxuZvxf49Pmvb/jztzr+1z+PLsA7H115YIZjBf3Vre+I9tAG3wj/N21AyFPK
+iBToN12rb02hnlJOU4wUQ7/+AUt92fqLKb4q6vvS/Lklvj72jeD/WVr/5ozA2R9u7E0Yy5v2t/f/
+Pz/+hD9lMmWcY/K7bh96AQXvUApxhb94Aftt6y+qv/6fSPTn6n/w6Dfv+cuT67P/aF/4RlqwStP9
+ppP/BXPQp4xKLBiTX8yBv/UE+ZRIqTilX81Bf9v6izkubj6V681PV8PNp7tQ/nbvz8T6c5scP//N
+q/7y5OLq/yvDxP9Nw/CnilDGMf5iF/StYSR6Cj50H8S+Zosjw7weR8itj7bL0eNHZnn9/9gs388r
+vyfa3c14k/+aoR+klh/f/S0nHT36o0T/JeKffvrliUgxRYQjsBGHfxBKxYMcdL/kNxnj/ObTTf27
+f3x3gTuItr88AdtSIjnlmKuUUqbSJz/Nd/d3BAFvxYhzqVL4B4Hg2PphLAFViKdICMkQpC2huBRw
+K/j46y1IdlRISGcUsAUDiPE7YLrybjW+/V1PXz//1MbmylftGEAYBjik+/K9e7kTglORCgT/w/Xb
+m2tAY/A1/F+pG32N67E8cbNo9hGE59p2s1GZ7Jp+0lS12zORtPIQ6RDO0MjEmSeyjHrio30+d1sy
+6laurNmJxQ1vWFLE50HJ9U1nG5VmbSXbbj/UTe10NffquulseCFqlC6ZsI1EmorNV73ujEmGrJtw
+kQeKCq+D7Yn5OMkp6U4n79OLQBg9cwueb6ZibT92Zc1CPqS2O/imHRq9sUqZzE2Bo5N55fzDsNbG
+a+rVsh5WNCKkiXNTfxp8UiRZv5ap3cUO2/7MSl69WDrBTGa3oX/FRGxeRimWHa/jVGTLOvD3ZK2b
+q2XBa5ItE6mnbLCbc3uy9iXXlJXofW/XmmpFk6HKVD2K66WtJq+ZpdOtZclypmyTnuFozDVLWJv3
+siIvCbPxLSoGdtUkZXMtmpofkjFVJ6nrtsOEljYvEi6K84lxuls963Nq+LIjfE7kfopDE7UhsbxV
+8wJ2TFwoVe4In6Ju6nl71iWcfp6LaXmJerPdVXPTTLowXf9+I3V6qeJqcV4GWwxZk1rzWqRuWnSM
+zXhVdgo9X61dZq2WbmM6mnU61K4yi7Zmml8LzJM3vapKp/ks0GsZcblqxfu1zqvEoSvJS/LR4rk/
+DJvsM0zG2ugFmXDVtDzx2ndtI/KmK9QzS+vx3Lbl0OueDu2JsH0VTtOmV4OucTt+aNI6GXYsjeHO
+NMXyik1+nnVIxwJrOSYyE0WUF74beMjAP5zbjSolh7q3QV0yFV2fj6ttl4ypKS31mjhfXcybWCrd
+rL1Pczu1Cd036SbuWkuLdFe6nhVZZ9tuy3lPHM4S1VivRzZ0H7bUle8Q6bzmTbW0lw1b2KTBa9YA
+ynDNfMJaEccMFLvErEqbCvQ3RZCTwkbLrmJrec1w2Q+gfW7eNYEWnyvbifVscKS4qws+nkjbR3zb
+uQk1uhw4ng60KTY4Ugsb/V4MtPRXkyP4PKqyLXThnDwt5zncRl4ueTJAHbRDVQOfAwnJOU4qX+dT
+jOpD6rfNXo3lxKNOl4Kd2nltXvejST+tbKveL6YupB5UIbpdWzUuw8izvUVJnWYpbufTrhSl16Xl
+Aukq4TzdkbZ3MkO+HnE2KRP3q0Jrp8ttlXdqGjjZ1UHhXArHrJ6WUbxAsQinE5/CpF0Tl5eJU+Gj
+Glh4a22JnqfLtu1ZDKPfNeXCpe4GNb1IkjS8nQfG9MBm/2zbcL+fnEA8X6TtuK6mYsobosZKJ75M
+c9K1DnTReFPpzU7d27UJ9bMW16zMueWBaluk/rQdzUI0LuimGZzKWTs0+1KXbGJ6soLnPPjpVm1u
+6TW2UahsXLfxwtVuveZqK+XeF74rcsfW5dCbhB1w59Cp6Oq51QTM+H5Q9fZpTILhORnReoGaMbmI
+ojQXKrC61MSn4npuuurlNCWx0W7i+BTNfDtJQzFcV3KeLoMhfNRkbpOdgXrvnfelyKdtLvehKIpX
+Y4SQk9HGbHtbz27VTHVVnowottmWSvuhrWZ/ad3A8tAbpa1altNYDNunuFIvs7UsPT7UtadC82kF
+28e6K6lOZ9O973xXvxfYkPlMUUx9xhYxaIjh42uwzjJptBp8SZs5ZJMb+/UsYcsc9CwDVQcvrd8V
+VRLrDAU6d3BWrf/oGOWvxjTCIexRVESbubcfsE+7d6yfZ6X7fvBOk5iObJ/yjZSZr23d6lEMW3Ug
+HereBIttfU2kb0YwCYWgY1Da72jSIvKstCuadxOof8tFNSaL5t06LSfEzTQ9HdAa6GXXd8OF2aqi
+0nOr1nonDFHPh164j0tpys9lMvhdF1D1ypAhOK0chXQjXC0Pti9smTnjRV6suOsy04rqJG1RNLvE
+98tZOvVLqelauLM4T3zL2OSakDk/+ufIkinssAlmN8liuZq7nm67ZE3qw9SU6BSPRdxNIro0WxrM
+ln1PqT2nA05YRvxIT1BHy8O0XA5x2YwugXfp9BCm7Xy1XZfHpmmZRn2K6qznjf0o+rrNkaPP5qWa
+o7YuwlMeJHzReRHeUifnszEBxJGZdWSlDjWarPYzqnZmFP4M3Ib5t0299lanYzgRXB7G4DauV+ze
+OzmoZyNvAD/UvUp12Sp3VtIZG3CXoa+BnSkY0hB2WohDLDkM+JrK5QXBXmmJpu2Tg2wAiboaX7nW
+yWdm80u2NoXM0jaM120Rp88pJJ8DNSM9o4rfiGHmuy0qd7LN1JyQMYTXdGH0RNZMgOs65/QocXrX
+V6qYMu8mdRUxpvvazXHJNiG7M1yMTc7XKp4UCm+9plU1DLu5ssv5RvvxvDUe7dRU1BeOQSDP7dz2
+ncaL8WuWSpxEPXJc1Fk5JfgQ7Kqs3qq+Pt2AkbkmNnVnCxy1cylH+2xTVfosllH2uupieKfgnO0C
+a+UtXwvSat6m/WXaOHndNkic2HFscZZ2RaHJkpBPCg7Mrgi4fdFbVevebVWaN7VJTxAbu9eoRdVh
+jmB+r/ryXVPWotEzqbegK26QxsKK522t+C2uRobyQc0+48PYfRgHxbJt7MdXPQnhdjG4u+IjXy7a
+wa4ym2trngcWRE69KA8zQ1XQievoCJiLiA/NRu2a+eiW1zyt0kGzuTF3RdmXl02R0HMbO9FkrgEv
+1HM3YkigPsb3U7qKXEy9fJmkdEIQAArzXqC67LWppuVDwsvkQx3TodJ2tMubTll+KGUnLoFpoGdq
+mevPIO9wJUxYP6otVl5v3RoAnlWD6/Q0yPGVWuem1zbMzO6oqSTRnK3rC2kGuRcrm99sKed70bfN
+jSIcoEYX6tnoMRTzqIthbIeM9NQcwFTzOTZmhOhQFcOLaqC8B/jCa6vHzUGkIn4ZXd7FcqjOhE2i
+P8RxGIrTbhiR2Um1cLd3uMTPQ9elb4mYJ6NJQPW6r6ZmwnoZpKG6IoN8VhmxNZlPlzDuplkNZSY3
+tNEskp6rrFjn4f08VoPdDVWJfFZtrrioOKF+x0ZensIJUVvmSTXemFJAUpuZxNf1JED/QcZ01qax
+8YQAifsmTcv+uutdqPUA9dC1XVO1m/BksoQg8awKTF7iJaK7CvfSaTgFLckh77YQAEl0s67lwF6u
+LlZlXq0ACfQ8hLLNTbV11Q4nUMJcSdZMxX6eWHoiHPF+V9dpJyG9tZLuPKSK6YJUoSs0WMGYbFFe
+HDge5bVzpOt3m5rlpr1y6WfbJIrtWpXg14ol600lE/RJShfjiZ83yOT1MIwRwKptW93HfukyZ22X
+O+DDsjJ15jMxvroet85mq+pwtQeMuTU6lVW+CT+8iLINu0EMEKLaIPl+BdRmd+mCSa5KKSFOxVpq
+zkNxo+aeXKMWIEYOqFcl2dAo5vKl40sN+Noln11sNsBocThVG7y43qbe75OiXfJBUHCTFPLyDk52
+xHlvkb+hqu/IlZ2My4uJLxo+LVceuW7N2s7PRKNuKEoNp4pkRdOXV4Wr01NaS3NZo6YZ9MqDwFAB
+kX7TA53llAlY0ry2VQoy4YF2b7pZyLDrVeE+e1eR64G6tQaoU/OdK/q4S2yy7URcwMjDkpyMdBhz
+XtDOZAUCBKhXM6CdaccxjxuCs9hVNdMMme6mdMnwrF42AgAfb9tJMmL1eU1FsR6KpBHLBbZV8mpK
+JlhFloGdGiFrKMmg5iSHkcbizMOZvl2dAtC8pdhcQ+bujKakUs9k4dvTbkR1p5fF0wNKQsymXti9
+gBySm4H0OSdlvejWiu00taXVCRIxVz6ZdFxDvACh07OUEvQOcECfq1q1+xpXNAGncV6LudgKrabe
+ZVaYarfYOl77NCZBN9T5oIve9brtUfVCoM3luFOl0Uwq9gw1BOAUq4uc8OIj4FR1QOCTOVTyIQde
+1HwgQzN+XBFiVCcVLnZmJfUHE7x4YTYcFg3VgT2bfeIOW9I02WrG5dWyFFdrOeL3GLnyBasG8Euy
+iFYXnC1nsp/mk7Rz5hnnXQ1659WZLJ0qs0VU7OBrRN72wyYgRlWe3yP0hu5LhCqjRZp2jR6NBTRb
+V+gjgxBzUgEszWtwnHAxty7CIaJQHA9TA9g1qey4M3Rzp95HANGoqfwrbwDxAoTjV5wv6ct08/RU
+8JBc+cBoPnMfVm0sn171SWdmDZGXnHIjZS6WqXwFrle8LznZILQVsYPwaCqILnFSlXYtap63a1ee
+0aLkV1NK+KB7KddKU47qC5bQeFJWJX1ekW2RumitvRxcb9YdQ02yK1EUp0Vj1rAroh1frsRVr6OL
+05VKDLsF38VXuBzUXR/KsB+ULRrNyVomOplT/JaMHlA9ru0p67m9EAiNi0YTcBnNCPGqipGMOsrG
+nro2lrvYNs2hkH2ja5Usp6Tj3a5w6fIscfCytYBFdJG0PUBW43nOHI1vB0h1JezWuz1CGNZEo3tZ
+ECdfjWVMar3GjgTdlTPf97XtspKS5cL7BOPsHrmwLBVl+wo32O55Otkrn5LPAopByMp9HcJuicl4
+vqaLeHOfPvOprmV77ZZ0fsMhKYMtt97LfZz8+KlOlzX7LyjOXVe01J3QlQGiccOy7BC3PuptLdnl
+Bikl7pyyKGS/MmZfyb1vqKhb361DZcqv7bvfP/7rlW/gv18bTX9cvO/+/fHpcOfvuelw/KX7fX7/
+1h/Nqnuq7vfO1REV+KWF+B2e8Ic3/2ckIkaYEGj4/Yg5vLgz5Y27WaEx9wf7+MeDXxhDRZ4KhoCK
+ZBgTilIOS35hDKV6KjEwxRwrKb7e+UoZQicGcdhdKQFko+DqD8qQsKeIIIYVYZwpIBT/FmVI7rnQ
+B5ShkIijVFKGgJhMYbH0nlJ8QB3Gohwhswt+MqghBfTd15CzJN2WQWOghD4ttXNngCKX7hSqvPgy
+xas0OZ+x3fZGFfR1b20DZTfn9Q5wFJBOTZXMRcbmcekPQIbR1yoIelHMM7pskoSNV5S1nGZiURJI
+izS16iR4L+sDWmXfnaPEL6draNqMMVOaXBajeRWYKJCeEjdmMeLklcKxfyajiO+6dHGQLqTKIcJC
+idTKa7QN1W6iQHqtftKq7sBt6zANtxD7uzmzNDR9Bi9rzhGQSqMeUrydszJ0bjenJVRM0clDurnm
+RAAvd9mTipwUTC47wzZ6slZrdULSXmVtsi4ma9zKX8wlVa+kV/Iw43q+6KRTmV2BogPaF+VQaHba
+RdVmpOQZgVjYvZm8nON14YGv1D0UGVglHYD0rlqbHKhZis4JKSpzNrfz9KKfHF+hKvWpOe+r0c4Q
+q6aJ6mV2ptaq7RezC7hYup1JaCv16u047Q1eIXxDuZTgFxtmar0cjOTtC5yixOgN9cVwUtsE0G3Z
+SbydRjRye1ZAIgFAZws85TFytu3pVLp3wE/17IVshpHs8SYBRbmSpHVGIqlXTbcwxX3Bw3QQIyo/
+Id8ZkTVdow7tEPEbVgAA3hlkzN7b8Fmp5VmEyHlFWknO/bB2taYoOUkWOb0TfFh0iYqreWm55v08
+ApJfGnVBh3kHHF/1Alc12nPkGu1dYQFiMTQfAtSXn2gziRNPkrI6VNNW4Z3zqN/VvJPABtsi0avw
+fN011ShfOpys53NRbVm6VOx+7MC9HKEs3kWqgB7wbXmoDfVnSLTNLgnK5KiSZ3FYVb5ueHtVtBXe
+AxhkZ5xbChxacqhajC6NjFntQ3i5prbKSszDZWIwQGcoSSBj05jq1AGrre9Zn0b3wO+ag09md84E
+kTtYa9itjWvOhz7FAPhsWr2C0xqfeUSxzRDx66xXVdnT1dRAwXjgFxrAX9p1Jp4CoVtfKllM70ew
+baGNLzAwqWRZjV7nZUF6S+Z5Nwxlq5tGvFmqqnnRr/7gZ+vyXqHtTWOn6hMjyZwPUnQvm2jCQZTR
+gt7teuDW9O+FGtNTl2zxohvXO6gDAYt0K2lyuRTjSZ1YyGmDSOp3XTLzl7NfcZ1hKGU/dOuIQ44a
+np7Obkr2y7LEXUU6mvOExJxBdblH/dAfNiXmbFiYyxpM671bLMrSwbgTp5Iz4Nw4RJhmueAMxXcF
+CjPVwbgro2h/FoDrPYPGgLo0tC9u0nkqxv87Ce/itzmZ44z3MOH96z8vLd4+nD75JrthaGb+PlPz
+b720b6Yv7ltSQMPA47+2zpSAIRosoMtFoRiHRtjviZDLp1hBRpOIKSQJnOKj3hkkOg5jB1/7beFL
+74w/FZC6KOROAh0/rhT5O70z6Ns9SINfO2eM3Sfah+kvFEvh60rxkxLvFLsME8wj/P7+X4HRw57c
+99a9v/4grSpSTTy4ReRAwblSb9u6vi0JX74M9HyZ5/kby4OWHy5vwbXAmVuRQ6NlGK6BXUbmlVk2
+//nH4vPvqAWmbB6ur5qtlhF6FznAkLC96HCjkC6pZVijFColnQKrVux/vNn3dAXmf7gZdPq4nU0L
+zH+gkkJ1Ts2g/crlhx+v/y3U+cPG6Nv1oXpGnVUrhwq/Sy8wntPm5Yws4uerHNvlkIgNahPILN31
+jzf8zgtJOOkPX6iTqJvE/YaTU2I582UsYpaGWFb5jze4X+jf+r0wH3IE2mS1zWiMlOVzHcR8xlda
+kKyrAynPoQVhyQWONVD0fejbVWjkUmiuoLachpMf7/+d48GP9m/UBExcNOLQuNAX0O1s+viG9ptC
+QD2XSryA1jblpz/eDN/b6c/e9qi7DbQjUNZhZTm0XKc+k0QeBMWfu5r2MxCoZp4aIAdEcu5ng+s8
+AjklW50YSZrzH4vwPYPe6+GBNzsDUM6xGfQtCcvo4D8LNld/oczvLX4UgjyEhVkCVZ+vaxDvkF+9
+LqZoLx8n+v2uD0WXtoLmGHSKauDE7xB0F87bpKrjl4T4dwORPApEAFtY15eM5W4U0xtoEad6KTbx
+uDAnj8LQ4GZogQDuzEefbFuOlmQadrzzXjxS/KPQQ4Akl6uzEHqAJAI28Z4FgW4V+O3uUernR7HH
+AcGM18WKw5B088GMOHXaUGk+PWp5ebQ8sWvS+tAlh9avgl+FKpTjm2Yck8+PWl8cRbIATCmaFyYP
+m8dNvpo0GfRS1WH4C/3fn/E/cW1xFEiUr1MXyVoA/pVbs58H3E25m1dc7fqqTNUjtzmKIDT1hZy7
+RBzGEXifk5b7FuVbi6Gj3FXjvDzOk8VRmOj91Bd0aeShg37Nq3pYy8sWivtXP7bF93R1FCfmepF4
+Bgh1IMlSARkO9PO5SVffv62ZrJe/UNV9XPgzi9xffxAvSmm6GlC/PAwuXU+TZkOXyuDB6R+/xPeW
+p98u74tqRaAcfoiiJ8DI2SV9zzff5Y9b/ihgxEn4e8qDHyYHFhidaXIgf0X3SOmPwkWsaLu61QI7
+EKYabLDKJdEBrdX2yA2O/BnIR9bDkI48KNz0wJVj1kIVBmT4fPUoBd2D8IfmFWSlAScLP6hQVm+g
+ixCulsr06+Pk50eOJtaBKiDIxaGj6VidjBtdlC7rZkaPczF+5GJLtfZ8JIM41MF06WloyCS1vW8v
+/sUG95HnT84/P/Ky1ViDmhlM3BdrN+ysoULATNc28TMzFk2dL4as7TvXSPohtmZuH4ly+JHjucUU
+wm8zhEIHNO5ZmYQC+nBbrQA1ynG2KUzojXabsqrkXbOHHo0RO57O1L+cgLiJf/H+33FQfuSga8Gh
+21cnxaERSdzRahYHGPWhf3E+8L2n/Jl6ybfnj03jUvWkVwcKLJ3PN1xMY86KbXMnnaJivTSh8Z+7
+JJ2bk3STLXu+UEraCyKktO9kTWBg6HGecOTLsrUM2nFVeuhEEWjGN3XXLcvcPy6OsiNHi3jg0lqT
+Hky3yPcM0s/zgJLmcXHu10HQB1EaetmtTRKhDsxBJZNFLJtNx2pYw18cg++4ATty5FD1KyPQzD6M
+61yQU5kOA/q4dBhcoiTQrtZtdc/5kI135rZrtkAeqbcjB6fQtwIrD/zAZQEzkR3MBjTQSkmTR4ZY
+duTgW7rVfQRyKo89wzAzMpndxn2ye9SpYkdezAuFWtsv2yFEMx62VljNh87+RZD4jnOyI+fkGJXJ
+AnXWwZKqyciI7a5YPXnkoTryTShEvMSV3w4E6kaNSvy2NelfIb3viX7kbph3LTD1ZjsYsY4XcYUx
+l9z1JRCaj1P8UeYsbRw7OqzbISkadUqmpd4VVKaHR62eHnkz7SbWATe8HcaCpNlMRdChwdXjZD/u
+wciWbBLmOkD2EUbjahonzWuRPi7QHQ+Hw7DngOYibIceV24fVGsyGOLY9j/WzL3b/ElAT4/8tS1Y
+CbObyXyYE3YHlWA97dOxhhGwcRb8kW9w5LJ0ElNr62I+UHDcazV6m+PU14+rkNMjlx1bwCrzxueD
+h99GncIoQNzZtX1kuEmPXBaPjSvkZuPBBJc+q1wjLrrFPVL0I4+FTFrUNabjob/v12QDIyET5VKX
+ux8b9ztOmx45LStMqJMNmJeurZazejTjeSwK90inOnJZ4EeTCUNvfz9EM4eXdEbSXbIBps0fd27u
+u7kPwS7MhUy9gXELwGxxy+qOvV/V2v7Fwf+Obuh95nyQgpmFGWoJfZa8dyXWNESie6XiI0U/yr+0
+sykprJxA88n7gQAAa9VSPM6s9Mhn624bkiTwr6KnpCea3U+QP+rQ0GNvZTALIkvoHqoZSGNyv3p4
+vGLuzfFA7TDM2hUuwOqLhTGZKOsIg1zEPlL2I28tUyY9tN9h9ZTAvGnq9gbG+B4X5ik5Eh0m9WRl
+YHGYcmwOTsCcYgnd9sdhg/smykPFLCMVBUyBTTkbixmGtyYYg+9+a3z9XZ6PHvlqU3ak9RTFvJ22
+Vs9ldRfthh+ndXLkp2GD8VVfzhHGYMtU85S9T6ZAHrn4kZ+igg0UxoLGXPSo3YWlugkRhmkfddbJ
+kZv24X5IEYaJcstVqbmF8ac4EPHI1Y/8VFCbmCpRILqK+CJAe+SqEMY9rkV1/4u1bw5MTEkLIyHx
+sGH4sb/eWsnZLoGf4HydDvq7Z4YcuSrpF9XEzkyHNYWfdumEduzQzWS8fZzu/5uzK+uWE+Xav8i1
+FBD1VqvKU2dKTnIy3riSdLc44IAg4q//nuqrjm+68y1ue+BQyN5sNs9wiFVgz4gaN4mTtVp6kLKW
+6LR0rTv7jU5+Xh2jqonWgFGVOqNfo5a8LIy++A19jNTFtdK5QJeNCJ6RHr84knj218ghTjO85ifR
+kOiytSI9GRG/jl01+iWw6BCnQ7cECqAdUwaNboDJTR4TMod+mz06xCmehe20bGlwBs/nj8YBwhfL
+B68Fjw5RmjYWRJ42cCWGXQB3Jwu4fuCM1H6pNzrE6VrHRnRM6RKArvAzA4qmyZdmj/wqjegQqGbu
+SdhXoynlqPbTuCXfRQOctd/aHIK0Sps5WRtlytgpV0jwlsAY+d3L622QX1wObmCAf6aYbACTYAqk
+LsGUzZ7SpY6e+qCaPvlN/RCiRBOtIBWC7SgAxARj6XOSNp6f9BCjOxuBKBWdKVUMnFWUbl/6OX3r
+N+9DjDLLNttQjB20yysz7ilmy5PX0OEhQkdbVaDV1PocVkFQBG312OyhZ38gPERoBGZUsgckOIN7
+/Ua65EuqXO+XWsJDiAYCdboasSa9GF7GerxUUvhl8vAQnWyyjm5oep/Hfb1Tljyw2O8EDQ+BOTkQ
+NcYJdzsu68d03IB1q/xePsNDWDa93sQN6Xie5Id9NUCzf/TbIYeQBPpXTXuHj8hE911t2Uu6c788
+FR7i0cxrtznLdelA5nvdnSZla+hy8pv4ISLpUG1D22S6XAK87pOhu8uq7LPf2IeIBB0NANMoDM5x
+g+o2CPk3BtymV4YFU+DnJIiNPc99iCNZNIDWxgsLTsD9rl6Bw7JDUKbLmmgWr8F55u9BcEzxvuyz
+Jgw4459yNyiTM5uF06VJga+wdAFfbuavfoMfYtICPOLcUC3nSEx3tsdz+0xBT/Ab/BCWypiwC3oM
+nvbxW2qmHw1zynNVDnEJ7QcXzmkGyQJJ38YYezOr79iH0Ixsk1C6RWgbA0j+aNK6vZ/Zxj1X5RCd
+YmFrj3oWGyUG13MP2w89F14FFssOsblloKOBkqjLjToNiCqr+HgiqIAar9TCskOATlayCigKXdZs
++hbY9RMeHz547ZYjWGulNFScYl2MqePTbDoQVFKSeNURaAj9HEVKrAn60Rsmvm1vzRjeb+Am+e3F
+9BChrUxCUEjoUqYdfeoBOAQpPyF+K54eItTUCphLs+oynPoXFoBPpYRXkcLSY3zGweBqKpeSkJgU
+VkaqiFj7l9/nPASow4vCkkq9AAHAv9TLdt8k8Xu/oQ/xuSlddSkJVAmiNIQFxmS+DBK8RL/RD/E5
+go0JRQuMjiek/TTs43NCAd/3G/wQoDcmUiciq8oR+JQbRUsFD+DwuXd+wx/C0wYUWRGSHiVZ3R8g
+jr5sS/rda+gjAknj4BETeGhlx+t32zRdwZH024dH8NFapR1ve6ZKUDrFebU1OQX98MNv3ofgbHZW
+LWrrljITU9Ex9yzT35Wdtzj531sVO8KMbIB+8DolqhRyBc9LJSC4zXzactsS4wq/+R+CNO6GbejG
+WJV9Q7/2gn0Kpu7Vb+hDiG4AIfaQwlGI/3W5WxcV5dHK/J7qINr4c8atiQDLkhJMHDRAuQYDGLrT
+R7+ZH2JUbPPUqVAsZUwaZs87NY5BN6kXnd8hnRzilIka7JG0x5bcgpdGktdm9ruLQybq53Xpm3jG
+hRlDVy570WHzpqLc6xnqb4rbP6/5fepAZF6dKmklSRmkRL9EtW28wLfsCDYmyRrGa4OdWIW7yx24
+IZR5IrrYEbAktyrQ2yJUOaxTCIJocplt7dcdBuvh5yXXihnDMiw50uPD6shDH29+MXSEKWW27k07
+16pMqnrIk909ZJAR8DstjlCkDLsk3Einymhc39JoflSh9pz3ITpVg9cJSF7N5cLTT02kXvpu9rrE
+MX4IzmpjUNGYWlVyrEyeAReez06mfvmQHyJT03YOWkhy4N1GgD1IuhcTZB+80soRJByGuGcNcTiX
+dUNlm1s0Ks4mDLjfwhyhSG2bATbWOsRN5mSRGs7f9U24+33RIxRpbWNeAQx3Y2xB0SBa2DNOUr/X
+c3aEIRlI1o3xNmK7jBkUcG4add0i8jRbO68eDl74f45R4GfDrN4GrH0tbFIMaJ6VVcVmv3cEdoQb
+uc6YVMlqKtNg6eZitZP8y4Db5nlpPAKOIklCZsEdLZUAVV7WvAXXVcQXr515BBwlybZB1CecStNz
+UoQcwG+K269fnokPEat7YOMXOkzgbia1ziNI2X3r3DbUnuMfYhYCMlzZDWszCui9NVp+2PrI78yL
+j8cpGa0MEoN1H9Lpzi3hcrH9KO681v2IN1rpSt3U26lsq3j/FI5Vfcegc9T5LcwRcESRJ2Pi8Fmz
+oZqXS2JSyvK4GiGG4zf/Q/WLx7huHKYVK08Xe1Uq/SDm3q83z46Qo6STUNDRaioTpt839fJiO/3e
+b96HqreGKg/t+3oukyH7Oow2ygVjvwO/MqSUX9TtR6DRjJZ5CkW4qaSqTb8meFS4M51cPbfM4WTV
+YbC5ncZjiUjNcg7oSw4RsuTstzCHUFUuwBt9j9Hj1Zk8jqb7bvgdiunvEvRXC3OI07nZAK9LyViu
+vKurHK/FLZJN0mxdUcus7u7k5Ox7I5f+Shca8FILMcevoLgl81uWxYt6nyWSg3fc6PEOwnKMQ9it
+QTO+3uY0tPnO2ll9gNRPYIrQzUP3bRQimAuOwpKcIMomzDmZDKjIfYQuWcHxSg1FvTlI25Ikm2DX
+aoSyItQT0U34HADZ6y4RbZfkRJMNY9q+0ZBDmDOxgG1HdnORhGz7aVklHb5u0Gqp3mrGg/b7EsXz
+XKY7ydZSbfi9p0nv8bkN1zgthoSAJ81dUpu7Ohrr7JGnA6ha4bxDYTTNbL5CReU6NYvayxBqA+5i
+Zb+y0wp+eHxeE8vQwu7Fyoq6n+SIejbLXJGqBkKAcmxU9GCHqs2uPY00K3esti1i2q3XHYo1z2pY
+Q3Zi4bruEFNU1Q6KfDsmflXIEf0yDw3U5/ZsLDM02/KYtI9ir/1YK+wIfgnx02KWTmPpIN4oT2No
+23KDyo9n9ccO2V5uEDfsDB1LHosRLasgJzXN/JLlEaZGWeVQBfdTKbj8s2Ld+yppPBc9/bm6gSrX
+tvWQFCtjU5ULpPyqOPLrbP4tLPIPIFa8AlYTof1VEqg5QBwngxBFD1U4r3xzhKipsKa8w4tjWZO2
+zbdu/ou3yq9iPQLUWnBz1yEJIe0GiZ5n0L+au5Fq6ZeH6S37/2NdBG8g00n4UtaqY49QN2nBKzD6
+i9+6HLK8kvW6rtM6ltALMx9VOu94iRhS7bnsh30eQdJiDyg+Kq+hhHsmy2D2PAnibj55zf8I9dJy
+tlUg9FjioeovO7H7OFj8KBcw8vh55Sdj1TpD4KMUYQYcmV6gZV3QrCV/+c39UNSs8bzT1ZCp7Ods
+T/NknCne2CGJ5YfFgCLWzz/AQuI2CrcaBQIsVnKT2PbcNI1ngXDEe03QRmv3Gkc43mhUAUQZL6DO
+EZZ+i3PY9jYEezluhhFMVAgGcbrGGtotivvh+xk5bPylHSBlPI7IZINJ7sVAw6+40zq/VjA5lDfJ
+JuddLqhX0crarhWrTJmEOvHc9If6hlBo/zS3BN82si4WO9e50VL6xewR8hUpKDtuuCeXgRvonwJo
+8z93CeHvwuvDHkFfMaEDdPi6qYx5sgZXCO5FRQg1p/g3b4f/Qu9nR+AX+KBVxft0KPc+oup16qC2
+XlTJQKaThcj7Kxhhz0GQ9VBwbOcuK2qIgPOLCOJ49Pv6R3wYiLQ8NC3qTwsV+LQIZAsBCimGqfe7
+Rh8BYjykO+4st8xU6ah6kE0NRribnQ49P9Lh3rKHRoGSSoYSbiFNB12o1jIo+LLVs0aJDuHNoa+p
+BoI/4AwBbHk3n4De/+G3ww6h3WvpdGb2oZzUsBRbTf/adew78UNk1zOkGRdo6EKDn1160t0Tsvi1
+AP7mOP7jpIeYWVhbKIiUmq1L0QUMTw12f+e3KIeTWIte1ZFdh7IyKj0bAUFOGTeeR+URJ2YTuE4N
++KJlA33Q77K19IcKcNx4zf0IFFtaBqWyIZIlypXnZN0fIOv4Gy2X2377xVXxiBOrN7wzcjUO5bIR
+cR/1KoXM8Gj9DrEjVMx2vEnXjsoScqxjnbdpOt+LxAzCL0yPgDGWQfWUQxizTOKhLeYsvetY5PzO
+gSNkTE1DXVdZM5QZE/ZxUZIViW7Xl//+prdM8quFPwRpZju32gjne7+zGVVzuNQwqAijcTxzXIwG
+rxqLHvWYIMhRVZNWkFBVyXdc1J9kIj799y/49dahN+uWfxbmbA3xNAg6FhiCY9VCdM+sf1oKGXC/
+4Q8L1KBWHkQ19GU2pRW6O0t6lTw2XiFFIXb10+RH0kIdXmHyVS1wx4/IlEPzwS8d0CN+J+M7VLQX
+NDsiqyMHpwg8/hZQX25Xr8siNAB+nn662mpCGdGXkYD8HqT9w7cjyFNeuRIN6J9Hdxx2KFAThJlC
+VG/jfQuN42dCpth4zZ4dgY2p4xVkOuuxDA3VsMKIdXvL92E2nnz2DrsZSv1za8qgWWaI5iJhxuS9
+0eE76AV6bRwWHlYekiQ6DRXmjpYvRA4V3pd2Ew2em/6w8tDdTIMOUNVzlKjq3eqC6f0gYj+KHaTe
+fl6WHnKKJiRLfysM0pdJ0rjUTZx6LTo9AhzheSTDSt4CVqBVNs7pS8Cgi+zzRWFj8PPUjdODM67p
+AVuBrlgBRiycevoMeqT/Pf7fzYr/zcf0CCzj0MDeODfIZtzEECmNoO1713TrrC64iBlygXcVh0Z4
+3G/jY+BwK3icYMYjv5CIsouBaPM1YYGL82yvDOQP4FfRvYHVxEYKOc+uKfZaVPv3sYKpwmWYcOYW
+Jm63H1Qy9rBOrb53jVgvtDKwFdohUiFuitJsfxUR+C0v3U1I4hW+UdNywoWN7fi3yhYiBPLzuZ0E
+9MnxXy/NEyUVDFn+e1H+JcMfAXHANc7kRkg+11XUPq8QB3+Edmvtd8DSIyRuDGCcge5oV5It/JOT
++SWL6rd+M7+duv8oJXHXdDLgtishpAqpWMKuBArcv9krtz33q61yOPiMCeAks2xdOU8Q07iqBU4H
+p8wB9QC9W1j8XGEX1osvfr/kcAxGcxZDzTruygCWVWcG+5rLDoHzD36jk5/XSbjK4I5IYa0yMnEK
+qv2Tbsnv1um22L9ap0MWjsK6MZ0yXclhhPAeqGr2JhX19m1ro+A3zcF/+xOHbBxWGVxpprk7LxuF
+WL/QkDpt4HGBZvu1sWC0/eZS/S+f/IiaAzyhNivvazg46K67mHiLgA4L+nMj95QUQHT7dZVgZvfz
+F7lZU8hK9Vi0gQQAuvFPSESeNVVy6LgFEBxBI2DoSnhhfNXUXjSN3v33TvqXL3EE0SUUWM4dHNxT
+V8+Jvmb9El/GNMO7P6/XPvRCF9Cb9d8/4zrG2LxpkgAyHdD2A9e9/pzNiR+1lSaHwF5cNjeNU22Z
+JLGG+vIIGX0R+V1W6BFItzZoRVKYYpQNS9llWp2EwH/jdY+jySGQQz5FfZ/01Slam/uwgjfVyD3X
+/BDGjob9MmoMve/sXGXzRTbE635Ijxg6B6WyZsm66tQ15CGJgwc4Mv0mSf/L2XUU5gKsECaSvKlO
+U2thZbgsugxi+v6/N/u/DX4I0go+SqujATY7fKrO06QYBKR7dvEb/RClYdYpeEIFTZnA/+UBqNdP
+cHHwE4elRwxdzZM6WIlpyh4OEBeT6eEunHs/KCpE+n+OTwi4491QKqiFt+18mkT6GCRqOfutyyE8
+oVg9mwXGlSctWbNdCLEfJtV1fk1FeJ3+PHcxZnru2ZCdhnV+7vqxbNXod4gfoXRObFstaxRSvTZN
+PpghLPY+/k3m/bfNeIjPFej8HQw/BNECW02gxoqJQ1HYb80PB+wOkZ5l1VMD1pKE4U49jTMMoOCk
+5Df+EUuXSQfORRdnIFqNO8nTvlIP49Y1fjxIekTTGT5UQzLT7CTtjmfPF6AAfjPzv1u1vyhvjlg6
++O5FEKeqRQnvU7o+wFAyBsGohtjmK5SSxrKJs53mybzK+MzRXbPFrLt4hYTlxN1lNlk4n/cJxoHf
+ZBKTFRYEtEm8OvCUHeKwzzTdaQon2CbZ1CWuNGR+g87vXY0egTfUEtjedLDxoVYKoCz0KyiV22/W
+9V+281Hgx1i4i0LTajm7JNrzLuxUkXSe+YmRn2M87gwP6Lwu511CosFq91eoYNPqFStHdZ9ghzdw
+BSebcw3E/CmzQsBcAPQtv9GPkQjoc9WsSKbJRL4vkr6XgvhRKukRMSEkbuzjxMy5CVWYbxOpzlUF
+6IzXzI+Q0C2YI4jA6Fs7Sen62tAwNXB37Zbh5PcHDrt9aBrN00gkp00JjtPStTD2FDAcpz/8/sDh
+5FG6M/taTeZsRjGdZcrsacqY17MHPWJCcX+I6USlOUc3ETobz5ANYIkX2B8m6j9v+ClZ4ZKqMfhq
+oO3dL2yGxwdslPzW5XD0MGEgzWAGcyZtNBW0i1r4TvXf/QY/bPixS9MwpJU+r0TIPIXVzWneWOhX
+ZB0RoTWAzyELqD6PgHnlY6fq5z6h+qPX3I+AUGaniUZ81ucgwxMc6/YaPoCx38IcBegaZaMRqAB9
+hqIpeTvIrfvOwz3xq8mPaNA9FnbWBilyGHhfQNkc8kSs+p0Ezy0kf3FoHlW+4CA2E/jophde9fH6
+VhjZyIvjpFcXpiacgl7rfwRTVSuMqmH0AgMUkgZwiIOF+bAZPzAVPYKpJlElWnOMXtdDc0qBpCqy
+0f3hN/VDMutafAHgGdV52mBx2Mi5PS2y8ss1RzBVNrFQyzi+uZ+Z9SIFnD+hMLz7JRt6qKCdxHVj
+V1adtdj7S7R0H/aojT0/6SGT7QIW5CN6PecpFbBCgoFNAUiqH+wfr/o/58khcYlO0mo6BzJQsLuf
+hpzCNdXvBDyqfVUMBkVRy6czPBZFsccwDk8hLe93/B0xYCZyaDnDiurStsP+uofT9rENh99pvd/O
+uF9E7BEFVlFrIwOw8jlWEfgotxw/keh3PcJ/G/1w14XDDdrVLssuLEDrfA1+jP3w6hVIR/RXFxE4
+ENM5uUDnq+rzdQfAT4tt+ew3/CFOo36k4x6q7BJPcgCGtd24eORRP6R+sXqU+5pgSovCacou2RLB
+kpzc96Hn4XcEf0GIa9aOYGjJUArf8BCDHyCRHpFfMFBoKpHM2WW/SR91NmIFE6n1KzjIIUxbmH7q
+3Y3sBBWuu0FNb2H75xejR9hXGANURKVkJw74QzsEj2xoXry2yv9AviAjJBQd2IlwI6MSBqXgXQsr
+zQe/8Q/tqGGKZtiWj8mFjRF81Xe2MPh1yfR3eoK3YPxFCjjiuZqgm1hqK36RU7Dc6Wpd5fOSwHzu
+DJ5qUl1ruVvxpPfq/3G5/vt28Ks/emvF//MJx5FqWNu5x01hs8NWRH0D4+Nz1yHq+ouoYKSYz6OE
+g0w+0Bln+9Y6NSTXsZ+4kBdcrNtO5v3ere4qKhdU3yi1gN0NISCtsMdr3W7hwBqqaX7seJROTyvs
+rSN+3QIGT/hc7X0dwNaVZg2tc6WTCZeikePT5XE2j/W3SQnYxOWsSxp5pXsHueeTw4U+qU9uXq0q
+Okfb7T0k5Oza5HEH1x3IfLtmW4Y8ykzAWZ45aLd3d9HUcWjTS/QsNTz44NNtMMElGYcPE5GoHduk
+Tf+C+x/+sTIzW08wn4SEqcEKdcW6WtKUuzMbXJe6kC7DtxFN28TAPBvumhZ2vLwWX4aGddkPWZub
+jeLs9lHBPE/Bge7zDaR3N+3SwScYolFLYW2zRLD0BnGyOu94siHngFTbUlQpdlpWrNy6WJ7Iusfh
+Q5SuPLs0sdkleGHz6O4g4z8UCZ9W/tSGpklPYUMtLUTCZ1RhqUxPqYQAbr7NNZ8H4DfbUdQnneGK
+lRTokMBFHjObB5XkKeEJeCNrU1YsQdmIXMKlucfXGkWTqxSVXZ5FQS9PRg7k66wlP1m3b8kP0+yO
+XiY1xt3zrkjKP4qZJMkz1RWlj3slUlOf+h0cFXbJrImgiLDzxPRPYGik+F5T08DnsqjDPathoQdV
+Y1RjMhz37s5xutnvcwrD37oYVzSDrwkYSNlrtCXb4op+YHASq9PgJgPZm36wAVgsO0BbUNBJzGrO
+Dt9yHK8kRiMNBsDdkIq841124Z0YipFvVipcYF2wrLfKcl0eQrN0Z6uQo575WJsWRsikhjOlMiMx
+l5bGy1bAfJjBkdsK15/Q4xDpl1TTYXzINriPXgSc/WBCCqt5NPPzLIU5IioorSmlRRZTCjtCuJbz
+CwRWuu1hIDZCVzvU0Fbb8cys1xrcrdAtXAPJySGyFvbmO+kDcGbUmrDpfRLLKD2Jaonb7+iDpD2C
+RrJxPS1tPC7PnQlr/gp41iwvrUtAE8rGEF6PexyQ7jESttv/aIZ+NGDMqGBkzzOCVpyHSThynWDq
+O38SgUxDGIazruZxnkiWTc+h1l30nbVVlTr4i2eyLq1d1/g+VA0bP7eWu7iA5n0INnptaZRB2jnm
+/Y9K27qr827u0u/wYZ2nT2CXw3cZr0s4u0CVGN0TUH1Liv95DNiPsVXrfpVkcu6120N4Dk8CkfSj
+Zdjmd3VH9medhfUlJHPavkmVSfg5TJtJvJs7se1vLTgSJMBLNHQD0tNNiZhfF6uH4a8OLzfioeUz
+deU4tn1VziSL1IOZs4QULaOMfEk5Ydkfke2qZ1DIg3s8I+0/wA6ReWvjGj6grApOW7On9h4mD+t+
+B/Eg+rnPGtjWTz2Yji+JE/3wHNVVE13t2Bh3DmbRbneZUyEvE7izh59CXnXVOzFn9VTAVzKAJmIb
+Zgt4KBJGpPfrvsTqaQl3HV4pDJ37D3DWqMY3Js4ScQlFNyYnvbUrcqeNUyUuwE9H6mnOVv6jhybA
+UFTo0tg3YgsVUokYN3vm8ahVfQrxWrU+dC0Eji9VbSYwVIJkrV9FumTsKqdp4rmuAsW/C5HB+rke
+lk63eTpEVQhzIEa369LLRZ+0JWFw0stAonzodzt9oTrDDE4wY48gZ7hhFk1QLypvt2AZzsNNkieH
+oN3ePc8WxLRzPCn7lYTOcjiewR29KWAFwZ9QLtV/VgjhpGhh1CoLLm08fnIz/BkhcCQlJM9y2u17
+c7UaLNlXB386VeVi1smGfL9PdhzzVuOYtjk63uvyw5qVxh/hkaFwIHRQq8ne9Rjl9iEnbdQZJo54
+6TwPlsg4B/dziMs+i7LuvK41/OnzOtLp/mC3pUYHc4P1U3YXVg41IphsQlwXGJ8FOax7m+A9jztF
+ToJxE5yWcI2yU+L2vf2owp22d6vebVYaOQbVabakco8UznNvw2hpm/foIhPX5U3f6+wC1fha32cd
+bjDPDl2I9MK6Buedrqp4Bs6bie1R1mHbFeOuIl2wCaal4C2opWos2HNwzH4Hu3oJMsbAtH7bbGFC
+7kY8GbfPI5TumjlfHYPDDXTF89mqLLpGNFv0m3iZg+Ebaba0f+Q9XbDHBiF78Qft0x07QUKybTmP
+ddqsF/yyrT3HsmPLBxgoi+p+qZuWXkGi5f2TUQSmWGeko56f4GVEqz93SCVD03wRbQzn5KaugW0G
+iQl7JIWO0r1otZvuplZSYIYJMMTheZngepiv2g3kPf5m+nGNhN6+9hCNByc9I2JkxQz5xboIkJ+q
+Yqum7X1LuKZ3aTaB6xIPA8CqclVpULjJaLi8qdFuIJCsSVTgQSEVbzHdOH6zWVc3d8FAGF6OmqoL
+zKuU+zjcA7ordlRFw779wKmxDB00UmGc/nJ7qaFhQcWc7E97mDG5IBPvrrqmLT49hGY5HMEeLRLy
+/AbuF4u6hlpk+m7TMM6+ndybgCZAjWVcllxniPIQenX1bupibqxzLzTb+gymuybll4RJ5Le8o7ZV
+b0IdpfO3XS0Ta/Ner1t8dYyG2zPD7hef22WDRwx+JB2rNx1a4/Zd2mER73fSqu00UBPrO5z/wVRj
+cYlcz3ZPElujeNLjjo+p6vWy2i6QH5LIafl2xZqt93MLBN4bmOyKpmCtGJfPMIEm8RdJEpfKHAph
+4TBhpWhf/zFAMzV8C9V6ln0bobzSfYWJdUdwv4IgIi1kS9rkTiZ6cajfRJjyMZ8D43AU9huOD1R7
+kIzlQbwmpwUiDaMDbDQJvkNV3rEixKHeXnczd6+Jwf4+d6HtedFsO95fZDKwTzEBLqKgLq3aAndR
+lsCkcExMSfok5nC33kI5P0+wowflOIJ852XK2n58onKyQZ9zMLC+teOst0scNWx9Ew2hgv4u3lmz
+V5YOVlzWHk45b2ci6Od0gcvLaWEVWgFpE2j+7IapSi6hai15g/cnOrzru2TZH6J2mEckTIbYACwe
+QLW07CCiqp4q2WfTVqSM1W8dkC9BsfFGru+W3c4gRIP3SmwBGcOqK5IsaqY33YIeUy5k3c9n6sCr
+7S+gqEVwHafDcFJhRfAlGtFHT8xMNydXvtyKnxRoX1EXWbrGBObLcxiZvNs396lNe6gm5bsE8e91
+ArmNfqwXPj6qwaDiKkTdBkXUQhXOFcjua55YTvUnYiB7cFdzO+G8T7YQZToFgXfSuaMs0NcGUwhf
+zDjopIAvPBytnTBD2W0I9S9xqOx6IUnXR3AmUZA8i1hD0xPtgcTMFxrtlwyHkYXReVy1y7MBdApW
+5JLLpH/slsq9Sd3NAHVXO31Y0rQLzykcbDYcoyg5TmpnSPs3s+b62vEh1q+mr6L13c3Xu0BbeiZf
+XV/ZtaisYHco12Bk2YFFM+LVLVdbK+6EniCswcCrxmFLi33XGVyrYYbET1qF5K5GPfDJyoQ+1JBS
+kjnP2nmBcTbhNTRbJwKjbNby+9TW7g8G9k/7RBA6stzbZc+e5oCot6GFxCuuQFQ/1jwlO2qniKm3
+azABSa63pOCgkT+hhQ6yNvxEKdTIweR9ciolH0Yb1OeOtLzLpdz0w9r1cI62UNA/ddjGRbwZC+P2
+qrmDWX32aHjt7uto67+6em3fZ7RXRRPylz5W8kPcZkOW1+G0AHZi+q6b8y1sMrvAh7sW7uJg7+bu
++ErqjzzapnvdujQ7YTvzQu5m3y6DauN7B/gi+2CDNHlf9xaohRPRQxLcVTJZbZ9X2LkpaPJOhH80
+unL6Qxxz7vK1kVsKKGe0WndqbnoA195tO2RTUhW5Cc6687wQ3GMaOranmq9RcL9GDIRm0KdteK9E
+VGXPS7At+rKC5x9+3HlPeJE5tuoHw6a4/orKVc7nWJOA3E3N1LDHdlthxG7qYe1zG00q/UhNP4Vv
+ZmrodIZMgxsgSbBwcR2DNeu/BAJewm0RuyZuTuHSCp2buEEpmmmTNIXqUaPYvKIBpX3uYmeaH1sa
+0/lx3cZ1/w5TKotySOg0xu7uEVvxlLcgDLVnqOhUpFRp37QvW4S7/3kcGJUXnSDvnHCjqZPrfIPf
+nedEEvoGpJo2fgB+lkanKNvi7BqBNrX91YAfIN+YRadTWLisXsX9Mi805DkERVK8SO0t6d0LrsYJ
+wS0YkM39YVn6BXlBDImNniaJkHzf4bJqv3Rxl10Z/LZxQZY2+fJ/7H1Jk9xGd+1fUWht0EAixwjL
+C6Dmqp7ZA7lBdLObiRmJIZEAfr1PUfT3xPYn0dZ7mxfhEBdssatQhSHz3nPPEPRh4X2uMNNCmzw1
+DCmFAKHTGHcHiqUosSNW976z02qsdCcfOTT9w4N0WNuf+r5VJF8x0XrYr5KaeeMdd0s+6cgjRITR
+MCRdFaskLMllv8hp/koh9y9fuwxqtrXMEfV3O5fppGA4wJruGhnPrJjW9Qh3163KPNJcczxlWBH9
+sGsllqd0EgAL0xry/V0e+qnbhUVa+NWKLh1KgKjknGvYwDfoP1Dx5W08j+ZciyDGZXA3+dB12m1V
+oYvuoey9Ztw0uTeofd8ry3DFFuW6VUvKafxcKAYtEk8L1X8eXNGOG6P9yotVYYNj1uqExy1mj8Np
+znOqcUlEBjFgD5Q97szYoihtOexkHuwCl1wYAbTJqdGk3bpkkrdtSOYB1QFbFnM1l2UZdcjTjCAK
+0zZEvpjMm83sJJtjjQhSu1/CHg1aqqyI+sE1nokGO7j+RgROpF9HRJvI9VL4frri7ryvRrpHxsQu
+QZl9ymDNhbsuDKrwkOTIND0aPTePSuIkrMJhoEEZ+RmmzA99ueQeqtTZ97bTgvt6izogEIcBW0D+
+7FyYbdECBOpTA4tzkcZMaT+7NSNLU1hCBxXPbISbjIWxxKo6o5vzIJxbRBpklzJ3/hJ3eODvi4BV
+6zLJeI1HLbGHxgeCcQG8ImTXsp54cXBjp16AxDyh9BgIR6QKBwW8QUYMua2JTj7DzyLPVrrCopjl
+XXExDD4qswUGI25fCpnGZpkROAIGvb/LRBeWF+0Q9uVFl9j+aI1p8mdkNg9vXlv0/WqyHi4jncRD
+Yel5uFNI7O0TdQ8ctcSw0kuLWh28pmGKSieqDcTKike5cRq1AWgLI8Lu5AS8FithD3xnyC8dCP2I
+SJRnpAfC7+6hQDEWEQYG+h5QuupPYStb7zoUIPGBFCRqPe5HrvVQ4qLY2e+h6E7ybD35oczFOpc8
+u9EtsuHXAYQC7ddpJMUYeymQq8+wO0CCbMdkT9d1SmaCWzMjd12GfmQ713kfkRwLqIlG2yHFThOb
+fpGs6slD6Gw6xnPVB+h2BC3HKcpHWXqfsixIXuS5NNnJCSrz+5mbt6EoB4pyV7UBitmKFnankAki
+Y8W76q1heGQjiciOGLEgPl2Xispv4F8RLjgJs1zD3zKhaGUQqr6ZiHDiyWhPQX+cqQTIoKcqOCP1
+BlYcKxQllTsw3jRfynIKA6xzNM3rBzi1qTwmXerCXT7Q+RWts16OXUmStyotF8UQyT2P5FSljrb3
+XuJz9hYgMoO9orVMgYzkmp1U0xVYO/x0jokOWnfdqUQYSI0wW6Kaa/868zgHmo3Swz8yB0PRjRo7
+TlbTsPjheuRjP0ZlZac7eCIH9NF0arzxPNo/ykQE9xi3D8u2SaC32HkNGuOprKZxzamEoe+Sj+YR
+57w41kEBWhvPkYkNjxPa7JtUqTZmpq5cZLykeIJSd4paBp2MMdTxYzcZ71pwN11wtaRy0ySwGFmX
+bJ62LWIltoEp/T1FjjHWvDrsH1Kl2XxldAP18DjC7ydirU2GO2dh8foZHhxozvrZ0fQJ0HAoIj7O
+OA/E5TmWBRUGYYOKQ0B/LP3hPp04isQQUILWqDJy5sEeVizeqgMNnq2Z1MBNHBLPkVMiuiXbEuOb
+B9iv58UtkQ1E4BMSGG4zfJAozMbA2BjL9jy4qAM2Fl6ZIhU0Dg0+zn3TJK7Z5G2SpzGhwriXM9d1
+39RlVR0nIZYSxyi8/rYIqCuvQi0cCrY5CzdSGq/ZgUIp3A2g6HqNZaKuNx1jeb8i6VgGoMshuXXd
+OB+LCHxgDrgWgCMSwxqDdtuBtDzO83Dbe2k+xjWzQXnwvLFatrAfW149htikqEQ05FEvzYTHJ5E4
+HYXz14WiNm7bwR3CJkDBmWb1cTYpuwV7uYVCAP6OwDlg1BBSkTx5C+jkGwmFzHwPnGkasRH1fvA6
+yE4TgQycYgE80JfW1PsaE4rsc7q0fRXjSkHwLosUlTlWzHKs4rRNDPzLYV6kLmCRJkWsHDd2PzW0
+RUA9crORXZqMXGaRx2B7uHEqPD+EXj5qjXTFFh0TFp9ilS+9cvsBogwVkWYaSjzGmHe9Weydyd50
+g69XIxy1fTAxK0KDh4aiQluNTnVpLOjIofUZ+Fw8ZBxOLysffvPZUwlAg0ZVbdP03p8WrB7a83hw
+4CKoWFwpUpJVAzRsjJt6BLQVQZc36VUOHZd/RU3byRsEgmRjNMMF2qztnLAmmslCUcEoEwxfvA6p
+ChGD1EPdIMtmFNt0Nk584fhS7rFHgcpPrA9KEdNSFOS61M6HabJBU5BmfVXdzhDwFxuS9341Rwxi
++xEAZlovGo36AMgBN/WEohC55kmLMGrVJxdp42fLPqD+VF8oA5w24iZ08Es3affmszBLL8mS1KCC
+JH5R76wcPXINiZrgeKa6cHGY/9Sz2SC/0XUbkItMFWOqwuxL7areQ0DiMsi9VwJOefLL6nyFOBqf
+VdApk0P3hwasurTAD4sY+oqhtxE8hwJy9DlhaC7Z4NW7DDyL8cWRWfWrhPNk2Dqs127VMWOKdRmG
+sl0RJNIMRdR21Zxu0A2W6phQ2K+BfFme48GQltas8jRT0yEZfCFj6ES0Yis4Mfh4oLKkwjwbo9BG
+H/g4hQtqlsHQHUCCBtP6FrVdBBw2KCJo85Z81eI2KDd0skH7JjJWlB56h4AOIZLoYWLy1RRVCT1X
+gQnZgM20Qp1IY6/s1JYTQ+ZpXwQylA/wjK6Gk0NrPxl88YzmFDXIFDZXTGTl9Ojh2ygvSoMhbOzm
+7GaNhnSUy0gv7bmDPiZeU0wovsCXhcHUnGh9NVdBj2alsyHHA04LYFYixqyFoVv1+0rVX7IZ3TXo
+VLOo/LduGL0WxYBgaJiaAXLbEWk1TXfoVWPlFcPioVEqynx5LVJMIz7nuWuKDdW09hzOrglrhCXz
+LruhKPfxLBMlKNsYlEbtW2ooczIaAgW3ZieolR8D4HMZ4l+A/w8vqqO2eDCebbzrRmPgczOeG1U4
+FsyyJLEYW/gaQzZnunKfVph74SahJtx0Ao0PXyNH0bZHiFI1c/GCGVKDTjfrRCZWPuODPDqDSdIJ
+1bXkJ5RFtL+ry7zoDkKHrtl7FmHmn0PfT/yYn2u2jW0qz0alIM47NT4Mnm4829sMaxxs6GOFyrhe
+z7aS3WXWDxC6VMwX48elBIssln6PIU8WljUsZjrtDV8k703yMXQ9Fv8a+Qb5uBy8BfnaKFnha1ju
+ndHhjHoKGdRxIKbB7uamVuGuA8rutmXBF/8BqCJjh6zAJDA2fgUCwBrSTb+TK9ybC7CtM6LmbdqO
+EBuHvMq9CM/cBTf9TDFrZLDH2PgBqNXtJvMCzHt4jRHPHJWIWJPR3E6GrbpUMLobJquWnaGT59ew
+dCPOKmB6GllpjVVBfmJB1/cPrIer+pvQ1FYnFLaZ2JQsterOOYxmVqWWuYY6EeTU66yuS35MdFkX
+d07ixBxnIov+4FtE6lyM+KwEkePzwq5zKyp9mPJOFfdo9LJkjH2Larld5Y2sAFtTeLRlfmzxMBsv
+hvcHn80Kc0Ah1aYANfhsYSw+wcHQ74NYKRhgVusKo6De7lGAdTixg8hNd419ugbwDDIORmmo3dR8
+F+K0Q1ylWFos95ieJNNmxJO8UcsiTmiiuXckXqJQ2HEf7nXkPMaTZOvnnJttkYuWnZaygcg1IHMz
+fHKZVTCtKCysQzaDNtOcRoHjTGDGSUC68ttejjEHsNF/rkYqyXUD24WebM5WrwEwjYkhfV12ixrz
+WFXOFau56s6JckPPL1mX0HpPIS53u7Y2NlzpcTb1ifTwqQFE6mPe2sydsJsMIH4QeX0QeBvMKIds
+VUqt0HaatjeokMIqC58ngZj3Y7LofLqFJQMdgL2nSbe8hjUL9YspGr/c+yGkjnsfqG97AYF2N3ws
+YUmN2qZmdDoF1Ovnr3PLcnOaZ+31APgmIuNFoRyJgC9bzFayvgfZrx3ohfWr3sXDjODQfYePkK/s
+QkgRgxvPMTOn9MxoHOVGgUx6WY5IBr73XaH7i25YgvogEHu3nK+2SKB1UMOM6PZe0PwFMJ8XrnIm
+PdPDrBX9TNzXuNurNSrrAhskFtJzm+86466U141hPHte0OFhkW0HuYRh5zOoDOAqVBIdU1e9GEsP
+yu5MZK/2vD++CgulOuwNmN63jZqDyMd6V96FXUcGPHuaVe0QGdlD6A+ICUFRIvUzfxUS5oFeE+o2
+uSSpGNwGyyi8EMeyzsa3IZ/MdGoWUbHHbrKconlpc3uYZ7FMj1JUZrw6eziGu76ySVTB7KaNUI3q
+M1huphF7LgaY13KelTj0KZQGlxiUVPBgQG28ANpqC6BWDMGVlA3PEK62MoKwiLj1xE0B1K5r01vQ
+JAJURCNCmW9zMBuxLyJjA96NapSJehDGVyD31j7mWeO2Trq2GaIMej8aNRI8gjDG7LuzbwCSNMBb
+ADb+8Ay0Ysm8iA8oX/OIYZUdgCGWDdQeEUzq0XduJshDEQ5UT5Snn6Cwnm0XWYcQm3ZbjQPL8ti1
+8A9HHerziQWrLkxB5Vj9S98NsOf1mNxiUhUOsQ9GUB95cmiTGEbJ4X2IV3vH0aXa7FV6xn412u/J
+nNdMmlw1pO/WQAsWC16rl3j7f0ns5E9zT8sdjLqnaeXzvLHRMqfsCgOr2q54AvH332MwvQ+f4zOt
+q6buy7WvnnL6kY9/j8/83lCIleGIcQ3eN8xuJUCLjP1NCc370LkGhocqyYTYYJv0ASKp0b/osVr3
+u79mL/2JYRVGBj8yfQCFkQGMNEwmPDx/bdpkw7FyXgMbwb4zAJzImCMWQKiWXE89oFs0WLnnx403
+4Tr99Yc4s4r+GdvoHbFMY0QzZV4nNg3STMtVBh3BBciDbYx6DeNHzOLkT8wv/oxM9Y7W3rU9bjVw
+ijcwBGjF3TA3iV0ZjTp35bAzwZ0UjiQlqtJprn9yhv+EZPnenSgHPwy7CWEbLpHJMcB2Zt0Ca/7J
+F/qzd3/HPjNI9OtFqhiYI9VL0QUPTprk75Hy/Hf0UJTpbWV0wjYzYj+itJv3mS3Dv/nm7xhmQxAM
+dWM52wCDXmOQmkVJAOTxr2+oPzsr7+ihyTRmA1MZ32jf67Gnj0kUpNj9/967n4/6B3IcKUwIdhDO
+C1kqePMOCimTS3P312/+J3eoH/745rwLKmemHLdLKhR57YEpudjnM0GukCSViYwFG3sHXQkzfyue
+L3zvCJNK7QRshNgGcajskbZdf5kHgFf/+gt9W1z/ydP93g9G5HMIWEjTTSVVCgRa1bPDcAX/vc3B
+wB8oKm/8n5oGNd9mJv+YL9nHAHca2yV9ZlP0KjpdI53xdRpDRDdHg0BJ9vun+9cfcn37f/83/Pyl
+MWj2dTq8+/HfPzYV/vzb+TX/+J0fX/Hv27fm8rl669//0g+vwft+P+7qeXj+4Yc16vJhvrFv3Xz7
+1tty+Pb++q05/+Z/9x9/efv2Lh9n8/bbr8+vVVav0PR02Zfh1+//tH/97VewC33xTej+r388yPff
+OH+L335dPb92z78816+/XD7r5+6X3fP4Vmb//F3envvht19F+IGEXIJjRQVFNOZZQ+Levv0L+aAC
+img9GAOgJyMSq3iNKNT0t1+J/yEMmQKtLWQBA37w6y99Y7//ix8S7vvwIZIh8UH9/88Pe/37vfP7
+RcIZ+v7zL7WtrpusHvrffv1x/0Bzq8A4Fhy5tPgkSry3B8rzgUxgmydrBxJTnk9bTgFJ9GRVTD8L
+5PlGu/0/d/P5uzOugkDigGDB4Mcfn1NdeaYxrE/WrG6w+I63c9Xu4M23qfEgLar9VPksHtyjCjee
+WK7A0vVj8AJKTSLsLsepNNjSyU/2mHfP2PdPFRIA45iSKv4+XiYxWaM4CIBrMPfWQ9HuS+6G2BGx
+CXS3XriJhQf6FJiGsqgjTANXc0IrcPfgiAnGEDE/IV2Tb+f83XmSJJQBC4FjK/bePq9KhfHAzUvW
+/WLTLcnpXqN9uUXsXnI1pakfgVdQXpkSs4Vo4ssBXn5VDBdxC8fHke6XtP7sdTW7gddkeQytTI6U
+Znsj6g2MiNHO1+6zmL6Uc70aB5CdmvoCVI6sQGg8Jn4IIomI1ZHi3jrsfQy+VdTLLG6bZdWmLK4J
+u/BhtQVEbGNovcKA4QITuo1NswP3bh1pbhc4cBMNXmQ7xkyCuefb1bk/r31y0DzZ2rY59Zzssgoj
+u+4Jzjd7D5kqy/ji1cczpxU2iuHBoO0nFMzAh9GOj6MtTNTBsyY2k9jT4SFxdi/RUpXwQg67YQVz
++Cka9M1CkfiWX5aSxQvmX5jorSuRHBimSgVNIpWUp5m5u2qsD2H4TWuxQ8NSxbYaNm0OdqjnqgjD
+1BXhCsMeF2FAdTGmfNOHXyfhAGTjmKVbG4wyz3O/nj1iPnLIgaqKutgHJYtsaaMAxC5MlmJwSYGQ
+OPix9zg9OIyiK9O626ZjsA8CYdELd3aAi8TixpVgE+ZG3SpoX1JxRer2VC/oXTDucUCxfV8dDMWT
+Ocq1n1exl90Vrtl53eVsUOyq9HnMkzWlL+3UfO77L3U3Rlq2UaHRHwI1UvN11tU7GYxxJcUGZIEY
+yen20lfM3IFH8FmLyruYW1w5YYsrD0YUt2SZmiHWuLXIkKjrBATZLzpsE/CNDU5aBSOoNJrq8g09
+fXpDFt08K6jCeRSy80OTYGQeJKAbO3onAktAiSKA3J22n2Bt2UQ2VGf+q1DgCpW+fqhMgXZ0DlF7
+JPXSRgSjBlQ5zFZ3spjtJgCjCJyRxQuj2k1zh0/Bp2eGjW5Xs8qCldaO+iIdTXYC++CKdT2/6ZZR
+3IKc1f7euPy/3v4usi+gTTdfh/f73w9b5v9Hm6RQQKwI1u4/3yO3zfMfN8R/vOL7fkg/EMUZ9kMw
+QrlQZ6uT7/th+IEz8INFQLC5hfS8U37fDwP2AeRF7FOBACYLswsUed83xIB+kOgQA4hraYC3gxXa
+/8WGeP5gwOslFl7MQmC0/eMmhRHpWLPSuXWuQeufXLpsEmyScRCkTQRn4OknLjXnuvqHxf7b8XBA
+xqiP84GT8cfKuNRhX+DeR5gc7QHgUP11XLAVz877mUEBQmL/67GY9FEDK1C2xH/ZWNA6kDBMU7cm
+gX+O1mDMxK1Og31OiLkoEj1eWBBstyV61pVuO/XKSySA9fVU7CvM2SpwC4vgALKx8c6oIS2iQunu
+kZaY/EWZ5OwSbJDgcDbte5ndwpK4DwQWgXyCkVZULeUkgEk1bx4s5yIui+Aj4OkBC6nI2uA40A5T
+4DMzJu6zJVkNuaBvmCA36146jAUl5nJf7eSlb/pslFPUIlw1Sblco9HmIL+0s962o83jwg7jTc4X
++PP4yh93iKbE1l2kCh/FAo17hFJ7ySKStmAIZLoUGgvlLCgY1J7YmiUEsQUjEQSEWAStTVEPomET
+hWLsvgKyBiLf873QuB8C2MGvPVGf6pl/rFlWmFWRh8lh0d5yzCCXuEb8wmlKybCmiT/GOjNPXpXm
+wN/JTU5heVwzcZqxK0cZWLhRa7oWjvVedwL9HW4M1oJWh9SlqAxUCb8zxIFgo2bFOvCm4uDN/VMG
+OlyEeAogr23WRFx4EgRScTnUeQ60DYzDtIDSPZiGNfPUekzqeVtochN06MCIdwvlzwqMkz4CHS3d
+StSpq7JSe9Jil0DThsN3XR75gf56Dt+OmM3xl3SOhI+tpwfHOh5LUUdN2vsrTnFwwit/NUr/BhqV
+PrLNOROs1s+awMoVFu7YVvWLS3CrB30pV5jLbDPn30DPDldQnNEiTNUqoendEOQ6Bjr7isHGKSjA
+3ILWIIaEYOsbEHcyB9I/6cObJCygJKmC15xXG/ALQFy1wzb0868+4cW6SLonhh8Q9nkJzcjXQmWn
+atAHbYogLkbAk2Pa3umOw20Jbe88HtOk2A6hd4IBc7Y2CiWGnM6MwjZpW33KQ+r8VY5wz6t2YJeZ
+1zxB9WVAvAQWGrry6KvpjUMRgAIaJWMBJQJIkBJkSq1qkISdArgKh+5FAsHNVJujvpCXZE71ZZhM
+L5CjPE6acOjAwRkswiLDJurBn0WD9STgwoOwkKjx+iQmAuqtIqlRAeqjTgpEk3TkqfAVvkAC1DTB
+4UqXvSSMntWBA5haoYgxeo8oShcog3Bo7ogH3v0wrjDEcTEu7E1azSpOGjdHXln2UVLhQYUEfvk4
+QNsTJb346Hx801pUpxHaqIj65kVpmAB/2y/+d3P9SQeKdSrAjvPnW+u1fbVf0reum/+4w35/2e/7
+qyTYX2FOiAaRgfT3bRf9vr+yDwz0dYFGJ8BS/8P+yj8ISkKlIIXmSpKz08x/7q/+h3NrylQYou5l
+Z3fg/8H+et7PftjvcJtJ9H4CHaCPv74DaxieKN8a2649yT4lk42xtteR1lZgDjFilW7ttNFKnEz9
+MzeU970uf3fo9yAUyA1F4fftWoFHFWk4ukRpjiFikby4NpA/AW/I+Zv88ZsK4qOAkOgrfU4peS9E
+z5Mx5wOt580II/4DBipDrHJQfbCaFPBoNU++zvMtrnS7LiFNWCsxQk5ofLYauX0am7qN6KIf8qoA
+lV1cwHw1BrOWRYOfPLZtQnCqBkgsmvwYhOA8/OGu+ie4QPBPPj6KLRRWguJewQ31rjAhGPoJPrZQ
+GEHMsBNYPPuoGbwuakeKng79ZuzMLFdLEU7X2IWyO5qwK4LUJfhXSORg2fapWLiOc+l/gjf+KQ3p
+ljTFixYjA+M+2w8tlDCTw++SyuWg7i1n3rbc8gZ80xjM8r1uif/Rq33aRUnZ7RrgzPOoEXd6g9jG
+GAyJNaiQt5TlOz27F1CKoEtCkrOtVmDeoG/JihuRFremnO9o+wpVhI1QVn2eoHDYihlO1ENYiYum
+Uw32I1PsgebZPaZ7sJeH9mbFJL7MVIcPFHQraB6I/sgL/6b2yiwqMYS9hTVTeSJ6mp/zahDbRgFA
+mdKhO5Ic3Shtax/Ty0B1KxrY7AqTQGipStfufFHoDRPJtGIY1x6o55ITiPdLRCH6uXZjQneII6kP
+Q99IzPzBiYBxR3MFgywwOJXRNqo5/zwViVozl5IXw5bxzcA4Gnzuo4N11yW4nxqOvBLDzDwsmg0g
+puVQWxzC50tMxzrYeDD2es2y/DXTDd+D0KpiQlq3oTy48XrTRc2cHpKi/JTJ9NBSda9BNYoELg2D
+2mQX9HiByUGLd1WSo2ro2wvArevJNh8FfOl+4tHxTYj/x8dJMp9SPMLIixdQ0Z4RsT8WythkgtYM
+c7C2ZVnrVcYgKopNO6RFXEuAMRxL18csI9NpSa33OUXSVYsBJ6iiSQbAQYrwfiIjUIakPjrQCd6Q
+mYKJeuGX254lPRQCvX+bhk3x2LfWXogp8b/+76b234FVgZScMfm/2tTq/Pnlxw3t20u+N4z8g8Ju
+gfscMGrA6TmW4R8NI1YoGINL/ju2iiX9e8MYkg8sCIRQQr4HUBV2QXQ4Z2hVYJIK8P5/sp/J910V
+9tNz40QUoQx/3nsnaa0RG1EjGgXVer/rgsI+1xk3aCnC5Dosvf6IwfC8Kj3aHOsRIgGGQniPojA/
+wo8viC1j8kHWM3tVHcgsLRXeRgRI4gMndDp6RZ2iN/Q41DssOVBkx4B3sTxzS68bULJDS+aIT9XR
+80pM5JQUEWjMSIVX2eVZ0BSPS/ZAGvqagCeJVKbqUPSYUZKqhFtd6BfTpjXYe8F2ydZZLoL7EqRi
+iUF8Wh7ChdYXppiXqzoQ1RcLikXMJecvc0bSHY7nrrCdextCPY1njVP9QPyRxZ03mphCubECybf4
+DGSmBKUbR02qUFcR3BLN6+iH457Cl+ARej+39+omXAlIV1ZtXd2YrGiQBJsOhzyYq73r5HRlPSkh
+2GdTGPU9fCOiopnsdVpO086DLunYaGeBKPdsAmsIvVQKZ+h7JNRFGjPyOwgq9WWfggpNEiCGXiWu
+Ca3H+7MI+g3RpN1Txh29qXyQFBtfqutMQqoEhQPs03iS3Y15RfaKzA85eF7XiJgPsHS0bG9xro9D
+lWSnMZX1Axg5/haqxjCCzBVUV13EXduCyt+a7DJNJfDENgug82icGO+w2leXwqQI/QOfdYF3Vdxb
+3j7xbE5ij87mC1+SrzM0QmBzq+kxJWZXpOxgLSnWmQmCm/Gs1spkXlyjA1dPFLSBE6Q+9BhWXbi3
+GA2/UhBtQJLrQDeD2IZBVBd6l/UC6kfkAwT5AkZauzVSV/t+QmNXpJ07VBBoX7qybndYyYEtBxLC
+1tojF4hXe4PjZUCewhxH9gOl7nqvag4lA60f3EsB9DgHYXTRMxjLQPzrJcJFqK41b4pLlS79VoEJ
+d08WJPHWpe1iDbbXY9Av82U5qwTa8NE/zQRtKUapSBsWo1uBuAJFSYBc04vKWTTnaWP6nZ8m4crW
+0EOXHv9qHfooKIiGdUvOivihneK0IdN+QNF2yZW41xQcLVWAiZtlQm6wh4mPqvDAECir8pkjDxTi
+vizMYsa9JEoKHazzDu1bu8zzZqk9aAln28QemOkrbht/TRfILzR4zRcVh40Eaa3Ylrlf7atFXNVT
+t0X4p4mEXMxFIhO6YrmM2YDx5zyZ7aLHCEKGqMsTSGbmGhOH5oWl8zagZXbUDL2VsX5xYyaebWBj
+0oF+RiIaFHTDA7SrJAHRWRJffioweQfS69fjTQD9wS2vzSfKqxdQadds6U99Lb7kY82vF1he74zX
+0Q0mpgkWn/M7Vh0kYxgsllBw3Lqe3sogm4F+AFJHkTnfaZWBQO2AnyTw9oqnrHpFyOxlly3Tmg+k
+jgNYVN42YD4/ppD8ASoolm1XcP9KNPkQN9DUH/0cKuymD+kapCTxNsgi2fCGhxedDfEwoYxeg7Ch
+7kKU1Gs6UYLFQ01xP45t3LBm2eA+hnwpmNEpwOpqetTgf+9DkcOgFnKSDQrx5jAJL4Pz5tjDGz6f
+91BhgpyB7Cf4Fix6QYxSslxLvbCNFiEaW9DXozmZp5XucLVnqAJitkC7FyCdcFso+Lh4CZplM1tU
+rRawWkR5+GLyIG3x2818Gjo/QBs9TAe/aJLHufaWeGwKcxqUGw9+O9WHunRyB7lb/eJYPRxRqfmx
+VIV/i4fcpFGWigQ9esszUMpceM+zBg4Kw1xC7g33NxQucCK67DUWvnWayXCTjzmU8wnXr5Oq7kPX
+wlxszrZeiQwhnIhdSWFpgA2DPY21d2N7dzln+ObQ7qZjVsfdODMN5IHnTx2Ga+uqlHmcz8OwgQwY
+Jg8gWc8RZBtsHXZpj6mzxfM/wI+ih/50O9TMv+5FCZEwJjQphDhenYwQIouTzZmNbQhBbBHSY77A
+RgQSrLt6Gacja7B3Qz+OqObU4xnEsu61kGGxc40OVkkyXqTwLcpD0EmK3PsP7s5jSXIkW7JfhBJw
+sgXgnASnG0hkRpSBczOQr3/Hq7tHuntmWuSJvM3MrhZZwdzdcE2v6tF5Cw6CPOVAWdfYTOvOklSn
+Ww4nuGNgPJ0Tq9vIimk3EOMDiZUXKGVjECq+AKyvdnlv6bjoQ5FUhOOVm9jRsNpJpI86rv6k32G6
+XMMV7sBnxgT/qLulOvHVo9JX+0SJj7Hg1C+zZ3ZDV7Mif6qxvKmw3m6GUdNDp0y0CCZXeu41PT/O
+TWEfPFgYEeQu0tJVYH0MVj7FeJCLA0+JfT0mLSFOrd8tpECcyFCKfPitW+59JmoAQHwZ77xqaU+N
+5o0/qKwaXrj59hhcuGQUVb0duLDHHiGBx8HNDMQ+ucHd+S5NdU3y6iSnfL0aleAak5o8Zku4FQSF
+aeVAENRBd3CozoZ+1JCvEF+JQc2AYRiF0T9HAuK5tWtK7qGGoSOh5hahoKIqYqzwmB7ZCc5+e2Z7
+KuBw5j8GzHl8FnXBX7EczP7JElN3bv0fb7amPzNvSa7dXPjhlDjmyRl7Wv3UBO00bppp/Fp5DP3k
+q+7H7ayX90aRtreAwdzxeMNv/HwrMn1GwrJYLy5FZd56lbuHReljvLSwPBA805gKp94JM+rLXzl6
+cLe3ybwbuho8rrlMO92sjXj10Rbl1OfRQuHQkwbS5FCRcq7oNV2SNLbS4ZkOEh7SnX/naw6e2srX
+XpfMW6O2YUQRevtTtvP83BKSjjRuwltplzy9LasKHjAov86euic6UYGdTK9j1m9d6RMStOS7MfYv
+Pde30KoL6wFdpdnWGDi2PPaCS51U3FoXvfTec2cow4axQjjF7zy1d1Yj9uuQnfAp76dxYmk62dx0
+Vrti1VZYTbURuHLKId80rBW3ht7tG0feL5r+SK7qNw+016lX3wOKXzeTPmmF6LaCFXPk5uBknGU1
+eO4yhSUpK3jXi5HISW0Oth4lAyAxa7G7K/UpmKRpmYqn2RtiilTllXw2LbCsLW8m3bzFuqpbzxy/
+/nlZcZyHuPLtDSN8fTAIHlp2etWbIjsRJNbiTBEb69YBQbjnvoWIu25tNTn3BnZwUlYkuhlgbwXL
+J8kLHXWlvLj50By1lIDc4Dhl6AzmEOutFRwTMxtjAzV7b2kKQ12vfeXE5PZLV5bnyV94RCedu0Hl
+RKYY3Dlu1tQ5D1Ni3DN+d0ffU8SWm0kcSTmdKm3uPmROClEBuAEPlaWIncstKTCO/iMB2PYuSAxj
+h1n/yy9rft6gbzcTT59w9txDp2VLNHTje+f2X51qqFcyIWPgati5Y5EfE93Q3pys8t8Jl2mbrEu1
+F5gFceXebvAEoCU8I6X9zFpSbZgo3QdgFSKa85oAR1D1bIy7ApNn1+25Wrh7oi4uf9RKnBOhtfee
+z0NKNLf0Yi3fWjIiWMD9/qPJGiMunO5GW3I7jYPHwtM/FcMWN27PeydLopQEFe7TQNu6HpWaq2M7
+O2KvyUu9pN2DLkyfZX+XPFp9a13dDGcqMxhba7Os33oBDseqJtYljrM8mtQoET0fy29UeG/XkTL9
+Ewd6spup9438jgma4iH7bBr2WoarVldfGfn9s6NWAjwGPLRToy/ZkxBMecTyu+x10EseGSXVQaZM
+xNUgR7ATVqVfDQAZsQQnE7rpMByStTLQUmrxSbrACBPTM+OJ/f233cngqvmt87rgKadsFTqOa8nh
+Ixg68VhAn3uCxGEeJwr+eOSxrOdPT9K95Saw4ROTR0Stebiy06bMcLv2TsrARqBApkgzGoC3q2ep
+JHKnrr7awzicsK54mzVJfqZ66o0b4sLd1uXC6Ia9ZosO5n8Ycw/hoK6sx2l1h808Gt1JDLnL/Ok6
++4XkxCdXVhjrlQh+2jGBOMUF8JAufnPniiy7Am3J9o49MpDbdXdsqFnjqWEH27nufCMys/tCm+qN
+FDeCQxYYRzIU8FHMICcW1d9VeooRbGbNobyxOvprgXzYmsGBfLx1xm1e/Mkv2lGZ0XqnwksR3cqx
+ScKpXP50kvX3WBXQQ+gSi9rJF4Si6JThu2ShrQTnZ1knp4Q1BmFeJkcjuJjtUgB+c1SEMJe9ZVq+
+xNNafjQAn6JbA+qlve2unDXfUom4RBidp9PNQJWGY/3TTfhr/Co4NWOwbJKetVC7dPlrmpps/70Z
+C3jKZy4uCf+GbpfWsZS9cbYZwUBgmfUL7Ar8FY2uXgW+pFDr9Kd8EcnWTrYEJ3aAb4pjUrEnnNzY
+ExOHy8JIDo5IE8ZyXZK1IxJBFNRa5rvcHn7x9sTtPlc5AA21xqTjaNcaO487t2vv+hURFpod4BbH
+4o1K7AAmXO7eSZqV1lS/Cs5P+hJN/TYbZNum07SNajXWh/aS7P28KvGnZP2DakuwCOnQ7dUQrBvN
+yas9T4r8aEBUQnut/Du5LvZuWD3odI64KM/SBd9LF8eMiBcZO9SzOC3Y6cZGkwwJFQvmm2kyPNnw
+6LoyD1XZlJDgWq2IGHz3aXOGXY3TRajpjJbnA4zQZvUEGa3+qBKTD48FGuJ3jydDo2GGdPUtvzjr
+ka7yh6o3tMfZdqqxOvT2LQ8ygl9jzHTUtamK+pqPufHJE7C/tlrJNTdlxwmYCWv/mhmziAwteJfW
+mryahrQ3nbpFAMds4X5a1SAs6r4wdm4VjDuvFe5jzzL6uIyuPDhL4zxas23vpDL7326fB+wgU5l9
+NFRj/J7BDpFsbvkwKg5P/jSk7DqjOYz8kPvAZMWlXLuIsuYWpjR7+5279ITZKKuexm6yr4VHI3BK
+5eVKmqa/s3hNH8zK5IdZ/fFVmNNPW+bmhptQdkx1ZdwtBv8l5ySI8EsrdAOnK8Oh1ow7nrbGprIV
+aZAkrcJl0c5aDpejKG2xJQSeAgXsoK2x5s3xujloPCvF8Ve9Dbwnr5y1TVABrkEkqS56pW/MfvXx
+XTucWArakruo4hj0FljnsXkmG/ZFcuSyLiQa8in7Lgo7P3hdf4HfZBGWmslbWPPbwOXH5zNMLn+5
+yGD5bLpaO2Z5mv7N0fY/vcz7f8gDg8wX/EdF8+47G9J/McH8/X/5+4rO+4ODDD3bd3Uf+fLWSPE3
+RdM3/rgt7mwHgS/wdRwv/0vRNFE0Wd0FgevpNlbVG3n0Hys6D3eMabj8P6QTb8bR/46kiaz2b6sr
+TmWfTCfZNN9Cbv33hEOm3I4Zd1x5NHFQRU3llDVrbE2/pF6Psdgbgq2km4u3pZNWG7Os2NG7dblN
+yrmDi5dzoQcNlcTKymD9JLd5xzRHT4Z+Mnn9zqyZ5megRl4YNOO8EcxbRlRnU3/E2Ny9r6RBYgLA
+5YEkXrqvirzfS1I2GzXIdM9Fpr7LEITHsBOjCmI8RQhJFd6ylKWFTSOhafd9fTD90j5lc5YEoWwh
+B+M60S5wv6DyUNPBh6wKZu0HDxxoUX8ygl9Z0PO50if/0jh5diRKqAN4KVbWB5g13wbdN+eNwenM
+Ud96ehP2Wa+YUizYnCqv81eAeR/TqmeXrM+eCaetkSMqdXByJsQb5uVkmySYkn50n9zVLi96lpu7
+WWnDRvdoUMxw0R1o0SSgq/QDy7ZyK5p63QT86TYAYtNI64D06XU6cRCaY1QE/sUn8XIySc0BQym+
+TXo+Q+k22WPiO/mhBk+wcTy1fM5r455TB1Mk91+tBpUPbK6EGWdZx6LJuFwP0DpxhcC5mrnsOf5J
+GzGsYNLTMOFxNt32KfOUV1xfPf/FEKt+D3BlfiToWwYHn1gMkmIOpK3gitmHfmUOX42XTt1hUo08
+gdow+1AHLnxHUBJ+VwVhRiFAsRQl/ArvDAJtmzJWkr1lUmxFcD8oYUI0Gj0bHAhRpOMwD3mUoNih
+NCV+h8QKkT/buvZgoZcX+ZUcpXnNlJZ/aphztskwYbLJNRLuTanKR3LU/ks7DrATRn8Gf1Wpu9Hw
+Sl7KQA1LaMMaGkOTe9STbzQp80lmmW/SmdzXpjVosGwZ7x4CnG13MC5VFZNybPbS8co9d/cJI4hU
+y9uom+JXRybsYeBOsbG0VHSbPGO6P0/8SmorS6PZOEvZJxGbvOyRkmmf2Geh38yo87ZyADSiKahm
+37VecwHDOW6FejJ77gwOtC9PS1+bCYmzoZb5ynzbHYzByz9mr5P3kH0w3toIVX5f342zwSJg4UpA
+g/BD0ZXWJefmsnXBvUYIgd0lKB0qr0vHgZgoF2xAU9+DP0TRYj/bwlhbNzLI+zXS2tmJbU2ffrw8
++RghX53zzqovUxfMB9GCsECe87itcJs8NwtVvPU68Bz3IZvfUWnG8ri+rd8kyaVka05G5kW9nnkP
+dVYOr0bRp/Aq0tK7DABF32cE+ooxsyUq7/mNe3Jakm8HLgwkZWtYvNlGV5a/fNoUj1pPg99N8YC1
+/LsMpoa9M5g3t2XvB64d8biTmfGmCZqtDmnuORDKhfIhUljo478tN0mCc90Q/mOwszJeCvCU4SQ9
+v2KK5stHuqGWlxSXf+zIsXozzNmujkS/OuT+osgjCFQy32aSYzq87bKKjefI8i3L5mkng15zIg77
+V9kF09mwxuGqTXr9UrLT8SP8Ph4jVznr356Xe1SbJ4BzWJVvVaolWzXm+NZqkot3rD2WX/WQGB8E
+/8rI60dnP984TbBcxNbPx/Z5ykxjiEp9BVASlSxYvoUaG2zRbvKTE3/dF55cv/sJNkpt6nxhA8Sq
+AEyw2uyuBWDeZ64Nt0nRG3wB9K/x58cF2JLaeMMwA1Ds+KcHkQPNGus+mdgaEZ3eJybr6Ju6V5WX
+uvJa84B1SHKvNbMJOzTEmGfyu2bFKHkjD7DqpcBz8O2blO2A4sHdFxSX2Wk0Hi8CErKR4gZZpUEA
+s02a3RI0a0TjMi9lKe7KoSrPPdAO1iTzPIdwh9hm8eAJq2loj+hCK+azwJ12yzxXF8BL04sDQ+o8
+Yva/EcfN9lP2/DoRhWy3KQ2mgRN7suOGpmn+uoUQZgUIf1xd94UADxEhfy+/dbvLmRuLJfiVdhrL
+pTbPEKVbL12hSAFPgpngrZa54UKzLJGdOfZtpdKUj4PnDSaSa+6lp8S10owdghQBT7CmztDK9f5E
+ORVBfwRum7C9aU8X9Fx4W47Lp4Aly6lZSpbtCYv6UMvRLEl9MohP6fjozXLcDmWvf3Xj+mgrbDcs
+MBL5pM8FAW+SzpqOnbL3MH7VCrefuRbuVy/QoWDcze5bLx3J2Oq2udjDjFDpRnbu6oZDSoKcMxsl
+H9fn8iOoEHtxjHF6GhFgi5guhPHJtXCdkYpEm9ZM+9EYOvtNG4LqxIFtHwdHa0Inh5o7TctlpXZw
+jqSLlOY7xXkN1qM58oENQYWs31UJ6Y8Hjr1AGljhiV6zFDAHlr7AJWmJsrtsh37S6p1d2tafrIIx
+hbcaANEHS+jpi5OSKuWr6/6pgI4ldpDurJd8zjnvPN0d2yNZ6LHf9ISf7zSSBklIuWDw1pZBtTfq
+HAhBYeudtXc0g+t9Aj5m5krBvAYasC+cmBIoXmjQF3l1N8wqHTe+GsqPLin0ux6wGUqWJV11k9pr
+ZoiAFK/ulfIDBAdEORNwTyMSIshCOMMTyrT2dfMPmZEjBy/j5i44aPQqtaO0NG9hTrZvd/zW3TFJ
+NX3Yu60OdBUKzfAzlKluxZWYBKWffmB7+4bO6Rtg2wIU5mtdBkJRTzmw6X3ThigfqwlTg96uEF9G
+dwqFY7TfGDYcUJi1aohjdxZb26n77et6uW/xxv6WNttj/I8J2FeQf84Q8WRayT6goJAW0sUHSmF/
+xmCp3rSsJB4NVSi/KKN58afOMRErM9Zonuc5J/SsfJNXKpdxWtXfum0mPMqwZ641aPG+K3jNlXTl
+dS5a4oGpXo1hAjCEMyXHnlNiF162dSG7+zwD9RpqyagZED3zFPBt18mP7Fbei3JLBGkr8E++L2ll
+lmFBA4jAbWaLk4aM/QJ2Pv0hZmbxkYam2ACMaFYjItvNW28WVRevQAs7TmXJeqwbbDdCH0GCT0jo
+R0rK5FV1PVdxK+13PSuwENWojaCfrBsy2DsG0j0tcDffJ/0mWxt9ErvvikpRzGNztPypCaeqtjc6
+MIA0zqpieJsyMMm2GOeI5z7nCVtJojL4B/ajKNtzo8T0DKJ8Qi8kW2MZ9vwRdG5ZRkOvd79EXxHQ
+WdPU4tJLs0eiNvhB1480cX9UltxYl7og/mgq4EV0mELYWXwURtm4DWIwlYas5NN1t4AduDm7ev2d
+JeSsv0HH10imzJZzbykCxWs25D3LobLs9mJsSzqFA2l2HLR18atlZ0mIhwOCXHCDV9z1Uw16RBO0
++57HBR3ooBlmdv+PTZBNr8k4d6Ezlea0Q1MOpZbWJ2V6qPLYwlIgXkOFbbava6sC8x9Mz35R1n0I
++YXAj1dUvzyDIcHMCtuJK1VoP72tsfnxTZevPfv9AyeQbkZSt1oyMEUz3OvtFJxt3RBajG8yuC/y
+un/SDWDTu8QtSnAJS919ArHGnzu0OXsEBrTlw/fn9rdka0gSbKw7DLa6xWCY1SlhF1cOz46hrLO0
+LfO+mo3hBVZO0W6sFj5LaAl34TkrWKKpTAt2NlCjPe8eyLcVUf9ve1wCYuNrFpwwL1bQHBoPmSfv
+J8xV+mLVKs5ZPIWmjuGiLCsb0uPgiXeUTjdaeKuAHZIlL+DYABaMGNmMrwCQ7tGA43iZzKqBoenf
+RjA1CuaBiqImhgOLwl1mwgFpaBnOVLX3+JuBc8DfNhM92KW1XeG8n/KvnHTOBaBybsXoBvWGv5ne
+RMrP5kiNRloA/67BW9CKAycuVyc+rHZEg4QWqdYyjoaVzSHbPhC7jpw2nKp1nHqaacTseyEyGG6O
+OC3WRbzkogy+BbRpXvTULX7N0snPfesEeM5g/VWhGnrjlyUzHJQ6q0ZaPswtBkSgt3bdblj1n/oE
+8ne3FjnLiBRCWb7W943n5mYEvBaO6QBhPgRFiKEEYwz8je4rKLHoNYR4P7MiXX/NZVeVuMYWcVmC
+Ov/Vmk0dr3MpnihCKd7NpNKfsJ5z//N4hlwVOve0M416GCMsayN6GjY2WCo6uitLIYyAfCw2czWN
+N5DFnhUFpaT1E/z20mSHui4PgWfAyrWx2scSM9NpEfDWIgkG7HVIrXQ/rwwXce+WMEL7eki/Xatl
+WGwSf9M5XrWr4VrhJazq9CTGQN67t7xVyQvwHDiqfOK86M7C4tdgMoIIpeAihbjQGe/XRT3DDjq6
+vKAJ168PL+e0nQNbPBH2e/knQ9f/wU/6v3lvyZaiIxhYfm0vwPr7r+691nEmD4vgumOpAt7V92wV
+zg28GjBimBLLIKm///N3/Nc0uIdy4rJywuEVEIzD5/Vv/lXf4qW0WpiARPzzh3ZaxysQHnaDeJmO
+GdXfO6Oe0/g/f9MbO+CfTYr4SHQKKED5kHI1jVtK6Z9NimZmUEHiFfMOmkd5Zq4Z7wVUvZg8Qvrc
+rj2sm2XBkTBN3c9f3/l/WmT7/y6Oxkl3q1z9v5sLH79yYtjpV/0v/sK//V9/9xf6f5ie6wX2X8oZ
+Wex/iHFu8AexYI5SMlrcR/6S6f5hL9T/MAyTfHbANf+WVUPB+7sYZ1p/oOyh01FCovuG7jj/HTHO
+d3He/8t7ik/N7cPj87HxeGf9e2y6Ie+icRUftjrI7nKnUWyTXMzSYfEK9sw94H6F+s40Ori7IM/p
+a+gw+9ZxxR7/CvhEQ+cyhX8yVWGBvputs9sFBEswHfTcIaEMrfDIHHy9uaxMeQ6qeSu93FIYzD3o
+ektvYYpTql3pD3S0KZKZnVwkvXk900vtHtIAt/BGyqrChbvkxceazfPEnpYW6Q3JLe5sRVOpIdLr
+RJwJGbu/LAa2jfCCCfEr8O/XAgpYp/napmrXIgpwGm7aThaPymy734qOjK8F6mL1opeJ+6sqxvqd
+jLLosS2C2mWHlKTpVtiDwFbo5W+lX0GH6nQTozlMwgIco6rmp0HX5Y5ay9486+gkH8vSUre+LvOH
+5VMbE0613l4zPJN6XNVGrkK3Hlcs+aaZ6nE5ajBVXeQtqtmqDBVO9Qb8JgHY6I4dCA0PiyGDjxYK
+pfjSa5+ZNWsWjRYcIg1cXlAkr65tOJTcwK/nDE4NBrEAyX0YrHLkiyq5xhq9K9bJV8uAB53B2Dg0
+Rt1H9m3FK+XI2G2O48AvwOqgDfW5r0gt86CCYMttKrfbe6xy9ndqGPMLhGWdwYpVFpWYPLyPbbFC
+e4X2OW+ScmpfsZiXO7WirTDXS1Jw9dIxMOirdF5TKcbXrmshwHdrQPSrW+3m0XBF3m34CeZXNY3l
+fd126UNhMBZu4ZAH+zQbB8JXs3jPxXxTWUwHr12c1XK2Yh/l4Q0HmOqPLiwLkJzZrBlbJr/F3Gu2
+yr+cAe8+kjAEqZPBIMS4hyWW18yAX4o3U38eOsUImvgw1UL2tCTMW/Y3STguHhJwwNboVRI6XSNZ
+TvMHAQz/TG4toBAkAEW8UTwPqTILKOtiK+lC3CQIV1u7qWp6jBET9pfN2MG9j3WgfTsg/vKMmGXe
+zFT+S5EPjM0Fe0dWMUMFaRtC6T3xUKt8hDZKnhma2z7rXOveSNfxNCudO0I5kE0ODcOvP2pA/ycP
+cojGaq53f7ej7sVGjfdky71tPGbJ4lLLMFt0RTn1tAnqxv0IRE44pTIyAzec1EQbs6kPJqBCZrl1
+O7M/+NY85lv8PxQ/NbqEXkBCmoXqNIpHezUDGdKdE7zrU9a9UUnn/3KVb59Iuo5c2DS+eD4tRWQ3
+/ptUmV9GwE6xMYyG/eU5GU4+YZMQQLuY6EiiSkPedfUKtbGQ0j72yqaDYQV/lm9xC8h3hyzgrzQX
+2DtK1vXlruccyLdmsUprXywmeC/h0k8VEoi0ZMjkjSLStWJyoibz0O5TEkgqmt2gTaPZkQKDawE7
+HeMsSy26smwjBkvZk6bxmXVCJqFbnkQfF5/9a1AQCucNS1mGln0VgLeSvRmk5Tf2K2ObB8Iiq0nN
+AwHGIf3du25z9bzW2c26voLulS6x0MSyf/eyohZp8Vz7NK9gGq+Cre+ntpLay2t7iAxKa84+N8sX
+3lFwCquAd2Xdr82Wh8nyUcilvHbC1ycEThzd+KmFuUM4qUlseOp33qO2eWIAl44VA4T0zOglcwNY
+NtA05Z5F6a5PHDZO9YzGn3z5ueZfTTKEfANWeVTEtMV7RlKelcroex6kv0p76/RZXgsV6NhhsdqG
+fg76hvtUV3oEX8VZ183me7S64Bbqy0x95xOJ8l+hKOZQ+PXK0rZ42BdvZ9ND0G8m29GHaKwRtC69
+t4x7D+TNs58YAH2NSSJ24DWI7WEY680AUvxkOdmnGI1qb5UZXgOzlV/lLNsnOSmbtCb3FAf+45PN
+cUZztI2oGNGjhfgpgtLcyGVVX2gmlrvPZqu+x5zLwkAxp2I+Hp2DV3br+0gjWbsxmsnfGK3V1Ps+
+Ge3sSber2eHfJtkrxp9VD2Xql1t0eutQzCYw58JeWQWbE7BfLIXeHdqZ9XlDDN+bi9GAcpjlaylm
+P7uvUvzc/PAC14AFP/IzhyS9R+OcrUhObfbtIl9FadY3PlBPpG8a7YCUPwtNKhARmclSoKq6T6e3
+wTiPwwCmN8mFjLifAlPI5sTBrtt4INkVykHoqAUh2lmTe9mrVd94GUHs2B89Ti1bM1g7wcXmwU2D
+pL7iTzCrAGR2kNAwEHjziSYGKjSkSgH1yDRsDV9tWnY/RHdG+QG8a0pCQVdSiuZKApuaEhY6qM2k
+lh32wXdj5z7K0ptjWsXeGoHomgicV2nOlaXJnOSUWT3tBfNgf89prh9EGviR6aCQjKpdYnvJPgtS
+ImHSeT/OnP0aha3tjKxs4jERFb5Q3KMg9cRsv40F3odN03IScx8cAnTIBtTHweYKDuMQbbU90N2M
+NohmSCWRRUkHPnCAEMgxyGjrdkbzncM59b+bpmvS0DRG4zVtfW0NW33MnP1UlP58RbKov6HvUg0w
+KUYdOy2r8eaqaM42lRvAZvSbrJtrG1N1Ge8VXKBcufzY4wMxxKWV5Qda5/RNCtP6sXCMcuuopIwT
+FRS/EVvMP/0sGT9K34Jlvy7DL60D243Lx87iCbg+YGAnca9whxHug6k2MPSC+ofVWBcuSd5G017s
+NCvB0NO12EQ+slYdw21W67W7LdI2FW8YEVfgNZaNSEbL2KhezIc206xrZ9xUORDtAvHKkBZqAHaP
+Q7Baw49/CwZWFCbx3vHb8lBVQ2BFnAjK29LW49+tawnGda374DKtbXDWR5M76WgAjarawTo6fa8V
+YYK0yeV3BGlFodLyqZvemIO8HBHFCWJAJZHomN4OX0OF/09HSjoI7qi7anGQTAv+yhejh3ITysLy
+3NCc3WNRse3iQo3TpHHN4ZUhinVjERjm76Fb+ncJ0PdYVo6fxrXp01PCQ2m+CsJ5PEmIxmjocA6c
+0MEy8jvpGWkaUo0yxq0Lkz82irF3z7ghqoPTGz4qMofddqKTi6cfS6mSx+pfoX80kItT8jGNZnJF
+UHFLfHfB2rwCnfA8VIGsOfiahz9z6mS+rzF8P5DwFg0BdbNfNjLjS56xai/ZXW8k4jLnQ0+0xhyY
+X9ygezDbyn1Mht5j8W26I2ZkteKqrSRQBA1cNr+zVUp9q4Y87rEiQeFJWbdpDKYPDnDgk0z481A4
+Z6xpyDHu0GTAVMyRAWGbbVNddBs/tf3qTTh580NQ08weC4Qk/sl0m47ytF1bDO9j+cWgkDwuambx
+6LftoIeUMS0rH5sAR3NRZV7N1iLH5cQBvYyYhdPxtaCKnI0Sz+g72SzJqZZKbfgI9D+VdIzHqVDp
+EBttUD6k66y9mDAWXk2qs3amCoIfaSn9hT6w6QTxQvtY9ASMQkLl1cPU5GBfdINxwe5G04ZCM+Q7
+lFCE36nS/YNei+WtyRY2DpJnzBtJsHaMbdD6FYcALW27BmssxTd07gyRsFAgmZR1LNg6FnifOjFo
+n3usvxWYc8W2ulGpdcgG0y23nY4HDSn/rx1vmnbLLsGvnh3X0S1OjrQJm0rboFgmy0voRjIogz8V
+9t7fQ49HkGiyrM3NwF3q1c6XlN7FdJp7Y6ezAdQi3r2pfcSqwN7V0nLISM46TQpwdN0E2lfTD95+
+oTPGb+JgLdnKp3UOv5EsItedGANG47/j2DX8R6dhLtnRFGLSwVLMhuPRUiC/nBoIxSLcfDtRc4iJ
+r6Sv07QbWkNq2z1YfJ54Y64sQs4pWw5WIJatrCsrdAZWi4JQkqDOs87zZj0WyZI8gKPtyvuSWsaa
+UkkqQ81zaRN72aUEbMpN5Qu5AT2mu1ZkVUpxUymxbOBIr9Ou6y7p2jAetfQyklIz2sq+jjl9ZEfH
+GFR650+eZD2eJcm0zwccu7Ny6ge2252Gj4KZ5HnBCLfugm5xrO0wr2l2wN2f5e8YTftqz0qdxE1b
+gOn/rNZF/wqyvHBvUQwn+SxcUSf4/4ThMSSNViJ43ScW4+iDA2NmP3dZBN6YVudYLKb+aVEcMUb9
+2E/0BCStGSeZswRnHt/dtC98Qx5tKOT9xoRWv290E/oDQjwxpsSdn9J6rKrDkrm5vk3xwvow96TI
+L43tTV6E/bQZYYaZw7bTUkWRo5jcHbXyQXKEITKzm8JeQcFenYCgqju5dGaYjaZOYq9xq2IDkr8c
+PuaCcbvt5qW6lLcIPiYPfBoI6KiG7bHW6yXYs+K5CXdO5aWvPKTc4WDPY82Yo0/TGYs1ViJAUYOq
+XgD5wxg2+Aw3D0KOS1y7LdYS3Lws6PTBVfd5FwQfNB05dkgVROvFA78OFdV9tqx7Q7AxP6UaZl1K
+0BzPxrLrjVvP7DsXU1+vndhYfAQ5nuWwM1pxD1+EZ6KdtJ+aNePdZPVMFaB4pOsL7lefFQNvngCd
+P1wtle8KSL5sPRJY6CYrqVsvopb8SfZNMw8GtgKNSPSEj2cs0+X3InrLQi0zcPwSYxuOHXyXJzj2
+bkQNl8Xz3yEeqKxOs4Hjlo+SFp4hBl9enMTMJ5aphfBvnFAK41KAIP6LvTPpjttIs/Yvgg+mCADL
+zkTOJJMzKW1wSJEKzDMCw6/vJ+X6vpJsH/vUpnvTO1fZVIqZSOCN9977XP3eef6QM737tDlVsi0u
+ISDONfuka9kQd0AXnzvlKD4P/2JPzpGvzvTn5vY1WU2tQn6aHgaSg9R2NmkFZKOiT9BaI5pc5PPS
++2i49VMiQ4frU4eMwtcLmPdbYcjyYHS5QZuhB2y5zrth3ReLJVe5Em0eLoUAWAUO6J7YhrsD6liA
+5ZnN5d2xeDvkKFsWvFP/yDsf7F2KgPj5ysNGMi7doTbL6U11ILTmOelfgHj16c5KLfuoHYtGYlxV
+BE19lrwq0169zpCMzLVXWTQ5jVrUZlg2qZHfBMOAqWRxMN5uAdVMz43KghNw5JlewowQByn9aGyw
+4vZB2LURVXSgj1HgliQ1NZQ3P+KO3dCZ8z+73bysUb/9BLH811r1fx02Ccvq73aXj21SD+0vPsIf
+jMofP/b78jKwAUXaknTODyPhT9vLwPrNEiapZArvpIWM8G+alu3+JoSUuJTwHvrSubAp/t/2Eial
+HZik7J1LetCEPvgfpKPdP1oJ+R4R3cKJTnTfZvwxL1bDn8ivdZkZVE1aw54eonk9ZOilBqm4QqOz
+WMH06tPMt9K4ftaiy+bdUvWfk22/pL7/SvTGvI9gnm9EM370pHNWWV8Mm36SQwgQnfxO35QPIDO6
+k6dVio4D03DRcIcowbiT+JvDEU/gvuxINCtV33h1RrlaQk8z3uFXlMmG2M58X7nmZ1ETSJrLjFYA
+ZO4ygOC8ZMaHq5wbnuv2CmNK8zWuyFBRfDnte9b4OBiciFdV+mvS5XsDm2Cbp5d7F2WGDOHqVvFd
+JRQijI0JnGplOWlJWMpzTj3wp2Nt1DjyeDZMGEhcslZmPj9HgXo0k+xtjFtoPj1FZZqJ7RpPnNhg
++oCKVbHoossZ2qPtDvfFzD21zdyrGoLTwc7EsF2iuSI9GzDHN1ZCOs7D1TWuUmEN31lR3lwmiY3V
+Ot4dS2+4gHW8iZsu282dKNal0ZTXHne2NfGdiEWtMvbSbb1j3Nk1OlRjs1cKvAOqSn00cyXfezl/
+bbnzMyksDf44Fr12kPNPbEbfBxkY15HEzRiMNTTAfkxDRiD3ekGsR7aqPlPcJDsjaLxza6bBdlQO
+szt3rhUrFn+deZ67oS4W+HnA2qMhuHbvd8sHwhv9ZNnUnEfK51+dan7lvBOzTmBI6YLUXBWdeeU2
+2YBbAZmdpjJKW3T+PSn9bO9Vwdegz4knaP7zpc/pYRktssO6MI8ohlwAqM17s27jU+Llj4mUj3Ss
+pkef5lkKR6fksYvw/2MRzzYg7RWWOpXfjz29lxZi9HrJAmczJjHbk9p98uDrbzxliOshbV64XoPP
+iTqKDTbM4maxKyJBPTZaXXePWE4e45lobYXiaS7dc0p9eKhNHbAOdgAcGu6XHK75Pu27e0vU0ybr
+OWggo3YUTlb9s3k5wQvp32N7e1ym9Ja4N9cs3/e1jl0cPZrxZBVoVN5p6lR0nTp2Q1R5oWesjJJL
+onlu61tXTmxZhGGEcZvlZ0yV+aZy1XgoEgsMK9fgmbIYfYxIVVMnzmySxzG3s4Ba+r6mOiGNcKHk
+JF5w5KX3pGh8uqlIemEiebZUNz0U1IseR7i5e6tXqKWufLJM3LBZootnik+SNR8VjbpiJuGdpT0I
+rcGIvpDIv9gb7OaKVbM6LhRfc4rWnsu0zWY/HKL2kw0D/Lqq5LE5LcGNLNzpjnU0CRJAaZtpHDAj
+dJJDgu+czTbqQgYdTP7BmNyNlJuv5tofzma60NxmSIIvzF9JD45Sjl61RwvHkFgv1h0LFpZ2Bj7i
+OZ4qRN+gXptd5K21JD6X9eOlPKP2k71NEStDdQ7vlLCeJNdjDC9zF8inQQ3evvHn6AUdmsw/6gWb
+BjPdYW+OD6nXzKeGHexTkNTIuBWbZRYni32f4+m5ISLGgTvI0xeABy+smgnyUpaiOlXu6266rXtt
+f+ra0vfJKMfQSDpSmxg5YN5N1XLEnrHykG7eE6T5Tyogi7OHNnsMZjnuMWSzZIpqsTa8PNtai3rx
+3by+MVqfHp/ChtUAbdUMmG0LEymJ9QdyOhvvyOabe+nKKC5+wFrH3onzW3o7LlF9FVl9eo5x6KxZ
+U9OkmuhdQZHHSwnpjl1Q0d4A8RtIpyHB4NdkDcIycq3TJX3SAX8NeqCX+yhe7iaBNdSmTz2s5jE5
+1Olwx3PIOIBjaLbCFOod3gHDbG48qqkxN4vDCaqyy/5cZb4IfX+BnFH6A5uGBEUKRhDY0+pOpObF
+8QsmqLU8ml89zyYp4Uch0cnZ49ql4NsQxhD2RiM4SPjQ6NqsvZqM/gKHbDyAaTn8I8/hLpxcWvDI
+JQWSHiQ3CEjKyG+J7c9sA0cckAEuAvxYzibTKdv8oVsgF7HQLqKMYbyMnmmZ56l4+Tug9jkblYzB
+mjSU/eJrvs25sCWrIRpws4y6kDVil9uxWlDju4EpGisuSbRHu/a/kx66cBMuLNa9j+y0Afd1xjkb
+QAqkGS1MwVLc2yPqATgJg91biqHQqq89U6bPNUo3SAWBGLHEz8h9O+bzPGQl2ZZraQRflkVilwzq
+j2rigpJd/qibjNb5aR7DMjdvFr1cFxz1cA/L9KnrW/swGEYAF4NPGk9XtHUweeMW59bTB+VHaS/v
+g1d91Z5NI5axOIT8WXDhPkVRE1mZHKdI3SYxeRbfVPjYHPuO7CT7w0jjpCi1zZDecbRZypJ0s0cX
+ic7aR4b6Plw61ZDN7FlQT9WbaXAX4hiGsyuCZSDeZ+jSHIs+iqEUa+jJ5TpxxO+2hP/T6R//nq1u
+W+7fjrr/1XVvxS8S/Y8f+NeQK38zLccmEOMwR/6MjPWD3zy+dS5CDC5MuLI/5WW834jKCMRzyQ9f
+4iz/HnLd3xDvBZcuVWHCwSn2nwy5v+dh/m378N0fFhMBt+XSF8Zr4SD4ecitYm80Y7q+99ybOCOZ
+MEqtzWBFsFTNahjKtV8t+S07YzZHQeD45Vqruedu0aeU/8S9p3ELUs/Vhsy/1rbEL8jeBk222k/G
+ECU7Ui3G3g9avbEty72UAGCiAeCVHF2BAWylhsvtOtDJQZb0Couyu3WT0r4LOkveKHtG4LWN8mqy
+g+TAQ3+6Hmz3wXdrsFeemHcm0QYi+nZ/nXbelkYiCJdjuhHSOXrInF49DOHSjsuapFmJAk1fxtL6
+1dabM/ZXGRBURwwIjk1wTTTZuiHQonbuEn8trSQ5zWy+wpQONIjcBIcq4XzUgQ0+TgOpLlDnszrx
+EUp4BpOemw9pXfV3SxCMxywx4w+cjiC3Z6s7llb/5k2GT+bXbLdgZi7AI17TT+QnI4DF02P6WIZB
+bM1phiKeGjeSe3KVLu9BEx8M5YRIOy8TLm/WX1eul4b9PBwL19olMaEaGuKMb8ig4zaanI88r3ed
+y00no1IUk11FiNp5VEGs0UXSBS4eENoC9iVTNp4DyEQEz71XVkVXKRtoPE7h2I3ALIYJ5KBqfO5L
+hj5ZI1tGu7GORVHNuzlxdxNcDKDh/W3W1hctdeoKzKAF96LaBaML9I4nh3m3gGU+swOz1zkgu6+U
+yVKcWEmtvrGqihBsJv4EtJ1daY0ImO1g7PIBvkFRKO/kTHL+3gY9xbmUw7MaZe12ymraits4O5tW
+nXx32xEN49ITjkMSz0iHCiSSvP+osyFbY864p5blCFu3WFvKyi5ZbuQjOxqj/Zz7t1nFgDXK5d6P
+q7vMM3eGGr3bpUjGA0a05JQ0PTYVM4vs20BXTcgW7hu70GnrG/lXXNP6GsrCwbBzxDttd9m95w1i
+Q2o2PaFbaEwt/tZJ63FTXhoPK7ecT33mnS3DFfc92WzryvOAXdCvVFpNWM4GoQ0Kc4th2xf5kFBo
+OCpj4wU582Kq+WXDvHb53qXyIqZLYp85RB8MfkygdMGvDSO171n+wiZPnaLTIU2Al+OhRINbDyy3
+yMbgv1AbVkozlAa2mBencBV5IX0KI/aW1HKpiDIQd1elarW6IkdV9PuBAs1+HdtkjwD2U8/6YpBv
+S8i+g79YwqzwYR54l8OPrf1S39Bq2M97v8zamQBrnI9bfxJ4b1XZtv5DYTeiOmQiNyqKHJMl4HVT
+GB3I2zn12LaRSlZc0Y8mOfbKmxmQXrFWmv7vXexQkgJupBlhJthmEm+jwvC7j4pDc7GuLD+g+7Ka
+0dmwvQpEIPbz5cg3JiCScgsHwJ/DNAI6tKI8NK7IgIy5SV+WUTAapBNWDkHQmFxFRui4pjt2hVuA
+LBEu7Cw1L0lhn69CgsyBrbR46MAEfY5RU7n0GeGQW2dpYmW3skqLdLsMbulvil536ibOSj59l7DY
+TukJuLIdZViZ8FAt2FRhIyArDLFnHWTT9vm3pjWGZBuwf87WduFH0Gm0tbyVAXXzyL7xfVAiu6ID
+8YJDnYUI2GS4yppQ1mGOJmgjDS3NNKoeJVorG+iE8uzA7d9G6nhcDj5Tcz1UHSJpzNLwUNDJ8OYL
+xseYMcSU3WPae49xz66jTKewKxs8xWJstguMtTsnhcM2JIrinbLsH1zPoxtDd/4XqstbFK7eXb5a
+5vIxyiEKW3MonykDDuugDEFxXNJzuj9J/tx2JXvTEghu06gL6ESMdqC2It5RPVMKLxUNVaucIR0O
+ZW5tjHiKhp0a654iWI98zMamApEAPlOe7qnmpk2n6R9SljDOfZQ3OtrmHlaeaejkqbMvZvm57c3p
+XuQJTYwkjYhAmnkWP+RIcx8stukoHZMCYovfusljS+pAf1UV5vrjYk3esoVJ1EnyL3QOJhm5pHF6
+R2CGXSy5lnGqKwoYSDMuYCvI/LVTp297lkBn1yjVWmMqufad4W6mKvMQxTK9wzk3EIJZyidjMb0r
+I8inL90k6rvaMAPkgTkIHrsln+/mqC3yWx1U1XvpCLGHijkeIl14xooFZvEG7+1CwCQ1hqU3OE99
+oRtqQVP/HS7G8JInWdqEFGwkMPngE2WMio7/3c8XSDjzMH6PYo3WkAQVm4POaGhT9Iy5XduOjBlj
+KzNlC+FLskupARgg01reY/SSL0BCOPjphOqRgNhAfmWVDTkHkBwbowzax0phk8G2RKWlTSDuu/aM
+8XVs7KEOGxc+ghQFbDSL4ylY2GlpzlSSOdc0TxgIC1ntPhqp0xRXJfzsbJ9Zlcv5ITE0bmkz9l+9
+Sjn+Ou2CaZcSuLLxaGXuR2W0+o7WBv/RpAj6qkz6xDq1feQ95a0lvi7Dpe9+5q66AmKkXqU2zDt7
+shTw6Tmf6HfE1+zjvtxH1B8TYRXWKVZ2f9AuZeorjEVlyOmTZbpHjWu29Vts1euFjSFrwmDpnqaY
+gy7GGrL8E3aZYSVVvpBkNxJE9kUV5chdssnnVWsGJWb/Zc43MdiKY9dTor5dHKcTd22q89eiU1x0
+FREbovlaw46zqdJOj4AJnOXgI5dGB6oGjXZPPpvnH+4dWd5pYRvzWcgotu8Mwi0zruUUYr0RcXxE
+ivbo9qyBZl/STbnKVpguOdslvpWNO6Rroa6S0pDzWpejvrOAtqmjWy/CvCIsuVD4SDWgv6676j6o
+Jqoul9SYB3aeiaifIypFpgIjeZqTj7ADx9yUGV/5II4DiG1SX2csfXdj3wSP0VTIO/pHR5h7Efd9
+mErJHg3H2QfCn8LaTnDYpXZxxnhe7H2ifTvtIqCDNwcgY6TdctVFrt+vys5B4WEXwP4ub+qRC0K3
+3yZfNhxW54rxAboF9eVJiAXynqAQgMMuiTa9NEnR5bV+RVFrTkWa4OiHjbPOuhFulllL9egKFasN
+003JJ1xNhwXfS33VVpWf7TDYpsFeIsnzsda9cDgkExS8te3cPPud51znRuw8uSOpkV2eAMxdV+SX
+JzompczCmkDWwfAjB+KjTviYaaRUm2AehocJHld9sGY/O8YUlHzwmONmGbUjZSuULjpqnydmtLE4
+f7zVFsCR2YVNhdnxtvEsyFJEOtGv6pwoyiKuqrb2qYwVp2bhSE4E+5EcagYIBfrJaIjljQdG+qA8
+O/+oh1rvmqyxGsw7BtUwPQCNFUeZ5kMpghtVJaKDovphT504D6h6ipHjYYCkFtkgx902jmcOlPRe
+9nPjj10dLTbsAcHskU2dpuWcueQYUPSrb3U3f+tpZ2CzZSUFewLTFjQlOxjrQ4v9S/oPdGvszT+Z
+kv984rn4/X9a6zuoa2ZV9dOBHQVFoo7oiO5TQfr4k9zxF7GBv3oZH/lAumRgPVv8ITagl6KsqHAf
+D97UkouikyNFbW8w1P396/zq27/8OpfP18IAbnIi5H/++utYgWH3fiCGwzKUw1t6ecLLfuFEoHAw
+YkM0suQz17TIrcDv2P+ICv81HfH7y0PQ9kA+eJxu//hrkijBqdg6/cFFENrGl0HA9gu5dS/DgR67
+/M5vnGabVS7WwrkCWsg0wQr3cWG6cH+MGfBw8svgUUrm/mW6nTxSdRJbG1t6er1rktmXRbExJvm5
+a1tuVZW3RORXY+zZIvgHWvOffyFOwqbHkd0kQijF5f3+6fJYYICRqR/qS2SMrocmQ9lf6SoZzQ3x
+yIBnvMI8dfj7D/HPL+qYIDBw0jKZSrZTv75oG7GM1lnQ8aJquXJoB8mK/gvAIhqh5gaV7f+HCP7i
+yrwc6X898vNilklxmsWfBN/91xdTgWOXF5/5YaQ4dsPm+WPKjG1hTv0//FZ//goA6mcM8dn0oaSJ
+y7//6a20i84ib5mUhwR3fn92rRrqoiotMez//jey/uL9oxeWUyRjog2v6g8fmsrItYpF5BByLHmK
+B0YKAvfxxTYaOEOYwUDGm0LHMIv0eOzOGYt095bmAFQaRr7hx/THulmFfQttcz/9mA/bH7Pi3/9V
+//SekL3g0gpY7PC2oFT++p4o4t499svkkFGH5h1Y1/e3UzVxWPqPX4c1qPgdugJn+g/vPVgpeGFq
+iFFGOAyErWeXECeiPP+9BOj/loL/sBS0UIR/+kQucvwvZYv/VX7EtC3etm8fn13883bw95/8fTvo
+u795aNnsAQW3cB4XXA7j54+CRVotaB10YOwT4eA/4pL/V4DHCn6zJKEabvxMSZfMz78EcMv+TV6K
+MFgPCh475n+E0vlDRzApNF7CovWQpBB3QUDhv16prMMNbQ1pj79fjd1DPPj+4+IZZR0KSARnVB6/
+Cw2LwvvSRENyzT7d5D1n5p/etr+4W+ESukTP/n3DInVnoWddIkSCHSrtgn94xJlCy8SYAxvLKCA7
+zFVDGMkgOmg2TY9DlgRXk8Thg+OziKqJWMWAlS4wNlY6iT3/V7I1LFpmqiwuvooYnmQZgz4ml50A
+daXy9hYHfnRYbLojOWkNN3FKdp9kNm1FLlX0d3FHgXnS2OXBjwE7G42xQPtQVE8abTaGjvBIymJw
+J7U+jK80hHnkKKUoN5TykY4dMjGvAjJMnJpaQHTjMFkHDCjTW2WUxHxT9wZMB0tSmbI+WbreeTOF
+mV8LB+zrinUfRvjJRKGSWLBZV7w7Tr98wBwRjwEXARtWRx/7bOxooMpY+qVxRp+SGqv33vO7A0+t
+9sxASvtVZdkYCf1hK9kB3CrpRKFb4r8jI3vMq3pPLzMiEv6kp9lFB1+l7tyteZLLV2uADVZJ036K
+R9CL7BqcQ1rSdrdox75qYmVs+U/M3URnVljhANh3dIZdKcMZD0g+dIrPORgcNXPea4bT3BvJDWEs
+tanHpt5Ar6CcHiOxs529UWzwxeMdFrJ/FI1Zh0FyIayrhgN6OYpXb/GjDYWKlzy3aaIXOgu/WkMU
+CztmIY3xWoFdehzGyXhhF6O3Kba8vc0WftVWdrKB65iunQXeaFOk/gYZpbxzC5/kSiSN4Xqsi/aY
+KMcNLWnj8Ruv4dGwxDJOfgMaUbHz3GrTOyONox2bsPpYDic7u8C0ZYiWxV8GSyNz5n7VdbIO3ZiO
+PxjdYRkREOtSeLyyw8DIGTyPaXHyhq4Mx6JN9g4Hm7Du2+amzrL+NWGptCOfW60XpX4kpI13b2km
+wA3lfFMIVlwBpgF8n0a7dYcu29Scfi7/JD9Uy7gNGUS9LLjsyxXx5flauQyieVxZd+R0rFuwVNPZ
+rIE/N7WeABzWCVgp+FR53tJyMiy7WvX9XZ4Luctzd7lz+yjdNAuw6sKRRKnlArdxTkoAc7baONDf
+NuWQkqprsMiKmLVKS3HmGmZjva/Gun7OS8fh0/SaVcm6ZVMGxXeHuOnGGoPiMcKYCGC89UiT8KcP
+cSP3egoWSsgm91ABPdqVpWJfj6mwwrvmXSDtQbBplemvsZdg8VDwb9re8DcZfBBSKqIy0RX9VnCc
+EJozKtrfTUF6KoQH5NHEWMwgColTHOcL0Hpg1XxOOsO51xM1zGV3M9ULZk/4qKCq3HmX5qTaXS2t
+a+XH54CbzIY6vrM5FGsIu5RSmuVw0iTHv81Emr7jthjWQU6LuhUs0dVsjeZ58ZzmVXHX39OII4+t
+1vV1Obr9YSm12GLelueOv/a6wTF6r0rXeUMHpZ807cUesO7wrXXz5p47s3/IYcV+Bd2eri/uw3Wg
+ZEHHaIJog2lCyezguxzDufhxGXjDMO/E0hRjGKuU7XtHSHEbxdm4Jc3g1zfYAkdAlOAOrkmKQKhs
+jXQLaMgBRe8j9zKhxtShtV6P2d908rU/aKfHFwSDElLDs+Ma0ZmKB1A3Ntxg0BLQkJpVkNi9+FJY
+/nBn2JUkA2h27XPXENzMcKCfMZljecaXdI2ped5yT5t33TyUx3Eu4i+1VWrwOqrle41JtV9NTpBt
+l3pkjYYRnDxoXGfi6Lk4tMAWBJ9zBoTqUJdlsxmHvjz6eSde3STo98QHCxdDEuJT6XtyV7retKwI
+ydbfE0hU9SZa2v472wUA63rpXwsrGPa1rM6YPF9wOHf70jDhI8FcWBFzYKkDRCIAiCiDnu//grfF
+y2QA3VVVr27R5ocgxa4emKN3iEZ6UOeiKA8xmgNLC5sg7LpvInxb8aitXRGN7nSQ6ayDq7qIrOxT
+YjYZ7q20cB9UXTnTtsdy9UbNwfQWRXb5XOWxcQ1IinNeVPGAxhTFqxXBMj7VqdsaPKQi91lp/ZoV
+gXEi2z9FJ9NllyfluMi16BMYmIkzgii7XP+4l517WtEK5K6y7IDlz/K7Ndvinkdh5x9Gj1XOHYkg
+IJSelTwMbcNIYEEkgemBxn6jEcq/q6Jj1RMnnnxh/+d8m6EGHPq6FohFWp6Q4PzPoPAAI0U2MRaD
+AfwqSt0phnE6Ng+YTeR1CSAe6AUhd3zw7splDSnvM+yaXwpXNvcud+sHOMXNPi0pQMAxYgsM17Ev
+YVf50zU0TmfvgqFEdWd2IZPjAXkePZAExAfPnRWxONPZvRFo/5TaKRt1N1ObCwi/XoPhbMyXKmiT
+L6NIB3vV1glZNCDqvbNhbSe+Suih5TnFpFdt+qQkGEMXoLnJLaPFumcH1p1VOmj/lqHu4lGMr3lb
+W0+OMToPyKPFMbA6muSR8M9Rbqinku5bYrJdhg9K80cwa+Eyc+i/5UicjLsGYZM4KUwrpjTjTsxw
+Pa1mwOQ1LtWnl0z21te4FNk2R/qpnQABwaJvyksAmATKhUTeb5ZlJs2yxJqtHHGqaZ+SgAtHpQ5R
+V1Hcxy4WB/UcvyhObNeeA7LbiGOghoVL/oY3GLc/z88ibdZGMPmHuGB/Q0RDhm2DCWftmNQga+Xj
+ykqxIKGLFl23ziJ2LKc6Kg0qpwkh2HsP4W484oWIj4wzdADaFmgBxgb56AJHnNakfsqRILhn3UK2
+WkjR0C4MwhBTWwoi9J6f2oqU2oAWpQASvChD+ke9E1SLeRNXsyrCsmu71zqSyypKxXywUrvforAo
+HkdOsC0bAaMeZt4uqhZ11ssstr3LNerGrX8lMa/TqYkfP8FE7X7G5mFqy1d282+4yZHSsqPtvbZY
+1tExNUEwwofdO/MlBqqLny2E+QpMKJ6bWwoY0w2xN3x6hBP8GxK5EkqNeaG+d1mw89HNQvzJ+S6l
+5XDPcghzipn4JGqlbm4qCu3pf2Z9Zw1FvaHPyZpvu4kI5LGqFnEtg0LT5BIbZAydPD0lWZA9/nDg
+sHM0d0J3+SGFgXur49jpNqjS86e2i5wyrmpMX/ye1VoJnzcJA1RzZ52aDqif0XIAtVfFhRQ5lR0+
+OAJ+rOUrLXB0+d2UrFOCrOR7okLtxTRS2M1SkSBvS42oN5g36egRExiH7HmqYgcHtyJZkGJPjPZB
+FDX5PvWxkeLhgVpvLWLPr4x+qS1jrx1tvQ/412/d0e6Yq0lcPnC3iQUX7oBMEMPCDNneswCP9JFi
+6Ks2Q1VFn9sw9NQ7FZXqahSCYN6QG2/LGBHnBrBsHP00fWscIzizlMTmMy92/jmUnjpn3BV5+veF
+WrWTy+mBvDnRYNfERZpTHdIZ2nyuzSS45QHXgPoe3VMQGP0WN8ewdSeba2Kqou/Ib1RLsGs5TyKx
+GaA9NFtacizuorXxjA+Pe8g8AeTCsFoi0tZFt/Fy0dwvo6QUc+pt56YFXoPwstAJnULrnbmL72zF
+/rnApU6EGurlkHefrYvrQip6XDyBi1UKBQdMLKD9rPEmahkKktE5OXxCm3TOvI0GkfJU2zhRJQ+a
+VY4mvSmSyLu+tLQ+W0N7QwEtADYgQ7u8sjvCOhxurlqhspPMWo8biZ0P+4ozRhio2D6YrpjvXFTc
+tZuXJ2jMT9IuPo3IP/fah0EGWAdlMjO3SVzSjZSQdW3Tbl3BkFtJq1/OedMU39D1hnPF9IU4BVgh
+Rk/cS1+NR896z0hW9H3vbukQXZs01EHMd2POUssYXiLHW4sHEsZrNdNGmyi1lwkGDgRcqlyBNIlj
+PMurtlSnbEnktfKUdSr9BJBD6ozYW2tRhzmhfEbG4sMfG0UsT4+PdCowRJeqoiZqxgzJ3i+MfZ3d
+qZmJNmqVe/L7wb1zrcI/ahMnJ7Ia5RaGn+wivu2nYfamksRSazGCEm/hMqRXHS1sY0yEJGjG2Ee5
+lDiek6Of9eSv4Ez48c4ET4houx7pbg6ZOhLQ3haioU2DVstaOZwlz6bVUlXDwfIKkuBoYchPor1w
+Y1sX+X7a0w+0b0xmiMXFSYa9DrqDTPMLZp77n9Z81FFd0f9RzMam6mIDKashVi9qcNzRbL0QeHTX
+AU7gYz0tQ2gZlkK2EFQojoHeLzq1vwKHcl7gE9RQ+mR66KNEP2dlVB2cssZgoQdxny1Nxr2SHCQ5
+kza+asFhXcdFs2xMhrZvlmVxhCb7nLKLrj6cuBHgD/urCaNEV0QiJHL3btIgkoMAWIxMwOswHpt0
+ME72rIlRjUG3N+bcO0z2QAhUjsGDD8MgLFWTIvozwGqvdDbELP1QePXVxVCxtpIqlCYuE5aVoWcW
+xHumjDmhbN8A/7rARpxojRpBn6xj76dsMY6mk5Bst8b+pg/67kicmXgbLTt+SR7UbW8q+5JXvx6g
+1RM42dq9/JLF47kcTYuWq+nBD9KtMgo6vdp9BM6PxxIQwMiivZbRkBqC4LUogkttw1vLYgNXTNaE
+yi/j+4v1YB/0khv76JRXbjbaXMdtdQj8jFhiXBxJIy8n2cYYQoQPuhUTkkurDwaAON9HZpkcoFuo
+nUPayHTKZEWwQEPj44C3aAMbgWAMP5iCwxWaQPbNsVMY6kBTANuPpQzTgXukbRqg1VMnFCSJdyoo
+om2VedFpykWxMQLV7QN08AhvRepdJcqOVv7kYVH09aHNs3yXeAdSuScLI9DiFLQRWIl4qmuvvzJd
+z3lKUrfmnqt7iAIYvOAcFUUhV8T7fHyVKSaopUvqZ2MM8hAC17hdpMEUtgT1Ka5M/VB7xW0mzFU6
+U97ja7nBRHrsi+aznIAzw/oH/QbAoNxwgz+aqF4NsNgtK6b6ACE+WjfORJszppTrxaa2TXo2HFV+
+P3KqpDxgCk7uK1Hh5qDJctyiF4ltZGorLL1g1UG122gI8ltJTefgRBDorOrVkVSZAJKgF8Wegvnu
+UqqAM9SQ7bYXvr0bkxJ23mjy1mce2EJNm/JoGEpBqRVXJEndUNZyvKKGxr/STnWtEnM1Ldanix6x
+gph/DIKHycywlzi3c0I6uk/eRzV8kjPDWW3WFYO43YC3F1I1+85qqy2PTWM9inwKU9swNwDxxpsh
+03D2PSPZ8+RCSRd7i9T46BKAMoHncw7f+2Q9S0XGn6ftJz3LN0YpkO685YKWPAkqECgxm7eN1l8G
+e4RkMzlOdmh4HDy0ljlTBh1/GRyg/W1lPDtJIM5Uz/dvhnDqPf9+RawGewIHiIPTcBpjRDEepsC5
+rhzCWSlofq8iXNLYcGpSYb9yA1dQ7Bvx7DiFFRox3af+bD0XHmDDVPotfr54ywy9bmsgZoRwBhP6
+oebRvAo8TGnZgFVnLuR3Ig8HSWCzoHY7HotH2qsYL2mPThqaWRse4Nviv6k7jx3JmTXJvtBwQC22
+oUVGikhdGyKzsop0SieddNL59H3iR+POtNg0MJu5/+oCJbIiSBf2mR1LJdYrb1815oPxts/bAwZH
+TCnJucqvhmcu2WpX+eJCR67YJ87wOBGc2XqeyB9zBbCzTcyaRiHcR5XNeZEOHxoR3XHlKbFjsk2g
+X7gVUp7j389ziH+/gitXUqW2gbS/dZW9DRkrg3hz9MkvsYLYZzkJwevYPN+AQaNuTmmisPWr8T5c
+krnfqHFMNmPr1C+AXOaPpKF7kL6iVcWFY1XL+RB21bwfpHCbbcUk/Ej8YNzRPIgj3MndQ6kc/dgt
+OvuVlQ7Ansj74sr/AixxPT26YHic7idC5wLQy/XP4eh7zFGGcLPpO8wyXKjBFeBbjOKD71YFd5Px
+IauRW8axlW9E3pdDWRhAQsKKMVJISWHuoPtNJw39TBGKGdcGYMHREj4v+STojV/wXyz+jJbpht0x
+DCFv9tYsyEfOd1ZEGOHWL8IXZWd7iTNhG7mRgfMjPfGqg9m/5znbuqO5M2Gq7orUX3BS2qhex6Vw
+4y2/V30o5VtH0PcCkDIdl/yd0W+5pOqgk+k5SQvsaW2+pwlO7vtElm9Wg/LdBf3j6DX8XMIW27IL
+0w1EHAxz7POck0H9MPoH+wspMrQhhC+cE8wSwT60CScdF0mjfTdNn0HL/N+wih9pqPEvZIrLTQYy
+GYkYuwvtyRnf2WGavfguymTQrtCFSLsGBb8O+4be5HDUOaQEP9TxIuYAp3ls8K09EV/t4GXf9PDE
+jiaU1HkHBSp7LxeYtSpuqXbzbgEZJei/hUSqGpAJZi72U5mXv/oCahZFYgFIHiBNbV6Om9pnRxaL
+3RcrwAAukGN63pwL/Dp8gTo05yYorLfUlcuqkFw9tspyHBB+AdVublyWCv9ZXdzNiiNZBK3voCfH
+Ps8RfTLUZNRY6GYTRrTShOKcYpQ58Fu8re2K4Y67vPsmgHzjQAi7vyqXHB1TX91NRF73jeXh2KFI
+5MEKW2/f5X2x7xQ9pWsn7BwMQiM7r5Z1cGfrYdNz+POwQYNcRaW4S/rAhYzoZqfKuO4LC3/zMAI3
+3uusu7GF+o6m0aJmdE0bgEuctiObzuVfsvXBaIL4cQsrddgU1q1x8684ZL1YiWAqX10nvoxJAGjR
+TA2RZRhVzuz/SemN/bY90OzEP7z0J61E/cIx5BPPI3G3sn9yR/XiJiV+zZvgNS5kWRYjdwTJ1Hme
+bR5XcNNrvD0ab/XSfEkIVYdY0vkjs9Te6hascYY8SHq8XB7tEaAwc4QBjmYUI5uVUPdT+rDWLpbR
+Vd1GO8zA8j4uvXFNhjvaD/nwqg1xLtvt32E2deseStq+dIPwfgGofzWW6n75WQyRxU6jiXa70e/W
+o0+cWQZcbDISYHkCUP/GPE7HFpDqeJ5FgQ82nIuTcaO/guP/yqNzmpSRwIjKli1B08bJC14PNhO1
+3HBCBBjuKBB9HKPlMcRN95RH8bx2dCV37eD+bnIoGX2ARQxqbAqtdvHOqjDWF/GlbJv+E5FzYpjD
+GJ45JfnUVAJiaBIPTCgmo+I4a9c53Ei2hXRBV9nNa4Hp794FAH1oIis7jXNsHbjYTVsO70+DCEls
+MpgCIT7cORzUVTzovbegSm41uOdjSVnKvTZzgojhv+QS8HVT0iLh92Wxoj0QRCZBF4MbbOWB3B0c
+7wEAj33nRJQakOGiJIcmaGDjZYIyBNhhaOar4/a8nH1DL+40OSdMX89mHvwzLotnm5doZQfTrtdR
+QiNT9ULJ3b0ZFnudhxAYZhcHKjlQeobXwbhA528IWbmccFgLkUb97ZBo1mQYc+05AcGaowL0Pg/z
+RKTNCVmQHSrDXk1ihT8tJQEbq8W8xcECx1kSqGPLY7gxscRia5ZS7iTL4mXIFe7aZVluPTf0O5BU
+pBe+eA2y8ClUZCRHP/kKC+dczWA9ULv3fkDIHpLmU8K56CzykXQNDq26fzNj8RFoKmykIh3ZtYSY
+yqcUSgO97U3y3EP+X7tWW109u+3PnWrpwsnC/C1wi/CAK5QjzaxA+fQx1YJORCuY9LdRLK19TbA0
+G59mZk2XbMqLU8G79lXPKfViFew2SDs92ssY8AZkTXDnjHiRweBRXxPL4ZRpHzOp0x+dkPUUXs4i
+9jT0cRoUnBZWRWTYTuoqbdZ24NtIjpSy415M+BoplnizuxxzNSio4BjPVfNNdxjJTDm67R1/aHGi
+2/uVCNsegdDdEfwKLomBvb629Gz9XkoOZuyH05OYFk1zQVNihcOt8BGI3nrh3u/d0U8bvM1NBYkM
+jZ0435grQGiV6vhX+9UvrGr6dx4N3OsQDRLNUKgsg+UM7E2UqLf++BYMSjxoa+Y1NiVfAjOmKb9P
+lwmE/DIIjpmV9JKXyoHmQIBwYbnqbQ0iJQpex5zo2L6K0KmaLABCW82+T18DDWwPWRBbzdqrZhyq
+WCAnYGax8GF3u5F4hXvXHxlHcYxrRlfsuFH7h2isBQHHVrr8WrfW66Sc9EcRNb9zmF/rwQy/uZZb
+mOxFW2zszv1dceBj4LYgWAGbRxJRox3DZx4EK0XLf5tRNupiwjbnSGkHHzQ63QokWQbUxfJC9Q0z
+gXoHRYhrJ0cd/BQcyHeLBlcSp1l4Yco639Pli0dcMxPugV3spKiCp5FMMm97lPGgdKCCd2MeegfL
+SnvmT7lZFzFjH5Qu3NbK03/4dMZdM8wu3vtCHHDkX8PZZwxZpeS3Ch8fdpEW1WWwwHmgrOW7Dv/7
+soBEuiUWb5DxkgYOXr8C40oUgoSNnDT4hi816K1f2d1JWZAncQLDnUOVPURz5T1Uk1WqdZTG1EhN
+VJR40DFG7Ttr28uAsfWz2DFR3HcTD3C2xF9NblPQQOvgIw8+HW9WMh5bt3UfbJ1/JQpFD3wHtPJx
+0p++HCiC9qkMKf3lccx1tYEpRIcNYEbqt1yzDiFHbDrKTsWmVHa3gu97z0QQduPYOa+Z7DbalP0+
+EfHy1mjolXPWQugsxmkzzw65o6o/eQBd1viw+wO3wHyH7zO9jpKu6GgMf83pAHiqaMje24nuLwXA
+3u2MBHb1y5ToR9EE/gvDJlzcWLafKL0Tu2G25k9Sc3+qBdGhBO/8QEKhfmsEewexS5u0aSKeRozA
+ex2EUI57UjlixRQlXNbFkiZngSzJrYMeh5d8tOk1cBn4bF06zykuIKBwDhLDkSCLYQBmHntyQNIw
+Xbz5eTalcyDICrNxTrigtbepmjgav2V06uloe9upIy4eJEDwn0oMAaDSOvsNPF2/wtRO9cugq9tg
+1tnQ6aC3bSDBI2ecUga/38etpDdlKvSuNhS0mdL9xfwtPd86Yu4qTpPruuNCY0R96ylhqdVFUW0N
+s79LRev2e2TRt5vZ064QnjmoYYgOpZT9mRyx2JWjsq/55Oo9QwZkzkFOEu3GyI7W3Sl9zvVMiovX
+kj+VoWDUNT4e7MR55FOlsiAkCXFx0jEgvA8HZNUu+JTWUNGWu2aZo7/GNHBjmb5wB2TqNp+AYkH1
+p756U6KlvmSLPz54o3y0smXToOZdunkIj34VFQn5haCltTBDjOvsYOEX9HrcFdIB07q0f4mOONBF
+Q0YqUeuNPxXWgd1gVenByyr+vlZJd+9wUDj79nyoajN8lXiqnW2irSmihKARb3y/v4zbFfsZEYGt
+i7k6xDqHaxu4A7pAP2y/yPe5L/C1T04e9CsfmQ5xh/mdvfF9z8Iz7I0hpNWQkWLv6LNZqPaIu2b8
+HIxnHgvD/ii7qFgNOReD3mvPURMotZJhwGbDzJzzf2dycR3ATSAXF8p78DJW6KG1H5k17MTE81sH
+5tWpgvJnoRLmhYBA9MMELrkLRroWxwLIF/dtwGUx/UGA04RTEVuw2g+LgSzdLR1GywYWnCkca2OX
+nvw1JUR7aHTWYClmijPP7AX5bzRQbh5u5z1kMJi2GIOgtsYUSDD4n49t3lCppWbfPme14NUuBgZM
+FsWNzWB9pv3c/0pyzhuQ97V9Rn1mt9FFUPxOESu5JvhTuPcmpzjg2QG90Y7dO8LQJwUA39OcVGzj
+Yf/quTndW10AdoztVHw43D/fB2Mz1oGrZg5Ag+MVdw3FbQrjd0nVJqC+ROhtWc7NU2zqZZ02cfgA
+PinaurKaDktT0vuI0jfsHJW1/q7BXb4Q4C1SuoqnwYJnT/fy7YJTIkvslqh/YuLlrHrRUuRYZGo+
+xBbO5yW34r3Vze4T3A59F1lMXimn9q+YPKxbD4/YcGifH6sg8w/QcrOPfGi8164Ez04hfcF6UNmY
+OSDO7hV4OqJeZe/cFy4+W1buOmbgNag1fZgb+Ie3LFbGTiAag9CuRQnKdcLhaDlAeEfKlofGxeTT
+LCF4jDYmUhh2IWXlkfpbAN8A15GSWlAFdgZACsvW9ZyXCG1/LWyHshhW0y3z3frOqtzHgO7DnQpb
+4FPBEt2bvmu578/zt668Tq9UPMVP1GZMUMoCuAa2cOorQ9rk2bX8+ZEBdvjtxtQoWCZkrtbY+lT0
+kVloG6kA1LV5/Azqyjoab/hQ6NDlqh/75QKFl2Q9WLs9Wyl+F2FGqkrqKxa88m7mzHUowNpu/Cl+
+o4qE0p6iExwl47l47fDrPE6w3+aVPfrFG03OzAjgA2JuElqupbdceh6IdVOm4NBqEx1VXt4gY/kp
+qAVyZBrHpyII7mVa1pvRq+ND05rmiJah14uQNW/EPJ0ciXFmKXr0zT6KKO6Ijf1BKgTXBzT2dyv0
+rnGfvlK3Mj3mPZmSKOUWV/YKhOIU5LAIiqecOaHADXXwY3zQKknM2RQS5bWam/uypXWcpsmjx3H2
+iVwtugGXqLvE1FQKcHnyLjJK2gO63+9YyRffNmcKazecxALAXjVDGxtm2qGg9u6DgktCtFWd7APf
+r1+dMWLhGphJH5uiOTltOJ7RBPCE+MG8gXLQvVUlH1Ss0mHFNbmjxIVBtc3wQd2WdPh5XTjRBNdl
+xcG1BLaOdsS2Y3dyN4HChsw0Ajpb0TQAtpPwwhPLNM1ujOTnLTtHu2MmaZ9HV/+RvYPWo7LgkIoJ
+aa9iFHnPuhUQQfEM9cq2z3Q6m19ubRH3cQPALRnj5YrFstouQLsessRprh2Hi+s0GHeb5bX8NJUu
+AIyNsz7PNcDYPHHiv9BSKUpR5bzKFy6lKNJpB0dCEUtivJS8UxdkNlK0qAYUPW/KBpJK0ARALyby
+jDTMuU+OCGmTbhRC+ZJX0J0nb3hEG8h/VxPz5JWQDYxQhEjsDhiWTaj8D3I3M+vZolAN5+A80rkN
+JbycK3xbgnkC3v/fXZr4Jw4q2W9EQs4Q8LOZS0MMAmdH2UjSj8EpHj5uUtC7neLKgkhtD58LWEbg
+0p74xJ+2PKBtwGRIUmu79EnxJ7d852rmkMlB2lYvKfyTLWMBrveNZVYenbrPUObtfT52wdqNw/yq
+CcPRpUvX3WnIi/Iv4HD93LC9Mpgx6UOXdEGAd4K8Tj0U/tYq0vQ01p636xR7DZfnxn6sKjPhcO/C
+CyMrgG00WZQ88r56YGLgP9cjF3CrNeVz2VrfcCrjXdizf1J8dMqzWTHOCQC5dLMDYlAjK5a8M6um
+HWz2RGFhDCI5OHSLe1RlATQ2tPR1gdeLPj+N/aZqIrlbeoQMWZChJdTt/HWLOD3j0KHFRFojCUaT
+jvljyOFgxzAuPdUt7+HUdzWPLVd9rs6oBUyj3OvUqvRaJElLAzNnL2A0z+yunHkC7tJsv94BXFvE
+LC0vz6qs5tcQOCa9yYTRfasamFlzrN1wRi7fk0KCW+qsNP/QQHiLFZCUCdkBfRv7OnMhS1jlLoI2
+QJTxFpqQItzHOdM7NdTeOuHKuU6Kju2KWd8zathwCAIQudNy096lPaq/mGsMsf4seF46ZzlqA1aO
+743WMVckkNaJ1GpG9GteVcKDfj0hn6gIXcGE1BZhyxM8lkyw6/lei+EJEtyAM45kGcTOeIebjDMn
+6bx9w+jmWWliHJlWAdm0DkCgip0p4FJp4r8LjFx2ClKPZc5nEPrK24kqbI+tntL7vgDU46eK7JPD
+z58tGAVXZeTHfOTOHxYc66JTo4YtmcuYuHdVsQb9L7xiRQGv0pDRnAJnDbjyT9C16XYO0uqzGgzU
+Z9qWxGtYMf8IcF896iYtfpG90PeBx9AFnRYzbKmtihWpaJ7+cTP/v7bL/39UKIsl28e1/q8Ayn9x
+wr8Ow1f/3xnh//13/ssJTwOha9txGIYJrxvu+n93wkf/m5AGyY7EdwG7xQ55lf9TZUHtQIjH0rvR
+JYk5/MsLT5VFjKOX30lliwOI1P2fcDL+cyMLunBAvM0OcThHLnmr/+iFH5ohCVlb9V4WQ/LMAmIe
+YEPhmfES0X8T9yzPk510cv1/fVD/jffdCf3/GNaJfEpxIdPdsiL8w8M4+E9/M15eooKB1vvQH9Od
+6L1AflGoDI9caAdn1ch1Jl+Lfho/KllQdDH7LQJKTPZ5pIaTiePerqTjrlXvVZ8pKM2BtgeuWr5j
+MBXHPZBPW0mQV8iVajxM7q20AeI8bksG4KgREjbdtzdxVR9M3+xdwmBY8er5y7Ru8lbbRZ0jGGv9
+RMQ0ksi66Pgirzg4xDK9nVkdd/zAbil2gcNRO67rsy9asZ+ynblZEdXSfFPrCUuEqdnSOu1Gpe1v
+XfXOHYV5xROVGtF7soTd3kstepVqXKHrPPDxCFONlL5ausJstWRWezRYl9ZNav5ELc1YQOHxPhTu
+cXDngpBr/hjnY7TTMzethpbMteU0b0KgKU2SXKUzuc8aTZK+BZfJfdesceI066puRwBeHpKAnDbx
+DNzbZe60yaaR39h3AbeBsFpbAwfzUPa3uDdpTIvW4Szxz3agNuAMwJx4/b5Jqx3XD7SqFHx053GI
+Dnu1hh6CoJy35IHpfH2Y+rHjfC6xBKc9cU9wm7uBVjI8ev645uJPWDhTcDsnEW1LOnA3tG4ytQmy
+8Yi71tlByQiOvg3mytJuh/9mHE9oW4K7U46Xr5ipmAjgBZVpgQVYZpSB1iUFLEGFw4rq7f0y9TS8
+A+kFUOtk1bHBw/dzS0cdRvLFeF5C6x7NqTkS/mAosFSq3DTUGm4yNYoCL0CaD7eOPa/AMpHX2YZz
+q59sSo4OUNE8X32ZCFPLWi4e3zvXt+gTYTK+REY431CQ6p8hMiielJFBBXDzabxmbXkHm4bE70Tt
+KjeepDsOpjtntm+dKEuSp3yp2/c6Dn0+66JH6LeXIV+2fTAJ+oETNPiVbbdhiGUobB9rGnVvPbzB
+rcmkLSGYM+S591WJfj47HgVIqnb2oKSqel9aXD/qwOq7jVX79oZL0uJuGYZz1lgiZG679wC/q87o
+J9cazM7PcpOdoDbCrO/sLvpUQ8xZPHVLGOkRt5k16iBwa04GR9DvXDLCLqvvFl6oY+lMqaQTIs4O
+RDD8l7ZnDM/xJRaGD/M2AfaMT07bCSU1YXWr3+CzBPkqTiKo+uHs3mpAQYRs4TRk3clMqFpthxwT
+Mj1/K/HcjPuhdvy/TUgf547qN9MznO48G8qtCaxrHA4T+ZAOxgraXsl9zu29dQOFumJ0gWGTUwJM
+Q9FRgCVtZyf5n0dXtIiu40LzBz9fzYh8sR5S3/yEWfmt6vzOgZ8rbctH1MWLWmu3Oug88R5CHxNi
+50MlH0q6wfA63SWDKFeLY1FnYUu1qRdrOBSyu2/CRT12hf2Tl6Bn0XG5TOF0OdhFxGUqikqmG/yL
+IlPLXVZH4jFPrWGPRTPmLD2724Frw/cS9nrHTTK8t1G4iP+YdLrjkDH/rWsymCt4zOKc5LGb8wDH
+VK0sDTlzBhSB8x3RSH+q8HWdkwivH+cfJoDKGbwNviYV/ulag5a/iiAerYmL1LyX1gfuQtQN/LDw
+5gMOOob7VaPHp8RzUD9zkcY3DK0+LePyR3od64dqff9GbE43iWuii/bIUvjl4tFfYmXbqc7EsR3y
++tGynbRbBx5IwFsz9TWq/NJ70RY+drosy+FYZp3+PVj1eK+mWzokp3cArWYwD3Gvc8TB1qVL2Jsj
+nqyUhJOls+9YF4S6miA+eDG9N1C87TWWQj4N0KavcUVTBshdpmjzxJ8w8wBnU3l/m8mupyyFNeRC
+X6mDEwzk6CLdMD+NYfCX3UncAxSX+6rnKrgKeVLUEUMtYS3uVtmWkRGnU6EyBziI6fof8l4oR1nZ
+23dRSG0wJ2SUje0tlUArX6Bh1+f6KjjOvQ+iL7dV5MV/bAzpOM09yhwTXph90OlYHyTwNn+rtY7v
+u6Gs3yK+p7VGG+IgSXXbqEMfb22XfhuKwv1n1dUss7cE9bBpB8+eV6IP+2IjOR3cjN1Zvy0l2kMm
+KEMtRvtb5kELDpSCuAo30TkSyeZmG7aQZwFkzcqlVEBRJQCtOPTANdUjgxhfxjGdHp0YXqbSxeKT
+OsTAIhVRcIQvgPpRPXWPJm6eUkbE3FAFPg9ZW4/V4Kf3swXIuFTpGn0aXE4v8A3fumW6jNhUdqzJ
+gyDN+P25oDyATJKmYFhk/BPyC/jMny6afxvW9+Ok8CLFtmuO0HdoaJ87WAsWzcoig2YNwADkazVv
+l7EP9rHmLpPi9dosOQ7xllDOuQiyt8xLsm03YAuebtmGCXF7NQ2+Qva2lvxaz9Js24II3pRukZid
+Hdwq9w47L4Mha3AwRkTiZ85us+lRD5dKxUAokKhW7YzURH2zCxYy7ffyxqvgG5ow2zC1UE4DrXBe
+XtMKXyttkXJbh3ywVdeklzbW1IMq+YqCQptg2/SHgYj87aiBZzfsh30bxs6eFSg+Z4Gk6qvsw609
+4q4IoNIfYJJS+1gkj8oyvL616z/MfO/2VMFjd3s9+3vsMxhAcDHse0iAK8/rPV544Qdnjgtokvgp
+ERZwQexoEVGPoZDJtnAGRYkI2sQnEfTqGjGtPdvQIf8CewlhbNfO0cF+8l5IzPWjO7d6NwVMN9c+
+JrRNFtnpXztfxkMYGHgnQ4Vuxzab7i0idgK0l5PD7cU/vy6hJJ3CzAfs7RbeV+L03Z223fmhTggK
+rizZIKOnoxueMPfBw9G6wFnojuIZlSQ427F2XmhXSP9UKl30SjbgIqmsFiULk5Mei8EOThkftb2G
+0wq3ybPEiVdFiZWdGZ3tW8xk+9p2HXJBwBrhtUNCrW/j8dytsh/MFjZgNCoJW76EBjdfHFsvLn2X
+B8Cz5kzt8bJvbKM//GCoz2NHOygE9zC/N4RTdq6itvU02HaJgTD3lhfsReYPqbGa1xTHybWPEn1N
+8lYCYhIhE9A6HdcTR/tdkZbqLTatfZ8yRT/lKbqGuWFY2PyQ0lc8B9mH8DtsobVdnQMGQy96qv2D
+boR+shJAB4Mbpo+eauMLzQ0Og/o4+oDQhe0Z+9WH56dH1QIQCofsvo+L8M6NMyYonRVgVIxLhsgr
+iG3c5hfiRLTdCXpdPQKeUd/vW8vlwDOlVJRGHTeL1Yjpn1kr9wZAU0Fa38N9yfdJBYPDhcsCE8oM
+V0zuyzGS/AQNWNFXL9QaREI/eIyDpzBjYucWDFym2/5GGaw2LGBOuMFFTRVLpRTNDk2yCz0UXGgW
+HSMoHCVRlXwhsUFbcpmXiLgxe1cX4a7rZP7DoQVbcygHwYSwQmUaZ9Ps6+A2v+20+uSlXa4W5N31
+EswYSHr+ktiy3W2BEWULOjlbh7WXPbZz795PytZEYT137p7MLLrq2aIBNtoMciHVhsMmSdapkxXT
+amj6GcXE1bjxopGcH/4Sbe0DelGvtT9lLzNGU2SF0t1DgqViZpn8bD/2tnqSxnU+xzbxX4iOMKw0
+vZt8jEuWLNtCiOY5q638Z57C4mRBMvjqfHfImFYJwdchw/lqc0D9w/BlOZGrpUuhFnN3Nb3DWrEQ
+DObAplDV82Dosj0SOUt2r7zxPeTr/irTyH8NQjvsX2IyTMN92na+t12KCUOeo2Len5ruE+0xXSH1
+kRFvBjBMARMGJgMh1uEh3IwAuQvO7aReh9qEWPlL3l7fMFPGW66zc4sdHQ+t10mKZ6I830yW5146
+S0YO7zvjSPxpMjt27eh9VogpsPYSCSPVHb9crkTrzpfdtQ/8J7hKG+ZHaiNVHJ9RTLxNxnMISSa0
+v4oon35lMMYxrgUCxLO2PoA8BMRoE+N/hsLMJz1MZgcpo31wAf89ZX6MXd/J5vTgM1jsjCyPnKhz
+kI7+dEARXA4jH+GXjjJNyb0VPvqId7vaouZ0aKMHwRjoNIQU7456LK6Nb/mXZPDGchUkcMPWnRQM
+ouKOwsCoovSl7RfGbEGUXrI8/jVmEL10PT8xIIZhM3c94UePqPdKhTr5O8YyAkleix0YFzBgk5u/
+9XEyvk8Fb05lNcN7wTBwk87o6A3D2ZOg2PwJnMnfzM/ttSuH5NpxnH2sbqitWQj5B8vuwg46udDb
+y/CFef1wWjLb3jrLML0RFCE0ZpX5vcL289guvbdlXKKabe1IvPCpP+F1zOQxzOr8SSMAbDzEZonL
+aZKPNAtX351x/SeayIedWegIwtXXP2jU5WMbde+jPWN4n2OE2LUATrid2yRe95NxGdYOy1cegpxy
+5tFel5XHGWgo3A+dt+5Fa1QMrEfJBwHd9Nc/iGBKfdSRbVVfTUaXEgJkc98MGXXhCHAXpgPl88Ap
+D+NwZfu7hc66E8AReUkVj7xWrPeRbMdfQvQNActBfBmI/8GKbsKZhhkdXeKIy9oKCdL/I9hVNpDV
+Yqqd2VPiKdDrwnDH8tJb5jMvmJjo9K2KA3UKZFq8WS3PlcrDmpsgJtpYGgTknGBzlNjuKcVjvbH0
+WL3MRrqXHLLfX3+a824l7MalCq4Y7u2aPW9lmtT7iWGIAPnv6/5sZ1DYVwvFZweLB83ZepVG+ByG
+kiJLZnHZprV8+T7Msku4d83OMwF/+RL1rvqCi4a2Ev1TijUnXYPNtEq/psFm0JZQsVKcFe2JsCW9
+7G35p1Kr+KdeC5ivDxe0pC8vGybuV8EovG8dNuFb6zKRxAPYfs2TI0F/2dE75isswvXQ3mWc1Jgt
+s3bwAxU10wjK4wRQ8St8LmfrIJof+CTVQ+8oDbpeD19jPcLyvLWHKZckvWoZGZnRo1vs1jKmoEJQ
+DCDkRx/ZYpeVtQUoD1tEUROicCKw8J1u1xR8Nj9t04XzPdVCeXAg5kT5GW0dBidI5rw13DZQ18tZ
+/NW2H++SHk+uKZgzrPARgc5rGUu+ww21wZJQf6ZQ7YEWDVPGmeCfJjU3V3694xTQ3xm8Jp9uIhhA
+Fg0PkHAWfgYL+JjBqjwjBGXNm19jEf2np62LTPO10MXzt+UMeswDi2UotZYNWZR2E5CY3Iez+MY6
++40fs1yNkaHtLzCbga15PQ2MpbGF2bfD2BuLTHsyvXq208ndZyRSzllBwRwwSmtF2VKwwX1KgkKS
+MBnj6yCU/5B6aX1nZ75rrTz/1lw3p+UxGJrmPPm0zorZ8DhYiH6npe7HdlPl3m2bqsEkDd0miTDD
+tIniTbOWMxOy+CIIO+HiT/q9k6T2N9an7Fs6NhnJsmlrfn/VncPcDi6aG9QurLzhWpjo0Sy5s2dv
+ngjQ4l8mbOX169EKpn1lJbQ0IUo9BC6hdDShTztMsfzWkpHbprSa4oGTHdE4m/Xqgv0Sku2kAjT4
+JPczoBVcPOkyWnz0t2XYeNRgvNlVVOE7nvrwiaNB5a+xFKcPGBFxVzEsOQy0WGNw9gCYU2iL7dHw
+XlZpQmOOQ8RkWIYSL9GIm88n/xet/dFN37tMQ2HopfosjGdfCpy6zApyiwXc18GTJ0ZMH/xt67br
+0sfcsb2LLS36V1MohucRrMjBa8vi5FKPe6a1VJ6FL+Jr6OAlbRjGZRu34T01Sg8PiGsMFAJPcaSJ
+I1qOOm2ZabX4sthmvvmdLN2yoV7RY/rv2j/WkpVHnS7pc8jKtAoj0MRsR4u7wn1W7rJizHZ9YC90
+EKC+5W7Udisi3fFlLgf5tFizzaPXwY7ILa85hO20fM26ik4ywDIZBh2r4NxStOl6zH0k4hX5c0uq
+B+4E7luY4xDa2LbmzIVPzlNsZkMLXyliNOWVDqNY13rFpgon1kzAFU2NqcWW+UwZRzU/RalbrTsT
+W0eSvPJktXSpG6vpftlM0TdW1oqNgoXHYqwOXNf3xJi6B2238GBKvFXOMrOR8n8DmEuUd1VzNO28
+iu100+TMsKiTT4ctzmDecYzx1I5RFbAfy6532Hhcfe9UiXojOOC8xVMDAWw0TGJRrhgsEi/D0l/R
+Frfy/4298+iRHFm783/RngMyghaQNuld2Sy/IcpM09sI2l+vh3UvdC8+yOBbaCFAm8ZM91RPVSYz
+zHvOec6Q1E/gZgsChY4ap83s9Wm5M4i5VmeiI4KRbF0RUoCXywMZZ5HxWqa2ou6CAsR1zyE6W2P0
+Qvyb4jY5V56bXGNvphYaQgzD3hnwzbDBF9D9Sb1i3s/d4H5kYnYf/TGorJ0HGq7ZpqlLE5sjK9at
+tImDdpXnLoYfgLDyUeHpytZDkAh6pwkZvXa2TL96mIvzOvAH0z6OS9/QaWbU/5TYc/nWyJDikLRE
+UO4kJQyR06iHforwrIhJ+Pf1wCBO9nZxx3bz7lhJTREUiQ4w3sGHUcl4V0Otha/nyZPyRfGSknWv
+ARuMgPPcWGyn0sKwO+kjr8K8VWY93uJ48XyotkF11Zo0mBlOMzwfF8EYXe5eTi4jhnTw60vUzcSt
+dCP9H6YGLqHxElc6/hKkA2McDXtjeEN7YIaMzNhGRE4S32WDYIQ63ejC9rZd/JDUICc2EQH3p0yH
+5SUizmNnLs4UQWPnTSjYCQ6KbaZYQdHVX36cqgqJET8bnEoolyumzs6DX2McWtXDlNNG400YCrRk
+UrvpK6jCGymrFKoM4YfcDvSDxIL2yuB8eDDcroS5Y+GbKG2116qWzxJ/z52stb1NfGMwMb+LaaPg
+ON8pENncywff/dCgBN6T0c3P2GT6+9YQJPNQOGP7jG0E1cWycn6NIRfcTgmnrLX2jP4N9y/5YZfD
+9S52CFOYcTLeYXJdjL52Bhko44V4qNJ2NtZRLaKf0ILKtU5sy7pGIYPeVVKYxTVNPLEdjZALdODC
+UQeG7qxBBHCRGgvp3LbEnB6bqDLpPJDl3WQ46P8TPWHvM/WvxIHShrt847s3pqKtA7SjSstDonFW
+unEgAFljzMfuB5t8hRIfIdFAyT3hnA+/sQfNn8B5mZUNMQe2VW9iAd1ADiRlP0mucRBz8leeNpAc
+ZZ6wEzD1HO+UKcPvwdDLAseHiNxS/uqB1ztK0r43pijp34khA0VNoc6s7WxAKjB/lI3CvgmIie+H
+mk5R10jqh9GlrWekp/sCLbM/UqDQ/VFQv/cuj22zGvwAJnqjx/FvNw2LTZt3G+4QRI60q8tDaROT
+c1i3SYFW+ZXYinOCfQP6IJu6nzJtZL2eqZjb15ioDqlNXhd3adF8WjXI6S19JtUjVySm3/iDn7Ne
++g+YW/Pvufa86yxafmlZh1TUQ3DRpFtaorPIHYmnDPhL5rDteA2v5aD0NztQQTm1NwRPxmwRMC2L
+FvQQ0VuwO556rKolwDiztmAg72yC5abW94X08nMNDefJglq1imbXu3dHgHkrcyq6j5mx2rIh9+LG
+75TaUb9E9i8qh/yRZu8sxb6SivoaAjd4oPKMd4TDzcU0E/cBcas85qYVPypB4EJkI6U6fcNVw8Ze
+27ZWjDltCO9IIrsI7lV0x6fb+Brpzlzzr28xRr8tSVqq2oLZvyWXMd9PBKgby9kUGZ6eJl6o32kw
+QZ+ciisp9GHfVl61TmNSC4kS28yl92PlMro8amU66UoOY7JNhek+yYGfCy4iH55p6c3M+VyvWkMN
+u57rKwpNx4TDSIqQ1HGqP7y4cu9D0yTeZktc0yT22bD5KGMD9zt2OTx09SnpSQisgIYrmuPG9oK6
++g2oV9CAo5VzF0fCI0Jc2Q8j44yP0vNthyhnSNdG1CHfxB1P02BGB1bV8L5KSh+8DzOFrO3En7oM
+yXrhX6YgwaoURCTG7i3BKwduDXAVEZ07wytfMWJOHDoDjiwxE87MEgMVfKgtFK5b9Qt6qsYwRBNe
+3GgKE6BQbEy8HVtMYn61N6Vjs5tGGEITrYsPeF3qBu2w2+Yu/olelQpya0bgh+3+3fRik6BjByh7
+nZl9cOpCh4Osl6JbybnjBkMaccA1ohjlFA2l9qg5jHtr57N2bPxIwIeNY2gA+7GZkeBuZo5xo0fi
+q+vAa+qRnoP46pRoPtScD0+JNwJZHuCRJRxbn5qx6yB5Z+Oy/odld3GDFG8ZDufxo8nQL8mwcelh
+RMrRZCbMy0qVshiT/fHQYTIt2WgyHd8A3TW/cun4xXaoQ7JYLfElLmkBMXw6Rs/8UCCr2INJcday
+P06Ojti5iO4fW+VQrFBHogQaGubTa+NnAt0mDnZC1Oz5ZRPrbQgTAQZvKAwqybxkvumSkNVbDyIj
+6u0qItaqkBi0J++btuWEWZ6J4rfKxordSiR1aKws3Ny3dbH0BzJoIzScxuxiK0pmwBy7biebSzAS
+sV1nmR0d4KzQSla4tvWc9y06iigzCoc8fGw6NIwjQ/aCdF+rlt8Y+NARnkrEM5qtzOm3FYW3LkrH
++Wn6pLytUVAf2Lw4u+Rsl6vQYWs/arOwso0n5vGNebPYkjuiQGi5XRWg+XddFIx6baMP0u1FjHhM
+cpN4Ti9+ssVnrhn3AYbO6Pu2rQ5guoOLAKJUUJznwrROIzifW/AllMRay5C8iCvad1ux9ekp4ZPV
+C0xewwMMqHsZq4HbtSJBXbanKSzzI5kPg65Ri6Dx1PR/W7UDZIrjxK1YVucImPLG88zyYvS1WIc9
+/0SBJZkYC3P5m2k0ya2K4uyGTA8IQA3xG8JEr5K1dPRb3NXzAxSt8lJl9FQooNtbjKbFMbc88xuq
+M3Wztd9eaBiL70K4PS2ILBjQhE3mb3gj8SGyAu/YzhWNr13EmBjbk7P7v+L6ucFIW6nqj/6vi5/o
+f5Q+/pYY/uvf/h/yBlnIbP/b6pybz594+p9TMv/xpf80B4m/aNe1Xc8yhUmZjE8V4z/NQfZSr2Oa
+TBB+rUHYZ/7pDRLuXz5fAMELGxCZzKWuUpFsi//bfxHWX7gfRBBQyMM6IoP/VFGk9VthWf87oBKa
+rutCAyQI6TGtX1id/w66TSz8/nM2q92Yd7G9gdsb7y3Vxnc0cZgvTIWtVx8oO5762csvxChI8/kl
+Dg9/SNJraYsETybB01UzTPYPKSzwyFiOaMKuIuFeWE27+CWKqpASOqZeL4AGxIpOOrEZDWmyD+WP
+TJTHZ4B3zlrHXX8HZ+YF1/FooN2wVDs14XBapX46x5O0FRbYcZEgT6Bp4mNL1/09XtRcraTnjNVa
+5bogpxyzzGox6T27sjLXpS7nMx6uwVy3nT/hywn7iSA0TrqTaBvoYW4xP/aBquTRxY1xrU1/7kmk
+tP21sKoiOM32wKkpMEEirXxbxP1RRBQ7U+wW1j+G4XcTiwomGfqDzEhfurEMghO1bFgnp8EW7cM0
+ZfWPzZElAUoxZv0LcmzwU0FA+SLKVlkHQS6noMsGZzyCAaDGJAiArxhuBkCeo2E5nGaEmD+0AOjq
+dmQc9IGgbz3RQo2xog39B2FPzh7C/TF2pTROtQEvdF/lvvs1tYndHwElYZhoQnRsUIou6c14ZM+B
+sVntrBSnLlqFvWTyJhOqVZW8d7mN4NUYoOhN5d1iTJi8rfIb9qF4iND2mbicPUuAeozCwUfmaYs9
+rwqBLO2A0yK21xNtT2r4C302rCM6By8yN4rsgyGE+wg+Hp4C7iPzRMMdwg92fOTriDtFHU4sosS6
+knXdFdxZiUfiVAdigqFAiD01a96JWEF0scvsuyt4Wljos4j4ZdVhN43Sq6/QQRQBz6XhEz3KD5ng
+cKKN14iL9JBVY0graSf/RHnhv9pEEJaKYuTuj7jGgJTUpBC9DmSpVZmMzHrjAJM12gS0K+2pKdTx
+RhdBciYV9ljLNKFuBmyM40zOg+c5wXvb5gkRzUS525xh1r6BaPrdFsJNOeIY+VvfcupYoZqNekWS
+fozWnk0mh6RHCYcoT/PRJ7RNCcGJCkpj7/kztRRTHpEgh9+woO4e/RSyNzkNu9nbqYZbuOQabbt/
+b22PBGfd87wHA+gVzssK5JRfhb48mCG3JbbBLmbgXsU0PoLAzwHL0qFE7sQYhqPpaeLHQ0duBEuE
+CQbbEj6X/Tro4zc1ICCBdYp0tauk14+XhvaXYAOQsSHY7wvu+FyXRbOOjcECe56Qfavd1n2XpEsM
+PBARFqJ9WHT2K3pDY9w6topbhiREaHejhZ0SUKUicJe5A3F+jmmTuUlH3mhsNaXDgVSKqBxv7caL
+upuw9wcwkrhrOLoH/FePsT/QcjF5oTW8ap4uethpUxx3lGT5FaiY2KzXgDiZbdbzUB10jJOBehAy
+rURzmmumKq7UiaHxlw89nIc+r8io4F7kpDVhq39p+UbFmpKq7O980AEw1zBsawbGjcFEmMCx4kGa
+mYQr34BEUdJJ1nMTz/9gWW84S8mBpHdaZ+rIk8kxCLyFx7GstTkNcEoql/OSa4z43OzAg6rU2U77
+JYMco0sRc6kPuaj3q4Q/YpEYBSg+TmdkfOlwMjPL3uXLwc0x6yZax4tIRJcl9eyzBcl5EzoFx7zs
+98jHAukp5qFdU635EYsN0xoOiFksCYjmY8YkMi3b4Z0jin/TZ075WiFoFSvggNNtt5w5afEIxlVb
+04jKOhQZm1EFwwFY1nDTB01wHxp+TuhtOcWmREEfHEbCazsuxWPRl7HNvNpJIyYMHIDDRgREw3IA
+w1YzJWfNaXK9ONeerFLIVxonhp3VSkK8y3G6g97PmfX3qD0up+4x6vO1NLBLLvUqyDyRP3d7c+qC
+S10RcyoNRfQmq2gXje2yvqM7svs0lxN+Mlj2C4ev7Oh2fboz2z58ZLdM/H1jeeoJcXL8Ykpr/4BI
+HJ6GtuBq55TXgGUJI31Dmec27qtr2i3QDzXHNX3pGSuvb3nRgcmjRK7unX1flmmCHUrDJXXSgNon
++CnIfSp33yOPgeGmWy5F1J75f8C2dquSRvK1CXqB1lluUJ5XGMg3zE+Hgyk6ucUG6G9ykVeHougr
+LsLpcOv83s8aeI3pbrL4gbUZWX/XFamCLkxlvBZlZNWXqZBzvVGcHJ8betiJpo6wBVZlX9tHohH9
+mXJLLpPV78VyWu6YDsEtFL2JOGZDzp/QDpdRQuTfbM3tZV5uqunvpZWGjPpUj1l0LqwCHxT+h/LR
+Wa66BYA57gh2H9zxveiPYghMJEXlDqgu1fwoiAkfk99bdMh9Wnnp3yhuQNq8GUtQWCT6lnevfDdB
+lm5GRxv7tNXOvhJ2ukFk/AHCMt/HyxWfkwshQjpS33C14QgOjASYPIXEqxJs3DYLKggvFqibjbUM
+GEzkCApAu2B6sLit19dS5cZJMF34wFHMXS6yO0yvSN8gRocWiz+mRqW/3Ka3P5Rf9w8jArM8OnGZ
+vVXAKaO7ydZ0cpmpXX5Vy0wlRIcriQ9WrXFSv6OXiQhjuoMy6F2pHeLiKp1lfO5rlKSQ2msiHLFj
+cHGP6I5fnEZev2m5ygPBavjDLNTOg52Kau0MipWZN9d6wTBIv7HW/sw8PHYKimCjpoFvMSb7aR70
+n2WE2qxwZbODLQMqZxlV5YNTX4ZlfOUsgyz65sEkKbob4o2T9+kzjo1yHy8jsGQZhqG1uCdCmIsg
+0Cb5a2rldHVw92SzmXhxyGeTQIiBI/GH+Jd0cGjBlqTMfeX82fxO6QCsTp8QB8JvrUYyzkr1FChG
+vg3FUoxTnN1bWL/OvPEMBQVfXq6bomZgyPypZLBMOIqDacxVMMIQgSYSkQLscsaO/J3RXgRp9RFk
+SON4DMthB3EEoESY9fVKO039TtSGWWLCCOMzmxznbIdh+Cm7Tm37kHAeBzwjPEcVA6JVbTnZ0eNb
+2kasmUsO3qxetR8137NZNcjxlefcJjG6HEXJlfsIXmq8tKoun6qg43tr28q5pTOhT3Bqc9dl7hzJ
+rbCj6p5Vf9q0+H3mA4cdVHLTDKPnkMEv6w6MUFuJgCrjImBW1NL+m22misK2tRyn5sNPUrYaH/v+
+XVs0zFrqbuw+ta5geP+Oo4smy+5kIlobAgf3a+bTRA5W1jLB1q3VEbqh7/I5mnXwhPs/gzzDX3ZL
+S7tJGJBSh83IkOTNDJw+vmZjF9w3dkwejQXG/9GcLSEajyY9soqd+b6MJuCF5FJwCBUaB2YlDWZG
+QCtpRuY1O4Ci7PcOaES1cqzWe0jmFAXDLwdxdReNgKai7iVGZr8yCffvh19BIV60hVxop9+ZAbZL
+jiS/yoQG3bNqIWZcezdI7tJ+RsbHtkVllGyyb9jV8rGpWagP7q/skRiOu3V6x/hhxUt37M/uTkx+
++jd6E5UARew8B7+KiTIN99FcZJRqTumpC2KZYHBeWCbDpINT7Fbee+b1831htsZX5Rfp1fwVZwQR
+pnPZT94fMoRJfZkjtZAPlVP8SHvUL/MADDKfc0yWNRWWGyoIzHQNQBFFyI1bsBtJySp0aJrCPWBf
+Y6ockfDb5qpWe1M7+lzELZaEKaEHsXHoL7amru3WxGDzk5kR7QRq2U+v8yJdkY5HxfImr/GY4CVg
+lKyqxp8CpgR1LGm3qFbJmWYvZOKie2OIWKzCRTWbF/2MBtPmI1w0Nbam+jTG0j8mbc3KY0dYbAYK
+24H5MqpMFm0OMDPnMSN+EYtuZ7eCWdui5QlEvQpxT7myPY5RiNHS1/nOpgFv7w8xHsdkCv8OF03Q
+FhXrH7QWBqcjt0ND2/uKbvb9wBHB3oixd28jeuPuxyWp2KS12lnIfQdLDdm5ibzum0Bm/eAZAOiY
+wXA0QtGrnmz2vp3rg78e8iD64DgDyzOIHxP6kZEQ+EbBW4Xs4GBuvL4Kz7UDF60O2qX0rFOXbhFL
+mcvOmyEhfxq6mtAABfUMA5FXsbDpnwwb4bBNhxx4aYpjJ20EjUA4CzTj14VkTQPduW0Yn2LUp/RM
+Zf3n7Dc/86/Km9vhsp1yG6vjMjy6U8vQyRDznitQtEMh5FabLMJxkFDIEJMhWjeAo1ftIisn2Hoe
+dGHipmzGsT27yG0XJNL6OBmQUje+05p3zuxEa/qh3Iuswice+wfXjs792L3IebDvbS+jDtLJ5zUR
+RNK5TO9XvJ0LqCQCQtDMCwLT0CVoL2azL7C841cTpNGa2ydZ56Bsnl1Tj58JVol7dxYMXk1XpzcT
+w/+DK4DsVqTd5R53JfK8uSj1LpJ9Vqv2LitsZgRqKeZE2M/KDo3fJPjzwakTySFznDc1Vf1XPaub
+YvEIqByLSPNrHMAbFH2JxU0QcdwA506Hx7R4DTjozed+8R+ked9dcdSwz/mUhkdclXdNju+TR9Rw
+jsVciNvK9YYn7XE2nxQzXPKZhn5vQqwN2hI93tkuXgEyUF/gG6JdHngjJIxwuIYRCFnT1+ZuwCF6
+aCHz76RBlaBPYWe2KusoWjhYPfWWnEZIi45es8VilUMlg+uFn7JxaLPNuhJHrvA0W7jVoDJza+M2
+bEAo0AWHp01sdP0fj2yg9+RF4wKRoiySm4kWMQmaOvlpBXBuJOkCLvaclB8YfRlPdFLkIZzEtI7u
+i7Q2X6CdVhy/s+IeLqb4EORJcDbk1o9Kl8rHbGmKB+JjyWPH7WbneksZrDePyUsGPR7OqU+T3bWu
+VVkexqjxt3Xk6nrr582M/ap2jh4ToCPq5wIoG2V5T02tcA/LgOQzcgxr22ekV6n/HDFiSJvsNPF9
+bVwtQMnMjHvMFhjOr0D39afIExYAZRUH4SQw3TDtS6U09L+O+KM5MGfhXpdbGzesnCfMMvqgyhm3
+YDRO5Exl2WJHxCI3gwQjRGXs5GikeuUPRem/IJULc1+za8qVCvPlyAh4eajhTFD/tsp0AGEqVCYw
+kBRSzR+aZrtbf7bDV5Mht7eKJwk6O9Ne+paUSXtiglNWOx91jsBHPeYnw0tl8QS/GSlNW717KUbi
+oeTOR8hgMwDgbTIYZFKZSuw1WbSgaIpg23B920uGcx4rUmLSSm858w2XTpgSJTvWbhgY5GeRGnCl
+SOOp9gFt4lkCLR7A0427qv/gI5e0tyz5LmpvV6R31GDb33na+a9MZoiGsh9xkgZnX2Z5fesEdfNt
+t1GE2y+IJBjbzgKaFec/KUa48ND4abKU+rYZ4TJ0EGY7QdE6nPgYGKxkLVq9dpH6KUdJ6uEmzQBZ
+cy3sIuYReYPc74+o1RvW9W5Y1QiTzhrbMQpIHncOsrk98nFXlJA4q9AstDwobmLprvAm6FG915ub
+NnM0Npq27t5k2CxHZdxn7Dkqz5/wqC5V8Uws7yhPzfndomVxJxUfUburg8w9NU5hf0bG0kjfoUKt
+s2HKOOGwRU2eY9QrOy4gsgS1+5XlVv3qUvPwRgsPBriojY37yl84vsq2fbIBUk07f9IcYZO8a4+c
+xPNdP9dZvg6nDkZDQcKI4kZsDJgUYj/6sDGK7qmEc29JaYDhEQiq8Fm8DqEk8Z1vl/kHcHGRA6q2
+88U4xJnnLVWGwiTlUuSYNq68LxzC1zlGOVBQWuaPpZE3hyEkaLOOW+4eaxFEwHis1i0vVmpFuIqa
+gg9JITMbzmtRtc0+FAXRGEINYQFANmjDbtuBaN5nuOxG8nnh+N67XLD4SXz1ArWqo2WhGwN+as/F
+ziIyPeNNxRmHqJ5xSu7y2HryPZ80nK0xHYQVTqyzq3pEssjp008M7jNzi2Q0rN0UWaaxLnqYZKfA
+6+bXtOy4dPF4uv4mi0bPsVYAanCtg/XcU0LjnhiIkLYsfVnumdbmP1AeBLW/E5IbcCxsMoXyWppO
+uki/0I6cvjaDiWUc/Dm8r2H2ARZmhgdXCBQYWcuBR+VEQxKmZmBq0Dy6PgqeiqTlNk9u3ARkaaVf
+IVEz5iBCNAKerZ8QwzMtovQqc4g14EwhOxqhOMnzUPTdvEnS0ftuna59xkkTcxlLCh7qTDDSWyXk
+/9ZRjIV+Qc1CYM3AbaUrqmZl9Dl6iXceRcusNEFivE2hrCvOE23Dgp1GWPkL1n/aqEs7Mslz6Nlb
+56W16HIQDAiNgPe4TYt8hN0CXuHdBXiwmb2me+eT1IpLa5q0C9eR6i61KXqqgA1PBhtDqsW2kaTx
+Dvo0OTyaqbGjsC2xrozlCGgrxbKDy6dCKzQ73bjEQ0Forww3GPa2m9V46el2WfW1CZm0pNl5uUUa
+gBTascGmD0w93Yo4mR9EE2b13udk1HJlCtSmMfnMb/vEDm8G/CHDGrI2mQIzRdMcsoLxV2YG2l6x
+qko08GLcGdVgdpdpQManC4Rdhh76mjla0poMk5RHiS+Kf+DfKsiOTJnZ2biCuVO5CdO04nIu89bd
+47Bdms+HiGHRVPENR8aowhsKox1KlQvrT58Z/mOLZZTJIx6plW1UGm8Rvd/Ys+Oc7lEjrzH/KpZN
+ML66MR4irhr+C93ZZJXcPuECk+qGzcXqjR3Xeps6dxrSP3IOZJBhE5E8MsW1sW6XTrOJBy95zHJ/
+Onhk9PpdTATnhc6b+jyTO3khi8xJuvTr9D5v8rcatPe2SsgGHlM2kS2JF72C79mHm24My08EHeOn
+SurpKc2DztjE1RK38Fh2p3POVghey8+LW+6Qo39ohmWWnfXBN4e59stM/eJ5BtoG678eFBRZIz4Z
+FmLTWlfLT6TDTq6k6woW1dz+2zKaYcfUQu5GBgpnRjr2OpVOd6/MSWC4KyoJr9Eb5oPkwYXmNNSP
+4TzyCQBPB4teROK62MQReGZfP2U+lJAzaU4wFsxXot08eLjsCkMxibJqBZE3tDGXHXweX6B0FT1d
+m5By8vSWYUOG2Xe2+vlSUyLoHogfSeSZWEM8TjJhYaiOr3Fju2smidOnCWEXBn+1qU1gb34z5wPV
+LpA/q6DBPN5gnWVvS2P3mnE1AW4FVGlJzUVPLSzUJ86isMjMgKIRKmccorlItaCbKIr/Q+4eE6ts
+mQOsfWUWfwsFonvtyzTflO7IsL/pEmqVBWAtGwE950TZusX+/+uzpSbJ+X8oMZSBgCfwv0Y3kET6
+bP+9u/AfX/BPUdb/S6J1IscKgly2b1Mx+Q9R1pd/AU70BM+2dKQDoeFfqqz3F4Zi0NxYFYUr3OBf
+7YXC/ouvcP0AOdeRSL3/qfpC3/2PrYHC9H1JpYDtQMbhr/wP5ISmd3NFw5jc1yhyT0hz86ab4vI0
+ehDPe0D7+74p3mNWz9UofP898YriImyn46PLL/a+pOzpJq7s7DWNY/KrTEhurKD0wuOIcAUKXrQx
+QWiuLq9iHpDIhjJHrM0g53O+BfeckUJiz+vn10C61Z+58vQrYfcIg42kD5UTzHhP0JspKzOTtd1U
+2Q4KuziNbS8eOzU0Z1uVmM8tBfYJrPcxYjYybixhLOCoWdj4mVV6Zu2SXHJZI5+yJJzNI22oxplY
+NIFNxyanDxG2d0EmFOHzWKUNQS3DObsMcD+QFTn9pIafJWTSp+QlJNL7HDrTAKpVRvzdkiURYGeK
+I5T6cvETLB2i7KRFdcKuEu1ItWW3s0gZkaWk/y9Iy54N7BMZAm4hdc7oqO2DUVdZwHQ4QTamqnXX
+F155w6lumcqCJ0WT6p0CRBPZ0D9kqI1HZr0hkaMkHD6ZHhZgZwwcaORmpuaWi4AzEaz3CXoTrYIX
+F8UUdah5mo4uCCYy5uDY8fqAoKBMRO5qnH0X6SjnmFoWoEBC/JJjchocROcwlhrln1gvbWVuDMqa
+bjq7PXDVA35WBWZHuZw2eXfjLmBcP/sg/xRrMoDGEl0aQzlTdgtEUmV6u17K9mfSeZLwaoTdvqOr
+47sm0/9uMW/71VrPDimLB9zQ4pkwQHuTOVnqMFg0PWNHtDo1tmPXQ8YihBcxBk4x6EJHY+6VjQEu
+gbLe0ksJBtqp7OJE7sVDvE2HE2NB82F2au8sU2Mg90FZFXTi/AnjkL7aph0Ph0oAQU9mg/YdUjgE
+/lMH4qSJwfSuptiKUF3m6xun9eXFaYDlm5ZBbAw7YXfs1IxCXg4L1aN1QYky6IQ6FXWgCLIA+TIc
+1LUw5/AjINVyMjLbfvdaiJIMlPJDJFrBy1RZwW3b8UKtHK/00an6xiFJwvSflr6A6AycV3oGdlY4
+MOj31SyPiv4pBsQujqaEIMijUbGx+VNKFjcxNk7dfNQUplEHSgqCfd14aWx8YW1Qnbh2GjuvC8l7
+TPadzkAioyjvCMCiDbT2axgn26ITaldVHIbZeWOCmP4ABrL5ps2ruS3c9tq09Z8gIWgdSjLmQae5
+h9HchpHhrqDe0MNutrZSl3y1cDEUu11xhzbIU+96eDN3gxCgJZj6c1S1xwkkIylxBr6eXtnUXJy4
+gRBLlQB4bcYs5DB1cfE9293yMeyfy8Aubwzk61VryWqf27rrHrRLEx80kbzFRWcacCc4khFzY9fk
+eI7yAfWXA903iGTT3LCaUOZUgcIITv48xvFedrw4K8/JjZEbwsA3yRdhRa1kBGdilENnUKOkMYIN
+vpf9JLLsdp2VGjvfTR0eCz3urcKx92Zvm1tArwiNLVcfVHJzX0QUAOLnCsNnj5d23eneJz7pZDsf
+J1m7oSNlmW7l4GHLVHe7KU0xGDqJefVxRn/4Fjc2/HVtfy6EoFfGC7P7kIjSzkyr5A+2LQhPtMKg
+CMzanNC0ocRRnDqMNK95fOBl373Xdm4eGkRvXKBzlhwWd/Su44KF7qE8cdOSwyQeESQH2m7aN1wl
+3J7biTaCECBNgcy5ze2yv5q51RLr7bAEFtS2b0TqeXvVURjP66/uiV0vZjh0vq8I1PJWiuAwR86Z
+GeB00bAy3loRKUB7I+GJzLh2dc8ZtPSzxylpojuX+cid4My998tS3jflpU5wgvb9dI9QmGzoyO2f
+g0D2O0XZoVhzV2qOULaNW1OVRFgYh093A+f5C30Dab/OusA62QOAnyDQ756RZS8kGqobXubsochm
++0M7pZtRhGKOOHuocLiLYvoR4n4i/S2iWVH8Qsfd4GsY3zg+ae2ZS4a2+BC3dtBxGp4xiM69Q26p
+n88tifMENBlv3TxkObgPjM8E/ES7phsseyUVR6qxHvVdEdvy5OXFzEwtn+u1ctP0p8nijnAVObFV
+YTjJFYsMT9ny//ZI3N7rMhEgPLLpIKza/baGeNq7YcTS5xMxYD6VYwuArqihGMnSuHhAOZlJRkw9
+Brb7um2w4lgu6chseIwD5URMBKNq7/t+dgzmKdqHREzXSRjmr0bZzc/a9sVllrQwoGg24lTbkC/X
+ZSytY2TKH0ZsjM2sIftiMtFkW/SP+nnE6I4zmaNHuQma1ruMtZ/eCF9NPoYswe2n+JSKOh7pZZy5
+mRMRPlASlXEOIxAoQ5B9DKynOFliUxrbKSqrB/Bmlj4OTTI/AVcSoFVRa08QHtwX1WT985haPwTG
+qnmfhMoA7wnPGe08+ps4dLQrXXChq2k5K0+MXShPHIIRPpoUL9A0hyePpeYz5P7MokuYm5tXZpZI
+W6lTPwPcyf/OZU4Nr4SyU8QJ48xCW+9xKphDtszn7nRTw8NnER0xgUDsg1o/M+9/C8LoaykF4qPl
+E5MIqBgTyJ+9gXm6sa4mcb8VOI/hNDXhLVD9hjE2hU1+N8zHEpVFXLOWD8mhY0Z/HssUSQrqJhPM
+bvEoBdjk4pRDB0hX9VWnxS1lZLxRk2iPojacfUPNslg1rZFuIEFxb3DEQNyPZ7qbTLbWgua/mj3l
+uZqqfGfRpgSexWrvc8Y3z1k9GxtCr8wG89Jd1yoHEl85xhONRtvRnpJVawr/gehbcdtSuEPoJklf
+LTInx74tum3bl/UPA9NsP2RkeLncMt/1yuDtv7N3JktuK1t3fhWHx8YNAIkEEgNP2LNYJKtvNEGU
+VCX0QKJvnt4fdON3nKNzfK4990RSKKKKJAhk5t57rW+5Ip+ugeWWn8hwxh1MziFZDa47PdZLWhfB
+2hxM7OZAkyK6jcqO8NM+qmhWNnj+IG3+9GbDAo8irzQK41NusN0zVLK+T7+INPEvOg0yWLIXpt6I
+T9kvfg3TkfFnEJgDNKGFbzMuqBuAIiwkC/4mR328HRYkDnbIdj/kQ3znLsAc6xc6p7Vw2i44HdKe
+4ffFNJmtgG541Yyf+YLfieHwdEq0BPmA5pkWSI9acD3knKW35Gak6M+HWw6daKv8wrlmC+gn0Czr
+5QL/0QIqlxffTm30nYE9TCn/6oVhs8vLlp6Ds0CESr3whCqNzDyCMcSaiNqEWJnoKf/FIGI2XMRr
+mtgIreSCKfIWYBFpy6CLTAY974OelYdssCEA2NU+332ZOT85ZJXdHkeA9cImVe3HBYzk/WIkzXnF
+2Q/tnP+JGN2ydnPNbtQ4/fCIvdPbOLB5FkPNObUS+cBhcrqhZxytBDo3EGWxz2luaQgxyMRCXIYW
+uJqhluIpS63wkDctHYmMxMWhTU6LAOrCisD4b0E+uSH9rlUeivhN8xO3dBpJ3OacOV/qX8wobYKP
+yjhZP5a1Xd/yvMqOsxeQqXrBTaWIowe6sUConF88KuRVsKkCTrgbeJpWTU5BkT3OaFdJ4SLX9528
+gPxW/OJcWRipLngjyR9KKwwUHFZzexXR8blLmRdDZssbWDDNL4IWxr1FD8TAHm1ToJlhpZF1QrTU
+0lxYIFyhxxHD6QiGYJZy6U3pZpu2yc9273r3KjQdwQFMwNVHiEDw3oL6CnWnyLJMvXcyA7qjUj44
+bIj2oMFyBN8RHOagG5nJIuHd0PWEDVRCPsdJPqinZqoZn9Nbn7ajYq6AoFPtnEru/ZTYMAIDsJoZ
+8FzXUxLUe1atD2CV7cq38dtGyon2eBVzEhqRt9rhnV3Jn9VCOAuK0jiOSUCAKbxhZoEHR8YX1OH+
+qnc1VltCuR/NBZBWoGDfBws0LTUDsYa+tDeWEoPJ5oELMaMk3xUlZ0PeyQ1p8D9NQoI2cWgcbHck
+gz7lwE2JnK5inIiLE+rVrwcil6LwCXAZHv0sfIbc4a0oB4n5SNor1XlBsKQ6wy/AlUZIm4jJ96EY
++W4E4jaVyaaIpVrPfszeYIbfIDxBSKM0Axthb9rOczfzgOAiLaP26GFW2ua03VbSDWZ6Q7kgeZZQ
+sxSu6ybuGQbQuCzXQwaMIbM3ZjZ+MIDbENV6aMHfb0qnuM4wAO4GOGRb7MfzmWcPe5UI/A1bj0Xg
+2VQzEvRtcZMUTfgQQGfZOwHQXtBUHf3LDoqDEy9UU032+0w0N4dSY+ohr0lCMMGzBWtFt0qsSR1Q
+ZKVnbX3rkgwSk4bJ9VU1OcHpiApiFk5/cAwveOkW3iC+N9CDTH8pWJKFSDj+ghPOC6cw+4UsdEPt
+v8ByGD+gywcnGmaDPNSw1zjQyLdw0IQqt4b0kUXOFDhkAlrxg6vDkfwNIeaDHkFDsXGYryFSp0fm
+5BqwDrNDEzZQ1tx4nkf7uleMI1Ao6FfHaZFlcCuarXqCJYBipifpMo+1OoxZ9UH6ulhVLvBVfPxr
+ElZ8YvPM/sueusjmdGqqS9gJdaDGKloeOZ29T7gvFnIr+p6yDvpvPFkIUaWOUZbm0T53R3c/TmzV
+kuziox35IcFg9nhoFV2ClYosf4u2RZ+Aq9BgWBj/L6FMs/cy8+N97LYdTAqv8Z4VBxcHpjM980Uj
+lR7/f/ft/6b7BoZC2AtK9P/cgNt3yUf90f6xBfe/f+rfXTjP+ZfjucJ3XAn3ipuQ3/fvLpyr/oUY
+1eTUatmOaYulP/df3gjnXyjK6emSSqCW/hw/9F/eCPNflgUszbQc26ZJZzn/L9xUXuJPxgiTV1C+
+afk4MGy6IOafjRG+Hfduw+h+2zIMwGJIi+Y1Yvm7/OGi3P3bafHfio7Zegwr73/+98Vf8Uf/henD
+dQTMCjDKpWcvfnuZhoNnMoTk57l0lL71poFMG9k747Y27fdhrvt/N4xx3YRf5d+8oAXh9i+v6EqO
+41hPQPWp3xwffj6n7K8BmRzWkleugUVFkBXAw4MWFcUGnkf8qIjVPLSBeuiAwxqrip/6Vkww4Exm
+sTeNG4kbC3bM1p47dC1TNpzzcJ5vrTHV53++QNbvGNnlCvGV0wuVPg5Cb/mifnwg0wm5nNb/SCgJ
+p2GkYUUsd/45kLHCDMjiT8zJxCiS37uCuYSKNFblZ03D4JMErOFlCom/k91Cu2GpfkbTRvzRSHjG
+P789+6/3CW9v6RlbkHy5J3/r1Xp+ZcLhntxtBy//HM9WOrKQleS1NkME7B4pErJTXZ6yVoxb08CW
+2YZ0NnjP6gCJznu1Sf++Yoo/WZbG9W7cj6C4GdJxoqOtVPXpu3BctYdUyMGf+JrvXWiBKJsq/fDP
+n8WBOfyXW4MDB6hiAdyMv/98qVU8D2bbCbnVzHlvGSmqNQIbO9xQIEY3Qw1+ekkulFujbIZPMJxo
+3LK8WEQveSsPo+sb9904tu+u0wuchkSh5akh30YO500jz14d20SRxgyjiJAnWaPrj20ZRds6TN61
+XDLMA/nmY5O8tAZVbDFdOW3BQSRN/ZjWmXuxGLbfIs9kKm1HTAjpuVjBDqCQu+L0gn1zYg5kZ4M4
+19qMPhWzwnlldUKfpFvRsUmQDsFft80TfmhShBIbTs6mBAX39s/X8teD+9uDTVEqHcYBwhJMB/58
+LQl6ZXzcTHKLEiO/lmZa7Er8GkuE+N4T1k9Mh+O1w4jfrPMR1Oyhq7Php1tl9XdHV+25CoceyyaA
+g+NQZtnGYwjnQhYgm5sTk74D4N8c8HWE4ynU+fTpd4NFryYgEi0D3on4O7zVM6Fy60zHDLpDc7xV
+aZfs2s41/8ONw8r6lxuHJ3PZEpQjJI/Cbx9WYTZBJeBum7TqL2Fud2SH2AZqcpb1O5Ix/F1lAUZE
+uoPlsVLhSWjJABhrHMmqs6OeaXFPX1Sp5o9//h7+Zn1VmOjUMp9xIXQvq8sfVo8snPI+k4OkP2Qj
+QqnLnzSOjk6LIMcb+5t/frG/uQzKobdBf1IoiyX9zy9Wsj8QK9LK7TQ13ptJ0b48xcn1n1/lbxbE
+P73Kb09phjbHbQQT5lTE8ZeJLfN26opF1NIW0+6fX+tvVgRFs85fdlQlHPu3y8ctmWhNhbEtpLBP
+wsjnT3DW7q1TC0gO4yLeLygwSipKs7jzi6De/PMb+JtL6jsglj3F+u/wz98uqYE6vYqk3Gat179Y
+Q0UzPCCm5Z9fxV5+zR+fVqksDg5SKpZwpm8eLs0/3iY2S64iqo74AFk/aCA6a6SV+wRw4pgj5Y6v
+Y0Hc2Dh8jiizuygzrkjlaDrPpdokYpg2ftfRXY8c5iP0Pfek17S40B8aWwNyRFS91THTMrOLMFhw
+7l0Jf643+VB90er4D+j13+8PqZRcmncLgX05Vy3TxT/c8rMzM/9xa29bse2AygRL5qIw2MwukR//
+fN3+ctl8k73ZERThzEWl+u32iGZIPF5n+CBv3PAmmOiEkQrZn8K6yHaCMdKBS+3/hxflKPj7U+2a
+0Hs9jkusrJ7kePbnjzhQ49s5uOltnw1PmE7LrQjJbvCDcXgTRM25YOKaB7TOOESHdw/Twc4DI/eR
+hHCDsWHjWkT+6ykPQpt712i85ixu1R6d8z5rseA3Qfwe2M172YO9NdE5039tViS9063LkGQBuz3K
+tEde5jXmne8OtKZzpqHo58OVwYgCVNtk7iCOyjO2O0IgwAFr28h23jhgscTBj4wuv+8g8jDuCzUP
+0MME0pZF/5g6Cphp2V1n98PR82eBIvFazLmkPyjDt6Y0uqtRJfZuIDN3E8xoF/NK4RLAM7PPSLQi
+NKvKkveJNtxm7OICf8bY9J92BoXLiRzEVGjunPcxtoGbmfmT1vBi1B4bDmmJofUDqFm9hdmJMs0I
+sR5JSZBhm8l6J7EVbIvY1xR+khDLqc7x4SUYNkYXbaSdYA4FB8yeC2viC8uVOpNF1exii9yeIE6H
+YO1bfQDe0gV2ErBLfaP3OGzjpgBJnUxr8LGPlIGEX1YChBf2YSdbz1U0nSCVO/dB1Fd02mmcCNS1
+5XggmGve25k4BO5Tx5h1Gp0NGTn+z2mgrTB0T1TrXwmny5fYZkgNkTjf+qp/zSMiBvOx2TWMemD6
+VNZLlSTivk9rFCGTLnN+V8bo2J99EPrVfe7PL+jCFyMcsvZW1zVj1ZCojVQBuaCv1V/rcWbENGfy
+julR/kk7tLl2tTId8gPDn6pv/T0TpuZgVkrfN5my3opKZ69DLPZMO8BTISxTd2WZ63vqcIwoIw1W
+uc7tCtpP0k/PGXaNe4Hq8FnDK1njzJ2ejCjQe10a6QXdd3iYx9p4SDloXTpoTwSj2ubGqnKPV3Y1
+MZgkPqfDaG6B1lsfRkAUaEn01YVaGoUS395hJuD2Puqy73XvTd+T5RMOpjT2VOl3cOH2c/lkIl1Y
+K3rEVTCdA8Nr9omZDMfSSssfAXigp9LklqxEB8earuSGwYOFNjYDQNZW7WZerJflGGKUrYjmTKty
+3ph6stYljpyfymyQgPXOdJNj4bjC8/6KKvle4I5Bt4CRgShMOx5fqe5LOtCDsZomDMORYHTQNdGM
+MR2lT1eHr4DXXrVPtxVRhFV/z0qrfQlV6h5ynNZ7X0zlVgdMqKh8GrIZarmp/do9JKT/7GpDhdDU
+eFP45+Hz1YVxhi6Kz8YilrtOiwdW2PFQ5dVwBKMOgdktMB55C5G9/xIyPGXlSAMSsGmxKvAZrhOw
+Q3sb3uBjP/pqi03B2KVCqSuwZ/g0paEeRTd9b5QsH7J6cK+oafWKZ3DeOCLGppXLu1mb4r6Lcr4T
+eoHFBl5Fd+Pgg+ChaqNd5A8DXC/y3Gz8Hl7SI00kLm4FgY84g2COnlsB/YIMvPlkmuj2ZFk1a7Id
+E6AZDYAytyIY1IqSD1Ry3W0fyuESz0F2L6dyYNpp5FtD1+0GV/JeOvF7FYHLD92k2BAFhPTEZE7a
++ziHjDy50JxllmOM9g8xJB0AJEwJROGZmxi4+51t5D7zJEo7dydy5wWNr2QNDFFvR1CbLC/FoWl2
+D2EwnSxiLjrRMERMnoI0LfjEOr2H2UxGzhTbn0SuZw+6Tzjpq4EmXtLYUFcI50mgmbvX2nZB0WhS
+i7CdPVoBrlKwBasOBgDSy25fzLrb+rVNfEN1ijAf0w79XsTMDuKid/YwdO19bZiPZYplMhr7cyH7
+4HbokKOsJLOEt3bOrY2uhiL4FlKe9asoyD0mxBO2Gj3XpxbbO4QxsR2bNLx0c4PMzh6sdTSImQDV
+ckxJ7sHL08U+rGjZFM7O9XHjgz2GXsL4vEyS9IRIr78zLEbCQEALxi6lvpEuGEnHre7JFQCSSzP2
+I3bqEn6kme6twEMUg1KFrpwT38ZBLd541+WW+D2JJCjO9mgD533k6gjMtpHcVMoEjOiyc9Z05hY9
+tX/o446I7TahHIQ0tmFcmR+1kDFLP5rGtE7Nc0bDcddWLN4AE+5r62ca0UcAlzQ1T6rFid5Ykb6z
+h2x6IFNBnZj9Tnj7vOREZ30i7bUNXovZn946AuSZIGTWAzaDak+6IHthZCd7p8aCytBuXmsIRLu+
+glutwdIe4wi5RCJCttuI+bOb4glMoTPT2WnRWXTlLRmT8tT2jbwNRCe3wKDMJxvByH0WtwLqzqBu
+HT/stqafhOc+V/yr8XuyLpJPnVckosrcXMdMug7cotuqww2Sy2hXANDGilAvq4sfYR4mVZhzP1C6
+6dhASBZGfaO7qzRRajRucR0yOpuhHlW7Zi4cbA3QQWdRueVDO8fyE4N2/kZ+qMQy5LxMgSM3ZWSy
+/SEM2cuhrwFNzi1wNscnQ9Fxc6BdFbknAvKq4xliE5sJihu0H48wIhx8/HPm9zv0/himBHlh5sRM
+NbNAiM5Ozo0ftLWhNyPO8SNpqcwylfmqnNa7I1oPlfRoGPeQkrPzHFefKFisrZnWghNwVhePRd1d
+cFMfvIYoDlXfhOkc3snUdzfj1BPjDn/02Auuc+jFcl2BDFnRjjo3Iar0MFhzUAt2dZAPZIZbGCsB
+1PrXwfK7a9s24TMlJrBIKG3WDhGJG628pq8vjvCDF6/2rIc8b82zjf/lRiBROI/j2Hw2CDGIiayi
+6GkoeDOG6cgvMZr+DxUjm0tjUnbsiJ+zAmVsEMzXFnwHbe7AGCM6/mVHxX3u3eZ9MxlIVMpiW/te
+8aALrzhGVdJj9B+xPCXC0CfYzGRYEk2LMt6KrWfkXRUQpdRX2LPZr3vaP+UqdzHLOoMGhqG6Knhy
+tNXx5YOOXDUkYeynCscv58zK1asqIiIa9BEeK+mP0GvnLNzUDRMDrGFREGwTQpiZZZaJfwFM2u/s
+1Bg2gmKIoL/AkO9hxRbkaXLCQDt65OHgPENAht96GHL/7GeV5s2bDHY5zyRi22ujaggcMObrSLYN
+RyY8q1c9Rc056SGSu/N3x0teO/IkyBqe7JsaB9+h6+Y31P080MwdcRinkBTFXG7h6qF5WrYb0/ZQ
+s2Chq5YW0bgpcrfa6Ex1t7aomYqSSrfzREIgHYgxwtPzYDz20bAj+3uDrt1HPwWI32Iok4PuKJKT
+gUL+pRjnUxd8zo73oAb7qVb9B4apo5rCb9Ag3iLbcQ55aOT3VW+qQ2MWGEfM3LvNepW2m6yMCSAy
+LSTR4Fb8S27qGvkTtts8MzqLVhR+qkTJ4uzLun00mjTdYPRDl+hou7ukmL+cVeNKCcQYc8Cat9Dd
+VYEM7zN/fMQ5Lw6Mk4r3EV86cSuIog60loavPgnaxzn3qv00lszctPYOpBKGmETY9j67TjFfywlZ
+DR03WAWF0HueZAUmsi6ZOibDoTctpp6Y+VcYdtXWLaFerEOfEOlU37spDReoETGx002sjx4BNi/M
+9dh0lOoFrOhQauJoZ2pWE73tqgvc+Cc/g5eqzrH/V5OBH4tjDByGeYYDmA4q2XL+b64gteJo69Bq
+3da2n9/2TmRALsb9umOa7e0TkH8suU4p1lZsG7ui8dWjMXoUDB5Nw2dmgOU7Bbt5okVREjNh+zzc
+xJwaoYHwJJjvrWSAcJoXny1Nx90oWvODZxj6pxiCQ0r65Z3RmwDAPagXJG3WSKqYrp3NSATJCuV6
+es6iKrjWHD7IUUiZLVpZue8CFW9i4VinPFTPWW/e2HlDck4XYniPqujR6Y3ycZakr8PanO7jnOW0
+yX33nlg381skM/+hAy9ztj2A0fzK8MeyFH7LwzJ67Ia8kvxnyuw4AQeoE8N/9ua2ffJSBrebro1/
+sLBkF+L7xufBnGK4BF4KWwfp+7dhKio+Q5QeIsgUt1kbhxdrDqv7vh7LG1Q54qjDrr3EVl4CwrHD
+11h3AQIKclU1MpjTQCzMKefA9gp1htSFGoDznjOPRlXZOwb6otE/VHiniNDpovhKZ7B/SR06g6Mx
+5Tel3zc+IsWhuYcY6dFOmevpQDqwf3Kz1v3CgmhXqzkp4nvBrXqPA2wqoNoOtn2UHvVxRC6SdUhr
+mrKgKUhGRbtSHKJiSF6bJq/fq8Qx4Y2bDA5WZTWbzFHDIXnuLOlvbDVZWwfYD2aXPKewUeTM31ZR
+H10MAHVbS5b6gPe+XxnCgn+HpfqObTLZ1WLOBE/JQjKZ1AQ0qSiejdjIGK0quQFYTMxRVbSX1Fuw
+wAA0V6pPu4PmI8CPUrrA5tFhBhicjKMl0Y0e1hmjYtYxhko+GBFCE6IqOYUQcQUBGS3Qs9VaNExN
+hD4oCuIKElswbvu5t69Wn+M9ITGDSgod2YeMguS9kNDitoEl235dFs4QP4goavdZJTjsGvOEn6sE
+p4Rtd3rgg9JC1wvcasCeiNO3nfaj5+aHVBimeMmDoPnZY86ktKZzWNzYi3NgTWEgh5M/xS5JV4Hl
+TZuMMNgBD1VlGFf0Cq06WYzoF4mTfIOGlB9QkoiHbBb+ITZi5uZ5X0L+5oSflDztUgONLfMBXdRQ
+sRTMc8d8NI39aJcXeOLbEraV9Galt1NTT/Yt7b3AXLtE+W5dVSbzSg4VYgNEsOdU+M0zxMpkjTvf
+/UVEQeysxp+z9uecNrCzkKvK/Lu09CIKzNgiJ3ZYcKBDL25z0MWvNqjbn0TOQH+d8bXw0av3LkC5
+BGlbtzdshSwDfDdOsZ26XNUXqcLp0pQubg3VzfjxZG/e0g0LWc/7PBs2xE2TzhWU+hpj5byUUDu/
+UVpSLnpDpb4nSU2mtM3C/VpZyk+3SgynpI0ABA0DKGlQ4K4mDMSHcI6k7o2REs9Vn8UUenH5WPRY
+MINahunOUOJ7ZtOAGho8+K3D8IR+5h6n0E2aDuQpI+nhPDMb4QP4rOxp7MZ2J0wdnjQo3isaaoPG
+R93V3grxdLObirk9Tnllb7UR1y16tLJ+FQh1Dwnb10uYhkhJlYpcXOuD1dzUc5J+lByXtsNQtgce
+1RAhW2fd6QbkDjo5Ul5wCeA4XLcjOOP1OE4BCeJexC459vMZYTmFAdXwd1tW6kh3NTzZ/fjVWP1X
+3RjPJiXAkllsHQXMlI0qhbNzBpbQUhbdS43b+QZytH+boIH66r0cNO9cxtOFzhY7Q87BekWCuNet
+4ILRBq1jAmRGbXxBCkKywGztJ1zXocGsGhNq77gDsRRj5ERy6xKXgmy9jyntXcaZQLtJkFtpC4SO
+E/Dhygmraj6/yLrumQfOw/cYNUa67hXyzTHw7vqoleeWNVjysYINkhPi531w26eegN1jPTgtcXDT
+u8lvIfwdy9uGwiTdA4KFIMMSMW7qCXlvRx8u3JM3hDJcDVeUTeINsDufnG0YfyQGB2ZcpLYUuXhh
+dyIbN6pmQJ6TvBjWiOW3SJDQZanCwj6fyQ2qTj7SNmLgKv05ZSPttrwz9oGm1jXGhHTOCtMmKiJY
+8sQL8xwYljw2HGmhBbBZkSgzsiW3qT3uXdDM+9JskD7WqNBXYWdrjF9GsTOd2juWnh1iAI5C6xGa
+pPuDVkbib4ZE4Y4gkuw4W81DHtTRnWXTF/RxYVEDduIcEDzUQjQg1Gsi9Uapcjrwjbfkx9sOQ1c1
+cMdG/qns/bfBEB74Dte9SadarwG04PrGl76R7L03XeKKs+o7d6M4rrz1FlkSOCZBmcDt2cJ3GNZx
+T8Cb4/vDeRwUgvfWNKatLyKmdQX11T2pCNx1/dCfAKbEP8Iao6LOghqQJmM0WN/Fc+7K9CmEAP5g
+GKH3wry+pCSKgxx6d0dqNEKucp25CRkBTtGqF2Vg9BQ6sx/bqfCpZ2MEO06rj9YMoFgL2Gc1vvD1
+ol4t1lBmUWA5Y076J2dJlOQlKr7Yw66NrjuABx2RLeCWU/+NZRSttWtAedr55cDRnszM9sgUWs1L
+KpjOd03sdQ+tBRgl43hfspqqCgzSaIPy8eVg3MfZlFyqsgxuVJWj8ypBAQ6DdG8BnOECTolKwMyW
+bGTfUAM1ZG7VQaLv4rG8AwArni3gdkVtf4tL98PPkIjK0h1j/Jx9hdwJtdKmqN11O2VnF9buIQwj
+84EsnIUwIdRNPg3ZOW7SpwL0NmquPkJhZluPXu04TyTJBEe0zvPWqPrHwEYJBBxjeECRaZKiJ9PL
+yE6KJALrJDkCD4RXhI/unOf7pq0Br+R0mWnoivNQOMgaiWLadU1ZrBiGvHeqNgkxyYz9CAeVIFVv
+36Fz2iRR+7OlWvmcCLkU2hjXHfiT9ShnD62uxoGr86Npl2T04OHYexEho9kCSuQOF/hTxRw9YUHY
+ERO5FRhRjhazrq05NT+cJp9P4TCIq+paBPV16pDGgxX0UNB/QvFldrsSYB8YpdZWW1teK1lRirWp
+7te1JOCUtAoNKILRst6aVXZSxG8D+Nj6SUHItNG95778JBI83HfGaB2nAhdHqzL3Ho4s2DVStub2
+YGjqu7INHXAh0ZXeb8nsIN9DcrkvDUlsBqg6libKYXvIR9r5/XSiAfackoURatODZgTcK8a8E/ad
+PgpktyE8dGqJMfsUbRCvU1F/m+fw1rKoKlZhXBKRSso6geBa2WwHhtxpSQk0y/hI5FIDrMIHukRy
+FZMsjh7eSRqk2pGyaqzI4fGwXUAlUUC+aFJSTkjLH78VWDLRvabORpQuRXs37kLWXMjQYdojcZbf
+y7xwHskMLbptGNlRjUUZ/wlhUO0hmyY8KVQV0Q0kKmJdUbzK97q3jPCDpJiUx7PWLnWvbz0JQnmp
+tXq6benUb1OeW72mlt7OSk0+WDxNK6PGsxUYTvBYaZzjceeX/h7v7dGX5EIpxPKVtNGgFj1ivwP4
+sPgj8AJ2RS/hlgJbWCZPBqAiRo6WiPyPMA5YiC0MgGsTwmhwcmPqE8jPLiYp30/Sez/0pDgyzk6y
+9dQxH2FAm9xmsifTPIVUMlQ2PVG3hfIYsh+60PiX9dRHVp7W8UMy9Olj1xJeu2bdKPYimelpDgHY
+GxCRrveui6xbsovlJyifdFU7fgd2wefc3FDXre1yzDDHtvZaVZNF9Khku89MvmqKwZ5qEfGrcQ+T
+8I1GcQ2/fCDZYGy9G8+V9PCRIqL0w1MyZxc40zgUdHUVhBA3uf6ITEhqzLmuxKWuwrK4CiM8NQkY
+D8daIp2dsAjvJQeSM3dcRFpzUlERA75vQnIwJ7T/ciRUYbL1AUJozHRpQuqX+Ps+97+BQXuQ1fhG
+Zjo0TB5cnngCdo8jEshQhe0et1l58YXAnVRzo+cxzcZQ2ovIxuoe2LsLdsiULlmS6XxLGUCl2hoO
+FuRs7vMvzB8AbB3RrDn2kAkcCezmATWT0wOHRccSrLXfDI8Lruw5BMtMGpagSZ3J6pIgYDCz9NwI
+I9hao2dtLBXRpIDvFLxRL+SEY1letfFSQSB9KdpvsZU0+bp2p/E0t41JKAg+OQ6+MWPhqmXTzQlX
+YVSxhtOGuSD0D5NpdRuTUsdm/cnLi5kV8rFChspBi/5pbCKnx7Lw3oSGtZ8W7SW91fEcl7ImVGmc
+3yaPqi1fM8qis+Fys1zdOn8bBkvchzNg+F3TiumbNuP00HE6PhM54b5NFT5qxpmSo3U6y3WZTL55
+HjPDRK0KWpNUDigy+7wJg6ugNfSD2pQqhGi7S0yiJo0Krh9X0og8a4veNXumhCN6hTTAdLLXUMfM
+k+MbzAuaPn3O2+pQd3rYyXx4aZu84gqGzwyQ99pS3iFjlrTtZjKlTWAToOdqSY87Ma4iZKTIuhI/
+k6gG7E1pKpOeG22VuWb9s5jji64WvEw87T273hApgKI3HdiyaeSvZxXTgY/0NrLJ6G5Q2nQrx9bh
+zp9ymxofNYy7QSf93e5IF0DUqIdDTv35ZhY+vVXXqY4ysatPNM/k7Yw2N8gQ10G8yiu/f8ykRWx3
+ZbUpkdRkvvjz7N16EfZ6e3SRz+IP7eGoODg3AdZWq75ww/uoSi/AQDhZ9Dq+YXLCyMHOs8NY+zA4
+a7NbHEH5MD+A4CkOCM+GZmNHyj7gecFLUkD55rSSJG8Jq+KP2aqtdYG45tHVAbhdsr3ik5wdljDp
+9XdtytistwMKudI2TuB1NCVTVTrH2u4d4psJX7sMnGNu+okAAUZo2NBWUTQCIwDrwMPemraDAYBL
+vjbs7iUFcUn9MQMighy8H5QFbMq3j1AS2AaHSO5lwwkKZXZrn6ngylVUM1XsN1U132M4aZLY+CoR
+Pq9rD8Neupx4h9mOH9DrlRfh9x3I2Sy5S+bZPfAoiTvk0/OLQwbRFpW93GBKLqj3ZLuyZ9JFZFqi
+s08S1q3CTm/ROQEC8HrOzkE1nFhxxzXWVrXrWKVJkk6Z+5dkCK/SKrBeM9oNxK153UanfoQEXbhE
+QfsxfolS/oCuDiCMrh6bRwrZaAOI1VhFg5GsYVoMG3pIAmCEBcE1Ndo3sLDy0eL+vI+0xa0Uipa+
+w1w+SKRayJxtF220wK7GIkuDqneOJrYQuinpFG8UrJHHONfpvmvc9rUKWOtKkEAJFDSUbSt4kXzi
+3Ogi0kcLkIA69EgV9sroh4OO9l3iartOi7iecaIBV0oRQwukYa0IFF3bZuhypTIyLQoxnSJDseWE
+Zc+3M5SV+jAG471Q0xc4SnEG2XXHDUW3nm7SOs/a5C4yrLzbdEm9VA4LO+dCnpTO0MsPTbcvWTwj
+oDRNf+C2rjg+ClqmQ66io5XE4bNXmc20bERwfUof5C2SeM9DMjD7t0VvBQfp5fUPOySAm5574In2
+Whn5dCzMkTzY1OhreFcJ8pmojYP7kGbRI3dX/JoW2nobbIFnAh/dNjRkuAvKYL66RUlAFA5aBqgT
+ALc2s8w3VJftczrbNKZUjkE6mS11jGo4xcjGwi8/nNVGB2a6Jb9meqyAIt4W+D127BbZ1vXq5qYY
+TU09avY24xfrV5XcrQFeVScjofoCeJXdSKA3R9jBOGfYQ0jbAvixa5x+vtBoaY9zlBofaRi6L6Lh
+oF1QJB0aI4I+45KOOsakDVstxGh77D4NEBXHeLADa+XZg5uRZhLfYiAZ77gjM47UTv2OSSP5ARqY
+XnoUzo+eZ/eYaqh39GZifIyCYUPXeIW+kT9TuiRPE3apjlQMskHWZt82j9aYNxcnLav/Rd557EaS
+pNn6VXp1V9cT5sJcYIC7CC0YZFBFktw4KF1rN1dPP5+zqrqzCtN3MMDMpmdTQCKLTDIi3OwX53xH
+Xgs378Dl6Kj0pdartaTX2lVRyAZ9SsR5NMMZJQUsaefpYbou7RaNio4F2iG598GH03EdlgWFiO4w
+tEmNnueZRw8gDUtMd0ofwzpDQqIhoZqa4qQV2qOTa58m0s6HrNSqu0JZPvyXIZqr2qJbWlF0EVrd
+3Yykvz6YcNPvsFgURAff9oxaN7Bf1VNS2M1Z6ubwpPmQUmKEKEeziNylcnz1xLHyZJMXeRq1uT7o
+s+QaQJJxzNNGbNOANPIAG9jSh1D+0WG92lS9ASY+6yJaFcHpgMBqR28YERRTGm0I1dKS+9Rpqm1X
+u9NzFlQ19uhxMt7hjVGPNaXQFil18pH8DWiAls1c1sqJWJ5BS0GJu5jUeKQROf78zgzKfVbazH3s
+dlubjjqUvU+alK3rT9IjtJyBZudnUNQz/ZZha3TsJux3zGxjvqszbIpSJPtApea5dKpmnXmejnko
+d49KZ6QR51898xp74M5IcSRtKaM9olbgbuOHCMXSn2OWKpupse0Gz24YfqBS+nSZti5JogczqG8G
+B4lahft1W1bFZ2InBYE3s8euhlc0kkmTjNYqzDqCsoKr3ikug+LYGSZnNczUW00H300KxppHdql0
+C4qRo+/TrrwfG7D3ELEd0YW7kbwiSHgRCgS2QgRxDyyyXMW4J2vEIjC03SSqQ2pa+A/HK6ti+j3q
+NhshvuWucaGHWS0xA2zcI5pJpeIXB9z9RiOl80RMS3IPQcB+kDkdYzFFjMKzQt/+32mOe65Z3a8x
+tgWvWhhaJ1pgsZlI1dzmTdQ8fivm5tSLf+jvmz/nXvzlj//voUAzmP3LJGUA2Uaf98+dILvXenzN
+X391gui/fc3vPhDAKp4jhONInYLqFxrL7BCxTVsIpIXoCy3Bv/O7D8QUP6gqbBuXBoJ1VNZID//w
+gTg/cJUIPugGJJb5b77fjr++Pf/486/+DI60v0hDKZ2wSXiSf0W4HiLnP2sNE90IDXjYOSNdzb1B
+ltg7GxzmXAwTNVjAGfgs3TLd58zfk4VXIRGUAxIAgRR6Bw7F28eIZqA88z1WHeiOS4EP9cnoc+ea
+JG3rMZJkI3HomIx9zfgNWLd5jX5p2Of8d2dnSCGXrkBaOBea1kcyTCS/NhXLIjsVxgPtKtqCaA6J
+pYEGE+Da6QMiCuIFPWEcZiv4uanMBEsxUbNtiJQ+KF2IVnMQbTZH0iJ28i/4BeMTiQybCDAI40aq
+BqaU2KzmWNt4DrjlhgqIFiJTyYyxl5Ms4S9J2a3oE1hNXrOVyrdRg3TPGpJ0ZVYqWZvuQFXTMtvu
+BkJrFaP2lee7KzdE7cM6Q1zh9S5PLEy0wzDn8ALj7a4tKtNNR4d737WiPTEWIeraIb+3MqxmH6SN
+vub47e7SHC8gqjq6zxTlSqLktY+K/tomY2dbwSx+1mn6lpPGrRY4hrXWjCq5SefsYJkwSGrrclyk
+c7Iwk11mgVFcboq0IJkNIi9XnpOu/bqFdYFH6RGs2VeetyUizLYGpz9kSf8M/TS4tF3QP42h3zx4
+vvI/kbNzxljuVMLorzAsLEfW4tHeFgq5VMRWaJ4IWYRpYbqlFp+c4SUeq97aJBDEzrmLuihim3f0
+YOWu6xJFOT5e+hgQ1563GlHPMCXRTODgmpUyNi3VlF8xXs2+9HGQO7/TDdZXhY4nkLnaFfIqDSqH
+rO5ZGqUrq0LQwvzxaxzi/BZwVnHQBts8JXNWdDanRg9zfjTZ3uoneOLogv05WDWVdkd0RXmMu974
+YisvF5mIYejGqlLFIg7G4dYw4o8QCq6cA6zLGrZ9Nzj+EXGmXKk+n1EGcYFy0G/nBGwHccqpm2Ox
+wwKNYDQ142GoJucG1dEWOePjEOZEu/VztHY3h2zXkAV3I9ukXRARwV3PYdxESq+NOZ670Bom4+Zk
+2rf9HN/dtwR5j7Y9HKoglM+hWdvuOpkjv9GkRJegTJN9nvT9C8tf8UqiBkIK3PYQKwkO782qWUUe
++zVb3kaDXhFoScy4pwCaxmZVXeRghkTEKfO57Agmn1RHLgFw0Dl+mMnoycqg+KALnwPNG+nBljPh
+7qK9Yx3k1OUNQHYM6W5Z/vTZeRGwlgm1w+pBYyFoATYEgGEcEGMMksLS75A26KQkcDrcQK3CBDlA
+e8NHmREF3hl6f8Gx5RyQdo2MCLXixOATIFAbGzfR5DanMlf6ug3b+tB0DsoXF2oCWOuytE9g/qNu
+7acYyknQ0j9de2w/lS2rEyXcUK9YeU/6Uhpduia/AIlo3jRAasie7R+jOswreJWuIOJCqsRZeSNa
+72yM6S18M5bHypy9tirv5MnIHbUuUi5W5Vecg/CkhFyVVu66yzymPW9JEok2k6O51y00FfbbHMXP
+RKLM5P3BBu43p8tMEFIDss+QfdMN1ZENrLcmEf6qZfL9ZFphkGGaDtTtoHX5B6Nde2CHEhgvFuMn
+CZq3CZ8HtB0W6tQEiYxDb4VoGDqw88yGoe2BNZnuI1lOEl2q3j9VwoAgScqGyWZTK8a9hhg237aZ
+a+pILSPtjRBRg1gDWTpPCrGYu/ZSl4nR7A83i3E+tHt/5GAEtULUXpsPG2V0o9q6hpit1IanPdvh
+kJLRVgyEo4x6MwwnG3W02EU062w4GD5fkxRZhWusVXjI0LATz9pofVxvR7gs0LsMWdzTjlO39wyV
+kMT6dfMm6ondm2LAER7ZzxrtfRkK7ejUU7ZRWdnWawc2Kh6oKhvvRZDgOraMRD1HdUByahbReC56
+1VvROmkYuiVKs9mBNtJPIIfqMTIpE62YASrgAIHD3ut6SyvQmNHwVWt2/pMhdkPZ34zpEv01II1k
+qNK7KHH8n6r3mlPqWV+IUGqUH96dNQyCvYAMLFzjaWFvlCB2SUk1vIwopxn8qM5+sZRAPTnzVfbC
+DmjOI4wH20DvnDuf7Yp7Dua0aBqgTGekijxv48VIKde1w0Y+SWfOpA3wocfynsWP7AaGI1zD4CKs
+iJ0veUcNAl+BMYk8hP6T/YzCqNETP2dHWDhCHGcnLekahxiLWU/UZkruNS3lua95EJ5KCCEPY2sn
+xz5zUPhnOiDAZYErZNyCFuq2PjL4R4UN/ZRkElR4ohHSt87tPH5iWMPP7KRudrAtFt2raaLpICTe
+aw74v6qfUIwyax+RwMKk28lmpK5nEjVTiwale84bp5kpG1RNNPyAsgvSj0rrsK4OVTxdAw7niWkx
+YEFhTdWRM1R/FXo7/oTbBr48t0bmwyQucPbmJsksfGvWBMWgnj2+/rbpsMYTUuwxxJRSe67Y7h2B
+6IvHLG+59LpBgnTPvUswDeyMSy+9tUwQ86t+kN0qJPr2ZKbYgxaFzyvLodvexL7F/BEcRXvpOmtE
+GB6ZxYuWFOXeg9oX84yW5j2pQAilOBW1N9SQIxpfxn4IHNHKQtb1XUoF4Fbpa8SKpNxqXYfOI25H
+PIlxVNTVNqaLe2rJKr8vcpF/OiHd/0+sI4yJ6rF37mIzDoPZHcIr2cWTYqdaJGcv1Blztf6MwLTQ
+QR/9llxFN47D257AoH7RuCTM1qTx6fGUvvFe4Xwnyba89E3LLdAx47csfbojl3DeT5GoU4PvnHvl
+BE/creYkYCuMShOXEnoykVXKcq46VqgsZBhIYRKNak9dOfDHRhiyNnEsxP60rJ4T/vXeMQgRNJLQ
+f/LtId1nLIQwT6a8qiisyotqBvu27SMP9ULE+x7DRz7roIxO0yA4UYVrNXeKHPG73mUcwIxPGBu7
+1l2e+CDK0NWO9hUqL7NaWtxwfDLk6Oy0eKZEF7piPd0lBKBOoqWi1UHgNoyGbmzIBzoD+9x4nXT6
+QA35REZKTCOu7XrgFfHSpCLUdeAVKq0y2uls2F+TKDXf4aDzYwVe3F489uW8viGx8Y7lBO+QAtKd
+nSrvErHK2IZTpXH4tcZ1MhHvno4Sdw2Om2kb97HccdMyQ8tsHZxXFsMrQz3deFc+UufjYLVM1QBu
+tSizorB5YSGPHj7NG/MrLb3s01exeZC+FryxRBlZMTRMqGASXYeuKfYjA/px8T/SDv7rxSvCKcTq
+/v9pGqPs9T18Tf92rl8/PpvwT93jb1/8e/fo/RDCZekGVApPO9OUPygCjqSvpJ3kwEbyR/wpf/NH
+92j+MCQjIeFg8jcM+si/d480lqbjzCxPPq7O91/9F9pHw/yrVQ2bGigCITHjGSY29r9Y1QxsL5Tw
+rbvNoS4jCGzYezWeRtkOEPKdTyTHlQi9S19Jd2trfbbILL9dOX3s7w27wt6Ak2HHpWOsCsibKvOy
+rZW18UtaJ86mwNUDags1+HvVsrj2GhwdKfEp1xq7tDvXC7VNoXIwyTpt2AcGTfRmYePclcDL+nUo
+SuvdT4vMWjCnCjedlm1GT52i2EqP2Gp1Cne73RNaswduY1Gd5KTZl96NAG27KxHOP9lB5X0kGooR
+KujRxyrhq42ZY7dcziF2HwHk5xclfXWYmphFsz20W4Z/4Q6357gdSXTbNuDnV4GRnlgzuzfgM/v1
+SFYU3i6hI1NVs6jMohyC5Hju0fizWh9CPG+mPW79NEeNNvlR+dhNRfFJ0pl9Qj1i4mZQD1MjPAin
+jXs2HeRHC4OID17Vwucsjwp23EisMUr6IUT+xUgy2tYdGU8Dn0meGhBcBxrY9pAnxjuCdWxiKMmv
+QE3Txjluc5+y8dibWH1xZE9CLoLEid5CZ9B+Gn4ATixqrKvAbfy3cuAQXQyN1L4IqW5PGSXNU8HN
+dOIN5/dEOrjwq5yVprCue8YB+crBB7QE+kULKtyvwQJ1RB0HxjqFKnUgYAy0IucmogtccgyZFZ2l
+4S/5wFu8UFp+b2VGDNwOnk3oKvEEuJkL1QYh70kGqKVK9LntbnalgYK4Z++ydQPDoZNjA9wxKC4X
+QW/GLP39i0uJvZJs/x4skbaLruEWa6fQfB7owXbKQDTXWU52E6Vp7CxrN+wXDBQZSaNVWDl+s+4T
+x1gxwq7XeCc+Ac35VG55Ka91vYv3qnIXvOn4I1uRXREF5n3I0goeh05nSw6h5zIORnpwQyx+fQ5s
+n+Qhr6LjBRHQwzm/ZbohcnYKGmGWhVUTrc2i8aOxmhuPtI+ljpFqo8rYuJ7MMdvEvT0AYiXudIFY
+3sSo6aWPqeMZ1WqwyRvWMl4zL9YRb9Y5yeVsb46a65Z31MzOcQJ6sxl74qrNARqg1SxsKsFtOTrO
+JSkJQaawI6KF5bisx3jVy4SxPoXRI34R7zrktyPvAw7hWvg97W0VxsF1W4jgbE6MRtvQnKFoYHvQ
+PfW12DZmD+TIF0zMxxhtYybzdxeYnMcqSat2mqytDWpSd43o7Dyp4r3Rh4Ob+PFSE/3KQKa9qfFu
+ZZ1Z7tyqRljAEBQ42SogVQ93fmwnSyO0/zNfsDmfar/6qTn1DGFxTuvoPjiE56HaLx5k34mdvmg4
+DmgmDLjasgDbU5as3vk45uUVJf68ITbWcAaf0iE1w3VR1fg8Jh2WUEBs7LGduv7LJ6eSHPE8PXqM
+yrMlavPkqgjM/KmAlLBpHMyTaxtnKNGpbY1omwoxufO+n+fk+9km1Nm09jnPhb2HVWweejkSQoj0
+FDGpsrTk5Zdr6vzb7/jrwNCx/mpZ1yFmWtw8gBAsm8vnLyf+SH4RQ+VAbHUZgGEjPTxLzHsUsS/C
+EvGCYHuFDiGorpxaOcESK02/cbuB7WlVYzhZaIGs9bWcwiKl3fUHSlhJ2j2RNp9UisFDmA3j3qn6
+nUXlV5lTNSwNVb+4TbspQipemTcHIzVcVmfRe1WRistnKzsPiKv2DEwrxMOpOnh6Ex6MKstIAktQ
+hWHlMvd5V5v2UiSiXfM6kmjdJ/GqA3W/xZeSnZXTey9kIOUvYye6DTup/M3ITHUtg7G6TonO2IT9
+LFtqe+ep0GpCjTLTP49Z1N3xR2dTTyp6QoEXHhD9TSuIn+56Qri37RFdbAsbz67h9uMeiw0GA9SZ
+PvohI7hnjxWT/kWq1pIfm4SUOAk3ieXp27qX9ibhkl2nZqKgS3FGruvGry+tQTxJYHrlhRLfW1W0
+OF82+klUoElyVHinkT7JmNgnwmWXpNfIi4at/IbMHu3ebHpjx6YM/c3kiuIT2fRwsUH4XqRT5OfQ
+r+ozK9vuIDD/7UzdCq/8StQ7Jpf7rHZXbReSDF4Qk1K5s6bFUToDsr7vb4d5A9X1uUJdnhIlG1pM
+ZdNRIXkhlvxeYdJeMnSg0C10AxSI6T8UvkUGu8/6rI0J/Gkn2WPHxoTzwoKqP00Qua+mmsAsETbD
+MQ9cgmdc4NEUztGVI0c61dpxTRRl8YjdhL3sUtQdDlFWTTfMETCTMNQGLKgHSDwzUG9gTXBA4W5b
+e6Boz4rArpMNOhwpR04zFpjkgtmOdxvOpwjSDcoVZ6+xoqxRBo1GeA9weEHqQIbjY0SfyLooRnq/
+jLkmSAlMzs18ZgVEHmHB4hwzAz28zSZN+8Jdl79381mXkndW9LWxsKDfLQCVye30fTCq70OSk8Ja
+qfnkrOczFNUd5wzyhomDIBQkK83nLQjd/HGYz+DasIZD3hecuSV+6qfc79yN0Y+c6HpR3XVOVRwn
+ZDgvkuHWqkgdh+a8NmBtzxdDPN8RznxbkD2Efi+Z75AqSCJ4BwyIoiVuda4g4ZWMyD1tbJkd6pXz
+MIpC3iB5t/zVMN9rzMxM1NuYSOS2EXjntK6ELj3fk6qOpxWsUG5QEqTct75k4c/OXpFMZRtReSzT
+rOMMbbNqV/hJv/VDQCCY2eYrfRKAG4NRa9AwyKjbEDtKltTU8BY531XDOBcQGpXENJcUACQoLiAN
+x+g0HbkK57pDUD76XlgROTizWP3Udde+poZjRkLOCm/psPcldG/ym7JtSemzwuQe72OlSKZQLuHh
+euch/BwKvAR0eslJkoiwNzG2n+IgM36GhW1dtyB67/JRZ6VZN2GzYdTufVZTaZwHZnrvXaq6c9SM
+0aMGZvTeZ5jUrAKhnD1kaG2lYbsYwAdaCJx0oo0XtHHmta2ZaldrVYIiii/l3DDg8nFDyXM2luGh
+RFZ93arOixZl79RvQ909CeafK8/V5sGWKeQm811969JFk7XFLw6i1NhjkUSTEKK9fwg85liLspFY
+O0mKOMuJqHCsstY9Iaf2GUe3XEYOVxd9Z/FQItGJ4IbW6d7UorhdZdgQ80XYuTEXb6mWOMfi5mSX
+pF7aXe/tKCyJsPUm9Y4xouQ1hv8MeJYHbdP3kxQLm2kXig24lz8JyJHbJOYVJ+LCjhDvlcybalc7
+eFWHeCkehkPsMIBDElV7GJORHIFuFM86cIEJOeYDLk7wkaRtb6Pcjw4hCvCBF821b7H6JS+xaZMq
+I0g6WJh11r4FzJJeSoXaRDikWHhF4m/5X94EOqj1TOJct/CXjkbp8eHXnDblKhfRrUZ0C2BrcqwW
+BRuBhghF2zpH/Bp+EoP3JwjbLUpUr/H0KQyN2WdbRHTjFADaHNcBIjFqK0z4hngqmsRCoNSokzQZ
+fwQ60+QeTQ5f7EzIVclSIcLArbBxuOxM6AEWRLIePGF9QSt+w4BnYnbOSGDz/CLfOzAeeNqBii7y
+uArumPyPW04eCms/ERdieeDqFtlFt0rjyap0tetUWv7sJYFD5IPVn2QkwDxH9bHrWsBonriYdmoT
+RxBLey+t4gQI6CZmgk3RP+DsHgZ7nbjcFTxWMPTXohuw6SNItQFRMQrZu3bLvesn8sBMz9xNbRmv
+9VqOzxgaSqSBCBaGXkOmFNr+u1FH1jawif/GPT6X9VNOjA4L84lkPgtnYehvPavSNraOdSeqs+gI
+qTgYj1CCijtb64yHkP4FThlQtM8uYRG4NJPGvSLpldOmC8z4Pi97FhNTjxsgzpJs48Tk9dVofimN
+iQHnSSQieeUATOC7dtFrGgFD8Z2yPhiwd3l+Gn73LvX3vXLjY6737dLlFyWYKdZSrIVBdZPYTbjL
+Mbuuey9tyLqYBhonE5Qk/sj9gMthG0n+fYJtnKeMSjACnzp6J0x7I3kDZrExdeW8hFWkb40O6DPm
+3oSEqHTkqa1HAVkgDwl/K4tmH6fNM9u50+SIrxmAuEZ2pL+2nebcsLHleiwfGoQdjOQIbLszgnrM
+tn0UTR8xO6UFupdL1uYU1eA8Vjhg9RWe7H7riqpZjKAntkLZzJRYYV7aAFcUsiOO4qruao6krl0F
+SA5vS8fP4KGzstZWae62D4wnpge7VEiXE+Gqpe7IK9i07A3nMJ9zmhfGCRYxOGk/sE+skIxb1Uct
+ekXCrPKt53jaPdAk82zqef8FtcBvZp1hOWBlCabQvtHs0drVUUJZpOWnjOmeJSqsAg0SWyzW8daO
+VMUpYtBjDI22yuQHpLU0xraQswsh/4AILQ/Ja8lOEgnWdE1BeGyN7loK9eQmxKTeAbxhvM9Er8qN
++CuWwXWSZLgT4K/dOtKvnvl8cXmxWLrpCRAhAS4vn0TXsQ+IUqYQ2Ce0euvxRD8T8do/2plnPiPD
+kj9tFknLVjTWvmFMfuAmCK/sFB8TTG0dO2uarUn1pqiIg31bx4wXHSKZ1KDCWza59t0o/PFFMhYm
+wTDI9jVBfsspxk5H2rZMd65by4n71BmeGPvBz87J6EJzZ4S7wJLZPo3Gam0x3mWBjNEXpBk8QQ1+
++Qh9G1FMEe+sQtLIhlSyY4p8tYv0YUcNiWnJKnBVL4Bk+WeZ4jewqlkKnyprTUZR+Ii4PNp2RivJ
+e1AVzN3a26EeC9GmRCPe9Nl1wM8APDWAdNvBX3iqunHeoA4A3fIouwtyDlEktNq06eYL17VDlnF6
+8phqY3lILGR5sI4pyIgt3uDJpOdHe/FAxEWznlQJNYEzA934mJYzY9Uxlm2q9fYSah1PYJILDuwJ
+gf3SVjxZ/CjFsvUyvqJrs3Y5Yle+jDlWLo1l93sZ5OYuJHZuC+uuWTWtPfKoRNkuN5hytzlB8rqb
+xDDhQGTjY6l6VPNyNYKhPBq6759y9hb4fN4kg5k4Efug4CtC/4hBnICVBCK/KkKm+C4kf6cX61RO
+44EJHwiU2rujL18aHu7HxMiAadian53CxGiXWd856EW1aR0NMqRNQhg607LTY+hKh5fA1/d9Xegf
+bHCx0xlN/hX6ZDJAcYv2rjlqIHZ8DKmmz5ac/PYEhFKRPAMHQfpUJYZ/Z2mdRxqMnZ7pVdqjFUm1
+B5bMZIm9rnmJNatbtkFUPme2iaezTIsjYSHQWJwy3pWsXnbCjNKt1dXVVW7mza6J+mU5UEoOMWpn
+w/ImlqKxvuUJMx9b2rVzqwHwztnkrqOM2UeI/EEXYPnbGRJiyMPQ7EaX11PlHgZGtWRx6N4Zeecx
+IHfiiy1Sa18laXrlRI2LdJU4VL+Pz4Fp9+q36faftE6/9sLGf9QKS4sIAvipOKi9v6DqIPEYvm+Z
+7laDiLeWVoz9LOhA0lQSSTegAPpfMx2Ch4DsRQwNrJdAXIeldouWZnxDMFfWhFrIcI2bemK3MM8r
+memYmKXIt4HOE6J0hhI1TzgFwTGAugYGhCPO0AMYBmJnGzpE7TfC2v9mEZfQWbGY8N3++Uj+9Jrj
+Oa//NIn/+5f9Noz3rB8OcmNhupb8c7CWZ/zw0GohZ5CW4dmug17r92G8IX/Y0OoMBF46+gVTorD6
+Q8pl/nDRf0m+oyltz2S6/l8Zxn+PnX4ZS7nClvwzjiE9KWdR2fx5/WUsJXHil5pIPCBPnE5jKJJl
+EHkHq+WSLxEIk00UDATUxTmPZArrO5yGRzD42n2uRz/rwKtOWuVOYInYfiLK7e6azrrVEUotkonW
+UmdbvjOGQiBkagI6/Nq/WIab4UHV9k3te0tLuUSSJM2dliewHxhkv0ktwU9NEvgSncU5dmPXxW+b
+Ud023JoLrg4LGWPkTatS0ooQxkmuk0/kzdSP5amOrSFcyWoUywwoEPJkP96SyMy6jhQeufMaLq9U
+ZeETxJPPBDGUswraOUUUtfFLZMRvPU/uLrKs6xgd1yIBPH7s3axdMTfDJmiNX0JDvWqpvLoe6I4x
+d/vZHXLs6uQlcjfCIUDrTcJ8HclhyZ2hLzH4CL5R9ITqCw1qW5JsibKIX6jpsQThkRJ6HV9ix0PI
+LnDD1EamLxs+ImgZ2qy8E3380cvGosz0/aUZjuy5ddE3c9DeS4ZimW/l5x3rg9mZ6lnBPcyFZWv2
+2n2nnPS2S5k40E+yccG9LTAmOTjFARKEwORyHdePXs/f0+gFK+l59EWGRijyXdSChfCNgbjWii3L
+QuZ1t1IaOZ+7lN5eo4pI0yNZv2288SeD7DELqpN/xBTTEumIbI786Ub9bI3ar/dNRYm7ZavRHapW
+ViQUIJu3V50c7dleL3ApxPN0ACmYJd7tyhwuRNAyYXGB0ZAa6FTVuOwg3njrURu9c4smzsZ5YgX1
+EnOCZCTWT5z/eDCip7ax6xM4CsJfca4h2Q0IwLgJgxw6VdtrSBRags8jtIizYbm7oXBs9NsxaRnf
+e3GDbEJYTuqsewtGFkez3vd3ce344c4ZB1Ud+ISZiIhdQoNXjVMZ15rW519FGWVISlQAcn4swSd2
+NlJhEA4oklposN6ip4/pl3bvoSEI9nhYqE5lz7hCJmvkfRljBFMs2MkFa8u8ZsP3lDbOeYhTgWFQ
+GGjV6l3YWuFC1rCmyinAeVjcARh680vrXoHOHnVrvI48k9lVcsp6VV3Fgb8yk2Jvhyc7Y5WRO16y
+KolyhK3CW2b0ctVmI0JIkZhnMta1Tz7Oq8LNF14nzkZLQFc+uLdA0lAEUhBkHFEbLzNKYBHqy5xu
+M5xWjcvX6Hr5lJF1cNuAoyrtMFr1dU1IfEiUHOMPe1Uk2ocVpcm9V2o+tUlzRmS1argPGZDVAR8G
+N9hRz6QLGD8PmdmF2ySBodGnZrCr8E3S+2cjDkyN0XGGpXlENLpO2kJ7tSAvLipnO+RFuJ5MYki6
+EuUALKccVhDmOCuuIBN5ZgFpMS9OIortF28M7o00g5PiGmrbE4PNIxNvSAF3V7pJGjlgNOcdDWOz
+rvVxrbtDc4Wyb6AIwi6R09F10rnn6DsFFPsLs4IOlETups3A3jK/2lijYW8rSJNZ6WKgtcVH6gTM
+Wm3sJQlOMnYgy26yMH027oM2dfpn37rJm5qCr19up/9gEm/Yc3nxj+PeZe1goyi20TuasDwd5y/l
+R87eTaMo93ZoIvBaZrGBQwv3zCpg8nvDPIqnRJuUpASukuaE5zHCL1D4bJg6pt4wnPqQcxJBD566
+wvfOsVEqbx0MSU06dBS5JrqfBA9q1CXjpahzndGlz/Os1z2eQqdMmXaguqjt1VgoRplDWXeHRA9V
+uCWsRKv3tS45LPLSPzLz7Do4BfNpon2fLNX3KdPMB85AkLi2V+3oGDueSwQ1dY3YS5FesnHDJL5r
+Yw1LbloJZ19XkDnq3g7ecX0VC4N0JaYG6irF29Aj6dioKOLdjLurOVnvKEV+NBinHyHrxHhCcRcn
+Bl6oLAswxeeIFztl3jHlRkXCcXZl5z65RQgyV15H/6IXUbPKBiZCeW4cTOW0yKaK/LHugmINAiXl
+s9pUGUveRMd+QB+C+8SeMOs1AAmZs4gYrS0bJE4hEFlxch9hC+iPJENkLJCJnw/lYKwHaAm4brWM
+nUGQX8LKm862T4vVCMJ/izo+4ruxzsrKJ3ohAreeORTYhFdk8smCotIpphpFCPyTmw5t3gdrTrWO
+8vi2ZhN1sEWEJjHIYv0kLD25BrHj0LjUrcDq1WZTxEDdsI8hcR03uZtpWwJrrXfX77StrqXt2ddm
+LyF5QO8+Ro0R60+lXkZyCkFRwI3xpRK35AmkK/Svb1bq6zsxNNm6KYjSWRhZfU5DBMGRNLZphlZM
+r/QDtx0zTKV1Rzeo3JU91NW6D5t6iRAgQqmDBX1kYyqf8P0M5G3EP9OA698iR5PfxBvXmhuiziv1
+B3IDC9R7w6625njPtGQUZn4EQu83dqW9V2YM6Ce39G0ZtgccZ6tQx7Rs6Edwtz8J/ILfGe6LDriG
+bqMI867p3tlMKSU3w6Q+snDQEUuan4UVeKdElQyCHVFvXEb8O5ibr9JtmgOsk27ZsLz/GKE8HDrb
+bW6zwoCW19CFxyUi8yxLoNx3zTvFokRSan50FkgwDarFskoCd5XpUXS0Yu15CgGoZbhmr/PKOxHA
+R7Jaoox1Dl9rBZCdyVBb+ktofTmrx3pC7KpYI3YpvmpOK6uP161boiIl+bBs2tNUEjc0QozYOhYh
+idlg3AM8G06priMXyIz8ChOLTfGh29fEluu3CTu2s2R6y948wu7lpsugF6gUfej2B6JjAXQA+7U+
+Gz/t1obSy6+kC0gaTuxiQ8BOscoaEFJmZvC3s0uIaJJ4W/XYtJapMsbnATkgq+VhNH46o2rLRVcj
+Y0O6TOw560UiBaI4plmN6K9JzwJgRiK6vZAguRHBzZn38z41O/rzHV3Pt3XyfXGX35c41mQudNNJ
+A0KWvy/67vvSn74LgJKALTKrvwsD67tIsOd6IZwrh+8T+r+7j/rXUz+RXwKV+5+3WodXMFh/+z+v
+Wflvfzu+NiGJ9H9qu377+t8FUPYPx0XhxDRZtyyJxujvAijCjD2UR64j6KHIiOD++0MAJX+Q5y1x
+VlNYeTRkLOh/77lM44dBFsm/s3dmu5EjWbb9lf6AZoLGwUi+9INPcpdrnkMvhEIhcZ5pNJJf34vK
+rOqQsiqyCrho3AtcIJFTSKLL6TQ7ds7eawuEUxzlpESx9G+cuZwPwv7/bMIGx0BkejyxX85apUVM
+hUKycwJcBtcg0e8CzTpoaCa0w0Xt8ChsA0y68P4MHc8r1TnZFq1zc5zGITxUUdTspthzL2TJAcec
+Rm+D63bc52gpt0YfogaojYhnXbli2NCW5+wQQu1rqn46FBx2Vzkiwsdx6S17jAS3XWPGe3SYzaVQ
+VvYYUaFjK6lIG1q60xr66DGIguBQzpqW79LFLsq4PWV4TaSECJIXf+l2ewlmDpLmlyZ4t/TD/aUz
+ni098mFiXaw+Gud66aFXH+10zxf+GRgcxP3I9vu36KP1jgbEuuuXfnw/Ncl0bJohOU6Q8qCEc/oI
+gYafTDTzHXzQa+lj4Pv9BFVlVqbXoVU7wEGYBcBbGZAKMx+AUgnRsyvnb0iU0y3TWnsvlolC5sUT
+1BYsWMcu6sj7Cn6fQagCaKbAX3Reto5axVZOarChw6NLptJ3B7cEQ+ba2PgR+IH0Y+KxzD6qtMwe
+mSrXjxyd1d5cZiQeAxioGC6wzWSZpUAfBXZZo2F9VbYKqQuEtE4YOmQmuFSixjR4P2oTvOB3hlF4
+4zlLD9K0WeWQu8U873NcTkuH2GiPknyqF6NOMpd+GHZ6o+j7bWJyPgB9zk9J6riO1soGloU5wdiX
+DMS3KGnFZs4ptSFXQHeXFk7FKFHWDaKf4r3hQIirvrXrByKnaRr6+H2je6QYPpbnwcKAMEtiZnAt
+Fyh3HVbPywJW1SEomvjKZU9Yi7oNY253pXFaG22F0l8BoQ3ZOGg6YUxx+JHWVctLfFFkdiPpMHBR
+lVMDcMEz+pHuNTlghBkg/mem2h5ix5h2RSzC96mWvCbIhC7GCwFIay34qMTbUDfWjSe78IXuVwZJ
+MjT42ygsVBQJGWpxMAWMPRqCV8KkX7grVXtdWRb0tDmoRbJTMyp/C1PFTeLk0TvmrZheAhSmyUrQ
+lbsVgD3Mq21PY1DPzHACP1dqn/qG+YNJ/fQyMy28t7kshFpD2O8mU1geaUzZcCjhCukVsTIYYO2k
+g9RdD3k/oD4qfXuT0x/2Vz6stGozDq6DEK0Ywp1leL5zFSeEiG1og0YQ3tIRzk1DkRxv8VK4tzYY
+RbzhtVEwGXW70tqmovHpjo7KfNNTU7EDJ8JEjj9HpOFGQFtRwYfuqZiWkwfM1eAmH8dXy0SdMQmc
+/ZSJ+d5EzHYzQsk8G1WUbWbROFe8KcywMfGPD6ORRi/0LpMDccrZoZ5CDLpIAArAEz3hj1lgoQDs
+Cn7XGbjE0mzmPo2YaY4MDSg53alNBnAvgaq3GuXLHjEmgiCOEBtrqIO31kIHsBl7A82zl8TfQc3o
+71GYDpRl4XQxM3y+SkrAnP3kFlcpLa1+FbXGkjYpJucZ+LvNzNSzC9hJhBue5dwkHDtV9MwPKfa4
+e82rLhVo+Z3gGYNAvWUSIc/mgamOr8gPSQY/P+sn2332nYgjZ7lMrb0uRYnYExuxrT3WHnT12bCG
+eomVZaDlfsD6Up1icKrzjU9/Ntn0nhWepak37ieZ+NuYSqXeQhUKzyBB5AgCAYrQLm+9rl6sRpA+
+aye4l7YqYC13wU0159dTWTITGEcKHccvd67hT5QgrqrvpAuisqhzyKeOk7xWVuxgC5knZqjKPCFN
+OD8MqQ1QpsPxDY0221sJlIjcjTWnukZveNTbLRhUe1VOmJQon4xTGY3OtzzqcuaRsdOeuAggMVjl
+yYXBundemFJcBp3RoowIh41Ztd2Nyzp/1URDCDmrwjs/qKw54XzoXEnlZHcCF/+bID0V+V6SDVsF
+8/Q4F2O6NwMz2avS1SelExmnTMlRqWurBEbGcBg8ri7S8wgqChR4W8/fIyPo9mlWJDcFk4ID7pPr
+YAabsGG1xKWIocX6xr4NeK3NmI66NJOuZxNJJsRP3YCwNItTv4eee4mOeGSYXcXvAMSjG6Zc4Z1V
+Y87k6WAqHumOiWbXOhcCl8GLLgr5yLCH4E1z9tf4TYu9Q2fUWwWlgOQnyRvhoKu962K0geu2s9zk
+9qzPhtZw8FzGHlKdVISnEUdo2pCRxsaRJDt6qPahN4YI86jo+x1MmfzG9Tj+JEmIjHeu4/YNsUES
+X1jeML8AVBToS7PZtFZmVrnr1B7Hsxgw7TqaQrxNmBfOyLIfvlnwxXamY+KeYBc7gSdbLWu8H9dM
+0MJsLYRTIpW164uZDC/iEYPGerOHqkTPz/KbdROyKtOf51Wj/O41nP1qJebS2g3ALU9nf1ZvBQqR
+XSW6gQMB29AK7392YiMROY2Q/7xYCQpTJldWdBkBiEHblLfJrnEBqUWttGG+OSCau9pTR08LcRwK
+VJmBAVisttPkZHIqVjqD7zkQkIGwsQlHGsCxBAzKxLOTfsO72Tf3oS7bdcF2so5KmIfZWHU3moMN
+9MnQu+vSYLiKB41uoJjYrxlwH33Cc5FPl8TQGw7FQId02Euldxawr37/3y3jl/PCa4UbP4mYrv/X
+hzEed/bmpX/59B/bj2jCa/XWTjdvncr7v9Wly1f+q3/4H2//SsAh5Yj45TDk+NKWXDX7bGv//bv+
+qMv931yXnhRBgij/ifVCB/p7vCG2dpPWO59p1KGE5gSUxn/U5cL/zUExa5ofMzPPs/mjP+pyIX7D
+j4Calmmaw7/Q7frb7/9HM+x3zsA/9rUvAtz/qcoRppISxBwEd33AT7K/CnQlWvTaA1PCukkPn6A1
+GWbvgqWX3EG67v31UGXvDUKD3498/3Qk6H/k9X26svQx5nP0YBhDHPtyXPl5BoMd157lnKuthETx
+FnJ2WPGU8BhpdxDRwULskq4SfgN75SXGfMOJljUeBuEMHLmr35HeItHPUEwSh5b5/lPlT0xVLQcb
+JpW0U2yiiOxTnIqTz37ejB19siHe2W5I1kdLnsIsB+/U4Ly8i7oAeQCPFE6ACUrmKNtLHUFTlLb9
+mpqwl6mydnRQxbo3aKd4TXkzFUsZEplbaVgmaClcnM7Ypjf2KGgZjuNgXwhKo6s8opHksYksmoQU
+FIqfLjIyrhdOY3eCo7S4ntxqi+/yDIVqd57VvBWIwMS8DkfOO0CHEr5Zs5+sAT8Pr7Y0nPve64iM
+65SILhPkN2dI8ujCJQg7LdQccIEskKFW76Zo6tPoIYGsf8MeOqKdietNBCVbADC/nqrG2YRVz1Sd
+4THu4pZWIppfG7XwwjnQRte/h6MVjACnAoTjUdoHP/padwBBtQSS3wbmPTtFx78yc5ObsLbjm44l
+DESVM4Hkzi3iPFZ4NRehjB8fLdsEyAQt+cxygMnZhisvxqRwLs1kBjduZZN7hfTHW+N/NM+SD+EU
+o/CrMSK8fD2zdgCyaSDLSEDjAWrysDypHDWeDanf7wDylesFULRLk34+llgu7pvS99S6qTsc7J7t
+Vg8craj6e8MHA5zp2jgBwh5UV5Fl0xmLnYw5HlLcHoNx2RRrp6sD7A5AafYwKpIaJ6c5PxS5RRgC
+WicivtYWnL1xBeF+uuTrGG6BdRBvruG55jZSQ0meWB9cxVIDpDRJlXfXCmb52iUv6KCYHQLoLSts
+JxHHIQp+07IJaPIgMFdR7T64E1TC7ZxOCPJw90KJH3uGg7LtoMlW8E0OYdF5EF8rtz5H9tU/I8Lh
+g5Q15hO00/gt7L36lXcmuemycqlZXabszZQDgU8cFT+BpUnwDaok2lmQoXDHmmK44oTEVWYrRtkc
+ZgFyDxQvz7p2ulOJgAZLNcNRhC9DipM7tpkSEMhj7WAgTbdWNds3JWoPTCXC6pG0kn1esPUO4ysx
+RDLCYaLr6yEUwXPnkxzdUkj6W8dvK2IK8BJDrYjkw9ATaOIpVNNbhQb0paj67l5HAUclC3LpS5NQ
+pa5qskGZwLTYlSV8bxNARiPejC4Rt3FfFw9AqcNrSbXyVKockRMkp9DYWNommyJMkShjQKUspjgr
+bivZONsOsxHyQvK4UOrhjUDLQplq7/CgMr2UbW4IOrEUOlEs5Yx9ijBHEQ+gSOnCCrQxEF0nbx6G
+EzLA2xv0Mw2jtMjMj3OWjWIBFrOKZECSNTo1bVxO9QQrUGR+9pBOBgJV04Qru5alV72aZltC3XDt
+Yo/nkQKPjBZvYiW0vIMqE34fqZaghJqR8ZVR5DGDK89VSIpcgsQYc+rrBK/7A7cUbn0tC4YYfi23
+oSPb24hp08apHYpk2y2uUV2m27nupFxx9Gye7I7dhMXMnL5pPHfPLObcUXjqBl5PTxBUgo3WCNbN
+EKXUXGNNi9Lwi3Emx0z3aNRHXqkBultFkkqeV7icYYeSZWEIQ7dCXD0PF7qX+iE3UT6vZwDtHdAD
+jkd7E6vfN46vAwN45TKdMYVRwqCDgYYezlJXBsCVe38aIWx24eChU4Yl+6TBkP5oohlULq4RlnSc
+PQYKMosM0DXY8RmHlt9O0UHQrofabNs0+gFUx1eoyDV5BwgQTqtBRvFJl9t9cDoZCg/0pARPV1sV
+CcK7JjWgRbRjuIaj1Xbb0irDXVcCd1zpDlmYYzcppF6mlEQ/2otFmQ8OI+QG4h3JB5VRZIjageOD
+Jp/clZzcji8RLoTPsSUmo+1Idvd7fz4NaOesa8sPgTS07bM3GALvees9QGErTgcgqwydTRZis1v8
+sfHEDpqVanosfLR0pKwk+oKYS58gbJK+7+cyQxM9ZXHTrGzX8X5UpZS3Y2ZhgIK7A0YUjhT1rfLa
+90kN8TXlK70BJiRoJTnkX/jkrRP0APXWJgPosayiJfnFZ5yaemw7kcyXUWU5H2mXw7j0VHdEH41c
+mlf+QnbNBSaCcKU8051WM+UXJ103v3BC1emtAnm16LBRUKORcj1zH0aTqVcEQYQvZjQxRVOyz6az
+Sk45AAs5xI9kapncaD9P0BGPI/LJWvC7jWE8PS0ckDuW3/pqbBlGEn06favYn88ksBASPHIr/1Yo
+JLgr0c0eQw1TzmA6Uy8xsdIIhtbdxPljLQ2zfdbK7a8czxguwjG0rkyvI1tm0sgQw2S+d3mQXsFh
+hbB2QcPvxio/sWBR1oibwe5i0sN2OcPLpLnSdMw1AhiGoO87aV0nSDtuq0qogzKtLD9rhsH75tL2
+eJ8z5K6Imxpc3QJqOG9cGi8DrJ44Xucwjw6RM1UU+k+TqOULu0tyLYWIR5YtMkVG4sEQKmyqvqbl
+tGqQtl4ihqwWN/fsjNDLSnD9ht060DqVuxkx+/MQ0CFDBZq+NFYQXlRD9UjcAYaCFoM1istqnRRw
+IHYUBs0MatTwhiMdSgmIjpnuupmAH6yL0EkZN46ECxW8E6IIp3arasMGLW75r43V28cyBtuxYoyC
+iiGsOOw2hiHPlCO+NTJs7lH7Od99ZpD53jP5mG0DvO4NrGKKBCgQXv/uSyNtOLN5g9qiuPNvTFtG
+4W6hsEwrnFfg7eNRpTydtqKJqDXZM2DUClpwps+ok8iA0aiOanCcR903fKIANZQUQlAh1g5Ax32b
+m4yOAEqwXbLBi/c2A9PNOp1HT0lbwvM1lDNeyoTQHlrTxbCNE1KcV17sCWAMYzGdJg1wkDBpFSYF
+aD8ZKhPfXNdu1j/bDTFDgIcS4zkyZCXXdjelL6O2WQUCq6DBI8jauC0RTDv7aKipTUAJ6HudMWNa
+4/IgDG1CKB2s+AgwZ87SdIrOJ9u0b8wyn/1drqXOV8mco/JR8AkPvbS8H4RXMsxGBEveQb5pmzpY
+272QO3dw4kc9WkswzUzFRltTYGMksgIETQtjYaQnigx5BgMojNdJRPU3kwFd76IOdgxrlWKZWkW9
+X+ycBKgK2ZlE8aHcW491ZF2q1AckIV1GyjYGFsOdsEOM5T4K3DGFf+s712ltGFtdlDhyujbfekHo
+sOUOOMdCF0mfBwAUQXHxytlVPPJJtN910qXbdkhsnrDKC6481bZnaYxGnp+YezezmBJk9n0Q3xqT
+KM4tpXn/eCgeRkezXOU2SZAnfpdOj6Hjd3cd9imi6WZ3nDbAFjqxElOt3oFVqlcnBtu6AmQSF+vK
+Dk0GhJxu3m2fYCq0wXF8h669YovtLAfiqU1PyVo0nhgf6dqDa8D0KNSk3xMDsHE9N8WtRnSAML0M
+6QVCuvRg3KBgpKjs+9HaK8gZ/mbKxukUsBU6XGAbSH0mdlrk4RALXAcUI9tY2eQXBdV8scnmdDAP
+bpu320jI5LbOADZVwHKIJIOhTwwRLR2THtxWY7BbV0FqEzXXKG2CP5Bk/+Qhs4txSkhG8WIZ4Dkb
+FuF7OFEJslGidInaIXcYYDeoiCJI5AQA1agmNoYz8dZ6TnUv+qLYETadEYae1eZxnMd42PZdGXRY
+m7v8cVIIm8h+UvFb5uEWRLwSUhWVxu+TCBP+bKSt6sFUdn6nMUj9sIje2Ws82fWBHNPyqeRkXEGe
+adOX1KkidHYGSg49ZaimbaPMA5TvpmCOM1AeBmUwkaAFY8jeDDp0WBxQIMK1rqrmuiUnEm0uKgeg
+76QcbqQyOOZ0TosAyAPcdaT3jKZrgv5155WtvdJG/kbfePQA2fhYXVrhhagjCvrEe1dG4lS22r2o
++oESMu7BUDEL8c3TEBfxsiy72aFP3faqA/mIQJwpNPfR5ZiH9RPFnuWYB+1HZDYZVfoDoOliMfYS
+ceSU7F6Tc3QUPh5aTbe7oIF/McYZOUuy2PQcvraVTXuxc3D0VACXLRp6K23Jy44H4DIxQp8Qh74m
+6soxOTdQfrTV0NGp9Ppsq/CYLgkFTA8UE6Bx0CbBlG1yUjJGuNZOX+CiaglkFVSNdL+nNuQyk5Of
+VYgitwYk4hUKMYoLxH6XDB27HfjVPTgqpkbUl1GX6atStuaDWRYLTsXEjVm03SMWPBImEkveoAaA
+m1Sn2DrK8dKLjRHvsqskwVpjcADK7oTUJ1aETcEITAhyTXJE666B6iY+Vuo2X1p6VXA6D6121ih1
+UPqzeL/5nXfS+Gb3TrRZdhUNYC77AV10ZQz+qUfX/snCHvXDZwNde7xB0OMqvgTMELx/upMk+g1t
+ZlzNkjEqqNca2PMQd/VdgTRkbzUhqkIN9urOLmLgytiWVwwB6j2mu+G+9prsOVTmrNeWOWH9V17Z
+PdsZxyAKgGSwdmWIJ+ikTTPts5Ja46ZPnIhUQ1XnPwzRt2cTyYnJaohR4yEVFSbVQD1lepcPVJNZ
+6gfXiGr9dCf8RjEH1QNnHLOml62g10PnE1QKm2zZM2sfEAwzFFIUV762NfMOW3anONBYdnpe2rde
+OlCaR4X5YDOOBh+KAR+qi6iOYwLZ9TbhY1bFkHZNOxOePowH+dzT1nyr3cQKNw7qzWnjA447BEMw
+BnuyUTvk3WVMEQ1OSL75EajehE7OsdOdvmDOMzM0NGMKUyUWaXjhEK3sRE1CMpdT7Xtl2zdObw7F
+NvJNlsTQB/8fEVBDTnDdYSxLCm9yT+gjczhP83KwAA9Y5plqazDz/UD11PtxSwfXGPtXrOF+f/K/
+2/r8ufP5Xydv1cVL8dZ9JYP+X9kfJYv9VwqG41v7kn9pjn58yx/NUQ9pArRHyCg+AB9P0J/8e3OU
+9djnQCkA+DsfYM+/NUet3zyT0wsp8LbvoaJBQ/FHc9T/DYSYSXNUWPwszwLo8m80Ry0Ji+ZTe9RD
+rO4KBFp0Yun1yS/ihUClhs4yAcEy7GlUVtRkqsJOvca9p87KlP4VHh3rKJk47Uny6g8ICzJiyYqg
+xnti9I+OppJclXiVnmTNxsAHvawOSL/QWAd+RvR4Q0Nrh7nSvzTjXvqHQUqdnLVuU706s6uOHarV
+9lSZkvaCqhI17CICEpCvYu1COstKiAEoqVOc45zgIPDm0Q+gGm6B5cWXyLbstNWrHrZCs5qGcSyP
+mu7aPVjBlAxvDgtnLmLx49w1rYKuYcrHZtbWY+hZ/l0XG/oSVgVQgmFp8ZEpHp0OwicDM8nibpnj
+quDUEtl8QXx3Oa5IDcClDVHeGU7RPiO3IFyiZdI2xdatWXKI2mVZkOTwXJBAr7JI0KLVrukRHpzF
+Y3gZe/Adt248K8L8CgczZYeBXF/KofBQoEqnR64dYrxZ11UGJI4TyUhSKWUE+axpUTPSH6szSxkJ
+PtVkas+qKTVdGDLI2NfSXk7Y6L4mSi+IBVhQrSTeUW3lPXaqnh1JM5aBW6Lr7DXD5VUzKFZ5tZm6
+jAs4uC2fTGrOy8wIgz13xrnjKDHsp5BJLUf54ApFLIrMJEjbcdt1ZnVv2TYzF+K0EUfKqM1OiX0j
+DIIZ9whsNfOu6dLJV5Y1hpcK6wrgHzXy1viRj09UpzLfKrezHhuVqEcKAwfgAoA6HxZswcjL8bzm
+mBaqvHXiokGc6TeogWsqdH1wxj6eYEdGHNw+Fk73YxFVy3oKRK7au8sa230st8Oy8rKzsAgTQ0rv
+mLm2vgA2EVNFsV5HSDfenI9FPJxdKiR6NCzuqDeDgzMY6bRpPpZ/2BCCr2NPaD62h0KaNnH2c4Cg
+VH5sIfpjO5k+tpbpY5tRH1uOWnaf5mMj4iDXnXb+PGb0ppatiqR0ti0SO9W7/NjM2JHKkESMZZMD
+CgcdxVr2vvBjGzTtMrwulr3R+tgmabnxDOqP7ZMZB1tpZLGrNrnMfqiPrZYmFgkg6DPbDR1EeiL4
+oGM/W/FEF7dBkJB4zOkDKwagdoujDuVh+lDPwUXuKQQcqtUeTEQZ1EfTom2gPEmMDeymvdmZ6UOJ
+v4Dskmneeokzn0VBl3NkZuNvRits1kmmPX0+kR4mrkWbVA+txlU8EK0r3EEDaUfFmJ46xGTeRjGS
+xbybhpM0pGcBY2IJIcpS99xUfsIO7pem5gKQUFYmsRD1dxv65Zk14MlfM2Eo1CkSVUTKqMXgpzXT
+NBAvbE+jzHaDItuFY9+Q0n8s0iz5HhpNfKOR1n/Pcg1KnsIcCajGDjpfJlkuprXgkVG7wK2BJVC1
+jhz7gHnY/kFiYp8J7aCqPDcMI33oJ1wLoPzQ2+7UyFkBN2FsKewpqJltfxV2uCYWdBJ+b8RfL9VY
+H8tuSSI1EUfQsyBUFo5+7SqMm67Lb7v6T7cOJlPVCmpJMdZXnTX0J6IGnPr/N/d/afgJKw2p4D+X
+J569ZF388kO/vdWfZIm/f98fO7zzG24uPvqetIVvfww5/9jhLYhtwpSm47u+HXzwvv+2wwt2eDcI
+oHajrAmAgf+8w9PBAsWNXNGzHEgt/84O/wVQRCc3wLfseaaQ0vIpHCglfp5CogkPmQXSVZa6OA2K
+7gQdU34WFe1zjwUT640J/Vd/JDOehD7zJ7qSDxCozLOqG56ItP+m6has4bzw1Aa175v+iowFRm9S
+LKRmI9kwd3KICMufeh+dhhlkT5rGdzBMp3YgkXwpWcOvIqtDp5c/3Y0/hr0/+y4/M+c+fjnfBr2E
+D8/2EHJ++eVSM497InidDUapDQ4DyNLvZVtfmdJb/3tXcriTLgPdQPCXgwb189sYGRyCMSjRRxQI
+8SImcKVxNvXVRtTR5teXsv80snYWiQkuZXZr/mHhIPz5liEu0oWBMmNTyuHVCxsPHFb5SHgfa1cg
+DuGAFyyXJJDjcceoMyiyhKTD0DZqYsirmhQaVZ84ifeNr7ory+LccK1547rtU2ToYyW9F4uZCGsa
+lLrqe0sXb81MkzCosjmb8FytYKuQVW2byJ9Ud7Dhl6z7IRu3jpnoTRxOL3KYvzVNQofPo8eU0SX7
+9Xsgljv3aXiOijdAOUCBi5OSOfrn9yB0vXjArhTgVfJPYhzgohibNcL9XY1gNKie6kKioCHxJaad
+swBknaH4kaNN+vUL+bjQ5xfiCWFbNtx+DIy++PJCpngcoyLCmJv3VDl03lGHGd6TH3Xoh0T+mqsM
+qT6tMNwrrZrvKndi6Jd6J8j4iI0IrGtbtbcLaWN0mxPkZy9zGj0Xk9jNuXvzFy/2T9W8ROLAc0Cd
+T8gAS8jnd63EUWlkULO3pjkzfMXMTW7jHeFft40hz5Gp3nWqOqSB3M+jPEka8wH0OodSB6Yh2mMi
+VjeDmFdeDyBgzom6kZDo6tb5C23En+6uJznUoBSR6B043XxEEfxsT40aj5ayZxCRkd/WftrsEGVp
+fGLjpV4OBCF9ySKlZ+dISMZZOz8PzXw7FbTYOWP/+k1b3pOfb/CX1+Iv7+lPr8WUtchzLw83Ie6Q
+EftUFghKC1yJvnXS/eXlPtakr9djim7iKECVbn2lpnlMmkmI8YKN3VP+guzDyt23G1XAaJ+cWxHl
+1s6fimozVEa8poeSXDH0OnDIevYmkAVpCmgw0gXqg6B8IqkPemuwK9LubsZ9dwRyl68VGFiAU8l1
+QAW9oYRZGfZ85vedsyc1hjm+INWspYuAr5Q83UgdOcEyKGE+vMVsd5Y3BglDaLxWJB51e6a90xYL
+D+5d0kBXzBntbW/PV7++EZ8Xc89ZboS0TMnoXQoP6ObnG0FbP++qnhuByns7O9EurS/G1N9kxfmv
+L2T9+THxzKWRhYCOC+HE/nwll3Roxpk803bqQQzP3kpX0Kn0scTMga02pDw9pqO+dYjO7dV0Y0/W
+t9AvFuVh+NyGkNzd7kfkIagxM0Yo6Nv79nwZiP36dTp//mh+fp1fDudmGIBFpveMpEXSItM75luQ
+89PiKWSDXuGrxSBXDwnUk5iYuLE8b8d6gj/TPEUzeQyVno0LRCYGQPXG3qPEG87bri02JCJmZNz6
+4UnUSOd0Rvf7oLRTreumvxgqDhtOrToOWcQFGFYNNDXgwtIcUJnPE+6fxrGITMe0bWAD28JrVYg+
+q8exT1/CuF78f3rCF6YeLBSJm6U9/l6gkUY1HLW7UDXREQv2vMOD/fDr9+zPHyKqHdeh6mGbpgf7
+5WnO+oBywy6DTeSG8CYzFsFhndgeicPW7teXEv/oWtQcCGro3yD0+rJPj6mJ8cqugs1gzfapUvMj
+0Ez7WDN6fwAP6GBTJJ6gnM676D3y4F1UqA1WVsAGq/uq3cyTkNwUWuUimP7ixS3X/rzKMNZ3eWoR
+5fE0fS378nQQhQsfE1lKfjrB/XaN49zc/8U78LVSWajCJl0oaKvCoyP15R1orYzhMwNxdOoMG8dF
+Ge0m2SZ0Qd8m8dJUUDc6qusXsv/uUz1du50NBbjihOMQjNrMRY1eOim3aL2uUMDHZ7nRg8cIMRX/
++qX+o1cqfYdNkY/FIi78/Mj3SILz0cUy6MuKVSXBxJKSwBTT94nQx69k7O2Ifj/6MN5+feXFe/vp
+TkCwRR1JkoHLrux+XWxgx/VzRWDTBnrLQ6g9lhgkruSt26V1Q0AC0+bmLy4p/tE1cQPTLArYYen5
+fP5tAyyDDhoo8K5NeMJ5HiBwUo+nNf3GjZVQ2hfqNc6G+yZ2XtJEvlhooNah8b1HubqOjaq68Mfy
+PcUGIioid9O7X78lzp8WYB9FJriCZREGkfHx+n/ac0ejEfCHegNrudqgxD4J3XAXYuIG9RBL8Cgz
+VGY+RAxrIS3Fp2qWz13Vjrteht9aKHor8EY3dKLe0zjeFaO5iwYO0EaWXMFNxt8JN9KtklVQV6/o
+Pf2tB3thQHB+qPjjGTXQKTB6clmB7i0WwV3mdm9TYd6pyfkmOmJgJgSibbZzmDtvB7vN/uIOeUvZ
++OlTgY2WY4tHkcuzA+b/8x0qE/BWvoi9DVEld1bhXqPJ3nvlYCD3G3O4eaRWdG58Xo9RvhYh/4cU
+emBfebfto+6mb/UNHRo2AwP+aUIO9Wi1bPAIK338kx7Dnk1B0iuBvu1Z1PVLsjGLd6NBUGgpVpBa
+Qe47eoN+/AVIYrmSkX872CQJWcm5wAub5dahJcpoSIkk0SZdM/odP+LFe6Ws5qJVyWbghQqzIGho
+PBvT9CzLcS4BBXsZ+n5j2Ixj01Kf9L08J+bmpOEMgr0581aERcw7p8S8NNrNtjJMsTI1Wc09AdiT
+yMZdjKPZHpH88EfQj+pX+AGXVf7kzcQ09W+//jD+aZP1bcplHk2Odou78MvKoPB5l15jU4+RVzfv
+XW8/VPsGxQy50R9X+j/tAv1/ajpCx8NybQqof95EuXvLX8roazCa/Pt3/t5G8cVvNguWzaLAzwNk
+wBPxRxvF+w1ajke5zRCFQ/hyHv5bGyX4jaEvMwwGyBzOyK/8extFuBB1lg4Ljnq4Gu6/NyjhJ355
+YNFw26i1WKycgNwc68vHJMn8pLNTnp/O7G8kHJJ9gYQBbRJdh8Ao9Fu6OHkMGQRMhDlQe2Pe7YZY
+2ns5I6wMcBOa20EuYGQiy9zrTup+J+awBOmGthEYzXjhfeDv/AjEbBhUu94P3R+tFVYcFaFk8SPr
+/nvH2LI7T3Hvm6t2TOQTp+f4oa/L7rypWqoKKKUJoD9l+kdvnP1DojXKXexf6IxSShZGEpo5i3IM
+psylfkXc1W6J1zn6NJmfpEVMLcGjFgJH9BXzapg80HrSx+1hzDUC7dZpD7qr0vuywES+LhvJYmvl
+I2mLhuMb5bokK/oyGx3KydQRNcpZI3DPVegn5cnIDnlftubwLcCPAj/AS/pDHaThndlDFVyhOCYo
+NmlkfDFlra5WyhiR0oILTy77PB8eWloTGQznBNWFOeN619OFmMRAgm6nXytMjM+kw3RED+Rdd9kT
+vxtvdJkPSHuF+xCagJd72zbu4swzn4yKtOMVm9RwmJpBc27HldfaEYPyaeHTRnJcXnhu7+qM167i
+kl3Fb/eVsqozM08A5HKby+9S1e6hi02UiQMkF14k+Xorkxysk8xMxaVVBGi2M2+aUKIv+a6+QWRu
+BFjyhMqBxXcS7cGJyYsbOn1aIYnYktIMBwW15o0aEwjRaTQI1lYC0AoDse86UbN+ieImPQXtq8/5
+QCmwc8hejRNZDM42WsC+MONYpDtEqEhjNwF4jr1nFMkDI2VCaNiFj8Ko8hvDAFZc+GNz6QV+dFJB
+ZiDASduXcZCBoPORfSDAJePaqYhqMLqGWMDMfG7meT6N2SGvKrtMz6eUDyoMdu97nxH+hGyxO2T/
+zd6Z7MiNbFv2Vx5qzgRp7Ac1caf3Hh69FNKECIUk9qSxNZJf/xYj82ZKIT2p7kMVUAXUJHFvpkIM
+Oulmx87Ze21cbHvkTg/40wAsNtU6TPv4BokwUgG/kY/ALSFf9571nKAcOiV6Y60RvVRbh7mY6SKe
+0HWYcojOVobLGIzH9K4lOhmead+VFgoqO7kvRrVvxvRGCqKqYvvoyC2HM1SVZc40c/QIFaWHznmn
+A0CpC8EWJNsoeeB74F61RuHcwXdyyr3ejekxR0X+1HJ0fLBIccuCyiThAX0f/YqVHE1CCIgDRf5d
+6/WeCQFZsnx8UF86OFWC9G4iauj8rAoYwO/ox1gXorKYczR1TrZxQW5n6Krkqz7kkp2YSCHUJCER
+VnmBSLBHNoQEx2DG3yUsFBEJQKi0bWe6AZsR31p15gRuGrJhcq6KbuRYRyKY4O7djZ6HFFNNcbGh
+6Tp8kJAhL0lCoTPpJRlfkcnwRJnDzN+ExikfeuMO4LO792b2vkW1Mzx4/ige+8JVe0eN0yc/T4qH
+qRMVtG8ntT7xfidfY2egB+HZBlkGJQDsZ2oTiwxipHOglGPXvU6tGmurXghUGGlhUltVab1TUY2r
+obDDeEckQ3kNy8V8GAoRIRuyxT0qPPMM2VjwS8LYxSbbG0UgnBolY9NF1q6HnnU9q9S4xTrrQPhL
+ujNp58VLyivMUw1N8Q6hRHcGOWZuQmMGNmk6qGfS3LvQAiXkKG8mqM70X/STE0pj71MNnbDUp2dU
+/FnLTdlo8RvNMB5wbKh24zq5tuH7617ITC1uPZxxd4hXhKR/Aor/KGflPkZ5oUO4xfT1ouZqJtcO
+3ZyrS+JemXBDlfSO6SIZJVOpYnpJflEDbbrKdijQiLGFKBQf6XzEe+WXFxgx4OANzQYMTOwCGK3O
+2I+eUaCL6tTa5ou7AQST7Br+sTLUXN63iEGxr0OoNBL/mhzD6ApZpveSmaR7qyjMtgZWhWPddMMp
+cgqxdztb/5TNQKSHAY4ZbMhuF5O9uQSE8QxF5BAiVGdB3qcklLtteSqnCeF6Zfdq4xbFJ6MleD43
+tGZPsoDzXovrreP175njyh1fffR66OLimhazlmbDZ6tKvgD/cjdOq03rBQW/prNFvodZHxPNAuPf
+2+QWGMm10Cw3sENHu0UG7+4R9ZUHQvCOetTY6BKdUWc0qE1PkyxRyBIx1twyKDdNfFCa3DSWCOYy
+f0ACOG7JpvAICZBPuT4BbmdaHDhN8inVBpUfhSVcMHh+nwWKGtiHzDZztMDscWcMVnoFTEluvUx2
+l0aIE8e7j/0o91hI4Gu1M+6Vse3XxQQNxqvE2cA66q0q5s8zxgk/hs7gM5GoSAjHCYQmD1vkPNFa
+tBc5WazzP/vKKnbgaI6obXuyD+2pnoIZGzNEGa+bilVSKbkfmvy5mHJi0nKn/2BiwYaNH0/JVTp1
+w66MjZqJrqnVd3WXN7u5Zq6zamBkrN1h7E9FHEFqALmzHGZQOM69Zn4pumhINmzxIMks2cUUMxrn
+C6kgVaxxXrAPJKKtRvqCaP1pATMyL8G8XbtOp5iI0mWSJfwsF+8Yc1DiJXJTXFUVyo4JrQZL1ZQ+
+mK1em+vQ7+BfGaEa34Vh/Nnndf8w2xjOVHdlk9SyhZaUYncJ67sE7Puq6uzCXDc4hbmpZRiaRuI2
+HRIoD1GNx8jNx2NqNr5a6flMlLnqYOH4jbqCtWB/akUWfoy4MMhsHK9L6NGqKDSCGEzZPFbugAwX
+nQHANaw9TdHfyDSM3mV2IXfFrOyvpu7mT2qw5JZ8Lg5aXo5hCGVV1OxVyfR3NcgGU78sEfballXe
+sAeoHSSN4cLsbz6SuWy9S2Y3g0qqkcUpvCgw6xpSWmHj45IAj+cBzPHaEwl0sYbPyva7+UXUtr73
+IggGpj1jsCjwmYD/gXsekwLQZY+TAzOxsyFQ23iepdkEorUDuvqomxnX9Bz3emwFzRfTomtH+gjs
+HRjctFkRmNVlUHQg9y1yT+BC3GpmjfGjUtYhk5O9T4qwegY6JRGDUlLYbdEkG+brWwYFMCtmWiFp
+43m3DiLtcxTWalvIFoatMvAtTqHYSnz2wRA2a5tMnks09Cchpq8GyRVo+dimxrVNtf+559CK0AfV
+PWOW4eJnlbUtsXCTfIIFRZsrXAKKXQXx3/DQhU33SLA7vcJkRAlijBd9ke65NKID1BtpQIYpeiBF
+D5oMRIcMROlvTZayeG2a4wd+aDgjl5s/EVqOGTDVCcwGDnhGimK+5/NGyWg5fYm6TybuVkLz3diR
+Dk0jseKjSyTdrRzYy8MeYW8MJv1a2G5OwMIc3uoGhJNCL7PzEGsZlEOZ2Td8Q/EOEhPA+dvUi1tS
+OO0vsz6igOnC8tochXGxe+Ec0VzaX/w49K+c3kcsr+Lk3gRiBpnMQSOLzyv5oBlFd8WySd7JnKmg
+rd0XOmw+nQHcNpGV9hcCGb0PlgUZpExLGBb4meBoT2Yqr+RUF1T+aMURaUUtcau2nFg9CKQDnVVu
+aa/DZmhc56DZ7nQHBg2MdoYmqkpc3P6aXx7NEemEIqvmegSkyaQwvNFDmX1Qukd4hQsEYcrMHaLZ
+bDNFjG3cxDE2RTNGwRQb1aUhcTVfyTDaSOqmTQntNOh9B7BykdnvdY4yfMxecV33LHjUj9VTXCb2
+R7/Ms6MRwYO0G6KkPKOT7mqO+h6qLVbq20jk2rronX4j5Dy+MJjICKpk3ws9wZWndti2RPieR9iK
+p8qtHx2iit97kHjWAnkOQvfhQ9OQX0vUOZAweTCK/HkcquGGHRVbK6CdKtBtOt6ZrgW6PsmAYxb5
+FVK9JInqHzJfFkdEZhOv9TAcGNsaR3fsyeRtM0SkRRbuVQxKQJcskHWeHtz8s8JN9DnypHlIkdp6
+lLCEFau8eZm0eDrl2K/a1cJL3ApVabuwUPoGZW9F2rbi40NVd63ZHqSYOGtukKiUDOMqSdZpXV/I
+tBoOqYBcDtbUXXH0oZyofW3fuROhW74O6yRKpvswRCOGPid/zgx/5lZkDupnjl84jAnwho0RpKFm
+IeXt6kdNm9VdNswuLdnSND7gzNM+kgrSb4Gcyj2GAT9D9kV+IPmPBYce4mtvGrqbCKWwD3rkCKwH
+38+2npxQVwE4dmZOckOyli3Py4ZM+TSVo+LNUs6O8E21KgHVmwy5HLhvbgUnzOkdmImJ9xUow2ro
+/PNY4soMZbceh5IYnUSsKU/1IxYvfVO4xRcmhnvckg/ekhLhGEMCSATBf5aX07713GiLW6w+DGbV
+HTLu8kOtV8MzKMZm46Npf8dc3Ec/V4UvGjXTwnor+/XQ2D50z8ja+MXgXplzLs+MIYsPrhf21Eag
+QSqdkrY3SUSlrzZqGyOnq0o6ic0wFYbEeK7LkiWe2Yi/E2YM209V8J+IZ/C2YZN6L7pPRgSSIDxi
+ENXdjxirHAKRiFN6JymRNuh+/Eun5vyJiG/4CQDQ9o4wx2enjAv2jqzEd01uG2tZOd9GmgZt0Z7H
+Ww3wbLuyFSQTdCFiE2bERsx0Ku78wm+e4UokO6dR8kmyv7HEt4R7TGRKOZlqrrxOkANbd1gn+45Y
+MKRb1W1ndzTi+mqAXTFHw4NWOspdtYPVXjl25WxUP5nAdCfhfchbs965rfia4ME9WnEcYiqcEvPG
+iwx9DeczecfC0S1Brn0cwOPur0Z3FscmFGILOLt46u2MyhVQ0E3J1x1zQV5dwmawL+i2AIfO7TwF
+VVySHUjqW3uTIWW/prhOIZdH1bRvUsFSU7OJ3kVQ4XyYJ3YOrLTwdpkxM4WX1LArSrhiXxBtFfic
+Ys4iInOa0KT20dFJK6wWATxiyOidlXrJLmxCtFv+THybKhGz2K2ajziX5LFGRPqEd2R48KlCb3uh
+2E3m1HxXiDE5+sgNP0Vuz14Uqvliz7YEvSv16NzADrkq2wFoMo3QFcne9kGXw0jvu56hz1epQwfV
+0oB7+CS2PBPxmdU0DwiNsDJs0sCkmE8yoyfiYBP5VQ9Fk6B4s/I47dYhnPzJzeQV+7j8gN5UviPy
+B3m/tDgYMAFeTZ6oruFae4+Om7lHpi7jyugHO1CaKC7wlSmx0oVoC0YjGZ4MlxwGW0/j69Aaxa5p
+DUApjA+dDzP2UooGHR6R9PKTljG5LxJAYys8Y/XGrcP0Jm2diEfrPZPAxAqWaruZptVWnziDcx/G
+WiDvG4AKOSFxWKsM4W6L4YregwFobG/g+QgaLS8ezVyvj1XW9sOmnDvnk2ZxvhgxA0WBnxHZCGiq
+BmNsGjJEJos+h7umvNWc8T4J0/wqsYCjQw0kj2W0MFP9H+ns/pd8v/8Lhe+mTjLAr9q69wmxasW3
+sri/fuSvfq73h0+/A7X6n0i+ZTb4Zz/X8/5YVHEoH5gZesu//6ubKzyUdPwLn7cPJzCHsL+7ucL9
+gwa90JF5Wcgg0cz9O6K4RXT/zfQF7Yll8lsxBkSBggjAfjN9Cc0YpTaZDXuLQu4Iyhs8epVcWeDm
+2NdZ32JmTIG1JNiQnTM+JiqLjmQ3+Kta7zC5+a25AmnpvaRxawQh5codC9Z4qHCCX3H+jH8zLvp+
+nvfj7/tWsKDhakq8iZ5Fkqv9ZBkL/kInL6sMA12yC6DJ1a8Qe4S/kSAw//jNR/VGgyAdq+DoY077
+JGpReTPhJ/ek9rZzPVabtNeqYPZzNgiDOMpM2Ncjsu+VU/sAbF0/WrPkNpzkS1yDGst25dcY0pv4
+Gud7fxCST88xx+vcDKOrEKkF2VKwXTN4APsWdpuE79fkyWOGwh0WCXAAFCm5NzwRSDYRRlKr+qaK
+i2oXd0XP+IrlNWtdjkD5mGxyKYojxVB1ZRNgf9VQWH2Ie9UFhiarc8KevZmKud42stvo5cs0xDrx
+4NFO61KSFvx4CCJl6I+WqsYDB0i1y80cGS+V1RYn+Eva+C39nEr0T0i39V1caul2rsg1TBGdb5rY
+rnaVSB9tJ7zGFHlbp7I5tCpQufZkYRU8dbDvCZT337ez0HY20upmsnQKaUec0zm6Ar9CyzFiZOtN
+uFXtPtmZijjUwXOfu2KYsfpxUhV+ejQHcFFimK5HPba3bZ11m56O2FojhO3I1oIWqA9FEIL9qsLZ
+3I6Nvm+i6iEnKo6koRDLI+c4pE9Ci9h/6qNjhDAETL3eppmFlTMqSIKdxUDGtGdthJIEXo1TFjBn
+Bn6cMkTHn9Fhy3T0jypqCPuKSA9fMFjTHubnreohDvCtWSVafwonv0ZsIwYOX+PDQq6+BfvcUUZj
+2pNOj/uD7oceaw8G5eKGYE0f3SPPBOp/fO33HPzoQeZnP+bklqXGpvWc8OCVjr7rkjg8WCjqOWdD
+EawrlKfMtzGj9xxdhtGcH7QRwnsWbbRqGNZDXBxms4HZFyc5o0Xe5tE2tS1qVUYPHjshuN3ppKJY
+5zjaJTssWp8st3zoljLGFwsgmuog9h50vIatQ19a5HyWtrJgHmTD3jFp28EMJuvOZZcjrBKbe080
+jI/TffAxnfE0lyDknWODxG8JFzAnbzm45YFJBw5CkeaRiJgGHPYxLrge9Nxc3RFPrJ+0COYWrVoV
+ECkH0lJ27mmqZHafmoYWENS6G5V1D1lsDDJv5AQ1xajb+vTieCPSr5is2q4CX9mlOoNXTew01exs
+gUXZcqCoiRGjdOGf4Ncf6sK7SzwEkPU0PnRjcrIlWYBdfBlqQ5LrOwfKHTZj+w4r9rVbG0sLtL8j
+4MR7FAS5b1GocBrsyUAnuxeTyFWT0bguygewQRsx+ts6Ll6geG26Gf1I7sJQrkUbr/G0XCiV450B
+pBMUym2i/CNa3OvRjY5pWIorSNfYFUKOHNsodMqlgKvaTwhKbT73Ur8f22nbilzcaa2Opi1ROt9t
+GC0DhISVDmKlAK9o+s9xnvD/ua0DDDGwZrlvEZ6KkwSxk8y3BFQgusU4ukZJVe4bmZQHkQnG9SgS
+g4bj7a0XwsbOB7B6izBon2sRnV3WxSCz9Mci4ezC6gfwW+dA2fiYGWcIfRSumr5TsdHuUSFy6lGl
+q5+ZdegHv+6buzqkWaV6Um2TCpYHATb8wRSIBJVnTJRRo5+BKF5z5Do2wpw2tpM9TLAsjlnYsT9k
+1jsMCvGmkZBSID8RjiAIRkLT1VwEwdFQ4cI46Kyc3kyDYyHNgMTRaUkOEZOtVaoRzatFSbJxyXBg
+sWvtp6LUaJPMrHeptS5mL92Xirg/4TrzHpcIIVRG9dWNlnFK0u0Ac4m1NmTZvvWTD6bWWJAMwlsS
+BEuwD6G2peHHpGbAP6201DgUMi0vc/M7Zez309vXDZSsR2EbsINJAHXfyMIMzYoNSktjzwn7tkoK
+Z1+kkHg5H5y+qYFu/lRwfKtIN76Xtvx4pTelBerbElpOZO6HqId/GPpfjLkdVrlOaQ+a5JMjSo9e
+MIhBf1l5JfHBv9OPix+3bA9TIbqfxZjgv00DYKBIHlE7w17HUsZsxBLaGh13TVeToSCcLi3A9p3d
+d7Ps9lmp1ZdwWUniwddPehrWJ191DS7/6onOTXOb4SsKYLMsUinwERfbnSHzGXoSpEMe7WmUlHsx
+jsQoEFoXtKV+bGrynlwZfYWliIijayvGxsUtv4e2ibrFTfm3muAnH/nPnu23t/tmMp9aOajVzDYI
+iW7Du7YZzTXJMcD6PW3+jYrse8Xfnw/XcZfZOv8gJ3L579/olgxFIgwzZWOf9O7XziX3cbKtj6an
+yqCx5dOv7+sH6wZPEMfoP1dblCvfXE1LiGIfq1TsSTol89o23+O+7g+pij4bSQMB08m6mz7OYzCY
+Yt532oi6K5P4np2ou/JTcLY8SVpZ3S536hFuVQ+nKFyYjSMohSThEWa20oMYv34gJvJ+OedBm8qa
+EWanwd9WkTbXmtp5XIqSeilPLOqUX9/n9wKc1w+Vit9wbPyWHre7vM7f3GZGO0jX2Ef2Tm3DZ3M4
+wBWmyCjdHO0mGTRBYkhNB+nXV/3ZF/W7y76pqUUHy1ivYElqls1Xo7E/uxn5r7g5aXM1unYsp/ES
+gg29yZcqx1XwAv8bvwKLEiYkHMIeupLv7zzXDZh/RQJ9LMFn27IlJnZ7hV0oXIedra1y6Vzbnk69
+aTofWfXr34hEf/I6Q+j/5/pvvjm98ls4yJG17/L+o9km46UrQ/NY1A4vthadf327y0nhH8nbn88Z
+SqTNMzYE1o43dxurRGu6CnCYbbbMXIG8rJIW1/Gvr/KT1YDP85+rvLmnFjgMgVaVtchzDFhVlbFq
+EQp0BVaZf/9Ky63APrM5rf6wGDBALOfZ0fdzqNRKecb73PEP7DO/uaOfvqnfXujNOsD5A1Jf3ljs
+JtL9kqjuOhWutfOBRjGH6c37LOrogJCKEV/XS6EsZCd/o5n/yZHZ0nVXLCor4fuc3b9/V0OQM7Wb
+hOaejEW5n1UzPEhhGQcyVsw9w+rHShI9FA0R/Wj48OsaccraXRgqbqE9E+uVMRPQWDGpLspTFhXv
+ncbMb4xEvEsbhlW/fjYLPvTNy2ZhdrORauG713nHv/91NXh3IXk0/GqYG0rwkysj1pMdCOaFdjVf
+kbNCmEiv7/s2HtHZJIAxoX1vkzGjfLdLcOTQf4NmKA+UqeEmrQwEvJxpWhIyVhwivkqpooNeL1hs
+0zrhDqsXSgPHs8kjY1MjelXOFbWVDGtMtV9oEBurSUFb1J3BOrdte/d6y/+71YX/ZQ/q/1VCA+rN
+JYrh74phYeT+xb5dIBP/8388PBdJ/h+X58/9d82qP3/sr2aV/gcuENS4AlsSKzHtpX+JD50/hMEb
+7zhLdwtHFZf6l/jQ/MPygVqT2UfgH4sAG9fflAbdtQU/ZeFOt8mm+LcoDcu7+s/CiTHGN+mk8Q+b
+q7HcvPnqNbXp9c7okIMZyRsCxQEravXHwoJm2sxYMLrsaLXjzKuMmu2bT+ontdX3XyM0lwxAMCux
+N9kGgGl9+e/f7s1hKwqast2mCakfEQCW5xzP1m8qAIyyb27RY21xbLqFGDnxvjpvlrhRM/RUESPF
+JEWb92HnRCjQsPYveoBV1+M9R4tAxHNLahiD2eTcVYb+Uk4+1DQ5InoiOA21sz/P44WgMfRY82if
+ymYeVw3DaeQvfsmu3vpXJmGgQd9MiHxDYHjTPtRlEHI+uqX8tbMrWXgJlZXzYMY47/Hf8Be6cwVU
+e1TGtVUZhCz0TnsVJUWWwIjoEMZ08zaHIkiKHiOQi2vNtC70uiVHvTDnW+wg4iy8VntwYdKtEfz5
+18qMsNlBRb6KMr3cJZo2PaYJYE5AUfnKABiDItTpd2LS7ZPP6Gpns9Ae5kXtvx4bDf2MAB+U7S23
+FmfXrp2WPnnSq4NW25V5Yg5QYwFF7LQjvAJ2mBY6ABnjyfvoQa4z15mQ4g5yCbg+0hdY12DFtpR6
+034a0vaM8EHbq4xT+W1hRsMX8Hb6h9JqW3DDtlZOa7SX/CgEBfWkogjRi+ap4r402/d9rdmbIRQL
+4q07eaV18stS7kHktvuhYaSS1tpHp9d9HP3WCFodGASMuLYXpAalfXJyUnPEwlqM46WX9czDyrLT
+4I3FLkdjskNawbk1rb3qXGKgPsT5WOzNIVYPEXDbnR+qiNyoft62racRAczjbo1Mfwb/Bcq4RMGw
+9t1i3GWaf13QQTz7RNBvM5qczCIzWnYuXTVbxWBZtdZjBAGAbel0Qw/seuM8MbeXayLU4f2nKpRb
+bJ48/qaYtzSZLM7NHiRhTfjbwcJ063R9+x5mlveeSEP9SqaSdzqyT55Rm6t2ec9R76Gfg6N9ZU6N
+/zA4+Bbiou8Capd2Y5KfFdCFoaqPanYqnmD74ApyR1b4ebN7fKiMSIbFQ1utJ18jjTuraqMngTJR
+H1OvN42tdDwB/qzXyzrI2gHDVowCGXPDPINKNZWAuEF/Yr54pWt+KqHp3wGYQGLlpl2+QxoMTMQM
+3S8z9Px7V7X+Y9e1ghIx7rWPaSLGMzxm68HMcPYFYzXW7sWKM5/UambsDXoNO1RbQ9OIEfBtPAtK
+T2Dkj1kdVYcONfInOY0JQKlU0PhsjMb46Hktk2/XntZLtA81w+ykn9qxyW/IEMhIvujzhzYR9r6s
+6kOLhGDP8Ovr3GlyhRhBbbPSNL9GgIM/J2Ob7qfITq7qrI8Pc0MVb4QS5XBUm8PF8WOIFnYi+VKP
+RvfoKOG/pKEZHjTG14FmIzwoW6ViTJaFvc/0Oq0D5u3t1Ww0xO+aZfMeZ1G9yXtlXPRqtp9DhD7b
+XlXJVxzymCsZNNyV2uDdV8o3nguIcjdGP/e7MKYwmEavfQxThML5AAua1OviKU7t+h0YKvMR94h1
+iFsUalJOwJqJwCETp+8ztZNtm5eLwhVGNu5no3nJE1FGp9hs0BUUqB6tR1GhI9vY/ORTM4e7MJ3i
+r2FoOu7egioxbwxa1PNeKG22Vl2SYvEktMsj5h3GhT0XXpD2kFzWkQ6zhPCViURUQ/OxPSPLeuZN
+Gycm+PHEguT6iR5oCavxhA4GC1FWhenWlQrvCHSYYtO7teufOzkVx9mcjHZbWxmODw/3yiGsPeOj
+rdn+DdjC4VDrbvi+NWHrBItcTwswkSTaJgwHvjYDjLfnGDgqrbDOV6doshWg2LJzD0AfsXfVdLBu
+Ddi06CFNmkphBFS5TEd56Zq4Fce48PzNoE0fAJuWtCAjPhjy0si9pcf2hTiS4dBStm2UK4Bu6n1P
+twbnTFcHDnXgEy8/qMFiBr2C2DbzTcLHOyyx/ZJLi38ZJB4KhRqETw8oAU+pksaHUQ5w+bo4Mwi9
+0Uvg033dfUAA0SJgzqT1HmqM/lQnhDTqjIBfkr4Ta9OasW91c7PVye+4VqPjf26BMF30evTTnQnp
+BvGPM4fzOp/DajdFIxhh/lhyqrt6rtaRdM0HCOwELyiLL/2qsrp6zySBX6DI5ow8tXgmnhQ1F0zj
+KEupZLM2k5I102K9wOhJYHeVTWiUQ1wOpHoDgRoRRi488cKpoJkwvW3BLwEcZ+sJkeKQjoJodBzk
+Y7bAybMGTDmPDH7mgi63mMuc6wVnnkQwC1f6AjlHhgOCNI9NjRzzqihv6hB5pW3xdZALJN1YcOlo
+UwnJ8QvXvEaA41wMiwNzhIv3DLJPsZrO8amguwqOukfo7HpwBNcM/4js9RdcuwbVwcHGtCCerEHp
+yxddo0joGrGJiPP+nGIuJ1tpStByVZnffm0m3bueXznx6MI1lJIR9Za/gOQLa7ACT6+6Wy2rdmbn
+jDfYPf07FFvRO2Mh0pP3565JA4OHKGO6wmhHbQLdodi3cRRfo0LkaysWyn2+8O6HhXwfv0LwBRRg
+5vGxo8/wj5a8WMtGmTHHgBnKTd4MbMh93e6IxgOw74r4YViY+wMUUqaWCMQv4pXJn+TmxRoNQP3K
+1ZCHd52OUq5D0hZOZChB9h9Q/vcL6x8IFHN44pSSJQeAMvkF3BFyACICsiUroFhSA6xUcj1+0NkO
+YeEeO7Imd3PmIMhB+ra1pInuhDhp70bFQDdXTmuY0DqR2tKRd2R1qpYEA3Y5hZKXl4o6iELoa7Gk
+HUyvwQfekoHgiJQ4BEjoRCMovBTEJMQFtgpBD51uQd98oZ0N3M7yku4FzQ/IOxJqwd8NjYRGOMDE
+Q/sziBWxSQsq7xWblw+kGK58GL3qUCaO5K+OaH2Cfl2gUtZUn9qpmxH+vFKn3GghUMkFRtUtWCpV
+65BaX1lVS6nirLpXhhXHTivZpDVoK2wx7q3VhOqdQeADYpIhyY6RZ0rw4ILqa9MsmKyaIdq4MdRC
+zyom37+p0QVfMr0Z9s2C2UoX4BbuhBSoEBAu8lHhcY2vbK6MWDR5CMfEgq5b4CfikAkWaL1g4peI
++az54r9yvoZX5hfQluke2vlCAmtHYa3LV0KYPlbNudf8uEW7V1XneIGJda9csShdGGM8F3hjcIpg
+jxmOxSKWMGJsz80rn6x8ZZU1kQa3DEzrMG9I+ZnC60gfvTJIXzln8pV5lr7yzzIKYntrT2DRhldC
+GnG7kb5JByGGo+/UCLRBW1J0VLl/7AeX2Wpc6CMVMB3AFcFPgMRCpC5Ua3Da0NqTELmw2/hSp8PR
+sBrzVCxst5lFJ2NJh/g2yXAoT6CeAMFBKqkZLIzgJwIv8cmx1SXEJRTi2rOHa30MkMqQnwWmp8mA
+xZYA5wQnh2EL3hoQHc8EKF0M9+w9vqP0HdbLITnPrwA7u+Pon1dNv42bWvuiG2nIvGUB3unsKodp
+VCzF1ULEM5UFmCtZOHk8bXkF3jglmRvq1oF0EI4gbS5OsA4aCp2wO0NXAL1nv2L4uHVsWejv1qNj
+jRc52HkcuDHQZxBo8PsD6df2Q6eLWv4OifGm4/TnsU/HWAda2faWsMXvj31EGnZ9nlgdRgo9P1Rd
+9KlMyntGfU+mX9wLu2RjdZkKUGR+bNNhvv31qfMH6Mpy7FyyZExD59xpv6XtTO08CDVb/WaIOk5r
+Q0/unauZ5Kxa8Qz0JRtkIRh9l/Hnko1DBEKBDl4ZQ66ejHGyD5NW9mdHFt1dRnjI1XIzawdlyUVT
+cnoSghI+yRxkQj07VncD3gkf0v/vx/yvQLVMqtpf9mPef2m7/1h9wRKaf9eQ+fPn/mzI+PofiJ49
+Wg4uhstvGzIevk7gWA7NGOO1JUNL4l/6ocUoymTGp/kCO4vT898NGWH8YdMQRF2kuwwCXYYM/wY2
+8/u+OYk8tBV9AX4KCREG9tc47m+6Iq6FJSH3HG/XxH22reH8robISQKsid6qK6fDr78OP+ByuJ4F
+EoxeEp8I4qU308tUjCE9Jt/dGVkb7SKRpV8s06pvB6MkgG4aVFCE0C3ZN/2Foj0Nnr9KY7t/N4Mw
+Xiv0dY/ZEHpD8Jvf623XZvm9gIp5FloqOmcuDbBvu0PLnBj0EepKJfKPXcnvwYTMW+Gg2IvOOvrE
+ue2q3IT4keQQGqcrG1vq8de/xNKB+rY5tvwOEMCErnOcokX25nfIPFj6Y9p7O5mM9S7M2vDoGUn1
+8Our/OSJW9wqswsT2RL9vu/v1OVDJpcg9XZmhWYjU+9BTSR7leSIpRWinl9f7Sf3ZJs6dwOvQjBm
+fDMpaURj6JBv/J1fus529JZJfC/Fb66yLOJvPjkosq+IEKA7tAC+vycoiUat7NDd2fGC4SC+aFXm
+/d1QJC+/vp2ffHhQNxYKCffD0PTNhYDt84kur2+YIBYFIw7VHgtPZpY3Zppd/hsXc2Cf+FTGuq2/
+udjYAz13W8vdVaalr3N2NwbbAqnSDBdpTJ39ry8nlmfx9lMkQ5gePysC7cs3zyqBxjU3bgR+m0RF
+2JKVf1ZuqN/l1PDYMOIskFikt3DSxX6u0moLMSH85ORmidRjrO/SzGvIlC+GgP5JaNBeqyUYVy9n
+CjHPN52QhQy8uPTrA+fcZG0WhdetGjlTuVeUOGvZzUbQ2ymlvp46tw0Bq7/Zjl9nO2/vkSkhmjxQ
+hj++j4oMHmVPibuLylgcUkIrD9Ng62t3sB81SBmYqdpD2URfXTOWGwtdzAPGOu83H/XP3lefldvy
+DYoyc0EmfrvaNCknIDx0/i7Pe+swWsmlhMq4WpCuv5kN/3gluvrsH8IzPQQqb58pUBh6Lqnv7dww
+KdbjEhKFR/9ji7Bj8+vXB1/oj9+OpanPjMGkdwtD8s3SUheGqbmidXeWP4hNNmjJomMfb7BwjXeO
+xosg6u4hwtSJ3LJDdNd5er1G6iQpbyusz34r6dK5VIqrtrede7x89rM91N5e4RrN12bdT/doFa1z
+1w3VKUOQtyubGJuhNMjr3eb0Non0NTDVFW5/wJrg7WVsOVu/KaedVrd10DS12Jg29EH+oE6OiE0S
+V7hTnajXUWGEVz1Nq2soWmO6BhbobKJhFMHgesl1qBfp81SnBRBdX2303J/3k89wuxpq95D9J3tn
+shw7kl7pd9EebRgc00KbQMycZ/JuYLzkJQDH4HDHjKfXFyWTrJRSK633vahNlmWSjAB8OP8539F9
++F54q7jjPl4c1w7yh5XC4/GpoD4z2EtvHMi7cdl7uypt61PuF0zKayCMTEXbZ+Ga9t0dmvYzymy6
+OXJ6wdBIdZo06pLgbcZlDyatOhZ2L58su9V3UIVRFGfEKbJP82o28+Tp95Yq7hsz5ulrHq/FYax1
+9EUGeKbdyPY+Sku+NRXkJiYvKriSvYH/b5D663yraT31hFUfm9HxWlaAzH0kJwa03aP/5coWXne3
+cl+jOEQHh06b8sCfQ23OyDUZ6bDYIjgNFTpIQRSJVWq5jgeyldwahnoA55AOYTJwYzlU6Et/ODLx
+mUxec53nTbtR1eDc6j5lauB7WGq1Et2b0zXjBYCLVlmTcAo2SBHxK8c2gF0+iZqXqKoFnZ32mEwa
+Si69YoJSngCSl7a5XxTEllJgKGz9F4A1oTJZCTVsyzEqjm4Wm30T8X273cjHN1odoicBEjr3yEls
+7JGyBAGe+wMQ2HKFq1t8QOa2x01EqcfdmGkbhwrjWfSCwQbzzOJBB7QRiwGXXU/x69T5ffWKxRO8
+g23LL+0TI9iEqc8THzOdeKoEByG6r6Z2l3PEOdedSSq6JH/WzFuYUNCgkW3t3kvlIXJbjF4SF+e1
+S+sdqLM+ULD5J7DRAeJGns7BwV054GxYD+rfIDnHmFE69WnxJTpk0Jzw6JXDcSTPeEMUkupgKbL4
+oJS1msQuazDkTXpbDjPtGJ5Ci5gbh983nwzBGPrUgiKp3SCHwWcVkIonQ4GPo8957JurrG/qJ6+h
+lr0slv3chvmza8czjbFtv+/43Y6TpbJ9rPv4GPl2zfc70/sYzDwf1cpciDHREOxDlTmvoxeFV96i
+/yjH17tioNnC0IL1K04hhHFA9fTJcuAfUyrkMv8ZLzjL1Z8OFjrZFoMNnz75o5toaOIEbTc/5Y2J
++FtpccIbUn/aJpO3krY1kvUm/S691U/pZpjgZkhmaBVf8VMaevaRsvNqN+GnPlgzuzBHUfM1+nX/
+4MbdcownqyZGMkQ7TfRmj8gFLYFxyTxyQJxXR1ylgGJ3c0hUxwySdFp7Rr+PrjoVaSTCdSJm0GW4
+YmX6ki2juNKGjkiLCNKVMX38WUSB9wI+u99VWeZRepKagVO5SY+u7Sv8yH2xAwXGqxBZ2bkgS7cN
+Wg7HEAvyq6wd36PIdOdI2VC9fYqWMIEOR5OuzU1f+Zf6LTGtW0VcFD4D9eeMiSqZiEHiHUZc3hDk
+vSUIle9GGa5PIBa6m3aFNT3TM7yxLReOXuoUGIfL+b6DtUeQD+JES+vuZijX+CXQAk6Sod+2oWHv
+Jovl+wDj7aA6AOO0E1ExE9ynVf1o28RE67wOTvhDS0jvcputNPJVQ2TtlRdMfxg99EzV2rJeedcs
+532OtXcjqu4GKDDCbUvV8DzZS+KKxbmuek9kIETyam+qsNz6lZr2Cr8Xsn/PhcIJGIIaMz6mHQH8
+vREhzMF+pRapsX7mgKnDFPrPHJLWw6BRYHzFqxw49sHB+7WbJuXciKZ/aAtz7cmG8Ro+fOrwXOhf
+afPpKEW5IH/5BbbFfIiOUwG3Bql0S2c6zb7QvnAxTt6tnob0sbHTegcvZ7nCkX4j1NhsY/x+G9pG
+5/00DfoX3ShREtKCngTLeh/4ZBYkES7Q9/MUvDdhjhhXZcuenFLpobVmKY0DNNVzrFqa9oVz2fzg
+NoV3ZLSbHkwxIYqx2NwWNXkLR1vxU87f+0EifcTiO1eGT4PqwZnlXEsk3GpQ4TbUKrUZwRiasgPF
+J7JhgBDeV34D34TCaPM25qb7DXEd15tGcRpOmWQotA8a+I19t/7QV8+sqiBNOIXDZ71W6sR/jkx4
+NHd7KeClOH6syfhXj6z9W5vF55aXUB9WyaTT9eLyg6SIPrsZaTwGTyvS2sQcsMryfVEA26E1l9d4
+MlfMiOikqcTriFdlm8UWoauppTrL1feBRXKxW1NZJiWxNVTCYOLJpZc7WUOhnyBsPYVFp4+qxX/E
+2MI+EiGT53kBOVrrgeY3plys8kPDFBDN5zBq1z1kqoLlQWJyl6KRbqi+qYAq1+49xTDFtrHz5kNF
+ottp4QPNWCQTfVaLuYvVDxsS8mszVUcsWOMLCUOnSYrZn/6YavXFRlHCs2XmjGi9xjZnRn/ZWxaQ
+tahS9YlarR/luuo8T6nz5DkxMRB7uS/MWJ6X1Ue9iz06rRzHGl8xL2c//lqaXc53c6ejxT4xcU/3
+VhObx9WvYELV6bfBr33rNIBTq4IkdRDJSxeaHMrjPNrzYZJQdYZUg7ev7Qe9ighze+7ukbPm/Zr6
+AgOXyJqz9HkSotm194439JvZletezQWQYWYTFYy0AZDkXBIrGNAJv8CRVFf44Mt+3/R8InEgq0Pa
+gIkWuQJYkAdXpRjeFzMrCKXz7Vyp7hvswcAcxqMm16Fvnrvh7YBrfhenXffpdYF/qG09nmp/OZTK
+em3SpSwvRWfZTgNLO6u0lrscMh2dCUH9gkWjv43xMR9sNsHj3BKVYpryItocRkweuVsdj+ZbN9PK
+zn2hg7oFbYpqyKZt67I2lyrIbkMaeh4ozmySzm4ph4BaWG4Ao6gtQsZ4P+fmrb2MopQ1XOcuKNF6
+mXZQN8YtmISW+etM19MMNH9U64Go70jYYiTr2YY37kpeiob24oGDvW82mUy3dEEhmzZe5AIBbF47
+aRX7NqTGtsRWEhRHxrn9iYQtsyTGhkdPhdkuomOAvW/GL1n466Gyms0Qh/tO+eF+CUi6btrWis6x
+mrHD0/F4pNxrnK16qwlsI1H624bC1QNH+XIXZQxLg1ymB2zXBHv4+RtT+1+99tP3sA4oTYMGYk9L
+QC0u3t5Wvyw9dSQdVPXeGl4j6V6q0MlEj+Yj7i326Nz6igr16nrlDVOOJ0gfAkeac0eR15+s/GOm
+aDzogkE74/dnhhj5hqL1c+uH14Xv3FguExDKHjoK761rwxN0DaK3PKSTF32pOZT7zK2ZBWcJdX3j
+wQt0/bZ630hx1T5ytZM4k6yTiqwEw9DF4gvsimfaXCCHd82LWaPXQEv+pz/LNv01K/86d6oP4fr9
+VceEJxkqI/dNnb/kbkwVU/1MqOCjcfWpJZ1AzLS59YKS390d1SZoR7o0xwUwmKSwxrUIytAwRhuZ
+dk9NM4GTDqpHyVt1qmROOaF9CqZla0XaB2frECQDnKtlnh6BaI53AMt8CmrD7g+IsRjRzD9BloCW
+X/iXade0Huop/V2CP0gCrvvPvRbMVLnk88pCCvrKV6fd1zDws7T299RFQ1wt8Rm66ZRfjlKB3gmP
+gWBeQbvs5kZu4cybDbaYG1dgte6ambNKm1JTWE+CvAVXhG4iBzP4FmcY/mDpUok3u0NKsZtotqvi
+++beqqhqC59we98JbyqSwDW/RnwoXc85vwk4fdalO2z8lDW/zTjQe/Fjvno3nkzfoMnf1kEK2Xfm
+e4efY29kWJlTnq8tm37zYvd4lczokY6R7bt0RlD3OD9B0/wOLfEWVHafrIY9e2k7vjQAwq3rDdAw
+xvp1RgzFGe9XBEIy5yiINe9anAKwETr5WYwDxCGRA79GEDmHjU2lWgjuXtewSrLQ/GrIIx9EEPCX
+YgvDzTDe+Y5emA95areSi/oJcSncFWrmdBd41X6hTXhvxYTIFkw2DXeWveT+c56alMMRTAHfNfem
+54Lht5F+z8meA9BJhwMSy5MeMrVPW534Y3YbcTy867Q17GbWjp2IU+iVsYvVS87cmzFa6NvVZfRu
+cIru7YDLcXTxgJRy3Q2YUfcu3vFdhjkhCadgfnbJy2/CBnDeZOibw5Oivmb+qHNowmobzHylrjO0
+Rze3hgP7rX3banKImSobfNhHKlUkpiXl3tiLrqiYG+RNSXz2lRqC4DWa/T/0CjL+cBuamCvPfqvG
+qj82jrSe2nY0v4HXZPe9iYIbcvjMQ0HfHXCxjgcSdzmR/LiDTdIB/UbGYbiUQ63TBO42E6d5ICtO
+F77Q100JaNZ7exvWCPQjND6wP11NnX3eDqeuxuNLRe3HojkqZiheX2mW07utHXBPhqNQzxX5EEvf
+Q6uWnJWkPeD1b3ycHUFwbk2/fAwE+7kwBbuK13dvd1TFXmxqu0n6E+mqbL4vbJpcV1ES0KUaYNt0
+wUOOEJWMNd84wZP46I6+s5/RUsqNnAaMXB2J3tmYEzURuyae5n3Mi85dqjZX5BrGnSxII5H3q29i
+AoocYyHe+6Uzbcc1zU/tOprDMLvBoa56nCf0u+8GEEiH1XfHY1pO0TmNiPFB1Ndbr+A0zwXsaepc
+71fZSCcJ5v6b5l0GUmX2qwnX6kbPOcPEYv3mOm4eY0ZWJGqMBQGY/uW9U5rxyrK7F9f13/ix3bkx
+2MmDgbbunONwJxb8kJipXty5Kzq+KJPfuraFNtQYmGf1YKMF1ZaD6lgE9CI3PD5KtXs/VykhfOmK
+tyED+cEj2L6Nkm06LS9kkmYYaUQCTpYsMmge0Cqal9aaYgKOeftJjaz3WDCKv3e19nY5hQjLJlgL
+c1+68W+mbvEjetzF8ewx1xatSiYKVJM+DqlQbIeQQG5jrvFplbsgnssT8B4kUZ0GO22p+mBZeZO0
+XdRA+3OK85IvOFp9o8JN5KgJOtn6C5uMfcywar7nIIA3lZQGhSP4HZKN4XAQLwkDgmzX1V57CRIr
+poNLcU0/Hn3JsSdPPH4PUEdbsm9Npo9z5uXX2dhQA65UceWO+FkhB6OoXlUgXUKqd73xYQHo9D3K
+Sbtnay2XwziFXpR4wRq+k0q1wWdN4ezvzJAXP4qHLEy8dpHtdZ71CwiyGIhEZVsm3UU08gmqvwx8
+qcAfqJGcuOmt/fpMSkwcgKKzOy6l2DI1eZLBwJoZm/KrTsEXyMiZtxEFFOSTgy4pu9Z/SUvc8z3Y
+qdoxZ+rqCVaX7B28q9V605g63slLAG4jwrUbNnmjsXaGlXrlB5mXumrUe3lZOx1V36qmL/eyacNr
+P4+dPVhSuE34dJqPVrXeGSCXC4c/VMtWKJ3S1ZSOLxO1Zk9lOurnosS9apOvJriHOcNuqEZaLInK
+3lVtdXTaGBhKHxYDoB/49Zt+cVgTa+zNOE6qqN7QmDUmWThZO0LfWmxEbsmElo10r0ETl7AewZeX
+kE6GTTgMWPsC3VV7oD7tZ0B3l3/5TsrnkPXndqij4Q9oUIv+US6Th4GPOrpm/87LfeGax5SuTtsp
+H2FS14d4zAFToV+CgLMz0JnDvcgcn54Bfh9q1oPNOlq3CO4kGSAIdWPKwsscYW/5Ew0sZQvkBOzE
+hbCYDIFIYsuiHHYufShhgPNufMBIm1J3r6EuZL7NSwLFXU17NWFg9xiPkZsYQ+5lgkTErKwfHrlS
+prz/tTzQrhnsZt3yW2E0ogmX041PAZeFg/VCKvteOxdY3jyuG7VOZDvzo5766YBSS6AwSm06osh3
+UkZEzHWwyHwW4FubvqkSikH12YuKx6AHvU76+ZwKm1QwTwshfFThHarOcBN20v09K6Ie21rWtcMZ
+fAkPPchWHym07a9EaIZDCE+eelpDc20gcScPi9u+IX+0D03U9Y/ZFPXvGO3lHZ8892Kku70zmvCO
+s9wE7ieLQIgqmEuj+6fPgazFqzPf+StuvI0dV+lvNFhO+OjldGR5GTguwZpn078QhuEefqSFZSPT
+rUxKFff9D+4gZ97ZTrraAOZmxo6139Af3Hlt/MJeOkDg8SrULH8ZuAbjTjQ0O8QL3RumthmpRj10
+GRXWNz2J8pcyGFPckZG+7jKKOFP7MnFJabFeAIjOVUEZDFl0Vv6pe/SnVhzq1rHvkEVC/tMd2Jms
+Q9Hzw3BGROcsG8PH1G51B4FsV+d465j0gLkzuK1aMd6lVbXFZdzB55Q7bkBpghn5Z1jNS9PP8Qsh
+eNq5u2wB9ZQ1Xb0NnZUU7vy2dnh0RV+6+3wsttbF/R+1xJTVUhTnTKEJMdA5ZVVhvXYTPU0xDsOL
+7F4mRb4WuGvmbV3nYt8rbl068+UR2D+XWeAzCC+0Rp04wYKELAyeo73dsyuSCqUlA2kHWmViop7C
+7m4i9R5Z+UBw2LatW4WJXO1ti5pI8ur0Unuh59OyQfEM5i61I6PfPgUjLFQYNoEDMKvumFIjeATp
+ZoVefN9RV+WwgHnBs521+mjKjEuk4bYCNJ9mxLMFPxpwqr3M+zLqiMVnyJr2FAbv/F3rHoIiNbd6
+wJborWPvXW4s1X1qZ7j4AYN634urOfRaLfVCbdw4BLMj3b7Ab2axLOFpyk3ppd6PCMpLqzqdOgfJ
+DIHtDb3kzZ/L8L1f8vCaiZS6qbAIPDL4DE+Bi2XX9rOs3Qb+P3qxLYEpjja7+INQkOIgY9XNyWaH
+I+FIlRJyWoBoN/jwGDdyVNizLUc4lAsK7wVEnA2vWLY/ZUgZ86aPu/qu0bbLiEFLWJM6FuW3tnwb
+Y9gyw0uAhFsAWM3I6lod+44KfsFuDu/8Vla/K0K7KKZZdjfMSrwDg6RCtxuy+lP68Xpu8TSOm2aK
+kSEqiwtTMtcGhlSr/KdYwcy7VFU6nx0958cJlGi96aI8uC9tAvVJpLvsHhMx2m5u7V1YVa92F/c/
+qqHimiFS+lZntfqwePd3VscnL/k4y1PASfK4NMX6li4qf4ebd+FFESf+cI0VfKICi180AXbJ2OKC
+Tb0i42HjCL96Y7hreETOrSVoksA0tcPnN//AxJ0SC90maUjv4oCPqLlfgJm9Wn6dn7zZXm7MNMUf
+0nHLxA4pfreXqDgHyMxQiKweM78y6eeKyMILoCr9ETV9el45a3OoXqFslhwAoa3WXU7jgP/M5tX8
+GZtB3QdArQ8MGyzv4svPdhzzJNZV61eB3EP4DBsF2o2d0q+UVYcRu+0tPg6QuCz7eueptr5nXIZj
+eM7Qu/yi4lDSuHX7tHQTIKtyqSiXx+xcJcLt5A3st+okpiU6zWnenwuh2m9c2QwGldN7OpFOWEGK
+igp88vFk29u+rNUNC0YE1qbgm3MB1qoD12QY5qOruUWr2pdY9iHScc4m7/TlSDM9IFhP9xRj6Cd/
+DNUfXw/VTQMB8bwOafATCz+C29K215kILRrenNH78Yde/SndchIba1TDR4P15F0a04VE7EITYMfT
+eAiXSdB2vTRecORRjbeUVIvnztfAJSOAEhR6pZ39SGRUvGZhXX83mXl1qIjEj8+JZFxgbW3CKnNm
+FHddko+els+6i3NyGWinA+cp/Hgh0vt67CgvO/sUTtZ7rgF8yEM7csCwgna1zzLXoiYC7djMG+a0
+uF3mnvo6n6kra0TWRHsvy/urXLJ/YWj1+/20ah6duhnrKnEjNhsogAyi28iyb0YtoFPySLi39hAi
+2IU9oFI/CLPPwbQpCUnTvQtnaeUWn3h+GmujHnO+qGgvok68dAwIl51d65CCIXzbG8CpyxeFexPi
+StWG8tiG9SWY5HbLsudplh2Vb+yZm950c5CEcRP8GlSM67vlyH+Vpd4EDvGys8XBdMjWC6zaapz4
+nIXLb0PTxobJ8TRvuFrznnBG4i9gmOC4QQKyDiMmyhpznPAjq9bq22RTimTZ42YOFqwijnNN+glH
+nomECQ6eCAQmRRRsd1P4hoGHx//x7GDRHTYt3KJm12YXhvbghKrfibxAOusc+ZVS6X4KReG7SZX1
+xEhC2y52dZXqL7OEkK1nAe9+ZHSzXJWlVV34r8H7iv18wxCDy1tt0vrSxVR637LC5rwYqlxpZV2c
+wzLWzcErxyCpZL/sA9LBDPOi5kTvFYOykGHaPcWmlKkaMbCb0D72tcrW4YjnWuZNhnm9nUZOE/CE
+f7zRia98S8Rnidvqflo9GID82d15MZ25WZbB2jKr5Y6/ELAh2A4MbXQO3G3IgnJrpr43Gj2yUZUs
+7vPIv6uY+x7cTGfPeV17eFDhxx4lztZxz9w+31N2/+kre3m0YHB/WXBI6M+wrxfXUd8gAeSLF+YV
+GeRJxYi/Qr/H7ObXVqac24rA7WNGxOJvjBgXo8V/tYPE9iWUyMYN3kv81R2al3aI51tHlzs9w1Nu
+zPdhQPa46tuCfZuj6t3oWPKFeiq20v/dMCH+J7sEFhSmoIS7MN78xd8DKokugniODguQg7uYymlS
+ZR1TBJuxvTeRV0m5kzEYt+X4Pa1sKWYY6n07ls5m4Jst285PoqhG7CRHmFQNA6ZmDrz9xDGeebPr
+3MOm9ZBlavyxCKg+WJNAqPMk5HoDaPu2c4EATz7aoIdTi7K1qST7NXECZq8nL6SG0j3Uc2ltCtxB
+2yBlLRvMQF/t5D/PA5cDf1qce10EX7KhCskKx/6oLRZ8enmh53EZwyo1R97ffHTuhWjwl+8tRrOF
+iE1mlmHwX5wmNY8SH5/gtI6HknuDfS8ExbN4YBf421iWpgVvhhczd3eWC42/G5Z9XJGw5GHSGJi2
+KbmNMKnzkVTMUAc7GXvjyVaAetRsUcgwcN+tSg7AngQLI0lv/O/f/sVI+t/+BJ+BFsFUBz9DdHHO
+/ZPzsmAvacfYxAfbtPIfJJ+VLnL6xa5Wq3/ExB5sRzZnACBdfnZse/jDxGs4Gfvi1kNw8x3Av24H
+BAg+YvE378V/t+1dikjoM3JdihL8v5oEMzS8wAlAfgKbZA2dvSy+ttPG/M2P+UsU/2I/vdSa4Hjk
+FWBp/0cv2T99CC0DY9GlbXxg/LmUbN8hWc3JDNt5roLfLhd41siSag4nbbbpMAaPBYfQeYswXl7h
+2YnvqiUqsc3wsrR+U9/13mADX0xXyE+F/dz2Zff6N1/cXz8b1mvb8f1LVFpQfuH9xaapK70iSPDs
+jZ3LorC6jQ8iCnFQpiVYda4hr3F5p+xCfVQr6hnzHzvJR9gmi1gCMqDF8u3LeP53JsX/D80/Ly3R
+98/vumi2Rdeb4qv/Z7M1kGiX1///Hpq/+cw/zWeX9+bzf/j3/jM1j3WNSx2xzUuAO8IfjPei/9d/
+Cd3/wxCX98vB74n30+Zn/YdJm1Jkl38QRZSqxjzM/EsdlLH8X/+Fyh44PnT2wIRigWKU8v9i0iYn
+cHmo/suCh1tRhA7rXRTY+H/+suC5wxLNvWvNu6Vv0WyDAo76PHYM19Zc/GSUBQ5JX7PTbef4YmWK
+slGz9mW2cxVbxKZ2UShxQDWdr97p5ozj23EgDMkG3LlfnsbbsC1WCLqzsOuNCZHiNxV5GroJLFm1
+D74pijfoMkX2ZC9gBB/Iq1UdfWdFTxZbNFgNTBMA5uNiZMxW5i1Y8J47YbkJaJqkvqx2aUWNXXiz
+EL5h+ZI1b7L7ps+cH0cqsZMzps2EZGt80qW2Hl2ufsxyy3Wst04OhI55jaPLu8m007WNWAthu8Ii
+7jRmOhMJ8yO4RWpMb9N6CYtNE9FF/hiV7juZDk5Ok2UzBNchVF1U3YC6niInXbfOMGyvxeiBeUPu
+yUkGlnNmtmqEI4+QIPNnioBIimHHyQEauiZccaHLQt6BZ2E6UswuNhcaPyzbo5tw7aKxOlpRNpVn
+CiwZTMLG5vBOSzJWi6WLK/L82Dwe3J4wYMJgdNhYpJsoNuVSBKDTxbbQqWvHRPnDTKT9o3OsL9/0
+3BCwll2Ma3HtIz9PABvVEEDsE1Xxxn8t4BaXmfuUQQK2iqqdUIGaasV+YWfisVxIc900VMDBrMNz
+Gm9mq/Nwui6rhcmEtCwGPjij643oQ2NxonbagJPpKqyj8WP5BoGeQcTA7G28SQ0AbUD5Reduo8n1
+75t5dqakiNKuuY5sqipRDysuhGqkm8TvY+6uHbnA+GSLkpAy/k/8BFibIOBS23RBbkXUrDmeYriW
+wervtz3SxYLmlRfpnon9WKE1qG7Z5bQQO7s8bAN3I7J2fu7y3KIMavbE7zZI9UudK6goiCjfqkud
++cxTR/4On/JidqPp+5l9E+tKbmzsKVXXZ5vLao75zYpQAqwoDc40S3m/29jBAJA7Q0TEfM46hqyM
+zpZkATZ59qa+heHXmvKa5Sp/MEV4H0JE48ozgOXtU22dssEBZjVNoY2eXbdvEYOUR2vIu18rFMCr
+2C+PI2WjyKv8aPfpgoZGkqKIyX1mahUGmIFJvyeD3S5PReOt39ij1husymZK8OPkzp0ZshD3pyrd
+aec2azseVztjACRj0x9noUq95eBYf/TWqu9iGdqYX+MWIHzKMFwlFr7kZ73kVKLaHBDhRlmR1+9Q
+qf1r0Te5DysTo/RGgk9yrgaPNQHlrhY3Bq+t2JKNXLguyLr41cfKnXfAt3nanQxSmdPC0N4qnZNQ
+jez01VqrlAz8SOXWrJrvqrWw/Jm8AHMo5jdE7DphmhoRCtGm/liqjPeGtt7+DmuuSYSo1VVjV+Mz
+Eqak/GYhqlBU8YxWILx7E19Q5YLxyHEY1eXa75Cfkuix9ZFmI/ECfrkjFjllv/zSzePd2tPM+1DO
+RThhlMxHOrgXCiEGN8t/z63FcFbi9Bg3q+0gB7LdPxeB7cFS5FK3EYwdwHcGE6XKaRhU362fm7Nn
+yAUkHHTX1wH4/5cmCQw1ofLm7IA5EqWiLkNyX9U07sSYTbe5VhZjQdeTuBlVNT21U5FiGvOXWWxz
+Yp8dI6taO+fATdvzGLTVcJgXeCPYQGwu3AwsgGBgYpJ24tu6Ywi2hHekRRUZQ9RdJ0vD5iWSnWVv
+p5kXBQB3bJMTVP6lcoM97au2Fm+DtuMdfEMIpMmpfLXs36TlnB3IUcn5qTSAIHK9zbsIcHrMpW6r
+GJzaicgKfQxEB/O9IxDBsg+36ayXJW6eMTN7OLlEu+5GodPHerHs52zBpbkJ3AtaE291Me0qIeUD
+p+xQbAbbxWoKTVlYVxzr5SeatRqPWWEP5Y3wiIVHGUsOSpBX71ocXQhn3ELu06LMnp2IZW47ZrPT
+s14UlJFiGeVJjH0gtqRj4+klJsq5sl45lMl1fPLFBSEePFQzuE1Ikk2t6SBrWrTO5ZK/xTvZPhaa
+0jJ8wyF8yrwtAp3kFieIUxG5giA2Y0kgoKKMEycsZqZYMPN5mFfrNDROdppnBVR05HzQHTGDm3SP
+GSY+NtyUv7mj67dmMOrBGvui3sy6WL9KYdFQrcjQUDtJBEht+RE9LQSDXE9OIy7QSb+6OKkLCnYS
+RGxXbDB38iGQcOQ6xsTlvivXhQOC8bzPSK9sdBG0kudFRd2NsttJMBqZKYcSJUsrxC2PqFeY1bcz
+mI5HL8rH12lR8ZmgdMyAnA6FR1nbEaVd0dCNNyWMx+dxtSOznQAT0OhVGt0e52CI/qDuLEfgKs4t
+NhH4VPCRVcVUp5yA6xJQVtsIRXDjFEyN78Qi5+WIybSN7+FLodVaU5jfWJ6JPwJ/8R+4E1xpCp5n
+BKf6cajjguqrFVZ1SrPSwWOR26bZaOHNZVofDfNv2VKKV7Ssma7dld4v31CAkGRoqG99MXg/XQvw
+Mxez+iyt1eGCp8fyZM8TQ4XLBoCHSD4tQnKNngZJ8t/UMsH0XzxaugnPjg5t9zB6mB/qLED5qCTk
+ZicDcQBjgQaklezyRujchRHmc1eCKHq2GBSi42du8Cgqqy5/5U6fMcgtGRmpfD3OtY3S08ZMPfJ2
+8pyk4pc+yExNEdNitz8wSpqurJzsSWLTM7RrAKqGO7oaQzi1FibkSmTfJNDzj7xbntHaEXNdmYmC
+JAudc8XcClzlRO85eoCv3BjWIrwp3uqOJ6yrwW8NlR8/K1EA6zxKeXLE4h9cGsEfYL1QJ1wWzvOF
+BPTLd2CH33pSjz/cF5uJs0Hp1ndBT7Z6m8vJCvbUoXIVXaK2ZnCFOfaoRDn/zrDXf0+iKcZXlRK8
+OQQKoUcTFzMPU+qG4c5F26VdgbFVf13EDh9jlsXDAtYgbb+9rIJDxuUxH0/EKETA7ly6C5WTqo7P
+TeONT7A513FLJLl+uvD/vJOag3p9pInmcezaUp19o8dl46FoPCyh19iJt+Y3DtDfY+EvHbey2fQ4
+y9my+qqv2yQU+awSFxstkYco6O+L1eSnGkzPucHWdkxjcP4I8jlOnn5iADSj0KcK2BNOqYy9nDPI
+txEg5HxcuaBCEBowtAP1xXT6alnYDzcTNIYexnMVNJ+4AGPYRhyNnpdCiu9h1OQuMmGauyHu9OvA
+LRinyzI5Zw/d/LpzVUh/rs6cN/JNzmvAWe226/3s8G/sndly20japm+lbwAdSACJ5XBIEKQkSpZk
+2ZZ9gjBtCzuQ2Jer/x+wemZsyiNFn89BRbiqLGHL/PJb3sXLhwinrgIR4L0sbCvf6WgBbybGfPXW
+RJnjBwdk7nNkuWBgMG380oXtd6OpQwxWhpwOOz189aKyuv4iEontn6D/jM9A2JNwaMlcfkaqJnoa
+ET9Q5G5uvNHJFz+C/Jgk4EyvNp6X0aq3Xr3k4w88RsqNpVlE4xCIOjn5dzEt9pY24Mc0M8SVhn8S
+Ui1AVrzr2kQn8qAvYliOmcgzhBDyEm3npBpMwwdk76QbDSgDhA0YIEvAn2AyMCQb4i1QWTcK6MKr
+oHVqc7rpaek+tXVLUZ4YkfERnI9IfMPiKI/nTD02cxs9svaXw4LEgNhkLse8Xy59f5+4UKvRw0dG
+B/GrwNDICpLc+gV8y2i3CsAueSNskSsGnHP8hSFezFzJAA62WYXlyRhMXdwqs2YKP06+VoAxm/o+
+2dV2PF2DL6jQQAL8MLTDt6wfkzroMfAIAdM5zEXwVpF3CKJ0j0izLlBjjQQqj3RBAU5NBl6jzKpD
+onmazXjfQsdYt2Mz2yJwoX2Fyt9r16mmUCLpzcL5hD0iZkHIGgsTvdqh+qHnrjNtQg7auwiXKVze
+nDZj7ut5uErg25gHVQI8fxnl8tVM4vGbwV3YfjrGOh0M3jfDFlO1e8tspm+wHdDgSERmfUhiU38i
+wSXCpstAst438XVoVhM6WzUd6tnJrxqG2clhwErulqLBDa/rVBmnFGCGnzMGkT5JxgKmcPEQK1iy
+afo2GatQh1FCZOUrhnTPayQwoOSAqHEyEGo7NrOoNyO8kRPb1z62GS1bbEh0TvfBKqNDGMc5SvAw
+AEa0WczNHMrig6GTDO1CQFzimvlKaCOv1Oq47iVaSlVFeWNvKXKXPQNJ45vsOMC2oBqoX61Ih1Ew
+9zno9RAOw/wJGTlhHbTO9NIgaaHvD3Ujr4a4F1+B4aLUFcvmkCnC/GLgMsW83ibWZF21awCr+IV0
+o5TOLGX6Ft/ulCkMQKlvloYEdgQbcW+jyoTJjItHXYQUUYapeG4/LOiOttd1Bcjeb0H04e4VlfbO
+LVDS2fRjlJJQGjTKtzIupw+ucj30nrrE+5mgIPvRbKNPsec1MKxSxjxViV1voRYnMJ2EmR+kmeu5
+FSPQzLq8UlOi7p2h1n3V2Ej2cTbn+W5O+vYRgRDQFE3vzH5SJu2PtIvtLvAMrL4xZSzztWTvfkLn
+HD5MDXqTPJvu4PVTRRGH9DTr360Osd6c7/BiZdbyiHYKwm15Yh+tPrYfQHSh7BOH4201LDcR1qjd
+hlmHmrd1MRwyy/7R9iQ8yB4AbDHK8QaNs4+JUev7NkXUDu0i88uyxD9ZbhPvOJGb3k5+onpRXLUh
+Yi55AuC0SMmQ0ZW5swpNXRey5YaGSt1jEssB2jXRN3IKRvsEP/ujlX3XDSl3mMVJEv3S9JNZljth
+VfIqw5/mI85O+r5xh2ZL4PQroAN7kZTOzz7XBMJ8jXVlquywlNh8IZrErFxNqgzSojE/NkJALoOi
+dvIY9dwA9xrPEzbfCgHyBF4369MhX6HlO4Lk+GPBPgyCM5xnMD7Sve4yhPI2iMyjxzGMWv1dZraL
+NA4ixEc0VTH5ncjpM8yB92mqxoNiSM0yUdn96JrzHYw5kOTMY+fjOA1khe7YLb/mFNIDDaNSIWBU
+uE+ztG1GNeBU7FWENp5ydzsqLMMMMvlfuTY1+6arz4fJc+21vQCEIvvb1iaIdnZapTj+SYiWReVF
+h07Me2QHsn3ZIQQnTEXzI7NV94l0F6PRHBmd7XSuOYDg+3UrsxfXjD1cGarlESjR8hW+i/1YVjPT
+bT1OWyT2rbndoMsvtkzr8EBJ472s8qvRAKYe58L+0GcW89hscpnt4hJPsqMVVmD2VQhyq5PHAb37
+be8wdhob/cYRM0gVXTryEfl8hhqIsT3kukXjSI8Ld5uV2XMNSvUZUiiEsb5p7kZzFDsLJ9lAybV9
+BpdeMdrHsAHVp7iW9k46oFmUjqSPOfcHc3LA6Ebj1qod62aWhiCR8hYfk/J6VxqdpEZGp6VpI203
+cBgHtseUx7Gj4kiggrawdO4XJM8V2O2mrvGaREHHENETkmLesE/0YXqybag1Y1t1rA+vlx8w5HZt
+WAP2fIt5x7gj4s7YDJTgjrsISuESKeNmEik+InTTrma4VV+11NWfpF130FXqpf20DB7ZXpSZX+op
+1fcOqFW+KjQZZfP9ASZ2O6fN0+i6nkbSkDEGhYrqMHnOkjmnqcy/2xoPMlWCfkG3FL+G2Qn3xIfq
+ER+qkXQo1O6wVHV3Vjh+6VIO1l4UJZzMWFV7Oclhm+bTY1zlzp2SIbiujnIA/5KY8mYTjjK50bFd
+uXL0xv0FdfJeA+G6bScNWLMTzvc2XfjdpDHLxv5V26yNk3TSMF6Z0u7KnnBt2MzVYn+2jUJ+lZm2
+1duYkyRCz9HBUWwPNjIH+0hiexdOcj6B70KUIpv0FwYX2McsnrzvmeCltly6O6XN2XgbD0jO87vi
+A7QnWKDCwLnAbKcDqff8ErtpcZ+10jjUw1DvGr3o5gc9AyrWQ0kf3E6ALmAMRCa1yMggHcYiapul
+yQJihaLlQTcLlO5kKTj0/hm1/f+xwjtjBccTQljMHf/fg4X/Vf78Xnwv//W9/Pmvu+RHdfre/Ouq
+zfnX9vdBw//5Tf/RgzH/7aHlAFHV1AECM8T836MGz/i3ocOad1b9BUeehxD/V6CX/4KSEDK8FvXm
+Ok38z6jB/jeNkVXHxVmlQ/gb4r8aNfwpYc/u15Ek4M4YeSASi/nCn2NJQBv0qxOieTwW5iaVxalU
+brbDSg4TTsRlA3SnXyACw3f0slMlWsCayLShFIYqW1KheOaWrR9OI8fkmHweKgS0f3vJ9/8MPd7w
+pTjfIs0J3QNqwhtBPOfPW8QiSIKAjZq9W9CTBK2F8F2MBukce8cBVg71153dwk+JDGww4eq8M32+
+1JRa3xE3YNHY4lWRfFxI/AITUO6IbB9TS24AJcFhq0RubswkxC1aGZDjQkxxPCwK4rqHbsp9vP0O
+LobH5zuw4WAIhEFsncHUn6+gtRLG9WTFe5rANHOE89TH8i6py/eE7i8Em/9zIZvLAJPwKMr+vBCi
+jFBw5qrelxUyw13UeYHTqeeqLrwAY8dkO9vA1AGvmJsBPNoWKhGQjcl4IBihaBiiW2tqZvi9hf2w
+a+ACPpqwlLfrvtivjVv6ZdW8bwor22kK544M3badtBXQwH7gIFHRguOTcU+7Imf98SLn2v4KruVK
+b5DDtZI6vI5KlHrwgZn3raS+n8NPVKKs1mJ5qoQrA2saYQu22Yswl2zXDvmp1JAEzWHALq73i/bz
+o7k4X97+QhfIEl4cW0JnligQ47IY8v/54pyFjjVdUrWXZujukmn+moahD7QIE1BKuy1Gvt7GqWkT
+v33dS8ExLmxJ07Yd9H0YPRJG/rxwoTxHteCV94yz8h1oYCxc3aU7GAayO5GJ9XDiLMO2agx5g+Kk
+ApYD+ttxSz4oEDrwwFHQuy0DHuppXAgRnPFCundVPc77PA07qAgGmAB0yd6TEDEuppzrvUM7WxEH
+DGLxC7lY1vTELJKBON+j9lP6IELlDYLMEHcHqBljX+0yBxnfLuyKOzW5mKGKq9XOrof8swlhj/8T
+gKwpgJNng4bauG2PGTNWor4z8zRo1ZB4mMuPt9/5629tgYg1bAmOB9iEx6nxO5QDZURNbyg1mTLS
+IwALyIWZsfzzohsbm9m6h0UFatR4b3/ym38bC59fGMKTnq2vTONX6nK9gRBkTz23D2l40S2msPcS
+LLjffr4LxMP5KuZqMbhqdtGiuAAqlTni31qd5/t4dsq909QMN8P49PZFkNr6y8NYHpATsCA4iBgX
+X5/mFXwojHjgO+UvoRNSptotYucRWtwblMp4Nm3kbBlWx2ixYKsi8xcRWcsDAEomiTixgh+mJY88
+y7bAdYQUOdIPecsiR9wBroKuoTpUuk+arc0w3pw7atHmKhl7F9p7T00kci/QGO/t6C0bmBjLvT4R
+31CDoRGBLfGuSvhrlPbiiMljiZYV5aYX8vNW7SKvyzQVK1r+VE8THeqV+8/AwgsgMJSb2FNWYBjt
+56lDoNxQmFSFXXoqluQkU/OBQjy8DhUKbJaZvjRGXx0wl0Va1isP2uTpMDR0L8hRY26iENASJSaF
+BLqPaGew4ATru4xaMLAqPzFBmWj0R58wf1wYRHlPMYsDIfqM+zYfygSH5RExqZ1pdLCA2O3jGr3B
+4LRfaDoxJNAaFxBOibyGxcVyL7W+C9ykN42BnkI+Jqc2mlwfY3gDEYecCYohv5UNRKWoL4xHxCBI
+HhIk7O3F1nZOnr5AQgCUtoogwiLAp6LrHhsj+8VMAukWPPCiEVWEAYo8KhWq3WUcID7i8chkNNqz
+gx015XDjbb3YdH3pmuG2t4AuE8vKfSaTk2nxOWSNQonWcgLnc4evpVUcGYV/TIX3VLcFU8a+6fws
+dOM9yY/JwTJY8P/4NGXbPNrJgqSX6j+QYOwZn50w922u2p4BqcZQfudNfM2C7H8Lat0m8baDus5f
+YM7j9lwPaBUPN0uRveRO6e0n0N64nPOg7VhI6BC3oFcNJjKD69MLucvCytiKmjOAUV7mGz1tllCx
+zqv1yJwr8quMMmw7D9mLFmmsWL7s7MDeFxX/S6/l5yGDs1BG8M0Mq2j9KYxeqtXNs4yJ1miGur4W
+VxiJI3SPhDn4wKU4YQ+e01rGw9geNPcjbnLBAq0YxwjURGa9ubFD50nvcp6R9PRopz251fphyAzu
+WrthPiw4PM5rdx5ZNrrymEmGMApUnJzckJxRRuYDol/evpvzk6sPFN2scNGxNc4Lt1m477CcAsAm
+dFAKe8+0+El5JDJo62T/bIGCFSaE+QAeCNH4geQTL0RYYdPKVE/WbEPj91WFMjduzAoyBZ+/1dku
+qq9wf6TReRwZYu3EiBiGclm0VZeczjfO7ZLF4HgTpBpnGhYxzQ3UpPZL741e0Hc68Vph5Jc7sYIx
+66FAM/DtHFzDdwtKT4Ki2odRBiqy89JtOg1HJIQxCM1QCp+6sKTdlb9o7RqwHMnP8Bws3eyfD1zo
+8sHI6+dKsa/sKX2hO+zhzJeezuGid7KXDq0ZdIWIBGUacYEWbDADCm+rbABnjehaWn28RIoB8iH6
+5kiues5mwDgMOdL0mFdu5mc1UYlABVlxUc/SqI7n0wmeGFwB9I0CKazw2rDTl1kPw3sDPbeCJGmb
+2EiUNG0J2xLhK+LpzzInmJgGKxd+M84KbQLQgX1safzegVib2RUvZJJ7iMCnjvxqDWcz+gqr88Pd
+OSj1kvASd+1zOnFvSW8j7ozLXp3LB+odVLQFWwWhidOsrYNLs0nxH+TjnquJeE1Y7MTU8O5gsVbO
+3fkJUS1/WbdEnciH9ShwbOOhU9zY+Rsow0PgRBuh8yHCm41H+q1yi6oFy6aEsxcaEpEo0TzrdMmP
+sklfMhXlu2ZhqTRIV/8T6VyLYCJxxaxmSURFNGlHNBk/tO7c0URg/6bsTHiDCz/lgpbJV9nGbv06
+E+STrVyq4xKVuo/wE/9JLdP1ORIj5k8iZke5Pya4LHDGZwg5uE9Ojk/Ehp+wuRN3ClokE8li+ACo
+OKsgqXCD0LIC91NPz3xXovbP5IveuM4bO58rZsZNYS7NVrXlg4C3CV1u3sMmZSPOvMh1hU0LwRj9
+igdJpAkgCSPhV7HoGo/AkyuWVQGtFmEvPo3pkVCsX7dNm+ekZIc7MVGfKqjc1xG/sB6oCs7xN1+j
+I3TPck930txoXlUd6rTtkJlPTo3HBaKYVQ0NkIRsyY60lemB14QbQOqZf06H+yTNd/3YZLdamM+f
+dAb2B6dgd5vQuDb6lJ3Oa6XsilPqxi/lMj3BLZo5MBrciQZe9XrahB5xMevYAiE+CZiz25mPMb3O
+bDEHOtTB6JIGAhI9koaBMywQcuwmuRtBjYEQWvNz4PxpXccHoOcceMjm3xEl65vEijvoKiWWF8zZ
+QMbGk9+LxQuY6Li7qvLQ+q87RFvaERWHMJb406olOsXO1Dek01YSDIKWVucm7d5zYlKNCd5tXT2H
+zAWCicrqh+Zly0czTxlEldnkR6r7mKK3safOYZQVCvHM8A8H42IuyYjNxGfoEPomo/FDlNeBXCiT
+hipaUwM1VFeNjJ170RfdSiIwttaIxW4219WVuxZwWUyeXC/NnSkg0DkorV9DnTv1GjqnqcPgC30z
+c4uGcRtkqM7fIByEt21JsF/LPIwpMj8WKDxwvLeBlGN88LSivktknuH0miZbsADdjh6yvm1BPWym
+nJn2oOqBAi3j5J15Y4PR/EoXErZuAOcnalTudBrqO8Ox4DbWz/kqXeb1yLYPiEHdDmiTMbgz270S
+Tbplchpy+ZRf1vHLLCQXkPwvAUsI0QdNL6/zavgW5dH4K8M6AREfNwQVw+STAuqHcsZdGs0/+onk
+WRMxQQvqOjy6AVpNjeggq6FBdq1MQDfpwya0KvC8oZEwyUBSSUvjdGsCw96tA1iS53sNC264PqSJ
+OgbAcwP2MuKbRmAckCZKKuIvuv2fIOlcNzZS4UzXFKFc+6VsFh8j4wwbWYF+Yq99lx1RN62FedUt
+1gNUKySqGv3YaGbmlxEhU0977HISoR3qBIBiOzHFdtfKZ8kQh9dR/SfYJi9iqrwgjsmfREikqcp4
+/mR2Vr1+YQCNOSeQBX7zZUw15t/CzT+XdW+BxtGfB4NQoYn2uQxpcRRZ3fyIFs8ivMG9hV3VIaxD
+EhzTGw7GjIxJp4ZDt0AzCFxrHLe07GjqnHMRwQGYbbeDSwVyXzX81FrRS4/kzjHZpiAIoDDo4sGc
+3GaTl3gJIAKKL9G6RCmY99Y4nrwBidysHB7gnKC25BUNLCBYxAtHwXqfg6s/CLoP+3alZKJlPqHi
+lJ7A450y0K8o+5AjS/2hXaZ00wGn345xO10LAS8m0R3UyB2Aqfl4VDP2LW1fB/qAvl2rG80neMhf
+GcPdRR0qqcbsXY8NQQ2Rt+w2Hbkbl6yKoWpHdr2GU+h3y23Wc+LRxFXBKN0n5BVOai6OJBjT/eJM
+zIsQMlMNeQ3ODkcQHjZ1I8ZNnTFCYJyKjx74vsGIIYMaOc+aNEysxjS+1xuhviY67x7hk24nMucq
+t1hhKmc19MBASbB4pwVKHH5sOe5n+vzI9GnJ+FTUGhy+huVmrM2rJMIfOMvgGrjEtbAlz8EvabrT
+YKf2G9tbg3RBtTIMity77RYelhzTWAa1L5N0U1dNdYC/tg/1vr0SXvpSavFLxGnfNJxDzOLvIpP7
+PJ/oOFAknBHpqV7XKqNKrCktfIoicgKKa2OXmrO207hhnBo4M8u5As+3Vi3LRIPIsSVqMlHzXGFd
+wrirHz9Eii2F4xgfG3r4vuvn8HqmMwmJN58+ZHaXPdb9gHShLnZahFLk5MRkd1T0u/Mpx0i1PCaD
+SRplzUxbXU8cI8VlcoM1PMXm8q2AmvQTnRRvS9dioAPSY8SN7BNqlqwmD2n97/kI+hV+8Yu+6Pqp
+QL7/mHPqnVc/9eauc9LkmmL1hSYET5Xbj+4EJsYzHkosDA5tyMmVKu3X2qiS1lIf+sgbbiWcz82c
+rWdgxPrsKwNiPzkUQSFSD1iBFRxmntri1ZhuDT2+Q1oLpFVuZhBJIb5lsrvWmEYQcdXNbCxYHYCt
+2qwczG1qkWAlmvGBORMKNhZ4SBBHwscv3gtY7RxxPZ9oKK2H89nrTezT2Aqf3i785d/aC/bKgxI4
+K6/Ywz/bJ0M6IEKQztleQ6URaCMNW9l1z7WiKZjqqAAtkPl4Cr5yt+BQFRtFT6hRn2X9Bbbzk+4m
+gj1MobumGb2jaztAT0/ZEN0DglmQIoJVYuSwSuJRR6JjHO7tAqED6CUkwF0EQJBz8FwjOcL4Ce4u
+frEnZLdkZz/g61D62MaJo2HP07WtpuK4erxRlKxJqUMN1DE9p17KcIfuJLmXpot/irBemO5jjyOL
+FjY3ZVt7ACfXLDBOQIRT8/oycsOrTIjpv2+RMxEwGRTALKcrYF50pLBeiAGrSTSvWmpK1xnDa6DJ
+2sE2SLpw+P6cnAPvKuiJnuhaJZE0vv1Z/9IUQ5OELhsYE2Ypl708pIhrmRhZv0+dFgazscSHtiFP
+im0EMlChBe1qDzpOJYn5TrtK/KWNSPm+qqmbBAx6SX8uKHa2QN7G6/dujReIJKj7CHmKx2S0C99a
+lPrWYw69C/UFrKJM76uhGD56ytjP5iSe334Na7v1skNn645AUwVBByBRf95Lb4Dgjqsx21trEFgb
+BoCrSaFRmmPEaj0kEdH17Uu+7tmjK22szgAgeQWJ95+XNMtOp9xEEgqsg7vL6xl90og/ibx6mtpm
+2AyxNkKhatASjobi8PbV/7KbmRNwAzgLnEdZf1694KWaXal1+xpJIT+jobMtKSjeWeF/ea10mQ1p
+Y+rxlzEVpyn6+eQS+0UA2uoRzvPRZ/qmze0dJIuvc4f5yNvPJf72YKsWu0t/W9DdX1fdb1y1GlVw
+0pKiw4YwbW+wCscPqrOaK0ICrZzRfcLQDsdpne6ZYUenYsrR2pkEGLCoBls6JD+X/PPb97Syfi4W
+1zpHtHHTdC2awBeLC7++JvF0xR7L0m+VkvOvf5LfDGe5CnzzO4L0l5xFGsES3wAHESLE9tdB5J+v
+oIeeZ4dl1u5dcKiNYXh+qYGCqUJwpzpZ80YM9ncrTz8p9H1z3fnUJADHh2S87Y3sZ+eupBTgVe8Y
++q5T2YvXIHHJkJKlzta2zyOR376M6U5qjpyo3RfojoOyJ3m2a0INNoEcmYZxha7VMaZJ9sXsFEDB
+ik+kxQUtXa16Fs1EY4o8Do9qA653teq52uYdqomI/qTpD7uFw6JP/mKRgnTOldmaDwY5Th/FePRF
+fbrTughOCp0aZ4nibQf4C5Nyqm2oN0CSV0ndokNN3Fxrax34Rx6WeOeiy8eroZW1ju3OB1u66M3V
+2yvkkinLJ1snyXA5TbiWOBZcDEs9MUwdhSFajSHlwixraAjgJTb5WNAXA9CwnWMzoXVQAMccBv38
+mLRWt1ZeY8O4ogajkJNuSRtcjPRe20mdKdGw5s1LRlba4gN4S0sCRVSXTmhUvBvPLkX7z8/gYoph
+mRKMC8zLi2U3dMT5hmSTpBTLINRxfXpqQKCc5rkHzAMfozgi/d4AkIYSo+VI+o7wrd5+la9nrg6A
+fZaXweRed6yLN1mki6kAzNd79CauYTLQtWElwOO137mQ8TrSMDrERx29InyqnctIwxQkRGMnU6if
+0hUEjrYRM8TsGmjdS76AUwPSzeJdu8v11FdAwRATM3rkw3DUjfxRxScE3k/o/GKoWlDv4ST3wvvN
+dtVaM5YU7/S3j43JbN7MacNp0MZ2b7+tv300BngMQCUWB/LV5LikcjXwsgN9hcb9ihJDFbSc8Btt
+yTrR7EMqZOx/rvXSnNF+Qmf5ZS7cdyLW6wDpAItgnghD03qNZsiNvnWUEGqvW9UvE57PltfAxfLG
+2CI58s7VjNcTLMcxwawz9zUFLNLLkxfFEle3DcX8clyNWFH3WMeSKF3htyciSQOXhHrB4BdBEyv6
+gHLUcwWD69aGt7ax9OikXDHf5la9HAYK700GxWRjYbXoayEkjNQcP7z9mV6fo9wxljckxDYR/RJI
+0MjJwcuNreVoM57irep8DcGTXa9TP9HK1v1Bz98ZWv4l4edqrAiMUlbQ5OVOwn3AHavaqPDxpLFZ
+V6ZFIT7hmFpZcO6Kjn5qVBZUtP0VSlCQ5UwalWvPkH67tiuMCrJqSQshZFCEHMyA/rc0xTWtFRHU
+ZLPKpMTEsSDzTdk9Gwv51rknUgoKp5XwHkByJJolkn7tOn6xjD55yKiosG00Y1Q+HQttW8j3uMR/
+ymsD1VGNoZ5CYBpYY6GC2FmT+XDEzHidUOIM8DCN9EnOs40qR0SOmduPtRK2k47LTVAPRPjN1KZp
+q1Q7BsvCMnz7U/41bNhYwQheLrTkSzEL5S5J3CAruY/mLr7Hf4CmAOVLYEgL2DR9TM5AitzEM060
+zelmSz40THrXH3sDXUkbJq0z0yM6x/rCGBmNzvjJolWkpN91xtfzaNNSwgPzUzTXBePuuzjlI7z9
+JK8TWJf4SvIK4kQ3MEj5M943kcUItnHafelwGPeIhq0KM2wJKx5uosYrtp67FF8tN3R8E1rhO2em
+9Tr+wuJyIKLAs9aFuIRQeO6UoSNTogKdM0WrjGa6h63bIQhBJ9xErepzqWSxTcw4u+qRMPGBMNNV
+0OhjJ+ufZIb+Va87SMAuLFPOLiZKDgMge7a+6aKHY1U9ay1F53n+QGsDcW461ROgzjBunqVapwGS
+JntKU3KvF2uPb1rbuYtKHpp6tD7rOfxM3Ts2A6BPaS8yQISIrn3kvfAPQ49c039ZIIL3pQvAJnMY
+N779kf6SWbgG2TcCv57FqWyvb/G3rAtgOOKg0ED3NUOK84CgsNaRsGAipBK24dLlsMey5QqRSexA
+EjIG9LQYHigobYxhFr0HONXAnOS0fsjX+FbbT2iTJMzF1deSiT7Qd2YRjl7M+7fv/nXccw2bjIJ9
+r1OmXtZIPf7KbUHjBcsIay9C5otrqMhm2pHnblQeFu9EvVfJs8OaIj+lKEM6iIN9vaXf3lcscH5t
+MipBWttwwVUHdn2d3J9nMe358/YMheCwrkgOQCPImzHn7Gp3A5+i3zX4rewkYBZAvsSct9/H5UF5
+vjlJXst+W1FD6///7ebs2U1TDVDzPonBEXQN9wDpgCkA3ylf38p/fbl1i4NUMgXFxKtjJ1PA7VEz
+3I9yXbVOcZw1EiqrZe1QO75XEbuXFYJDjCOigOgEyCaoHP98vBgKjL1A1d7HcSxR0xwsYiEiWJPl
+BYyaPESwMzISzFY4M0hD4YeNyIQKrbyzKsv5MlqFd58OiP2a/YfWdvH2tDt7Y43AdUf2qE93pb3J
+XVXuIZvZG9WVybE0Uw+0CpJNydKVQZvwy5OhWfXZtIeEdvhV2pciqFKUl7XKQOPfddWBGsaKt1qV
+jL6FkOFWh6KMNNoIqjwDGxzVaDQakXkNlkNjopJ9aGfd2q52b3vHMHmHokmOdq2lPhYH0YeSOjlY
+Bm3w89LFgBJlUvTJtJNY0XZirPsHPPYMGFdhimoylRrUW1wpyejoCDa01RPm1H6ZFeY1AFUJDizz
+Ut8u6jIolZVc92kzwIazkMKFMWTuTad2D17CPWgqjOjvflSd9SGKE8PX6A7fgOpfaP8s4ls/4jnd
+OZl8Z6OZl4k6JqokYVh8Ua4Cw7v0vPKiuvG0nFMeBIULLZc9ZuagRqD6MNkml0qNQv+g6rrch9Bi
+IQXO1s5Q6wfENtZ3mw6ST4rYzMZpnBSHnfhHbqRm4AI93HAyIL3NAtrNmov8OQHSt9C/DBgiWNu1
+KxG45qJBux2to7f++rTqPnSx8SQd0CYj7iI7T/bmrm8KlA/S1n2n4XR5eAH7Y0Oxg8ljCDT6xVIn
+ciI3VGcuhq4L3MZ5Q4vond17GTzPl3BAGEpPt4XU19bfb8GCKkzSCFiVTxFURyuD9uuA3YSfqQUw
+CKJ9vBvtvaroMingosROi+SGeoKwcRGhIrx9UjtunKCuHPgRkdds0byrGbtlMNRMRnqaKdurqtHD
+rYXszzttLXGZ22OXuCbIqBvSWTXpuPz50HNd4J1bVGi22goV3AnSCTLxiw8FnwuG0rtSXoerojCe
+aDtkexirw6e3o+YZAfd7v+d8D7TI0SpzAf2uKjW/v3i2TeOsipJBameaP8x1eyhg5FGI67iDwBbx
+tgjwtt8nfQnveJHWXTWBOsU6x/2Iq/Dix4OD5xiSGEFfLJhYtwavEn6N38Xo/mdxA7tmbuHZODxO
+hzBoXVv20VFj/dlAt7pcDaGSPXK/96YTwbcbtPyd5EsaPMMfz0gCC6PSNk2TxjVn85/POCcd0m8c
+oUHPrjqO8A0DXUXQaNBUuD4/BHTB/F4fI2e1IBdbBo8h3EB9gU0IdmQhBfPR6mu2ZhxGBy+KXTi4
+qca+1ltUHIwXBRbjoA02EDIX24kkMh9gNJs71SQDFJi4PeS1je6EXNy9PTkDU23YGjJNQXNggJBD
+WgHhU60z9lILCmUsfhPKTaRiRFybur2b+MlAIXyziePocdakhlHSmN/Pi8KSAS14zFavJWRzVOAx
+iIvqeLg1Eqd71lDHeHvJmK8Odl4nTXgwlQ6tYPOy1lKeFyYLdVMAX5/eSa81Wycdjkk0fiwKK8SH
+yBLB0gkMNuwZlx06XtsUa4FD5iIgjpQbwsTMl7e5xzZLyyG+qbNI/16vEr764i03/Bb7OKCOyUTY
+Kg80kvoNL93eZ/qwig96N1R5+hYiTshApbWC2oDyWKA3t9Xs6nOfz32AtchTQUPaz5bmvczGehWt
+LEHNzY41JRpKtEv/XFBIFM027RSJbDOHN74i5jcDo7yUQ4sl0PausesrjNi7cdICUys0gDh1jOZA
+5x5mK1GoGYX9psBr5xOaccA7ErZdtkBK27gyRSV2VCxMO9L8BnCcrzeskbmD8CYSN0XAxRVoMqzy
+HTHOIob1cRzMZ0sT+Wb2nI9hnPyk1kFSkvnUTdFpziECtHEblYl735FP7rDaqHfekFOOl/CQClQ/
+9za9gb3FyC9gMMlCH7jk5OXmOz2cv60dJhcWTW9i36ukcEYjiRkla2fI5QtsA/d+3StNDwlwFNHw
+ThvXeXVyWXwiE4QanVzDcy6tsoueXpXed0RY4FQ+XnreM8Cy+EYtpdjqSzEFph6md1BN4xvDbQh4
+DemXGHnp01CvjH3UjZgmfhm88DhG9m24IJYuQPlM9vUc4WpWz+zrIQXyyt/dKnJCX/NYl03K8WGM
+7GbS9peqrZcHowLMJ+pl+IWdV3uAcy6YHE7lMW11e5dFZhTEQOI/jYjRPzLwD32BUgGWYMmCri04
+DeiGtLjspd5FGqUNYC7vionsQwc/5uBlM5EDwvNtYZfIL8OuuB11wnKrsixACyf0mZiuSqjF8EnO
+rK124JjR4sEtttLAwgaTA3Zhp6UYJ1S6RW9N/2aGq1TuIBhnx3GlBd6qZNEOkRbUvMhN7Ah7F9ML
+IgNlQyzvZAV/WS0sEnoxKx59PSX/3GetbedZEYGKdRtAOZg/pUGjJIdThQyAI9kQb4e219djqggi
+nRSLQl1eVul2VoIMhmQa5Gi7M99mNwCb867AHLmHeEEP9e3rideJJWUbWohUvMDU0ZJd7+i3vMcF
+3gb1PbICcEwmVGCQoUK49jEpGESVix7fTKhOY21io77cN4cGhjaiK3hN4J4rcFEpGQXgtoPpFX/y
+eg4qfeBT6xWuQZMjur3CQxUEZtU8YgQJMqZcD3f5P8yd2XLc2Jl1X6VfABWYh4iOvsgEcmQOZHLU
+DYKkRMzDAQ7Gp+8F2r9dVf7b3b7paNtRDlmyRCWBM+xv77UhA0ERzq9WWb1PyzIS0R6L45qHztby
+d/yLIkhtXKFplSh+hDb5WLlsdrPtnvJ+KQ5ojS9RwcYh3w+EO3+HgyQCRZXjZnLD+YiupQcArxBW
+quaxnXnWtaUK8HtrrTOOWo0bxa84yozAKzDca5h88YjwNtGM7W5jHsFjBbwVJqMpt5W97KYF9OWo
+5lySJewzFIDOK3V5V79DxE3RTR/lzPoGzZapkOARzwAr73DFs/dkLLttVotnet2UDZ8bnakNX1Dt
+OCAlSvZ6T4mZAkwCetn3z+Y87wnI2k3jLFzgCmeI3+nk90esBatp2XXTWG/3wDYcXhaWi0QbOA/I
+ceZDHNt9LFX3pAkG+F3ODz0ZubuWJtpTGfNL1IgTRBl60m8rzN94vgnzR21zTiiKxXcWVuwL/DUV
+S0vPvTLPft1rbdBNlb0lo+TtSaHz2dG6uM1n+8menE9Q6do6y019z9vZ35GpMQJWMJ5ia3K3vcg5
+siQco79fd8/m48Npyp8AvMKHHJOu6UtkiO4Zkks7347vp/1/Lfe5/EGfJPKbBKR0+x///tc/2H+X
+73/4QVBKNuD77lczPfxqu1z+vzL75Vf+T3/y3359/y7/TaRTU/m3vdhL/kmmk9q+98/4Pf+3a/P+
+81cb/z7J+fff4K9RTuc3k9Alcj9t7ZqHxvy3KKf2GzkgMIqWpjkkmqy/QyO939hPbX61TlrTZLzz
+tySnboOaVKGt8tuhxJBu/FeSnFwsWI5+f5LGAoG/nMQoQTDXQvz443IloqKekgWfA7wxgo42t9nF
+aWGa+0bYSZLsdMSkO1grNbUkdRPLVUKDjqBVh2psdDHqmjS92c9xadknTSUhs+rHhH/iKUne5gTo
+C3AoEjQBDQnRYa5sgi5Wo6sBep4RnWGNFclOMaf6zc4pQFzgYSXMRQhZ3KOjonUD8p0OjQ4sqZp0
+FpRt3QfqNOjY3FyIfjPsP3AdJhogR2OZ+6UeufN6HrzhHkBfmuzGCo1ircOoJjw9pkAIsIXhPO4J
+WlwNXcAlMeua6MdkaQAQVcO855xHyUwmegA0WjrUNEYrok04PhTqV5yo1YxdwuVNNwHYPNCtZZJH
+C4voVZDfwlPihtOnYSvyShlBuDguy27twlXoIGKY/Ts0gnFvuVaBrlXbyRu+j5bOVZONe6hUlTmB
+DUIL2Mde02AkUhAB2gjzqm6vDMIKj9LWp1fGRxR1lLMeSibIFeQb1+G6YMwN3bYQtGBA1q1jnPRC
+G060hChHo8ixJM5mMp/B43TaTWePoifInES0ofnU8F56WYr9JOJWC3JPxZMwU1QgttOo0WKzAlbe
+JHvRtpZ6cZfPJQvEbLTeJiUH4QJanLiqSLZ2+Cd1/crskyzl1C8fVrwHigr3kB5vSt6keSQ8K3Zu
+5hbTRSNEFK0LJ+41uCZgSQnT0PiYDjQ6A/UVZNzV8QF+2lcK2SwoM2xUA+vcnnbEnmKLUF81QtPJ
+6rTTup/CmX5GB+COAdRjmk25STJtwj2IQR0Ogg3lzPA654awuh9qRSPZqITeQcm7IjDT8MbRKjob
+ef+i1wY3G5spKM8Hhj7rp1YU+7Jv9sMYlVslVwEptZ6+XjzMgYGAd4p0gzJMHpuHwqgVUAEAI1ID
+HFwuIIgTNlqi0PWhszEbRIpJGSUxyTl0T1xQ2pNrwkEBtC/u8nhw+K6a8U+zb/Ota5bFSyKt8twb
+mQXEcAlRedWEfT6m8q5vowvMJScwwD4+OI1ZnZmjMp/PrDmYmbAthjKV/uB8vGWUK64mmUX7qRvo
+1XCc5lCDCVrBxQt9Z6Rx1KxSUtupcROVlnFgigjjUlexscPchF4BFA0/FR3LVPglmuxOgvmwwMeO
+0pJOVvcIhOHa1w3OFnUeVh35Ek7PsbyEcd5ySpkkZxUcXVaRYq2CmyaaNc3GD9xSc0ycyg2gyC+Y
+SNcMfwV9fsRTcinlukxbKnUkb1nkKhj1+Blm21lJwYBXsxgZj2bP8z8VysqioTTX4q1GuzNdHbP6
+q0mBtTdVfaxth6bTASqu6lHq02Tjl1PKY8cAdS0Ghe98bRRreGyzgjGY7qq8k9gbLJLcBigII+Hy
+MQMavUtjxSEURisCF/1xPTggZfPJml8Vvu5NmoYz9zJTbA0jHU5unOEId5Xhhr/4ZsswPeRW4ZDJ
+yHtuh40TuOZoBpkxlvcNfWcBjRbRilHwfMa3BEtzKkYL1mhoEOVT+s63U90AsgjGyJ9yoVBEHurT
+c5JC8YCdO5w9j5pQO3OywAMaRdFm81ULw/DVzhWH0Q6NTawNXsClnibFrC+uFshREnetfhhxhn5U
+dVluKKEDmhENVnk1JUy9vFcRS/WQlVBi5QmsSbgvg6dHP+usx4r8u131+pdd6Pchfvt7iPeH3QkI
+wuLoUJkBL9eGP+mUdCSLOI3VeO/qbS/9UBsK25dJNV1aMiZPQyVN1riKZMFgCIh0ZdOXj6VQJtST
+XPvZRcJL71BZNdA2ErK9otsEE5rlu495X2ObGtSBnsvYCblAM+Cl5a90tXhvUbE1XEby+xAXM6qn
+WtvIHiZSSEaOvGv31rFOZvcEbT27xi71z6aoQ1rqqByU2LJl+4EvejmYxfZL1kKd78sMlqbjkFde
+qYLffQVnbTh5YOT2EGCnbcf6fpwjULt5TPyE2pdxx+TdO3gT4rmrc7YzchJkyAvy2YPj5dsD9Mqm
+Q0jnKJs3a8k5hCG0lWLqZt+SboUSj5VxbQ+AGXeu3VBBx9WP6ygNDTqllSPRu12jTlZxB7jUDbzG
+jlZM3JRfOLymQ9vSvpVHFWTMxlSVhwz+TjBW0roUU2tcQe9GNxLfwUyJNe3KtQVpeV4isqlWXQqo
+XWsXj/kFi6wFhAaUV2+4AoyeYDguy3YVqQxMazWWdI64t9hyacMlIZpORxpt3yupbalcxFeOJn+u
+04++5xataO4dVBhtbSF0+kyk2odYhbEZV3xwnDfWZafiq0JZV3agfpJ3jut4uHMmGZ3TH6RSPuhD
+l5zjsIgxfxv2tU/inYM4u2dboSdH2vlz49QVHFA08v3sdNw9aP3sA8DGC+G0KV9p/Gh9Va8/RliW
+66aBlWzNRHA1ns2LcIR2SyLr08Gq8FDFvHm4WLqFwddSTOjGrQLDn5rSvdtpJu3BfeQBvJ3M+hU9
+GI3MzRzPBC/WW+d6rnvwgKNljS/ePEKh8wq1fp/w6bzJkFvWzQoVveTrc8S0thlrvGn0t5wpxjLO
+SVzaH0MaUtNV90wTIstQPrjqtdjc7X4AmC+trQdnh6GOQ2CzSO0bjZny08B9saLvsLjp5djFgcOA
+dmvlLiXD1EydHNqJT13VeT2z2hJkLvDDB9WU5ilPWW+EGNjn4Yz5tjkmgW0r7qNA6ViZiWG/c6oF
+7I21gKZUqGv5IRkWxKpFqgYKcq5kD0MpBpg1bm3Ar2syypmyfPHGgWYa2oDFrhYbAHC0ObNi4Zxs
+5m6BXE3RuZAR1Ef2RrZ9Bxs7E2TxAMeqeFn05F9dZXc7jl6UxE8GTRRGLUCqkZcBsOp25a6evJnV
+j3KaMRiY2T/bFpmNbMqMc2UW/UOUet5r13JzTgoTvaQJo4dZyTjyGGpT3vgyskdtnvnuioStaTZz
+9WC7Q3+kcsciIO62zl2c5T1VYp4AJRfSQa03+ttEUuqA8EJ6ghqV9C2XifM6hcNXX3eKuta0vt9p
+arnRQS2zYlmptc2yafyBN2uBr4/YolYtccV3sq39Tatz8zUcHbvmOwokcxW19O2sEgJsO5Qh48ec
+kSNmU1LebJmkD4kWeu91K8ZHjS6fuxTRHUBpScnPcgq3diaY5DxAgwZKptEtt0mM2f7sbJNuHqWT
+6Ffo5WNgdVnHvlohGq/NUU4/VBfuJA47soBlmIIM08swOypmKk5m5wy+Cmb0p1o05A5U2bov3Ngb
+iXFPV4wjvOqIm4auRtQ2DFOI7XJMinWtNExGJZvFG/pRcbMGN9sPIdEzM8KzSA7HRAQzwxIwhcdJ
+bDX0Xntg0QP0ok79mPtVKAogSOOg/5BOPVFWbg7xx5TCylsXYd6faiiyYNJCQjR55rTz0eWMrWp1
+Fh0nsE/1BtcJXUUxXv8wsbtDnOrUFzOXmp+Jjel1oEkNL2g0Kk9w9OOrtEv3oxo1eSPRh8i4PJJc
+nrIx5yGIeAmp80J8dAXPyLpBm7ojMKPtE7LK3H/GYqD0WUZFDm7PjK5EB+ZHqSbKBUAui72jxljm
+xjlXvmRnlsTJCh1Catuq1nn2EkQ8hpr9SRB0e5tjw/hAZpzI6KW6+AXMK9trwg6B8zNofi1HlOtN
+hkcV3oppfukJrdEkBHIR0ENE0F4kzkgtfZ/B8U8z8azhdgT7WY5FgJEEWB6bKLSwzAV4KxVI9DSz
+zdRdN6l3Qaz0Hvh8yvMgNU6ddtu8FQIWmhsaZekzj9OhuYFCeStkBfC8cGXXrEMlsQItGsZ9YyrD
+1ihYAfzUQj5Zp5hVolVaj9WF0Hdy6QB50ipj0Bk+mJGxa8rEain4znsGu2km9XWc0O3pl430ngmN
+UZFuVc6TpmjTB/cYyqPTMTHNlSgnG3ZymDTnZhonhDZJBmtqhlddVW8gxMQjOEaRBB3enwtkB7W6
+9tkY7wCFWu9Efx1+asrlOYn0cS+sIQuwfrevnTDarzFS3cIHfOzeKpXU1mym0fM05OxEWe8AkW3o
+mlnPjhsfI8Jp2YaDsHKKKGS2Nl2tlPsYhYmRgRE/Nb2tH2gTk80hg0ORbr1OAYUbNe5Al2fcXByX
+WEMeixlmQTGuSAK0e8fu3TewOuOt4bg1+hrx4z1XJTvaaKOR7/HgF81Giqnw546nk+zjVDkXoTF/
+8YkRqGu6r6atKgbjndrcZg+RoDqrWjauBs+ZiBk15uBxnwRoFsSIk9HKE8p4VZqhgMZuDZ8O7ZY/
+ozqnPLVL3aIheNgvJ1bWiXeus1DcuMI7wPds4felAsp3tAaHY1E6PUdDmmt08SoeVRFenXKXrmNY
+H0WfcfwVvNjTOupnw1ccV+zTuZOPppWnGkyIEWVbzY2S6kvS/CssIOLkKua4ZYi35Me78bWuaJy4
+FPQ48Aw3y7pZJ+pk+KznBtgGRlbXmulYH9D1RIXVKMBZl6pTzXAvOBVhhKGYAPc2tYdq7s2rWsjo
+c25m49i6bqYGxExmQoZFlEV+weTxiO9KqCtjCKfpMOS9Eu2B3jRxQHZ0+lF7HNvULi2eRuGJX1Y2
+uHtV8coXy8riZ6/su2nV6+qwHdSlAVlDUAXj1+2nMnbXM6nLL2qqoAyG2CYJvxZlPq4FvRP+pIUt
+VkNL2bIlCZ8ZA/c4lctYoTtc82GwZxjEHOvTxCu/5Ppq63H2NJx/OpfIyLMPDr6GzZQzSAIJMt96
+SJ3nHHXG1xVgsV7YQmFPxrR6aG0v/Kzm+rsbTdxyFdCwH7Vtt+kqqXBflEbyMCNKMSiP8xfTU/pz
+npnjY1U7JX6wmRgUn7V6AcLv+l5Zh6c2V61Dzwv/OEmO/o2ST7vIGSFMJWP5VYGevlh6Yz3y2HMS
+Ts2Dhqq9H7VQvkayN4+Frc1QNDUcpJbR7XHnw2GQRrnVM7Gin/HGmRzwtDOKI6AF/D+dUe0yO7Hf
+VL5zH6GRRoQ0VGvTJ2bjh7OW3dVdmVxbZ1ojU5krfMzUvdF3kQC80KMv14yfQkx/O9OqgwLANi47
+b1hX3DODybCaO1gEb5SxkJLP2mHrxV4TMDIitW/jN0I2f6GowUNeroe91SafmsNkALUC2FoDORjP
+O+cBvTssLZQ7GsLyY+imus8UMFnTFZj/wA1cnmZTwKOnEZYvMm93GFjkjhmu4yvSTTf8fdqNk5iA
+++FtVWye//wa9w+uCJXuedzwGE2o89Q0+0/DVYXltwQb7+z1PtE5di6nNNeoonM9lOawtniEpjVO
+BG1VdwYYnqlz9oDl6Iz9b76Qfxh04zO3sXct2ir/Zfy5Ta3pQgKlmjPuJ9r70r6VH0jjA2yg3vTa
+i+uW2lLySVw+AIQyPPRTxf0P4oRkPEtvQhCb/fMw6hY6GTUv0aagEQzIbWwV4h2So0PzdatYL4IU
+7pWhOp+8beSvrgAebnwLcsXQax9OOdJAq3NrfEH+UMCBSOOm94Py2cQhB+/OjZ4c1egcWCdR8ioT
+YwnD9eYJtieiAMCFF7eJeFCSeLwXlZ1CcSH6E0yzmh1BDzQ+lbQGBwkjugzEbtcSu9KD4xTTEW+x
+ceryiO2wtPKNMeavulGp91KPDs6guWt9ES2dRb6sv5VMkiGskAp+7zhAcrUe6m/ZM/qWQDF7qV+0
+YSAH6ABKf4Llc6+jlTUPVBtrLxgJhVgJQDTIX8uBnabJDr5Y5MJWZ4DyBKeH5zT/Pt1r3yd97/vU
+P37fAJI+mz4tikYDbqnuJf2+J2iyMnYh0YCVJCupYyVbrhOoSfY7FgaYxZnn7pVQf2JA0oEnbiJc
+8Sih1B5YKyX1aFpXljsLXgSuL+5ykymWOw0he3643HPCeJRxQMlacUurCXaHNnAjWu5G7nJLiuMh
+8Zu6gA0roJ6niyK6ZjVRPvLvS9a43LfS5eblLXcwfbmNTQrytoBSMa3Rcriu1V6szzfbarM3S8/r
+d8vB5+qX8IjGF2JBfEhwaa2znLlfbgfTRgtHSK9fm7C2y59KbAMMj60u+pKwacX1n78m+j/EMpBb
+IBYSD9SZT1Cd9SfvVldScg2zotsnnLVOtTJGwGsS4beNke1LCh/2wm2KgerBKgzGprq4eRXegcUn
+s6rYAwlYQLGoabMS+SgA5dJ4lg0P3Hqq0jfRSV8ZWdf9KkoMcTMHMA+1nppogHR+2M54wWh4GchK
+gxIYtP5OI1C3FHeM4Se+T2MDWNLe27HI7iGtjUj6dnowbO1WGzFWxvAKoo5wdhhhyDAoGlejG++4
+cSYlfOJiRjybAveeFU+1FMJOc8eWLVx7FyfCgrlhc0Bl71B3fe3kV9tO1atRaXj5KtOiSsSxy20E
+dieIxk6JVpVRDWhvMLHOLC7i6jYtQBZOMtK30JaHFeuqR4XRmNMhK1RqRDoNogMX8Lr86XQtto3M
+7ThIWvKqU9n6PFM56ldG2i/eotz3SKcWZLWd8C1mqvA2WhOdsENRUREss3ibENOnoyI0HWYWqdyk
+zhTtStfilTPtwebv18A2mAraIYvQ89i+OjXcchMu6QZrvWkxemIyXDld7+1stQnvQzjCHwXcH3yX
+URLQL688jCgjKAWJSyWW1R/yFGeEDpj7jLQ481Ry6MxpqztiklV+0B1dB/x2kvmwWz5kSerq6Ly1
+eFKnkDeAmOmqHySaGZOceGN3HVvabPWbiaTZW69ryaMSt/qzSDE/kr9VaePoBUvTOKT3M20cPihI
+42ixSq1Nx5FBxayBNAgAEyfW0qdSbQnEZLGH6514qXlIDJWug0La4R0RKXVrO7HKe+2lxl1dVDfP
+G8Db5AgU9vdOhLnLvLeVJjoN85gXyDtU0KxSIrPutcxCYIH1MkTSvudJmhy7eR1+z5nUZeTUoOrO
+zLSXSVTY5kylvGRKASyV+of2PbXymF/p35OsFqvLhgG085x/T7pKXVGsFa7eBeHA6l36rG71W4S6
+l+xo89GiM8FkTQ2Wfeyn2Q1jw+1bdwUHAaZt6TLQXtXNyD+5GRj2CWpds29oGAyGwdL2uKok52ph
+crnuvBmpCTZVlu5S126ZfyNgWH6TaNXR6AzOE+Jb0x0XeTeztFfh1lh7ZfQIKOw1aZYXRE+ZDDnJ
+QYQzDv7ecza1Rv8YXzWYFyalxzFmRNTSKLSrs6l9/+cLFQPSP84uQQC6BJNMEyIuxrVltvk7q4WK
+Mp8hiTp7LwIe4V1E1tzV/f33H/IvzbhPyWdTtdWX/J5Q/21i/T2F/vuPHquC//z5l/wfnXFjfcaZ
+8l/PuE/JXDXvxZ8n23/5v/0NUmyScCbti/fL4ZvzlzLEhVC8uKt59cgm6hhJ/j7XNn8zDWw//AuT
+jOZYbCx/JRTr2m8ejk7Mwlh1+P/a9r8y1/6HHcyCpoozlPQGI22Lm+kfH41Ra2foUvQAlL1JxWxW
+1tvBEsW2SbWzgeVmn4Q97wtt2lbU/dLpSDhFFkrV7z6y/88Aw/sO8/1+gLF8HczwidcSiDaRzv74
+dRhepFBoE1LGmLX5TjraxjQy8Mhru8N+dWQCKuxrCKqrS1D/JgTilR6Fp5QzyEo0xmMnQOrpu5l9
+ITkbank0UuKRCY3UXJ/IZNnOsdao7hnwkZqWvJ+6iaRKS+cuoCBmPU9DywAErO4YlkFatNcxGy9D
+BtLCQI3CJBy2iKNFdFHSmkI0K3vsEqMJWiN6N4Gt+yrqt2+xLtbw4BrEf/4gv3Mxw7NMvbZt/WhM
+GFrDCY6lcaVgZ0GbUjPEB9syCXmlBC1bRYDfNwwQV1Tv3PVlAcM+jtaTfqqUamMLA6Lji5LN6Kvp
+DUrwAWrkTjecQ8m8mHgCI0FxG0frDU6ts5rG7IwHu6Nto7fWVNi5O8NKXsianekfPNij9auKk52r
+/lBa9QnlmpmWc2qs5sEOta1OtQaqhz/ouljpDl8GcJX11GXBAiKs8v5nImho72ZDI89gf8HaD/et
+paPNzAZdcRnWh9GZj5wRTopL5AriSr4aNJ3zvX0r8oju3Ye2dNZkDmxi0sNNjNEVbxq6IWrVo+Fl
+IIumAICPtAdKToynAgjGSlVMNLGbKMevvnD3Y6u+zRAxJuJbq3ioX6Mh2UxA63VhWDjqkRBCmoUc
+74nHa5VZcEq5I+CLLzhj98Gk9udICV/Dej5Sc/GAUxtXttM9UZ/oa9rPqijOrdofu35EVu8ivxqZ
+0zINwHWsl+ss5NwxSu6Ocq2bGJlVrgkOj6aI7SdGZOoKgPPPCv0bnHbhV21aMKomdJnKT1UCsQ/V
+EPbvdED8DJC1ueHFL3R8P5rFi9M08yUl4fTSz8Wxzcz7cOz7rTstupEdDXtTt33iekcAmb4typ2M
+s1e7C39lSnWa5kttPbVmQdaSBmnwqOo9OymHzmHeU3fwYmrlsDT8+X0aX+fQuetH4cM42fSWcTGn
++8atTyRO120Ts8+aU3XHvW/XdZSfdzZiLR03QZRK9lq8zhKZhAwpJYxufO0j7Y4mFETbfVsa5Rr8
+9Irl4JosrFcI3y81+OQ5sz+osQnSoWRKqGjNSXjaUvGV5Rj2jGAasYa5kFxzdyOyKyP/9VBr90VB
+F0plbnJ1fkYg3PV6vqJKdFgRAH1REk45Sr7l0XB8FazN3qg6kymeSqtUb5+rTjvEOr1++vyU9Lrl
+i855Q/l11hniKaE/gK0cMorx4ujtFljRupxd59iXQ4Cn/NPuzasWoqWZ1Ip6Kp0hgvFe4tFPl3k/
+ykzsk876WWXaPsXwSooICJ5eFZssL3dWqQ53zJ4xmjqE+sCsPSw+LyoH1UsE7yYotWtjz2u1Vfnk
+GcpFqrJ36+REi+/gM4LGXtv0G3NigKnY1tXi9FnkKe4EKumwGW17fDVUdcQainb9UVmeTy3Dc4F2
+a/M/+HqabXIs1v40VjgLmydKOi9hKd+6qaiXXs4YL6D7PA/TzRkYR40ejD95rKJw1RfNI3raZTbE
+m8ytH7rUUaXCO3Xq3sSUvWSTU2xlzd8DNsWk0MfTM+Z0Ev1hMpUHz+XjKTBUIjgdEN6TdQc1cSWg
+vmGgbdKd4w77gVG5rhvbuam/jKzY0lb17kbkFplnoLTG+kkwdF6Voh7XmnB/4c5/Hi2MgsgzAVPV
+jTAWZpMJVRYjS7ZqtXLnzt673gGcEq3H8yfVbW5jW9BT5Unnxr8AZQPesLOctBfhlUR4icGYRVeu
+1aJ9TzOHFwMHSiyHN/zPV1iBj8rg3qm9PM+62q9arg/bFqyiXkX7OTJ/YblkXN2AoERJu5v5WJUw
+PHEu3GAyovGoQsufFgexopjuOm6IrzdjSIVVduTV20v8FwFDmWtTY7ia4iiDvqCcTNUqAYolP/Fj
+bNs5f4AmC6RUie5bOiyFw/PQuHySWdDYzqnzKG2bzcPQ4hxqDnYs1xnws12FNYEbxcG23jojewqL
+Nkhks0U+WuGiXYuKRUitqFWMw23d2H5d/Yjb8lx4zkvfaPsx93yZm8ehlbuhr5FKS1/DQ8/k0d6r
+yYj9K5WrzLmJcPChNe6m5Cwq+TKh1g9DvoN4Cd9Xe8WueNEHGodmL1o53jaRIXjINtzNSryYzptH
+O5TvTcYdIjbH7GA3L67X+FaOugoAufT03ZB3d5pzN6Jd4xBKQNU198psnKaRlase7ZWX8sorlnO1
+xvhXPR2j3gkqR73E41fRz2cibvhN8LqrxhcuU0ZyXerT0Xnk/Ab+LPmi/+hnHJkXw5Znw252Sykm
+FrpA7eJoZTXeq5sCcuy+JG5T6l6vM3fM1mrOlhh5CatXXpFnMVkHJ//Ru9Dt+vJHREaQ9p+7Tu0u
+Dm5XA2DKVg/jE/mXF3CzuFgqJKXx3IG/neriIqziRxEpuT8p5ofnCMqldVqHphO3zIJuY2Odetqu
+MFpyA917N3evYECDHNcGET2U9PKD/pJjrAAADFflqBOsqKyVDX63hRxU5LQzpwx/kpteHAwWBSpl
+KI6tOwJNlGSasqOJr9gOxmlO3f2g5xfVS371bo9nKkqYEbB/VqjoIyaXXEBDVk/QMZk8euIuMrN7
+qqtBY9oPXYEGhEMtKeRbfCrzO719SsEDGELZ1G2KT6HdYRquVkZPjjlxUJ1mPShj/lrplXRV2Tnb
+fBx2DCV/Auc4xglDSMEH2Oh3ZkHZnD3me48BU9TmR3MkRunYz83YfHiiCwNpmgXQ2xismYKVKpPz
+elyGBBQM3A/o9Gs7bkG7qSoHm4oxBe14a5C+h4zaJ4ZgYEBM61rH9hsDlU897F5oOtgCRCpWjtk8
+N1m9q4b0OXVo8rKoodT7bTRymJkfe4bmHQsvYOy1YRUPogZPE7bbSbMCp6cuKTr1gwUiPB7vUD6p
+YaBldvjK42INNkEKKIikY0OZXFImssnk27mzHh/GOd5ULbyv8iIYh/sKOXrGhjH7R4L3vHvo2Ir8
+iZtqOmxn7yly9JdoUB+STmU9cLcJt9Ek26KD77rEvM5EGuumuxvV4r7XroXBAwScdE5+KGpMM5GW
+UYiNOSD9GAa5swf9joLmCITneBi9FkCcsL+88jnm3Zyq6ECABZRmRaUjFwlcBwkVlNoUrXL30Ybd
+4ZryPYFKqKpe51uhitzA+aFTnJdMMlCcxLOYI2jQFL7qR4A0QEhZskyOpCMV0qKwb1rx2FtBVFGX
+vu7aTMB4dmyA2UXxFGGEW5e0iB88ks+dw45MNm0+OLCVTrVrQwu1KCouoQfsmYA3nCEbT74ycKye
+hZwpGkysDnKanL5KiXLhpVjXm8zof/b0MwYwQ9StZVGitprtECNHh8DiWmOAIVf9tMs8vneNwj6q
+IrJoBs3sYkeLYfZckSgNcq3wHpCX+SQVGf8oOA3vcjLACJ942wMJa/EAgUfv1lhz4oDBGy9snuy1
+RZzCnaj+4o90PwmizB8M3NRdYU0SMGSq3Sq7MTaaE8mLG4PQUcu0OKqK09y473E+5mA2rvqmbO9F
+kRmPLl/xWvEEe0saD3tVa+tj1ZtMsBWGX04TscfNyuiHk+buI3wmDLeAbqB/1eJUVmkUsNcweGas
+vlcgjJ700gkPpKzag4dbCCS0wtVrbDw+d1SmkyQ+vi716VS5OszyaFLTG7Ew51ltVBTzqmRuhMy0
+iWhSv5jjXL1RJOGd0Y7EExcd3h+XeuwPN7W7VyU3rAHrZpxezF5aj5aXxg+eoU737eDVZ21AbO/N
+dLw0lRcfJ/O5x83KCK/ZerMcH0KGfk+KaU79qkwm/c3CW7gZKfoCXjfm903vdJCKZ+duYsP8EVuJ
+syuqziWyNtKG28zltcsHebUAhV/yTkv3RQK5H1v6ksxbKmcrt9vgmmVkyrl+ZRs1foR+xlEQ6tq6
+MtOCaVVUb4vlgo23LYHMHmHEzfKBYAgjkReD8dp6ZHn6kVq5fq7HzsBM4mhH/Jh4lTAWE5hLrhVV
+jnG3ThOcVL3MpwtDZ3bSupj6W8uTOVHN2U7Ftqq00u/E/MlMF+F1aDvoFmH/GCr2k1vOF1tkb3ay
+TNqKfQzJwpy7nGUfc7k9HkWSBsxml3o1a41ZIfJNxcO+yP6rOq/04e37ic5q/Fg/bepUDQqmTUgK
+eIfWZIc3EtIMbN+BjcG0RvR7ykjPbmSq2zJsXka9eqSHcp+o7jk3O9/U5nWcGnzF3bbPyF41z5om
+vaBW2leio/FqihJOlIX9n+ydyXLcSNalX+W33kPmcAAOYNG9iDkYQTI4k9rASA1wzPP49P1BqbRU
+5l9VXbnrtq5VLpiURIYP1+895zuPvd0/BYZ5W05ozOg4riKdnKeRZHhvwoUY9sfSrOyNY8j0kOWL
+e3qWt5OHXkTa6bqI861faZraQwMhgKK8iaJVJ+1dX7e7vDHkptw23QsiuhWJkCdfe4h8vV2Y5t/L
+vHn6180O64d5649mB0Zyh4kO6C0FaQu/lf+XpgtzMiomRw0Hlb7wzI9O89iNt+PABBgr43QlVF7d
+jEU433E+6fshUs6jCb71tg4qNawalfevHlLUD/fHVkmWXUMasX/jLDtJL3sqWXYXU4TqZP7Yccve
+K+YweRisnAZKwdbslj3qLbsVTM18lS47OPixmcfQasiBSYyrMGCvT8uu95b9D3U83GbZXF1nfuPv
+4cUigSK3yTvGQTJtcrOGfU8jcsecMESSzylDIsJwDANOHtEyqKzswXp0yQu+q8yG+jzUun0QcdE8
+iKLJTnBGEFnPNWn1M68xfznpZIAhDPKT4NfFOegsJ6IRFuY3uZyS9dRGR7LsVn5Z6S1DLQ5TEv0K
+7s4QOeOPw5ZIm+EwJZ7+nJfUGaWY/Hs7TvyttmTyzASHBwN9XxooelCnahr0ne0X5pfAN8ZtBpzI
+KmMu+R+XQNEl5n5YbgbSsfuvwXJbFMu9EUf+9F0sd0m93Cr0c4pnc7lpADlw6fBpFseQdIItI5Ts
+i7fcTs1yT2Ez1MdxLM7Fcofp5TZDPP8UBQh1Vt7czF9pEp6QPPg1eiuzeR7qTLx6U9fCPYlS+TI5
+Lk2trJPT20CsBrvGYlhdhjSgEtbmtlN9Ad6cAk5CK1ohnL4hUjC/gd4RQWqQ+qakQY0AqtqVPNoO
+ytA+ivjaDd7tzCE4BfvbzOMGmekOP4OLFqX98TdaNe98N0Otxz1tuDmLKdd63RRFeinyWBGcLuUp
+izkk9mrweK8yc6ZSwJibDytYp8mHJcq73kpx9pVCOtVOI7cua14L645xDQ2vDEhUjAJtJZxy3CIo
+ute8Ng+DYb/VOa2cTvS8JGbqypnlO+FM4LIZt74RPMZx9Zi2OtsaQ1xv0HpkqOxywEM82L/xiHkx
+POFcW53vb5vSfkLdSgVkSGsrEMpwwiIQQe6V3nuDMs5eNCZbLnoSc0QSPbqChFXVNvGVVuoxMuNH
+pIz6FFd+cshdyuwuE1ehZZKt0+uR2c3YU/S0UNxhrn+O8P8cPDP6Pk1GglR01lTFSbeV5nSuqT9W
+Q8b/PrAwkG/1r05nFlc5luxdrkYbB3kh99WU1huz97NVM9t7TxdAMfPBWGEtcHY0U2mriPqdGdYd
+daFcCTUy+zCHp7IYn6Gj5A+DUfIc81K9t7uu9yBGJyCt3FJv0gSSDzlljIoM09xbsSp3HipRlHV9
+s+sle63w6GsG6MlXRji5q3BsPg957x4nM2HiMeefHZKnV5mDtSF1cYNnvoUrgDEEyypqVlWWjeva
+XMTxJfYCfCig5Mg+WbexgzQk9DNKi1LwnL84AFcJ2qJimoiUXGkvKAhAb/mEJ16tkK/VuvH7R77P
+OYaWk3LtAq97ajyVn9BfB0dZ+oRpcu1eF4H71QRU9JhI0iu9kQPFyNAT9+n32FKPGADBH5gRbhIj
+REZdYMwmJRbApK+/gpciQZTskFVSNdmGqgB7yhR9TJN8HdI35P/XwOpYEYQdTLl7mc1CbqYk/66a
++X4yC0Up3AElT1uw74bnSsINovCmqWW/IQ3e4iWy5M3mHpcV/lU0kFI8QU5teL2aX8ZCWFunip9c
+KLPM/33iLr2Bl3GJ6CI09Tl0rdPkDqhbLfbXWHNJECMYbWhI3xDwJ8nPc4vqELUEGGhJcGY4hPNr
+7C2PzNCadvMI33k1NnDB1nHbz5+DKMnw/sDOccncXTPQlbcu6aHvsZ6sY2gocdKDHx/T1m5ug8Jt
+Lz3M7Qsa6/Ej4Pw5mbJyD+NSUfVLbYU/rLuxlnpr+FF5LTWYNOB/ovEzNsGP6owT137ylpJtSf7d
+d/zGf1y8f2tC9Y9nT7/aK//XvzfE2n8rbt6zb83/G2MsemKLxuefj7Fu3sP3JWzzL3Osn9/3c47l
+fJJIdiCdCFcS0KaYI/4cZVmfLEuqhRgrfAfJzS+jLPUJ1SUJZP7C0WPvYU35fZTlfDJh3gBSlZZy
++CPdvzPKkkvW55/HnCRVWZ6CKEy4GoZP/hG/jjlnr6E1h3roOEUW5jf3PXQjfxVFdXaj7Sk4RymV
+MGmFT0WZMKwhEmJf0bF/H23HvY49wjdHXsqxA0wQGdmFybAmyMF7CuFVEXDow9TqFu7aBNx/SOz+
+rmeGjYbNwoJYdulDo4FIxX5d0we36f00a9mo66lBKO056FBg1kOFDe46MGAKW86WVFpSTOLgadSB
+t0Opmq7czDnTvlHvbmSmFMXcTQVmxsTz5+s0m7N1O7Q0NjDPYx6hI294w25oevLdY283U23y6O4y
+a1Nl+EFG091A9zfQqw13lbYPfIJfB+muhjI7Y2vcTo28x29/KuoyXOPqWXeF/O6Y0Xhl6GDpkyXe
+vJe6foj43d4WUVYQb2OUe0bZT0Q3r5QxnDuHX6bfltY5nviRIyu5sXOA1QbKfnoB15bT0f8TRbaP
+xvZLKaf5JnhufAvhX0VwEpmeV7apU7Q/LT6CaYNzYpti46oyu1qbXv69teHK+AqABLOm0VOEGMSP
+Fc98XWZyU7s0rOHxrwSlxcaY44MxdXeGdHoaQ8341EWzc7TcbFvSDt5ESYEClUnE6FYh77xQPwA+
+uNdW/xE4y03W2OluHCcP0FRm3zqIB8lKn/G1BBgbJ3p5e6/FmY713Dky85oeray4t5LKZpRn8aSJ
+Mz09iDSYOYsb8o1hSoS3o7rG4/NEbgeI7Vjll6E2jDWA4OtQ2LealiKGoZcwnRCHlAg/utHex0N9
+DuvmaJCmI+bwZQhJo8AlMjlTxEfV3NR1+z3JH9CMkaeMJezguGW6nshUw6u2tcd+LbC9k1RtGWSs
+z8TMyOpm6sU5cRDikD248jwP8sW0DNFoCj+jrxoJHgPZMqrl746PlTBWdVqKJ0JborU39Q7uSFxG
+OwaOdBK9wdxX2MRyx3y3kaCfZtP/jrzl2krmlS0yWjDVxWo97rV4g1Phvp61+dajYReQoaOt3fne
+g69gnwXEHK3kxJPTAkNxiwLfuaB+x4/q403MwZx8Ke2qO5E0FLXrhvj0S1pZ5ZUVNNMptmvv3cEA
+BwQiD08G0YtHXiLdkXzN9CW2SH7AXtVEZy21OOo4rA8THY/HxkVpx1JtGBSJ6Q1lEojmaiguWln9
+0XXz9HMyBS7icygkqUiSNVIkddKq8E8lnoGdqQbi2E1z6aLM4zUP/OxxbqPxkeSV7ioWZfaU1bgI
+qh4J5Kou/fq9DXp3U5m6J3XEd66J6CjPSe8Nd/T/rRvHnLurliiSNzNOu60bYtUia4YnSaqSY619
+53auC/3Nskfa3A2Bo18BQ2Rc9uisrtFnRddx6Q9nJ0jbUxp4Jv2HvhcXzxvF/WD11Q2BNeY5Swr9
+RNKZz9QNZS1LxT1bxiDOGY3dBl0MxAqyKty9mcr0xucHpDMMdiBOtcgPv9wy/2Dyb4nlVP71MezB
+JaW9zi3goWqAq/TnUztJmEtazYyqOwzTm9Kui/4YN31zUy2Ghy4AFl6aw7CaJKYuc0jmzYA7B6EY
+ymCa1U+qb4xdak3oddx4KSkbsyALIhI7HlsNc6EoxAHWwcYFaetcVC7iUyuyGzdQYJoqf76UysxX
+BDOm11OIbJSV9OSghEee7zsHeL7ZGvqEs9KT81jXdCW6bshuVRdCrBumLngsh0EaBPBOVE+NO1f5
+Ruf8wSs5EFK5Vthn4JmAPVo3iCnGvcjI7dr2yNff8HJV0abqw2LrzGb+RDCK9wbf+KpJW6LJJIEX
+rkEqTJuvJ8bkZT7hr2/dfBOJFBRGRjqwFTJwyUx0Sp11X47tWZf1Q0DgIEQe0a760cGvHY3Y04OI
+vEHmYxYRJmt3iIls10yWZ7s/BXVxdiO2fxRNTFJw3w15BDC1q6dt5mTk3Q8q/KJ7Z8A1Ntg7A3sF
+wHDl3BRItjhjzHTn6iS+L2cVbsouzG66eXAXpz9LaXZZVbNQ4gwfgD5bFzdnaMH+decI/aRFKM9h
+pKqbBNHLfWEqcdEJXL41ZMn2xGc9nvFbRNeDQOCNaJr17sEH/OqGaFZWlmvpb/Ck8vVYB+OuXnbK
+tOwZb9k9ctlH3bKj0sbDhBSM1k2CE+eurKLqbIuc+1k3PQJrrkqYvQ0srowBPtm5uH+WHewve1ks
+uzpwk/wRGsl4Db4iPDKoG3bVcg6AmPFP00zroLQLXo5VvqyDyntg6pl+Zp7dH+flXJmXE8Zezhpn
+OXXa5fyZl5MoWs4k3yjFMeFVeM5DxZE1git6QanRHeMkWwByQ3hKW0a1fau89ziV06kMjJJmUeJe
+dEZS7QLy7U4UIOoLicZ6P4KxYSwWqQv/t3HbVaFam7TQt1EEFhAxx7TMO4OaULxm9qlQEt/kx/b8
+BPuIdNx4QPsJR3fD5FVlazO06glEns76m9yNvbVwKgfajOs380b69IaZ5/j4tfO5CcsXoFQ1cgcn
+KVtQZ1bSHoqw7sOzTEVIamCDMWDVtV7fMVfKSXerqwjxhQgNFAWe1lO48aexot00OzP3NfpJgbmW
+vBW2QVyQRtJat5bRy2svHJ270UAylPpWs60h+Nw3c+0kEB6CTOyJhEzTrVGbaDGDuPCZG5fBx4L5
+Gjaej4p4VbuzNrZdllIB9fhh0rXLsfk6p8SprCF2mJwtUxz7LDGzMkG9t/I+QSDIbKe6c4MJiEYc
+MyRsphJLc35oHE8gMG2f2v6smJxvw0Bcu55fXtvkiq0kgCuMGBZmphrRAtIhhKsBCmpiO8dNVpTD
+CuHXsCLt8zO8oGE3xcMXM7eqtVdb0BUmeQmwFt2QwSnXGMQ+IvcDdYF/NUlCEpU7yQ0hgsPZKgiH
+iV2xd3VBQ8u8jxlKbMbUQ8gAkFVnrlqHGbLxrrLdU6tGdUCeDIo5sq4ITr3Hw8idF5nW2eD+34q5
+/JI2hbF8Rox7ppKEQz1cuM6fZrOMvjs4BI9NR+9rSIv5hJlhWI04z59NT0yb2Kym7zzxWINkD5UW
+0pJWxJDwIjf8zzvv30Xy8Iay6Sb/83fe5luqo//+yFu+6bdHnuvylEPT7nAdQ5Djv78/8lz1yTPt
+BYMD89dC7P7LI8/75MHE/YHiMRGZSkSOvz/yvE/Ls4/cV6SnJn/i3+Lw+H+RstrCQzOJbI1z3l5e
+lX9pnaMyKjP+edU+qvU8cS9V7WPXh8Or7tv+1hqHx86ojXvebthyNXwNBkIMSZzShBfsYIx7y5K6
+f6+rIjoGpBptyQ5z1jPwOFAdLQVnGnGYKCgq/PHU8FgeL4zd02+xUh9D16gN02Oih2IychQstgv1
+VvAIyKxA9WU2L9ils/fCIyATTx46kSBJLlPh3BPr159SE1DiaKnhmaaa2Ip4DmiAMxP1k7Z4IO7y
+dTSQ98OrWSZF1bhVBm5OkY/1apSS6U5Dw6ebqgeRWRrfIDWKVbY+175BjBsW4wcbv/W2CeOMoOGG
+yX/dQl8OkmpPDu/wItFJHBoZpN/9oMzPCKf1B81o9OUTDp8u95rHuJPZPg4C1SOLt9AR9eiTeNWQ
+0rXCAmt+TugArcHld1tBJtF5MMcBS9fc0QpucP99xgASlfTMHPy2ld2Lt4KIB5gboMhWXmiSDFP3
+zrXT9j+854n3TBOqwfhtoqSwPFz8q9kvUFf9p/Xzb1K6liOBnfovjoT37D3/L3o//4WJ9B8cDXzz
+z6NBfvJNiRodiKXCq7bMtX7r/7jiE9sfwTJuMdcmI43WTF4gvfuf/0OKT3wFnTOsMFjKxP39cTSI
+TxZKX7he6G5AbkAt+Z1X9vPlAOqM1lz4rfgHLwmf7tMvDwn+TR5aaglFa5kieGiZ//yQKGsDln9u
+2iinou+dq27c2tmXyn+MgxKBUwyoaaKF0zMaYDREzL16o/jad/5nPXQpDsrwFOj5OenUnjCLnUne
+dXwmveGqHdDPuggeg/6a0LvnCrFa0oa7cnb28VwfRLkudLC105Jh21p13k4NfC9BRGlcH7AUHhNl
+3anauWEuuB8q+84OTFDoK0myFQOb3VT6xCFUD55RPsyowgKFUV8X6wTKStp+zOnDFEIMymBLjGrn
+2sO1W3qYMrOzWdo3uT0+lxa47Da/gETbltO0TzOFIKMFDxg8zuQTbrzAfmwU47Ihvs0CGx+LXmYH
+Tn2YA9oBcZjetaF7sFDmICTsP7e1TxRg/Rrb/MroUhB5rI6MZLZYjL7gLaL2yc424cK/rLx/8CH+
+VY/+24e4uKrwHIId95Ye3y9WhQmUbaMR+ZK0hiA1Vz9w9uFQ3TrTdOvW8Pq1TtbJ7G4NUiNR0vwf
+rI9/Bdwyt+chQo4B7U2uUmu5/n79B/Bu87CRR8GWDFE8JNHZ6+rdKKiI+8nBHqflrR0kat8F8wWl
+53OfR9aZa9Q4Zoqelrv6NuE1382qVoT9WtHONYNsGxTzeUzrA+QLSiovNI6iZUBC/BC99TTb7PF9
+YsVhJsLbJt0OpOuQ7atWRRE4qGqsUzXSiYK+Q7HWyC8TZujVMM53nYj2c8N7nb33YlXyFLjjtRd3
+pxxOwlVRleHp7x+k/16D/J/+X/93Gj2WY5LWwz8/JteaIzIK3+u/Ugx/fufPM5IiiXQtHwgTxYmt
+Fl7+zzNSfQJeCPxAYcX5zQfy84i0OCJ9ZADciTSwAc3/0SLnS8qj3vIU8G5evoDa/3Ik/qsj0uQv
+/9MRKXhk+MJljbPIbdIc/7y4O63cTGTxxDi2rp4y4O+vlQvKz0OPuCBF6vENXNVHkJj1N94a+Wcq
+Hm77XutuazdDgYKtqLcub/fX2uyLqz4rw43pRelXJw27l7+/1P6/HNdwfyFLEbAs/9Vq1O9tGzX/
+bT3+8c2/LUgPKxGWcmIdPYtPn9r89wXpiU94knzmObTGBYU+X/n90rY/mYKbnsVCGA1W8D+4mqb7
+ybVZRZ6yIatgXbL+zopknf9lSSq4BSxEX3rSX14Jy5L95cCHQU0ketyPXGuFljsMSTXIwlha68kH
+2UiBC95gCww8xwwZBsw9XHfRqtqjHI3FhEoMBKOncz780CxCY1t1AVxAjEbpQxINxqNjBvoYjsUS
+VJvrU525ItzVDrp10Cv+1rWoDpq80V976k+ayFyXGoQ/0VXBCOIKUD/exoDAj1No5jaoF6k8avRg
+ulNjkUFUnB/CzpqgSRyAJ3feSvb4qLuork/a8+lLUavI3VR0vKaDMYTP56YTdX0uB5Ldi6lZItRm
+8RA4UfpqjWP4UEjsv0pIYp29KbyG5ATXZjL6+SMsfAcVmO1iuujq9wEgHlloydGJJbCPmvw5xE4m
+1EdomvllbJr0tpyTeJsT+rvK5XgK8Z1szUyTeGfVEs9vGmJsARAMcNT8WIhOwOGKDn1a60XJGSNL
+8jEoiFowRlP/a1gY4ZNUsbUoE7CMQksypLkJZZ9vWkdABLESeyWsaFwRtSevYj4ANP8wpFqs0icA
+o89TRLt/48oRGN3c5OM6jXNRrOexysEGzIm15L4jZldD/B7ldvZNyED4e3wFpQF1poeBLPwJjb3P
+ZVk6jYH5OZsB4Pt9G45rlYeA+AwLCKdEe8pYfvDRrOblm26Cpl1nMPIZ1I9RUdE7JNQZ1pt+zdIM
+wwZ5PvpgNfw95mTlPQzlwfPXSdhWgMOcGh1eQRYsDgpiAA40w7uvZZ0PemfJYkRWa/h7t3Np0cpQ
+TShreBOtXMsDL4jPunlqbUteMPna50B1zaPOdfEeEkgTIxvIK/9E/WVB2PTG8kuFzvOt8XVhbtAj
+0rP147r8bHZAQVezuUQRx3FeP5CT6194K4OunsvBP8dJ0VwyXQET8HKN18on+f0OKcT43NhgZVe0
+w4xvEOcdZ8NwoH7FupZ9KIjJe8izfL2Q/vDY5LmFiqbN6AvWLc+9AyNDTfKoofMTGgCkTakc9kaL
+pCTUw/Dsq6G8d9piPlp0qdi3SYWxQxs4s0tFb0swBd4gjx2rdSBk8hGyuZZvDSiq7DpNq4OImrje
+2r3yjr1DvzIl5YHeoZ2O4iWsJvGKu5yRrqiKeekp8wF6OLOLvTV5zsqzKqJBG1EP5oqua4gJUIPM
+C9S3IJXz2xCOWxORNX1j60vR+6TBiySuPxx3hEiJf2l8G/s4xw6kRxJ2muERW3B51p4VHBISka9y
+Qt9z7I8tX3ajdFvBtHuZG9fWQFqAq0jy94Aitaj4xYychektcD1YZQA6LNWATAsOgMaRsE3ztmBc
+R9mKKh8TPiKHioiGWbrBsy/jbJ23DEqAnPtqbZgUeuBH67JaD2FWbfSck+xnz5Ew19kwZsVWBomd
+rSUjhG9xV+qn2dX6JBIzCbc0R/FGGbYcXg02Ckl+TKk7xCtV95ZZsa7ZIi1P+iSa2dpz5lQX8MbZ
+tMN8UxDmMJdAj1AIrVqKCaSSnepuqiqZMD/nRXFss6Z5bQSIFWYQXxOC34Ey1JzTfZoyIfMTDbCq
+MwBvzT5u9lbGIPvlnK98PfYvdhDWZyvQ+s1kZJMyP8zmbScNOFT+SOMRwG0monVVze4XcG3pIeTN
+IarIBi2bU3VwldDcDcECfbWNkEapUSN35Zc3DNdR14U0wp1wcjaNCfRwbRBKodf2EAN55OdU7qHz
+UwSeTRya1iYRfvNtspuiXQ+ju4LCwy1j99mhzurqKlBRDuqImojkJqjxm2xIk3YvYTZrjAl4oexI
+tciy55xRE87OMAJBoJwKNgmEWX56YTcblmb1nTaJxxwBWZDZgPZB2TdyOPlp/pAbbDcw8RGOiqGq
+3iIXjCO9YM+7a8taPk9uAWQJ1a48C/S6T0CXqldCWLwrL05Di1dBCz/TK0PrtiQP4VbReX+qJqYV
+HBuK5ePiXbB4ZJpoepqov57cFrMZFNXwGe6zwAqJyOi7qEhRPfEv1NZG9QiREVtN3lsL+pLc31Q2
+1+xbJzsEtnSWjF9HPXI21ec+8+ObISjkzvIYooyBRJ88GjWCsdSIDL1O59TcGTTcEAgE7ssUi2GV
+FmN2m8S+WKeywqA1FNGFx2C+1rNp8q5SBZMKXT13oUieSt8qNyaGs1K41mOLtvSSEKO26ZLYOlRO
+Jh6haxnfZEw+z0qGstuAKbOOsYjRUkIzCx4zEboXt4gei0IYl6CYyNJGplUR3h0nFyOWpADYpAys
+hyl30HD7qI+3kcgJTGz5ten15Mb4SYKUQSorIbXKd2x3AcPZLmRe5ibM9uZiwErnu0e4DVDO0mH+
+kmo0WMZcEc+ed4W+LVTanLMSTxIK6+gzJqw3Cuh5P3b+uA8ipjGuyqL3oJvsTeENyb2HP2tvVFh7
+kL/nuwoPmsJ2JY3fkianTuOwlNBH62vXybLPqe7RKnimHL2tSBOmclBhFjJpyeHSWJ597HTUPlbz
+UBxyo9bXPirBbdtMLnsuRJ6SFEhYRGNbJKyb3RqlYP/ocLXc4ay0QsKOsERj+fHUthBD8z7Dmbv2
+GiuIt5wI+tgXgb4JRS8fhN2VFxNLE6CQkKGfCHuYmY4mNDa1FwVtY8l97I3eDTCesD3lzWIL8YVO
+r1VMpgKIyQB7YpLc4wX3v9dVarncypQS9FpK/LdmtcwXzKk2yjXW9Dy9RCO5aSuHYT73d8aAo27a
+CHcqmLAXORNFgAqwvCQlaJSVzXwOSHljWu+qp2jGVhXqZ2U3ut4NdAAMYodqbOdhPG8a0uuCvaVd
+OpQgCKfh6BNxWBzaKVYvPVlzT0i4+3vCjGmzJpl5O0gtobc6TYvuzuB4IJUk3Kssbd/AhhV3NToS
+fyPDjsC3SlQnpRP26ox94OxOFhJQJlPQupnT3lHADpCB/F6/arNFRZAOfUssXaKtRxGP1Qva2vLi
+N3AzEG3MN16nsFxxbdnjxqlAOa/qOoL3O2Xu18K2sa4TnjbdGH2QX/llLvb17KMUqYfW2LqNq77M
+s9eaGw/S+XuL0nZaE+xobO2p7D9iCc5kx4it2w1AQw4xI967PsG6+NtPyRApXyPT6OF0uY9WjBFq
+ICLjhc2JULeK8vLiDdnCasqenCS9x/IEWiUNm7OfaZs9S/A5QS89A+/MAcACC6jd5Mg53RX9aP+l
+NJFdrmgkh7RQbCIgVgtd4TlWQXX2yZW594tC3aMYLq95vKTnJpzSV8MLiP1T4PG/4DzV+zkxSFEZ
+iXy7QUrU06FPaVp70SSmq2K0+unAELRPrnQuzRRxZTgd8Ew5X4I0RMGaCyRaOZpFcqZK0LcrWXv+
+TV6F88Hk5vpmmI36FoZB3W37OGFs2c000TaKYHOCRXsrkntZ+NETtE25gxMfv86GMd8LP0P3DETL
+527T/bMJHuaeMV56A79uvsyR1X6zfly+dRAvuVMzmOQhDO4nPTUfY+E11y4ExMcahKpZhUCQmNGq
+dw2uEkCr7WmkZgEZQWup8Hz2s7RuQecOG2K/kIvraIK31KSLo0XkdpLg844XSglKV3r6BfDxtJPO
+qwjNCgVc1TY4taMaA7QQ5RfbqLCFFjX6WoJc7qJsqF6wEyCZrRgIp8AlnrFgMyIdpzE8+n3XtDtz
+gIC0zuCbYSayZ+OY5JU4SDcCjAOr1Vw502LFWbwbiFnb7hxpKyv3ifJaUpxNSA08CcC41YM8lKOo
+EsKVsUCajqYOnfqen6nLy3JjlVgV1nHgzEQeuWiic5J7rrIsDgjtQcOWbmRgFhdguvOhQ0JCdYMh
+dO+IJj54Tg40GgW0vEd+bB8GU+UfXjFnn5dXdsvfQEjAprMt40F0dXfBV1m/EHs5HRPTyihVufDX
+jhXM6xLxCF/pBSWGIYtTI6byXPhhqlfMgItgXaRF/J4Vaa0Pso3CW2zj/AhJUsKmTsAS3nV+9r1u
+6aWzXXBm1ml8MZYYihV692Jdz45zCvVogrGcDIEWGoToKON5a3uztNcwKVWCNL2nIMHmCDYicjy5
+UbNtTwjeVHloWiBUvZNHBk9Tjb0nlVHmHOq24aOhjBeZD2naGWiFcyO9Rwmj4nUeBU2wzKUIiMmB
+sNuLSCjomfgThDMPbUzCbqP0wkCFqLsSidqSaaZPjWQIVuOQ+pp5pkJ6PGbtUkZm5dbtdO2tUXBE
+Rz+hLhvDpLgOa/yY6MwDH8uIK54yZ3lTtJ6TEvHJLb4mE6y+tTvG1JlqgwMa0PzQg6Q95t2kK6j8
+2fjM3ECKPWyy4mgQY0F724uq9azm9Dr37UoeLXAL4YvbjbgqeneA8vOfZta/NYD62Y+irfPPm1lP
+Lb7u92RpsP5p/vTH9/7sZZmfhC09j/YYmYZLy+r3XhZTa8cltIUB1J8TYizzk830CUWwbZmWr2z+
+IX9MpvnCkvzowrWizer8nU6Wcv/ayTLJWISh49KdoEFGx+3PnSwdTGXtWEruw9jJAMenagDp4BRI
+wwLXeW+mQN6ZE8V0VSZiDUGP3odIJkXhbHMoDo47nOHCROukp0IGNVGtdfnUzfkm74llcQl33WjF
+NMmlBP7QUdceRRxZDHrakIh2n2R2RMGeg0Nzyrxk7bmRuOeNjW2kreZbyWyHcA2IljHk92LFnEqv
+8FeOyJCHA+y5+ltIk2XdUs0G8FcjNM++6d2ItovOIfOF7SRjylm3q3aZZP5st1m0bdrYO8VAmNe+
+nut1BbVgj6XP/xpjpwAdzON9R1azvS+mTjy4vHJuk1JV+0UNvsmskfwoux3mK9wKcsNbrNnJ2c2h
+xEDTj1Yg195TQmEBCYRpvM+8iio87KdkWGu7h1zqdN7dkMYQ1KsSvrBnlx+CbL0bOxFne1afW19c
+z0UUc46mBwZhZCsCyXWmO22QAOPY3cXFh0WlUW9G2wWvXzNPUSG5JRj9211hqDSlKZCVOInHod3o
+JFCPLR1TFExpH4gNqRCk28Un0jGItPcyexPwgqD/srhCdTYxZGv9GmJE3sninZpuwm1XB5/9eHRA
+73rlZW5MDvGZDITHFOb3VR1PDc4JQ1yPWqcYY1oLY7fXkvotl1afykb30DfYK2i59089Iyx4oKGT
+AGefMYJZhnlmDmAcC1kZXxqrJS4scaS3YqU1qy4f3JchVfKUAwyHYKtROAE/mcDpZtHXiMHAVrAq
+DzSfkAgXjs73onDyz70j1a2LFWyV4lX5qMvirfUm9833Z3dPaZzcZ9RuF54S6hkwWwoVWIszOkj3
+jAYvRPSq9Abm3zkooCT2Ysx3dWUZB18Q4h2EtrzjguYJAL68wF6bsKKdBLu9GXQ3NLOS63S06ZSm
+CWAW8D3meUIKC6HcjN3n1qXixgeE/qiooukBQPd4zIbGvFDEdTY8/7J/txxv+N/kndly21gWZX8l
+ox76qVEBXMzRURXRnEVqoObhBUFbEubpYsbX9wJtZVpOp6sqldFdEa032zJIgsDFPefsvfaWyZ2B
+LKyKkNaP9VOXet2pR+2+IfpFv6lURwkYwOUdyrJIPiVsLeU8jsaqnJOqaZbnrhon/czrUkUuoAiR
+ph7HCmEkHakYXkfgNEHSPWpPhZch6Knbt5aV3hk5YOdZpfBVlHFvByg0mEaRX6PnEJtBHepVi1o6
+Ekwd8cZesFwggotDEZ5HAYWLAyF/39VjfdparrrnSU9rTuCivIZNp22NuK4oaUot/6zCoLtQ6wHW
+ktAigb+1BPbR2yo+A81WdilaEKpcrcs1XjSLLsSoZ2deO8b7SnaQH7w+W9aJBsbEMfqNbXfAjmul
+Ky6dovMuHBu9cpDST2kLGECzCrDZysHNKWeulYSnIvJwk+eDdaqhTtmpKATWqi7q00wturOALuuT
+WVAZs1+bgAtiuC2QwQKhZ/N/o8kU8p8Y87XX4bmMh1JemxmNqNCguxySR7vGFMG9NXRpfO75SXdJ
+LkR/yVi2w2GBHGFewOimsrcIhak3SqnKjZ23AYp3TyUlEiBjbSvlXrPcdB9icL4rgXBCElLzl06n
+EJ+NfS423ugo1/bQiIu2Euad5pWKOdfQr+wAR5J0V9vRjkRjLulM118BHTpkcXXFnZmr2kKBpHoX
+BmBHYz1u6hlg9XGpawPcERR4a0g8wUqtgg7Wgl/hhpUUyAqK32vDTr1VEDg1yTlON5zkcaaf+mk4
+rofUMteOWzsIG+S48LUIxhBpJg9U8AQ4V6K5Kl2Mt/zRm2Si9kPYaek69WWwQo1Ynguras4xl0yY
+mxqMkCbSJ8we7pPrpOm+sdpwzSyFWmxkcBBHVr1MW6nTaFBsccJOjWBGHHvEoidxsI3Zc25pwZSL
+rnHkiTFq6b4o+xwAWfgZKIVDB77aFoFkjeepBn7rqdDHskdual/5JbTltB9OIMT6N2WUtC9ZpYI4
+knq/ruVEg7IbUWpLaxipFFX0WwEybGT2yqBb/ryWenFa2Eo9Hw0o27Ih5iVxJHekiuzSJKtylmIb
+M/QHCRPBpCV/puXtJvUdBA+hf0ZbSm5YqpfaQDGfRmm5Qd9LB0Qi3IACnRVLbBU49DVSs5NtjIpM
+pQ2G4yYgXR7wQ9AAcauj5CRooumzaH62lD2K5EDKJ8ZprMwNidpzp9MhwY2q2V3LahyoE8S4FGVn
+rjI3ba90BefQEh2ku+m1Ao01fiZ2870766Ire6RBkaRNtacRU3wqYPYgASBDhWFQuu0LTg86cJOm
+Fhy+sS+Ms6AiMmagS0hvMRt2WifWtT6OG3B0I8oCkTxQnT6za+ew3iHo7WrTpehZnEzZ4HenReLP
+SzMHca8ZOag4Rb+CFoUvJ8rVa8AJkFKkAmAhsCHvzqBfgPY0A9VYMFnQVimRArg3VOW196S11QRD
+Hu6P8tR2imajk8rEY6bJn9MazKAjCntbi2Jkzk7mL0F2+2naPDmaxqXfpt41X0DKORVOChEZZ4cj
+yL4xqjI413y0yPyiTt+919aFOuZ7kBnqKW7+9KFrVZjzkBaIR1ZaOEUdefAbYdW07FwkS6+pousk
+JSgu7YvYQPWrS2sW+k4XLrEZWcYa1GtwkhlgXKHhQXQNegOcSd83Kk3kzIL/4mb5FfuLMDtLfKIj
+F0qa4AdgGZgHJ2qljc5ClGXUXbh9L7edK5PLid3+krLiQH0wrG6e9CWtZ90Kb3Xq0GXEdnfuxJqG
+G6XFeSSysebPtr5JCTNe6ZEAw5yH6lIHaT0vHRFu1DQkY9lm5EI37mIKKspQ4vKC1YnM+3zRkKQ2
+c9SeopitBQV87M9l1fXPXdj3rzAGnqn/5BOBDweraFU6ZoafX7iKP9H8GthsdhjOs1zvTm1d4h8q
+4N+NhpBEgtAmtCtANV3C46lSG32rl86NGDtsBIIAB4EdbeEBHVkEFZDypKh8TKpmtgqqJtxFWdZd
+1JqnrD2w7te0yup1Z2rW3BDI8C2aw8+McvQV96i/zoJR52to0pvQzOGz6o6/V9Ogh4LV1isFOBcE
+n8S69u1plpDx6JxHYowWplEnmOFa198OCmnjlU2TQeL2+qQxZF6isPL2aUh/Ru1yey5ZopCiR+Z5
+QzbWXEk8wn9KYMxeoqMF75wMqiCNeXM5Jsi4TRLF8rkIO3sZeGqwimrb89lddYh/3NzY2Y5sl5rs
+jU3aW9q1V7vBUhaYzBtFeBtzMGKgW51GAAoCz4IpAsj8tjsJEy/f211C46OxmGRO+LfwwQxlvSm7
+uLhSAUQuekFnwAgze4YX27jjQUfFbUmH6iC0xNIg4WVLWIezsT0ITg1c3Vcni50zqzKT25Z43zVT
+RnVZYu0Ev4db2i0HY2WTJk5OX0H2Q+y5PGqGLKNBxBCW7nd/Wqn1Jd2QFftUfGM2eFwnkfcK+axI
+7YLzdlAe8YMEM93PsbchpZ1ZjoQPkFO0FJZdzQuh9tvCDOql9DDazXoDcnUzTVso4gmV48Kgo5bW
+SXelxkwUVGM0sSTXHp+AcYykxbD9prL8gcJM/E7h9X2d9p3CS3GcMepUsqyY8zEjmxBYCkRehsRO
+uBImydYRTvrb0hX9jaNp7sPgtMWFCEZ/5wyifPQgkDKrZIMPaUz466AZipted8eVapJZQ5IccyLp
+KnvyD0XATRtC0zH4BtS5a7CVALoePhiWqyhsajKIQqLO1gwFpsTAmBidUPnsW7m/0BUyW5SIHIJU
+WndNWWknSl2YRHi62oNoGiT7mom3oiSKGHsVN21smudGQuZ1gnHRXKSlM57IwLaf2Kn7a3Mi8dCw
+P+StuW/q5hrCKvimOIsXWLSGhTkGw2XbZOT1xOMpUHlw8eTWB8xvSeChKg0Ca5X0cmTZ9qX5LOqS
+FpQCI5mHe8qmcNkqWn4/ijSBpxI6JEXIwGpPPdseTgIm9zqjAGFdkgDeXlSwliegv+ZhwInFi4mS
+7bnwxnZRGIq9hHotrvIxRhSnBCW5j5auLvOhtXZYvpSNKWLCQqMxL2Ex4fCEP6P2L23VP1TBWDLE
+NMOVIdNkZfZlsgJMw8SfocFMJ0TpzOtM8j3KVNb2rDEZUzV5Wy1h0YQXY5zxhKb3u/WoX/chmG9S
+cWA3XHGjuye923cnIjfw8zComGnhUL0WQc1WMO26HoJAZ6J2YL9AKlcJv2zuEMsB94x9dnvccifH
+7beYduI8hdmURwVJXZxIsVKp5Ql17EB66dNOHsMMa5Mz7e/hA7PTV+GGsz6w/+8Upz51p5ognqqD
+ZKoTmqQV5Jb7pMihWdeIzHYrAngoMOSx1rDYmbEYTSWIfqxGmqkwoZfW7dNjtQIkvae1GPCwtjox
+BypFqLUOhWPpB6gu3WPJ4xzLH82WWbGpS7vHkGJp216aZCoYBYAPGXPhEqhI6CZY4wMTBgH9k1ag
+yNp6byBiXA+IzWFJTPXWWI7XBZ6eRaIUV4oIw02hcMJ0pcivsCcb5C2xU4a6htInZyu8tXuANm1A
+kWZIr7aIxmkgPyIrh5TC9wBvTtXuRWma8wal3d51IIaXfAcDaFxKRnLr+nl8rCNRAMRnQVzTKaDI
+JBEqmnfHytM6VqHuVJAWmh6vy6lIbaZytdEs/7Skgi2mUjacitp0Km95k1OhS8krp+KXZJZ2Uhox
+vZtKY1PxncfMKB97hjSfrKmAbqZSmqz17CmbymvgHVTaRFIMm2Aqv92pEB+ONXkylefpVKi3U8lO
+Ooh9309lfH2s6DEieVC2KPPHqeCPWKRTD69djfE3nTXHzkA8NQnA59sbc2ociLpxFz9fUY/48N8c
+nKjLDYHimzBo2m+gqZ3vs+pdRD+QWZT1UDvGNqN7WwvPARoFOUpMaTgov8y9akyCA83Fs2SCSl23
+wtYeK5xepLzltv88tE23JX6Q7A1Hq/bAr90HNgb5ne4Up02Ykf+tEvbD5qm7kgRtEVqgFDHfaaRP
+duYh3sBkqSgF6ogxtOUr9rZy/Az678C70l3RsrPyxuxADB54Kij3IB3HaSGLj2tadFzfxuNaZxzX
+vWBaAt1pMfz5CTtaWt+dsGOnkM00XhZh2+Z3ImeXvKfBwGS+Rh90PT7oD+VBeSivuvPqEld8dqEk
+5z9/RWP6Cr57RU01cO4YhstSaX/3ih0NFprjobdGYuN9SnDf1ZjpouE87sNRzNlJFzs5lDUGQT8O
+PmnmSN4kOufXUTN7oHFD6K2yqEN9J2x21MvR03mGCwKI1DUJjco9XnfrxrJdHnVWlkM2iw3bARYd
+DxJqY16eYuwG6ZmN/Qk7GdYn2ikzXIpXTT8665btJ82GNFqRLlCuhqord05ujk+IwMBKd15y0pam
+A5UmUW7TsJOnSKHiS6Zc/k4kDVlF9OyL68C1xoPRhVGMkqInAa0P5R0hZ9P6lYrk/7I+9b9RB/21
+487l88fd+m0AhPWPevX8z6+9evvvrumgEf2dENrRcZiphmHo+nsdtIAv4tgO/8FAioB7mJ3ZW68e
+6j33ChJpWPi4Raz/yCpiI5t+fz9Y+At0JglooR3MLBMb5Z3qNFUjMkqHcU1+B21rOEl5xtoEjg8O
+nNlAljQ9657bVE0WlbRC7oYqdtq5P0hfw4clcFB4Rdled2rnklZr1uaqTpT0zOmbab4Z1Fc5WhIG
+YznRN+ibUB8MZFMExLbteEMp/Fr0Ip2LzBG+mtP1p1auyh3gsiy8MBExuRSthP5Q70Y2olXbrsQy
+CvLkCmKBOSDZGsiCIg5HF8u+VDN3TdD8qM8ISUSshiqFgTOZr85GdTMT5m7rRVdtY5abkrIoJtAu
+ezCzvHfnDZEcz3w47lin8qaRt97c2JUF1VQoXuLNulTz1p1Z2LCLOwupWwe6ZGUaVouKVi/tfBWO
+nZGT3e6F52GtMbuIA/r0C98uRnXLTm1ixHU9bQDmdZ69gWyoqxtjpB5cetIIWWOtzurnpLAqT0hP
+XRy6yRCe5h5j0ZLuwilcF4M04jy3w10vUNktnGTAE5/qNrjiWEoIZHnrOdDf8+YxEXEHJL6p8xdB
+Jt1rYNjQNtg6F6cwx4ezvsPgPqtNF/p/Q7ILTeSijzeaIjoSsJX2MtJl+llPA4VM8yjwkyVUCOWh
+IsgOVBHc/XxtlJW1hzFCx0UYUAJnY0U/b05TM7nJCURnv1GrhHczgihyRuuO9moVqjuNErTkET88
+cTuNAn0BjOkYrUHUYDTGuA8onmBYHLSNp7g7LSyKlVYgRBWymgR6SrEPWjpYep3DQYsc9bwkZkaZ
+RWOUdovENJ1lbKbFQa3q/hz3sN4AtBjEnGU63iqyFkuYawUiuwJRWkhVMxuHbFjXRpmvclMbVnCn
++3ub8Jkz1c9cfMxxddcXeUjmXMT0SB+xUDuq4zywzRivtbzv95jVSVSoEZHEmttdRBqrfhKbIdrP
+Mj5rNBAvDcdiHEYSsKehZ4KL4tAQy9RJPimW3SjFclDC8UyhITYpbL0tFMh8I9LAXWU6MUJgAtI7
+qaH/yx39FmcomlILeODE9i7bHTsJrnwmVgOyNFRTbmvqJwAii3nXqM4idMJqV3pSXUDVpePsZ0AZ
+mqbf6nU2qefGdl6qFhNfCw4i7D2D8x8Lz99r8DguddE6iyGj+8W1rq9JcrGLRcDm7dXpjPqy8QoB
+ENrUrskjGu8Q2WKitp2BJlNU2i3FQ5HdJVQU92TFF3dxXjevTLmjO1szT4DiNRsj5tiRSlU5r6A2
+7geRlo+lSKvLLDW0A456InFLYbvXApjvPAsSgn6jlBIH5OEAZq2PdGJr9IHWMNPHQzdG9TADoWnc
+ClHSM2ihzskOWmTvR/YFtg7riUT2ahmkpgc6x6roRzo2GtUiJE8VHcKzXXn0q/JSFfAwFXO4iOwM
+XRklSPEqwlK7my6EG320x9fA7rpi4XRqcktqk305pP0ktCNnsocmLedMMjo+J0P3RYKj+FHHc6qs
+GwJ0zYWbJN65rtvNdmCNuPIY27ykQYyrlcblcB+Tj0SaFUvzRrfIuSVZyNNfod+hq4EfNGX5xsK6
+adwMpXNDFTgfE9Nnb+hnB0sa3P0UswWsuiLZq6HVCsYDGcB0zelPqdtrNH9jOK56HLQLPM3U6MAO
+UPNSljERQ7fAhmhFHYDYA+i13NLNLYuFTCh5IF024yZBfVzSiw2aabeagGGJuUkKC+vr3KlFdeWL
+BKNy3gf5rA2b6hoi4RTzTFg2xZy1063Eu/ITw3ikZxZvM3X0npSuugY70Z9GfgP0HFRldAnQIU7h
+TcfhDPW7QIeo+80Ju1ZSPzX4vYA2B/3Uip36LCnjAAkqmYgXsdm756C5qMCiUWk4EYkxXnZW5Xcb
+Edb1NRKa5CZofaD+kdIt29a3d4xa1Uvaad02ZCN5mgjmUmHcpKixgKMu47h3L9JsGDZtDliEIkrB
+rdHAMJ0lahcqSAlrS1mhrQjNObaBEurBIG6toMov/TJis1a31hZpX3roSaU7ICoEY4/qD9qhrstn
+ra5tRJWhuGk1UtZHI7OXJP460Ihk8dn3/O5AnikNCFB/cIVihWnWbGw7ubEGmNHMZhJEnVr2CptQ
+xnSqbQdEFkloLVXcsBBmZZ4w4spPoy7WYR9NZ3TQgfjanZmv6nGgUcGu/1KxDQVngOqkxQrwI89b
+p3CZ/qF2h3aimSnRAF3bMc9NaBAEqfDAUg7Nq96aaXOhxQ1ldO4YBAAjeGO+FhoRTYlwuJTgmXiy
+y0peZrmdErBBnY5aMbLhOtIkPUXwVfLwaq34vKp6H6pKmm8Ds0qIKaMb/GwjbKxmCiWhOvd0PdyB
+nenclRCtemvZSXjHMzsO5zIsamYpbt5SYyrmLkmcYu1apkuUIMZEKnjEpg5cZ0JMRKPsktAb1ZOw
+rbIbYLI6iMa6inZjqajGLsgG/T4vVIjviCJPwsqyiplZZdi/pn16ndviqlcdsTXcICYnRwVg6viA
+QfKx249ZxQlxWXRnil3X9ybRdq+B0473aietdYK14qQaHbQ8IxForlcap7aEysq0urLuayEDsrc6
+GE4I8A1wjvgg6AZDLj1PvDK+zzHNgZHhnK09Oi5IJSs3OXWHxnl0R0wofWg9kGlWrAcr7gleNbic
+fQOcmCyMGyUipS9Al0ncLOIIBrJIIG+Zf5HFUACmWDOhSB4zX+3uBEtnMYuELIADa4Bj65F0FyDD
+/Ub0SbC1wrw5gebpTM0ca+15yipsdDpXShSFtDG69mkQA8keYWxYc7Ss8aMzyOwoI3M20gOIrKPm
+FYzJ1fbFMyuwrUTOAHK0lmoRwofUq0MWFs6m67j8G+r/nVY7N2Dt5Lpz22vNbot7aSRy3RqyJl+h
+dVixotZU171S5axNiZ9ch1wm92WvAvph5rvBnNOmS7Bq4ZUY3bbfItknhCBvitpforw0HtyqHj4V
+NnMHOO8hc6kucVnVo9SrGnwWhRfMSTKRc9VP6PbyNY+gYBuzYtkuksewtDpOoovMchA8PtfepLQe
+gybeR0f5tTspsfNBUfYW4mzAMDawBfTa4VG6TWSgftIYHdino7S7mFTexaT3rifldzRpwCOgMiuf
+dO95QhDcTWeceJxySHgeYOzKPKtSlaaI2hnLLpWMSVyVmjsL0pOUoPi5jSZxXzl1sVAs7dxOQ+3c
+YqtMopTaXXqTZD2exOuIEdCx1xrP2Fl31LfbZUdEyCR6byb5u8b45dQvU2YgSjWJ5FNMQ2dyZLNI
+1oRp3ZlHQf14FNeLIVNAerFBRN4uLWehT0r8krWOJ9hgXhU2k6uF3rBLXGlllrQzT3FcZWZOun4m
+wO55h51k79uT7B+jA2zulsj1LcOH8qGyNOvWSazhlNwAbANG1lp3lZWblyx2TG1S0jUfuYHVlT50
+hKsyFMN8MNkQ7MmQUMQmNhHep1jQa3G2gg/+6lptivSl82262+w3T7IuxeiQHE0PqGYqAKuTF0Kv
+JltEmhR6xqo5aMqiqZi8z3w0/ojtGN9gA/N9vO1NRegN2gFToF40lAOhKNV15nujPq/Zsy8K5IAX
+o500j7ltEYZcEqJ91jg2A3PHAgBHPABaTaNVL5zKSh4ruhg15rEoSi+qLFBJqi7LxFyYgYGTAhaw
+h5ul7TtYO+RL6Ju+YM7JHeHiZmiFe+8BOSXqxvZQ68Tobum50W4HIZ0YgDWgbqn4L0btvqrodq9r
+S3V27kDHl5GTH97mipMOlwRNDs2KianxWkkmauuCDvOw8tQavg16HL9eMDOsgotaNyg5kgQyPE1L
+beShB56aZ9VwxT0D6B7IcD+vg5G9Bqv/rg7ajWzSbNeDP7hnWTKvrJzHQRh57i5rh/q6B11HDz8Z
+77vRtxVMNmEPcCuP6PEEaoLaorTg0R9r/qkp8Rtv4Yu5+Nfkvu/++M//H925cCZcLNyaEMaErCD8
+FR3gHzdLFodneTjCNSbCqvxlc2hfkvCX/z3RNv6Iu/HDl/jSVbF1EKy2QCpCODNXjfarm/eI4NAg
+adgQz74az9/cvPjLUT+yPGBgFAaz7t/6KiqKSvKm4XrQxuWQzn+igdT07/E8XxgcKo8MFPgmU6f3
+fZXSi7qITAcDMdRtM+Rn7o228lc0sWXII2fuTHAJ9C9X+m3GQ7eBm3VbleEqTO89Ir9CT5k7rYEq
+Mn1yPfyXAZAqNGvKisnqui0cmNNkFjifhh61MTlm8Fjvm+6J7exSGZjmq+O1jnuzE8OFjpNDV7aF
+8yqxmG6Q7bXi3H8OkJhk5ulANyLrznJJNpj1mhJZE0sMT+wgNQszLYIPV9XO2zRbDBhYk2BYp1aM
+UbNvkEdEK1NZq1YkV5FW+zwuk/MetDxZ9lbWfaLhclvV6mU6Yb1D33a4o2FpV/RPjOxznVxYTgut
+D+MEwzhqah83FBsFCdDBFnssa9d+gpNSlyt1EJtpxxLjOsDCcKr3WjSviuKiatjclr5cNDBKptxd
+BFuzvogippn5i0ltPc9K41FFi8nXtGyB9qM3n0VetzKqeDUYw1zW5BhZEth3daaH9b62dOCQ+ufY
+tvZ9znvlGQMpXxN3PTVzrowrkRLla7BoRXT9ZhNJgG0qR/WDcO+nhCSWqDdnhhOelxU9r/7sm9vm
+B3Nb7Xdd8y9kDlW1NQA0NnOG99cWqtgK1y4zhX5Mb2XNJN4wqn3fmhuo/UsStstFYlvbOs7WSXHB
+tGNtasYOG2uzGFRmBGnV0rTz3JMp/CJWVHZopHNFGJoaT9/rbQ741bzWDZOxXFQtSjbXZbZTG2Mt
+i2xHd4SUXqq9AmXjeGkmwQYt/FJq7nnNV4h78tWQ5pUZPyqcZvZAc7jDK5/kNQDdc0QtjMwJjgd9
+6Lj2QiDU8KWyoUO2l6ZctbqxH1T31DIQKeHRcHsEXEF9ExVYLDWLRJ+toT1ZJqSWsdmynJ+rOX0+
+JfdL/PB9MHO5KhHDr4oWYkl2ZpeoVYALm6nzKa2HTZKoML8nsCFhj/O4GU/HHhK+4x2GwlzlGcMU
+DghNHzq7og2IeIx7IfzzKLsRUp5JDBCV1t1k/dMYmf2uEAOCL1T/j6WnMwYPMNpE+jIotLUVcYl0
+lrGiCN2U1HRqz3ts0+HCh5VJ8E9O4V/rzQ50F7Xy+PTzy0RMk4xvJx3TVYJJVqcLBWvDPU7/v+EJ
+jLnqYNvOvKWVxy++0tx7nD5Pak+lDOZjK5mmyqvSi8/Hpr3wK3kSEb0V4hPT4qpcMdRELehGi6gq
+TthqXQSCKMOwvqocF6xnzcY1aF8LM/sXVze97+/eN0AllOMqCzgPGA3N4furuyowBrda5C1LW9pU
+GiD48B2O9H76ht6LTOgVYltdY7FYFGh1FORUlKLNQVAxF9m6DJJhZisENcgS3XkBv3ankYCRIxmy
+m0jghoexHLbXLKxrPen3YdRcF4p2OyIvhrrzjD/7OjUqmgtOvSAksJ6hA+CFLZJAe8dhaWzFKzlo
+DdbwWmGeg+gyGrEIJ0V3FbTtnmbWrrA8slms7Cyg4byyLPeptEdtxnzwxtKSC8KjGbebxSvemmBp
+6sVNVyuvbqATJhdar8xerysrekjHcC3bivG99lok1GG9P3cz3oFfnkjqtBFXPl7UO1rTa8SS7syW
+n7pAgfvtMCfulpC8KdrgHwfzMDbvswInGnoPg/ZOatZnqGv2pGNHdFcoIBx3o2gYB4OmuY9kfUvX
+i3XceBjj8tYP+wti6MdF2yA5VMi7jMp56asbs8yuzaDbqBQ8WR199tTiOgnqbSMwzyL6kJG5sCJn
+72fqCTzHfWcgDUuc61QTNHdTa8Esc+mimg/xj/qBuuKrP1U1yD9tN8EJ7tGJbWDmL2sbeyPt2Py0
+9sYl5OMVnuF5YtPkqR6i8XpCRcWhswianVvEJ1Hm3UtO4XogLA7nE8ZvlD9OPC4D2vZI3mBGE9HR
+02ds0O/hEHwsU/jkOAizjQDNOR91pHGRZdf3UWpf5jA/Sf0qcXd3Hf3GFt1s9LlMDFSr4jV0Usot
+996oEmqU/Bmu0Qo2B7JxEiIzbsOZ2+b7uow3+C9XUV5cp511FfvRzhBDt0DVMSuRnqO70vj/9cLN
+mxXqhYXnVxlPpodIdBu97zdpEwBHykI6X3V6S1zLg1+Zp73U75LaIbXYejDH8qZPm3rJVX1Sevbr
+KPSdB+9m2aEwQrLu7wZMfxTOw7CQvpMsTWM8ZTY+w2p8gVBGrm2pHgwyFpcwNa5yfTjEZYCFqakf
+1ARUp8Yoek7Ey14a9W07OtuWrAyIEeFSiU9idMIYRjJqxH4ugugGH+BDI5qdSoZU2jP9UTIk1Ym+
+UTq6KKq6T+HkIku+SzGxOjJmGOteWY1y5sePqCJoHjVzFy9t1YaXOu74gavdoPs6hjABOGN977Lt
+19E6EF1Xo/LRyitP+dTGzqs7qk89hFVf9CutcT9HhliEqc3syjSvPPclpUNmu0tDOZfOeaGdE/ia
+NVdRG+6lki4anVJHv2oHACCRc5v2FX19WgLIEjOLQhM5tohe4hCkcce0oXqw3ZvOxMnWg+KFKxgG
+C008Nv617aM4cyShIZc0xfGZdVd5I7hclLNIxZ4WFrNgPFWZONlkiYCX3oSWcYKg2TTSJVF1k3ed
+58OF1n12zQJ7sv5Qw1axBu7rWDyQKJv2HXa1S3XyVrJW3peeiMnQMxd++KnDSJI2r32Uz9PC/dTr
+erJy2+qTUlibUPobauHntqNAatyAmi934c0ToGy63YI2zax2cyKNAswpKMOqheOndyGpm8teDMaz
+IgkfdFA65gB3Vh2oU9AgN4Ff2osx0m7cWHnMh+E+j8ebsY9I163JlgSqPdcJrDnx6zgBOukQ+Gtl
+zaLtss95M66d0d7UzKnxf9NNQTjLvqq/VowSHrVKEgt1bIp0q6ah0GiSjroHWLlm8GTZn9K23eJ9
+eCET6AbQSTEvI7GJIgi6Oc3eGd3WeOnZkw4DUEjU1jeJPrK1Swm9NU5Bsb7GajKPtLVfW1uDSZ6W
+y7O4K1h9kRaX5vlA5hzKTEH2o87Mz4CLaaB0WqDSD6G+SGVeGW7N1EcZZv8zGD2R2A3btMJ097Eg
+zYYdGB2d9AGHXTZLc3qjfuVd6YG25dyES2YNuAYLiGa5bQPHyRp8qAqeHyQL139V0fqBYfzXknlx
+qA/LoyXusnmRw9VLRaDpr3Su6V/3eZjVN/mf+6U37NePD/TLvweIdXG5fbOf+vVYx3f8s2Mkhzqs
+m+cXeI76380J5MAwUT3+UP5C1/a//rPtMMMn60PH8nX8+cJU++Yc/dFZ+PkH/HI6f/47P/sAX87P
+yfM//qZT7n7vRjy+p//kJEyhJpN8ioDQH5wEyFpIFOheORCtpp//VyeBpSOrp2uRnLzsnbVyqq7e
+dS3+4BR8d4RvrgPx9+kD2upE7Tr+vL8O3IntCVcMuOfxh0YFr/dfdB0IpJL/5kk4PBO0vQirWoaf
+az7mrzcDeD7HgGkKwez9pzf/TnfIsPW3k/Plgvtv+vQ0kT766YX196N6xsJ3+/Ydf7sU6JycifvM
+Pvb4Q7Po370E/o0z9evSCsIleT4uquFL9aO1949+4W01+f2/f11JpuVi6kO8+8WboXj58tq/rbn/
+fHeFHK/yb/7x7ao/vs7X//71A/7+pd+91tunevvLTfgiD/JzQHoR6/Hw9W1OOVT/+BstxYBW414e
+nl+q4N3Nbk6k3t/e0D/+9u7tfrMQ/PT4VXVI3w4znRmhTcX1Rw9LUudBvh3muD67gpvpo4fdHORw
+yA5vBzp+kzg80Xl9+MhhevgcHJIfnmmIsRNJ/Y+d8b+uuT871dsDnMBf/schLf7XL7sDjprw3RnS
+TNaVj7/K7iAzdiXx+5NkoT7/C47NdZp8d2BjokJ/9NScHuIqODx3Ly/F28GO363N1ubtL6Zb7M9d
+42eH52D48T30Zev00bd/8Rzy9t/e6PEuot3zF3yZ++a5+Ry8oEl5d/CJuf/2F3/+tOybLDp8ejvO
+8V1/eXh+9HRcHaJDVaMlfXfsL4+mjx77Oozj8N2CRU/Q/Auu7ZtDGia/nB+em2/fNfF3Fg+4j77r
+IwrjR0vL123rR49//1LVv8xeMtL+3t7s9H3qbGX/gnd/dmAxZ8Gq5btr3IB7/BesvOsm4uhswL6c
+hOl92+zhhP4XPC/W+bt3PB0XO8PbS/35W4en8q9jvvPwc/6JGeBJNSUtVm8H//I5NI1sjbe/+sDr
+Idz548eTqqnYNP6KhTIcc/l+O8Ch8Q66f8H3fIM6CXjt28mYzs/Xg/8Fd++PB7K/ey2GqG9/9+e/
+jH8RqvnBXcLZJPhp3u8MVObSDIA//tbPXnz2OIfh+29hOvxfsJn8WQzNB0/LH47VuYZ491MWxkcX
+0X+Jgv/gR5gH/xru/cGXOD5nfo5c+uAr/EubyAePf/PCKup/v8e3NHwd5jRd++iXfHp45vy8Hee4
+SBsYEwTyCUFrAyUF0uS3f/7za8SP16M/IxD56fn8Ub35azvm91XoW7vtR//tfYk9/cbn5OUg//l/
+AAAA//8=</cx:binary>
+              </cx:geoCache>
+            </cx:geography>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+    </cx:plotArea>
+    <cx:legend pos="r" align="min" overlay="0"/>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1387,6 +4521,83 @@
   <a:schemeClr val="accent4"/>
   <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -1935,6 +5146,1059 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="496">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="850"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="3175">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="288">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:sp3d/>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr/>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1976,50 +6240,259 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>87751</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="state">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CCBDBC1-E024-53B5-A29D-FBAF6DA158EA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="state"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1885950" y="0"/>
+              <a:ext cx="2288026" cy="1695450"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a table slicer. Table slicers are not supported in this version of Excel.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2007 or earlier, the slicer can't be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx4="http://schemas.microsoft.com/office/drawing/2016/5/10/chartex" Requires="cx4">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Chart 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA91F7D6-B6B2-A413-6E11-1CA1D04C4F12}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4591050" y="95250"/>
+              <a:ext cx="3562350" cy="2486025"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>285748</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49F7C950-8FB2-67FC-C9BA-9FB249935D58}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_state" xr10:uid="{28B91DC0-80C8-45CD-95E4-2D6F4E97AB19}" sourceName="state">
+  <extLst>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
+      <x15:tableSlicerCache tableId="2" column="1"/>
+    </x:ext>
+  </extLst>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="state" xr10:uid="{B09F645A-8336-409F-A172-60C0DA693196}" cache="Slicer_state" caption="state" columnCount="2" rowHeight="288000"/>
+</slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F5150032-0159-4CA8-893D-099E996638F2}" name="Table5" displayName="Table5" ref="A1:P21" totalsRowShown="0" headerRowDxfId="0" dataDxfId="2" headerRowBorderDxfId="20" tableBorderDxfId="21" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F5150032-0159-4CA8-893D-099E996638F2}" name="Table5" displayName="Table5" ref="A1:P21" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
   <autoFilter ref="A1:P21" xr:uid="{F5150032-0159-4CA8-893D-099E996638F2}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{C5CBFC98-8E7D-4C21-89E4-FAF15EA36526}" name="roll no" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{90E1E575-36AE-4B57-9554-F810D22C4069}" name="name" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{41CE8180-A4B3-4981-A46A-5797578CAEBC}" name="class" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{4F43BF84-4F85-45AF-A5B7-BFD0B0B34915}" name="age" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{723CA5DE-548C-4380-AD3E-C06E34485EB9}" name="math" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{37F8BA1F-733A-4691-BF51-B91D7018745E}" name="science" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{C5CBFC98-8E7D-4C21-89E4-FAF15EA36526}" name="roll no" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{90E1E575-36AE-4B57-9554-F810D22C4069}" name="name" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{41CE8180-A4B3-4981-A46A-5797578CAEBC}" name="class" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{4F43BF84-4F85-45AF-A5B7-BFD0B0B34915}" name="age" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{723CA5DE-548C-4380-AD3E-C06E34485EB9}" name="math" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{37F8BA1F-733A-4691-BF51-B91D7018745E}" name="science" dataDxfId="19">
       <calculatedColumnFormula>E2-5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{CDC30C63-68AB-41E4-A290-A45A3E040F06}" name="marathi" dataDxfId="12">
+    <tableColumn id="7" xr3:uid="{CDC30C63-68AB-41E4-A290-A45A3E040F06}" name="marathi" dataDxfId="18">
       <calculatedColumnFormula>F2+10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BEE1DACA-0144-458E-B4DB-2E8FA27BD48F}" name="hindi" dataDxfId="11">
+    <tableColumn id="8" xr3:uid="{BEE1DACA-0144-458E-B4DB-2E8FA27BD48F}" name="hindi" dataDxfId="17">
       <calculatedColumnFormula>G2-15</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{BBBCAECC-4D66-4109-B234-FD85295AFE78}" name="english" dataDxfId="10">
+    <tableColumn id="9" xr3:uid="{BBBCAECC-4D66-4109-B234-FD85295AFE78}" name="english" dataDxfId="16">
       <calculatedColumnFormula>E2+10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B96932F1-5DF6-40E6-82DD-186EBF3F6BDB}" name="total " dataDxfId="9">
+    <tableColumn id="10" xr3:uid="{B96932F1-5DF6-40E6-82DD-186EBF3F6BDB}" name="total " dataDxfId="15">
       <calculatedColumnFormula>E2+F2+G2+H2+I2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{ACBC5DBF-7793-4B03-BAEE-DA459C59102B}" name="percentage" dataDxfId="8">
+    <tableColumn id="11" xr3:uid="{ACBC5DBF-7793-4B03-BAEE-DA459C59102B}" name="percentage" dataDxfId="14">
       <calculatedColumnFormula>J2/5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{86B97156-9599-4332-9136-4948BFDC7CA4}" name="max mark" dataDxfId="7">
+    <tableColumn id="12" xr3:uid="{86B97156-9599-4332-9136-4948BFDC7CA4}" name="max mark" dataDxfId="13">
       <calculatedColumnFormula>MAX(E2:I2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{59256C59-67E2-4019-929E-7A2B13AA2E2D}" name="min mark" dataDxfId="6">
+    <tableColumn id="13" xr3:uid="{59256C59-67E2-4019-929E-7A2B13AA2E2D}" name="min mark" dataDxfId="12">
       <calculatedColumnFormula>MIN(E2:I2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{87E2380E-FA60-4C28-B452-18BA6BEEB07B}" name="grade" dataDxfId="5">
+    <tableColumn id="14" xr3:uid="{87E2380E-FA60-4C28-B452-18BA6BEEB07B}" name="grade" dataDxfId="11">
       <calculatedColumnFormula>IF(K2&gt;=75,"A grade",IF(K2&gt;=60,"B grade",IF(K2&gt;=50,"C grade","Fail")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{AC83FF28-CE7B-48BB-BB92-5021D9540420}" name="pass/fail" dataDxfId="4">
+    <tableColumn id="15" xr3:uid="{AC83FF28-CE7B-48BB-BB92-5021D9540420}" name="pass/fail" dataDxfId="10">
       <calculatedColumnFormula>IF(K2&gt;=35,"pass","fail")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D4F53D51-E319-4A77-BCBF-62DC45AD5BB4}" name="rank" dataDxfId="3">
+    <tableColumn id="16" xr3:uid="{D4F53D51-E319-4A77-BCBF-62DC45AD5BB4}" name="rank" dataDxfId="9">
       <calculatedColumnFormula>RANK(K2,$K$2:$K$20,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2031,11 +6504,31 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C9B4D063-B7D8-4E47-8C86-D164EA8A7EDA}" name="Table6" displayName="Table6" ref="A1:E5" totalsRowShown="0">
   <autoFilter ref="A1:E5" xr:uid="{C9B4D063-B7D8-4E47-8C86-D164EA8A7EDA}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{49C51BA5-B62E-40F7-85F4-4331E95A2AC7}" name="Timeline" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{49C51BA5-B62E-40F7-85F4-4331E95A2AC7}" name="Timeline" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{B8340230-C8E7-4489-9FB7-8C38F220FDCA}" name="Values"/>
     <tableColumn id="3" xr3:uid="{CA2197FD-54B9-44BE-ABAB-9BCC80299CC5}" name="Forecast"/>
     <tableColumn id="4" xr3:uid="{BE0ED526-ABE0-4DA3-B130-5A3417BAF8EE}" name="Lower Confidence Bound"/>
     <tableColumn id="5" xr3:uid="{6F90FA9C-79B9-4964-B299-CAEBB276AB66}" name="Upper Confidence Bound"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C6AA5265-49D3-4EB4-80BD-70DACE080A45}" name="Table2" displayName="Table2" ref="A1:B9" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
+  <autoFilter ref="A1:B9" xr:uid="{C6AA5265-49D3-4EB4-80BD-70DACE080A45}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="mp"/>
+        <filter val="punjab"/>
+        <filter val="rajasthan"/>
+        <filter val="up"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{553CBF5C-1418-431F-8EFC-CA566146E442}" name="state" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{A28E1ABC-9C4A-497C-9AAC-60EF532B1514}" name="population" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2683,7 +7176,7 @@
         <f>E2+F2+G2+H2+I2</f>
         <v>325</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="23">
         <f>J2/5</f>
         <v>65</v>
       </c>
@@ -2704,7 +7197,7 @@
         <v>pass</v>
       </c>
       <c r="P2" s="9">
-        <f>RANK(K2,$K$2:$K$20,0)</f>
+        <f t="shared" ref="P2:P21" si="0">RANK(K2,$K$2:$K$20,0)</f>
         <v>6</v>
       </c>
     </row>
@@ -2725,47 +7218,47 @@
         <v>35</v>
       </c>
       <c r="F3" s="2">
-        <f t="shared" ref="F3:F21" si="0">E3-5</f>
+        <f t="shared" ref="F3:F21" si="1">E3-5</f>
         <v>30</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G21" si="1">F3+10</f>
+        <f t="shared" ref="G3:G21" si="2">F3+10</f>
         <v>40</v>
       </c>
       <c r="H3" s="2">
-        <f t="shared" ref="H3:H21" si="2">G3-15</f>
+        <f t="shared" ref="H3:H21" si="3">G3-15</f>
         <v>25</v>
       </c>
       <c r="I3" s="2">
-        <f t="shared" ref="I3:I21" si="3">E3+10</f>
+        <f t="shared" ref="I3:I21" si="4">E3+10</f>
         <v>45</v>
       </c>
       <c r="J3" s="2">
-        <f t="shared" ref="J3:J20" si="4">E3+F3+G3+H3+I3</f>
+        <f t="shared" ref="J3:J20" si="5">E3+F3+G3+H3+I3</f>
         <v>175</v>
       </c>
       <c r="K3" s="2">
-        <f t="shared" ref="K3:K21" si="5">J3/5</f>
+        <f t="shared" ref="K3:K21" si="6">J3/5</f>
         <v>35</v>
       </c>
       <c r="L3" s="2">
-        <f t="shared" ref="L3:M21" si="6">MAX(E3:I3)</f>
+        <f t="shared" ref="L3:L21" si="7">MAX(E3:I3)</f>
         <v>45</v>
       </c>
       <c r="M3" s="2">
-        <f t="shared" ref="M3:M20" si="7">MIN(E3:I3)</f>
+        <f t="shared" ref="M3:M20" si="8">MIN(E3:I3)</f>
         <v>25</v>
       </c>
       <c r="N3" s="2" t="str">
-        <f t="shared" ref="N3:N21" si="8">IF(K3&gt;=75,"A grade",IF(K3&gt;=60,"B grade",IF(K3&gt;=50,"C grade","Fail")))</f>
+        <f t="shared" ref="N3:N21" si="9">IF(K3&gt;=75,"A grade",IF(K3&gt;=60,"B grade",IF(K3&gt;=50,"C grade","Fail")))</f>
         <v>Fail</v>
       </c>
       <c r="O3" s="2" t="str">
-        <f t="shared" ref="O3:O21" si="9">IF(K3&gt;=35,"pass","fail")</f>
+        <f t="shared" ref="O3:O21" si="10">IF(K3&gt;=35,"pass","fail")</f>
         <v>pass</v>
       </c>
       <c r="P3" s="9">
-        <f>RANK(K3,$K$2:$K$20,0)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
@@ -2786,47 +7279,47 @@
         <v>58</v>
       </c>
       <c r="F4" s="2">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="I4" s="2">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="J4" s="2">
+        <f t="shared" si="5"/>
+        <v>290</v>
+      </c>
+      <c r="K4" s="2">
+        <f t="shared" si="6"/>
+        <v>58</v>
+      </c>
+      <c r="L4" s="2">
+        <f t="shared" si="7"/>
+        <v>68</v>
+      </c>
+      <c r="M4" s="2">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="N4" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>C grade</v>
+      </c>
+      <c r="O4" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>pass</v>
+      </c>
+      <c r="P4" s="9">
         <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="G4" s="2">
-        <f t="shared" si="1"/>
-        <v>63</v>
-      </c>
-      <c r="H4" s="2">
-        <f t="shared" si="2"/>
-        <v>48</v>
-      </c>
-      <c r="I4" s="2">
-        <f t="shared" si="3"/>
-        <v>68</v>
-      </c>
-      <c r="J4" s="2">
-        <f t="shared" si="4"/>
-        <v>290</v>
-      </c>
-      <c r="K4" s="2">
-        <f t="shared" si="5"/>
-        <v>58</v>
-      </c>
-      <c r="L4" s="2">
-        <f t="shared" si="6"/>
-        <v>68</v>
-      </c>
-      <c r="M4" s="2">
-        <f t="shared" si="7"/>
-        <v>48</v>
-      </c>
-      <c r="N4" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>C grade</v>
-      </c>
-      <c r="O4" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>pass</v>
-      </c>
-      <c r="P4" s="9">
-        <f>RANK(K4,$K$2:$K$20,0)</f>
         <v>7</v>
       </c>
     </row>
@@ -2847,47 +7340,47 @@
         <v>89</v>
       </c>
       <c r="F5" s="2">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="2"/>
+        <v>94</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="3"/>
+        <v>79</v>
+      </c>
+      <c r="I5" s="2">
+        <f t="shared" si="4"/>
+        <v>99</v>
+      </c>
+      <c r="J5" s="2">
+        <f t="shared" si="5"/>
+        <v>445</v>
+      </c>
+      <c r="K5" s="2">
+        <f t="shared" si="6"/>
+        <v>89</v>
+      </c>
+      <c r="L5" s="2">
+        <f t="shared" si="7"/>
+        <v>99</v>
+      </c>
+      <c r="M5" s="2">
+        <f t="shared" si="8"/>
+        <v>79</v>
+      </c>
+      <c r="N5" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>A grade</v>
+      </c>
+      <c r="O5" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>pass</v>
+      </c>
+      <c r="P5" s="9">
         <f t="shared" si="0"/>
-        <v>84</v>
-      </c>
-      <c r="G5" s="2">
-        <f t="shared" si="1"/>
-        <v>94</v>
-      </c>
-      <c r="H5" s="2">
-        <f t="shared" si="2"/>
-        <v>79</v>
-      </c>
-      <c r="I5" s="2">
-        <f t="shared" si="3"/>
-        <v>99</v>
-      </c>
-      <c r="J5" s="2">
-        <f t="shared" si="4"/>
-        <v>445</v>
-      </c>
-      <c r="K5" s="2">
-        <f t="shared" si="5"/>
-        <v>89</v>
-      </c>
-      <c r="L5" s="2">
-        <f t="shared" si="6"/>
-        <v>99</v>
-      </c>
-      <c r="M5" s="2">
-        <f t="shared" si="7"/>
-        <v>79</v>
-      </c>
-      <c r="N5" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>A grade</v>
-      </c>
-      <c r="O5" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>pass</v>
-      </c>
-      <c r="P5" s="9">
-        <f>RANK(K5,$K$2:$K$20,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -2908,47 +7401,47 @@
         <v>24</v>
       </c>
       <c r="F6" s="2">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="I6" s="2">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J6" s="2">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+      <c r="K6" s="2">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="L6" s="2">
+        <f t="shared" si="7"/>
+        <v>34</v>
+      </c>
+      <c r="M6" s="2">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+      <c r="N6" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>Fail</v>
+      </c>
+      <c r="O6" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>fail</v>
+      </c>
+      <c r="P6" s="9">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="G6" s="2">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="H6" s="2">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="I6" s="2">
-        <f t="shared" si="3"/>
-        <v>34</v>
-      </c>
-      <c r="J6" s="2">
-        <f t="shared" si="4"/>
-        <v>120</v>
-      </c>
-      <c r="K6" s="2">
-        <f t="shared" si="5"/>
-        <v>24</v>
-      </c>
-      <c r="L6" s="2">
-        <f t="shared" si="6"/>
-        <v>34</v>
-      </c>
-      <c r="M6" s="2">
-        <f t="shared" si="7"/>
-        <v>14</v>
-      </c>
-      <c r="N6" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>Fail</v>
-      </c>
-      <c r="O6" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>fail</v>
-      </c>
-      <c r="P6" s="9">
-        <f>RANK(K6,$K$2:$K$20,0)</f>
         <v>16</v>
       </c>
     </row>
@@ -2969,47 +7462,47 @@
         <v>28</v>
       </c>
       <c r="F7" s="2">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="I7" s="2">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+      <c r="J7" s="2">
+        <f t="shared" si="5"/>
+        <v>140</v>
+      </c>
+      <c r="K7" s="2">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="L7" s="2">
+        <f t="shared" si="7"/>
+        <v>38</v>
+      </c>
+      <c r="M7" s="2">
+        <f t="shared" si="8"/>
+        <v>18</v>
+      </c>
+      <c r="N7" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>Fail</v>
+      </c>
+      <c r="O7" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>fail</v>
+      </c>
+      <c r="P7" s="9">
         <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="G7" s="2">
-        <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-      <c r="H7" s="2">
-        <f t="shared" si="2"/>
-        <v>18</v>
-      </c>
-      <c r="I7" s="2">
-        <f t="shared" si="3"/>
-        <v>38</v>
-      </c>
-      <c r="J7" s="2">
-        <f t="shared" si="4"/>
-        <v>140</v>
-      </c>
-      <c r="K7" s="2">
-        <f t="shared" si="5"/>
-        <v>28</v>
-      </c>
-      <c r="L7" s="2">
-        <f t="shared" si="6"/>
-        <v>38</v>
-      </c>
-      <c r="M7" s="2">
-        <f t="shared" si="7"/>
-        <v>18</v>
-      </c>
-      <c r="N7" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>Fail</v>
-      </c>
-      <c r="O7" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>fail</v>
-      </c>
-      <c r="P7" s="9">
-        <f>RANK(K7,$K$2:$K$20,0)</f>
         <v>15</v>
       </c>
     </row>
@@ -3030,47 +7523,47 @@
         <v>86</v>
       </c>
       <c r="F8" s="2">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="2"/>
+        <v>91</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="3"/>
+        <v>76</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="J8" s="2">
+        <f t="shared" si="5"/>
+        <v>430</v>
+      </c>
+      <c r="K8" s="2">
+        <f t="shared" si="6"/>
+        <v>86</v>
+      </c>
+      <c r="L8" s="2">
+        <f t="shared" si="7"/>
+        <v>96</v>
+      </c>
+      <c r="M8" s="2">
+        <f t="shared" si="8"/>
+        <v>76</v>
+      </c>
+      <c r="N8" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>A grade</v>
+      </c>
+      <c r="O8" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>pass</v>
+      </c>
+      <c r="P8" s="9">
         <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-      <c r="G8" s="2">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
-      <c r="H8" s="2">
-        <f t="shared" si="2"/>
-        <v>76</v>
-      </c>
-      <c r="I8" s="2">
-        <f t="shared" si="3"/>
-        <v>96</v>
-      </c>
-      <c r="J8" s="2">
-        <f t="shared" si="4"/>
-        <v>430</v>
-      </c>
-      <c r="K8" s="2">
-        <f t="shared" si="5"/>
-        <v>86</v>
-      </c>
-      <c r="L8" s="2">
-        <f t="shared" si="6"/>
-        <v>96</v>
-      </c>
-      <c r="M8" s="2">
-        <f t="shared" si="7"/>
-        <v>76</v>
-      </c>
-      <c r="N8" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>A grade</v>
-      </c>
-      <c r="O8" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>pass</v>
-      </c>
-      <c r="P8" s="9">
-        <f>RANK(K8,$K$2:$K$20,0)</f>
         <v>3</v>
       </c>
     </row>
@@ -3091,47 +7584,47 @@
         <v>24</v>
       </c>
       <c r="F9" s="2">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J9" s="2">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+      <c r="K9" s="2">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="L9" s="2">
+        <f t="shared" si="7"/>
+        <v>34</v>
+      </c>
+      <c r="M9" s="2">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+      <c r="N9" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>Fail</v>
+      </c>
+      <c r="O9" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>fail</v>
+      </c>
+      <c r="P9" s="9">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="G9" s="2">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="H9" s="2">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="I9" s="2">
-        <f t="shared" si="3"/>
-        <v>34</v>
-      </c>
-      <c r="J9" s="2">
-        <f t="shared" si="4"/>
-        <v>120</v>
-      </c>
-      <c r="K9" s="2">
-        <f t="shared" si="5"/>
-        <v>24</v>
-      </c>
-      <c r="L9" s="2">
-        <f t="shared" si="6"/>
-        <v>34</v>
-      </c>
-      <c r="M9" s="2">
-        <f t="shared" si="7"/>
-        <v>14</v>
-      </c>
-      <c r="N9" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>Fail</v>
-      </c>
-      <c r="O9" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>fail</v>
-      </c>
-      <c r="P9" s="9">
-        <f>RANK(K9,$K$2:$K$20,0)</f>
         <v>16</v>
       </c>
     </row>
@@ -3152,47 +7645,47 @@
         <v>84</v>
       </c>
       <c r="F10" s="2">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="3"/>
+        <v>74</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="4"/>
+        <v>94</v>
+      </c>
+      <c r="J10" s="2">
+        <f t="shared" si="5"/>
+        <v>420</v>
+      </c>
+      <c r="K10" s="2">
+        <f t="shared" si="6"/>
+        <v>84</v>
+      </c>
+      <c r="L10" s="2">
+        <f t="shared" si="7"/>
+        <v>94</v>
+      </c>
+      <c r="M10" s="2">
+        <f t="shared" si="8"/>
+        <v>74</v>
+      </c>
+      <c r="N10" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>A grade</v>
+      </c>
+      <c r="O10" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>pass</v>
+      </c>
+      <c r="P10" s="9">
         <f t="shared" si="0"/>
-        <v>79</v>
-      </c>
-      <c r="G10" s="2">
-        <f t="shared" si="1"/>
-        <v>89</v>
-      </c>
-      <c r="H10" s="2">
-        <f t="shared" si="2"/>
-        <v>74</v>
-      </c>
-      <c r="I10" s="2">
-        <f t="shared" si="3"/>
-        <v>94</v>
-      </c>
-      <c r="J10" s="2">
-        <f t="shared" si="4"/>
-        <v>420</v>
-      </c>
-      <c r="K10" s="2">
-        <f t="shared" si="5"/>
-        <v>84</v>
-      </c>
-      <c r="L10" s="2">
-        <f t="shared" si="6"/>
-        <v>94</v>
-      </c>
-      <c r="M10" s="2">
-        <f t="shared" si="7"/>
-        <v>74</v>
-      </c>
-      <c r="N10" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>A grade</v>
-      </c>
-      <c r="O10" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>pass</v>
-      </c>
-      <c r="P10" s="9">
-        <f>RANK(K10,$K$2:$K$20,0)</f>
         <v>4</v>
       </c>
     </row>
@@ -3213,47 +7706,47 @@
         <v>24</v>
       </c>
       <c r="F11" s="2">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J11" s="2">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+      <c r="K11" s="2">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="L11" s="2">
+        <f t="shared" si="7"/>
+        <v>34</v>
+      </c>
+      <c r="M11" s="2">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+      <c r="N11" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>Fail</v>
+      </c>
+      <c r="O11" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>fail</v>
+      </c>
+      <c r="P11" s="9">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="G11" s="2">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="H11" s="2">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="I11" s="2">
-        <f t="shared" si="3"/>
-        <v>34</v>
-      </c>
-      <c r="J11" s="2">
-        <f t="shared" si="4"/>
-        <v>120</v>
-      </c>
-      <c r="K11" s="2">
-        <f t="shared" si="5"/>
-        <v>24</v>
-      </c>
-      <c r="L11" s="2">
-        <f t="shared" si="6"/>
-        <v>34</v>
-      </c>
-      <c r="M11" s="2">
-        <f t="shared" si="7"/>
-        <v>14</v>
-      </c>
-      <c r="N11" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>Fail</v>
-      </c>
-      <c r="O11" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>fail</v>
-      </c>
-      <c r="P11" s="9">
-        <f>RANK(K11,$K$2:$K$20,0)</f>
         <v>16</v>
       </c>
     </row>
@@ -3274,47 +7767,47 @@
         <v>88</v>
       </c>
       <c r="F12" s="2">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" si="2"/>
+        <v>93</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="3"/>
+        <v>78</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" si="4"/>
+        <v>98</v>
+      </c>
+      <c r="J12" s="2">
+        <f t="shared" si="5"/>
+        <v>440</v>
+      </c>
+      <c r="K12" s="2">
+        <f t="shared" si="6"/>
+        <v>88</v>
+      </c>
+      <c r="L12" s="2">
+        <f t="shared" si="7"/>
+        <v>98</v>
+      </c>
+      <c r="M12" s="2">
+        <f t="shared" si="8"/>
+        <v>78</v>
+      </c>
+      <c r="N12" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>A grade</v>
+      </c>
+      <c r="O12" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>pass</v>
+      </c>
+      <c r="P12" s="9">
         <f t="shared" si="0"/>
-        <v>83</v>
-      </c>
-      <c r="G12" s="2">
-        <f t="shared" si="1"/>
-        <v>93</v>
-      </c>
-      <c r="H12" s="2">
-        <f t="shared" si="2"/>
-        <v>78</v>
-      </c>
-      <c r="I12" s="2">
-        <f t="shared" si="3"/>
-        <v>98</v>
-      </c>
-      <c r="J12" s="2">
-        <f t="shared" si="4"/>
-        <v>440</v>
-      </c>
-      <c r="K12" s="2">
-        <f t="shared" si="5"/>
-        <v>88</v>
-      </c>
-      <c r="L12" s="2">
-        <f t="shared" si="6"/>
-        <v>98</v>
-      </c>
-      <c r="M12" s="2">
-        <f t="shared" si="7"/>
-        <v>78</v>
-      </c>
-      <c r="N12" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>A grade</v>
-      </c>
-      <c r="O12" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>pass</v>
-      </c>
-      <c r="P12" s="9">
-        <f>RANK(K12,$K$2:$K$20,0)</f>
         <v>2</v>
       </c>
     </row>
@@ -3335,47 +7828,47 @@
         <v>58</v>
       </c>
       <c r="F13" s="2">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="G13" s="2">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="I13" s="2">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="J13" s="2">
+        <f t="shared" si="5"/>
+        <v>290</v>
+      </c>
+      <c r="K13" s="2">
+        <f t="shared" si="6"/>
+        <v>58</v>
+      </c>
+      <c r="L13" s="2">
+        <f t="shared" si="7"/>
+        <v>68</v>
+      </c>
+      <c r="M13" s="2">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="N13" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>C grade</v>
+      </c>
+      <c r="O13" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>pass</v>
+      </c>
+      <c r="P13" s="9">
         <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="G13" s="2">
-        <f t="shared" si="1"/>
-        <v>63</v>
-      </c>
-      <c r="H13" s="2">
-        <f t="shared" si="2"/>
-        <v>48</v>
-      </c>
-      <c r="I13" s="2">
-        <f t="shared" si="3"/>
-        <v>68</v>
-      </c>
-      <c r="J13" s="2">
-        <f t="shared" si="4"/>
-        <v>290</v>
-      </c>
-      <c r="K13" s="2">
-        <f t="shared" si="5"/>
-        <v>58</v>
-      </c>
-      <c r="L13" s="2">
-        <f t="shared" si="6"/>
-        <v>68</v>
-      </c>
-      <c r="M13" s="2">
-        <f t="shared" si="7"/>
-        <v>48</v>
-      </c>
-      <c r="N13" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>C grade</v>
-      </c>
-      <c r="O13" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>pass</v>
-      </c>
-      <c r="P13" s="9">
-        <f>RANK(K13,$K$2:$K$20,0)</f>
         <v>7</v>
       </c>
     </row>
@@ -3396,47 +7889,47 @@
         <v>56</v>
       </c>
       <c r="F14" s="2">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="G14" s="2">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="4"/>
+        <v>66</v>
+      </c>
+      <c r="J14" s="2">
+        <f t="shared" si="5"/>
+        <v>280</v>
+      </c>
+      <c r="K14" s="2">
+        <f t="shared" si="6"/>
+        <v>56</v>
+      </c>
+      <c r="L14" s="2">
+        <f t="shared" si="7"/>
+        <v>66</v>
+      </c>
+      <c r="M14" s="2">
+        <f t="shared" si="8"/>
+        <v>46</v>
+      </c>
+      <c r="N14" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>C grade</v>
+      </c>
+      <c r="O14" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>pass</v>
+      </c>
+      <c r="P14" s="9">
         <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-      <c r="G14" s="2">
-        <f t="shared" si="1"/>
-        <v>61</v>
-      </c>
-      <c r="H14" s="2">
-        <f t="shared" si="2"/>
-        <v>46</v>
-      </c>
-      <c r="I14" s="2">
-        <f t="shared" si="3"/>
-        <v>66</v>
-      </c>
-      <c r="J14" s="2">
-        <f t="shared" si="4"/>
-        <v>280</v>
-      </c>
-      <c r="K14" s="2">
-        <f t="shared" si="5"/>
-        <v>56</v>
-      </c>
-      <c r="L14" s="2">
-        <f t="shared" si="6"/>
-        <v>66</v>
-      </c>
-      <c r="M14" s="2">
-        <f t="shared" si="7"/>
-        <v>46</v>
-      </c>
-      <c r="N14" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>C grade</v>
-      </c>
-      <c r="O14" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>pass</v>
-      </c>
-      <c r="P14" s="9">
-        <f>RANK(K14,$K$2:$K$20,0)</f>
         <v>11</v>
       </c>
     </row>
@@ -3457,47 +7950,47 @@
         <v>68</v>
       </c>
       <c r="F15" s="2">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="G15" s="2">
+        <f t="shared" si="2"/>
+        <v>73</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="3"/>
+        <v>58</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="4"/>
+        <v>78</v>
+      </c>
+      <c r="J15" s="2">
+        <f t="shared" si="5"/>
+        <v>340</v>
+      </c>
+      <c r="K15" s="2">
+        <f t="shared" si="6"/>
+        <v>68</v>
+      </c>
+      <c r="L15" s="2">
+        <f t="shared" si="7"/>
+        <v>78</v>
+      </c>
+      <c r="M15" s="2">
+        <f t="shared" si="8"/>
+        <v>58</v>
+      </c>
+      <c r="N15" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>B grade</v>
+      </c>
+      <c r="O15" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>pass</v>
+      </c>
+      <c r="P15" s="9">
         <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-      <c r="G15" s="2">
-        <f t="shared" si="1"/>
-        <v>73</v>
-      </c>
-      <c r="H15" s="2">
-        <f t="shared" si="2"/>
-        <v>58</v>
-      </c>
-      <c r="I15" s="2">
-        <f t="shared" si="3"/>
-        <v>78</v>
-      </c>
-      <c r="J15" s="2">
-        <f t="shared" si="4"/>
-        <v>340</v>
-      </c>
-      <c r="K15" s="2">
-        <f t="shared" si="5"/>
-        <v>68</v>
-      </c>
-      <c r="L15" s="2">
-        <f t="shared" si="6"/>
-        <v>78</v>
-      </c>
-      <c r="M15" s="2">
-        <f t="shared" si="7"/>
-        <v>58</v>
-      </c>
-      <c r="N15" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>B grade</v>
-      </c>
-      <c r="O15" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>pass</v>
-      </c>
-      <c r="P15" s="9">
-        <f>RANK(K15,$K$2:$K$20,0)</f>
         <v>5</v>
       </c>
     </row>
@@ -3518,7 +8011,7 @@
         <v>55</v>
       </c>
       <c r="F16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="G16" s="2">
@@ -3526,39 +8019,39 @@
         <v>60</v>
       </c>
       <c r="H16" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="I16" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>65</v>
       </c>
       <c r="J16" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>275</v>
       </c>
       <c r="K16" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>55</v>
       </c>
       <c r="L16" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>65</v>
       </c>
       <c r="M16" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="N16" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>C grade</v>
       </c>
       <c r="O16" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>pass</v>
       </c>
       <c r="P16" s="9">
-        <f>RANK(K16,$K$2:$K$20,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
@@ -3579,47 +8072,47 @@
         <v>24</v>
       </c>
       <c r="F17" s="2">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="G17" s="2">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J17" s="2">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+      <c r="K17" s="2">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="L17" s="2">
+        <f t="shared" si="7"/>
+        <v>34</v>
+      </c>
+      <c r="M17" s="2">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+      <c r="N17" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>Fail</v>
+      </c>
+      <c r="O17" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>fail</v>
+      </c>
+      <c r="P17" s="9">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="G17" s="2">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="H17" s="2">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="I17" s="2">
-        <f t="shared" si="3"/>
-        <v>34</v>
-      </c>
-      <c r="J17" s="2">
-        <f t="shared" si="4"/>
-        <v>120</v>
-      </c>
-      <c r="K17" s="2">
-        <f t="shared" si="5"/>
-        <v>24</v>
-      </c>
-      <c r="L17" s="2">
-        <f t="shared" si="6"/>
-        <v>34</v>
-      </c>
-      <c r="M17" s="2">
-        <f t="shared" si="7"/>
-        <v>14</v>
-      </c>
-      <c r="N17" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>Fail</v>
-      </c>
-      <c r="O17" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>fail</v>
-      </c>
-      <c r="P17" s="9">
-        <f>RANK(K17,$K$2:$K$20,0)</f>
         <v>16</v>
       </c>
     </row>
@@ -3640,47 +8133,47 @@
         <v>58</v>
       </c>
       <c r="F18" s="2">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="G18" s="2">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="J18" s="2">
+        <f t="shared" si="5"/>
+        <v>290</v>
+      </c>
+      <c r="K18" s="2">
+        <f t="shared" si="6"/>
+        <v>58</v>
+      </c>
+      <c r="L18" s="2">
+        <f t="shared" si="7"/>
+        <v>68</v>
+      </c>
+      <c r="M18" s="2">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="N18" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v>C grade</v>
+      </c>
+      <c r="O18" s="2" t="str">
+        <f t="shared" si="10"/>
+        <v>pass</v>
+      </c>
+      <c r="P18" s="9">
         <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="G18" s="2">
-        <f t="shared" si="1"/>
-        <v>63</v>
-      </c>
-      <c r="H18" s="2">
-        <f t="shared" si="2"/>
-        <v>48</v>
-      </c>
-      <c r="I18" s="2">
-        <f t="shared" si="3"/>
-        <v>68</v>
-      </c>
-      <c r="J18" s="2">
-        <f t="shared" si="4"/>
-        <v>290</v>
-      </c>
-      <c r="K18" s="2">
-        <f t="shared" si="5"/>
-        <v>58</v>
-      </c>
-      <c r="L18" s="2">
-        <f t="shared" si="6"/>
-        <v>68</v>
-      </c>
-      <c r="M18" s="2">
-        <f t="shared" si="7"/>
-        <v>48</v>
-      </c>
-      <c r="N18" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>C grade</v>
-      </c>
-      <c r="O18" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>pass</v>
-      </c>
-      <c r="P18" s="9">
-        <f>RANK(K18,$K$2:$K$20,0)</f>
         <v>7</v>
       </c>
     </row>
@@ -3705,43 +8198,43 @@
         <v>49</v>
       </c>
       <c r="G19" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>59</v>
       </c>
       <c r="H19" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>44</v>
       </c>
       <c r="I19" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>64</v>
       </c>
       <c r="J19" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>270</v>
       </c>
       <c r="K19" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>54</v>
       </c>
       <c r="L19" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>64</v>
       </c>
       <c r="M19" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>44</v>
       </c>
       <c r="N19" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>C grade</v>
       </c>
       <c r="O19" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>pass</v>
       </c>
       <c r="P19" s="9">
-        <f>RANK(K19,$K$2:$K$20,0)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
@@ -3762,23 +8255,23 @@
         <v>58</v>
       </c>
       <c r="F20" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="G20" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>63</v>
       </c>
       <c r="H20" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
       <c r="I20" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>68</v>
       </c>
       <c r="J20" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>290</v>
       </c>
       <c r="K20" s="2">
@@ -3786,23 +8279,23 @@
         <v>58</v>
       </c>
       <c r="L20" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>68</v>
       </c>
       <c r="M20" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>48</v>
       </c>
       <c r="N20" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>C grade</v>
       </c>
       <c r="O20" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>pass</v>
       </c>
       <c r="P20" s="9">
-        <f>RANK(K20,$K$2:$K$20,0)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -3823,19 +8316,19 @@
         <v>87</v>
       </c>
       <c r="F21" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="G21" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>92</v>
       </c>
       <c r="H21" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>77</v>
       </c>
       <c r="I21" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>97</v>
       </c>
       <c r="J21" s="11">
@@ -3843,11 +8336,11 @@
         <v>435</v>
       </c>
       <c r="K21" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>87</v>
       </c>
       <c r="L21" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>97</v>
       </c>
       <c r="M21" s="11">
@@ -3855,15 +8348,15 @@
         <v>77</v>
       </c>
       <c r="N21" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>A grade</v>
       </c>
       <c r="O21" s="11" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>pass</v>
       </c>
       <c r="P21" s="12" t="e">
-        <f>RANK(K21,$K$2:$K$20,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -3882,12 +8375,6 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
-    <cfRule type="top10" dxfId="23" priority="3" rank="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P1:P23">
-    <cfRule type="top10" dxfId="22" priority="2" bottom="1" rank="10"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K2:K21">
     <cfRule type="iconSet" priority="1">
       <iconSet iconSet="3Symbols">
@@ -3896,6 +8383,12 @@
         <cfvo type="percent" val="67"/>
       </iconSet>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P1:P23">
+    <cfRule type="top10" dxfId="1" priority="2" bottom="1" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P21">
+    <cfRule type="top10" dxfId="0" priority="3" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4013,17 +8506,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2994953-FFE3-4C8D-AE6A-122C63BE2058}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="4"/>
     <col min="3" max="3" width="25.5703125" style="4" customWidth="1"/>
-    <col min="4" max="8" width="9.140625" style="4"/>
-    <col min="9" max="9" width="9.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="4"/>
+    <col min="4" max="7" width="9.140625" style="4"/>
+    <col min="8" max="8" width="13.140625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="4"/>
+    <col min="10" max="10" width="9.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>55</v>
       </c>
@@ -4043,14 +8538,17 @@
       <c r="G1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1000</v>
       </c>
@@ -4067,16 +8565,20 @@
         <v>2</v>
       </c>
       <c r="G2" s="4">
-        <v>52</v>
-      </c>
-      <c r="I2" s="13">
+        <v>60</v>
+      </c>
+      <c r="H2" s="4" t="str">
+        <f>IF(G2&gt;60,"extraordinary","average")</f>
+        <v>average</v>
+      </c>
+      <c r="J2" s="13">
         <v>46023</v>
       </c>
-      <c r="J2" s="4">
+      <c r="K2" s="4">
         <v>208.1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1001</v>
       </c>
@@ -4093,16 +8595,20 @@
         <v>36</v>
       </c>
       <c r="G3" s="4">
-        <v>79</v>
-      </c>
-      <c r="I3" s="13">
+        <v>80</v>
+      </c>
+      <c r="H3" s="4" t="str">
+        <f t="shared" ref="H3:H5" si="0">IF(G3&gt;60,"extraordinary","average")</f>
+        <v>extraordinary</v>
+      </c>
+      <c r="J3" s="13">
         <v>46054</v>
       </c>
-      <c r="J3" s="4">
+      <c r="K3" s="4">
         <v>208.3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1002</v>
       </c>
@@ -4119,16 +8625,20 @@
         <v>37</v>
       </c>
       <c r="G4" s="4">
-        <v>95</v>
-      </c>
-      <c r="I4" s="13">
+        <v>51</v>
+      </c>
+      <c r="H4" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>average</v>
+      </c>
+      <c r="J4" s="13">
         <v>46082</v>
       </c>
-      <c r="J4" s="4">
+      <c r="K4" s="4">
         <v>208.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1003</v>
       </c>
@@ -4145,42 +8655,71 @@
         <v>38</v>
       </c>
       <c r="G5" s="4">
-        <v>54</v>
-      </c>
-      <c r="I5" s="13">
+        <v>59</v>
+      </c>
+      <c r="H5" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>average</v>
+      </c>
+      <c r="J5" s="13">
         <v>46113</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E6"/>
       <c r="F6"/>
       <c r="G6"/>
-      <c r="I6" s="13">
+      <c r="J6" s="13">
         <v>46143</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E12" s="4">
         <f>B9+B11+B13</f>
         <v>600</v>
       </c>
+      <c r="G12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>300</v>
       </c>
+      <c r="G13" s="4">
+        <v>70</v>
+      </c>
+      <c r="H13" s="4">
+        <f>G13/J13</f>
+        <v>0.7</v>
+      </c>
+      <c r="J13" s="4">
+        <v>100</v>
+      </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G14" s="4">
+        <v>60</v>
+      </c>
+      <c r="H14" s="4" t="e">
+        <f>G14/J14</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E15" s="4">
         <f>600+100</f>
         <v>700</v>
@@ -4199,9 +8738,177 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0695BAEB-1CFB-4118-AB7D-51B52EBDE8A5}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="9">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="9">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="9">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="9">
+        <v>820000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="9">
+        <v>588100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="9">
+        <v>545222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="9">
+        <v>54820000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="12">
+        <v>5486555</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{3A4CF648-6AED-40f4-86FF-DC5316D8AED3}">
+      <x14:slicerList xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD3DE508-F655-476C-BEE4-DB9C4CE70159}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/practice_excel.xlsx
+++ b/practice_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4bff1f7f1b08cbf8/Documents/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="673" documentId="8_{13A36251-90CA-4812-B750-A4E5E3B4B7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20245839-6C5B-4916-B5F4-B2363672321F}"/>
+  <xr:revisionPtr revIDLastSave="799" documentId="8_{13A36251-90CA-4812-B750-A4E5E3B4B7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F9B8BC7-CD64-471D-A08A-A93D1DF1B6A8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="3" xr2:uid="{8833C839-1A56-48AD-BAD5-E70EFDA34D12}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" firstSheet="2" activeTab="8" xr2:uid="{8833C839-1A56-48AD-BAD5-E70EFDA34D12}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
+    <sheet name="consolidation data" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v5.0" hidden="1">Sheet5!$A$1</definedName>
@@ -34,7 +37,7 @@
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
       <x15:slicerCaches xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-        <x14:slicerCache r:id="rId7"/>
+        <x14:slicerCache r:id="rId10"/>
       </x15:slicerCaches>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -56,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="89">
   <si>
     <t>sr.no</t>
   </si>
@@ -295,44 +298,41 @@
     <t>population</t>
   </si>
   <si>
-    <t>order id</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>clothing</t>
-  </si>
-  <si>
-    <t>electronics</t>
-  </si>
-  <si>
-    <t>home care</t>
-  </si>
-  <si>
-    <t>grocery</t>
-  </si>
-  <si>
-    <t>personal care</t>
-  </si>
-  <si>
-    <t>payment mode</t>
-  </si>
-  <si>
-    <t>UPI</t>
-  </si>
-  <si>
     <t>remark</t>
   </si>
   <si>
     <t>dollar sign</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>quarter1</t>
+  </si>
+  <si>
+    <t>quarter2</t>
+  </si>
+  <si>
+    <t>quarter3</t>
+  </si>
+  <si>
+    <t>quarter4</t>
+  </si>
+  <si>
+    <t>Practice_Excel</t>
+  </si>
+  <si>
+    <t>consolidation data</t>
+  </si>
+  <si>
+    <t>from sheet 6,7 and 8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,8 +371,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,6 +396,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -510,7 +530,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -561,6 +581,8 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -662,9 +684,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1014,6 +1033,9 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1646,18 +1668,9 @@
             <c:strRef>
               <c:f>Sheet5!$A$2:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>punjab</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>rajasthan</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>up</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>mp</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1667,18 +1680,9 @@
               <c:f>Sheet5!$B$2:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>750000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>820000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>54820000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5486555</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1918,2590 +1922,87 @@
               <cx:v>population</cx:v>
             </cx:txData>
           </cx:tx>
+          <cx:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+          </cx:spPr>
           <cx:dataId val="0"/>
           <cx:layoutPr>
-            <cx:geography cultureLanguage="en-US" cultureRegion="IN" attribution="Powered by Bing">
+            <cx:geography viewedRegionType="dataOnly" cultureLanguage="en-US" cultureRegion="IN" attribution="Powered by Bing">
               <cx:geoCache provider="{E9337A44-BEBE-4D9F-B70C-5C5E7DAFC167}">
-                <cx:binary>1Htbc9y2su5fSfl508GFuK1aWQ/gcEaSJUuW735hybIMEgQJkiB4+/W7FTuJPCt2dnT2ObWOKyl7
-yCHQ7EZ3f/11zz9vl3/curub4aelcW34x+3yy5NyHLt//PxzuC3vmpvwtKluBx/85/HprW9+9p8/
-V7d3P38abuaqNT8ThNOfb8ubYbxbnvzrn7CaufPn/vZmrHz7It4N6/VdiG4MP7j3p7d+uvnUVO2u
-CuNQ3Y74lyddbO3Nxyc/3bVjNa6v1u7ulyfffOfJTz8fr/Rvu/7kQLAxfoJnKXoqUyKVSMmTn5xv
-zdfrgj1NMUsFVVT9+kf+tufzmwaeu/pLOX6V4ubTp+EuBHiNX//+47lvZIbL+slPtz62472mDCjt
-lyen7afq5slPVfDZlxuZvxf49Pmvb/jztzr+1z+PLsA7H115YIZjBf3Vre+I9tAG3wj/N21AyFPK
-iBToN12rb02hnlJOU4wUQ7/+AUt92fqLKb4q6vvS/Lklvj72jeD/WVr/5ozA2R9u7E0Yy5v2t/f/
-Pz/+hD9lMmWcY/K7bh96AQXvUApxhb94Aftt6y+qv/6fSPTn6n/w6Dfv+cuT67P/aF/4RlqwStP9
-ppP/BXPQp4xKLBiTX8yBv/UE+ZRIqTilX81Bf9v6izkubj6V681PV8PNp7tQ/nbvz8T6c5scP//N
-q/7y5OLq/yvDxP9Nw/CnilDGMf5iF/StYSR6Cj50H8S+Zosjw7weR8itj7bL0eNHZnn9/9gs388r
-vyfa3c14k/+aoR+klh/f/S0nHT36o0T/JeKffvrliUgxRYQjsBGHfxBKxYMcdL/kNxnj/ObTTf27
-f3x3gTuItr88AdtSIjnlmKuUUqbSJz/Nd/d3BAFvxYhzqVL4B4Hg2PphLAFViKdICMkQpC2huBRw
-K/j46y1IdlRISGcUsAUDiPE7YLrybjW+/V1PXz//1MbmylftGEAYBjik+/K9e7kTglORCgT/w/Xb
-m2tAY/A1/F+pG32N67E8cbNo9hGE59p2s1GZ7Jp+0lS12zORtPIQ6RDO0MjEmSeyjHrio30+d1sy
-6laurNmJxQ1vWFLE50HJ9U1nG5VmbSXbbj/UTe10NffquulseCFqlC6ZsI1EmorNV73ujEmGrJtw
-kQeKCq+D7Yn5OMkp6U4n79OLQBg9cwueb6ZibT92Zc1CPqS2O/imHRq9sUqZzE2Bo5N55fzDsNbG
-a+rVsh5WNCKkiXNTfxp8UiRZv5ap3cUO2/7MSl69WDrBTGa3oX/FRGxeRimWHa/jVGTLOvD3ZK2b
-q2XBa5ItE6mnbLCbc3uy9iXXlJXofW/XmmpFk6HKVD2K66WtJq+ZpdOtZclypmyTnuFozDVLWJv3
-siIvCbPxLSoGdtUkZXMtmpofkjFVJ6nrtsOEljYvEi6K84lxuls963Nq+LIjfE7kfopDE7UhsbxV
-8wJ2TFwoVe4In6Ju6nl71iWcfp6LaXmJerPdVXPTTLowXf9+I3V6qeJqcV4GWwxZk1rzWqRuWnSM
-zXhVdgo9X61dZq2WbmM6mnU61K4yi7Zmml8LzJM3vapKp/ks0GsZcblqxfu1zqvEoSvJS/LR4rk/
-DJvsM0zG2ugFmXDVtDzx2ndtI/KmK9QzS+vx3Lbl0OueDu2JsH0VTtOmV4OucTt+aNI6GXYsjeHO
-NMXyik1+nnVIxwJrOSYyE0WUF74beMjAP5zbjSolh7q3QV0yFV2fj6ttl4ypKS31mjhfXcybWCrd
-rL1Pczu1Cd036SbuWkuLdFe6nhVZZ9tuy3lPHM4S1VivRzZ0H7bUle8Q6bzmTbW0lw1b2KTBa9YA
-ynDNfMJaEccMFLvErEqbCvQ3RZCTwkbLrmJrec1w2Q+gfW7eNYEWnyvbifVscKS4qws+nkjbR3zb
-uQk1uhw4ng60KTY4Ugsb/V4MtPRXkyP4PKqyLXThnDwt5zncRl4ueTJAHbRDVQOfAwnJOU4qX+dT
-jOpD6rfNXo3lxKNOl4Kd2nltXvejST+tbKveL6YupB5UIbpdWzUuw8izvUVJnWYpbufTrhSl16Xl
-Aukq4TzdkbZ3MkO+HnE2KRP3q0Jrp8ttlXdqGjjZ1UHhXArHrJ6WUbxAsQinE5/CpF0Tl5eJU+Gj
-Glh4a22JnqfLtu1ZDKPfNeXCpe4GNb1IkjS8nQfG9MBm/2zbcL+fnEA8X6TtuK6mYsobosZKJ75M
-c9K1DnTReFPpzU7d27UJ9bMW16zMueWBaluk/rQdzUI0LuimGZzKWTs0+1KXbGJ6soLnPPjpVm1u
-6TW2UahsXLfxwtVuveZqK+XeF74rcsfW5dCbhB1w59Cp6Oq51QTM+H5Q9fZpTILhORnReoGaMbmI
-ojQXKrC61MSn4npuuurlNCWx0W7i+BTNfDtJQzFcV3KeLoMhfNRkbpOdgXrvnfelyKdtLvehKIpX
-Y4SQk9HGbHtbz27VTHVVnowottmWSvuhrWZ/ad3A8tAbpa1altNYDNunuFIvs7UsPT7UtadC82kF
-28e6K6lOZ9O973xXvxfYkPlMUUx9xhYxaIjh42uwzjJptBp8SZs5ZJMb+/UsYcsc9CwDVQcvrd8V
-VRLrDAU6d3BWrf/oGOWvxjTCIexRVESbubcfsE+7d6yfZ6X7fvBOk5iObJ/yjZSZr23d6lEMW3Ug
-HereBIttfU2kb0YwCYWgY1Da72jSIvKstCuadxOof8tFNSaL5t06LSfEzTQ9HdAa6GXXd8OF2aqi
-0nOr1nonDFHPh164j0tpys9lMvhdF1D1ypAhOK0chXQjXC0Pti9smTnjRV6suOsy04rqJG1RNLvE
-98tZOvVLqelauLM4T3zL2OSakDk/+ufIkinssAlmN8liuZq7nm67ZE3qw9SU6BSPRdxNIro0WxrM
-ln1PqT2nA05YRvxIT1BHy8O0XA5x2YwugXfp9BCm7Xy1XZfHpmmZRn2K6qznjf0o+rrNkaPP5qWa
-o7YuwlMeJHzReRHeUifnszEBxJGZdWSlDjWarPYzqnZmFP4M3Ib5t0299lanYzgRXB7G4DauV+ze
-OzmoZyNvAD/UvUp12Sp3VtIZG3CXoa+BnSkY0hB2WohDLDkM+JrK5QXBXmmJpu2Tg2wAiboaX7nW
-yWdm80u2NoXM0jaM120Rp88pJJ8DNSM9o4rfiGHmuy0qd7LN1JyQMYTXdGH0RNZMgOs65/QocXrX
-V6qYMu8mdRUxpvvazXHJNiG7M1yMTc7XKp4UCm+9plU1DLu5ssv5RvvxvDUe7dRU1BeOQSDP7dz2
-ncaL8WuWSpxEPXJc1Fk5JfgQ7Kqs3qq+Pt2AkbkmNnVnCxy1cylH+2xTVfosllH2uupieKfgnO0C
-a+UtXwvSat6m/WXaOHndNkic2HFscZZ2RaHJkpBPCg7Mrgi4fdFbVevebVWaN7VJTxAbu9eoRdVh
-jmB+r/ryXVPWotEzqbegK26QxsKK522t+C2uRobyQc0+48PYfRgHxbJt7MdXPQnhdjG4u+IjXy7a
-wa4ym2trngcWRE69KA8zQ1XQievoCJiLiA/NRu2a+eiW1zyt0kGzuTF3RdmXl02R0HMbO9FkrgEv
-1HM3YkigPsb3U7qKXEy9fJmkdEIQAArzXqC67LWppuVDwsvkQx3TodJ2tMubTll+KGUnLoFpoGdq
-mevPIO9wJUxYP6otVl5v3RoAnlWD6/Q0yPGVWuem1zbMzO6oqSTRnK3rC2kGuRcrm99sKed70bfN
-jSIcoEYX6tnoMRTzqIthbIeM9NQcwFTzOTZmhOhQFcOLaqC8B/jCa6vHzUGkIn4ZXd7FcqjOhE2i
-P8RxGIrTbhiR2Um1cLd3uMTPQ9elb4mYJ6NJQPW6r6ZmwnoZpKG6IoN8VhmxNZlPlzDuplkNZSY3
-tNEskp6rrFjn4f08VoPdDVWJfFZtrrioOKF+x0ZensIJUVvmSTXemFJAUpuZxNf1JED/QcZ01qax
-8YQAifsmTcv+uutdqPUA9dC1XVO1m/BksoQg8awKTF7iJaK7CvfSaTgFLckh77YQAEl0s67lwF6u
-LlZlXq0ACfQ8hLLNTbV11Q4nUMJcSdZMxX6eWHoiHPF+V9dpJyG9tZLuPKSK6YJUoSs0WMGYbFFe
-HDge5bVzpOt3m5rlpr1y6WfbJIrtWpXg14ol600lE/RJShfjiZ83yOT1MIwRwKptW93HfukyZ22X
-O+DDsjJ15jMxvroet85mq+pwtQeMuTU6lVW+CT+8iLINu0EMEKLaIPl+BdRmd+mCSa5KKSFOxVpq
-zkNxo+aeXKMWIEYOqFcl2dAo5vKl40sN+Noln11sNsBocThVG7y43qbe75OiXfJBUHCTFPLyDk52
-xHlvkb+hqu/IlZ2My4uJLxo+LVceuW7N2s7PRKNuKEoNp4pkRdOXV4Wr01NaS3NZo6YZ9MqDwFAB
-kX7TA53llAlY0ry2VQoy4YF2b7pZyLDrVeE+e1eR64G6tQaoU/OdK/q4S2yy7URcwMjDkpyMdBhz
-XtDOZAUCBKhXM6CdaccxjxuCs9hVNdMMme6mdMnwrF42AgAfb9tJMmL1eU1FsR6KpBHLBbZV8mpK
-JlhFloGdGiFrKMmg5iSHkcbizMOZvl2dAtC8pdhcQ+bujKakUs9k4dvTbkR1p5fF0wNKQsymXti9
-gBySm4H0OSdlvejWiu00taXVCRIxVz6ZdFxDvACh07OUEvQOcECfq1q1+xpXNAGncV6LudgKrabe
-ZVaYarfYOl77NCZBN9T5oIve9brtUfVCoM3luFOl0Uwq9gw1BOAUq4uc8OIj4FR1QOCTOVTyIQde
-1HwgQzN+XBFiVCcVLnZmJfUHE7x4YTYcFg3VgT2bfeIOW9I02WrG5dWyFFdrOeL3GLnyBasG8Euy
-iFYXnC1nsp/mk7Rz5hnnXQ1659WZLJ0qs0VU7OBrRN72wyYgRlWe3yP0hu5LhCqjRZp2jR6NBTRb
-V+gjgxBzUgEszWtwnHAxty7CIaJQHA9TA9g1qey4M3Rzp95HANGoqfwrbwDxAoTjV5wv6ct08/RU
-8JBc+cBoPnMfVm0sn171SWdmDZGXnHIjZS6WqXwFrle8LznZILQVsYPwaCqILnFSlXYtap63a1ee
-0aLkV1NK+KB7KddKU47qC5bQeFJWJX1ekW2RumitvRxcb9YdQ02yK1EUp0Vj1rAroh1frsRVr6OL
-05VKDLsF38VXuBzUXR/KsB+ULRrNyVomOplT/JaMHlA9ru0p67m9EAiNi0YTcBnNCPGqipGMOsrG
-nro2lrvYNs2hkH2ja5Usp6Tj3a5w6fIscfCytYBFdJG0PUBW43nOHI1vB0h1JezWuz1CGNZEo3tZ
-ECdfjWVMar3GjgTdlTPf97XtspKS5cL7BOPsHrmwLBVl+wo32O55Otkrn5LPAopByMp9HcJuicl4
-vqaLeHOfPvOprmV77ZZ0fsMhKYMtt97LfZz8+KlOlzX7LyjOXVe01J3QlQGiccOy7BC3PuptLdnl
-Bikl7pyyKGS/MmZfyb1vqKhb361DZcqv7bvfP/7rlW/gv18bTX9cvO/+/fHpcOfvuelw/KX7fX7/
-1h/Nqnuq7vfO1REV+KWF+B2e8Ic3/2ckIkaYEGj4/Yg5vLgz5Y27WaEx9wf7+MeDXxhDRZ4KhoCK
-ZBgTilIOS35hDKV6KjEwxRwrKb7e+UoZQicGcdhdKQFko+DqD8qQsKeIIIYVYZwpIBT/FmVI7rnQ
-B5ShkIijVFKGgJhMYbH0nlJ8QB3Gohwhswt+MqghBfTd15CzJN2WQWOghD4ttXNngCKX7hSqvPgy
-xas0OZ+x3fZGFfR1b20DZTfn9Q5wFJBOTZXMRcbmcekPQIbR1yoIelHMM7pskoSNV5S1nGZiURJI
-izS16iR4L+sDWmXfnaPEL6draNqMMVOaXBajeRWYKJCeEjdmMeLklcKxfyajiO+6dHGQLqTKIcJC
-idTKa7QN1W6iQHqtftKq7sBt6zANtxD7uzmzNDR9Bi9rzhGQSqMeUrydszJ0bjenJVRM0clDurnm
-RAAvd9mTipwUTC47wzZ6slZrdULSXmVtsi4ma9zKX8wlVa+kV/Iw43q+6KRTmV2BogPaF+VQaHba
-RdVmpOQZgVjYvZm8nON14YGv1D0UGVglHYD0rlqbHKhZis4JKSpzNrfz9KKfHF+hKvWpOe+r0c4Q
-q6aJ6mV2ptaq7RezC7hYup1JaCv16u047Q1eIXxDuZTgFxtmar0cjOTtC5yixOgN9cVwUtsE0G3Z
-SbydRjRye1ZAIgFAZws85TFytu3pVLp3wE/17IVshpHs8SYBRbmSpHVGIqlXTbcwxX3Bw3QQIyo/
-Id8ZkTVdow7tEPEbVgAA3hlkzN7b8Fmp5VmEyHlFWknO/bB2taYoOUkWOb0TfFh0iYqreWm55v08
-ApJfGnVBh3kHHF/1Alc12nPkGu1dYQFiMTQfAtSXn2gziRNPkrI6VNNW4Z3zqN/VvJPABtsi0avw
-fN011ShfOpys53NRbVm6VOx+7MC9HKEs3kWqgB7wbXmoDfVnSLTNLgnK5KiSZ3FYVb5ueHtVtBXe
-AxhkZ5xbChxacqhajC6NjFntQ3i5prbKSszDZWIwQGcoSSBj05jq1AGrre9Zn0b3wO+ag09md84E
-kTtYa9itjWvOhz7FAPhsWr2C0xqfeUSxzRDx66xXVdnT1dRAwXjgFxrAX9p1Jp4CoVtfKllM70ew
-baGNLzAwqWRZjV7nZUF6S+Z5Nwxlq5tGvFmqqnnRr/7gZ+vyXqHtTWOn6hMjyZwPUnQvm2jCQZTR
-gt7teuDW9O+FGtNTl2zxohvXO6gDAYt0K2lyuRTjSZ1YyGmDSOp3XTLzl7NfcZ1hKGU/dOuIQ44a
-np7Obkr2y7LEXUU6mvOExJxBdblH/dAfNiXmbFiYyxpM671bLMrSwbgTp5Iz4Nw4RJhmueAMxXcF
-CjPVwbgro2h/FoDrPYPGgLo0tC9u0nkqxv87Ce/itzmZ44z3MOH96z8vLd4+nD75JrthaGb+PlPz
-b720b6Yv7ltSQMPA47+2zpSAIRosoMtFoRiHRtjviZDLp1hBRpOIKSQJnOKj3hkkOg5jB1/7beFL
-74w/FZC6KOROAh0/rhT5O70z6Ns9SINfO2eM3Sfah+kvFEvh60rxkxLvFLsME8wj/P7+X4HRw57c
-99a9v/4grSpSTTy4ReRAwblSb9u6vi0JX74M9HyZ5/kby4OWHy5vwbXAmVuRQ6NlGK6BXUbmlVk2
-//nH4vPvqAWmbB6ur5qtlhF6FznAkLC96HCjkC6pZVijFColnQKrVux/vNn3dAXmf7gZdPq4nU0L
-zH+gkkJ1Ts2g/crlhx+v/y3U+cPG6Nv1oXpGnVUrhwq/Sy8wntPm5Yws4uerHNvlkIgNahPILN31
-jzf8zgtJOOkPX6iTqJvE/YaTU2I582UsYpaGWFb5jze4X+jf+r0wH3IE2mS1zWiMlOVzHcR8xlda
-kKyrAynPoQVhyQWONVD0fejbVWjkUmiuoLachpMf7/+d48GP9m/UBExcNOLQuNAX0O1s+viG9ptC
-QD2XSryA1jblpz/eDN/b6c/e9qi7DbQjUNZhZTm0XKc+k0QeBMWfu5r2MxCoZp4aIAdEcu5ng+s8
-AjklW50YSZrzH4vwPYPe6+GBNzsDUM6xGfQtCcvo4D8LNld/oczvLX4UgjyEhVkCVZ+vaxDvkF+9
-LqZoLx8n+v2uD0WXtoLmGHSKauDE7xB0F87bpKrjl4T4dwORPApEAFtY15eM5W4U0xtoEad6KTbx
-uDAnj8LQ4GZogQDuzEefbFuOlmQadrzzXjxS/KPQQ4Akl6uzEHqAJAI28Z4FgW4V+O3uUernR7HH
-AcGM18WKw5B088GMOHXaUGk+PWp5ebQ8sWvS+tAlh9avgl+FKpTjm2Yck8+PWl8cRbIATCmaFyYP
-m8dNvpo0GfRS1WH4C/3fn/E/cW1xFEiUr1MXyVoA/pVbs58H3E25m1dc7fqqTNUjtzmKIDT1hZy7
-RBzGEXifk5b7FuVbi6Gj3FXjvDzOk8VRmOj91Bd0aeShg37Nq3pYy8sWivtXP7bF93R1FCfmepF4
-Bgh1IMlSARkO9PO5SVffv62ZrJe/UNV9XPgzi9xffxAvSmm6GlC/PAwuXU+TZkOXyuDB6R+/xPeW
-p98u74tqRaAcfoiiJ8DI2SV9zzff5Y9b/ihgxEn4e8qDHyYHFhidaXIgf0X3SOmPwkWsaLu61QI7
-EKYabLDKJdEBrdX2yA2O/BnIR9bDkI48KNz0wJVj1kIVBmT4fPUoBd2D8IfmFWSlAScLP6hQVm+g
-ixCulsr06+Pk50eOJtaBKiDIxaGj6VidjBtdlC7rZkaPczF+5GJLtfZ8JIM41MF06WloyCS1vW8v
-/sUG95HnT84/P/Ky1ViDmhlM3BdrN+ysoULATNc28TMzFk2dL4as7TvXSPohtmZuH4ly+JHjucUU
-wm8zhEIHNO5ZmYQC+nBbrQA1ynG2KUzojXabsqrkXbOHHo0RO57O1L+cgLiJf/H+33FQfuSga8Gh
-21cnxaERSdzRahYHGPWhf3E+8L2n/Jl6ybfnj03jUvWkVwcKLJ3PN1xMY86KbXMnnaJivTSh8Z+7
-JJ2bk3STLXu+UEraCyKktO9kTWBg6HGecOTLsrUM2nFVeuhEEWjGN3XXLcvcPy6OsiNHi3jg0lqT
-Hky3yPcM0s/zgJLmcXHu10HQB1EaetmtTRKhDsxBJZNFLJtNx2pYw18cg++4ATty5FD1KyPQzD6M
-61yQU5kOA/q4dBhcoiTQrtZtdc/5kI135rZrtkAeqbcjB6fQtwIrD/zAZQEzkR3MBjTQSkmTR4ZY
-duTgW7rVfQRyKo89wzAzMpndxn2ye9SpYkdezAuFWtsv2yFEMx62VljNh87+RZD4jnOyI+fkGJXJ
-AnXWwZKqyciI7a5YPXnkoTryTShEvMSV3w4E6kaNSvy2NelfIb3viX7kbph3LTD1ZjsYsY4XcYUx
-l9z1JRCaj1P8UeYsbRw7OqzbISkadUqmpd4VVKaHR62eHnkz7SbWATe8HcaCpNlMRdChwdXjZD/u
-wciWbBLmOkD2EUbjahonzWuRPi7QHQ+Hw7DngOYibIceV24fVGsyGOLY9j/WzL3b/ElAT4/8tS1Y
-CbObyXyYE3YHlWA97dOxhhGwcRb8kW9w5LJ0ElNr62I+UHDcazV6m+PU14+rkNMjlx1bwCrzxueD
-h99GncIoQNzZtX1kuEmPXBaPjSvkZuPBBJc+q1wjLrrFPVL0I4+FTFrUNabjob/v12QDIyET5VKX
-ux8b9ztOmx45LStMqJMNmJeurZazejTjeSwK90inOnJZ4EeTCUNvfz9EM4eXdEbSXbIBps0fd27u
-u7kPwS7MhUy9gXELwGxxy+qOvV/V2v7Fwf+Obuh95nyQgpmFGWoJfZa8dyXWNESie6XiI0U/yr+0
-sykprJxA88n7gQAAa9VSPM6s9Mhn624bkiTwr6KnpCea3U+QP+rQ0GNvZTALIkvoHqoZSGNyv3p4
-vGLuzfFA7TDM2hUuwOqLhTGZKOsIg1zEPlL2I28tUyY9tN9h9ZTAvGnq9gbG+B4X5ik5Eh0m9WRl
-YHGYcmwOTsCcYgnd9sdhg/smykPFLCMVBUyBTTkbixmGtyYYg+9+a3z9XZ6PHvlqU3ak9RTFvJ22
-Vs9ldRfthh+ndXLkp2GD8VVfzhHGYMtU85S9T6ZAHrn4kZ+igg0UxoLGXPSo3YWlugkRhmkfddbJ
-kZv24X5IEYaJcstVqbmF8ac4EPHI1Y/8VFCbmCpRILqK+CJAe+SqEMY9rkV1/4u1bw5MTEkLIyHx
-sGH4sb/eWsnZLoGf4HydDvq7Z4YcuSrpF9XEzkyHNYWfdumEduzQzWS8fZzu/5uzK+uWE+Xav8i1
-FBD1VqvKU2dKTnIy3riSdLc44IAg4q//nuqrjm+68y1ue+BQyN5sNs9wiFVgz4gaN4mTtVp6kLKW
-6LR0rTv7jU5+Xh2jqonWgFGVOqNfo5a8LIy++A19jNTFtdK5QJeNCJ6RHr84knj218ghTjO85ifR
-kOiytSI9GRG/jl01+iWw6BCnQ7cECqAdUwaNboDJTR4TMod+mz06xCmehe20bGlwBs/nj8YBwhfL
-B68Fjw5RmjYWRJ42cCWGXQB3Jwu4fuCM1H6pNzrE6VrHRnRM6RKArvAzA4qmyZdmj/wqjegQqGbu
-SdhXoynlqPbTuCXfRQOctd/aHIK0Sps5WRtlytgpV0jwlsAY+d3L622QX1wObmCAf6aYbACTYAqk
-LsGUzZ7SpY6e+qCaPvlN/RCiRBOtIBWC7SgAxARj6XOSNp6f9BCjOxuBKBWdKVUMnFWUbl/6OX3r
-N+9DjDLLNttQjB20yysz7ilmy5PX0OEhQkdbVaDV1PocVkFQBG312OyhZ38gPERoBGZUsgckOIN7
-/Ua65EuqXO+XWsJDiAYCdboasSa9GF7GerxUUvhl8vAQnWyyjm5oep/Hfb1Tljyw2O8EDQ+BOTkQ
-NcYJdzsu68d03IB1q/xePsNDWDa93sQN6Xie5Id9NUCzf/TbIYeQBPpXTXuHj8hE911t2Uu6c788
-FR7i0cxrtznLdelA5nvdnSZla+hy8pv4ISLpUG1D22S6XAK87pOhu8uq7LPf2IeIBB0NANMoDM5x
-g+o2CPk3BtymV4YFU+DnJIiNPc99iCNZNIDWxgsLTsD9rl6Bw7JDUKbLmmgWr8F55u9BcEzxvuyz
-Jgw4459yNyiTM5uF06VJga+wdAFfbuavfoMfYtICPOLcUC3nSEx3tsdz+0xBT/Ab/BCWypiwC3oM
-nvbxW2qmHw1zynNVDnEJ7QcXzmkGyQJJ38YYezOr79iH0Ixsk1C6RWgbA0j+aNK6vZ/Zxj1X5RCd
-YmFrj3oWGyUG13MP2w89F14FFssOsblloKOBkqjLjToNiCqr+HgiqIAar9TCskOATlayCigKXdZs
-+hbY9RMeHz547ZYjWGulNFScYl2MqePTbDoQVFKSeNURaAj9HEVKrAn60Rsmvm1vzRjeb+Am+e3F
-9BChrUxCUEjoUqYdfeoBOAQpPyF+K54eItTUCphLs+oynPoXFoBPpYRXkcLSY3zGweBqKpeSkJgU
-VkaqiFj7l9/nPASow4vCkkq9AAHAv9TLdt8k8Xu/oQ/xuSlddSkJVAmiNIQFxmS+DBK8RL/RD/E5
-go0JRQuMjiek/TTs43NCAd/3G/wQoDcmUiciq8oR+JQbRUsFD+DwuXd+wx/C0wYUWRGSHiVZ3R8g
-jr5sS/rda+gjAknj4BETeGhlx+t32zRdwZH024dH8NFapR1ve6ZKUDrFebU1OQX98MNv3ofgbHZW
-LWrrljITU9Ex9yzT35Wdtzj531sVO8KMbIB+8DolqhRyBc9LJSC4zXzactsS4wq/+R+CNO6GbejG
-WJV9Q7/2gn0Kpu7Vb+hDiG4AIfaQwlGI/3W5WxcV5dHK/J7qINr4c8atiQDLkhJMHDRAuQYDGLrT
-R7+ZH2JUbPPUqVAsZUwaZs87NY5BN6kXnd8hnRzilIka7JG0x5bcgpdGktdm9ruLQybq53Xpm3jG
-hRlDVy570WHzpqLc6xnqb4rbP6/5fepAZF6dKmklSRmkRL9EtW28wLfsCDYmyRrGa4OdWIW7yx24
-IZR5IrrYEbAktyrQ2yJUOaxTCIJocplt7dcdBuvh5yXXihnDMiw50uPD6shDH29+MXSEKWW27k07
-16pMqnrIk909ZJAR8DstjlCkDLsk3Einymhc39JoflSh9pz3ITpVg9cJSF7N5cLTT02kXvpu9rrE
-MX4IzmpjUNGYWlVyrEyeAReez06mfvmQHyJT03YOWkhy4N1GgD1IuhcTZB+80soRJByGuGcNcTiX
-dUNlm1s0Ks4mDLjfwhyhSG2bATbWOsRN5mSRGs7f9U24+33RIxRpbWNeAQx3Y2xB0SBa2DNOUr/X
-c3aEIRlI1o3xNmK7jBkUcG4add0i8jRbO68eDl74f45R4GfDrN4GrH0tbFIMaJ6VVcVmv3cEdoQb
-uc6YVMlqKtNg6eZitZP8y4Db5nlpPAKOIklCZsEdLZUAVV7WvAXXVcQXr515BBwlybZB1CecStNz
-UoQcwG+K269fnokPEat7YOMXOkzgbia1ziNI2X3r3DbUnuMfYhYCMlzZDWszCui9NVp+2PrI78yL
-j8cpGa0MEoN1H9Lpzi3hcrH9KO681v2IN1rpSt3U26lsq3j/FI5Vfcegc9T5LcwRcESRJ2Pi8Fmz
-oZqXS2JSyvK4GiGG4zf/Q/WLx7huHKYVK08Xe1Uq/SDm3q83z46Qo6STUNDRaioTpt839fJiO/3e
-b96HqreGKg/t+3oukyH7Oow2ygVjvwO/MqSUX9TtR6DRjJZ5CkW4qaSqTb8meFS4M51cPbfM4WTV
-YbC5ncZjiUjNcg7oSw4RsuTstzCHUFUuwBt9j9Hj1Zk8jqb7bvgdiunvEvRXC3OI07nZAK9LyViu
-vKurHK/FLZJN0mxdUcus7u7k5Ox7I5f+Shca8FILMcevoLgl81uWxYt6nyWSg3fc6PEOwnKMQ9it
-QTO+3uY0tPnO2ll9gNRPYIrQzUP3bRQimAuOwpKcIMomzDmZDKjIfYQuWcHxSg1FvTlI25Ikm2DX
-aoSyItQT0U34HADZ6y4RbZfkRJMNY9q+0ZBDmDOxgG1HdnORhGz7aVklHb5u0Gqp3mrGg/b7EsXz
-XKY7ydZSbfi9p0nv8bkN1zgthoSAJ81dUpu7Ohrr7JGnA6ha4bxDYTTNbL5CReU6NYvayxBqA+5i
-Zb+y0wp+eHxeE8vQwu7Fyoq6n+SIejbLXJGqBkKAcmxU9GCHqs2uPY00K3esti1i2q3XHYo1z2pY
-Q3Zi4bruEFNU1Q6KfDsmflXIEf0yDw3U5/ZsLDM02/KYtI9ir/1YK+wIfgnx02KWTmPpIN4oT2No
-23KDyo9n9ccO2V5uEDfsDB1LHosRLasgJzXN/JLlEaZGWeVQBfdTKbj8s2Ld+yppPBc9/bm6gSrX
-tvWQFCtjU5ULpPyqOPLrbP4tLPIPIFa8AlYTof1VEqg5QBwngxBFD1U4r3xzhKipsKa8w4tjWZO2
-zbdu/ou3yq9iPQLUWnBz1yEJIe0GiZ5n0L+au5Fq6ZeH6S37/2NdBG8g00n4UtaqY49QN2nBKzD6
-i9+6HLK8kvW6rtM6ltALMx9VOu94iRhS7bnsh30eQdJiDyg+Kq+hhHsmy2D2PAnibj55zf8I9dJy
-tlUg9FjioeovO7H7OFj8KBcw8vh55Sdj1TpD4KMUYQYcmV6gZV3QrCV/+c39UNSs8bzT1ZCp7Ods
-T/NknCne2CGJ5YfFgCLWzz/AQuI2CrcaBQIsVnKT2PbcNI1ngXDEe03QRmv3Gkc43mhUAUQZL6DO
-EZZ+i3PY9jYEezluhhFMVAgGcbrGGtotivvh+xk5bPylHSBlPI7IZINJ7sVAw6+40zq/VjA5lDfJ
-JuddLqhX0crarhWrTJmEOvHc9If6hlBo/zS3BN82si4WO9e50VL6xewR8hUpKDtuuCeXgRvonwJo
-8z93CeHvwuvDHkFfMaEDdPi6qYx5sgZXCO5FRQg1p/g3b4f/Qu9nR+AX+KBVxft0KPc+oup16qC2
-XlTJQKaThcj7Kxhhz0GQ9VBwbOcuK2qIgPOLCOJ49Pv6R3wYiLQ8NC3qTwsV+LQIZAsBCimGqfe7
-Rh8BYjykO+4st8xU6ah6kE0NRribnQ49P9Lh3rKHRoGSSoYSbiFNB12o1jIo+LLVs0aJDuHNoa+p
-BoI/4AwBbHk3n4De/+G3ww6h3WvpdGb2oZzUsBRbTf/adew78UNk1zOkGRdo6EKDn1160t0Tsvi1
-AP7mOP7jpIeYWVhbKIiUmq1L0QUMTw12f+e3KIeTWIte1ZFdh7IyKj0bAUFOGTeeR+URJ2YTuE4N
-+KJlA33Q77K19IcKcNx4zf0IFFtaBqWyIZIlypXnZN0fIOv4Gy2X2377xVXxiBOrN7wzcjUO5bIR
-cR/1KoXM8Gj9DrEjVMx2vEnXjsoScqxjnbdpOt+LxAzCL0yPgDGWQfWUQxizTOKhLeYsvetY5PzO
-gSNkTE1DXVdZM5QZE/ZxUZIViW7Xl//+prdM8quFPwRpZju32gjne7+zGVVzuNQwqAijcTxzXIwG
-rxqLHvWYIMhRVZNWkFBVyXdc1J9kIj799y/49dahN+uWfxbmbA3xNAg6FhiCY9VCdM+sf1oKGXC/
-4Q8L1KBWHkQ19GU2pRW6O0t6lTw2XiFFIXb10+RH0kIdXmHyVS1wx4/IlEPzwS8d0CN+J+M7VLQX
-NDsiqyMHpwg8/hZQX25Xr8siNAB+nn662mpCGdGXkYD8HqT9w7cjyFNeuRIN6J9Hdxx2KFAThJlC
-VG/jfQuN42dCpth4zZ4dgY2p4xVkOuuxDA3VsMKIdXvL92E2nnz2DrsZSv1za8qgWWaI5iJhxuS9
-0eE76AV6bRwWHlYekiQ6DRXmjpYvRA4V3pd2Ew2em/6w8tDdTIMOUNVzlKjq3eqC6f0gYj+KHaTe
-fl6WHnKKJiRLfysM0pdJ0rjUTZx6LTo9AhzheSTDSt4CVqBVNs7pS8Cgi+zzRWFj8PPUjdODM67p
-AVuBrlgBRiycevoMeqT/Pf7fzYr/zcf0CCzj0MDeODfIZtzEECmNoO1713TrrC64iBlygXcVh0Z4
-3G/jY+BwK3icYMYjv5CIsouBaPM1YYGL82yvDOQP4FfRvYHVxEYKOc+uKfZaVPv3sYKpwmWYcOYW
-Jm63H1Qy9rBOrb53jVgvtDKwFdohUiFuitJsfxUR+C0v3U1I4hW+UdNywoWN7fi3yhYiBPLzuZ0E
-9MnxXy/NEyUVDFn+e1H+JcMfAXHANc7kRkg+11XUPq8QB3+Edmvtd8DSIyRuDGCcge5oV5It/JOT
-+SWL6rd+M7+duv8oJXHXdDLgtishpAqpWMKuBArcv9krtz33q61yOPiMCeAks2xdOU8Q07iqBU4H
-p8wB9QC9W1j8XGEX1osvfr/kcAxGcxZDzTruygCWVWcG+5rLDoHzD36jk5/XSbjK4I5IYa0yMnEK
-qv2Tbsnv1um22L9ap0MWjsK6MZ0yXclhhPAeqGr2JhX19m1ro+A3zcF/+xOHbBxWGVxpprk7LxuF
-WL/QkDpt4HGBZvu1sWC0/eZS/S+f/IiaAzyhNivvazg46K67mHiLgA4L+nMj95QUQHT7dZVgZvfz
-F7lZU8hK9Vi0gQQAuvFPSESeNVVy6LgFEBxBI2DoSnhhfNXUXjSN3v33TvqXL3EE0SUUWM4dHNxT
-V8+Jvmb9El/GNMO7P6/XPvRCF9Cb9d8/4zrG2LxpkgAyHdD2A9e9/pzNiR+1lSaHwF5cNjeNU22Z
-JLGG+vIIGX0R+V1W6BFItzZoRVKYYpQNS9llWp2EwH/jdY+jySGQQz5FfZ/01Slam/uwgjfVyD3X
-/BDGjob9MmoMve/sXGXzRTbE635Ijxg6B6WyZsm66tQ15CGJgwc4Mv0mSf/L2XUU5gKsECaSvKlO
-U2thZbgsugxi+v6/N/u/DX4I0go+SqujATY7fKrO06QYBKR7dvEb/RClYdYpeEIFTZnA/+UBqNdP
-cHHwE4elRwxdzZM6WIlpyh4OEBeT6eEunHs/KCpE+n+OTwi4491QKqiFt+18mkT6GCRqOfutyyE8
-oVg9mwXGlSctWbNdCLEfJtV1fk1FeJ3+PHcxZnru2ZCdhnV+7vqxbNXod4gfoXRObFstaxRSvTZN
-PpghLPY+/k3m/bfNeIjPFej8HQw/BNECW02gxoqJQ1HYb80PB+wOkZ5l1VMD1pKE4U49jTMMoOCk
-5Df+EUuXSQfORRdnIFqNO8nTvlIP49Y1fjxIekTTGT5UQzLT7CTtjmfPF6AAfjPzv1u1vyhvjlg6
-+O5FEKeqRQnvU7o+wFAyBsGohtjmK5SSxrKJs53mybzK+MzRXbPFrLt4hYTlxN1lNlk4n/cJxoHf
-ZBKTFRYEtEm8OvCUHeKwzzTdaQon2CbZ1CWuNGR+g87vXY0egTfUEtjedLDxoVYKoCz0KyiV22/W
-9V+281Hgx1i4i0LTajm7JNrzLuxUkXSe+YmRn2M87gwP6Lwu511CosFq91eoYNPqFStHdZ9ghzdw
-BSebcw3E/CmzQsBcAPQtv9GPkQjoc9WsSKbJRL4vkr6XgvhRKukRMSEkbuzjxMy5CVWYbxOpzlUF
-6IzXzI+Q0C2YI4jA6Fs7Sen62tAwNXB37Zbh5PcHDrt9aBrN00gkp00JjtPStTD2FDAcpz/8/sDh
-5FG6M/taTeZsRjGdZcrsacqY17MHPWJCcX+I6USlOUc3ETobz5ANYIkX2B8m6j9v+ClZ4ZKqMfhq
-oO3dL2yGxwdslPzW5XD0MGEgzWAGcyZtNBW0i1r4TvXf/QY/bPixS9MwpJU+r0TIPIXVzWneWOhX
-ZB0RoTWAzyELqD6PgHnlY6fq5z6h+qPX3I+AUGaniUZ81ucgwxMc6/YaPoCx38IcBegaZaMRqAB9
-hqIpeTvIrfvOwz3xq8mPaNA9FnbWBilyGHhfQNkc8kSs+p0Ezy0kf3FoHlW+4CA2E/jophde9fH6
-VhjZyIvjpFcXpiacgl7rfwRTVSuMqmH0AgMUkgZwiIOF+bAZPzAVPYKpJlElWnOMXtdDc0qBpCqy
-0f3hN/VDMutafAHgGdV52mBx2Mi5PS2y8ss1RzBVNrFQyzi+uZ+Z9SIFnD+hMLz7JRt6qKCdxHVj
-V1adtdj7S7R0H/aojT0/6SGT7QIW5CN6PecpFbBCgoFNAUiqH+wfr/o/58khcYlO0mo6BzJQsLuf
-hpzCNdXvBDyqfVUMBkVRy6czPBZFsccwDk8hLe93/B0xYCZyaDnDiurStsP+uofT9rENh99pvd/O
-uF9E7BEFVlFrIwOw8jlWEfgotxw/keh3PcJ/G/1w14XDDdrVLssuLEDrfA1+jP3w6hVIR/RXFxE4
-ENM5uUDnq+rzdQfAT4tt+ew3/CFOo36k4x6q7BJPcgCGtd24eORRP6R+sXqU+5pgSovCacou2RLB
-kpzc96Hn4XcEf0GIa9aOYGjJUArf8BCDHyCRHpFfMFBoKpHM2WW/SR91NmIFE6n1KzjIIUxbmH7q
-3Y3sBBWuu0FNb2H75xejR9hXGANURKVkJw74QzsEj2xoXry2yv9AviAjJBQd2IlwI6MSBqXgXQsr
-zQe/8Q/tqGGKZtiWj8mFjRF81Xe2MPh1yfR3eoK3YPxFCjjiuZqgm1hqK36RU7Dc6Wpd5fOSwHzu
-DJ5qUl1ruVvxpPfq/3G5/vt28Ks/emvF//MJx5FqWNu5x01hs8NWRH0D4+Nz1yHq+ouoYKSYz6OE
-g0w+0Bln+9Y6NSTXsZ+4kBdcrNtO5v3ere4qKhdU3yi1gN0NISCtsMdr3W7hwBqqaX7seJROTyvs
-rSN+3QIGT/hc7X0dwNaVZg2tc6WTCZeikePT5XE2j/W3SQnYxOWsSxp5pXsHueeTw4U+qU9uXq0q
-Okfb7T0k5Oza5HEH1x3IfLtmW4Y8ykzAWZ45aLd3d9HUcWjTS/QsNTz44NNtMMElGYcPE5GoHduk
-Tf+C+x/+sTIzW08wn4SEqcEKdcW6WtKUuzMbXJe6kC7DtxFN28TAPBvumhZ2vLwWX4aGddkPWZub
-jeLs9lHBPE/Bge7zDaR3N+3SwScYolFLYW2zRLD0BnGyOu94siHngFTbUlQpdlpWrNy6WJ7Iusfh
-Q5SuPLs0sdkleGHz6O4g4z8UCZ9W/tSGpklPYUMtLUTCZ1RhqUxPqYQAbr7NNZ8H4DfbUdQnneGK
-lRTokMBFHjObB5XkKeEJeCNrU1YsQdmIXMKlucfXGkWTqxSVXZ5FQS9PRg7k66wlP1m3b8kP0+yO
-XiY1xt3zrkjKP4qZJMkz1RWlj3slUlOf+h0cFXbJrImgiLDzxPRPYGik+F5T08DnsqjDPathoQdV
-Y1RjMhz37s5xutnvcwrD37oYVzSDrwkYSNlrtCXb4op+YHASq9PgJgPZm36wAVgsO0BbUNBJzGrO
-Dt9yHK8kRiMNBsDdkIq841124Z0YipFvVipcYF2wrLfKcl0eQrN0Z6uQo575WJsWRsikhjOlMiMx
-l5bGy1bAfJjBkdsK15/Q4xDpl1TTYXzINriPXgSc/WBCCqt5NPPzLIU5IioorSmlRRZTCjtCuJbz
-CwRWuu1hIDZCVzvU0Fbb8cys1xrcrdAtXAPJySGyFvbmO+kDcGbUmrDpfRLLKD2Jaonb7+iDpD2C
-RrJxPS1tPC7PnQlr/gp41iwvrUtAE8rGEF6PexyQ7jESttv/aIZ+NGDMqGBkzzOCVpyHSThynWDq
-O38SgUxDGIazruZxnkiWTc+h1l30nbVVlTr4i2eyLq1d1/g+VA0bP7eWu7iA5n0INnptaZRB2jnm
-/Y9K27qr827u0u/wYZ2nT2CXw3cZr0s4u0CVGN0TUH1Liv95DNiPsVXrfpVkcu6120N4Dk8CkfSj
-Zdjmd3VH9medhfUlJHPavkmVSfg5TJtJvJs7se1vLTgSJMBLNHQD0tNNiZhfF6uH4a8OLzfioeUz
-deU4tn1VziSL1IOZs4QULaOMfEk5Ydkfke2qZ1DIg3s8I+0/wA6ReWvjGj6grApOW7On9h4mD+t+
-B/Eg+rnPGtjWTz2Yji+JE/3wHNVVE13t2Bh3DmbRbneZUyEvE7izh59CXnXVOzFn9VTAVzKAJmIb
-Zgt4KBJGpPfrvsTqaQl3HV4pDJ37D3DWqMY3Js4ScQlFNyYnvbUrcqeNUyUuwE9H6mnOVv6jhybA
-UFTo0tg3YgsVUokYN3vm8ahVfQrxWrU+dC0Eji9VbSYwVIJkrV9FumTsKqdp4rmuAsW/C5HB+rke
-lk63eTpEVQhzIEa369LLRZ+0JWFw0stAonzodzt9oTrDDE4wY48gZ7hhFk1QLypvt2AZzsNNkieH
-oN3ePc8WxLRzPCn7lYTOcjiewR29KWAFwZ9QLtV/VgjhpGhh1CoLLm08fnIz/BkhcCQlJM9y2u17
-c7UaLNlXB386VeVi1smGfL9PdhzzVuOYtjk63uvyw5qVxh/hkaFwIHRQq8ne9Rjl9iEnbdQZJo54
-6TwPlsg4B/dziMs+i7LuvK41/OnzOtLp/mC3pUYHc4P1U3YXVg41IphsQlwXGJ8FOax7m+A9jztF
-ToJxE5yWcI2yU+L2vf2owp22d6vebVYaOQbVabakco8UznNvw2hpm/foIhPX5U3f6+wC1fha32cd
-bjDPDl2I9MK6Buedrqp4Bs6bie1R1mHbFeOuIl2wCaal4C2opWos2HNwzH4Hu3oJMsbAtH7bbGFC
-7kY8GbfPI5TumjlfHYPDDXTF89mqLLpGNFv0m3iZg+Ebaba0f+Q9XbDHBiF78Qft0x07QUKybTmP
-ddqsF/yyrT3HsmPLBxgoi+p+qZuWXkGi5f2TUQSmWGeko56f4GVEqz93SCVD03wRbQzn5KaugW0G
-iQl7JIWO0r1otZvuplZSYIYJMMTheZngepiv2g3kPf5m+nGNhN6+9hCNByc9I2JkxQz5xboIkJ+q
-Yqum7X1LuKZ3aTaB6xIPA8CqclVpULjJaLi8qdFuIJCsSVTgQSEVbzHdOH6zWVc3d8FAGF6OmqoL
-zKuU+zjcA7ordlRFw779wKmxDB00UmGc/nJ7qaFhQcWc7E97mDG5IBPvrrqmLT49hGY5HMEeLRLy
-/AbuF4u6hlpk+m7TMM6+ndybgCZAjWVcllxniPIQenX1bupibqxzLzTb+gymuybll4RJ5Le8o7ZV
-b0IdpfO3XS0Ta/Ner1t8dYyG2zPD7hef22WDRwx+JB2rNx1a4/Zd2mER73fSqu00UBPrO5z/wVRj
-cYlcz3ZPElujeNLjjo+p6vWy2i6QH5LIafl2xZqt93MLBN4bmOyKpmCtGJfPMIEm8RdJEpfKHAph
-4TBhpWhf/zFAMzV8C9V6ln0bobzSfYWJdUdwv4IgIi1kS9rkTiZ6cajfRJjyMZ8D43AU9huOD1R7
-kIzlQbwmpwUiDaMDbDQJvkNV3rEixKHeXnczd6+Jwf4+d6HtedFsO95fZDKwTzEBLqKgLq3aAndR
-lsCkcExMSfok5nC33kI5P0+wowflOIJ852XK2n58onKyQZ9zMLC+teOst0scNWx9Ew2hgv4u3lmz
-V5YOVlzWHk45b2ci6Od0gcvLaWEVWgFpE2j+7IapSi6hai15g/cnOrzru2TZH6J2mEckTIbYACwe
-QLW07CCiqp4q2WfTVqSM1W8dkC9BsfFGru+W3c4gRIP3SmwBGcOqK5IsaqY33YIeUy5k3c9n6sCr
-7S+gqEVwHafDcFJhRfAlGtFHT8xMNydXvtyKnxRoX1EXWbrGBObLcxiZvNs396lNe6gm5bsE8e91
-ArmNfqwXPj6qwaDiKkTdBkXUQhXOFcjua55YTvUnYiB7cFdzO+G8T7YQZToFgXfSuaMs0NcGUwhf
-zDjopIAvPBytnTBD2W0I9S9xqOx6IUnXR3AmUZA8i1hD0xPtgcTMFxrtlwyHkYXReVy1y7MBdApW
-5JLLpH/slsq9Sd3NAHVXO31Y0rQLzykcbDYcoyg5TmpnSPs3s+b62vEh1q+mr6L13c3Xu0BbeiZf
-XV/ZtaisYHco12Bk2YFFM+LVLVdbK+6EniCswcCrxmFLi33XGVyrYYbET1qF5K5GPfDJyoQ+1JBS
-kjnP2nmBcTbhNTRbJwKjbNby+9TW7g8G9k/7RBA6stzbZc+e5oCot6GFxCuuQFQ/1jwlO2qniKm3
-azABSa63pOCgkT+hhQ6yNvxEKdTIweR9ciolH0Yb1OeOtLzLpdz0w9r1cI62UNA/ddjGRbwZC+P2
-qrmDWX32aHjt7uto67+6em3fZ7RXRRPylz5W8kPcZkOW1+G0AHZi+q6b8y1sMrvAh7sW7uJg7+bu
-+ErqjzzapnvdujQ7YTvzQu5m3y6DauN7B/gi+2CDNHlf9xaohRPRQxLcVTJZbZ9X2LkpaPJOhH80
-unL6Qxxz7vK1kVsKKGe0WndqbnoA195tO2RTUhW5Cc6687wQ3GMaOranmq9RcL9GDIRm0KdteK9E
-VGXPS7At+rKC5x9+3HlPeJE5tuoHw6a4/orKVc7nWJOA3E3N1LDHdlthxG7qYe1zG00q/UhNP4Vv
-ZmrodIZMgxsgSbBwcR2DNeu/BAJewm0RuyZuTuHSCp2buEEpmmmTNIXqUaPYvKIBpX3uYmeaH1sa
-0/lx3cZ1/w5TKotySOg0xu7uEVvxlLcgDLVnqOhUpFRp37QvW4S7/3kcGJUXnSDvnHCjqZPrfIPf
-nedEEvoGpJo2fgB+lkanKNvi7BqBNrX91YAfIN+YRadTWLisXsX9Mi805DkERVK8SO0t6d0LrsYJ
-wS0YkM39YVn6BXlBDImNniaJkHzf4bJqv3Rxl10Z/LZxQZY2+fJ/7H1Jk9xGd+1fUWht0EAixwjL
-C6Dmqp7ZA7lBdLObiRmJIZEAfr1PUfT3xPYn0dZ7mxfhEBdssatQhSHz3nPPEPRh4X2uMNNCmzw1
-DCmFAKHTGHcHiqUosSNW976z02qsdCcfOTT9w4N0WNuf+r5VJF8x0XrYr5KaeeMdd0s+6cgjRITR
-MCRdFaskLMllv8hp/koh9y9fuwxqtrXMEfV3O5fppGA4wJruGhnPrJjW9Qh3163KPNJcczxlWBH9
-sGsllqd0EgAL0xry/V0e+qnbhUVa+NWKLh1KgKjknGvYwDfoP1Dx5W08j+ZciyDGZXA3+dB12m1V
-oYvuoey9Ztw0uTeofd8ry3DFFuW6VUvKafxcKAYtEk8L1X8eXNGOG6P9yotVYYNj1uqExy1mj8Np
-znOqcUlEBjFgD5Q97szYoihtOexkHuwCl1wYAbTJqdGk3bpkkrdtSOYB1QFbFnM1l2UZdcjTjCAK
-0zZEvpjMm83sJJtjjQhSu1/CHg1aqqyI+sE1nokGO7j+RgROpF9HRJvI9VL4frri7ryvRrpHxsQu
-QZl9ymDNhbsuDKrwkOTIND0aPTePSuIkrMJhoEEZ+RmmzA99ueQeqtTZ97bTgvt6izogEIcBW0D+
-7FyYbdECBOpTA4tzkcZMaT+7NSNLU1hCBxXPbISbjIWxxKo6o5vzIJxbRBpklzJ3/hJ3eODvi4BV
-6zLJeI1HLbGHxgeCcQG8ImTXsp54cXBjp16AxDyh9BgIR6QKBwW8QUYMua2JTj7DzyLPVrrCopjl
-XXExDD4qswUGI25fCpnGZpkROAIGvb/LRBeWF+0Q9uVFl9j+aI1p8mdkNg9vXlv0/WqyHi4jncRD
-Yel5uFNI7O0TdQ8ctcSw0kuLWh28pmGKSieqDcTKike5cRq1AWgLI8Lu5AS8FithD3xnyC8dCP2I
-SJRnpAfC7+6hQDEWEQYG+h5QuupPYStb7zoUIPGBFCRqPe5HrvVQ4qLY2e+h6E7ybD35oczFOpc8
-u9EtsuHXAYQC7ddpJMUYeymQq8+wO0CCbMdkT9d1SmaCWzMjd12GfmQ713kfkRwLqIlG2yHFThOb
-fpGs6slD6Gw6xnPVB+h2BC3HKcpHWXqfsixIXuS5NNnJCSrz+5mbt6EoB4pyV7UBitmKFnankAki
-Y8W76q1heGQjiciOGLEgPl2Xispv4F8RLjgJs1zD3zKhaGUQqr6ZiHDiyWhPQX+cqQTIoKcqOCP1
-BlYcKxQllTsw3jRfynIKA6xzNM3rBzi1qTwmXerCXT7Q+RWts16OXUmStyotF8UQyT2P5FSljrb3
-XuJz9hYgMoO9orVMgYzkmp1U0xVYO/x0jokOWnfdqUQYSI0wW6Kaa/868zgHmo3Swz8yB0PRjRo7
-TlbTsPjheuRjP0ZlZac7eCIH9NF0arzxPNo/ykQE9xi3D8u2SaC32HkNGuOprKZxzamEoe+Sj+YR
-57w41kEBWhvPkYkNjxPa7JtUqTZmpq5cZLykeIJSd4paBp2MMdTxYzcZ71pwN11wtaRy0ySwGFmX
-bJ62LWIltoEp/T1FjjHWvDrsH1Kl2XxldAP18DjC7ydirU2GO2dh8foZHhxozvrZ0fQJ0HAoIj7O
-OA/E5TmWBRUGYYOKQ0B/LP3hPp04isQQUILWqDJy5sEeVizeqgMNnq2Z1MBNHBLPkVMiuiXbEuOb
-B9iv58UtkQ1E4BMSGG4zfJAozMbA2BjL9jy4qAM2Fl6ZIhU0Dg0+zn3TJK7Z5G2SpzGhwriXM9d1
-39RlVR0nIZYSxyi8/rYIqCuvQi0cCrY5CzdSGq/ZgUIp3A2g6HqNZaKuNx1jeb8i6VgGoMshuXXd
-OB+LCHxgDrgWgCMSwxqDdtuBtDzO83Dbe2k+xjWzQXnwvLFatrAfW149htikqEQ05FEvzYTHJ5E4
-HYXz14WiNm7bwR3CJkDBmWb1cTYpuwV7uYVCAP6OwDlg1BBSkTx5C+jkGwmFzHwPnGkasRH1fvA6
-yE4TgQycYgE80JfW1PsaE4rsc7q0fRXjSkHwLosUlTlWzHKs4rRNDPzLYV6kLmCRJkWsHDd2PzW0
-RUA9crORXZqMXGaRx2B7uHEqPD+EXj5qjXTFFh0TFp9ilS+9cvsBogwVkWYaSjzGmHe9Weydyd50
-g69XIxy1fTAxK0KDh4aiQluNTnVpLOjIofUZ+Fw8ZBxOLysffvPZUwlAg0ZVbdP03p8WrB7a83hw
-4CKoWFwpUpJVAzRsjJt6BLQVQZc36VUOHZd/RU3byRsEgmRjNMMF2qztnLAmmslCUcEoEwxfvA6p
-ChGD1EPdIMtmFNt0Nk584fhS7rFHgcpPrA9KEdNSFOS61M6HabJBU5BmfVXdzhDwFxuS9341Rwxi
-+xEAZlovGo36AMgBN/WEohC55kmLMGrVJxdp42fLPqD+VF8oA5w24iZ08Es3affmszBLL8mS1KCC
-JH5R76wcPXINiZrgeKa6cHGY/9Sz2SC/0XUbkItMFWOqwuxL7areQ0DiMsi9VwJOefLL6nyFOBqf
-VdApk0P3hwasurTAD4sY+oqhtxE8hwJy9DlhaC7Z4NW7DDyL8cWRWfWrhPNk2Dqs127VMWOKdRmG
-sl0RJNIMRdR21Zxu0A2W6phQ2K+BfFme48GQltas8jRT0yEZfCFj6ES0Yis4Mfh4oLKkwjwbo9BG
-H/g4hQtqlsHQHUCCBtP6FrVdBBw2KCJo85Z81eI2KDd0skH7JjJWlB56h4AOIZLoYWLy1RRVCT1X
-gQnZgM20Qp1IY6/s1JYTQ+ZpXwQylA/wjK6Gk0NrPxl88YzmFDXIFDZXTGTl9Ojh2ygvSoMhbOzm
-7GaNhnSUy0gv7bmDPiZeU0wovsCXhcHUnGh9NVdBj2alsyHHA04LYFYixqyFoVv1+0rVX7IZ3TXo
-VLOo/LduGL0WxYBgaJiaAXLbEWk1TXfoVWPlFcPioVEqynx5LVJMIz7nuWuKDdW09hzOrglrhCXz
-LruhKPfxLBMlKNsYlEbtW2ooczIaAgW3ZieolR8D4HMZ4l+A/w8vqqO2eDCebbzrRmPgczOeG1U4
-FsyyJLEYW/gaQzZnunKfVph74SahJtx0Ao0PXyNH0bZHiFI1c/GCGVKDTjfrRCZWPuODPDqDSdIJ
-1bXkJ5RFtL+ry7zoDkKHrtl7FmHmn0PfT/yYn2u2jW0qz0alIM47NT4Mnm4829sMaxxs6GOFyrhe
-z7aS3WXWDxC6VMwX48elBIssln6PIU8WljUsZjrtDV8k703yMXQ9Fv8a+Qb5uBy8BfnaKFnha1ju
-ndHhjHoKGdRxIKbB7uamVuGuA8rutmXBF/8BqCJjh6zAJDA2fgUCwBrSTb+TK9ybC7CtM6LmbdqO
-EBuHvMq9CM/cBTf9TDFrZLDH2PgBqNXtJvMCzHt4jRHPHJWIWJPR3E6GrbpUMLobJquWnaGT59ew
-dCPOKmB6GllpjVVBfmJB1/cPrIer+pvQ1FYnFLaZ2JQsterOOYxmVqWWuYY6EeTU66yuS35MdFkX
-d07ixBxnIov+4FtE6lyM+KwEkePzwq5zKyp9mPJOFfdo9LJkjH2Larld5Y2sAFtTeLRlfmzxMBsv
-hvcHn80Kc0Ah1aYANfhsYSw+wcHQ74NYKRhgVusKo6De7lGAdTixg8hNd419ugbwDDIORmmo3dR8
-F+K0Q1ylWFos95ieJNNmxJO8UcsiTmiiuXckXqJQ2HEf7nXkPMaTZOvnnJttkYuWnZaygcg1IHMz
-fHKZVTCtKCysQzaDNtOcRoHjTGDGSUC68ttejjEHsNF/rkYqyXUD24WebM5WrwEwjYkhfV12ixrz
-WFXOFau56s6JckPPL1mX0HpPIS53u7Y2NlzpcTb1ifTwqQFE6mPe2sydsJsMIH4QeX0QeBvMKIds
-VUqt0HaatjeokMIqC58ngZj3Y7LofLqFJQMdgL2nSbe8hjUL9YspGr/c+yGkjnsfqG97AYF2N3ws
-YUmN2qZmdDoF1Ovnr3PLcnOaZ+31APgmIuNFoRyJgC9bzFayvgfZrx3ohfWr3sXDjODQfYePkK/s
-QkgRgxvPMTOn9MxoHOVGgUx6WY5IBr73XaH7i25YgvogEHu3nK+2SKB1UMOM6PZe0PwFMJ8XrnIm
-PdPDrBX9TNzXuNurNSrrAhskFtJzm+86466U141hPHte0OFhkW0HuYRh5zOoDOAqVBIdU1e9GEsP
-yu5MZK/2vD++CgulOuwNmN63jZqDyMd6V96FXUcGPHuaVe0QGdlD6A+ICUFRIvUzfxUS5oFeE+o2
-uSSpGNwGyyi8EMeyzsa3IZ/MdGoWUbHHbrKconlpc3uYZ7FMj1JUZrw6eziGu76ySVTB7KaNUI3q
-M1huphF7LgaY13KelTj0KZQGlxiUVPBgQG28ANpqC6BWDMGVlA3PEK62MoKwiLj1xE0B1K5r01vQ
-JAJURCNCmW9zMBuxLyJjA96NapSJehDGVyD31j7mWeO2Trq2GaIMej8aNRI8gjDG7LuzbwCSNMBb
-ADb+8Ay0Ysm8iA8oX/OIYZUdgCGWDdQeEUzq0XduJshDEQ5UT5Snn6Cwnm0XWYcQm3ZbjQPL8ti1
-8A9HHerziQWrLkxB5Vj9S98NsOf1mNxiUhUOsQ9GUB95cmiTGEbJ4X2IV3vH0aXa7FV6xn412u/J
-nNdMmlw1pO/WQAsWC16rl3j7f0ns5E9zT8sdjLqnaeXzvLHRMqfsCgOr2q54AvH332MwvQ+f4zOt
-q6buy7WvnnL6kY9/j8/83lCIleGIcQ3eN8xuJUCLjP1NCc370LkGhocqyYTYYJv0ASKp0b/osVr3
-u79mL/2JYRVGBj8yfQCFkQGMNEwmPDx/bdpkw7FyXgMbwb4zAJzImCMWQKiWXE89oFs0WLnnx403
-4Tr99Yc4s4r+GdvoHbFMY0QzZV4nNg3STMtVBh3BBciDbYx6DeNHzOLkT8wv/oxM9Y7W3rU9bjVw
-ijcwBGjF3TA3iV0ZjTp35bAzwZ0UjiQlqtJprn9yhv+EZPnenSgHPwy7CWEbLpHJMcB2Zt0Ca/7J
-F/qzd3/HPjNI9OtFqhiYI9VL0QUPTprk75Hy/Hf0UJTpbWV0wjYzYj+itJv3mS3Dv/nm7xhmQxAM
-dWM52wCDXmOQmkVJAOTxr2+oPzsr7+ihyTRmA1MZ32jf67Gnj0kUpNj9/967n4/6B3IcKUwIdhDO
-C1kqePMOCimTS3P312/+J3eoH/745rwLKmemHLdLKhR57YEpudjnM0GukCSViYwFG3sHXQkzfyue
-L3zvCJNK7QRshNgGcajskbZdf5kHgFf/+gt9W1z/ydP93g9G5HMIWEjTTSVVCgRa1bPDcAX/vc3B
-wB8oKm/8n5oGNd9mJv+YL9nHAHca2yV9ZlP0KjpdI53xdRpDRDdHg0BJ9vun+9cfcn37f/83/Pyl
-MWj2dTq8+/HfPzYV/vzb+TX/+J0fX/Hv27fm8rl669//0g+vwft+P+7qeXj+4Yc16vJhvrFv3Xz7
-1tty+Pb++q05/+Z/9x9/efv2Lh9n8/bbr8+vVVav0PR02Zfh1+//tH/97VewC33xTej+r388yPff
-OH+L335dPb92z78816+/XD7r5+6X3fP4Vmb//F3envvht19F+IGEXIJjRQVFNOZZQ+Levv0L+aAC
-img9GAOgJyMSq3iNKNT0t1+J/yEMmQKtLWQBA37w6y99Y7//ix8S7vvwIZIh8UH9/88Pe/37vfP7
-RcIZ+v7zL7WtrpusHvrffv1x/0Bzq8A4Fhy5tPgkSry3B8rzgUxgmydrBxJTnk9bTgFJ9GRVTD8L
-5PlGu/0/d/P5uzOugkDigGDB4Mcfn1NdeaYxrE/WrG6w+I63c9Xu4M23qfEgLar9VPksHtyjCjee
-WK7A0vVj8AJKTSLsLsepNNjSyU/2mHfP2PdPFRIA45iSKv4+XiYxWaM4CIBrMPfWQ9HuS+6G2BGx
-CXS3XriJhQf6FJiGsqgjTANXc0IrcPfgiAnGEDE/IV2Tb+f83XmSJJQBC4FjK/bePq9KhfHAzUvW
-/WLTLcnpXqN9uUXsXnI1pakfgVdQXpkSs4Vo4ssBXn5VDBdxC8fHke6XtP7sdTW7gddkeQytTI6U
-Znsj6g2MiNHO1+6zmL6Uc70aB5CdmvoCVI6sQGg8Jn4IIomI1ZHi3jrsfQy+VdTLLG6bZdWmLK4J
-u/BhtQVEbGNovcKA4QITuo1NswP3bh1pbhc4cBMNXmQ7xkyCuefb1bk/r31y0DzZ2rY59Zzssgoj
-u+4Jzjd7D5kqy/ji1cczpxU2iuHBoO0nFMzAh9GOj6MtTNTBsyY2k9jT4SFxdi/RUpXwQg67YQVz
-+Cka9M1CkfiWX5aSxQvmX5jorSuRHBimSgVNIpWUp5m5u2qsD2H4TWuxQ8NSxbYaNm0OdqjnqgjD
-1BXhCsMeF2FAdTGmfNOHXyfhAGTjmKVbG4wyz3O/nj1iPnLIgaqKutgHJYtsaaMAxC5MlmJwSYGQ
-OPix9zg9OIyiK9O626ZjsA8CYdELd3aAi8TixpVgE+ZG3SpoX1JxRer2VC/oXTDucUCxfV8dDMWT
-Ocq1n1exl90Vrtl53eVsUOyq9HnMkzWlL+3UfO77L3U3Rlq2UaHRHwI1UvN11tU7GYxxJcUGZIEY
-yen20lfM3IFH8FmLyruYW1w5YYsrD0YUt2SZmiHWuLXIkKjrBATZLzpsE/CNDU5aBSOoNJrq8g09
-fXpDFt08K6jCeRSy80OTYGQeJKAbO3onAktAiSKA3J22n2Bt2UQ2VGf+q1DgCpW+fqhMgXZ0DlF7
-JPXSRgSjBlQ5zFZ3spjtJgCjCJyRxQuj2k1zh0/Bp2eGjW5Xs8qCldaO+iIdTXYC++CKdT2/6ZZR
-3IKc1f7euPy/3v4usi+gTTdfh/f73w9b5v9Hm6RQQKwI1u4/3yO3zfMfN8R/vOL7fkg/EMUZ9kMw
-QrlQZ6uT7/th+IEz8INFQLC5hfS8U37fDwP2AeRF7FOBACYLswsUed83xIB+kOgQA4hraYC3gxXa
-/8WGeP5gwOslFl7MQmC0/eMmhRHpWLPSuXWuQeufXLpsEmyScRCkTQRn4OknLjXnuvqHxf7b8XBA
-xqiP84GT8cfKuNRhX+DeR5gc7QHgUP11XLAVz877mUEBQmL/67GY9FEDK1C2xH/ZWNA6kDBMU7cm
-gX+O1mDMxK1Og31OiLkoEj1eWBBstyV61pVuO/XKSySA9fVU7CvM2SpwC4vgALKx8c6oIS2iQunu
-kZaY/EWZ5OwSbJDgcDbte5ndwpK4DwQWgXyCkVZULeUkgEk1bx4s5yIui+Aj4OkBC6nI2uA40A5T
-4DMzJu6zJVkNuaBvmCA36146jAUl5nJf7eSlb/pslFPUIlw1Sblco9HmIL+0s962o83jwg7jTc4X
-+PP4yh93iKbE1l2kCh/FAo17hFJ7ySKStmAIZLoUGgvlLCgY1J7YmiUEsQUjEQSEWAStTVEPomET
-hWLsvgKyBiLf873QuB8C2MGvPVGf6pl/rFlWmFWRh8lh0d5yzCCXuEb8wmlKybCmiT/GOjNPXpXm
-wN/JTU5heVwzcZqxK0cZWLhRa7oWjvVedwL9HW4M1oJWh9SlqAxUCb8zxIFgo2bFOvCm4uDN/VMG
-OlyEeAogr23WRFx4EgRScTnUeQ60DYzDtIDSPZiGNfPUekzqeVtochN06MCIdwvlzwqMkz4CHS3d
-StSpq7JSe9Jil0DThsN3XR75gf56Dt+OmM3xl3SOhI+tpwfHOh5LUUdN2vsrTnFwwit/NUr/BhqV
-PrLNOROs1s+awMoVFu7YVvWLS3CrB30pV5jLbDPn30DPDldQnNEiTNUqoendEOQ6Bjr7isHGKSjA
-3ILWIIaEYOsbEHcyB9I/6cObJCygJKmC15xXG/ALQFy1wzb0868+4cW6SLonhh8Q9nkJzcjXQmWn
-atAHbYogLkbAk2Pa3umOw20Jbe88HtOk2A6hd4IBc7Y2CiWGnM6MwjZpW33KQ+r8VY5wz6t2YJeZ
-1zxB9WVAvAQWGrry6KvpjUMRgAIaJWMBJQJIkBJkSq1qkISdArgKh+5FAsHNVJujvpCXZE71ZZhM
-L5CjPE6acOjAwRkswiLDJurBn0WD9STgwoOwkKjx+iQmAuqtIqlRAeqjTgpEk3TkqfAVvkAC1DTB
-4UqXvSSMntWBA5haoYgxeo8oShcog3Bo7ogH3v0wrjDEcTEu7E1azSpOGjdHXln2UVLhQYUEfvk4
-QNsTJb346Hx801pUpxHaqIj65kVpmAB/2y/+d3P9SQeKdSrAjvPnW+u1fbVf0reum/+4w35/2e/7
-qyTYX2FOiAaRgfT3bRf9vr+yDwz0dYFGJ8BS/8P+yj8ISkKlIIXmSpKz08x/7q/+h3NrylQYou5l
-Z3fg/8H+et7PftjvcJtJ9H4CHaCPv74DaxieKN8a2649yT4lk42xtteR1lZgDjFilW7ttNFKnEz9
-MzeU970uf3fo9yAUyA1F4fftWoFHFWk4ukRpjiFikby4NpA/AW/I+Zv88ZsK4qOAkOgrfU4peS9E
-z5Mx5wOt580II/4DBipDrHJQfbCaFPBoNU++zvMtrnS7LiFNWCsxQk5ofLYauX0am7qN6KIf8qoA
-lV1cwHw1BrOWRYOfPLZtQnCqBkgsmvwYhOA8/OGu+ie4QPBPPj6KLRRWguJewQ31rjAhGPoJPrZQ
-GEHMsBNYPPuoGbwuakeKng79ZuzMLFdLEU7X2IWyO5qwK4LUJfhXSORg2fapWLiOc+l/gjf+KQ3p
-ljTFixYjA+M+2w8tlDCTw++SyuWg7i1n3rbc8gZ80xjM8r1uif/Rq33aRUnZ7RrgzPOoEXd6g9jG
-GAyJNaiQt5TlOz27F1CKoEtCkrOtVmDeoG/JihuRFremnO9o+wpVhI1QVn2eoHDYihlO1ENYiYum
-Uw32I1PsgebZPaZ7sJeH9mbFJL7MVIcPFHQraB6I/sgL/6b2yiwqMYS9hTVTeSJ6mp/zahDbRgFA
-mdKhO5Ic3Shtax/Ty0B1KxrY7AqTQGipStfufFHoDRPJtGIY1x6o55ITiPdLRCH6uXZjQneII6kP
-Q99IzPzBiYBxR3MFgywwOJXRNqo5/zwViVozl5IXw5bxzcA4Gnzuo4N11yW4nxqOvBLDzDwsmg0g
-puVQWxzC50tMxzrYeDD2es2y/DXTDd+D0KpiQlq3oTy48XrTRc2cHpKi/JTJ9NBSda9BNYoELg2D
-2mQX9HiByUGLd1WSo2ro2wvArevJNh8FfOl+4tHxTYj/x8dJMp9SPMLIixdQ0Z4RsT8WythkgtYM
-c7C2ZVnrVcYgKopNO6RFXEuAMRxL18csI9NpSa33OUXSVYsBJ6iiSQbAQYrwfiIjUIakPjrQCd6Q
-mYKJeuGX254lPRQCvX+bhk3x2LfWXogp8b/+76b234FVgZScMfm/2tTq/Pnlxw3t20u+N4z8g8Ju
-gfscMGrA6TmW4R8NI1YoGINL/ju2iiX9e8MYkg8sCIRQQr4HUBV2QXQ4Z2hVYJIK8P5/sp/J910V
-9tNz40QUoQx/3nsnaa0RG1EjGgXVer/rgsI+1xk3aCnC5Dosvf6IwfC8Kj3aHOsRIgGGQniPojA/
-wo8viC1j8kHWM3tVHcgsLRXeRgRI4gMndDp6RZ2iN/Q41DssOVBkx4B3sTxzS68bULJDS+aIT9XR
-80pM5JQUEWjMSIVX2eVZ0BSPS/ZAGvqagCeJVKbqUPSYUZKqhFtd6BfTpjXYe8F2ydZZLoL7EqRi
-iUF8Wh7ChdYXppiXqzoQ1RcLikXMJecvc0bSHY7nrrCdextCPY1njVP9QPyRxZ03mphCubECybf4
-DGSmBKUbR02qUFcR3BLN6+iH457Cl+ARej+39+omXAlIV1ZtXd2YrGiQBJsOhzyYq73r5HRlPSkh
-2GdTGPU9fCOiopnsdVpO086DLunYaGeBKPdsAmsIvVQKZ+h7JNRFGjPyOwgq9WWfggpNEiCGXiWu
-Ca3H+7MI+g3RpN1Txh29qXyQFBtfqutMQqoEhQPs03iS3Y15RfaKzA85eF7XiJgPsHS0bG9xro9D
-lWSnMZX1Axg5/haqxjCCzBVUV13EXduCyt+a7DJNJfDENgug82icGO+w2leXwqQI/QOfdYF3Vdxb
-3j7xbE5ij87mC1+SrzM0QmBzq+kxJWZXpOxgLSnWmQmCm/Gs1spkXlyjA1dPFLSBE6Q+9BhWXbi3
-GA2/UhBtQJLrQDeD2IZBVBd6l/UC6kfkAwT5AkZauzVSV/t+QmNXpJ07VBBoX7qybndYyYEtBxLC
-1tojF4hXe4PjZUCewhxH9gOl7nqvag4lA60f3EsB9DgHYXTRMxjLQPzrJcJFqK41b4pLlS79VoEJ
-d08WJPHWpe1iDbbXY9Av82U5qwTa8NE/zQRtKUapSBsWo1uBuAJFSYBc04vKWTTnaWP6nZ8m4crW
-0EOXHv9qHfooKIiGdUvOivihneK0IdN+QNF2yZW41xQcLVWAiZtlQm6wh4mPqvDAECir8pkjDxTi
-vizMYsa9JEoKHazzDu1bu8zzZqk9aAln28QemOkrbht/TRfILzR4zRcVh40Eaa3Ylrlf7atFXNVT
-t0X4p4mEXMxFIhO6YrmM2YDx5zyZ7aLHCEKGqMsTSGbmGhOH5oWl8zagZXbUDL2VsX5xYyaebWBj
-0oF+RiIaFHTDA7SrJAHRWRJffioweQfS69fjTQD9wS2vzSfKqxdQadds6U99Lb7kY82vF1he74zX
-0Q0mpgkWn/M7Vh0kYxgsllBw3Lqe3sogm4F+AFJHkTnfaZWBQO2AnyTw9oqnrHpFyOxlly3Tmg+k
-jgNYVN42YD4/ppD8ASoolm1XcP9KNPkQN9DUH/0cKuymD+kapCTxNsgi2fCGhxedDfEwoYxeg7Ch
-7kKU1Gs6UYLFQ01xP45t3LBm2eA+hnwpmNEpwOpqetTgf+9DkcOgFnKSDQrx5jAJL4Pz5tjDGz6f
-91BhgpyB7Cf4Fix6QYxSslxLvbCNFiEaW9DXozmZp5XucLVnqAJitkC7FyCdcFso+Lh4CZplM1tU
-rRawWkR5+GLyIG3x2818Gjo/QBs9TAe/aJLHufaWeGwKcxqUGw9+O9WHunRyB7lb/eJYPRxRqfmx
-VIV/i4fcpFGWigQ9esszUMpceM+zBg4Kw1xC7g33NxQucCK67DUWvnWayXCTjzmU8wnXr5Oq7kPX
-wlxszrZeiQwhnIhdSWFpgA2DPY21d2N7dzln+ObQ7qZjVsfdODMN5IHnTx2Ga+uqlHmcz8OwgQwY
-Jg8gWc8RZBtsHXZpj6mzxfM/wI+ih/50O9TMv+5FCZEwJjQphDhenYwQIouTzZmNbQhBbBHSY77A
-RgQSrLt6Gacja7B3Qz+OqObU4xnEsu61kGGxc40OVkkyXqTwLcpD0EmK3PsP7s5jSXIkW7JfhBJw
-sgXgnASnG0hkRpSBczOQr3/Hq7tHuntmWuSJvM3MrhZZwdzdcE2v6tF5Cw6CPOVAWdfYTOvOklSn
-Ww4nuGNgPJ0Tq9vIimk3EOMDiZUXKGVjECq+AKyvdnlv6bjoQ5FUhOOVm9jRsNpJpI86rv6k32G6
-XMMV7sBnxgT/qLulOvHVo9JX+0SJj7Hg1C+zZ3ZDV7Mif6qxvKmw3m6GUdNDp0y0CCZXeu41PT/O
-TWEfPFgYEeQu0tJVYH0MVj7FeJCLA0+JfT0mLSFOrd8tpECcyFCKfPitW+59JmoAQHwZ77xqaU+N
-5o0/qKwaXrj59hhcuGQUVb0duLDHHiGBx8HNDMQ+ucHd+S5NdU3y6iSnfL0aleAak5o8Zku4FQSF
-aeVAENRBd3CozoZ+1JCvEF+JQc2AYRiF0T9HAuK5tWtK7qGGoSOh5hahoKIqYqzwmB7ZCc5+e2Z7
-KuBw5j8GzHl8FnXBX7EczP7JElN3bv0fb7amPzNvSa7dXPjhlDjmyRl7Wv3UBO00bppp/Fp5DP3k
-q+7H7ayX90aRtreAwdzxeMNv/HwrMn1GwrJYLy5FZd56lbuHReljvLSwPBA805gKp94JM+rLXzl6
-cLe3ybwbuho8rrlMO92sjXj10Rbl1OfRQuHQkwbS5FCRcq7oNV2SNLbS4ZkOEh7SnX/naw6e2srX
-XpfMW6O2YUQRevtTtvP83BKSjjRuwltplzy9LasKHjAov86euic6UYGdTK9j1m9d6RMStOS7MfYv
-Pde30KoL6wFdpdnWGDi2PPaCS51U3FoXvfTec2cow4axQjjF7zy1d1Yj9uuQnfAp76dxYmk62dx0
-Vrti1VZYTbURuHLKId80rBW3ht7tG0feL5r+SK7qNw+016lX3wOKXzeTPmmF6LaCFXPk5uBknGU1
-eO4yhSUpK3jXi5HISW0Oth4lAyAxa7G7K/UpmKRpmYqn2RtiilTllXw2LbCsLW8m3bzFuqpbzxy/
-/nlZcZyHuPLtDSN8fTAIHlp2etWbIjsRJNbiTBEb69YBQbjnvoWIu25tNTn3BnZwUlYkuhlgbwXL
-J8kLHXWlvLj50By1lIDc4Dhl6AzmEOutFRwTMxtjAzV7b2kKQ12vfeXE5PZLV5bnyV94RCedu0Hl
-RKYY3Dlu1tQ5D1Ni3DN+d0ffU8SWm0kcSTmdKm3uPmROClEBuAEPlaWIncstKTCO/iMB2PYuSAxj
-h1n/yy9rft6gbzcTT59w9txDp2VLNHTje+f2X51qqFcyIWPgati5Y5EfE93Q3pys8t8Jl2mbrEu1
-F5gFceXebvAEoCU8I6X9zFpSbZgo3QdgFSKa85oAR1D1bIy7ApNn1+25Wrh7oi4uf9RKnBOhtfee
-z0NKNLf0Yi3fWjIiWMD9/qPJGiMunO5GW3I7jYPHwtM/FcMWN27PeydLopQEFe7TQNu6HpWaq2M7
-O2KvyUu9pN2DLkyfZX+XPFp9a13dDGcqMxhba7Os33oBDseqJtYljrM8mtQoET0fy29UeG/XkTL9
-Ewd6spup9438jgma4iH7bBr2WoarVldfGfn9s6NWAjwGPLRToy/ZkxBMecTyu+x10EseGSXVQaZM
-xNUgR7ATVqVfDQAZsQQnE7rpMByStTLQUmrxSbrACBPTM+OJ/f233cngqvmt87rgKadsFTqOa8nh
-Ixg68VhAn3uCxGEeJwr+eOSxrOdPT9K95Saw4ROTR0Stebiy06bMcLv2TsrARqBApkgzGoC3q2ep
-JHKnrr7awzicsK54mzVJfqZ66o0b4sLd1uXC6Ia9ZosO5n8Ycw/hoK6sx2l1h808Gt1JDLnL/Ok6
-+4XkxCdXVhjrlQh+2jGBOMUF8JAufnPniiy7Am3J9o49MpDbdXdsqFnjqWEH27nufCMys/tCm+qN
-FDeCQxYYRzIU8FHMICcW1d9VeooRbGbNobyxOvprgXzYmsGBfLx1xm1e/Mkv2lGZ0XqnwksR3cqx
-ScKpXP50kvX3WBXQQ+gSi9rJF4Si6JThu2ShrQTnZ1knp4Q1BmFeJkcjuJjtUgB+c1SEMJe9ZVq+
-xNNafjQAn6JbA+qlve2unDXfUom4RBidp9PNQJWGY/3TTfhr/Co4NWOwbJKetVC7dPlrmpps/70Z
-C3jKZy4uCf+GbpfWsZS9cbYZwUBgmfUL7Ar8FY2uXgW+pFDr9Kd8EcnWTrYEJ3aAb4pjUrEnnNzY
-ExOHy8JIDo5IE8ZyXZK1IxJBFNRa5rvcHn7x9sTtPlc5AA21xqTjaNcaO487t2vv+hURFpod4BbH
-4o1K7AAmXO7eSZqV1lS/Cs5P+hJN/TYbZNum07SNajXWh/aS7P28KvGnZP2DakuwCOnQ7dUQrBvN
-yas9T4r8aEBUQnut/Du5LvZuWD3odI64KM/SBd9LF8eMiBcZO9SzOC3Y6cZGkwwJFQvmm2kyPNnw
-6LoyD1XZlJDgWq2IGHz3aXOGXY3TRajpjJbnA4zQZvUEGa3+qBKTD48FGuJ3jydDo2GGdPUtvzjr
-ka7yh6o3tMfZdqqxOvT2LQ8ygl9jzHTUtamK+pqPufHJE7C/tlrJNTdlxwmYCWv/mhmziAwteJfW
-mryahrQ3nbpFAMds4X5a1SAs6r4wdm4VjDuvFe5jzzL6uIyuPDhL4zxas23vpDL7326fB+wgU5l9
-NFRj/J7BDpFsbvkwKg5P/jSk7DqjOYz8kPvAZMWlXLuIsuYWpjR7+5279ITZKKuexm6yr4VHI3BK
-5eVKmqa/s3hNH8zK5IdZ/fFVmNNPW+bmhptQdkx1ZdwtBv8l5ySI8EsrdAOnK8Oh1ow7nrbGprIV
-aZAkrcJl0c5aDpejKG2xJQSeAgXsoK2x5s3xujloPCvF8Ve9Dbwnr5y1TVABrkEkqS56pW/MfvXx
-XTucWArakruo4hj0FljnsXkmG/ZFcuSyLiQa8in7Lgo7P3hdf4HfZBGWmslbWPPbwOXH5zNMLn+5
-yGD5bLpaO2Z5mv7N0fY/vcz7f8gDg8wX/EdF8+47G9J/McH8/X/5+4rO+4ODDD3bd3Uf+fLWSPE3
-RdM3/rgt7mwHgS/wdRwv/0vRNFE0Wd0FgevpNlbVG3n0Hys6D3eMabj8P6QTb8bR/46kiaz2b6sr
-TmWfTCfZNN9Cbv33hEOm3I4Zd1x5NHFQRU3llDVrbE2/pF6Psdgbgq2km4u3pZNWG7Os2NG7dblN
-yrmDi5dzoQcNlcTKymD9JLd5xzRHT4Z+Mnn9zqyZ5megRl4YNOO8EcxbRlRnU3/E2Ny9r6RBYgLA
-5YEkXrqvirzfS1I2GzXIdM9Fpr7LEITHsBOjCmI8RQhJFd6ylKWFTSOhafd9fTD90j5lc5YEoWwh
-B+M60S5wv6DyUNPBh6wKZu0HDxxoUX8ygl9Z0PO50if/0jh5diRKqAN4KVbWB5g13wbdN+eNwenM
-Ud96ehP2Wa+YUizYnCqv81eAeR/TqmeXrM+eCaetkSMqdXByJsQb5uVkmySYkn50n9zVLi96lpu7
-WWnDRvdoUMxw0R1o0SSgq/QDy7ZyK5p63QT86TYAYtNI64D06XU6cRCaY1QE/sUn8XIySc0BQym+
-TXo+Q+k22WPiO/mhBk+wcTy1fM5r455TB1Mk91+tBpUPbK6EGWdZx6LJuFwP0DpxhcC5mrnsOf5J
-GzGsYNLTMOFxNt32KfOUV1xfPf/FEKt+D3BlfiToWwYHn1gMkmIOpK3gitmHfmUOX42XTt1hUo08
-gdow+1AHLnxHUBJ+VwVhRiFAsRQl/ArvDAJtmzJWkr1lUmxFcD8oYUI0Gj0bHAhRpOMwD3mUoNih
-NCV+h8QKkT/buvZgoZcX+ZUcpXnNlJZ/aphztskwYbLJNRLuTanKR3LU/ks7DrATRn8Gf1Wpu9Hw
-Sl7KQA1LaMMaGkOTe9STbzQp80lmmW/SmdzXpjVosGwZ7x4CnG13MC5VFZNybPbS8co9d/cJI4hU
-y9uom+JXRybsYeBOsbG0VHSbPGO6P0/8SmorS6PZOEvZJxGbvOyRkmmf2Geh38yo87ZyADSiKahm
-37VecwHDOW6FejJ77gwOtC9PS1+bCYmzoZb5ynzbHYzByz9mr5P3kH0w3toIVX5f342zwSJg4UpA
-g/BD0ZXWJefmsnXBvUYIgd0lKB0qr0vHgZgoF2xAU9+DP0TRYj/bwlhbNzLI+zXS2tmJbU2ffrw8
-+RghX53zzqovUxfMB9GCsECe87itcJs8NwtVvPU68Bz3IZvfUWnG8ri+rd8kyaVka05G5kW9nnkP
-dVYOr0bRp/Aq0tK7DABF32cE+ooxsyUq7/mNe3Jakm8HLgwkZWtYvNlGV5a/fNoUj1pPg99N8YC1
-/LsMpoa9M5g3t2XvB64d8biTmfGmCZqtDmnuORDKhfIhUljo478tN0mCc90Q/mOwszJeCvCU4SQ9
-v2KK5stHuqGWlxSXf+zIsXozzNmujkS/OuT+osgjCFQy32aSYzq87bKKjefI8i3L5mkng15zIg77
-V9kF09mwxuGqTXr9UrLT8SP8Ph4jVznr356Xe1SbJ4BzWJVvVaolWzXm+NZqkot3rD2WX/WQGB8E
-/8rI60dnP984TbBcxNbPx/Z5ykxjiEp9BVASlSxYvoUaG2zRbvKTE3/dF55cv/sJNkpt6nxhA8Sq
-AEyw2uyuBWDeZ64Nt0nRG3wB9K/x58cF2JLaeMMwA1Ds+KcHkQPNGus+mdgaEZ3eJybr6Ju6V5WX
-uvJa84B1SHKvNbMJOzTEmGfyu2bFKHkjD7DqpcBz8O2blO2A4sHdFxSX2Wk0Hi8CErKR4gZZpUEA
-s02a3RI0a0TjMi9lKe7KoSrPPdAO1iTzPIdwh9hm8eAJq2loj+hCK+azwJ12yzxXF8BL04sDQ+o8
-Yva/EcfN9lP2/DoRhWy3KQ2mgRN7suOGpmn+uoUQZgUIf1xd94UADxEhfy+/dbvLmRuLJfiVdhrL
-pTbPEKVbL12hSAFPgpngrZa54UKzLJGdOfZtpdKUj4PnDSaSa+6lp8S10owdghQBT7CmztDK9f5E
-ORVBfwRum7C9aU8X9Fx4W47Lp4Aly6lZSpbtCYv6UMvRLEl9MohP6fjozXLcDmWvf3Xj+mgrbDcs
-MBL5pM8FAW+SzpqOnbL3MH7VCrefuRbuVy/QoWDcze5bLx3J2Oq2udjDjFDpRnbu6oZDSoKcMxsl
-H9fn8iOoEHtxjHF6GhFgi5guhPHJtXCdkYpEm9ZM+9EYOvtNG4LqxIFtHwdHa0Inh5o7TctlpXZw
-jqSLlOY7xXkN1qM58oENQYWs31UJ6Y8Hjr1AGljhiV6zFDAHlr7AJWmJsrtsh37S6p1d2tafrIIx
-hbcaANEHS+jpi5OSKuWr6/6pgI4ldpDurJd8zjnvPN0d2yNZ6LHf9ISf7zSSBklIuWDw1pZBtTfq
-HAhBYeudtXc0g+t9Aj5m5krBvAYasC+cmBIoXmjQF3l1N8wqHTe+GsqPLin0ux6wGUqWJV11k9pr
-ZoiAFK/ulfIDBAdEORNwTyMSIshCOMMTyrT2dfMPmZEjBy/j5i44aPQqtaO0NG9hTrZvd/zW3TFJ
-NX3Yu60OdBUKzfAzlKluxZWYBKWffmB7+4bO6Rtg2wIU5mtdBkJRTzmw6X3ThigfqwlTg96uEF9G
-dwqFY7TfGDYcUJi1aohjdxZb26n77et6uW/xxv6WNttj/I8J2FeQf84Q8WRayT6goJAW0sUHSmF/
-xmCp3rSsJB4NVSi/KKN58afOMRErM9Zonuc5J/SsfJNXKpdxWtXfum0mPMqwZ641aPG+K3jNlXTl
-dS5a4oGpXo1hAjCEMyXHnlNiF162dSG7+zwD9RpqyagZED3zFPBt18mP7Fbei3JLBGkr8E++L2ll
-lmFBA4jAbWaLk4aM/QJ2Pv0hZmbxkYam2ACMaFYjItvNW28WVRevQAs7TmXJeqwbbDdCH0GCT0jo
-R0rK5FV1PVdxK+13PSuwENWojaCfrBsy2DsG0j0tcDffJ/0mWxt9ErvvikpRzGNztPypCaeqtjc6
-MIA0zqpieJsyMMm2GOeI5z7nCVtJojL4B/ajKNtzo8T0DKJ8Qi8kW2MZ9vwRdG5ZRkOvd79EXxHQ
-WdPU4tJLs0eiNvhB1480cX9UltxYl7og/mgq4EV0mELYWXwURtm4DWIwlYas5NN1t4AduDm7ev2d
-JeSsv0HH10imzJZzbykCxWs25D3LobLs9mJsSzqFA2l2HLR18atlZ0mIhwOCXHCDV9z1Uw16RBO0
-+57HBR3ooBlmdv+PTZBNr8k4d6Ezlea0Q1MOpZbWJ2V6qPLYwlIgXkOFbbava6sC8x9Mz35R1n0I
-+YXAj1dUvzyDIcHMCtuJK1VoP72tsfnxTZevPfv9AyeQbkZSt1oyMEUz3OvtFJxt3RBajG8yuC/y
-un/SDWDTu8QtSnAJS919ArHGnzu0OXsEBrTlw/fn9rdka0gSbKw7DLa6xWCY1SlhF1cOz46hrLO0
-LfO+mo3hBVZO0W6sFj5LaAl34TkrWKKpTAt2NlCjPe8eyLcVUf9ve1wCYuNrFpwwL1bQHBoPmSfv
-J8xV+mLVKs5ZPIWmjuGiLCsb0uPgiXeUTjdaeKuAHZIlL+DYABaMGNmMrwCQ7tGA43iZzKqBoenf
-RjA1CuaBiqImhgOLwl1mwgFpaBnOVLX3+JuBc8DfNhM92KW1XeG8n/KvnHTOBaBybsXoBvWGv5ne
-RMrP5kiNRloA/67BW9CKAycuVyc+rHZEg4QWqdYyjoaVzSHbPhC7jpw2nKp1nHqaacTseyEyGG6O
-OC3WRbzkogy+BbRpXvTULX7N0snPfesEeM5g/VWhGnrjlyUzHJQ6q0ZaPswtBkSgt3bdblj1n/oE
-8ne3FjnLiBRCWb7W943n5mYEvBaO6QBhPgRFiKEEYwz8je4rKLHoNYR4P7MiXX/NZVeVuMYWcVmC
-Ov/Vmk0dr3MpnihCKd7NpNKfsJ5z//N4hlwVOve0M416GCMsayN6GjY2WCo6uitLIYyAfCw2czWN
-N5DFnhUFpaT1E/z20mSHui4PgWfAyrWx2scSM9NpEfDWIgkG7HVIrXQ/rwwXce+WMEL7eki/Xatl
-WGwSf9M5XrWr4VrhJazq9CTGQN67t7xVyQvwHDiqfOK86M7C4tdgMoIIpeAihbjQGe/XRT3DDjq6
-vKAJ168PL+e0nQNbPBH2e/knQ9f/wU/6v3lvyZaiIxhYfm0vwPr7r+691nEmD4vgumOpAt7V92wV
-zg28GjBimBLLIKm///N3/Nc0uIdy4rJywuEVEIzD5/Vv/lXf4qW0WpiARPzzh3ZaxysQHnaDeJmO
-GdXfO6Oe0/g/f9MbO+CfTYr4SHQKKED5kHI1jVtK6Z9NimZmUEHiFfMOmkd5Zq4Z7wVUvZg8Qvrc
-rj2sm2XBkTBN3c9f3/l/WmT7/y6Oxkl3q1z9v5sLH79yYtjpV/0v/sK//V9/9xf6f5ie6wX2X8oZ
-Wex/iHFu8AexYI5SMlrcR/6S6f5hL9T/MAyTfHbANf+WVUPB+7sYZ1p/oOyh01FCovuG7jj/HTHO
-d3He/8t7ik/N7cPj87HxeGf9e2y6Ie+icRUftjrI7nKnUWyTXMzSYfEK9sw94H6F+s40Ori7IM/p
-a+gw+9ZxxR7/CvhEQ+cyhX8yVWGBvputs9sFBEswHfTcIaEMrfDIHHy9uaxMeQ6qeSu93FIYzD3o
-ektvYYpTql3pD3S0KZKZnVwkvXk900vtHtIAt/BGyqrChbvkxceazfPEnpYW6Q3JLe5sRVOpIdLr
-RJwJGbu/LAa2jfCCCfEr8O/XAgpYp/napmrXIgpwGm7aThaPymy734qOjK8F6mL1opeJ+6sqxvqd
-jLLosS2C2mWHlKTpVtiDwFbo5W+lX0GH6nQTozlMwgIco6rmp0HX5Y5ay9486+gkH8vSUre+LvOH
-5VMbE0613l4zPJN6XNVGrkK3Hlcs+aaZ6nE5ajBVXeQtqtmqDBVO9Qb8JgHY6I4dCA0PiyGDjxYK
-pfjSa5+ZNWsWjRYcIg1cXlAkr65tOJTcwK/nDE4NBrEAyX0YrHLkiyq5xhq9K9bJV8uAB53B2Dg0
-Rt1H9m3FK+XI2G2O48AvwOqgDfW5r0gt86CCYMttKrfbe6xy9ndqGPMLhGWdwYpVFpWYPLyPbbFC
-e4X2OW+ScmpfsZiXO7WirTDXS1Jw9dIxMOirdF5TKcbXrmshwHdrQPSrW+3m0XBF3m34CeZXNY3l
-fd126UNhMBZu4ZAH+zQbB8JXs3jPxXxTWUwHr12c1XK2Yh/l4Q0HmOqPLiwLkJzZrBlbJr/F3Gu2
-yr+cAe8+kjAEqZPBIMS4hyWW18yAX4o3U38eOsUImvgw1UL2tCTMW/Y3STguHhJwwNboVRI6XSNZ
-TvMHAQz/TG4toBAkAEW8UTwPqTILKOtiK+lC3CQIV1u7qWp6jBET9pfN2MG9j3WgfTsg/vKMmGXe
-zFT+S5EPjM0Fe0dWMUMFaRtC6T3xUKt8hDZKnhma2z7rXOveSNfxNCudO0I5kE0ODcOvP2pA/ycP
-cojGaq53f7ej7sVGjfdky71tPGbJ4lLLMFt0RTn1tAnqxv0IRE44pTIyAzec1EQbs6kPJqBCZrl1
-O7M/+NY85lv8PxQ/NbqEXkBCmoXqNIpHezUDGdKdE7zrU9a9UUnn/3KVb59Iuo5c2DS+eD4tRWQ3
-/ptUmV9GwE6xMYyG/eU5GU4+YZMQQLuY6EiiSkPedfUKtbGQ0j72yqaDYQV/lm9xC8h3hyzgrzQX
-2DtK1vXlruccyLdmsUprXywmeC/h0k8VEoi0ZMjkjSLStWJyoibz0O5TEkgqmt2gTaPZkQKDawE7
-HeMsSy26smwjBkvZk6bxmXVCJqFbnkQfF5/9a1AQCucNS1mGln0VgLeSvRmk5Tf2K2ObB8Iiq0nN
-AwHGIf3du25z9bzW2c26voLulS6x0MSyf/eyohZp8Vz7NK9gGq+Cre+ntpLay2t7iAxKa84+N8sX
-3lFwCquAd2Xdr82Wh8nyUcilvHbC1ycEThzd+KmFuUM4qUlseOp33qO2eWIAl44VA4T0zOglcwNY
-NtA05Z5F6a5PHDZO9YzGn3z5ueZfTTKEfANWeVTEtMV7RlKelcroex6kv0p76/RZXgsV6NhhsdqG
-fg76hvtUV3oEX8VZ183me7S64Bbqy0x95xOJ8l+hKOZQ+PXK0rZ42BdvZ9ND0G8m29GHaKwRtC69
-t4x7D+TNs58YAH2NSSJ24DWI7WEY680AUvxkOdmnGI1qb5UZXgOzlV/lLNsnOSmbtCb3FAf+45PN
-cUZztI2oGNGjhfgpgtLcyGVVX2gmlrvPZqu+x5zLwkAxp2I+Hp2DV3br+0gjWbsxmsnfGK3V1Ps+
-Ge3sSber2eHfJtkrxp9VD2Xql1t0eutQzCYw58JeWQWbE7BfLIXeHdqZ9XlDDN+bi9GAcpjlaylm
-P7uvUvzc/PAC14AFP/IzhyS9R+OcrUhObfbtIl9FadY3PlBPpG8a7YCUPwtNKhARmclSoKq6T6e3
-wTiPwwCmN8mFjLifAlPI5sTBrtt4INkVykHoqAUh2lmTe9mrVd94GUHs2B89Ti1bM1g7wcXmwU2D
-pL7iTzCrAGR2kNAwEHjziSYGKjSkSgH1yDRsDV9tWnY/RHdG+QG8a0pCQVdSiuZKApuaEhY6qM2k
-lh32wXdj5z7K0ptjWsXeGoHomgicV2nOlaXJnOSUWT3tBfNgf89prh9EGviR6aCQjKpdYnvJPgtS
-ImHSeT/OnP0aha3tjKxs4jERFb5Q3KMg9cRsv40F3odN03IScx8cAnTIBtTHweYKDuMQbbU90N2M
-NohmSCWRRUkHPnCAEMgxyGjrdkbzncM59b+bpmvS0DRG4zVtfW0NW33MnP1UlP58RbKov6HvUg0w
-KUYdOy2r8eaqaM42lRvAZvSbrJtrG1N1Ge8VXKBcufzY4wMxxKWV5Qda5/RNCtP6sXCMcuuopIwT
-FRS/EVvMP/0sGT9K34Jlvy7DL60D243Lx87iCbg+YGAnca9whxHug6k2MPSC+ofVWBcuSd5G017s
-NCvB0NO12EQ+slYdw21W67W7LdI2FW8YEVfgNZaNSEbL2KhezIc206xrZ9xUORDtAvHKkBZqAHaP
-Q7Baw49/CwZWFCbx3vHb8lBVQ2BFnAjK29LW49+tawnGda374DKtbXDWR5M76WgAjarawTo6fa8V
-YYK0yeV3BGlFodLyqZvemIO8HBHFCWJAJZHomN4OX0OF/09HSjoI7qi7anGQTAv+yhejh3ITysLy
-3NCc3WNRse3iQo3TpHHN4ZUhinVjERjm76Fb+ncJ0PdYVo6fxrXp01PCQ2m+CsJ5PEmIxmjocA6c
-0MEy8jvpGWkaUo0yxq0Lkz82irF3z7ghqoPTGz4qMofddqKTi6cfS6mSx+pfoX80kItT8jGNZnJF
-UHFLfHfB2rwCnfA8VIGsOfiahz9z6mS+rzF8P5DwFg0BdbNfNjLjS56xai/ZXW8k4jLnQ0+0xhyY
-X9ygezDbyn1Mht5j8W26I2ZkteKqrSRQBA1cNr+zVUp9q4Y87rEiQeFJWbdpDKYPDnDgk0z481A4
-Z6xpyDHu0GTAVMyRAWGbbVNddBs/tf3qTTh580NQ08weC4Qk/sl0m47ytF1bDO9j+cWgkDwuambx
-6LftoIeUMS0rH5sAR3NRZV7N1iLH5cQBvYyYhdPxtaCKnI0Sz+g72SzJqZZKbfgI9D+VdIzHqVDp
-EBttUD6k66y9mDAWXk2qs3amCoIfaSn9hT6w6QTxQvtY9ASMQkLl1cPU5GBfdINxwe5G04ZCM+Q7
-lFCE36nS/YNei+WtyRY2DpJnzBtJsHaMbdD6FYcALW27BmssxTd07gyRsFAgmZR1LNg6FnifOjFo
-n3usvxWYc8W2ulGpdcgG0y23nY4HDSn/rx1vmnbLLsGvnh3X0S1OjrQJm0rboFgmy0voRjIogz8V
-9t7fQ49HkGiyrM3NwF3q1c6XlN7FdJp7Y6ezAdQi3r2pfcSqwN7V0nLISM46TQpwdN0E2lfTD95+
-oTPGb+JgLdnKp3UOv5EsItedGANG47/j2DX8R6dhLtnRFGLSwVLMhuPRUiC/nBoIxSLcfDtRc4iJ
-r6Sv07QbWkNq2z1YfJ54Y64sQs4pWw5WIJatrCsrdAZWi4JQkqDOs87zZj0WyZI8gKPtyvuSWsaa
-UkkqQ81zaRN72aUEbMpN5Qu5AT2mu1ZkVUpxUymxbOBIr9Ou6y7p2jAetfQyklIz2sq+jjl9ZEfH
-GFR650+eZD2eJcm0zwccu7Ny6ge2252Gj4KZ5HnBCLfugm5xrO0wr2l2wN2f5e8YTftqz0qdxE1b
-gOn/rNZF/wqyvHBvUQwn+SxcUSf4/4ThMSSNViJ43ScW4+iDA2NmP3dZBN6YVudYLKb+aVEcMUb9
-2E/0BCStGSeZswRnHt/dtC98Qx5tKOT9xoRWv290E/oDQjwxpsSdn9J6rKrDkrm5vk3xwvow96TI
-L43tTV6E/bQZYYaZw7bTUkWRo5jcHbXyQXKEITKzm8JeQcFenYCgqju5dGaYjaZOYq9xq2IDkr8c
-PuaCcbvt5qW6lLcIPiYPfBoI6KiG7bHW6yXYs+K5CXdO5aWvPKTc4WDPY82Yo0/TGYs1ViJAUYOq
-XgD5wxg2+Aw3D0KOS1y7LdYS3Lws6PTBVfd5FwQfNB05dkgVROvFA78OFdV9tqx7Q7AxP6UaZl1K
-0BzPxrLrjVvP7DsXU1+vndhYfAQ5nuWwM1pxD1+EZ6KdtJ+aNePdZPVMFaB4pOsL7lefFQNvngCd
-P1wtle8KSL5sPRJY6CYrqVsvopb8SfZNMw8GtgKNSPSEj2cs0+X3InrLQi0zcPwSYxuOHXyXJzj2
-bkQNl8Xz3yEeqKxOs4Hjlo+SFp4hBl9enMTMJ5aphfBvnFAK41KAIP6LvTPpjttIs/Yvgg+mCADL
-zkTOJJMzKW1wSJEKzDMCw6/vJ+X6vpJsH/vUpnvTO1fZVIqZSOCN9977XP3eef6QM737tDlVsi0u
-ISDONfuka9kQd0AXnzvlKD4P/2JPzpGvzvTn5vY1WU2tQn6aHgaSg9R2NmkFZKOiT9BaI5pc5PPS
-+2i49VMiQ4frU4eMwtcLmPdbYcjyYHS5QZuhB2y5zrth3ReLJVe5Em0eLoUAWAUO6J7YhrsD6liA
-5ZnN5d2xeDvkKFsWvFP/yDsf7F2KgPj5ysNGMi7doTbL6U11ILTmOelfgHj16c5KLfuoHYtGYlxV
-BE19lrwq0169zpCMzLVXWTQ5jVrUZlg2qZHfBMOAqWRxMN5uAdVMz43KghNw5JlewowQByn9aGyw
-4vZB2LURVXSgj1HgliQ1NZQ3P+KO3dCZ8z+73bysUb/9BLH811r1fx02Ccvq73aXj21SD+0vPsIf
-jMofP/b78jKwAUXaknTODyPhT9vLwPrNEiapZArvpIWM8G+alu3+JoSUuJTwHvrSubAp/t/2Eial
-HZik7J1LetCEPvgfpKPdP1oJ+R4R3cKJTnTfZvwxL1bDn8ivdZkZVE1aw54eonk9ZOilBqm4QqOz
-WMH06tPMt9K4ftaiy+bdUvWfk22/pL7/SvTGvI9gnm9EM370pHNWWV8Mm36SQwgQnfxO35QPIDO6
-k6dVio4D03DRcIcowbiT+JvDEU/gvuxINCtV33h1RrlaQk8z3uFXlMmG2M58X7nmZ1ETSJrLjFYA
-ZO4ygOC8ZMaHq5wbnuv2CmNK8zWuyFBRfDnte9b4OBiciFdV+mvS5XsDm2Cbp5d7F2WGDOHqVvFd
-JRQijI0JnGplOWlJWMpzTj3wp2Nt1DjyeDZMGEhcslZmPj9HgXo0k+xtjFtoPj1FZZqJ7RpPnNhg
-+oCKVbHoossZ2qPtDvfFzD21zdyrGoLTwc7EsF2iuSI9GzDHN1ZCOs7D1TWuUmEN31lR3lwmiY3V
-Ot4dS2+4gHW8iZsu282dKNal0ZTXHne2NfGdiEWtMvbSbb1j3Nk1OlRjs1cKvAOqSn00cyXfezl/
-bbnzMyksDf44Fr12kPNPbEbfBxkY15HEzRiMNTTAfkxDRiD3ekGsR7aqPlPcJDsjaLxza6bBdlQO
-szt3rhUrFn+deZ67oS4W+HnA2qMhuHbvd8sHwhv9ZNnUnEfK51+dan7lvBOzTmBI6YLUXBWdeeU2
-2YBbAZmdpjJKW3T+PSn9bO9Vwdegz4knaP7zpc/pYRktssO6MI8ohlwAqM17s27jU+Llj4mUj3Ss
-pkef5lkKR6fksYvw/2MRzzYg7RWWOpXfjz29lxZi9HrJAmczJjHbk9p98uDrbzxliOshbV64XoPP
-iTqKDTbM4maxKyJBPTZaXXePWE4e45lobYXiaS7dc0p9eKhNHbAOdgAcGu6XHK75Pu27e0vU0ybr
-OWggo3YUTlb9s3k5wQvp32N7e1ym9Ja4N9cs3/e1jl0cPZrxZBVoVN5p6lR0nTp2Q1R5oWesjJJL
-onlu61tXTmxZhGGEcZvlZ0yV+aZy1XgoEgsMK9fgmbIYfYxIVVMnzmySxzG3s4Ba+r6mOiGNcKHk
-JF5w5KX3pGh8uqlIemEiebZUNz0U1IseR7i5e6tXqKWufLJM3LBZootnik+SNR8VjbpiJuGdpT0I
-rcGIvpDIv9gb7OaKVbM6LhRfc4rWnsu0zWY/HKL2kw0D/Lqq5LE5LcGNLNzpjnU0CRJAaZtpHDAj
-dJJDgu+czTbqQgYdTP7BmNyNlJuv5tofzma60NxmSIIvzF9JD45Sjl61RwvHkFgv1h0LFpZ2Bj7i
-OZ4qRN+gXptd5K21JD6X9eOlPKP2k71NEStDdQ7vlLCeJNdjDC9zF8inQQ3evvHn6AUdmsw/6gWb
-BjPdYW+OD6nXzKeGHexTkNTIuBWbZRYni32f4+m5ISLGgTvI0xeABy+smgnyUpaiOlXu6266rXtt
-f+ra0vfJKMfQSDpSmxg5YN5N1XLEnrHykG7eE6T5Tyogi7OHNnsMZjnuMWSzZIpqsTa8PNtai3rx
-3by+MVqfHp/ChtUAbdUMmG0LEymJ9QdyOhvvyOabe+nKKC5+wFrH3onzW3o7LlF9FVl9eo5x6KxZ
-U9OkmuhdQZHHSwnpjl1Q0d4A8RtIpyHB4NdkDcIycq3TJX3SAX8NeqCX+yhe7iaBNdSmTz2s5jE5
-1Olwx3PIOIBjaLbCFOod3gHDbG48qqkxN4vDCaqyy/5cZb4IfX+BnFH6A5uGBEUKRhDY0+pOpObF
-8QsmqLU8ml89zyYp4Uch0cnZ49ql4NsQxhD2RiM4SPjQ6NqsvZqM/gKHbDyAaTn8I8/hLpxcWvDI
-JQWSHiQ3CEjKyG+J7c9sA0cckAEuAvxYzibTKdv8oVsgF7HQLqKMYbyMnmmZ56l4+Tug9jkblYzB
-mjSU/eJrvs25sCWrIRpws4y6kDVil9uxWlDju4EpGisuSbRHu/a/kx66cBMuLNa9j+y0Afd1xjkb
-QAqkGS1MwVLc2yPqATgJg91biqHQqq89U6bPNUo3SAWBGLHEz8h9O+bzPGQl2ZZraQRflkVilwzq
-j2rigpJd/qibjNb5aR7DMjdvFr1cFxz1cA/L9KnrW/swGEYAF4NPGk9XtHUweeMW59bTB+VHaS/v
-g1d91Z5NI5axOIT8WXDhPkVRE1mZHKdI3SYxeRbfVPjYHPuO7CT7w0jjpCi1zZDecbRZypJ0s0cX
-ic7aR4b6Plw61ZDN7FlQT9WbaXAX4hiGsyuCZSDeZ+jSHIs+iqEUa+jJ5TpxxO+2hP/T6R//nq1u
-W+7fjrr/1XVvxS8S/Y8f+NeQK38zLccmEOMwR/6MjPWD3zy+dS5CDC5MuLI/5WW834jKCMRzyQ9f
-4iz/HnLd3xDvBZcuVWHCwSn2nwy5v+dh/m378N0fFhMBt+XSF8Zr4SD4ecitYm80Y7q+99ybOCOZ
-MEqtzWBFsFTNahjKtV8t+S07YzZHQeD45Vqruedu0aeU/8S9p3ELUs/Vhsy/1rbEL8jeBk222k/G
-ECU7Ui3G3g9avbEty72UAGCiAeCVHF2BAWylhsvtOtDJQZb0Couyu3WT0r4LOkveKHtG4LWN8mqy
-g+TAQ3+6Hmz3wXdrsFeemHcm0QYi+nZ/nXbelkYiCJdjuhHSOXrInF49DOHSjsuapFmJAk1fxtL6
-1dabM/ZXGRBURwwIjk1wTTTZuiHQonbuEn8trSQ5zWy+wpQONIjcBIcq4XzUgQ0+TgOpLlDnszrx
-EUp4BpOemw9pXfV3SxCMxywx4w+cjiC3Z6s7llb/5k2GT+bXbLdgZi7AI17TT+QnI4DF02P6WIZB
-bM1phiKeGjeSe3KVLu9BEx8M5YRIOy8TLm/WX1eul4b9PBwL19olMaEaGuKMb8ig4zaanI88r3ed
-y00no1IUk11FiNp5VEGs0UXSBS4eENoC9iVTNp4DyEQEz71XVkVXKRtoPE7h2I3ALIYJ5KBqfO5L
-hj5ZI1tGu7GORVHNuzlxdxNcDKDh/W3W1hctdeoKzKAF96LaBaML9I4nh3m3gGU+swOz1zkgu6+U
-yVKcWEmtvrGqihBsJv4EtJ1daY0ImO1g7PIBvkFRKO/kTHL+3gY9xbmUw7MaZe12ymraits4O5tW
-nXx32xEN49ITjkMSz0iHCiSSvP+osyFbY864p5blCFu3WFvKyi5ZbuQjOxqj/Zz7t1nFgDXK5d6P
-q7vMM3eGGr3bpUjGA0a05JQ0PTYVM4vs20BXTcgW7hu70GnrG/lXXNP6GsrCwbBzxDttd9m95w1i
-Q2o2PaFbaEwt/tZJ63FTXhoPK7ecT33mnS3DFfc92WzryvOAXdCvVFpNWM4GoQ0Kc4th2xf5kFBo
-OCpj4wU582Kq+WXDvHb53qXyIqZLYp85RB8MfkygdMGvDSO171n+wiZPnaLTIU2Al+OhRINbDyy3
-yMbgv1AbVkozlAa2mBencBV5IX0KI/aW1HKpiDIQd1elarW6IkdV9PuBAs1+HdtkjwD2U8/6YpBv
-S8i+g79YwqzwYR54l8OPrf1S39Bq2M97v8zamQBrnI9bfxJ4b1XZtv5DYTeiOmQiNyqKHJMl4HVT
-GB3I2zn12LaRSlZc0Y8mOfbKmxmQXrFWmv7vXexQkgJupBlhJthmEm+jwvC7j4pDc7GuLD+g+7Ka
-0dmwvQpEIPbz5cg3JiCScgsHwJ/DNAI6tKI8NK7IgIy5SV+WUTAapBNWDkHQmFxFRui4pjt2hVuA
-LBEu7Cw1L0lhn69CgsyBrbR46MAEfY5RU7n0GeGQW2dpYmW3skqLdLsMbulvil536ibOSj59l7DY
-TukJuLIdZViZ8FAt2FRhIyArDLFnHWTT9vm3pjWGZBuwf87WduFH0Gm0tbyVAXXzyL7xfVAiu6ID
-8YJDnYUI2GS4yppQ1mGOJmgjDS3NNKoeJVorG+iE8uzA7d9G6nhcDj5Tcz1UHSJpzNLwUNDJ8OYL
-xseYMcSU3WPae49xz66jTKewKxs8xWJstguMtTsnhcM2JIrinbLsH1zPoxtDd/4XqstbFK7eXb5a
-5vIxyiEKW3MonykDDuugDEFxXNJzuj9J/tx2JXvTEghu06gL6ESMdqC2It5RPVMKLxUNVaucIR0O
-ZW5tjHiKhp0a654iWI98zMamApEAPlOe7qnmpk2n6R9SljDOfZQ3OtrmHlaeaejkqbMvZvm57c3p
-XuQJTYwkjYhAmnkWP+RIcx8stukoHZMCYovfusljS+pAf1UV5vrjYk3esoVJ1EnyL3QOJhm5pHF6
-R2CGXSy5lnGqKwoYSDMuYCvI/LVTp297lkBn1yjVWmMqufad4W6mKvMQxTK9wzk3EIJZyidjMb0r
-I8inL90k6rvaMAPkgTkIHrsln+/mqC3yWx1U1XvpCLGHijkeIl14xooFZvEG7+1CwCQ1hqU3OE99
-oRtqQVP/HS7G8JInWdqEFGwkMPngE2WMio7/3c8XSDjzMH6PYo3WkAQVm4POaGhT9Iy5XduOjBlj
-KzNlC+FLskupARgg01reY/SSL0BCOPjphOqRgNhAfmWVDTkHkBwbowzax0phk8G2RKWlTSDuu/aM
-8XVs7KEOGxc+ghQFbDSL4ylY2GlpzlSSOdc0TxgIC1ntPhqp0xRXJfzsbJ9Zlcv5ITE0bmkz9l+9
-Sjn+Ou2CaZcSuLLxaGXuR2W0+o7WBv/RpAj6qkz6xDq1feQ95a0lvi7Dpe9+5q66AmKkXqU2zDt7
-shTw6Tmf6HfE1+zjvtxH1B8TYRXWKVZ2f9AuZeorjEVlyOmTZbpHjWu29Vts1euFjSFrwmDpnqaY
-gy7GGrL8E3aZYSVVvpBkNxJE9kUV5chdssnnVWsGJWb/Zc43MdiKY9dTor5dHKcTd22q89eiU1x0
-FREbovlaw46zqdJOj4AJnOXgI5dGB6oGjXZPPpvnH+4dWd5pYRvzWcgotu8Mwi0zruUUYr0RcXxE
-ivbo9qyBZl/STbnKVpguOdslvpWNO6Rroa6S0pDzWpejvrOAtqmjWy/CvCIsuVD4SDWgv6676j6o
-Jqoul9SYB3aeiaifIypFpgIjeZqTj7ADx9yUGV/5II4DiG1SX2csfXdj3wSP0VTIO/pHR5h7Efd9
-mErJHg3H2QfCn8LaTnDYpXZxxnhe7H2ifTvtIqCDNwcgY6TdctVFrt+vys5B4WEXwP4ub+qRC0K3
-3yZfNhxW54rxAboF9eVJiAXynqAQgMMuiTa9NEnR5bV+RVFrTkWa4OiHjbPOuhFulllL9egKFasN
-003JJ1xNhwXfS33VVpWf7TDYpsFeIsnzsda9cDgkExS8te3cPPud51znRuw8uSOpkV2eAMxdV+SX
-JzompczCmkDWwfAjB+KjTviYaaRUm2AehocJHld9sGY/O8YUlHzwmONmGbUjZSuULjpqnydmtLE4
-f7zVFsCR2YVNhdnxtvEsyFJEOtGv6pwoyiKuqrb2qYwVp2bhSE4E+5EcagYIBfrJaIjljQdG+qA8
-O/+oh1rvmqyxGsw7BtUwPQCNFUeZ5kMpghtVJaKDovphT504D6h6ipHjYYCkFtkgx902jmcOlPRe
-9nPjj10dLTbsAcHskU2dpuWcueQYUPSrb3U3f+tpZ2CzZSUFewLTFjQlOxjrQ4v9S/oPdGvszT+Z
-kv984rn4/X9a6zuoa2ZV9dOBHQVFoo7oiO5TQfr4k9zxF7GBv3oZH/lAumRgPVv8ITagl6KsqHAf
-D97UkouikyNFbW8w1P396/zq27/8OpfP18IAbnIi5H/++utYgWH3fiCGwzKUw1t6ecLLfuFEoHAw
-YkM0suQz17TIrcDv2P+ICv81HfH7y0PQ9kA+eJxu//hrkijBqdg6/cFFENrGl0HA9gu5dS/DgR67
-/M5vnGabVS7WwrkCWsg0wQr3cWG6cH+MGfBw8svgUUrm/mW6nTxSdRJbG1t6er1rktmXRbExJvm5
-a1tuVZW3RORXY+zZIvgHWvOffyFOwqbHkd0kQijF5f3+6fJYYICRqR/qS2SMrocmQ9lf6SoZzQ3x
-yIBnvMI8dfj7D/HPL+qYIDBw0jKZSrZTv75oG7GM1lnQ8aJquXJoB8mK/gvAIhqh5gaV7f+HCP7i
-yrwc6X898vNilklxmsWfBN/91xdTgWOXF5/5YaQ4dsPm+WPKjG1hTv0//FZ//goA6mcM8dn0oaSJ
-y7//6a20i84ib5mUhwR3fn92rRrqoiotMez//jey/uL9oxeWUyRjog2v6g8fmsrItYpF5BByLHmK
-B0YKAvfxxTYaOEOYwUDGm0LHMIv0eOzOGYt095bmAFQaRr7hx/THulmFfQttcz/9mA/bH7Pi3/9V
-//SekL3g0gpY7PC2oFT++p4o4t499svkkFGH5h1Y1/e3UzVxWPqPX4c1qPgdugJn+g/vPVgpeGFq
-iFFGOAyErWeXECeiPP+9BOj/loL/sBS0UIR/+kQucvwvZYv/VX7EtC3etm8fn13883bw95/8fTvo
-u795aNnsAQW3cB4XXA7j54+CRVotaB10YOwT4eA/4pL/V4DHCn6zJKEabvxMSZfMz78EcMv+TV6K
-MFgPCh475n+E0vlDRzApNF7CovWQpBB3QUDhv16prMMNbQ1pj79fjd1DPPj+4+IZZR0KSARnVB6/
-Cw2LwvvSRENyzT7d5D1n5p/etr+4W+ESukTP/n3DInVnoWddIkSCHSrtgn94xJlCy8SYAxvLKCA7
-zFVDGMkgOmg2TY9DlgRXk8Thg+OziKqJWMWAlS4wNlY6iT3/V7I1LFpmqiwuvooYnmQZgz4ml50A
-daXy9hYHfnRYbLojOWkNN3FKdp9kNm1FLlX0d3FHgXnS2OXBjwE7G42xQPtQVE8abTaGjvBIymJw
-J7U+jK80hHnkKKUoN5TykY4dMjGvAjJMnJpaQHTjMFkHDCjTW2WUxHxT9wZMB0tSmbI+WbreeTOF
-mV8LB+zrinUfRvjJRKGSWLBZV7w7Tr98wBwRjwEXARtWRx/7bOxooMpY+qVxRp+SGqv33vO7A0+t
-9sxASvtVZdkYCf1hK9kB3CrpRKFb4r8jI3vMq3pPLzMiEv6kp9lFB1+l7tyteZLLV2uADVZJ036K
-R9CL7BqcQ1rSdrdox75qYmVs+U/M3URnVljhANh3dIZdKcMZD0g+dIrPORgcNXPea4bT3BvJDWEs
-tanHpt5Ar6CcHiOxs529UWzwxeMdFrJ/FI1Zh0FyIayrhgN6OYpXb/GjDYWKlzy3aaIXOgu/WkMU
-CztmIY3xWoFdehzGyXhhF6O3Kba8vc0WftVWdrKB65iunQXeaFOk/gYZpbxzC5/kSiSN4Xqsi/aY
-KMcNLWnj8Ruv4dGwxDJOfgMaUbHz3GrTOyONox2bsPpYDic7u8C0ZYiWxV8GSyNz5n7VdbIO3ZiO
-PxjdYRkREOtSeLyyw8DIGTyPaXHyhq4Mx6JN9g4Hm7Du2+amzrL+NWGptCOfW60XpX4kpI13b2km
-wA3lfFMIVlwBpgF8n0a7dYcu29Scfi7/JD9Uy7gNGUS9LLjsyxXx5flauQyieVxZd+R0rFuwVNPZ
-rIE/N7WeABzWCVgp+FR53tJyMiy7WvX9XZ4Luctzd7lz+yjdNAuw6sKRRKnlArdxTkoAc7baONDf
-NuWQkqprsMiKmLVKS3HmGmZjva/Gun7OS8fh0/SaVcm6ZVMGxXeHuOnGGoPiMcKYCGC89UiT8KcP
-cSP3egoWSsgm91ABPdqVpWJfj6mwwrvmXSDtQbBplemvsZdg8VDwb9re8DcZfBBSKqIy0RX9VnCc
-EJozKtrfTUF6KoQH5NHEWMwgColTHOcL0Hpg1XxOOsO51xM1zGV3M9ULZk/4qKCq3HmX5qTaXS2t
-a+XH54CbzIY6vrM5FGsIu5RSmuVw0iTHv81Emr7jthjWQU6LuhUs0dVsjeZ58ZzmVXHX39OII4+t
-1vV1Obr9YSm12GLelueOv/a6wTF6r0rXeUMHpZ807cUesO7wrXXz5p47s3/IYcV+Bd2eri/uw3Wg
-ZEHHaIJog2lCyezguxzDufhxGXjDMO/E0hRjGKuU7XtHSHEbxdm4Jc3g1zfYAkdAlOAOrkmKQKhs
-jXQLaMgBRe8j9zKhxtShtV6P2d908rU/aKfHFwSDElLDs+Ma0ZmKB1A3Ntxg0BLQkJpVkNi9+FJY
-/nBn2JUkA2h27XPXENzMcKCfMZljecaXdI2ped5yT5t33TyUx3Eu4i+1VWrwOqrle41JtV9NTpBt
-l3pkjYYRnDxoXGfi6Lk4tMAWBJ9zBoTqUJdlsxmHvjz6eSde3STo98QHCxdDEuJT6XtyV7retKwI
-ydbfE0hU9SZa2v472wUA63rpXwsrGPa1rM6YPF9wOHf70jDhI8FcWBFzYKkDRCIAiCiDnu//grfF
-y2QA3VVVr27R5ocgxa4emKN3iEZ6UOeiKA8xmgNLC5sg7LpvInxb8aitXRGN7nSQ6ayDq7qIrOxT
-YjYZ7q20cB9UXTnTtsdy9UbNwfQWRXb5XOWxcQ1IinNeVPGAxhTFqxXBMj7VqdsaPKQi91lp/ZoV
-gXEi2z9FJ9NllyfluMi16BMYmIkzgii7XP+4l517WtEK5K6y7IDlz/K7Ndvinkdh5x9Gj1XOHYkg
-IJSelTwMbcNIYEEkgemBxn6jEcq/q6Jj1RMnnnxh/+d8m6EGHPq6FohFWp6Q4PzPoPAAI0U2MRaD
-AfwqSt0phnE6Ng+YTeR1CSAe6AUhd3zw7splDSnvM+yaXwpXNvcud+sHOMXNPi0pQMAxYgsM17Ev
-YVf50zU0TmfvgqFEdWd2IZPjAXkePZAExAfPnRWxONPZvRFo/5TaKRt1N1ObCwi/XoPhbMyXKmiT
-L6NIB3vV1glZNCDqvbNhbSe+Suih5TnFpFdt+qQkGEMXoLnJLaPFumcH1p1VOmj/lqHu4lGMr3lb
-W0+OMToPyKPFMbA6muSR8M9Rbqinku5bYrJdhg9K80cwa+Eyc+i/5UicjLsGYZM4KUwrpjTjTsxw
-Pa1mwOQ1LtWnl0z21te4FNk2R/qpnQABwaJvyksAmATKhUTeb5ZlJs2yxJqtHHGqaZ+SgAtHpQ5R
-V1Hcxy4WB/UcvyhObNeeA7LbiGOghoVL/oY3GLc/z88ibdZGMPmHuGB/Q0RDhm2DCWftmNQga+Xj
-ykqxIKGLFl23ziJ2LKc6Kg0qpwkh2HsP4W484oWIj4wzdADaFmgBxgb56AJHnNakfsqRILhn3UK2
-WkjR0C4MwhBTWwoi9J6f2oqU2oAWpQASvChD+ke9E1SLeRNXsyrCsmu71zqSyypKxXywUrvforAo
-HkdOsC0bAaMeZt4uqhZ11ssstr3LNerGrX8lMa/TqYkfP8FE7X7G5mFqy1d282+4yZHSsqPtvbZY
-1tExNUEwwofdO/MlBqqLny2E+QpMKJ6bWwoY0w2xN3x6hBP8GxK5EkqNeaG+d1mw89HNQvzJ+S6l
-5XDPcghzipn4JGqlbm4qCu3pf2Z9Zw1FvaHPyZpvu4kI5LGqFnEtg0LT5BIbZAydPD0lWZA9/nDg
-sHM0d0J3+SGFgXur49jpNqjS86e2i5wyrmpMX/ye1VoJnzcJA1RzZ52aDqif0XIAtVfFhRQ5lR0+
-OAJ+rOUrLXB0+d2UrFOCrOR7okLtxTRS2M1SkSBvS42oN5g36egRExiH7HmqYgcHtyJZkGJPjPZB
-FDX5PvWxkeLhgVpvLWLPr4x+qS1jrx1tvQ/412/d0e6Yq0lcPnC3iQUX7oBMEMPCDNneswCP9JFi
-6Ks2Q1VFn9sw9NQ7FZXqahSCYN6QG2/LGBHnBrBsHP00fWscIzizlMTmMy92/jmUnjpn3BV5+veF
-WrWTy+mBvDnRYNfERZpTHdIZ2nyuzSS45QHXgPoe3VMQGP0WN8ewdSeba2Kqou/Ib1RLsGs5TyKx
-GaA9NFtacizuorXxjA+Pe8g8AeTCsFoi0tZFt/Fy0dwvo6QUc+pt56YFXoPwstAJnULrnbmL72zF
-/rnApU6EGurlkHefrYvrQip6XDyBi1UKBQdMLKD9rPEmahkKktE5OXxCm3TOvI0GkfJU2zhRJQ+a
-VY4mvSmSyLu+tLQ+W0N7QwEtADYgQ7u8sjvCOhxurlqhspPMWo8biZ0P+4ozRhio2D6YrpjvXFTc
-tZuXJ2jMT9IuPo3IP/fah0EGWAdlMjO3SVzSjZSQdW3Tbl3BkFtJq1/OedMU39D1hnPF9IU4BVgh
-Rk/cS1+NR896z0hW9H3vbukQXZs01EHMd2POUssYXiLHW4sHEsZrNdNGmyi1lwkGDgRcqlyBNIlj
-PMurtlSnbEnktfKUdSr9BJBD6ozYW2tRhzmhfEbG4sMfG0UsT4+PdCowRJeqoiZqxgzJ3i+MfZ3d
-qZmJNmqVe/L7wb1zrcI/ahMnJ7Ia5RaGn+wivu2nYfamksRSazGCEm/hMqRXHS1sY0yEJGjG2Ee5
-lDiek6Of9eSv4Ez48c4ET4houx7pbg6ZOhLQ3haioU2DVstaOZwlz6bVUlXDwfIKkuBoYchPor1w
-Y1sX+X7a0w+0b0xmiMXFSYa9DrqDTPMLZp77n9Z81FFd0f9RzMam6mIDKashVi9qcNzRbL0QeHTX
-AU7gYz0tQ2gZlkK2EFQojoHeLzq1vwKHcl7gE9RQ+mR66KNEP2dlVB2cssZgoQdxny1Nxr2SHCQ5
-kza+asFhXcdFs2xMhrZvlmVxhCb7nLKLrj6cuBHgD/urCaNEV0QiJHL3btIgkoMAWIxMwOswHpt0
-ME72rIlRjUG3N+bcO0z2QAhUjsGDD8MgLFWTIvozwGqvdDbELP1QePXVxVCxtpIqlCYuE5aVoWcW
-xHumjDmhbN8A/7rARpxojRpBn6xj76dsMY6mk5Bst8b+pg/67kicmXgbLTt+SR7UbW8q+5JXvx6g
-1RM42dq9/JLF47kcTYuWq+nBD9KtMgo6vdp9BM6PxxIQwMiivZbRkBqC4LUogkttw1vLYgNXTNaE
-yi/j+4v1YB/0khv76JRXbjbaXMdtdQj8jFhiXBxJIy8n2cYYQoQPuhUTkkurDwaAON9HZpkcoFuo
-nUPayHTKZEWwQEPj44C3aAMbgWAMP5iCwxWaQPbNsVMY6kBTANuPpQzTgXukbRqg1VMnFCSJdyoo
-om2VedFpykWxMQLV7QN08AhvRepdJcqOVv7kYVH09aHNs3yXeAdSuScLI9DiFLQRWIl4qmuvvzJd
-z3lKUrfmnqt7iAIYvOAcFUUhV8T7fHyVKSaopUvqZ2MM8hAC17hdpMEUtgT1Ka5M/VB7xW0mzFU6
-U97ja7nBRHrsi+aznIAzw/oH/QbAoNxwgz+aqF4NsNgtK6b6ACE+WjfORJszppTrxaa2TXo2HFV+
-P3KqpDxgCk7uK1Hh5qDJctyiF4ltZGorLL1g1UG122gI8ltJTefgRBDorOrVkVSZAJKgF8Wegvnu
-UqqAM9SQ7bYXvr0bkxJ23mjy1mce2EJNm/JoGEpBqRVXJEndUNZyvKKGxr/STnWtEnM1Ldanix6x
-gph/DIKHycywlzi3c0I6uk/eRzV8kjPDWW3WFYO43YC3F1I1+85qqy2PTWM9inwKU9swNwDxxpsh
-03D2PSPZ8+RCSRd7i9T46BKAMoHncw7f+2Q9S0XGn6ftJz3LN0YpkO685YKWPAkqECgxm7eN1l8G
-e4RkMzlOdmh4HDy0ljlTBh1/GRyg/W1lPDtJIM5Uz/dvhnDqPf9+RawGewIHiIPTcBpjRDEepsC5
-rhzCWSlofq8iXNLYcGpSYb9yA1dQ7Bvx7DiFFRox3af+bD0XHmDDVPotfr54ywy9bmsgZoRwBhP6
-oebRvAo8TGnZgFVnLuR3Ig8HSWCzoHY7HotH2qsYL2mPThqaWRse4Nviv6k7jx3JmTXJvtBwQC22
-oUVGikhdGyKzsop0SieddNL59H3iR+POtNg0MJu5/+oCJbIiSBf2mR1LJdYrb1815oPxts/bAwZH
-TCnJucqvhmcu2WpX+eJCR67YJ87wOBGc2XqeyB9zBbCzTcyaRiHcR5XNeZEOHxoR3XHlKbFjsk2g
-X7gVUp7j389ziH+/gitXUqW2gbS/dZW9DRkrg3hz9MkvsYLYZzkJwevYPN+AQaNuTmmisPWr8T5c
-krnfqHFMNmPr1C+AXOaPpKF7kL6iVcWFY1XL+RB21bwfpHCbbcUk/Ej8YNzRPIgj3MndQ6kc/dgt
-OvuVlQ7Ansj74sr/AixxPT26YHic7idC5wLQy/XP4eh7zFGGcLPpO8wyXKjBFeBbjOKD71YFd5Px
-IauRW8axlW9E3pdDWRhAQsKKMVJISWHuoPtNJw39TBGKGdcGYMHREj4v+STojV/wXyz+jJbpht0x
-DCFv9tYsyEfOd1ZEGOHWL8IXZWd7iTNhG7mRgfMjPfGqg9m/5znbuqO5M2Gq7orUX3BS2qhex6Vw
-4y2/V30o5VtH0PcCkDIdl/yd0W+5pOqgk+k5SQvsaW2+pwlO7vtElm9Wg/LdBf3j6DX8XMIW27IL
-0w1EHAxz7POck0H9MPoH+wspMrQhhC+cE8wSwT60CScdF0mjfTdNn0HL/N+wih9pqPEvZIrLTQYy
-GYkYuwvtyRnf2WGavfguymTQrtCFSLsGBb8O+4be5HDUOaQEP9TxIuYAp3ls8K09EV/t4GXf9PDE
-jiaU1HkHBSp7LxeYtSpuqXbzbgEZJei/hUSqGpAJZi72U5mXv/oCahZFYgFIHiBNbV6Om9pnRxaL
-3RcrwAAukGN63pwL/Dp8gTo05yYorLfUlcuqkFw9tspyHBB+AdVublyWCv9ZXdzNiiNZBK3voCfH
-Ps8RfTLUZNRY6GYTRrTShOKcYpQ58Fu8re2K4Y67vPsmgHzjQAi7vyqXHB1TX91NRF73jeXh2KFI
-5MEKW2/f5X2x7xQ9pWsn7BwMQiM7r5Z1cGfrYdNz+POwQYNcRaW4S/rAhYzoZqfKuO4LC3/zMAI3
-3uusu7GF+o6m0aJmdE0bgEuctiObzuVfsvXBaIL4cQsrddgU1q1x8684ZL1YiWAqX10nvoxJAGjR
-TA2RZRhVzuz/SemN/bY90OzEP7z0J61E/cIx5BPPI3G3sn9yR/XiJiV+zZvgNS5kWRYjdwTJ1Hme
-bR5XcNNrvD0ab/XSfEkIVYdY0vkjs9Te6hascYY8SHq8XB7tEaAwc4QBjmYUI5uVUPdT+rDWLpbR
-Vd1GO8zA8j4uvXFNhjvaD/nwqg1xLtvt32E2deseStq+dIPwfgGofzWW6n75WQyRxU6jiXa70e/W
-o0+cWQZcbDISYHkCUP/GPE7HFpDqeJ5FgQ82nIuTcaO/guP/yqNzmpSRwIjKli1B08bJC14PNhO1
-3HBCBBjuKBB9HKPlMcRN95RH8bx2dCV37eD+bnIoGX2ARQxqbAqtdvHOqjDWF/GlbJv+E5FzYpjD
-GJ45JfnUVAJiaBIPTCgmo+I4a9c53Ei2hXRBV9nNa4Hp794FAH1oIis7jXNsHbjYTVsO70+DCEls
-MpgCIT7cORzUVTzovbegSm41uOdjSVnKvTZzgojhv+QS8HVT0iLh92Wxoj0QRCZBF4MbbOWB3B0c
-7wEAj33nRJQakOGiJIcmaGDjZYIyBNhhaOar4/a8nH1DL+40OSdMX89mHvwzLotnm5doZQfTrtdR
-QiNT9ULJ3b0ZFnudhxAYZhcHKjlQeobXwbhA528IWbmccFgLkUb97ZBo1mQYc+05AcGaowL0Pg/z
-RKTNCVmQHSrDXk1ihT8tJQEbq8W8xcECx1kSqGPLY7gxscRia5ZS7iTL4mXIFe7aZVluPTf0O5BU
-pBe+eA2y8ClUZCRHP/kKC+dczWA9ULv3fkDIHpLmU8K56CzykXQNDq26fzNj8RFoKmykIh3ZtYSY
-yqcUSgO97U3y3EP+X7tWW109u+3PnWrpwsnC/C1wi/CAK5QjzaxA+fQx1YJORCuY9LdRLK19TbA0
-G59mZk2XbMqLU8G79lXPKfViFew2SDs92ssY8AZkTXDnjHiRweBRXxPL4ZRpHzOp0x+dkPUUXs4i
-9jT0cRoUnBZWRWTYTuoqbdZ24NtIjpSy415M+BoplnizuxxzNSio4BjPVfNNdxjJTDm67R1/aHGi
-2/uVCNsegdDdEfwKLomBvb629Gz9XkoOZuyH05OYFk1zQVNihcOt8BGI3nrh3u/d0U8bvM1NBYkM
-jZ0435grQGiV6vhX+9UvrGr6dx4N3OsQDRLNUKgsg+UM7E2UqLf++BYMSjxoa+Y1NiVfAjOmKb9P
-lwmE/DIIjpmV9JKXyoHmQIBwYbnqbQ0iJQpex5zo2L6K0KmaLABCW82+T18DDWwPWRBbzdqrZhyq
-WCAnYGax8GF3u5F4hXvXHxlHcYxrRlfsuFH7h2isBQHHVrr8WrfW66Sc9EcRNb9zmF/rwQy/uZZb
-mOxFW2zszv1dceBj4LYgWAGbRxJRox3DZx4EK0XLf5tRNupiwjbnSGkHHzQ63QokWQbUxfJC9Q0z
-gXoHRYhrJ0cd/BQcyHeLBlcSp1l4Yco639Pli0dcMxPugV3spKiCp5FMMm97lPGgdKCCd2MeegfL
-SnvmT7lZFzFjH5Qu3NbK03/4dMZdM8wu3vtCHHDkX8PZZwxZpeS3Ch8fdpEW1WWwwHmgrOW7Dv/7
-soBEuiUWb5DxkgYOXr8C40oUgoSNnDT4hi816K1f2d1JWZAncQLDnUOVPURz5T1Uk1WqdZTG1EhN
-VJR40DFG7Ttr28uAsfWz2DFR3HcTD3C2xF9NblPQQOvgIw8+HW9WMh5bt3UfbJ1/JQpFD3wHtPJx
-0p++HCiC9qkMKf3lccx1tYEpRIcNYEbqt1yzDiFHbDrKTsWmVHa3gu97z0QQduPYOa+Z7DbalP0+
-EfHy1mjolXPWQugsxmkzzw65o6o/eQBd1viw+wO3wHyH7zO9jpKu6GgMf83pAHiqaMje24nuLwXA
-3u2MBHb1y5ToR9EE/gvDJlzcWLafKL0Tu2G25k9Sc3+qBdGhBO/8QEKhfmsEewexS5u0aSKeRozA
-ex2EUI57UjlixRQlXNbFkiZngSzJrYMeh5d8tOk1cBn4bF06zykuIKBwDhLDkSCLYQBmHntyQNIw
-Xbz5eTalcyDICrNxTrigtbepmjgav2V06uloe9upIy4eJEDwn0oMAaDSOvsNPF2/wtRO9cugq9tg
-1tnQ6aC3bSDBI2ecUga/38etpDdlKvSuNhS0mdL9xfwtPd86Yu4qTpPruuNCY0R96ylhqdVFUW0N
-s79LRev2e2TRt5vZ064QnjmoYYgOpZT9mRyx2JWjsq/55Oo9QwZkzkFOEu3GyI7W3Sl9zvVMiovX
-kj+VoWDUNT4e7MR55FOlsiAkCXFx0jEgvA8HZNUu+JTWUNGWu2aZo7/GNHBjmb5wB2TqNp+AYkH1
-p756U6KlvmSLPz54o3y0smXToOZdunkIj34VFQn5haCltTBDjOvsYOEX9HrcFdIB07q0f4mOONBF
-Q0YqUeuNPxXWgd1gVenByyr+vlZJd+9wUDj79nyoajN8lXiqnW2irSmihKARb3y/v4zbFfsZEYGt
-i7k6xDqHaxu4A7pAP2y/yPe5L/C1T04e9CsfmQ5xh/mdvfF9z8Iz7I0hpNWQkWLv6LNZqPaIu2b8
-HIxnHgvD/ii7qFgNOReD3mvPURMotZJhwGbDzJzzf2dycR3ATSAXF8p78DJW6KG1H5k17MTE81sH
-5tWpgvJnoRLmhYBA9MMELrkLRroWxwLIF/dtwGUx/UGA04RTEVuw2g+LgSzdLR1GywYWnCkca2OX
-nvw1JUR7aHTWYClmijPP7AX5bzRQbh5u5z1kMJi2GIOgtsYUSDD4n49t3lCppWbfPme14NUuBgZM
-FsWNzWB9pv3c/0pyzhuQ97V9Rn1mt9FFUPxOESu5JvhTuPcmpzjg2QG90Y7dO8LQJwUA39OcVGzj
-Yf/quTndW10AdoztVHw43D/fB2Mz1oGrZg5Ag+MVdw3FbQrjd0nVJqC+ROhtWc7NU2zqZZ02cfgA
-PinaurKaDktT0vuI0jfsHJW1/q7BXb4Q4C1SuoqnwYJnT/fy7YJTIkvslqh/YuLlrHrRUuRYZGo+
-xBbO5yW34r3Vze4T3A59F1lMXimn9q+YPKxbD4/YcGifH6sg8w/QcrOPfGi8164Ez04hfcF6UNmY
-OSDO7hV4OqJeZe/cFy4+W1buOmbgNag1fZgb+Ie3LFbGTiAag9CuRQnKdcLhaDlAeEfKlofGxeTT
-LCF4jDYmUhh2IWXlkfpbAN8A15GSWlAFdgZACsvW9ZyXCG1/LWyHshhW0y3z3frOqtzHgO7DnQpb
-4FPBEt2bvmu578/zt668Tq9UPMVP1GZMUMoCuAa2cOorQ9rk2bX8+ZEBdvjtxtQoWCZkrtbY+lT0
-kVloG6kA1LV5/Azqyjoab/hQ6NDlqh/75QKFl2Q9WLs9Wyl+F2FGqkrqKxa88m7mzHUowNpu/Cl+
-o4qE0p6iExwl47l47fDrPE6w3+aVPfrFG03OzAjgA2JuElqupbdceh6IdVOm4NBqEx1VXt4gY/kp
-qAVyZBrHpyII7mVa1pvRq+ND05rmiJah14uQNW/EPJ0ciXFmKXr0zT6KKO6Ijf1BKgTXBzT2dyv0
-rnGfvlK3Mj3mPZmSKOUWV/YKhOIU5LAIiqecOaHADXXwY3zQKknM2RQS5bWam/uypXWcpsmjx3H2
-iVwtugGXqLvE1FQKcHnyLjJK2gO63+9YyRffNmcKazecxALAXjVDGxtm2qGg9u6DgktCtFWd7APf
-r1+dMWLhGphJH5uiOTltOJ7RBPCE+MG8gXLQvVUlH1Ss0mHFNbmjxIVBtc3wQd2WdPh5XTjRBNdl
-xcG1BLaOdsS2Y3dyN4HChsw0Ajpb0TQAtpPwwhPLNM1ujOTnLTtHu2MmaZ9HV/+RvYPWo7LgkIoJ
-aa9iFHnPuhUQQfEM9cq2z3Q6m19ubRH3cQPALRnj5YrFstouQLsessRprh2Hi+s0GHeb5bX8NJUu
-AIyNsz7PNcDYPHHiv9BSKUpR5bzKFy6lKNJpB0dCEUtivJS8UxdkNlK0qAYUPW/KBpJK0ARALyby
-jDTMuU+OCGmTbhRC+ZJX0J0nb3hEG8h/VxPz5JWQDYxQhEjsDhiWTaj8D3I3M+vZolAN5+A80rkN
-JbycK3xbgnkC3v/fXZr4Jw4q2W9EQs4Q8LOZS0MMAmdH2UjSj8EpHj5uUtC7neLKgkhtD58LWEbg
-0p74xJ+2PKBtwGRIUmu79EnxJ7d852rmkMlB2lYvKfyTLWMBrveNZVYenbrPUObtfT52wdqNw/yq
-CcPRpUvX3WnIi/Iv4HD93LC9Mpgx6UOXdEGAd4K8Tj0U/tYq0vQ01p636xR7DZfnxn6sKjPhcO/C
-CyMrgG00WZQ88r56YGLgP9cjF3CrNeVz2VrfcCrjXdizf1J8dMqzWTHOCQC5dLMDYlAjK5a8M6um
-HWz2RGFhDCI5OHSLe1RlATQ2tPR1gdeLPj+N/aZqIrlbeoQMWZChJdTt/HWLOD3j0KHFRFojCUaT
-jvljyOFgxzAuPdUt7+HUdzWPLVd9rs6oBUyj3OvUqvRaJElLAzNnL2A0z+yunHkC7tJsv94BXFvE
-LC0vz6qs5tcQOCa9yYTRfasamFlzrN1wRi7fk0KCW+qsNP/QQHiLFZCUCdkBfRv7OnMhS1jlLoI2
-QJTxFpqQItzHOdM7NdTeOuHKuU6Kju2KWd8zathwCAIQudNy096lPaq/mGsMsf4seF46ZzlqA1aO
-743WMVckkNaJ1GpG9GteVcKDfj0hn6gIXcGE1BZhyxM8lkyw6/lei+EJEtyAM45kGcTOeIebjDMn
-6bx9w+jmWWliHJlWAdm0DkCgip0p4FJp4r8LjFx2ClKPZc5nEPrK24kqbI+tntL7vgDU46eK7JPD
-z58tGAVXZeTHfOTOHxYc66JTo4YtmcuYuHdVsQb9L7xiRQGv0pDRnAJnDbjyT9C16XYO0uqzGgzU
-Z9qWxGtYMf8IcF896iYtfpG90PeBx9AFnRYzbKmtihWpaJ7+cTP/v7bL/39UKIsl28e1/q8Ayn9x
-wr8Ow1f/3xnh//13/ssJTwOha9txGIYJrxvu+n93wkf/m5AGyY7EdwG7xQ55lf9TZUHtQIjH0rvR
-JYk5/MsLT5VFjKOX30lliwOI1P2fcDL+cyMLunBAvM0OcThHLnmr/+iFH5ohCVlb9V4WQ/LMAmIe
-YEPhmfES0X8T9yzPk510cv1/fVD/jffdCf3/GNaJfEpxIdPdsiL8w8M4+E9/M15eooKB1vvQH9Od
-6L1AflGoDI9caAdn1ch1Jl+Lfho/KllQdDH7LQJKTPZ5pIaTiePerqTjrlXvVZ8pKM2BtgeuWr5j
-MBXHPZBPW0mQV8iVajxM7q20AeI8bksG4KgREjbdtzdxVR9M3+xdwmBY8er5y7Ru8lbbRZ0jGGv9
-RMQ0ksi66Pgirzg4xDK9nVkdd/zAbil2gcNRO67rsy9asZ+ynblZEdXSfFPrCUuEqdnSOu1Gpe1v
-XfXOHYV5xROVGtF7soTd3kstepVqXKHrPPDxCFONlL5ausJstWRWezRYl9ZNav5ELc1YQOHxPhTu
-cXDngpBr/hjnY7TTMzethpbMteU0b0KgKU2SXKUzuc8aTZK+BZfJfdesceI066puRwBeHpKAnDbx
-DNzbZe60yaaR39h3AbeBsFpbAwfzUPa3uDdpTIvW4Szxz3agNuAMwJx4/b5Jqx3XD7SqFHx053GI
-Dnu1hh6CoJy35IHpfH2Y+rHjfC6xBKc9cU9wm7uBVjI8ev645uJPWDhTcDsnEW1LOnA3tG4ytQmy
-8Yi71tlByQiOvg3mytJuh/9mHE9oW4K7U46Xr5ipmAjgBZVpgQVYZpSB1iUFLEGFw4rq7f0y9TS8
-A+kFUOtk1bHBw/dzS0cdRvLFeF5C6x7NqTkS/mAosFSq3DTUGm4yNYoCL0CaD7eOPa/AMpHX2YZz
-q59sSo4OUNE8X32ZCFPLWi4e3zvXt+gTYTK+REY431CQ6p8hMiielJFBBXDzabxmbXkHm4bE70Tt
-KjeepDsOpjtntm+dKEuSp3yp2/c6Dn0+66JH6LeXIV+2fTAJ+oETNPiVbbdhiGUobB9rGnVvPbzB
-rcmkLSGYM+S591WJfj47HgVIqnb2oKSqel9aXD/qwOq7jVX79oZL0uJuGYZz1lgiZG679wC/q87o
-J9cazM7PcpOdoDbCrO/sLvpUQ8xZPHVLGOkRt5k16iBwa04GR9DvXDLCLqvvFl6oY+lMqaQTIs4O
-RDD8l7ZnDM/xJRaGD/M2AfaMT07bCSU1YXWr3+CzBPkqTiKo+uHs3mpAQYRs4TRk3clMqFpthxwT
-Mj1/K/HcjPuhdvy/TUgf547qN9MznO48G8qtCaxrHA4T+ZAOxgraXsl9zu29dQOFumJ0gWGTUwJM
-Q9FRgCVtZyf5n0dXtIiu40LzBz9fzYh8sR5S3/yEWfmt6vzOgZ8rbctH1MWLWmu3Oug88R5CHxNi
-50MlH0q6wfA63SWDKFeLY1FnYUu1qRdrOBSyu2/CRT12hf2Tl6Bn0XG5TOF0OdhFxGUqikqmG/yL
-IlPLXVZH4jFPrWGPRTPmLD2724Frw/cS9nrHTTK8t1G4iP+YdLrjkDH/rWsymCt4zOKc5LGb8wDH
-VK0sDTlzBhSB8x3RSH+q8HWdkwivH+cfJoDKGbwNviYV/ulag5a/iiAerYmL1LyX1gfuQtQN/LDw
-5gMOOob7VaPHp8RzUD9zkcY3DK0+LePyR3od64dqff9GbE43iWuii/bIUvjl4tFfYmXbqc7EsR3y
-+tGynbRbBx5IwFsz9TWq/NJ70RY+drosy+FYZp3+PVj1eK+mWzokp3cArWYwD3Gvc8TB1qVL2Jsj
-nqyUhJOls+9YF4S6miA+eDG9N1C87TWWQj4N0KavcUVTBshdpmjzxJ8w8wBnU3l/m8mupyyFNeRC
-X6mDEwzk6CLdMD+NYfCX3UncAxSX+6rnKrgKeVLUEUMtYS3uVtmWkRGnU6EyBziI6fof8l4oR1nZ
-23dRSG0wJ2SUje0tlUArX6Bh1+f6KjjOvQ+iL7dV5MV/bAzpOM09yhwTXph90OlYHyTwNn+rtY7v
-u6Gs3yK+p7VGG+IgSXXbqEMfb22XfhuKwv1n1dUss7cE9bBpB8+eV6IP+2IjOR3cjN1Zvy0l2kMm
-KEMtRvtb5kELDpSCuAo30TkSyeZmG7aQZwFkzcqlVEBRJQCtOPTANdUjgxhfxjGdHp0YXqbSxeKT
-OsTAIhVRcIQvgPpRPXWPJm6eUkbE3FAFPg9ZW4/V4Kf3swXIuFTpGn0aXE4v8A3fumW6jNhUdqzJ
-gyDN+P25oDyATJKmYFhk/BPyC/jMny6afxvW9+Ok8CLFtmuO0HdoaJ87WAsWzcoig2YNwADkazVv
-l7EP9rHmLpPi9dosOQ7xllDOuQiyt8xLsm03YAuebtmGCXF7NQ2+Qva2lvxaz9Js24II3pRukZid
-Hdwq9w47L4Mha3AwRkTiZ85us+lRD5dKxUAokKhW7YzURH2zCxYy7ffyxqvgG5ow2zC1UE4DrXBe
-XtMKXyttkXJbh3ywVdeklzbW1IMq+YqCQptg2/SHgYj87aiBZzfsh30bxs6eFSg+Z4Gk6qvsw609
-4q4IoNIfYJJS+1gkj8oyvL616z/MfO/2VMFjd3s9+3vsMxhAcDHse0iAK8/rPV544Qdnjgtokvgp
-ERZwQexoEVGPoZDJtnAGRYkI2sQnEfTqGjGtPdvQIf8CewlhbNfO0cF+8l5IzPWjO7d6NwVMN9c+
-JrRNFtnpXztfxkMYGHgnQ4Vuxzab7i0idgK0l5PD7cU/vy6hJJ3CzAfs7RbeV+L03Z223fmhTggK
-rizZIKOnoxueMPfBw9G6wFnojuIZlSQ427F2XmhXSP9UKl30SjbgIqmsFiULk5Mei8EOThkftb2G
-0wq3ybPEiVdFiZWdGZ3tW8xk+9p2HXJBwBrhtUNCrW/j8dytsh/MFjZgNCoJW76EBjdfHFsvLn2X
-B8Cz5kzt8bJvbKM//GCoz2NHOygE9zC/N4RTdq6itvU02HaJgTD3lhfsReYPqbGa1xTHybWPEn1N
-8lYCYhIhE9A6HdcTR/tdkZbqLTatfZ8yRT/lKbqGuWFY2PyQ0lc8B9mH8DtsobVdnQMGQy96qv2D
-boR+shJAB4Mbpo+eauMLzQ0Og/o4+oDQhe0Z+9WH56dH1QIQCofsvo+L8M6NMyYonRVgVIxLhsgr
-iG3c5hfiRLTdCXpdPQKeUd/vW8vlwDOlVJRGHTeL1Yjpn1kr9wZAU0Fa38N9yfdJBYPDhcsCE8oM
-V0zuyzGS/AQNWNFXL9QaREI/eIyDpzBjYucWDFym2/5GGaw2LGBOuMFFTRVLpRTNDk2yCz0UXGgW
-HSMoHCVRlXwhsUFbcpmXiLgxe1cX4a7rZP7DoQVbcygHwYSwQmUaZ9Ps6+A2v+20+uSlXa4W5N31
-EswYSHr+ktiy3W2BEWULOjlbh7WXPbZz795PytZEYT137p7MLLrq2aIBNtoMciHVhsMmSdapkxXT
-amj6GcXE1bjxopGcH/4Sbe0DelGvtT9lLzNGU2SF0t1DgqViZpn8bD/2tnqSxnU+xzbxX4iOMKw0
-vZt8jEuWLNtCiOY5q638Z57C4mRBMvjqfHfImFYJwdchw/lqc0D9w/BlOZGrpUuhFnN3Nb3DWrEQ
-DObAplDV82Dosj0SOUt2r7zxPeTr/irTyH8NQjvsX2IyTMN92na+t12KCUOeo2Len5ruE+0xXSH1
-kRFvBjBMARMGJgMh1uEh3IwAuQvO7aReh9qEWPlL3l7fMFPGW66zc4sdHQ+t10mKZ6I830yW5146
-S0YO7zvjSPxpMjt27eh9VogpsPYSCSPVHb9crkTrzpfdtQ/8J7hKG+ZHaiNVHJ9RTLxNxnMISSa0
-v4oon35lMMYxrgUCxLO2PoA8BMRoE+N/hsLMJz1MZgcpo31wAf89ZX6MXd/J5vTgM1jsjCyPnKhz
-kI7+dEARXA4jH+GXjjJNyb0VPvqId7vaouZ0aKMHwRjoNIQU7456LK6Nb/mXZPDGchUkcMPWnRQM
-ouKOwsCoovSl7RfGbEGUXrI8/jVmEL10PT8xIIZhM3c94UePqPdKhTr5O8YyAkleix0YFzBgk5u/
-9XEyvk8Fb05lNcN7wTBwk87o6A3D2ZOg2PwJnMnfzM/ttSuH5NpxnH2sbqitWQj5B8vuwg46udDb
-y/CFef1wWjLb3jrLML0RFCE0ZpX5vcL289guvbdlXKKabe1IvPCpP+F1zOQxzOr8SSMAbDzEZonL
-aZKPNAtX351x/SeayIedWegIwtXXP2jU5WMbde+jPWN4n2OE2LUATrid2yRe95NxGdYOy1cegpxy
-5tFel5XHGWgo3A+dt+5Fa1QMrEfJBwHd9Nc/iGBKfdSRbVVfTUaXEgJkc98MGXXhCHAXpgPl88Ap
-D+NwZfu7hc66E8AReUkVj7xWrPeRbMdfQvQNActBfBmI/8GKbsKZhhkdXeKIy9oKCdL/I9hVNpDV
-Yqqd2VPiKdDrwnDH8tJb5jMvmJjo9K2KA3UKZFq8WS3PlcrDmpsgJtpYGgTknGBzlNjuKcVjvbH0
-WL3MRrqXHLLfX3+a824l7MalCq4Y7u2aPW9lmtT7iWGIAPnv6/5sZ1DYVwvFZweLB83ZepVG+ByG
-kiJLZnHZprV8+T7Msku4d83OMwF/+RL1rvqCi4a2Ev1TijUnXYPNtEq/psFm0JZQsVKcFe2JsCW9
-7G35p1Kr+KdeC5ivDxe0pC8vGybuV8EovG8dNuFb6zKRxAPYfs2TI0F/2dE75isswvXQ3mWc1Jgt
-s3bwAxU10wjK4wRQ8St8LmfrIJof+CTVQ+8oDbpeD19jPcLyvLWHKZckvWoZGZnRo1vs1jKmoEJQ
-DCDkRx/ZYpeVtQUoD1tEUROicCKw8J1u1xR8Nj9t04XzPdVCeXAg5kT5GW0dBidI5rw13DZQ18tZ
-/NW2H++SHk+uKZgzrPARgc5rGUu+ww21wZJQf6ZQ7YEWDVPGmeCfJjU3V3694xTQ3xm8Jp9uIhhA
-Fg0PkHAWfgYL+JjBqjwjBGXNm19jEf2np62LTPO10MXzt+UMeswDi2UotZYNWZR2E5CY3Iez+MY6
-+40fs1yNkaHtLzCbga15PQ2MpbGF2bfD2BuLTHsyvXq208ndZyRSzllBwRwwSmtF2VKwwX1KgkKS
-MBnj6yCU/5B6aX1nZ75rrTz/1lw3p+UxGJrmPPm0zorZ8DhYiH6npe7HdlPl3m2bqsEkDd0miTDD
-tIniTbOWMxOy+CIIO+HiT/q9k6T2N9an7Fs6NhnJsmlrfn/VncPcDi6aG9QurLzhWpjo0Sy5s2dv
-ngjQ4l8mbOX169EKpn1lJbQ0IUo9BC6hdDShTztMsfzWkpHbprSa4oGTHdE4m/Xqgv0Sku2kAjT4
-JPczoBVcPOkyWnz0t2XYeNRgvNlVVOE7nvrwiaNB5a+xFKcPGBFxVzEsOQy0WGNw9gCYU2iL7dHw
-XlZpQmOOQ8RkWIYSL9GIm88n/xet/dFN37tMQ2HopfosjGdfCpy6zApyiwXc18GTJ0ZMH/xt67br
-0sfcsb2LLS36V1MohucRrMjBa8vi5FKPe6a1VJ6FL+Jr6OAlbRjGZRu34T01Sg8PiGsMFAJPcaSJ
-I1qOOm2ZabX4sthmvvmdLN2yoV7RY/rv2j/WkpVHnS7pc8jKtAoj0MRsR4u7wn1W7rJizHZ9YC90
-EKC+5W7Udisi3fFlLgf5tFizzaPXwY7ILa85hO20fM26ik4ywDIZBh2r4NxStOl6zH0k4hX5c0uq
-B+4E7luY4xDa2LbmzIVPzlNsZkMLXyliNOWVDqNY13rFpgon1kzAFU2NqcWW+UwZRzU/RalbrTsT
-W0eSvPJktXSpG6vpftlM0TdW1oqNgoXHYqwOXNf3xJi6B2238GBKvFXOMrOR8n8DmEuUd1VzNO28
-iu100+TMsKiTT4ctzmDecYzx1I5RFbAfy6532Hhcfe9UiXojOOC8xVMDAWw0TGJRrhgsEi/D0l/R
-Frfy/4298+iRHFm783/RngMyghaQNuld2Sy/IcpM09sI2l+vh3UvdC8+yOBbaCFAm8ZM91RPVSYz
-zHvOec6Q1E/gZgsChY4ap83s9Wm5M4i5VmeiI4KRbF0RUoCXywMZZ5HxWqa2ou6CAsR1zyE6W2P0
-Qvyb4jY5V56bXGNvphYaQgzD3hnwzbDBF9D9Sb1i3s/d4H5kYnYf/TGorJ0HGq7ZpqlLE5sjK9at
-tImDdpXnLoYfgLDyUeHpytZDkAh6pwkZvXa2TL96mIvzOvAH0z6OS9/QaWbU/5TYc/nWyJDikLRE
-UO4kJQyR06iHforwrIhJ+Pf1wCBO9nZxx3bz7lhJTREUiQ4w3sGHUcl4V0Otha/nyZPyRfGSknWv
-ARuMgPPcWGyn0sKwO+kjr8K8VWY93uJ48XyotkF11Zo0mBlOMzwfF8EYXe5eTi4jhnTw60vUzcSt
-dCP9H6YGLqHxElc6/hKkA2McDXtjeEN7YIaMzNhGRE4S32WDYIQ63ejC9rZd/JDUICc2EQH3p0yH
-5SUizmNnLs4UQWPnTSjYCQ6KbaZYQdHVX36cqgqJET8bnEoolyumzs6DX2McWtXDlNNG400YCrRk
-UrvpK6jCGymrFKoM4YfcDvSDxIL2yuB8eDDcroS5Y+GbKG2116qWzxJ/z52stb1NfGMwMb+LaaPg
-ON8pENncywff/dCgBN6T0c3P2GT6+9YQJPNQOGP7jG0E1cWycn6NIRfcTgmnrLX2jP4N9y/5YZfD
-9S52CFOYcTLeYXJdjL52Bhko44V4qNJ2NtZRLaKf0ILKtU5sy7pGIYPeVVKYxTVNPLEdjZALdODC
-UQeG7qxBBHCRGgvp3LbEnB6bqDLpPJDl3WQ46P8TPWHvM/WvxIHShrt847s3pqKtA7SjSstDonFW
-unEgAFljzMfuB5t8hRIfIdFAyT3hnA+/sQfNn8B5mZUNMQe2VW9iAd1ADiRlP0mucRBz8leeNpAc
-ZZ6wEzD1HO+UKcPvwdDLAseHiNxS/uqB1ztK0r43pijp34khA0VNoc6s7WxAKjB/lI3CvgmIie+H
-mk5R10jqh9GlrWekp/sCLbM/UqDQ/VFQv/cuj22zGvwAJnqjx/FvNw2LTZt3G+4QRI60q8tDaROT
-c1i3SYFW+ZXYinOCfQP6IJu6nzJtZL2eqZjb15ioDqlNXhd3adF8WjXI6S19JtUjVySm3/iDn7Ne
-+g+YW/Pvufa86yxafmlZh1TUQ3DRpFtaorPIHYmnDPhL5rDteA2v5aD0NztQQTm1NwRPxmwRMC2L
-FvQQ0VuwO556rKolwDiztmAg72yC5abW94X08nMNDefJglq1imbXu3dHgHkrcyq6j5mx2rIh9+LG
-75TaUb9E9i8qh/yRZu8sxb6SivoaAjd4oPKMd4TDzcU0E/cBcas85qYVPypB4EJkI6U6fcNVw8Ze
-27ZWjDltCO9IIrsI7lV0x6fb+Brpzlzzr28xRr8tSVqq2oLZvyWXMd9PBKgby9kUGZ6eJl6o32kw
-QZ+ciisp9GHfVl61TmNSC4kS28yl92PlMro8amU66UoOY7JNhek+yYGfCy4iH55p6c3M+VyvWkMN
-u57rKwpNx4TDSIqQ1HGqP7y4cu9D0yTeZktc0yT22bD5KGMD9zt2OTx09SnpSQisgIYrmuPG9oK6
-+g2oV9CAo5VzF0fCI0Jc2Q8j44yP0vNthyhnSNdG1CHfxB1P02BGB1bV8L5KSh+8DzOFrO3En7oM
-yXrhX6YgwaoURCTG7i3BKwduDXAVEZ07wytfMWJOHDoDjiwxE87MEgMVfKgtFK5b9Qt6qsYwRBNe
-3GgKE6BQbEy8HVtMYn61N6Vjs5tGGEITrYsPeF3qBu2w2+Yu/olelQpya0bgh+3+3fRik6BjByh7
-nZl9cOpCh4Osl6JbybnjBkMaccA1ohjlFA2l9qg5jHtr57N2bPxIwIeNY2gA+7GZkeBuZo5xo0fi
-q+vAa+qRnoP46pRoPtScD0+JNwJZHuCRJRxbn5qx6yB5Z+Oy/odld3GDFG8ZDufxo8nQL8mwcelh
-RMrRZCbMy0qVshiT/fHQYTIt2WgyHd8A3TW/cun4xXaoQ7JYLfElLmkBMXw6Rs/8UCCr2INJcday
-P06Ojti5iO4fW+VQrFBHogQaGubTa+NnAt0mDnZC1Oz5ZRPrbQgTAQZvKAwqybxkvumSkNVbDyIj
-6u0qItaqkBi0J++btuWEWZ6J4rfKxordSiR1aKws3Ny3dbH0BzJoIzScxuxiK0pmwBy7biebSzAS
-sV1nmR0d4KzQSla4tvWc9y06iigzCoc8fGw6NIwjQ/aCdF+rlt8Y+NARnkrEM5qtzOm3FYW3LkrH
-+Wn6pLytUVAf2Lw4u+Rsl6vQYWs/arOwso0n5vGNebPYkjuiQGi5XRWg+XddFIx6baMP0u1FjHhM
-cpN4Ti9+ssVnrhn3AYbO6Pu2rQ5guoOLAKJUUJznwrROIzifW/AllMRay5C8iCvad1ux9ekp4ZPV
-C0xewwMMqHsZq4HbtSJBXbanKSzzI5kPg65Ri6Dx1PR/W7UDZIrjxK1YVucImPLG88zyYvS1WIc9
-/0SBJZkYC3P5m2k0ya2K4uyGTA8IQA3xG8JEr5K1dPRb3NXzAxSt8lJl9FQooNtbjKbFMbc88xuq
-M3Wztd9eaBiL70K4PS2ILBjQhE3mb3gj8SGyAu/YzhWNr13EmBjbk7P7v+L6ucFIW6nqj/6vi5/o
-f5Q+/pYY/uvf/h/yBlnIbP/b6pybz594+p9TMv/xpf80B4m/aNe1Xc8yhUmZjE8V4z/NQfZSr2Oa
-TBB+rUHYZ/7pDRLuXz5fAMELGxCZzKWuUpFsi//bfxHWX7gfRBBQyMM6IoP/VFGk9VthWf87oBKa
-rutCAyQI6TGtX1id/w66TSz8/nM2q92Yd7G9gdsb7y3Vxnc0cZgvTIWtVx8oO5762csvxChI8/kl
-Dg9/SNJraYsETybB01UzTPYPKSzwyFiOaMKuIuFeWE27+CWKqpASOqZeL4AGxIpOOrEZDWmyD+WP
-TJTHZ4B3zlrHXX8HZ+YF1/FooN2wVDs14XBapX46x5O0FRbYcZEgT6Bp4mNL1/09XtRcraTnjNVa
-5bogpxyzzGox6T27sjLXpS7nMx6uwVy3nT/hywn7iSA0TrqTaBvoYW4xP/aBquTRxY1xrU1/7kmk
-tP21sKoiOM32wKkpMEEirXxbxP1RRBQ7U+wW1j+G4XcTiwomGfqDzEhfurEMghO1bFgnp8EW7cM0
-ZfWPzZElAUoxZv0LcmzwU0FA+SLKVlkHQS6noMsGZzyCAaDGJAiArxhuBkCeo2E5nGaEmD+0AOjq
-dmQc9IGgbz3RQo2xog39B2FPzh7C/TF2pTROtQEvdF/lvvs1tYndHwElYZhoQnRsUIou6c14ZM+B
-sVntrBSnLlqFvWTyJhOqVZW8d7mN4NUYoOhN5d1iTJi8rfIb9qF4iND2mbicPUuAeozCwUfmaYs9
-rwqBLO2A0yK21xNtT2r4C302rCM6By8yN4rsgyGE+wg+Hp4C7iPzRMMdwg92fOTriDtFHU4sosS6
-knXdFdxZiUfiVAdigqFAiD01a96JWEF0scvsuyt4Wljos4j4ZdVhN43Sq6/QQRQBz6XhEz3KD5ng
-cKKN14iL9JBVY0graSf/RHnhv9pEEJaKYuTuj7jGgJTUpBC9DmSpVZmMzHrjAJM12gS0K+2pKdTx
-RhdBciYV9ljLNKFuBmyM40zOg+c5wXvb5gkRzUS525xh1r6BaPrdFsJNOeIY+VvfcupYoZqNekWS
-fozWnk0mh6RHCYcoT/PRJ7RNCcGJCkpj7/kztRRTHpEgh9+woO4e/RSyNzkNu9nbqYZbuOQabbt/
-b22PBGfd87wHA+gVzssK5JRfhb48mCG3JbbBLmbgXsU0PoLAzwHL0qFE7sQYhqPpaeLHQ0duBEuE
-CQbbEj6X/Tro4zc1ICCBdYp0tauk14+XhvaXYAOQsSHY7wvu+FyXRbOOjcECe56Qfavd1n2XpEsM
-PBARFqJ9WHT2K3pDY9w6topbhiREaHejhZ0SUKUicJe5A3F+jmmTuUlH3mhsNaXDgVSKqBxv7caL
-upuw9wcwkrhrOLoH/FePsT/QcjF5oTW8ap4uethpUxx3lGT5FaiY2KzXgDiZbdbzUB10jJOBehAy
-rURzmmumKq7UiaHxlw89nIc+r8io4F7kpDVhq39p+UbFmpKq7O980AEw1zBsawbGjcFEmMCx4kGa
-mYQr34BEUdJJ1nMTz/9gWW84S8mBpHdaZ+rIk8kxCLyFx7GstTkNcEoql/OSa4z43OzAg6rU2U77
-JYMco0sRc6kPuaj3q4Q/YpEYBSg+TmdkfOlwMjPL3uXLwc0x6yZax4tIRJcl9eyzBcl5EzoFx7zs
-98jHAukp5qFdU635EYsN0xoOiFksCYjmY8YkMi3b4Z0jin/TZ075WiFoFSvggNNtt5w5afEIxlVb
-04jKOhQZm1EFwwFY1nDTB01wHxp+TuhtOcWmREEfHEbCazsuxWPRl7HNvNpJIyYMHIDDRgREw3IA
-w1YzJWfNaXK9ONeerFLIVxonhp3VSkK8y3G6g97PmfX3qD0up+4x6vO1NLBLLvUqyDyRP3d7c+qC
-S10RcyoNRfQmq2gXje2yvqM7svs0lxN+Mlj2C4ev7Oh2fboz2z58ZLdM/H1jeeoJcXL8Ykpr/4BI
-HJ6GtuBq55TXgGUJI31Dmec27qtr2i3QDzXHNX3pGSuvb3nRgcmjRK7unX1flmmCHUrDJXXSgNon
-+CnIfSp33yOPgeGmWy5F1J75f8C2dquSRvK1CXqB1lluUJ5XGMg3zE+Hgyk6ucUG6G9ykVeHougr
-LsLpcOv83s8aeI3pbrL4gbUZWX/XFamCLkxlvBZlZNWXqZBzvVGcHJ8betiJpo6wBVZlX9tHohH9
-mXJLLpPV78VyWu6YDsEtFL2JOGZDzp/QDpdRQuTfbM3tZV5uqunvpZWGjPpUj1l0LqwCHxT+h/LR
-Wa66BYA57gh2H9zxveiPYghMJEXlDqgu1fwoiAkfk99bdMh9Wnnp3yhuQNq8GUtQWCT6lnevfDdB
-lm5GRxv7tNXOvhJ2ukFk/AHCMt/HyxWfkwshQjpS33C14QgOjASYPIXEqxJs3DYLKggvFqibjbUM
-GEzkCApAu2B6sLit19dS5cZJMF34wFHMXS6yO0yvSN8gRocWiz+mRqW/3Ka3P5Rf9w8jArM8OnGZ
-vVXAKaO7ydZ0cpmpXX5Vy0wlRIcriQ9WrXFSv6OXiQhjuoMy6F2pHeLiKp1lfO5rlKSQ2msiHLFj
-cHGP6I5fnEZev2m5ygPBavjDLNTOg52Kau0MipWZN9d6wTBIv7HW/sw8PHYKimCjpoFvMSb7aR70
-n2WE2qxwZbODLQMqZxlV5YNTX4ZlfOUsgyz65sEkKbob4o2T9+kzjo1yHy8jsGQZhqG1uCdCmIsg
-0Cb5a2rldHVw92SzmXhxyGeTQIiBI/GH+Jd0cGjBlqTMfeX82fxO6QCsTp8QB8JvrUYyzkr1FChG
-vg3FUoxTnN1bWL/OvPEMBQVfXq6bomZgyPypZLBMOIqDacxVMMIQgSYSkQLscsaO/J3RXgRp9RFk
-SON4DMthB3EEoESY9fVKO039TtSGWWLCCOMzmxznbIdh+Cm7Tm37kHAeBzwjPEcVA6JVbTnZ0eNb
-2kasmUsO3qxetR8137NZNcjxlefcJjG6HEXJlfsIXmq8tKoun6qg43tr28q5pTOhT3Bqc9dl7hzJ
-rbCj6p5Vf9q0+H3mA4cdVHLTDKPnkMEv6w6MUFuJgCrjImBW1NL+m22misK2tRyn5sNPUrYaH/v+
-XVs0zFrqbuw+ta5geP+Oo4smy+5kIlobAgf3a+bTRA5W1jLB1q3VEbqh7/I5mnXwhPs/gzzDX3ZL
-S7tJGJBSh83IkOTNDJw+vmZjF9w3dkwejQXG/9GcLSEajyY9soqd+b6MJuCF5FJwCBUaB2YlDWZG
-QCtpRuY1O4Ci7PcOaES1cqzWe0jmFAXDLwdxdReNgKai7iVGZr8yCffvh19BIV60hVxop9+ZAbZL
-jiS/yoQG3bNqIWZcezdI7tJ+RsbHtkVllGyyb9jV8rGpWagP7q/skRiOu3V6x/hhxUt37M/uTkx+
-+jd6E5UARew8B7+KiTIN99FcZJRqTumpC2KZYHBeWCbDpINT7Fbee+b1831htsZX5Rfp1fwVZwQR
-pnPZT94fMoRJfZkjtZAPlVP8SHvUL/MADDKfc0yWNRWWGyoIzHQNQBFFyI1bsBtJySp0aJrCPWBf
-Y6ockfDb5qpWe1M7+lzELZaEKaEHsXHoL7amru3WxGDzk5kR7QRq2U+v8yJdkY5HxfImr/GY4CVg
-lKyqxp8CpgR1LGm3qFbJmWYvZOKie2OIWKzCRTWbF/2MBtPmI1w0Nbam+jTG0j8mbc3KY0dYbAYK
-24H5MqpMFm0OMDPnMSN+EYtuZ7eCWdui5QlEvQpxT7myPY5RiNHS1/nOpgFv7w8xHsdkCv8OF03Q
-FhXrH7QWBqcjt0ND2/uKbvb9wBHB3oixd28jeuPuxyWp2KS12lnIfQdLDdm5ibzum0Bm/eAZAOiY
-wXA0QtGrnmz2vp3rg78e8iD64DgDyzOIHxP6kZEQ+EbBW4Xs4GBuvL4Kz7UDF60O2qX0rFOXbhFL
-mcvOmyEhfxq6mtAABfUMA5FXsbDpnwwb4bBNhxx4aYpjJ20EjUA4CzTj14VkTQPduW0Yn2LUp/RM
-Zf3n7Dc/86/Km9vhsp1yG6vjMjy6U8vQyRDznitQtEMh5FabLMJxkFDIEJMhWjeAo1ftIisn2Hoe
-dGHipmzGsT27yG0XJNL6OBmQUje+05p3zuxEa/qh3Iuswice+wfXjs792L3IebDvbS+jDtLJ5zUR
-RNK5TO9XvJ0LqCQCQtDMCwLT0CVoL2azL7C841cTpNGa2ydZ56Bsnl1Tj58JVol7dxYMXk1XpzcT
-w/+DK4DsVqTd5R53JfK8uSj1LpJ9Vqv2LitsZgRqKeZE2M/KDo3fJPjzwakTySFznDc1Vf1XPaub
-YvEIqByLSPNrHMAbFH2JxU0QcdwA506Hx7R4DTjozed+8R+ked9dcdSwz/mUhkdclXdNju+TR9Rw
-jsVciNvK9YYn7XE2nxQzXPKZhn5vQqwN2hI93tkuXgEyUF/gG6JdHngjJIxwuIYRCFnT1+ZuwCF6
-aCHz76RBlaBPYWe2KusoWjhYPfWWnEZIi45es8VilUMlg+uFn7JxaLPNuhJHrvA0W7jVoDJza+M2
-bEAo0AWHp01sdP0fj2yg9+RF4wKRoiySm4kWMQmaOvlpBXBuJOkCLvaclB8YfRlPdFLkIZzEtI7u
-i7Q2X6CdVhy/s+IeLqb4EORJcDbk1o9Kl8rHbGmKB+JjyWPH7WbneksZrDePyUsGPR7OqU+T3bWu
-VVkexqjxt3Xk6nrr582M/ap2jh4ToCPq5wIoG2V5T02tcA/LgOQzcgxr22ekV6n/HDFiSJvsNPF9
-bVwtQMnMjHvMFhjOr0D39afIExYAZRUH4SQw3TDtS6U09L+O+KM5MGfhXpdbGzesnCfMMvqgyhm3
-YDRO5Exl2WJHxCI3gwQjRGXs5GikeuUPRem/IJULc1+za8qVCvPlyAh4eajhTFD/tsp0AGEqVCYw
-kBRSzR+aZrtbf7bDV5Mht7eKJwk6O9Ne+paUSXtiglNWOx91jsBHPeYnw0tl8QS/GSlNW717KUbi
-oeTOR8hgMwDgbTIYZFKZSuw1WbSgaIpg23B920uGcx4rUmLSSm858w2XTpgSJTvWbhgY5GeRGnCl
-SOOp9gFt4lkCLR7A0427qv/gI5e0tyz5LmpvV6R31GDb33na+a9MZoiGsh9xkgZnX2Z5fesEdfNt
-t1GE2y+IJBjbzgKaFec/KUa48ND4abKU+rYZ4TJ0EGY7QdE6nPgYGKxkLVq9dpH6KUdJ6uEmzQBZ
-cy3sIuYReYPc74+o1RvW9W5Y1QiTzhrbMQpIHncOsrk98nFXlJA4q9AstDwobmLprvAm6FG915ub
-NnM0Npq27t5k2CxHZdxn7Dkqz5/wqC5V8Uws7yhPzfndomVxJxUfUburg8w9NU5hf0bG0kjfoUKt
-s2HKOOGwRU2eY9QrOy4gsgS1+5XlVv3qUvPwRgsPBriojY37yl84vsq2fbIBUk07f9IcYZO8a4+c
-xPNdP9dZvg6nDkZDQcKI4kZsDJgUYj/6sDGK7qmEc29JaYDhEQiq8Fm8DqEk8Z1vl/kHcHGRA6q2
-88U4xJnnLVWGwiTlUuSYNq68LxzC1zlGOVBQWuaPpZE3hyEkaLOOW+4eaxFEwHis1i0vVmpFuIqa
-gg9JITMbzmtRtc0+FAXRGEINYQFANmjDbtuBaN5nuOxG8nnh+N67XLD4SXz1ArWqo2WhGwN+as/F
-ziIyPeNNxRmHqJ5xSu7y2HryPZ80nK0xHYQVTqyzq3pEssjp008M7jNzi2Q0rN0UWaaxLnqYZKfA
-6+bXtOy4dPF4uv4mi0bPsVYAanCtg/XcU0LjnhiIkLYsfVnumdbmP1AeBLW/E5IbcCxsMoXyWppO
-uki/0I6cvjaDiWUc/Dm8r2H2ARZmhgdXCBQYWcuBR+VEQxKmZmBq0Dy6PgqeiqTlNk9u3ARkaaVf
-IVEz5iBCNAKerZ8QwzMtovQqc4g14EwhOxqhOMnzUPTdvEnS0ftuna59xkkTcxlLCh7qTDDSWyXk
-/9ZRjIV+Qc1CYM3AbaUrqmZl9Dl6iXceRcusNEFivE2hrCvOE23Dgp1GWPkL1n/aqEs7Mslz6Nlb
-56W16HIQDAiNgPe4TYt8hN0CXuHdBXiwmb2me+eT1IpLa5q0C9eR6i61KXqqgA1PBhtDqsW2kaTx
-Dvo0OTyaqbGjsC2xrozlCGgrxbKDy6dCKzQ73bjEQ0Forww3GPa2m9V46el2WfW1CZm0pNl5uUUa
-gBTascGmD0w93Yo4mR9EE2b13udk1HJlCtSmMfnMb/vEDm8G/CHDGrI2mQIzRdMcsoLxV2YG2l6x
-qko08GLcGdVgdpdpQManC4Rdhh76mjla0poMk5RHiS+Kf+DfKsiOTJnZ2biCuVO5CdO04nIu89bd
-47Bdms+HiGHRVPENR8aowhsKox1KlQvrT58Z/mOLZZTJIx6plW1UGm8Rvd/Ys+Oc7lEjrzH/KpZN
-ML66MR4irhr+C93ZZJXcPuECk+qGzcXqjR3Xeps6dxrSP3IOZJBhE5E8MsW1sW6XTrOJBy95zHJ/
-Onhk9PpdTATnhc6b+jyTO3khi8xJuvTr9D5v8rcatPe2SsgGHlM2kS2JF72C79mHm24My08EHeOn
-SurpKc2DztjE1RK38Fh2p3POVghey8+LW+6Qo39ohmWWnfXBN4e59stM/eJ5BtoG678eFBRZIz4Z
-FmLTWlfLT6TDTq6k6woW1dz+2zKaYcfUQu5GBgpnRjr2OpVOd6/MSWC4KyoJr9Eb5oPkwYXmNNSP
-4TzyCQBPB4teROK62MQReGZfP2U+lJAzaU4wFsxXot08eLjsCkMxibJqBZE3tDGXHXweX6B0FT1d
-m5By8vSWYUOG2Xe2+vlSUyLoHogfSeSZWEM8TjJhYaiOr3Fju2smidOnCWEXBn+1qU1gb34z5wPV
-LpA/q6DBPN5gnWVvS2P3mnE1AW4FVGlJzUVPLSzUJ86isMjMgKIRKmccorlItaCbKIr/Q+4eE6ts
-mQOsfWUWfwsFonvtyzTflO7IsL/pEmqVBWAtGwE950TZusX+/+uzpSbJ+X8oMZSBgCfwv0Y3kET6
-bP+9u/AfX/BPUdb/S6J1IscKgly2b1Mx+Q9R1pd/AU70BM+2dKQDoeFfqqz3F4Zi0NxYFYUr3OBf
-7YXC/ouvcP0AOdeRSL3/qfpC3/2PrYHC9H1JpYDtQMbhr/wP5ISmd3NFw5jc1yhyT0hz86ab4vI0
-ehDPe0D7+74p3mNWz9UofP898YriImyn46PLL/a+pOzpJq7s7DWNY/KrTEhurKD0wuOIcAUKXrQx
-QWiuLq9iHpDIhjJHrM0g53O+BfeckUJiz+vn10C61Z+58vQrYfcIg42kD5UTzHhP0JspKzOTtd1U
-2Q4KuziNbS8eOzU0Z1uVmM8tBfYJrPcxYjYybixhLOCoWdj4mVV6Zu2SXHJZI5+yJJzNI22oxplY
-NIFNxyanDxG2d0EmFOHzWKUNQS3DObsMcD+QFTn9pIafJWTSp+QlJNL7HDrTAKpVRvzdkiURYGeK
-I5T6cvETLB2i7KRFdcKuEu1ItWW3s0gZkaWk/y9Iy54N7BMZAm4hdc7oqO2DUVdZwHQ4QTamqnXX
-F155w6lumcqCJ0WT6p0CRBPZ0D9kqI1HZr0hkaMkHD6ZHhZgZwwcaORmpuaWi4AzEaz3CXoTrYIX
-F8UUdah5mo4uCCYy5uDY8fqAoKBMRO5qnH0X6SjnmFoWoEBC/JJjchocROcwlhrln1gvbWVuDMqa
-bjq7PXDVA35WBWZHuZw2eXfjLmBcP/sg/xRrMoDGEl0aQzlTdgtEUmV6u17K9mfSeZLwaoTdvqOr
-47sm0/9uMW/71VrPDimLB9zQ4pkwQHuTOVnqMFg0PWNHtDo1tmPXQ8YihBcxBk4x6EJHY+6VjQEu
-gbLe0ksJBtqp7OJE7sVDvE2HE2NB82F2au8sU2Mg90FZFXTi/AnjkL7aph0Ph0oAQU9mg/YdUjgE
-/lMH4qSJwfSuptiKUF3m6xun9eXFaYDlm5ZBbAw7YXfs1IxCXg4L1aN1QYky6IQ6FXWgCLIA+TIc
-1LUw5/AjINVyMjLbfvdaiJIMlPJDJFrBy1RZwW3b8UKtHK/00an6xiFJwvSflr6A6AycV3oGdlY4
-MOj31SyPiv4pBsQujqaEIMijUbGx+VNKFjcxNk7dfNQUplEHSgqCfd14aWx8YW1Qnbh2GjuvC8l7
-TPadzkAioyjvCMCiDbT2axgn26ITaldVHIbZeWOCmP4ABrL5ps2ruS3c9tq09Z8gIWgdSjLmQae5
-h9HchpHhrqDe0MNutrZSl3y1cDEUu11xhzbIU+96eDN3gxCgJZj6c1S1xwkkIylxBr6eXtnUXJy4
-gRBLlQB4bcYs5DB1cfE9293yMeyfy8Aubwzk61VryWqf27rrHrRLEx80kbzFRWcacCc4khFzY9fk
-eI7yAfWXA903iGTT3LCaUOZUgcIITv48xvFedrw4K8/JjZEbwsA3yRdhRa1kBGdilENnUKOkMYIN
-vpf9JLLsdp2VGjvfTR0eCz3urcKx92Zvm1tArwiNLVcfVHJzX0QUAOLnCsNnj5d23eneJz7pZDsf
-J1m7oSNlmW7l4GHLVHe7KU0xGDqJefVxRn/4Fjc2/HVtfy6EoFfGC7P7kIjSzkyr5A+2LQhPtMKg
-CMzanNC0ocRRnDqMNK95fOBl373Xdm4eGkRvXKBzlhwWd/Su44KF7qE8cdOSwyQeESQH2m7aN1wl
-3J7biTaCECBNgcy5ze2yv5q51RLr7bAEFtS2b0TqeXvVURjP66/uiV0vZjh0vq8I1PJWiuAwR86Z
-GeB00bAy3loRKUB7I+GJzLh2dc8ZtPSzxylpojuX+cid4My998tS3jflpU5wgvb9dI9QmGzoyO2f
-g0D2O0XZoVhzV2qOULaNW1OVRFgYh093A+f5C30Dab/OusA62QOAnyDQ756RZS8kGqobXubsochm
-+0M7pZtRhGKOOHuocLiLYvoR4n4i/S2iWVH8Qsfd4GsY3zg+ae2ZS4a2+BC3dtBxGp4xiM69Q26p
-n88tifMENBlv3TxkObgPjM8E/ES7phsseyUVR6qxHvVdEdvy5OXFzEwtn+u1ctP0p8nijnAVObFV
-YTjJFYsMT9ny//ZI3N7rMhEgPLLpIKza/baGeNq7YcTS5xMxYD6VYwuArqihGMnSuHhAOZlJRkw9
-Brb7um2w4lgu6chseIwD5URMBKNq7/t+dgzmKdqHREzXSRjmr0bZzc/a9sVllrQwoGg24lTbkC/X
-ZSytY2TKH0ZsjM2sIftiMtFkW/SP+nnE6I4zmaNHuQma1ruMtZ/eCF9NPoYswe2n+JSKOh7pZZy5
-mRMRPlASlXEOIxAoQ5B9DKynOFliUxrbKSqrB/Bmlj4OTTI/AVcSoFVRa08QHtwX1WT985haPwTG
-qnmfhMoA7wnPGe08+ps4dLQrXXChq2k5K0+MXShPHIIRPpoUL9A0hyePpeYz5P7MokuYm5tXZpZI
-W6lTPwPcyf/OZU4Nr4SyU8QJ48xCW+9xKphDtszn7nRTw8NnER0xgUDsg1o/M+9/C8LoaykF4qPl
-E5MIqBgTyJ+9gXm6sa4mcb8VOI/hNDXhLVD9hjE2hU1+N8zHEpVFXLOWD8mhY0Z/HssUSQrqJhPM
-bvEoBdjk4pRDB0hX9VWnxS1lZLxRk2iPojacfUPNslg1rZFuIEFxb3DEQNyPZ7qbTLbWgua/mj3l
-uZqqfGfRpgSexWrvc8Y3z1k9GxtCr8wG89Jd1yoHEl85xhONRtvRnpJVawr/gehbcdtSuEPoJklf
-LTInx74tum3bl/UPA9NsP2RkeLncMt/1yuDtv7N3JktuK1t3fhWHx8YNAIkEEgNP2LNYJKtvNEGU
-VCX0QKJvnt4fdON3nKNzfK4990RSKKKKJAhk5t57rW+5Ip+ugeWWn8hwxh1MziFZDa47PdZLWhfB
-2hxM7OZAkyK6jcqO8NM+qmhWNnj+IG3+9GbDAo8irzQK41NusN0zVLK+T7+INPEvOg0yWLIXpt6I
-T9kvfg3TkfFnEJgDNKGFbzMuqBuAIiwkC/4mR328HRYkDnbIdj/kQ3znLsAc6xc6p7Vw2i44HdKe
-4ffFNJmtgG541Yyf+YLfieHwdEq0BPmA5pkWSI9acD3knKW35Gak6M+HWw6daKv8wrlmC+gn0Czr
-5QL/0QIqlxffTm30nYE9TCn/6oVhs8vLlp6Ds0CESr3whCqNzDyCMcSaiNqEWJnoKf/FIGI2XMRr
-mtgIreSCKfIWYBFpy6CLTAY974OelYdssCEA2NU+332ZOT85ZJXdHkeA9cImVe3HBYzk/WIkzXnF
-2Q/tnP+JGN2ydnPNbtQ4/fCIvdPbOLB5FkPNObUS+cBhcrqhZxytBDo3EGWxz2luaQgxyMRCXIYW
-uJqhluIpS63wkDctHYmMxMWhTU6LAOrCisD4b0E+uSH9rlUeivhN8xO3dBpJ3OacOV/qX8wobYKP
-yjhZP5a1Xd/yvMqOsxeQqXrBTaWIowe6sUConF88KuRVsKkCTrgbeJpWTU5BkT3OaFdJ4SLX9528
-gPxW/OJcWRipLngjyR9KKwwUHFZzexXR8blLmRdDZssbWDDNL4IWxr1FD8TAHm1ToJlhpZF1QrTU
-0lxYIFyhxxHD6QiGYJZy6U3pZpu2yc9273r3KjQdwQFMwNVHiEDw3oL6CnWnyLJMvXcyA7qjUj44
-bIj2oMFyBN8RHOagG5nJIuHd0PWEDVRCPsdJPqinZqoZn9Nbn7ajYq6AoFPtnEru/ZTYMAIDsJoZ
-8FzXUxLUe1atD2CV7cq38dtGyon2eBVzEhqRt9rhnV3Jn9VCOAuK0jiOSUCAKbxhZoEHR8YX1OH+
-qnc1VltCuR/NBZBWoGDfBws0LTUDsYa+tDeWEoPJ5oELMaMk3xUlZ0PeyQ1p8D9NQoI2cWgcbHck
-gz7lwE2JnK5inIiLE+rVrwcil6LwCXAZHv0sfIbc4a0oB4n5SNor1XlBsKQ6wy/AlUZIm4jJ96EY
-+W4E4jaVyaaIpVrPfszeYIbfIDxBSKM0Axthb9rOczfzgOAiLaP26GFW2ua03VbSDWZ6Q7kgeZZQ
-sxSu6ybuGQbQuCzXQwaMIbM3ZjZ+MIDbENV6aMHfb0qnuM4wAO4GOGRb7MfzmWcPe5UI/A1bj0Xg
-2VQzEvRtcZMUTfgQQGfZOwHQXtBUHf3LDoqDEy9UU032+0w0N4dSY+ohr0lCMMGzBWtFt0qsSR1Q
-ZKVnbX3rkgwSk4bJ9VU1OcHpiApiFk5/cAwveOkW3iC+N9CDTH8pWJKFSDj+ghPOC6cw+4UsdEPt
-v8ByGD+gywcnGmaDPNSw1zjQyLdw0IQqt4b0kUXOFDhkAlrxg6vDkfwNIeaDHkFDsXGYryFSp0fm
-5BqwDrNDEzZQ1tx4nkf7uleMI1Ao6FfHaZFlcCuarXqCJYBipifpMo+1OoxZ9UH6ulhVLvBVfPxr
-ElZ8YvPM/sueusjmdGqqS9gJdaDGKloeOZ29T7gvFnIr+p6yDvpvPFkIUaWOUZbm0T53R3c/TmzV
-kuziox35IcFg9nhoFV2ClYosf4u2RZ+Aq9BgWBj/L6FMs/cy8+N97LYdTAqv8Z4VBxcHpjM980Uj
-lR7/f/ft/6b7BoZC2AtK9P/cgNt3yUf90f6xBfe/f+rfXTjP+ZfjucJ3XAn3ipuQ3/fvLpyr/oUY
-1eTUatmOaYulP/df3gjnXyjK6emSSqCW/hw/9F/eCPNflgUszbQc26ZJZzn/L9xUXuJPxgiTV1C+
-afk4MGy6IOafjRG+Hfduw+h+2zIMwGJIi+Y1Yvm7/OGi3P3bafHfio7Zegwr73/+98Vf8Uf/henD
-dQTMCjDKpWcvfnuZhoNnMoTk57l0lL71poFMG9k747Y27fdhrvt/N4xx3YRf5d+8oAXh9i+v6EqO
-41hPQPWp3xwffj6n7K8BmRzWkleugUVFkBXAw4MWFcUGnkf8qIjVPLSBeuiAwxqrip/6Vkww4Exm
-sTeNG4kbC3bM1p47dC1TNpzzcJ5vrTHV53++QNbvGNnlCvGV0wuVPg5Cb/mifnwg0wm5nNb/SCgJ
-p2GkYUUsd/45kLHCDMjiT8zJxCiS37uCuYSKNFblZ03D4JMErOFlCom/k91Cu2GpfkbTRvzRSHjG
-P789+6/3CW9v6RlbkHy5J3/r1Xp+ZcLhntxtBy//HM9WOrKQleS1NkME7B4pErJTXZ6yVoxb08CW
-2YZ0NnjP6gCJznu1Sf++Yoo/WZbG9W7cj6C4GdJxoqOtVPXpu3BctYdUyMGf+JrvXWiBKJsq/fDP
-n8WBOfyXW4MDB6hiAdyMv/98qVU8D2bbCbnVzHlvGSmqNQIbO9xQIEY3Qw1+ekkulFujbIZPMJxo
-3LK8WEQveSsPo+sb9904tu+u0wuchkSh5akh30YO500jz14d20SRxgyjiJAnWaPrj20ZRds6TN61
-XDLMA/nmY5O8tAZVbDFdOW3BQSRN/ZjWmXuxGLbfIs9kKm1HTAjpuVjBDqCQu+L0gn1zYg5kZ4M4
-19qMPhWzwnlldUKfpFvRsUmQDsFft80TfmhShBIbTs6mBAX39s/X8teD+9uDTVEqHcYBwhJMB/58
-LQl6ZXzcTHKLEiO/lmZa7Er8GkuE+N4T1k9Mh+O1w4jfrPMR1Oyhq7Php1tl9XdHV+25CoceyyaA
-g+NQZtnGYwjnQhYgm5sTk74D4N8c8HWE4ynU+fTpd4NFryYgEi0D3on4O7zVM6Fy60zHDLpDc7xV
-aZfs2s41/8ONw8r6lxuHJ3PZEpQjJI/Cbx9WYTZBJeBum7TqL2Fud2SH2AZqcpb1O5Ix/F1lAUZE
-uoPlsVLhSWjJABhrHMmqs6OeaXFPX1Sp5o9//h7+Zn1VmOjUMp9xIXQvq8sfVo8snPI+k4OkP2Qj
-QqnLnzSOjk6LIMcb+5t/frG/uQzKobdBf1IoiyX9zy9Wsj8QK9LK7TQ13ptJ0b48xcn1n1/lbxbE
-P73Kb09phjbHbQQT5lTE8ZeJLfN26opF1NIW0+6fX+tvVgRFs85fdlQlHPu3y8ctmWhNhbEtpLBP
-wsjnT3DW7q1TC0gO4yLeLygwSipKs7jzi6De/PMb+JtL6jsglj3F+u/wz98uqYE6vYqk3Gat179Y
-Q0UzPCCm5Z9fxV5+zR+fVqksDg5SKpZwpm8eLs0/3iY2S64iqo74AFk/aCA6a6SV+wRw4pgj5Y6v
-Y0Hc2Dh8jiizuygzrkjlaDrPpdokYpg2ftfRXY8c5iP0Pfek17S40B8aWwNyRFS91THTMrOLMFhw
-7l0Jf643+VB90er4D+j13+8PqZRcmncLgX05Vy3TxT/c8rMzM/9xa29bse2AygRL5qIw2MwukR//
-fN3+ctl8k73ZERThzEWl+u32iGZIPF5n+CBv3PAmmOiEkQrZn8K6yHaCMdKBS+3/hxflKPj7U+2a
-0Hs9jkusrJ7kePbnjzhQ49s5uOltnw1PmE7LrQjJbvCDcXgTRM25YOKaB7TOOESHdw/Twc4DI/eR
-hHCDsWHjWkT+6ykPQpt712i85ixu1R6d8z5rseA3Qfwe2M172YO9NdE5039tViS9063LkGQBuz3K
-tEde5jXmne8OtKZzpqHo58OVwYgCVNtk7iCOyjO2O0IgwAFr28h23jhgscTBj4wuv+8g8jDuCzUP
-0MME0pZF/5g6Cphp2V1n98PR82eBIvFazLmkPyjDt6Y0uqtRJfZuIDN3E8xoF/NK4RLAM7PPSLQi
-NKvKkveJNtxm7OICf8bY9J92BoXLiRzEVGjunPcxtoGbmfmT1vBi1B4bDmmJofUDqFm9hdmJMs0I
-sR5JSZBhm8l6J7EVbIvY1xR+khDLqc7x4SUYNkYXbaSdYA4FB8yeC2viC8uVOpNF1exii9yeIE6H
-YO1bfQDe0gV2ErBLfaP3OGzjpgBJnUxr8LGPlIGEX1YChBf2YSdbz1U0nSCVO/dB1Fd02mmcCNS1
-5XggmGve25k4BO5Tx5h1Gp0NGTn+z2mgrTB0T1TrXwmny5fYZkgNkTjf+qp/zSMiBvOx2TWMemD6
-VNZLlSTivk9rFCGTLnN+V8bo2J99EPrVfe7PL+jCFyMcsvZW1zVj1ZCojVQBuaCv1V/rcWbENGfy
-julR/kk7tLl2tTId8gPDn6pv/T0TpuZgVkrfN5my3opKZ69DLPZMO8BTISxTd2WZ63vqcIwoIw1W
-uc7tCtpP0k/PGXaNe4Hq8FnDK1njzJ2ejCjQe10a6QXdd3iYx9p4SDloXTpoTwSj2ubGqnKPV3Y1
-MZgkPqfDaG6B1lsfRkAUaEn01YVaGoUS395hJuD2Puqy73XvTd+T5RMOpjT2VOl3cOH2c/lkIl1Y
-K3rEVTCdA8Nr9omZDMfSSssfAXigp9LklqxEB8earuSGwYOFNjYDQNZW7WZerJflGGKUrYjmTKty
-3ph6stYljpyfymyQgPXOdJNj4bjC8/6KKvle4I5Bt4CRgShMOx5fqe5LOtCDsZomDMORYHTQNdGM
-MR2lT1eHr4DXXrVPtxVRhFV/z0qrfQlV6h5ynNZ7X0zlVgdMqKh8GrIZarmp/do9JKT/7GpDhdDU
-eFP45+Hz1YVxhi6Kz8YilrtOiwdW2PFQ5dVwBKMOgdktMB55C5G9/xIyPGXlSAMSsGmxKvAZrhOw
-Q3sb3uBjP/pqi03B2KVCqSuwZ/g0paEeRTd9b5QsH7J6cK+oafWKZ3DeOCLGppXLu1mb4r6Lcr4T
-eoHFBl5Fd+Pgg+ChaqNd5A8DXC/y3Gz8Hl7SI00kLm4FgY84g2COnlsB/YIMvPlkmuj2ZFk1a7Id
-E6AZDYAytyIY1IqSD1Ry3W0fyuESz0F2L6dyYNpp5FtD1+0GV/JeOvF7FYHLD92k2BAFhPTEZE7a
-+ziHjDy50JxllmOM9g8xJB0AJEwJROGZmxi4+51t5D7zJEo7dydy5wWNr2QNDFFvR1CbLC/FoWl2
-D2EwnSxiLjrRMERMnoI0LfjEOr2H2UxGzhTbn0SuZw+6Tzjpq4EmXtLYUFcI50mgmbvX2nZB0WhS
-i7CdPVoBrlKwBasOBgDSy25fzLrb+rVNfEN1ijAf0w79XsTMDuKid/YwdO19bZiPZYplMhr7cyH7
-4HbokKOsJLOEt3bOrY2uhiL4FlKe9asoyD0mxBO2Gj3XpxbbO4QxsR2bNLx0c4PMzh6sdTSImQDV
-ckxJ7sHL08U+rGjZFM7O9XHjgz2GXsL4vEyS9IRIr78zLEbCQEALxi6lvpEuGEnHre7JFQCSSzP2
-I3bqEn6kme6twEMUg1KFrpwT38ZBLd541+WW+D2JJCjO9mgD533k6gjMtpHcVMoEjOiyc9Z05hY9
-tX/o446I7TahHIQ0tmFcmR+1kDFLP5rGtE7Nc0bDcddWLN4AE+5r62ca0UcAlzQ1T6rFid5Ykb6z
-h2x6IFNBnZj9Tnj7vOREZ30i7bUNXovZn946AuSZIGTWAzaDak+6IHthZCd7p8aCytBuXmsIRLu+
-glutwdIe4wi5RCJCttuI+bOb4glMoTPT2WnRWXTlLRmT8tT2jbwNRCe3wKDMJxvByH0WtwLqzqBu
-HT/stqafhOc+V/yr8XuyLpJPnVckosrcXMdMug7cotuqww2Sy2hXANDGilAvq4sfYR4mVZhzP1C6
-6dhASBZGfaO7qzRRajRucR0yOpuhHlW7Zi4cbA3QQWdRueVDO8fyE4N2/kZ+qMQy5LxMgSM3ZWSy
-/SEM2cuhrwFNzi1wNscnQ9Fxc6BdFbknAvKq4xliE5sJihu0H48wIhx8/HPm9zv0/himBHlh5sRM
-NbNAiM5Ozo0ftLWhNyPO8SNpqcwylfmqnNa7I1oPlfRoGPeQkrPzHFefKFisrZnWghNwVhePRd1d
-cFMfvIYoDlXfhOkc3snUdzfj1BPjDn/02Auuc+jFcl2BDFnRjjo3Iar0MFhzUAt2dZAPZIZbGCsB
-1PrXwfK7a9s24TMlJrBIKG3WDhGJG628pq8vjvCDF6/2rIc8b82zjf/lRiBROI/j2Hw2CDGIiayi
-6GkoeDOG6cgvMZr+DxUjm0tjUnbsiJ+zAmVsEMzXFnwHbe7AGCM6/mVHxX3u3eZ9MxlIVMpiW/te
-8aALrzhGVdJj9B+xPCXC0CfYzGRYEk2LMt6KrWfkXRUQpdRX2LPZr3vaP+UqdzHLOoMGhqG6Knhy
-tNXx5YOOXDUkYeynCscv58zK1asqIiIa9BEeK+mP0GvnLNzUDRMDrGFREGwTQpiZZZaJfwFM2u/s
-1Bg2gmKIoL/AkO9hxRbkaXLCQDt65OHgPENAht96GHL/7GeV5s2bDHY5zyRi22ujaggcMObrSLYN
-RyY8q1c9Rc056SGSu/N3x0teO/IkyBqe7JsaB9+h6+Y31P080MwdcRinkBTFXG7h6qF5WrYb0/ZQ
-s2Chq5YW0bgpcrfa6Ex1t7aomYqSSrfzREIgHYgxwtPzYDz20bAj+3uDrt1HPwWI32Iok4PuKJKT
-gUL+pRjnUxd8zo73oAb7qVb9B4apo5rCb9Ag3iLbcQ55aOT3VW+qQ2MWGEfM3LvNepW2m6yMCSAy
-LSTR4Fb8S27qGvkTtts8MzqLVhR+qkTJ4uzLun00mjTdYPRDl+hou7ukmL+cVeNKCcQYc8Cat9Dd
-VYEM7zN/fMQ5Lw6Mk4r3EV86cSuIog60loavPgnaxzn3qv00lszctPYOpBKGmETY9j67TjFfywlZ
-DR03WAWF0HueZAUmsi6ZOibDoTctpp6Y+VcYdtXWLaFerEOfEOlU37spDReoETGx002sjx4BNi/M
-9dh0lOoFrOhQauJoZ2pWE73tqgvc+Cc/g5eqzrH/V5OBH4tjDByGeYYDmA4q2XL+b64gteJo69Bq
-3da2n9/2TmRALsb9umOa7e0TkH8suU4p1lZsG7ui8dWjMXoUDB5Nw2dmgOU7Bbt5okVREjNh+zzc
-xJwaoYHwJJjvrWSAcJoXny1Nx90oWvODZxj6pxiCQ0r65Z3RmwDAPagXJG3WSKqYrp3NSATJCuV6
-es6iKrjWHD7IUUiZLVpZue8CFW9i4VinPFTPWW/e2HlDck4XYniPqujR6Y3ycZakr8PanO7jnOW0
-yX33nlg381skM/+hAy9ztj2A0fzK8MeyFH7LwzJ67Ia8kvxnyuw4AQeoE8N/9ua2ffJSBrebro1/
-sLBkF+L7xufBnGK4BF4KWwfp+7dhKio+Q5QeIsgUt1kbhxdrDqv7vh7LG1Q54qjDrr3EVl4CwrHD
-11h3AQIKclU1MpjTQCzMKefA9gp1htSFGoDznjOPRlXZOwb6otE/VHiniNDpovhKZ7B/SR06g6Mx
-5Tel3zc+IsWhuYcY6dFOmevpQDqwf3Kz1v3CgmhXqzkp4nvBrXqPA2wqoNoOtn2UHvVxRC6SdUhr
-mrKgKUhGRbtSHKJiSF6bJq/fq8Qx4Y2bDA5WZTWbzFHDIXnuLOlvbDVZWwfYD2aXPKewUeTM31ZR
-H10MAHVbS5b6gPe+XxnCgn+HpfqObTLZ1WLOBE/JQjKZ1AQ0qSiejdjIGK0quQFYTMxRVbSX1Fuw
-wAA0V6pPu4PmI8CPUrrA5tFhBhicjKMl0Y0e1hmjYtYxhko+GBFCE6IqOYUQcQUBGS3Qs9VaNExN
-hD4oCuIKElswbvu5t69Wn+M9ITGDSgod2YeMguS9kNDitoEl235dFs4QP4goavdZJTjsGvOEn6sE
-p4Rtd3rgg9JC1wvcasCeiNO3nfaj5+aHVBimeMmDoPnZY86ktKZzWNzYi3NgTWEgh5M/xS5JV4Hl
-TZuMMNgBD1VlGFf0Cq06WYzoF4mTfIOGlB9QkoiHbBb+ITZi5uZ5X0L+5oSflDztUgONLfMBXdRQ
-sRTMc8d8NI39aJcXeOLbEraV9Galt1NTT/Yt7b3AXLtE+W5dVSbzSg4VYgNEsOdU+M0zxMpkjTvf
-/UVEQeysxp+z9uecNrCzkKvK/Lu09CIKzNgiJ3ZYcKBDL25z0MWvNqjbn0TOQH+d8bXw0av3LkC5
-BGlbtzdshSwDfDdOsZ26XNUXqcLp0pQubg3VzfjxZG/e0g0LWc/7PBs2xE2TzhWU+hpj5byUUDu/
-UVpSLnpDpb4nSU2mtM3C/VpZyk+3SgynpI0ABA0DKGlQ4K4mDMSHcI6k7o2REs9Vn8UUenH5WPRY
-MINahunOUOJ7ZtOAGho8+K3D8IR+5h6n0E2aDuQpI+nhPDMb4QP4rOxp7MZ2J0wdnjQo3isaaoPG
-R93V3grxdLObirk9Tnllb7UR1y16tLJ+FQh1Dwnb10uYhkhJlYpcXOuD1dzUc5J+lByXtsNQtgce
-1RAhW2fd6QbkDjo5Ul5wCeA4XLcjOOP1OE4BCeJexC459vMZYTmFAdXwd1tW6kh3NTzZ/fjVWP1X
-3RjPJiXAkllsHQXMlI0qhbNzBpbQUhbdS43b+QZytH+boIH66r0cNO9cxtOFzhY7Q87BekWCuNet
-4ILRBq1jAmRGbXxBCkKywGztJ1zXocGsGhNq77gDsRRj5ERy6xKXgmy9jyntXcaZQLtJkFtpC4SO
-E/Dhygmraj6/yLrumQfOw/cYNUa67hXyzTHw7vqoleeWNVjysYINkhPi531w26eegN1jPTgtcXDT
-u8lvIfwdy9uGwiTdA4KFIMMSMW7qCXlvRx8u3JM3hDJcDVeUTeINsDufnG0YfyQGB2ZcpLYUuXhh
-dyIbN6pmQJ6TvBjWiOW3SJDQZanCwj6fyQ2qTj7SNmLgKv05ZSPttrwz9oGm1jXGhHTOCtMmKiJY
-8sQL8xwYljw2HGmhBbBZkSgzsiW3qT3uXdDM+9JskD7WqNBXYWdrjF9GsTOd2juWnh1iAI5C6xGa
-pPuDVkbib4ZE4Y4gkuw4W81DHtTRnWXTF/RxYVEDduIcEDzUQjQg1Gsi9Uapcjrwjbfkx9sOQ1c1
-cMdG/qns/bfBEB74Dte9SadarwG04PrGl76R7L03XeKKs+o7d6M4rrz1FlkSOCZBmcDt2cJ3GNZx
-T8Cb4/vDeRwUgvfWNKatLyKmdQX11T2pCNx1/dCfAKbEP8Iao6LOghqQJmM0WN/Fc+7K9CmEAP5g
-GKH3wry+pCSKgxx6d0dqNEKucp25CRkBTtGqF2Vg9BQ6sx/bqfCpZ2MEO06rj9YMoFgL2Gc1vvD1
-ol4t1lBmUWA5Y076J2dJlOQlKr7Yw66NrjuABx2RLeCWU/+NZRSttWtAedr55cDRnszM9sgUWs1L
-KpjOd03sdQ+tBRgl43hfspqqCgzSaIPy8eVg3MfZlFyqsgxuVJWj8ypBAQ6DdG8BnOECTolKwMyW
-bGTfUAM1ZG7VQaLv4rG8AwArni3gdkVtf4tL98PPkIjK0h1j/Jx9hdwJtdKmqN11O2VnF9buIQwj
-84EsnIUwIdRNPg3ZOW7SpwL0NmquPkJhZluPXu04TyTJBEe0zvPWqPrHwEYJBBxjeECRaZKiJ9PL
-yE6KJALrJDkCD4RXhI/unOf7pq0Br+R0mWnoivNQOMgaiWLadU1ZrBiGvHeqNgkxyYz9CAeVIFVv
-36Fz2iRR+7OlWvmcCLkU2hjXHfiT9ShnD62uxoGr86Npl2T04OHYexEho9kCSuQOF/hTxRw9YUHY
-ERO5FRhRjhazrq05NT+cJp9P4TCIq+paBPV16pDGgxX0UNB/QvFldrsSYB8YpdZWW1teK1lRirWp
-7te1JOCUtAoNKILRst6aVXZSxG8D+Nj6SUHItNG95778JBI83HfGaB2nAhdHqzL3Ho4s2DVStub2
-YGjqu7INHXAh0ZXeb8nsIN9DcrkvDUlsBqg6libKYXvIR9r5/XSiAfackoURatODZgTcK8a8E/ad
-PgpktyE8dGqJMfsUbRCvU1F/m+fw1rKoKlZhXBKRSso6geBa2WwHhtxpSQk0y/hI5FIDrMIHukRy
-FZMsjh7eSRqk2pGyaqzI4fGwXUAlUUC+aFJSTkjLH78VWDLRvabORpQuRXs37kLWXMjQYdojcZbf
-y7xwHskMLbptGNlRjUUZ/wlhUO0hmyY8KVQV0Q0kKmJdUbzK97q3jPCDpJiUx7PWLnWvbz0JQnmp
-tXq6benUb1OeW72mlt7OSk0+WDxNK6PGsxUYTvBYaZzjceeX/h7v7dGX5EIpxPKVtNGgFj1ivwP4
-sPgj8AJ2RS/hlgJbWCZPBqAiRo6WiPyPMA5YiC0MgGsTwmhwcmPqE8jPLiYp30/Sez/0pDgyzk6y
-9dQxH2FAm9xmsifTPIVUMlQ2PVG3hfIYsh+60PiX9dRHVp7W8UMy9Olj1xJeu2bdKPYimelpDgHY
-GxCRrveui6xbsovlJyifdFU7fgd2wefc3FDXre1yzDDHtvZaVZNF9Khku89MvmqKwZ5qEfGrcQ+T
-8I1GcQ2/fCDZYGy9G8+V9PCRIqL0w1MyZxc40zgUdHUVhBA3uf6ITEhqzLmuxKWuwrK4CiM8NQkY
-D8daIp2dsAjvJQeSM3dcRFpzUlERA75vQnIwJ7T/ciRUYbL1AUJozHRpQuqX+Ps+97+BQXuQ1fhG
-Zjo0TB5cnngCdo8jEshQhe0et1l58YXAnVRzo+cxzcZQ2ovIxuoe2LsLdsiULlmS6XxLGUCl2hoO
-FuRs7vMvzB8AbB3RrDn2kAkcCezmATWT0wOHRccSrLXfDI8Lruw5BMtMGpagSZ3J6pIgYDCz9NwI
-I9hao2dtLBXRpIDvFLxRL+SEY1letfFSQSB9KdpvsZU0+bp2p/E0t41JKAg+OQ6+MWPhqmXTzQlX
-YVSxhtOGuSD0D5NpdRuTUsdm/cnLi5kV8rFChspBi/5pbCKnx7Lw3oSGtZ8W7SW91fEcl7ImVGmc
-3yaPqi1fM8qis+Fys1zdOn8bBkvchzNg+F3TiumbNuP00HE6PhM54b5NFT5qxpmSo3U6y3WZTL55
-HjPDRK0KWpNUDigy+7wJg6ugNfSD2pQqhGi7S0yiJo0Krh9X0og8a4veNXumhCN6hTTAdLLXUMfM
-k+MbzAuaPn3O2+pQd3rYyXx4aZu84gqGzwyQ99pS3iFjlrTtZjKlTWAToOdqSY87Ma4iZKTIuhI/
-k6gG7E1pKpOeG22VuWb9s5jji64WvEw87T273hApgKI3HdiyaeSvZxXTgY/0NrLJ6G5Q2nQrx9bh
-zp9ymxofNYy7QSf93e5IF0DUqIdDTv35ZhY+vVXXqY4ysatPNM/k7Yw2N8gQ10G8yiu/f8ykRWx3
-ZbUpkdRkvvjz7N16EfZ6e3SRz+IP7eGoODg3AdZWq75ww/uoSi/AQDhZ9Dq+YXLCyMHOs8NY+zA4
-a7NbHEH5MD+A4CkOCM+GZmNHyj7gecFLUkD55rSSJG8Jq+KP2aqtdYG45tHVAbhdsr3ik5wdljDp
-9XdtytistwMKudI2TuB1NCVTVTrH2u4d4psJX7sMnGNu+okAAUZo2NBWUTQCIwDrwMPemraDAYBL
-vjbs7iUFcUn9MQMighy8H5QFbMq3j1AS2AaHSO5lwwkKZXZrn6ngylVUM1XsN1U132M4aZLY+CoR
-Pq9rD8Neupx4h9mOH9DrlRfh9x3I2Sy5S+bZPfAoiTvk0/OLQwbRFpW93GBKLqj3ZLuyZ9JFZFqi
-s08S1q3CTm/ROQEC8HrOzkE1nFhxxzXWVrXrWKVJkk6Z+5dkCK/SKrBeM9oNxK153UanfoQEXbhE
-QfsxfolS/oCuDiCMrh6bRwrZaAOI1VhFg5GsYVoMG3pIAmCEBcE1Ndo3sLDy0eL+vI+0xa0Uipa+
-w1w+SKRayJxtF220wK7GIkuDqneOJrYQuinpFG8UrJHHONfpvmvc9rUKWOtKkEAJFDSUbSt4kXzi
-3Ogi0kcLkIA69EgV9sroh4OO9l3iartOi7iecaIBV0oRQwukYa0IFF3bZuhypTIyLQoxnSJDseWE
-Zc+3M5SV+jAG471Q0xc4SnEG2XXHDUW3nm7SOs/a5C4yrLzbdEm9VA4LO+dCnpTO0MsPTbcvWTwj
-oDRNf+C2rjg+ClqmQ66io5XE4bNXmc20bERwfUof5C2SeM9DMjD7t0VvBQfp5fUPOySAm5574In2
-Whn5dCzMkTzY1OhreFcJ8pmojYP7kGbRI3dX/JoW2nobbIFnAh/dNjRkuAvKYL66RUlAFA5aBqgT
-ALc2s8w3VJftczrbNKZUjkE6mS11jGo4xcjGwi8/nNVGB2a6Jb9meqyAIt4W+D127BbZ1vXq5qYY
-TU09avY24xfrV5XcrQFeVScjofoCeJXdSKA3R9jBOGfYQ0jbAvixa5x+vtBoaY9zlBofaRi6L6Lh
-oF1QJB0aI4I+45KOOsakDVstxGh77D4NEBXHeLADa+XZg5uRZhLfYiAZ77gjM47UTv2OSSP5ARqY
-XnoUzo+eZ/eYaqh39GZifIyCYUPXeIW+kT9TuiRPE3apjlQMskHWZt82j9aYNxcnLav/Rd557EaS
-pNn6VXp1V9cT5sJcYIC7CC0YZFBFktw4KF1rN1dPP5+zqrqzCtN3MMDMpmdTQCKLTDIi3OwX53xH
-Xgs378Dl6Kj0pdartaTX2lVRyAZ9SsR5NMMZJQUsaefpYbou7RaNio4F2iG598GH03EdlgWFiO4w
-tEmNnueZRw8gDUtMd0ofwzpDQqIhoZqa4qQV2qOTa58m0s6HrNSqu0JZPvyXIZqr2qJbWlF0EVrd
-3Yykvz6YcNPvsFgURAff9oxaN7Bf1VNS2M1Z6ubwpPmQUmKEKEeziNylcnz1xLHyZJMXeRq1uT7o
-s+QaQJJxzNNGbNOANPIAG9jSh1D+0WG92lS9ASY+6yJaFcHpgMBqR28YERRTGm0I1dKS+9Rpqm1X
-u9NzFlQ19uhxMt7hjVGPNaXQFil18pH8DWiAls1c1sqJWJ5BS0GJu5jUeKQROf78zgzKfVbazH3s
-dlubjjqUvU+alK3rT9IjtJyBZudnUNQz/ZZha3TsJux3zGxjvqszbIpSJPtApea5dKpmnXmejnko
-d49KZ6QR51898xp74M5IcSRtKaM9olbgbuOHCMXSn2OWKpupse0Gz24YfqBS+nSZti5JogczqG8G
-B4lahft1W1bFZ2InBYE3s8euhlc0kkmTjNYqzDqCsoKr3ikug+LYGSZnNczUW00H300KxppHdql0
-C4qRo+/TrrwfG7D3ELEd0YW7kbwiSHgRCgS2QgRxDyyyXMW4J2vEIjC03SSqQ2pa+A/HK6ti+j3q
-NhshvuWucaGHWS0xA2zcI5pJpeIXB9z9RiOl80RMS3IPQcB+kDkdYzFFjMKzQt/+32mOe65Z3a8x
-tgWvWhhaJ1pgsZlI1dzmTdQ8fivm5tSLf+jvmz/nXvzlj//voUAzmP3LJGUA2Uaf98+dILvXenzN
-X391gui/fc3vPhDAKp4jhONInYLqFxrL7BCxTVsIpIXoCy3Bv/O7D8QUP6gqbBuXBoJ1VNZID//w
-gTg/cJUIPugGJJb5b77fjr++Pf/486/+DI60v0hDKZ2wSXiSf0W4HiLnP2sNE90IDXjYOSNdzb1B
-ltg7GxzmXAwTNVjAGfgs3TLd58zfk4VXIRGUAxIAgRR6Bw7F28eIZqA88z1WHeiOS4EP9cnoc+ea
-JG3rMZJkI3HomIx9zfgNWLd5jX5p2Of8d2dnSCGXrkBaOBea1kcyTCS/NhXLIjsVxgPtKtqCaA6J
-pYEGE+Da6QMiCuIFPWEcZiv4uanMBEsxUbNtiJQ+KF2IVnMQbTZH0iJ28i/4BeMTiQybCDAI40aq
-BqaU2KzmWNt4DrjlhgqIFiJTyYyxl5Ms4S9J2a3oE1hNXrOVyrdRg3TPGpJ0ZVYqWZvuQFXTMtvu
-BkJrFaP2lee7KzdE7cM6Q1zh9S5PLEy0wzDn8ALj7a4tKtNNR4d737WiPTEWIeraIb+3MqxmH6SN
-vub47e7SHC8gqjq6zxTlSqLktY+K/tomY2dbwSx+1mn6lpPGrRY4hrXWjCq5SefsYJkwSGrrclyk
-c7Iwk11mgVFcboq0IJkNIi9XnpOu/bqFdYFH6RGs2VeetyUizLYGpz9kSf8M/TS4tF3QP42h3zx4
-vvI/kbNzxljuVMLorzAsLEfW4tHeFgq5VMRWaJ4IWYRpYbqlFp+c4SUeq97aJBDEzrmLuihim3f0
-YOWu6xJFOT5e+hgQ1563GlHPMCXRTODgmpUyNi3VlF8xXs2+9HGQO7/TDdZXhY4nkLnaFfIqDSqH
-rO5ZGqUrq0LQwvzxaxzi/BZwVnHQBts8JXNWdDanRg9zfjTZ3uoneOLogv05WDWVdkd0RXmMu974
-YisvF5mIYejGqlLFIg7G4dYw4o8QCq6cA6zLGrZ9Nzj+EXGmXKk+n1EGcYFy0G/nBGwHccqpm2Ox
-wwKNYDQ142GoJucG1dEWOePjEOZEu/VztHY3h2zXkAV3I9ukXRARwV3PYdxESq+NOZ670Bom4+Zk
-2rf9HN/dtwR5j7Y9HKoglM+hWdvuOpkjv9GkRJegTJN9nvT9C8tf8UqiBkIK3PYQKwkO782qWUUe
-+zVb3kaDXhFoScy4pwCaxmZVXeRghkTEKfO57Agmn1RHLgFw0Dl+mMnoycqg+KALnwPNG+nBljPh
-7qK9Yx3k1OUNQHYM6W5Z/vTZeRGwlgm1w+pBYyFoATYEgGEcEGMMksLS75A26KQkcDrcQK3CBDlA
-e8NHmREF3hl6f8Gx5RyQdo2MCLXixOATIFAbGzfR5DanMlf6ug3b+tB0DsoXF2oCWOuytE9g/qNu
-7acYyknQ0j9de2w/lS2rEyXcUK9YeU/6Uhpduia/AIlo3jRAasie7R+jOswreJWuIOJCqsRZeSNa
-72yM6S18M5bHypy9tirv5MnIHbUuUi5W5Vecg/CkhFyVVu66yzymPW9JEok2k6O51y00FfbbHMXP
-RKLM5P3BBu43p8tMEFIDss+QfdMN1ZENrLcmEf6qZfL9ZFphkGGaDtTtoHX5B6Nde2CHEhgvFuMn
-CZq3CZ8HtB0W6tQEiYxDb4VoGDqw88yGoe2BNZnuI1lOEl2q3j9VwoAgScqGyWZTK8a9hhg237aZ
-a+pILSPtjRBRg1gDWTpPCrGYu/ZSl4nR7A83i3E+tHt/5GAEtULUXpsPG2V0o9q6hpit1IanPdvh
-kJLRVgyEo4x6MwwnG3W02EU062w4GD5fkxRZhWusVXjI0LATz9pofVxvR7gs0LsMWdzTjlO39wyV
-kMT6dfMm6ondm2LAER7ZzxrtfRkK7ejUU7ZRWdnWawc2Kh6oKhvvRZDgOraMRD1HdUByahbReC56
-1VvROmkYuiVKs9mBNtJPIIfqMTIpE62YASrgAIHD3ut6SyvQmNHwVWt2/pMhdkPZ34zpEv01II1k
-qNK7KHH8n6r3mlPqWV+IUGqUH96dNQyCvYAMLFzjaWFvlCB2SUk1vIwopxn8qM5+sZRAPTnzVfbC
-DmjOI4wH20DvnDuf7Yp7Dua0aBqgTGekijxv48VIKde1w0Y+SWfOpA3wocfynsWP7AaGI1zD4CKs
-iJ0veUcNAl+BMYk8hP6T/YzCqNETP2dHWDhCHGcnLekahxiLWU/UZkruNS3lua95EJ5KCCEPY2sn
-xz5zUPhnOiDAZYErZNyCFuq2PjL4R4UN/ZRkElR4ohHSt87tPH5iWMPP7KRudrAtFt2raaLpICTe
-aw74v6qfUIwyax+RwMKk28lmpK5nEjVTiwale84bp5kpG1RNNPyAsgvSj0rrsK4OVTxdAw7niWkx
-YEFhTdWRM1R/FXo7/oTbBr48t0bmwyQucPbmJsksfGvWBMWgnj2+/rbpsMYTUuwxxJRSe67Y7h2B
-6IvHLG+59LpBgnTPvUswDeyMSy+9tUwQ86t+kN0qJPr2ZKbYgxaFzyvLodvexL7F/BEcRXvpOmtE
-GB6ZxYuWFOXeg9oX84yW5j2pQAilOBW1N9SQIxpfxn4IHNHKQtb1XUoF4Fbpa8SKpNxqXYfOI25H
-PIlxVNTVNqaLe2rJKr8vcpF/OiHd/0+sI4yJ6rF37mIzDoPZHcIr2cWTYqdaJGcv1Blztf6MwLTQ
-QR/9llxFN47D257AoH7RuCTM1qTx6fGUvvFe4Xwnyba89E3LLdAx47csfbojl3DeT5GoU4PvnHvl
-BE/creYkYCuMShOXEnoykVXKcq46VqgsZBhIYRKNak9dOfDHRhiyNnEsxP60rJ4T/vXeMQgRNJLQ
-f/LtId1nLIQwT6a8qiisyotqBvu27SMP9ULE+x7DRz7roIxO0yA4UYVrNXeKHPG73mUcwIxPGBu7
-1l2e+CDK0NWO9hUqL7NaWtxwfDLk6Oy0eKZEF7piPd0lBKBOoqWi1UHgNoyGbmzIBzoD+9x4nXT6
-QA35REZKTCOu7XrgFfHSpCLUdeAVKq0y2uls2F+TKDXf4aDzYwVe3F489uW8viGx8Y7lBO+QAtKd
-nSrvErHK2IZTpXH4tcZ1MhHvno4Sdw2Om2kb97HccdMyQ8tsHZxXFsMrQz3deFc+UufjYLVM1QBu
-tSizorB5YSGPHj7NG/MrLb3s01exeZC+FryxRBlZMTRMqGASXYeuKfYjA/px8T/SDv7rxSvCKcTq
-/v9pGqPs9T18Tf92rl8/PpvwT93jb1/8e/fo/RDCZekGVApPO9OUPygCjqSvpJ3kwEbyR/wpf/NH
-92j+MCQjIeFg8jcM+si/d480lqbjzCxPPq7O91/9F9pHw/yrVQ2bGigCITHjGSY29r9Y1QxsL5Tw
-rbvNoS4jCGzYezWeRtkOEPKdTyTHlQi9S19Jd2trfbbILL9dOX3s7w27wt6Ak2HHpWOsCsibKvOy
-rZW18UtaJ86mwNUDags1+HvVsrj2GhwdKfEp1xq7tDvXC7VNoXIwyTpt2AcGTfRmYePclcDL+nUo
-SuvdT4vMWjCnCjedlm1GT52i2EqP2Gp1Cne73RNaswduY1Gd5KTZl96NAG27KxHOP9lB5X0kGooR
-KujRxyrhq42ZY7dcziF2HwHk5xclfXWYmphFsz20W4Z/4Q6357gdSXTbNuDnV4GRnlgzuzfgM/v1
-SFYU3i6hI1NVs6jMohyC5Hju0fizWh9CPG+mPW79NEeNNvlR+dhNRfFJ0pl9Qj1i4mZQD1MjPAin
-jXs2HeRHC4OID17Vwucsjwp23EisMUr6IUT+xUgy2tYdGU8Dn0meGhBcBxrY9pAnxjuCdWxiKMmv
-QE3Txjluc5+y8dibWH1xZE9CLoLEid5CZ9B+Gn4ATixqrKvAbfy3cuAQXQyN1L4IqW5PGSXNU8HN
-dOIN5/dEOrjwq5yVprCue8YB+crBB7QE+kULKtyvwQJ1RB0HxjqFKnUgYAy0IucmogtccgyZFZ2l
-4S/5wFu8UFp+b2VGDNwOnk3oKvEEuJkL1QYh70kGqKVK9LntbnalgYK4Z++ydQPDoZNjA9wxKC4X
-QW/GLP39i0uJvZJs/x4skbaLruEWa6fQfB7owXbKQDTXWU52E6Vp7CxrN+wXDBQZSaNVWDl+s+4T
-x1gxwq7XeCc+Ac35VG55Ka91vYv3qnIXvOn4I1uRXREF5n3I0goeh05nSw6h5zIORnpwQyx+fQ5s
-n+Qhr6LjBRHQwzm/ZbohcnYKGmGWhVUTrc2i8aOxmhuPtI+ljpFqo8rYuJ7MMdvEvT0AYiXudIFY
-3sSo6aWPqeMZ1WqwyRvWMl4zL9YRb9Y5yeVsb46a65Z31MzOcQJ6sxl74qrNARqg1SxsKsFtOTrO
-JSkJQaawI6KF5bisx3jVy4SxPoXRI34R7zrktyPvAw7hWvg97W0VxsF1W4jgbE6MRtvQnKFoYHvQ
-PfW12DZmD+TIF0zMxxhtYybzdxeYnMcqSat2mqytDWpSd43o7Dyp4r3Rh4Ob+PFSE/3KQKa9qfFu
-ZZ1Z7tyqRljAEBQ42SogVQ93fmwnSyO0/zNfsDmfar/6qTn1DGFxTuvoPjiE56HaLx5k34mdvmg4
-DmgmDLjasgDbU5as3vk45uUVJf68ITbWcAaf0iE1w3VR1fg8Jh2WUEBs7LGduv7LJ6eSHPE8PXqM
-yrMlavPkqgjM/KmAlLBpHMyTaxtnKNGpbY1omwoxufO+n+fk+9km1Nm09jnPhb2HVWweejkSQoj0
-FDGpsrTk5Zdr6vzb7/jrwNCx/mpZ1yFmWtw8gBAsm8vnLyf+SH4RQ+VAbHUZgGEjPTxLzHsUsS/C
-EvGCYHuFDiGorpxaOcESK02/cbuB7WlVYzhZaIGs9bWcwiKl3fUHSlhJ2j2RNp9UisFDmA3j3qn6
-nUXlV5lTNSwNVb+4TbspQipemTcHIzVcVmfRe1WRistnKzsPiKv2DEwrxMOpOnh6Ex6MKstIAktQ
-hWHlMvd5V5v2UiSiXfM6kmjdJ/GqA3W/xZeSnZXTey9kIOUvYye6DTup/M3ITHUtg7G6TonO2IT9
-LFtqe+ep0GpCjTLTP49Z1N3xR2dTTyp6QoEXHhD9TSuIn+56Qri37RFdbAsbz67h9uMeiw0GA9SZ
-PvohI7hnjxWT/kWq1pIfm4SUOAk3ieXp27qX9ibhkl2nZqKgS3FGruvGry+tQTxJYHrlhRLfW1W0
-OF82+klUoElyVHinkT7JmNgnwmWXpNfIi4at/IbMHu3ebHpjx6YM/c3kiuIT2fRwsUH4XqRT5OfQ
-r+ozK9vuIDD/7UzdCq/8StQ7Jpf7rHZXbReSDF4Qk1K5s6bFUToDsr7vb4d5A9X1uUJdnhIlG1pM
-ZdNRIXkhlvxeYdJeMnSg0C10AxSI6T8UvkUGu8/6rI0J/Gkn2WPHxoTzwoKqP00Qua+mmsAsETbD
-MQ9cgmdc4NEUztGVI0c61dpxTRRl8YjdhL3sUtQdDlFWTTfMETCTMNQGLKgHSDwzUG9gTXBA4W5b
-e6Boz4rArpMNOhwpR04zFpjkgtmOdxvOpwjSDcoVZ6+xoqxRBo1GeA9weEHqQIbjY0SfyLooRnq/
-jLkmSAlMzs18ZgVEHmHB4hwzAz28zSZN+8Jdl79381mXkndW9LWxsKDfLQCVye30fTCq70OSk8Ja
-qfnkrOczFNUd5wzyhomDIBQkK83nLQjd/HGYz+DasIZD3hecuSV+6qfc79yN0Y+c6HpR3XVOVRwn
-ZDgvkuHWqkgdh+a8NmBtzxdDPN8RznxbkD2Efi+Z75AqSCJ4BwyIoiVuda4g4ZWMyD1tbJkd6pXz
-MIpC3iB5t/zVMN9rzMxM1NuYSOS2EXjntK6ELj3fk6qOpxWsUG5QEqTct75k4c/OXpFMZRtReSzT
-rOMMbbNqV/hJv/VDQCCY2eYrfRKAG4NRa9AwyKjbEDtKltTU8BY531XDOBcQGpXENJcUACQoLiAN
-x+g0HbkK57pDUD76XlgROTizWP3Udde+poZjRkLOCm/psPcldG/ym7JtSemzwuQe72OlSKZQLuHh
-euch/BwKvAR0eslJkoiwNzG2n+IgM36GhW1dtyB67/JRZ6VZN2GzYdTufVZTaZwHZnrvXaq6c9SM
-0aMGZvTeZ5jUrAKhnD1kaG2lYbsYwAdaCJx0oo0XtHHmta2ZaldrVYIiii/l3DDg8nFDyXM2luGh
-RFZ93arOixZl79RvQ909CeafK8/V5sGWKeQm811969JFk7XFLw6i1NhjkUSTEKK9fwg85liLspFY
-O0mKOMuJqHCsstY9Iaf2GUe3XEYOVxd9Z/FQItGJ4IbW6d7UorhdZdgQ80XYuTEXb6mWOMfi5mSX
-pF7aXe/tKCyJsPUm9Y4xouQ1hv8MeJYHbdP3kxQLm2kXig24lz8JyJHbJOYVJ+LCjhDvlcybalc7
-eFWHeCkehkPsMIBDElV7GJORHIFuFM86cIEJOeYDLk7wkaRtb6Pcjw4hCvCBF821b7H6JS+xaZMq
-I0g6WJh11r4FzJJeSoXaRDikWHhF4m/5X94EOqj1TOJct/CXjkbp8eHXnDblKhfRrUZ0C2BrcqwW
-BRuBhghF2zpH/Bp+EoP3JwjbLUpUr/H0KQyN2WdbRHTjFADaHNcBIjFqK0z4hngqmsRCoNSokzQZ
-fwQ60+QeTQ5f7EzIVclSIcLArbBxuOxM6AEWRLIePGF9QSt+w4BnYnbOSGDz/CLfOzAeeNqBii7y
-uArumPyPW04eCms/ERdieeDqFtlFt0rjyap0tetUWv7sJYFD5IPVn2QkwDxH9bHrWsBonriYdmoT
-RxBLey+t4gQI6CZmgk3RP+DsHgZ7nbjcFTxWMPTXohuw6SNItQFRMQrZu3bLvesn8sBMz9xNbRmv
-9VqOzxgaSqSBCBaGXkOmFNr+u1FH1jawif/GPT6X9VNOjA4L84lkPgtnYehvPavSNraOdSeqs+gI
-qTgYj1CCijtb64yHkP4FThlQtM8uYRG4NJPGvSLpldOmC8z4Pi97FhNTjxsgzpJs48Tk9dVofimN
-iQHnSSQieeUATOC7dtFrGgFD8Z2yPhiwd3l+Gn73LvX3vXLjY6737dLlFyWYKdZSrIVBdZPYTbjL
-Mbuuey9tyLqYBhonE5Qk/sj9gMthG0n+fYJtnKeMSjACnzp6J0x7I3kDZrExdeW8hFWkb40O6DPm
-3oSEqHTkqa1HAVkgDwl/K4tmH6fNM9u50+SIrxmAuEZ2pL+2nebcsLHleiwfGoQdjOQIbLszgnrM
-tn0UTR8xO6UFupdL1uYU1eA8Vjhg9RWe7H7riqpZjKAntkLZzJRYYV7aAFcUsiOO4qruao6krl0F
-SA5vS8fP4KGzstZWae62D4wnpge7VEiXE+Gqpe7IK9i07A3nMJ9zmhfGCRYxOGk/sE+skIxb1Uct
-ekXCrPKt53jaPdAk82zqef8FtcBvZp1hOWBlCabQvtHs0drVUUJZpOWnjOmeJSqsAg0SWyzW8daO
-VMUpYtBjDI22yuQHpLU0xraQswsh/4AILQ/Ja8lOEgnWdE1BeGyN7loK9eQmxKTeAbxhvM9Er8qN
-+CuWwXWSZLgT4K/dOtKvnvl8cXmxWLrpCRAhAS4vn0TXsQ+IUqYQ2Ce0euvxRD8T8do/2plnPiPD
-kj9tFknLVjTWvmFMfuAmCK/sFB8TTG0dO2uarUn1pqiIg31bx4wXHSKZ1KDCWza59t0o/PFFMhYm
-wTDI9jVBfsspxk5H2rZMd65by4n71BmeGPvBz87J6EJzZ4S7wJLZPo3Gam0x3mWBjNEXpBk8QQ1+
-+Qh9G1FMEe+sQtLIhlSyY4p8tYv0YUcNiWnJKnBVL4Bk+WeZ4jewqlkKnyprTUZR+Ii4PNp2RivJ
-e1AVzN3a26EeC9GmRCPe9Nl1wM8APDWAdNvBX3iqunHeoA4A3fIouwtyDlEktNq06eYL17VDlnF6
-8phqY3lILGR5sI4pyIgt3uDJpOdHe/FAxEWznlQJNYEzA934mJYzY9Uxlm2q9fYSah1PYJILDuwJ
-gf3SVjxZ/CjFsvUyvqJrs3Y5Yle+jDlWLo1l93sZ5OYuJHZuC+uuWTWtPfKoRNkuN5hytzlB8rqb
-xDDhQGTjY6l6VPNyNYKhPBq6759y9hb4fN4kg5k4Efug4CtC/4hBnICVBCK/KkKm+C4kf6cX61RO
-44EJHwiU2rujL18aHu7HxMiAadian53CxGiXWd856EW1aR0NMqRNQhg607LTY+hKh5fA1/d9Xegf
-bHCx0xlN/hX6ZDJAcYv2rjlqIHZ8DKmmz5ac/PYEhFKRPAMHQfpUJYZ/Z2mdRxqMnZ7pVdqjFUm1
-B5bMZIm9rnmJNatbtkFUPme2iaezTIsjYSHQWJwy3pWsXnbCjNKt1dXVVW7mza6J+mU5UEoOMWpn
-w/ImlqKxvuUJMx9b2rVzqwHwztnkrqOM2UeI/EEXYPnbGRJiyMPQ7EaX11PlHgZGtWRx6N4Zeecx
-IHfiiy1Sa18laXrlRI2LdJU4VL+Pz4Fp9+q36faftE6/9sLGf9QKS4sIAvipOKi9v6DqIPEYvm+Z
-7laDiLeWVoz9LOhA0lQSSTegAPpfMx2Ch4DsRQwNrJdAXIeldouWZnxDMFfWhFrIcI2bemK3MM8r
-memYmKXIt4HOE6J0hhI1TzgFwTGAugYGhCPO0AMYBmJnGzpE7TfC2v9mEZfQWbGY8N3++Uj+9Jrj
-Oa//NIn/+5f9Noz3rB8OcmNhupb8c7CWZ/zw0GohZ5CW4dmug17r92G8IX/Y0OoMBF46+gVTorD6
-Q8pl/nDRf0m+oyltz2S6/l8Zxn+PnX4ZS7nClvwzjiE9KWdR2fx5/WUsJXHil5pIPCBPnE5jKJJl
-EHkHq+WSLxEIk00UDATUxTmPZArrO5yGRzD42n2uRz/rwKtOWuVOYInYfiLK7e6azrrVEUotkonW
-UmdbvjOGQiBkagI6/Nq/WIab4UHV9k3te0tLuUSSJM2dliewHxhkv0ktwU9NEvgSncU5dmPXxW+b
-Ud023JoLrg4LGWPkTatS0ooQxkmuk0/kzdSP5amOrSFcyWoUywwoEPJkP96SyMy6jhQeufMaLq9U
-ZeETxJPPBDGUswraOUUUtfFLZMRvPU/uLrKs6xgd1yIBPH7s3axdMTfDJmiNX0JDvWqpvLoe6I4x
-d/vZHXLs6uQlcjfCIUDrTcJ8HclhyZ2hLzH4CL5R9ITqCw1qW5JsibKIX6jpsQThkRJ6HV9ix0PI
-LnDD1EamLxs+ImgZ2qy8E3380cvGosz0/aUZjuy5ddE3c9DeS4ZimW/l5x3rg9mZ6lnBPcyFZWv2
-2n2nnPS2S5k40E+yccG9LTAmOTjFARKEwORyHdePXs/f0+gFK+l59EWGRijyXdSChfCNgbjWii3L
-QuZ1t1IaOZ+7lN5eo4pI0yNZv2288SeD7DELqpN/xBTTEumIbI786Ub9bI3ar/dNRYm7ZavRHapW
-ViQUIJu3V50c7dleL3ApxPN0ACmYJd7tyhwuRNAyYXGB0ZAa6FTVuOwg3njrURu9c4smzsZ5YgX1
-EnOCZCTWT5z/eDCip7ax6xM4CsJfca4h2Q0IwLgJgxw6VdtrSBRags8jtIizYbm7oXBs9NsxaRnf
-e3GDbEJYTuqsewtGFkez3vd3ce344c4ZB1Ud+ISZiIhdQoNXjVMZ15rW519FGWVISlQAcn4swSd2
-NlJhEA4oklposN6ip4/pl3bvoSEI9nhYqE5lz7hCJmvkfRljBFMs2MkFa8u8ZsP3lDbOeYhTgWFQ
-GGjV6l3YWuFC1rCmyinAeVjcARh680vrXoHOHnVrvI48k9lVcsp6VV3Fgb8yk2Jvhyc7Y5WRO16y
-KolyhK3CW2b0ctVmI0JIkZhnMta1Tz7Oq8LNF14nzkZLQFc+uLdA0lAEUhBkHFEbLzNKYBHqy5xu
-M5xWjcvX6Hr5lJF1cNuAoyrtMFr1dU1IfEiUHOMPe1Uk2ocVpcm9V2o+tUlzRmS1argPGZDVAR8G
-N9hRz6QLGD8PmdmF2ySBodGnZrCr8E3S+2cjDkyN0XGGpXlENLpO2kJ7tSAvLipnO+RFuJ5MYki6
-EuUALKccVhDmOCuuIBN5ZgFpMS9OIortF28M7o00g5PiGmrbE4PNIxNvSAF3V7pJGjlgNOcdDWOz
-rvVxrbtDc4Wyb6AIwi6R09F10rnn6DsFFPsLs4IOlETups3A3jK/2lijYW8rSJNZ6WKgtcVH6gTM
-Wm3sJQlOMnYgy26yMH027oM2dfpn37rJm5qCr19up/9gEm/Yc3nxj+PeZe1goyi20TuasDwd5y/l
-R87eTaMo93ZoIvBaZrGBQwv3zCpg8nvDPIqnRJuUpASukuaE5zHCL1D4bJg6pt4wnPqQcxJBD566
-wvfOsVEqbx0MSU06dBS5JrqfBA9q1CXjpahzndGlz/Os1z2eQqdMmXaguqjt1VgoRplDWXeHRA9V
-uCWsRKv3tS45LPLSPzLz7Do4BfNpon2fLNX3KdPMB85AkLi2V+3oGDueSwQ1dY3YS5FesnHDJL5r
-Yw1LbloJZ19XkDnq3g7ecX0VC4N0JaYG6irF29Aj6dioKOLdjLurOVnvKEV+NBinHyHrxHhCcRcn
-Bl6oLAswxeeIFztl3jHlRkXCcXZl5z65RQgyV15H/6IXUbPKBiZCeW4cTOW0yKaK/LHugmINAiXl
-s9pUGUveRMd+QB+C+8SeMOs1AAmZs4gYrS0bJE4hEFlxch9hC+iPJENkLJCJnw/lYKwHaAm4brWM
-nUGQX8LKm862T4vVCMJ/izo+4ruxzsrKJ3ohAreeORTYhFdk8smCotIpphpFCPyTmw5t3gdrTrWO
-8vi2ZhN1sEWEJjHIYv0kLD25BrHj0LjUrcDq1WZTxEDdsI8hcR03uZtpWwJrrXfX77StrqXt2ddm
-LyF5QO8+Ro0R60+lXkZyCkFRwI3xpRK35AmkK/Svb1bq6zsxNNm6KYjSWRhZfU5DBMGRNLZphlZM
-r/QDtx0zTKV1Rzeo3JU91NW6D5t6iRAgQqmDBX1kYyqf8P0M5G3EP9OA698iR5PfxBvXmhuiziv1
-B3IDC9R7w6625njPtGQUZn4EQu83dqW9V2YM6Ce39G0ZtgccZ6tQx7Rs6Edwtz8J/ILfGe6LDriG
-bqMI867p3tlMKSU3w6Q+snDQEUuan4UVeKdElQyCHVFvXEb8O5ibr9JtmgOsk27ZsLz/GKE8HDrb
-bW6zwoCW19CFxyUi8yxLoNx3zTvFokRSan50FkgwDarFskoCd5XpUXS0Yu15CgGoZbhmr/PKOxHA
-R7Jaoox1Dl9rBZCdyVBb+ktofTmrx3pC7KpYI3YpvmpOK6uP161boiIl+bBs2tNUEjc0QozYOhYh
-idlg3AM8G06priMXyIz8ChOLTfGh29fEluu3CTu2s2R6y948wu7lpsugF6gUfej2B6JjAXQA+7U+
-Gz/t1obSy6+kC0gaTuxiQ8BOscoaEFJmZvC3s0uIaJJ4W/XYtJapMsbnATkgq+VhNH46o2rLRVcj
-Y0O6TOw560UiBaI4plmN6K9JzwJgRiK6vZAguRHBzZn38z41O/rzHV3Pt3XyfXGX35c41mQudNNJ
-A0KWvy/67vvSn74LgJKALTKrvwsD67tIsOd6IZwrh+8T+r+7j/rXUz+RXwKV+5+3WodXMFh/+z+v
-Wflvfzu+NiGJ9H9qu377+t8FUPYPx0XhxDRZtyyJxujvAijCjD2UR64j6KHIiOD++0MAJX+Q5y1x
-VlNYeTRkLOh/77lM44dBFsm/s3dmu5EjWbb9lf6AZoLGwUi+9INPcpdrnkMvhEIhcZ5pNJJf34vK
-rOqQsiqyCrho3AtcIJFTSKLL6TQ7ds7eawuEUxzlpESx9G+cuZwPwv7/bMIGx0BkejyxX85apUVM
-hUKycwJcBtcg0e8CzTpoaCa0w0Xt8ChsA0y68P4MHc8r1TnZFq1zc5zGITxUUdTspthzL2TJAcec
-Rm+D63bc52gpt0YfogaojYhnXbli2NCW5+wQQu1rqn46FBx2Vzkiwsdx6S17jAS3XWPGe3SYzaVQ
-VvYYUaFjK6lIG1q60xr66DGIguBQzpqW79LFLsq4PWV4TaSECJIXf+l2ewlmDpLmlyZ4t/TD/aUz
-ni098mFiXaw+Gud66aFXH+10zxf+GRgcxP3I9vu36KP1jgbEuuuXfnw/Ncl0bJohOU6Q8qCEc/oI
-gYafTDTzHXzQa+lj4Pv9BFVlVqbXoVU7wEGYBcBbGZAKMx+AUgnRsyvnb0iU0y3TWnsvlolC5sUT
-1BYsWMcu6sj7Cn6fQagCaKbAX3Reto5axVZOarChw6NLptJ3B7cEQ+ba2PgR+IH0Y+KxzD6qtMwe
-mSrXjxyd1d5cZiQeAxioGC6wzWSZpUAfBXZZo2F9VbYKqQuEtE4YOmQmuFSixjR4P2oTvOB3hlF4
-4zlLD9K0WeWQu8U873NcTkuH2GiPknyqF6NOMpd+GHZ6o+j7bWJyPgB9zk9J6riO1soGloU5wdiX
-DMS3KGnFZs4ptSFXQHeXFk7FKFHWDaKf4r3hQIirvrXrByKnaRr6+H2je6QYPpbnwcKAMEtiZnAt
-Fyh3HVbPywJW1SEomvjKZU9Yi7oNY253pXFaG22F0l8BoQ3ZOGg6YUxx+JHWVctLfFFkdiPpMHBR
-lVMDcMEz+pHuNTlghBkg/mem2h5ix5h2RSzC96mWvCbIhC7GCwFIay34qMTbUDfWjSe78IXuVwZJ
-MjT42ygsVBQJGWpxMAWMPRqCV8KkX7grVXtdWRb0tDmoRbJTMyp/C1PFTeLk0TvmrZheAhSmyUrQ
-lbsVgD3Mq21PY1DPzHACP1dqn/qG+YNJ/fQyMy28t7kshFpD2O8mU1geaUzZcCjhCukVsTIYYO2k
-g9RdD3k/oD4qfXuT0x/2Vz6stGozDq6DEK0Ywp1leL5zFSeEiG1og0YQ3tIRzk1DkRxv8VK4tzYY
-RbzhtVEwGXW70tqmovHpjo7KfNNTU7EDJ8JEjj9HpOFGQFtRwYfuqZiWkwfM1eAmH8dXy0SdMQmc
-/ZSJ+d5EzHYzQsk8G1WUbWbROFe8KcywMfGPD6ORRi/0LpMDccrZoZ5CDLpIAArAEz3hj1lgoQDs
-Cn7XGbjE0mzmPo2YaY4MDSg53alNBnAvgaq3GuXLHjEmgiCOEBtrqIO31kIHsBl7A82zl8TfQc3o
-71GYDpRl4XQxM3y+SkrAnP3kFlcpLa1+FbXGkjYpJucZ+LvNzNSzC9hJhBue5dwkHDtV9MwPKfa4
-e82rLhVo+Z3gGYNAvWUSIc/mgamOr8gPSQY/P+sn2332nYgjZ7lMrb0uRYnYExuxrT3WHnT12bCG
-eomVZaDlfsD6Up1icKrzjU9/Ntn0nhWepak37ieZ+NuYSqXeQhUKzyBB5AgCAYrQLm+9rl6sRpA+
-aye4l7YqYC13wU0159dTWTITGEcKHccvd67hT5QgrqrvpAuisqhzyKeOk7xWVuxgC5knZqjKPCFN
-OD8MqQ1QpsPxDY0221sJlIjcjTWnukZveNTbLRhUe1VOmJQon4xTGY3OtzzqcuaRsdOeuAggMVjl
-yYXBundemFJcBp3RoowIh41Ztd2Nyzp/1URDCDmrwjs/qKw54XzoXEnlZHcCF/+bID0V+V6SDVsF
-8/Q4F2O6NwMz2avS1SelExmnTMlRqWurBEbGcBg8ri7S8wgqChR4W8/fIyPo9mlWJDcFk4ID7pPr
-YAabsGG1xKWIocX6xr4NeK3NmI66NJOuZxNJJsRP3YCwNItTv4eee4mOeGSYXcXvAMSjG6Zc4Z1V
-Y87k6WAqHumOiWbXOhcCl8GLLgr5yLCH4E1z9tf4TYu9Q2fUWwWlgOQnyRvhoKu962K0geu2s9zk
-9qzPhtZw8FzGHlKdVISnEUdo2pCRxsaRJDt6qPahN4YI86jo+x1MmfzG9Tj+JEmIjHeu4/YNsUES
-X1jeML8AVBToS7PZtFZmVrnr1B7Hsxgw7TqaQrxNmBfOyLIfvlnwxXamY+KeYBc7gSdbLWu8H9dM
-0MJsLYRTIpW164uZDC/iEYPGerOHqkTPz/KbdROyKtOf51Wj/O41nP1qJebS2g3ALU9nf1ZvBQqR
-XSW6gQMB29AK7392YiMROY2Q/7xYCQpTJldWdBkBiEHblLfJrnEBqUWttGG+OSCau9pTR08LcRwK
-VJmBAVisttPkZHIqVjqD7zkQkIGwsQlHGsCxBAzKxLOTfsO72Tf3oS7bdcF2so5KmIfZWHU3moMN
-9MnQu+vSYLiKB41uoJjYrxlwH33Cc5FPl8TQGw7FQId02Euldxawr37/3y3jl/PCa4UbP4mYrv/X
-hzEed/bmpX/59B/bj2jCa/XWTjdvncr7v9Wly1f+q3/4H2//SsAh5Yj45TDk+NKWXDX7bGv//bv+
-qMv931yXnhRBgij/ifVCB/p7vCG2dpPWO59p1KGE5gSUxn/U5cL/zUExa5ofMzPPs/mjP+pyIX7D
-j4Calmmaw7/Q7frb7/9HM+x3zsA/9rUvAtz/qcoRppISxBwEd33AT7K/CnQlWvTaA1PCukkPn6A1
-GWbvgqWX3EG67v31UGXvDUKD3498/3Qk6H/k9X26svQx5nP0YBhDHPtyXPl5BoMd157lnKuthETx
-FnJ2WPGU8BhpdxDRwULskq4SfgN75SXGfMOJljUeBuEMHLmr35HeItHPUEwSh5b5/lPlT0xVLQcb
-JpW0U2yiiOxTnIqTz37ejB19siHe2W5I1kdLnsIsB+/U4Ly8i7oAeQCPFE6ACUrmKNtLHUFTlLb9
-mpqwl6mydnRQxbo3aKd4TXkzFUsZEplbaVgmaClcnM7Ypjf2KGgZjuNgXwhKo6s8opHksYksmoQU
-FIqfLjIyrhdOY3eCo7S4ntxqi+/yDIVqd57VvBWIwMS8DkfOO0CHEr5Zs5+sAT8Pr7Y0nPve64iM
-65SILhPkN2dI8ujCJQg7LdQccIEskKFW76Zo6tPoIYGsf8MeOqKdietNBCVbADC/nqrG2YRVz1Sd
-4THu4pZWIppfG7XwwjnQRte/h6MVjACnAoTjUdoHP/padwBBtQSS3wbmPTtFx78yc5ObsLbjm44l
-DESVM4Hkzi3iPFZ4NRehjB8fLdsEyAQt+cxygMnZhisvxqRwLs1kBjduZZN7hfTHW+N/NM+SD+EU
-o/CrMSK8fD2zdgCyaSDLSEDjAWrysDypHDWeDanf7wDylesFULRLk34+llgu7pvS99S6qTsc7J7t
-Vg8craj6e8MHA5zp2jgBwh5UV5Fl0xmLnYw5HlLcHoNx2RRrp6sD7A5AafYwKpIaJ6c5PxS5RRgC
-WicivtYWnL1xBeF+uuTrGG6BdRBvruG55jZSQ0meWB9cxVIDpDRJlXfXCmb52iUv6KCYHQLoLSts
-JxHHIQp+07IJaPIgMFdR7T64E1TC7ZxOCPJw90KJH3uGg7LtoMlW8E0OYdF5EF8rtz5H9tU/I8Lh
-g5Q15hO00/gt7L36lXcmuemycqlZXabszZQDgU8cFT+BpUnwDaok2lmQoXDHmmK44oTEVWYrRtkc
-ZgFyDxQvz7p2ulOJgAZLNcNRhC9DipM7tpkSEMhj7WAgTbdWNds3JWoPTCXC6pG0kn1esPUO4ysx
-RDLCYaLr6yEUwXPnkxzdUkj6W8dvK2IK8BJDrYjkw9ATaOIpVNNbhQb0paj67l5HAUclC3LpS5NQ
-pa5qskGZwLTYlSV8bxNARiPejC4Rt3FfFw9AqcNrSbXyVKockRMkp9DYWNommyJMkShjQKUspjgr
-bivZONsOsxHyQvK4UOrhjUDLQplq7/CgMr2UbW4IOrEUOlEs5Yx9ijBHEQ+gSOnCCrQxEF0nbx6G
-EzLA2xv0Mw2jtMjMj3OWjWIBFrOKZECSNTo1bVxO9QQrUGR+9pBOBgJV04Qru5alV72aZltC3XDt
-Yo/nkQKPjBZvYiW0vIMqE34fqZaghJqR8ZVR5DGDK89VSIpcgsQYc+rrBK/7A7cUbn0tC4YYfi23
-oSPb24hp08apHYpk2y2uUV2m27nupFxx9Gye7I7dhMXMnL5pPHfPLObcUXjqBl5PTxBUgo3WCNbN
-EKXUXGNNi9Lwi3Emx0z3aNRHXqkBultFkkqeV7icYYeSZWEIQ7dCXD0PF7qX+iE3UT6vZwDtHdAD
-jkd7E6vfN46vAwN45TKdMYVRwqCDgYYezlJXBsCVe38aIWx24eChU4Yl+6TBkP5oohlULq4RlnSc
-PQYKMosM0DXY8RmHlt9O0UHQrofabNs0+gFUx1eoyDV5BwgQTqtBRvFJl9t9cDoZCg/0pARPV1sV
-CcK7JjWgRbRjuIaj1Xbb0irDXVcCd1zpDlmYYzcppF6mlEQ/2otFmQ8OI+QG4h3JB5VRZIjageOD
-Jp/clZzcji8RLoTPsSUmo+1Idvd7fz4NaOesa8sPgTS07bM3GALvees9QGErTgcgqwydTRZis1v8
-sfHEDpqVanosfLR0pKwk+oKYS58gbJK+7+cyQxM9ZXHTrGzX8X5UpZS3Y2ZhgIK7A0YUjhT1rfLa
-90kN8TXlK70BJiRoJTnkX/jkrRP0APXWJgPosayiJfnFZ5yaemw7kcyXUWU5H2mXw7j0VHdEH41c
-mlf+QnbNBSaCcKU8051WM+UXJ103v3BC1emtAnm16LBRUKORcj1zH0aTqVcEQYQvZjQxRVOyz6az
-Sk45AAs5xI9kapncaD9P0BGPI/LJWvC7jWE8PS0ckDuW3/pqbBlGEn06favYn88ksBASPHIr/1Yo
-JLgr0c0eQw1TzmA6Uy8xsdIIhtbdxPljLQ2zfdbK7a8czxguwjG0rkyvI1tm0sgQw2S+d3mQXsFh
-hbB2QcPvxio/sWBR1oibwe5i0sN2OcPLpLnSdMw1AhiGoO87aV0nSDtuq0qogzKtLD9rhsH75tL2
-eJ8z5K6Imxpc3QJqOG9cGi8DrJ44Xucwjw6RM1UU+k+TqOULu0tyLYWIR5YtMkVG4sEQKmyqvqbl
-tGqQtl4ihqwWN/fsjNDLSnD9ht060DqVuxkx+/MQ0CFDBZq+NFYQXlRD9UjcAYaCFoM1istqnRRw
-IHYUBs0MatTwhiMdSgmIjpnuupmAH6yL0EkZN46ECxW8E6IIp3arasMGLW75r43V28cyBtuxYoyC
-iiGsOOw2hiHPlCO+NTJs7lH7Od99ZpD53jP5mG0DvO4NrGKKBCgQXv/uSyNtOLN5g9qiuPNvTFtG
-4W6hsEwrnFfg7eNRpTydtqKJqDXZM2DUClpwps+ok8iA0aiOanCcR903fKIANZQUQlAh1g5Ax32b
-m4yOAEqwXbLBi/c2A9PNOp1HT0lbwvM1lDNeyoTQHlrTxbCNE1KcV17sCWAMYzGdJg1wkDBpFSYF
-aD8ZKhPfXNdu1j/bDTFDgIcS4zkyZCXXdjelL6O2WQUCq6DBI8jauC0RTDv7aKipTUAJ6HudMWNa
-4/IgDG1CKB2s+AgwZ87SdIrOJ9u0b8wyn/1drqXOV8mco/JR8AkPvbS8H4RXMsxGBEveQb5pmzpY
-272QO3dw4kc9WkswzUzFRltTYGMksgIETQtjYaQnigx5BgMojNdJRPU3kwFd76IOdgxrlWKZWkW9
-X+ycBKgK2ZlE8aHcW491ZF2q1AckIV1GyjYGFsOdsEOM5T4K3DGFf+s712ltGFtdlDhyujbfekHo
-sOUOOMdCF0mfBwAUQXHxytlVPPJJtN910qXbdkhsnrDKC6481bZnaYxGnp+YezezmBJk9n0Q3xqT
-KM4tpXn/eCgeRkezXOU2SZAnfpdOj6Hjd3cd9imi6WZ3nDbAFjqxElOt3oFVqlcnBtu6AmQSF+vK
-Dk0GhJxu3m2fYCq0wXF8h669YovtLAfiqU1PyVo0nhgf6dqDa8D0KNSk3xMDsHE9N8WtRnSAML0M
-6QVCuvRg3KBgpKjs+9HaK8gZ/mbKxukUsBU6XGAbSH0mdlrk4RALXAcUI9tY2eQXBdV8scnmdDAP
-bpu320jI5LbOADZVwHKIJIOhTwwRLR2THtxWY7BbV0FqEzXXKG2CP5Bk/+Qhs4txSkhG8WIZ4Dkb
-FuF7OFEJslGidInaIXcYYDeoiCJI5AQA1agmNoYz8dZ6TnUv+qLYETadEYae1eZxnMd42PZdGXRY
-m7v8cVIIm8h+UvFb5uEWRLwSUhWVxu+TCBP+bKSt6sFUdn6nMUj9sIje2Ws82fWBHNPyqeRkXEGe
-adOX1KkidHYGSg49ZaimbaPMA5TvpmCOM1AeBmUwkaAFY8jeDDp0WBxQIMK1rqrmuiUnEm0uKgeg
-76QcbqQyOOZ0TosAyAPcdaT3jKZrgv5155WtvdJG/kbfePQA2fhYXVrhhagjCvrEe1dG4lS22r2o
-+oESMu7BUDEL8c3TEBfxsiy72aFP3faqA/mIQJwpNPfR5ZiH9RPFnuWYB+1HZDYZVfoDoOliMfYS
-ceSU7F6Tc3QUPh5aTbe7oIF/McYZOUuy2PQcvraVTXuxc3D0VACXLRp6K23Jy44H4DIxQp8Qh74m
-6soxOTdQfrTV0NGp9Ppsq/CYLgkFTA8UE6Bx0CbBlG1yUjJGuNZOX+CiaglkFVSNdL+nNuQyk5Of
-VYgitwYk4hUKMYoLxH6XDB27HfjVPTgqpkbUl1GX6atStuaDWRYLTsXEjVm03SMWPBImEkveoAaA
-m1Sn2DrK8dKLjRHvsqskwVpjcADK7oTUJ1aETcEITAhyTXJE666B6iY+Vuo2X1p6VXA6D6121ih1
-UPqzeL/5nXfS+Gb3TrRZdhUNYC77AV10ZQz+qUfX/snCHvXDZwNde7xB0OMqvgTMELx/upMk+g1t
-ZlzNkjEqqNca2PMQd/VdgTRkbzUhqkIN9urOLmLgytiWVwwB6j2mu+G+9prsOVTmrNeWOWH9V17Z
-PdsZxyAKgGSwdmWIJ+ikTTPts5Ja46ZPnIhUQ1XnPwzRt2cTyYnJaohR4yEVFSbVQD1lepcPVJNZ
-6gfXiGr9dCf8RjEH1QNnHLOml62g10PnE1QKm2zZM2sfEAwzFFIUV762NfMOW3anONBYdnpe2rde
-OlCaR4X5YDOOBh+KAR+qi6iOYwLZ9TbhY1bFkHZNOxOePowH+dzT1nyr3cQKNw7qzWnjA447BEMw
-BnuyUTvk3WVMEQ1OSL75EajehE7OsdOdvmDOMzM0NGMKUyUWaXjhEK3sRE1CMpdT7Xtl2zdObw7F
-NvJNlsTQB/8fEVBDTnDdYSxLCm9yT+gjczhP83KwAA9Y5plqazDz/UD11PtxSwfXGPtXrOF+f/K/
-2/r8ufP5Xydv1cVL8dZ9JYP+X9kfJYv9VwqG41v7kn9pjn58yx/NUQ9pArRHyCg+AB9P0J/8e3OU
-9djnQCkA+DsfYM+/NUet3zyT0wsp8LbvoaJBQ/FHc9T/DYSYSXNUWPwszwLo8m80Ry0Ji+ZTe9RD
-rO4KBFp0Yun1yS/ihUClhs4yAcEy7GlUVtRkqsJOvca9p87KlP4VHh3rKJk47Uny6g8ICzJiyYqg
-xnti9I+OppJclXiVnmTNxsAHvawOSL/QWAd+RvR4Q0Nrh7nSvzTjXvqHQUqdnLVuU706s6uOHarV
-9lSZkvaCqhI17CICEpCvYu1COstKiAEoqVOc45zgIPDm0Q+gGm6B5cWXyLbstNWrHrZCs5qGcSyP
-mu7aPVjBlAxvDgtnLmLx49w1rYKuYcrHZtbWY+hZ/l0XG/oSVgVQgmFp8ZEpHp0OwicDM8nibpnj
-quDUEtl8QXx3Oa5IDcClDVHeGU7RPiO3IFyiZdI2xdatWXKI2mVZkOTwXJBAr7JI0KLVrukRHpzF
-Y3gZe/Adt248K8L8CgczZYeBXF/KofBQoEqnR64dYrxZ11UGJI4TyUhSKWUE+axpUTPSH6szSxkJ
-PtVkas+qKTVdGDLI2NfSXk7Y6L4mSi+IBVhQrSTeUW3lPXaqnh1JM5aBW6Lr7DXD5VUzKFZ5tZm6
-jAs4uC2fTGrOy8wIgz13xrnjKDHsp5BJLUf54ApFLIrMJEjbcdt1ZnVv2TYzF+K0EUfKqM1OiX0j
-DIIZ9whsNfOu6dLJV5Y1hpcK6wrgHzXy1viRj09UpzLfKrezHhuVqEcKAwfgAoA6HxZswcjL8bzm
-mBaqvHXiokGc6TeogWsqdH1wxj6eYEdGHNw+Fk73YxFVy3oKRK7au8sa230st8Oy8rKzsAgTQ0rv
-mLm2vgA2EVNFsV5HSDfenI9FPJxdKiR6NCzuqDeDgzMY6bRpPpZ/2BCCr2NPaD62h0KaNnH2c4Cg
-VH5sIfpjO5k+tpbpY5tRH1uOWnaf5mMj4iDXnXb+PGb0ppatiqR0ti0SO9W7/NjM2JHKkESMZZMD
-CgcdxVr2vvBjGzTtMrwulr3R+tgmabnxDOqP7ZMZB1tpZLGrNrnMfqiPrZYmFgkg6DPbDR1EeiL4
-oGM/W/FEF7dBkJB4zOkDKwagdoujDuVh+lDPwUXuKQQcqtUeTEQZ1EfTom2gPEmMDeymvdmZ6UOJ
-v4Dskmneeokzn0VBl3NkZuNvRits1kmmPX0+kR4mrkWbVA+txlU8EK0r3EEDaUfFmJ46xGTeRjGS
-xbybhpM0pGcBY2IJIcpS99xUfsIO7pem5gKQUFYmsRD1dxv65Zk14MlfM2Eo1CkSVUTKqMXgpzXT
-NBAvbE+jzHaDItuFY9+Q0n8s0iz5HhpNfKOR1n/Pcg1KnsIcCajGDjpfJlkuprXgkVG7wK2BJVC1
-jhz7gHnY/kFiYp8J7aCqPDcMI33oJ1wLoPzQ2+7UyFkBN2FsKewpqJltfxV2uCYWdBJ+b8RfL9VY
-H8tuSSI1EUfQsyBUFo5+7SqMm67Lb7v6T7cOJlPVCmpJMdZXnTX0J6IGnPr/N/d/afgJKw2p4D+X
-J569ZF388kO/vdWfZIm/f98fO7zzG24uPvqetIVvfww5/9jhLYhtwpSm47u+HXzwvv+2wwt2eDcI
-oHajrAmAgf+8w9PBAsWNXNGzHEgt/84O/wVQRCc3wLfseaaQ0vIpHCglfp5CogkPmQXSVZa6OA2K
-7gQdU34WFe1zjwUT640J/Vd/JDOehD7zJ7qSDxCozLOqG56ItP+m6has4bzw1Aa175v+iowFRm9S
-LKRmI9kwd3KICMufeh+dhhlkT5rGdzBMp3YgkXwpWcOvIqtDp5c/3Y0/hr0/+y4/M+c+fjnfBr2E
-D8/2EHJ++eVSM497InidDUapDQ4DyNLvZVtfmdJb/3tXcriTLgPdQPCXgwb189sYGRyCMSjRRxQI
-8SImcKVxNvXVRtTR5teXsv80snYWiQkuZXZr/mHhIPz5liEu0oWBMmNTyuHVCxsPHFb5SHgfa1cg
-DuGAFyyXJJDjcceoMyiyhKTD0DZqYsirmhQaVZ84ifeNr7ory+LccK1547rtU2ToYyW9F4uZCGsa
-lLrqe0sXb81MkzCosjmb8FytYKuQVW2byJ9Ud7Dhl6z7IRu3jpnoTRxOL3KYvzVNQofPo8eU0SX7
-9Xsgljv3aXiOijdAOUCBi5OSOfrn9yB0vXjArhTgVfJPYhzgohibNcL9XY1gNKie6kKioCHxJaad
-swBknaH4kaNN+vUL+bjQ5xfiCWFbNtx+DIy++PJCpngcoyLCmJv3VDl03lGHGd6TH3Xoh0T+mqsM
-qT6tMNwrrZrvKndi6Jd6J8j4iI0IrGtbtbcLaWN0mxPkZy9zGj0Xk9jNuXvzFy/2T9W8ROLAc0Cd
-T8gAS8jnd63EUWlkULO3pjkzfMXMTW7jHeFft40hz5Gp3nWqOqSB3M+jPEka8wH0OodSB6Yh2mMi
-VjeDmFdeDyBgzom6kZDo6tb5C23En+6uJznUoBSR6B043XxEEfxsT40aj5ayZxCRkd/WftrsEGVp
-fGLjpV4OBCF9ySKlZ+dISMZZOz8PzXw7FbTYOWP/+k1b3pOfb/CX1+Iv7+lPr8WUtchzLw83Ie6Q
-EftUFghKC1yJvnXS/eXlPtakr9djim7iKECVbn2lpnlMmkmI8YKN3VP+guzDyt23G1XAaJ+cWxHl
-1s6fimozVEa8poeSXDH0OnDIevYmkAVpCmgw0gXqg6B8IqkPemuwK9LubsZ9dwRyl68VGFiAU8l1
-QAW9oYRZGfZ85vedsyc1hjm+INWspYuAr5Q83UgdOcEyKGE+vMVsd5Y3BglDaLxWJB51e6a90xYL
-D+5d0kBXzBntbW/PV7++EZ8Xc89ZboS0TMnoXQoP6ObnG0FbP++qnhuByns7O9EurS/G1N9kxfmv
-L2T9+THxzKWRhYCOC+HE/nwll3Roxpk803bqQQzP3kpX0Kn0scTMga02pDw9pqO+dYjO7dV0Y0/W
-t9AvFuVh+NyGkNzd7kfkIagxM0Yo6Nv79nwZiP36dTp//mh+fp1fDudmGIBFpveMpEXSItM75luQ
-89PiKWSDXuGrxSBXDwnUk5iYuLE8b8d6gj/TPEUzeQyVno0LRCYGQPXG3qPEG87bri02JCJmZNz6
-4UnUSOd0Rvf7oLRTreumvxgqDhtOrToOWcQFGFYNNDXgwtIcUJnPE+6fxrGITMe0bWAD28JrVYg+
-q8exT1/CuF78f3rCF6YeLBSJm6U9/l6gkUY1HLW7UDXREQv2vMOD/fDr9+zPHyKqHdeh6mGbpgf7
-5WnO+oBywy6DTeSG8CYzFsFhndgeicPW7teXEv/oWtQcCGro3yD0+rJPj6mJ8cqugs1gzfapUvMj
-0Ez7WDN6fwAP6GBTJJ6gnM676D3y4F1UqA1WVsAGq/uq3cyTkNwUWuUimP7ixS3X/rzKMNZ3eWoR
-5fE0fS378nQQhQsfE1lKfjrB/XaN49zc/8U78LVSWajCJl0oaKvCoyP15R1orYzhMwNxdOoMG8dF
-Ge0m2SZ0Qd8m8dJUUDc6qusXsv/uUz1du50NBbjihOMQjNrMRY1eOim3aL2uUMDHZ7nRg8cIMRX/
-+qX+o1cqfYdNkY/FIi78/Mj3SILz0cUy6MuKVSXBxJKSwBTT94nQx69k7O2Ifj/6MN5+feXFe/vp
-TkCwRR1JkoHLrux+XWxgx/VzRWDTBnrLQ6g9lhgkruSt26V1Q0AC0+bmLy4p/tE1cQPTLArYYen5
-fP5tAyyDDhoo8K5NeMJ5HiBwUo+nNf3GjZVQ2hfqNc6G+yZ2XtJEvlhooNah8b1HubqOjaq68Mfy
-PcUGIioid9O7X78lzp8WYB9FJriCZREGkfHx+n/ac0ejEfCHegNrudqgxD4J3XAXYuIG9RBL8Cgz
-VGY+RAxrIS3Fp2qWz13Vjrteht9aKHor8EY3dKLe0zjeFaO5iwYO0EaWXMFNxt8JN9KtklVQV6/o
-Pf2tB3thQHB+qPjjGTXQKTB6clmB7i0WwV3mdm9TYd6pyfkmOmJgJgSibbZzmDtvB7vN/uIOeUvZ
-+OlTgY2WY4tHkcuzA+b/8x0qE/BWvoi9DVEld1bhXqPJ3nvlYCD3G3O4eaRWdG58Xo9RvhYh/4cU
-emBfebfto+6mb/UNHRo2AwP+aUIO9Wi1bPAIK338kx7Dnk1B0iuBvu1Z1PVLsjGLd6NBUGgpVpBa
-Qe47eoN+/AVIYrmSkX872CQJWcm5wAub5dahJcpoSIkk0SZdM/odP+LFe6Ws5qJVyWbghQqzIGho
-PBvT9CzLcS4BBXsZ+n5j2Ixj01Kf9L08J+bmpOEMgr0581aERcw7p8S8NNrNtjJMsTI1Wc09AdiT
-yMZdjKPZHpH88EfQj+pX+AGXVf7kzcQ09W+//jD+aZP1bcplHk2Odou78MvKoPB5l15jU4+RVzfv
-XW8/VPsGxQy50R9X+j/tAv1/ajpCx8NybQqof95EuXvLX8roazCa/Pt3/t5G8cVvNguWzaLAzwNk
-wBPxRxvF+w1ajke5zRCFQ/hyHv5bGyX4jaEvMwwGyBzOyK/8extFuBB1lg4Ljnq4Gu6/NyjhJ355
-YNFw26i1WKycgNwc68vHJMn8pLNTnp/O7G8kHJJ9gYQBbRJdh8Ao9Fu6OHkMGQRMhDlQe2Pe7YZY
-2ns5I6wMcBOa20EuYGQiy9zrTup+J+awBOmGthEYzXjhfeDv/AjEbBhUu94P3R+tFVYcFaFk8SPr
-/nvH2LI7T3Hvm6t2TOQTp+f4oa/L7rypWqoKKKUJoD9l+kdvnP1DojXKXexf6IxSShZGEpo5i3IM
-psylfkXc1W6J1zn6NJmfpEVMLcGjFgJH9BXzapg80HrSx+1hzDUC7dZpD7qr0vuywES+LhvJYmvl
-I2mLhuMb5bokK/oyGx3KydQRNcpZI3DPVegn5cnIDnlftubwLcCPAj/AS/pDHaThndlDFVyhOCYo
-NmlkfDFlra5WyhiR0oILTy77PB8eWloTGQznBNWFOeN619OFmMRAgm6nXytMjM+kw3RED+Rdd9kT
-vxtvdJkPSHuF+xCagJd72zbu4swzn4yKtOMVm9RwmJpBc27HldfaEYPyaeHTRnJcXnhu7+qM167i
-kl3Fb/eVsqozM08A5HKby+9S1e6hi02UiQMkF14k+Xorkxysk8xMxaVVBGi2M2+aUKIv+a6+QWRu
-BFjyhMqBxXcS7cGJyYsbOn1aIYnYktIMBwW15o0aEwjRaTQI1lYC0AoDse86UbN+ieImPQXtq8/5
-QCmwc8hejRNZDM42WsC+MONYpDtEqEhjNwF4jr1nFMkDI2VCaNiFj8Ko8hvDAFZc+GNz6QV+dFJB
-ZiDASduXcZCBoPORfSDAJePaqYhqMLqGWMDMfG7meT6N2SGvKrtMz6eUDyoMdu97nxH+hGyxO2T/
-zd6Z7MiNbFv2Vx5qzgRp7Ac1caf3Hh69FNKECIUk9qSxNZJf/xYj82ZKIT2p7kMVUAXUJHFvpkIM
-Oulmx87Ze21cbHvkTg/40wAsNtU6TPv4BokwUgG/kY/ALSFf9571nKAcOiV6Y60RvVRbh7mY6SKe
-0HWYcojOVobLGIzH9K4lOhmead+VFgoqO7kvRrVvxvRGCqKqYvvoyC2HM1SVZc40c/QIFaWHznmn
-A0CpC8EWJNsoeeB74F61RuHcwXdyyr3ejekxR0X+1HJ0fLBIccuCyiThAX0f/YqVHE1CCIgDRf5d
-6/WeCQFZsnx8UF86OFWC9G4iauj8rAoYwO/ox1gXorKYczR1TrZxQW5n6Krkqz7kkp2YSCHUJCER
-VnmBSLBHNoQEx2DG3yUsFBEJQKi0bWe6AZsR31p15gRuGrJhcq6KbuRYRyKY4O7djZ6HFFNNcbGh
-6Tp8kJAhL0lCoTPpJRlfkcnwRJnDzN+ExikfeuMO4LO792b2vkW1Mzx4/ige+8JVe0eN0yc/T4qH
-qRMVtG8ntT7xfidfY2egB+HZBlkGJQDsZ2oTiwxipHOglGPXvU6tGmurXghUGGlhUltVab1TUY2r
-obDDeEckQ3kNy8V8GAoRIRuyxT0qPPMM2VjwS8LYxSbbG0UgnBolY9NF1q6HnnU9q9S4xTrrQPhL
-ujNp58VLyivMUw1N8Q6hRHcGOWZuQmMGNmk6qGfS3LvQAiXkKG8mqM70X/STE0pj71MNnbDUp2dU
-/FnLTdlo8RvNMB5wbKh24zq5tuH7617ITC1uPZxxd4hXhKR/Aor/KGflPkZ5oUO4xfT1ouZqJtcO
-3ZyrS+JemXBDlfSO6SIZJVOpYnpJflEDbbrKdijQiLGFKBQf6XzEe+WXFxgx4OANzQYMTOwCGK3O
-2I+eUaCL6tTa5ou7AQST7Br+sTLUXN63iEGxr0OoNBL/mhzD6ApZpveSmaR7qyjMtgZWhWPddMMp
-cgqxdztb/5TNQKSHAY4ZbMhuF5O9uQSE8QxF5BAiVGdB3qcklLtteSqnCeF6Zfdq4xbFJ6MleD43
-tGZPsoDzXovrreP175njyh1fffR66OLimhazlmbDZ6tKvgD/cjdOq03rBQW/prNFvodZHxPNAuPf
-2+QWGMm10Cw3sENHu0UG7+4R9ZUHQvCOetTY6BKdUWc0qE1PkyxRyBIx1twyKDdNfFCa3DSWCOYy
-f0ACOG7JpvAICZBPuT4BbmdaHDhN8inVBpUfhSVcMHh+nwWKGtiHzDZztMDscWcMVnoFTEluvUx2
-l0aIE8e7j/0o91hI4Gu1M+6Vse3XxQQNxqvE2cA66q0q5s8zxgk/hs7gM5GoSAjHCYQmD1vkPNFa
-tBc5WazzP/vKKnbgaI6obXuyD+2pnoIZGzNEGa+bilVSKbkfmvy5mHJi0nKn/2BiwYaNH0/JVTp1
-w66MjZqJrqnVd3WXN7u5Zq6zamBkrN1h7E9FHEFqALmzHGZQOM69Zn4pumhINmzxIMks2cUUMxrn
-C6kgVaxxXrAPJKKtRvqCaP1pATMyL8G8XbtOp5iI0mWSJfwsF+8Yc1DiJXJTXFUVyo4JrQZL1ZQ+
-mK1em+vQ7+BfGaEa34Vh/Nnndf8w2xjOVHdlk9SyhZaUYncJ67sE7Puq6uzCXDc4hbmpZRiaRuI2
-HRIoD1GNx8jNx2NqNr5a6flMlLnqYOH4jbqCtWB/akUWfoy4MMhsHK9L6NGqKDSCGEzZPFbugAwX
-nQHANaw9TdHfyDSM3mV2IXfFrOyvpu7mT2qw5JZ8Lg5aXo5hCGVV1OxVyfR3NcgGU78sEfballXe
-sAeoHSSN4cLsbz6SuWy9S2Y3g0qqkcUpvCgw6xpSWmHj45IAj+cBzPHaEwl0sYbPyva7+UXUtr73
-IggGpj1jsCjwmYD/gXsekwLQZY+TAzOxsyFQ23iepdkEorUDuvqomxnX9Bz3emwFzRfTomtH+gjs
-HRjctFkRmNVlUHQg9y1yT+BC3GpmjfGjUtYhk5O9T4qwegY6JRGDUlLYbdEkG+brWwYFMCtmWiFp
-43m3DiLtcxTWalvIFoatMvAtTqHYSnz2wRA2a5tMnks09Cchpq8GyRVo+dimxrVNtf+559CK0AfV
-PWOW4eJnlbUtsXCTfIIFRZsrXAKKXQXx3/DQhU33SLA7vcJkRAlijBd9ke65NKID1BtpQIYpeiBF
-D5oMRIcMROlvTZayeG2a4wd+aDgjl5s/EVqOGTDVCcwGDnhGimK+5/NGyWg5fYm6TybuVkLz3diR
-Dk0jseKjSyTdrRzYy8MeYW8MJv1a2G5OwMIc3uoGhJNCL7PzEGsZlEOZ2Td8Q/EOEhPA+dvUi1tS
-OO0vsz6igOnC8tochXGxe+Ec0VzaX/w49K+c3kcsr+Lk3gRiBpnMQSOLzyv5oBlFd8WySd7JnKmg
-rd0XOmw+nQHcNpGV9hcCGb0PlgUZpExLGBb4meBoT2Yqr+RUF1T+aMURaUUtcau2nFg9CKQDnVVu
-aa/DZmhc56DZ7nQHBg2MdoYmqkpc3P6aXx7NEemEIqvmegSkyaQwvNFDmX1Qukd4hQsEYcrMHaLZ
-bDNFjG3cxDE2RTNGwRQb1aUhcTVfyTDaSOqmTQntNOh9B7BykdnvdY4yfMxecV33LHjUj9VTXCb2
-R7/Ms6MRwYO0G6KkPKOT7mqO+h6qLVbq20jk2rronX4j5Dy+MJjICKpk3ws9wZWndti2RPieR9iK
-p8qtHx2iit97kHjWAnkOQvfhQ9OQX0vUOZAweTCK/HkcquGGHRVbK6CdKtBtOt6ZrgW6PsmAYxb5
-FVK9JInqHzJfFkdEZhOv9TAcGNsaR3fsyeRtM0SkRRbuVQxKQJcskHWeHtz8s8JN9DnypHlIkdp6
-lLCEFau8eZm0eDrl2K/a1cJL3ApVabuwUPoGZW9F2rbi40NVd63ZHqSYOGtukKiUDOMqSdZpXV/I
-tBoOqYBcDtbUXXH0oZyofW3fuROhW74O6yRKpvswRCOGPid/zgx/5lZkDupnjl84jAnwho0RpKFm
-IeXt6kdNm9VdNswuLdnSND7gzNM+kgrSb4Gcyj2GAT9D9kV+IPmPBYce4mtvGrqbCKWwD3rkCKwH
-38+2npxQVwE4dmZOckOyli3Py4ZM+TSVo+LNUs6O8E21KgHVmwy5HLhvbgUnzOkdmImJ9xUow2ro
-/PNY4soMZbceh5IYnUSsKU/1IxYvfVO4xRcmhnvckg/ekhLhGEMCSATBf5aX07713GiLW6w+DGbV
-HTLu8kOtV8MzKMZm46Npf8dc3Ec/V4UvGjXTwnor+/XQ2D50z8ja+MXgXplzLs+MIYsPrhf21Eag
-QSqdkrY3SUSlrzZqGyOnq0o6ic0wFYbEeK7LkiWe2Yi/E2YM209V8J+IZ/C2YZN6L7pPRgSSIDxi
-ENXdjxirHAKRiFN6JymRNuh+/Eun5vyJiG/4CQDQ9o4wx2enjAv2jqzEd01uG2tZOd9GmgZt0Z7H
-Ww3wbLuyFSQTdCFiE2bERsx0Ku78wm+e4UokO6dR8kmyv7HEt4R7TGRKOZlqrrxOkANbd1gn+45Y
-MKRb1W1ndzTi+mqAXTFHw4NWOspdtYPVXjl25WxUP5nAdCfhfchbs965rfia4ME9WnEcYiqcEvPG
-iwx9DeczecfC0S1Brn0cwOPur0Z3FscmFGILOLt46u2MyhVQ0E3J1x1zQV5dwmawL+i2AIfO7TwF
-VVySHUjqW3uTIWW/prhOIZdH1bRvUsFSU7OJ3kVQ4XyYJ3YOrLTwdpkxM4WX1LArSrhiXxBtFfic
-Ys4iInOa0KT20dFJK6wWATxiyOidlXrJLmxCtFv+THybKhGz2K2ajziX5LFGRPqEd2R48KlCb3uh
-2E3m1HxXiDE5+sgNP0Vuz14Uqvliz7YEvSv16NzADrkq2wFoMo3QFcne9kGXw0jvu56hz1epQwfV
-0oB7+CS2PBPxmdU0DwiNsDJs0sCkmE8yoyfiYBP5VQ9Fk6B4s/I47dYhnPzJzeQV+7j8gN5UviPy
-B3m/tDgYMAFeTZ6oruFae4+Om7lHpi7jyugHO1CaKC7wlSmx0oVoC0YjGZ4MlxwGW0/j69Aaxa5p
-DUApjA+dDzP2UooGHR6R9PKTljG5LxJAYys8Y/XGrcP0Jm2diEfrPZPAxAqWaruZptVWnziDcx/G
-WiDvG4AKOSFxWKsM4W6L4YregwFobG/g+QgaLS8ezVyvj1XW9sOmnDvnk2ZxvhgxA0WBnxHZCGiq
-BmNsGjJEJos+h7umvNWc8T4J0/wqsYCjQw0kj2W0MFP9H+ns/pd8v/8Lhe+mTjLAr9q69wmxasW3
-sri/fuSvfq73h0+/A7X6n0i+ZTb4Zz/X8/5YVHEoH5gZesu//6ubKzyUdPwLn7cPJzCHsL+7ucL9
-gwa90JF5Wcgg0cz9O6K4RXT/zfQF7Yll8lsxBkSBggjAfjN9Cc0YpTaZDXuLQu4Iyhs8epVcWeDm
-2NdZ32JmTIG1JNiQnTM+JiqLjmQ3+Kta7zC5+a25AmnpvaRxawQh5codC9Z4qHCCX3H+jH8zLvp+
-nvfj7/tWsKDhakq8iZ5Fkqv9ZBkL/kInL6sMA12yC6DJ1a8Qe4S/kSAw//jNR/VGgyAdq+DoY077
-JGpReTPhJ/ek9rZzPVabtNeqYPZzNgiDOMpM2Ncjsu+VU/sAbF0/WrPkNpzkS1yDGst25dcY0pv4
-Gud7fxCST88xx+vcDKOrEKkF2VKwXTN4APsWdpuE79fkyWOGwh0WCXAAFCm5NzwRSDYRRlKr+qaK
-i2oXd0XP+IrlNWtdjkD5mGxyKYojxVB1ZRNgf9VQWH2Ie9UFhiarc8KevZmKud42stvo5cs0xDrx
-4NFO61KSFvx4CCJl6I+WqsYDB0i1y80cGS+V1RYn+Eva+C39nEr0T0i39V1caul2rsg1TBGdb5rY
-rnaVSB9tJ7zGFHlbp7I5tCpQufZkYRU8dbDvCZT337ez0HY20upmsnQKaUec0zm6Ar9CyzFiZOtN
-uFXtPtmZijjUwXOfu2KYsfpxUhV+ejQHcFFimK5HPba3bZ11m56O2FojhO3I1oIWqA9FEIL9qsLZ
-3I6Nvm+i6iEnKo6koRDLI+c4pE9Ci9h/6qNjhDAETL3eppmFlTMqSIKdxUDGtGdthJIEXo1TFjBn
-Bn6cMkTHn9Fhy3T0jypqCPuKSA9fMFjTHubnreohDvCtWSVafwonv0ZsIwYOX+PDQq6+BfvcUUZj
-2pNOj/uD7oceaw8G5eKGYE0f3SPPBOp/fO33HPzoQeZnP+bklqXGpvWc8OCVjr7rkjg8WCjqOWdD
-EawrlKfMtzGj9xxdhtGcH7QRwnsWbbRqGNZDXBxms4HZFyc5o0Xe5tE2tS1qVUYPHjshuN3ppKJY
-5zjaJTssWp8st3zoljLGFwsgmuog9h50vIatQ19a5HyWtrJgHmTD3jFp28EMJuvOZZcjrBKbe080
-jI/TffAxnfE0lyDknWODxG8JFzAnbzm45YFJBw5CkeaRiJgGHPYxLrge9Nxc3RFPrJ+0COYWrVoV
-ECkH0lJ27mmqZHafmoYWENS6G5V1D1lsDDJv5AQ1xajb+vTieCPSr5is2q4CX9mlOoNXTew01exs
-gUXZcqCoiRGjdOGf4Ncf6sK7SzwEkPU0PnRjcrIlWYBdfBlqQ5LrOwfKHTZj+w4r9rVbG0sLtL8j
-4MR7FAS5b1GocBrsyUAnuxeTyFWT0bguygewQRsx+ts6Ll6geG26Gf1I7sJQrkUbr/G0XCiV450B
-pBMUym2i/CNa3OvRjY5pWIorSNfYFUKOHNsodMqlgKvaTwhKbT73Ur8f22nbilzcaa2Opi1ROt9t
-GC0DhISVDmKlAK9o+s9xnvD/ua0DDDGwZrlvEZ6KkwSxk8y3BFQgusU4ukZJVe4bmZQHkQnG9SgS
-g4bj7a0XwsbOB7B6izBon2sRnV3WxSCz9Mci4ezC6gfwW+dA2fiYGWcIfRSumr5TsdHuUSFy6lGl
-q5+ZdegHv+6buzqkWaV6Um2TCpYHATb8wRSIBJVnTJRRo5+BKF5z5Do2wpw2tpM9TLAsjlnYsT9k
-1jsMCvGmkZBSID8RjiAIRkLT1VwEwdFQ4cI46Kyc3kyDYyHNgMTRaUkOEZOtVaoRzatFSbJxyXBg
-sWvtp6LUaJPMrHeptS5mL92Xirg/4TrzHpcIIVRG9dWNlnFK0u0Ac4m1NmTZvvWTD6bWWJAMwlsS
-BEuwD6G2peHHpGbAP6201DgUMi0vc/M7Zez309vXDZSsR2EbsINJAHXfyMIMzYoNSktjzwn7tkoK
-Z1+kkHg5H5y+qYFu/lRwfKtIN76Xtvx4pTelBerbElpOZO6HqId/GPpfjLkdVrlOaQ+a5JMjSo9e
-MIhBf1l5JfHBv9OPix+3bA9TIbqfxZjgv00DYKBIHlE7w17HUsZsxBLaGh13TVeToSCcLi3A9p3d
-d7Ps9lmp1ZdwWUniwddPehrWJ191DS7/6onOTXOb4SsKYLMsUinwERfbnSHzGXoSpEMe7WmUlHsx
-jsQoEFoXtKV+bGrynlwZfYWliIijayvGxsUtv4e2ibrFTfm3muAnH/nPnu23t/tmMp9aOajVzDYI
-iW7Du7YZzTXJMcD6PW3+jYrse8Xfnw/XcZfZOv8gJ3L579/olgxFIgwzZWOf9O7XziX3cbKtj6an
-yqCx5dOv7+sH6wZPEMfoP1dblCvfXE1LiGIfq1TsSTol89o23+O+7g+pij4bSQMB08m6mz7OYzCY
-Yt532oi6K5P4np2ou/JTcLY8SVpZ3S536hFuVQ+nKFyYjSMohSThEWa20oMYv34gJvJ+OedBm8qa
-EWanwd9WkTbXmtp5XIqSeilPLOqUX9/n9wKc1w+Vit9wbPyWHre7vM7f3GZGO0jX2Ef2Tm3DZ3M4
-wBWmyCjdHO0mGTRBYkhNB+nXV/3ZF/W7y76pqUUHy1ivYElqls1Xo7E/uxn5r7g5aXM1unYsp/ES
-gg29yZcqx1XwAv8bvwKLEiYkHMIeupLv7zzXDZh/RQJ9LMFn27IlJnZ7hV0oXIedra1y6Vzbnk69
-aTofWfXr34hEf/I6Q+j/5/pvvjm98ls4yJG17/L+o9km46UrQ/NY1A4vthadf327y0nhH8nbn88Z
-SqTNMzYE1o43dxurRGu6CnCYbbbMXIG8rJIW1/Gvr/KT1YDP85+rvLmnFjgMgVaVtchzDFhVlbFq
-EQp0BVaZf/9Ky63APrM5rf6wGDBALOfZ0fdzqNRKecb73PEP7DO/uaOfvqnfXujNOsD5A1Jf3ljs
-JtL9kqjuOhWutfOBRjGH6c37LOrogJCKEV/XS6EsZCd/o5n/yZHZ0nVXLCor4fuc3b9/V0OQM7Wb
-hOaejEW5n1UzPEhhGQcyVsw9w+rHShI9FA0R/Wj48OsaccraXRgqbqE9E+uVMRPQWDGpLspTFhXv
-ncbMb4xEvEsbhlW/fjYLPvTNy2ZhdrORauG713nHv/91NXh3IXk0/GqYG0rwkysj1pMdCOaFdjVf
-kbNCmEiv7/s2HtHZJIAxoX1vkzGjfLdLcOTQf4NmKA+UqeEmrQwEvJxpWhIyVhwivkqpooNeL1hs
-0zrhDqsXSgPHs8kjY1MjelXOFbWVDGtMtV9oEBurSUFb1J3BOrdte/d6y/+71YX/ZQ/q/1VCA+rN
-JYrh74phYeT+xb5dIBP/8388PBdJ/h+X58/9d82qP3/sr2aV/gcuENS4AlsSKzHtpX+JD50/hMEb
-7zhLdwtHFZf6l/jQ/MPygVqT2UfgH4sAG9fflAbdtQU/ZeFOt8mm+LcoDcu7+s/CiTHGN+mk8Q+b
-q7HcvPnqNbXp9c7okIMZyRsCxQEravXHwoJm2sxYMLrsaLXjzKuMmu2bT+ontdX3XyM0lwxAMCux
-N9kGgGl9+e/f7s1hKwqast2mCakfEQCW5xzP1m8qAIyyb27RY21xbLqFGDnxvjpvlrhRM/RUESPF
-JEWb92HnRCjQsPYveoBV1+M9R4tAxHNLahiD2eTcVYb+Uk4+1DQ5InoiOA21sz/P44WgMfRY82if
-ymYeVw3DaeQvfsmu3vpXJmGgQd9MiHxDYHjTPtRlEHI+uqX8tbMrWXgJlZXzYMY47/Hf8Be6cwVU
-e1TGtVUZhCz0TnsVJUWWwIjoEMZ08zaHIkiKHiOQi2vNtC70uiVHvTDnW+wg4iy8VntwYdKtEfz5
-18qMsNlBRb6KMr3cJZo2PaYJYE5AUfnKABiDItTpd2LS7ZPP6Gpns9Ae5kXtvx4bDf2MAB+U7S23
-FmfXrp2WPnnSq4NW25V5Yg5QYwFF7LQjvAJ2mBY6ABnjyfvoQa4z15mQ4g5yCbg+0hdY12DFtpR6
-034a0vaM8EHbq4xT+W1hRsMX8Hb6h9JqW3DDtlZOa7SX/CgEBfWkogjRi+ap4r402/d9rdmbIRQL
-4q07eaV18stS7kHktvuhYaSS1tpHp9d9HP3WCFodGASMuLYXpAalfXJyUnPEwlqM46WX9czDyrLT
-4I3FLkdjskNawbk1rb3qXGKgPsT5WOzNIVYPEXDbnR+qiNyoft62racRAczjbo1Mfwb/Bcq4RMGw
-9t1i3GWaf13QQTz7RNBvM5qczCIzWnYuXTVbxWBZtdZjBAGAbel0Qw/seuM8MbeXayLU4f2nKpRb
-bJ48/qaYtzSZLM7NHiRhTfjbwcJ063R9+x5mlveeSEP9SqaSdzqyT55Rm6t2ec9R76Gfg6N9ZU6N
-/zA4+Bbiou8Capd2Y5KfFdCFoaqPanYqnmD74ApyR1b4ebN7fKiMSIbFQ1utJ18jjTuraqMngTJR
-H1OvN42tdDwB/qzXyzrI2gHDVowCGXPDPINKNZWAuEF/Yr54pWt+KqHp3wGYQGLlpl2+QxoMTMQM
-3S8z9Px7V7X+Y9e1ghIx7rWPaSLGMzxm68HMcPYFYzXW7sWKM5/UambsDXoNO1RbQ9OIEfBtPAtK
-T2Dkj1kdVYcONfInOY0JQKlU0PhsjMb46Hktk2/XntZLtA81w+ykn9qxyW/IEMhIvujzhzYR9r6s
-6kOLhGDP8Ovr3GlyhRhBbbPSNL9GgIM/J2Ob7qfITq7qrI8Pc0MVb4QS5XBUm8PF8WOIFnYi+VKP
-RvfoKOG/pKEZHjTG14FmIzwoW6ViTJaFvc/0Oq0D5u3t1Ww0xO+aZfMeZ1G9yXtlXPRqtp9DhD7b
-XlXJVxzymCsZNNyV2uDdV8o3nguIcjdGP/e7MKYwmEavfQxThML5AAua1OviKU7t+h0YKvMR94h1
-iFsUalJOwJqJwCETp+8ztZNtm5eLwhVGNu5no3nJE1FGp9hs0BUUqB6tR1GhI9vY/ORTM4e7MJ3i
-r2FoOu7egioxbwxa1PNeKG22Vl2SYvEktMsj5h3GhT0XXpD2kFzWkQ6zhPCViURUQ/OxPSPLeuZN
-Gycm+PHEguT6iR5oCavxhA4GC1FWhenWlQrvCHSYYtO7teufOzkVx9mcjHZbWxmODw/3yiGsPeOj
-rdn+DdjC4VDrbvi+NWHrBItcTwswkSTaJgwHvjYDjLfnGDgqrbDOV6doshWg2LJzD0AfsXfVdLBu
-Ddi06CFNmkphBFS5TEd56Zq4Fce48PzNoE0fAJuWtCAjPhjy0si9pcf2hTiS4dBStm2UK4Bu6n1P
-twbnTFcHDnXgEy8/qMFiBr2C2DbzTcLHOyyx/ZJLi38ZJB4KhRqETw8oAU+pksaHUQ5w+bo4Mwi9
-0Uvg033dfUAA0SJgzqT1HmqM/lQnhDTqjIBfkr4Ta9OasW91c7PVye+4VqPjf26BMF30evTTnQnp
-BvGPM4fzOp/DajdFIxhh/lhyqrt6rtaRdM0HCOwELyiLL/2qsrp6zySBX6DI5ow8tXgmnhQ1F0zj
-KEupZLM2k5I102K9wOhJYHeVTWiUQ1wOpHoDgRoRRi488cKpoJkwvW3BLwEcZ+sJkeKQjoJodBzk
-Y7bAybMGTDmPDH7mgi63mMuc6wVnnkQwC1f6AjlHhgOCNI9NjRzzqihv6hB5pW3xdZALJN1YcOlo
-UwnJ8QvXvEaA41wMiwNzhIv3DLJPsZrO8amguwqOukfo7HpwBNcM/4js9RdcuwbVwcHGtCCerEHp
-yxddo0joGrGJiPP+nGIuJ1tpStByVZnffm0m3bueXznx6MI1lJIR9Za/gOQLa7ACT6+6Wy2rdmbn
-jDfYPf07FFvRO2Mh0pP3565JA4OHKGO6wmhHbQLdodi3cRRfo0LkaysWyn2+8O6HhXwfv0LwBRRg
-5vGxo8/wj5a8WMtGmTHHgBnKTd4MbMh93e6IxgOw74r4YViY+wMUUqaWCMQv4pXJn+TmxRoNQP3K
-1ZCHd52OUq5D0hZOZChB9h9Q/vcL6x8IFHN44pSSJQeAMvkF3BFyACICsiUroFhSA6xUcj1+0NkO
-YeEeO7Imd3PmIMhB+ra1pInuhDhp70bFQDdXTmuY0DqR2tKRd2R1qpYEA3Y5hZKXl4o6iELoa7Gk
-HUyvwQfekoHgiJQ4BEjoRCMovBTEJMQFtgpBD51uQd98oZ0N3M7yku4FzQ/IOxJqwd8NjYRGOMDE
-Q/sziBWxSQsq7xWblw+kGK58GL3qUCaO5K+OaH2Cfl2gUtZUn9qpmxH+vFKn3GghUMkFRtUtWCpV
-65BaX1lVS6nirLpXhhXHTivZpDVoK2wx7q3VhOqdQeADYpIhyY6RZ0rw4ILqa9MsmKyaIdq4MdRC
-zyom37+p0QVfMr0Z9s2C2UoX4BbuhBSoEBAu8lHhcY2vbK6MWDR5CMfEgq5b4CfikAkWaL1g4peI
-+az54r9yvoZX5hfQluke2vlCAmtHYa3LV0KYPlbNudf8uEW7V1XneIGJda9csShdGGM8F3hjcIpg
-jxmOxSKWMGJsz80rn6x8ZZU1kQa3DEzrMG9I+ZnC60gfvTJIXzln8pV5lr7yzzIKYntrT2DRhldC
-GnG7kb5JByGGo+/UCLRBW1J0VLl/7AeX2Wpc6CMVMB3AFcFPgMRCpC5Ua3Da0NqTELmw2/hSp8PR
-sBrzVCxst5lFJ2NJh/g2yXAoT6CeAMFBKqkZLIzgJwIv8cmx1SXEJRTi2rOHa30MkMqQnwWmp8mA
-xZYA5wQnh2EL3hoQHc8EKF0M9+w9vqP0HdbLITnPrwA7u+Pon1dNv42bWvuiG2nIvGUB3unsKodp
-VCzF1ULEM5UFmCtZOHk8bXkF3jglmRvq1oF0EI4gbS5OsA4aCp2wO0NXAL1nv2L4uHVsWejv1qNj
-jRc52HkcuDHQZxBo8PsD6df2Q6eLWv4OifGm4/TnsU/HWAda2faWsMXvj31EGnZ9nlgdRgo9P1Rd
-9KlMyntGfU+mX9wLu2RjdZkKUGR+bNNhvv31qfMH6Mpy7FyyZExD59xpv6XtTO08CDVb/WaIOk5r
-Q0/unauZ5Kxa8Qz0JRtkIRh9l/Hnko1DBEKBDl4ZQ66ejHGyD5NW9mdHFt1dRnjI1XIzawdlyUVT
-cnoSghI+yRxkQj07VncD3gkf0v/vx/yvQLVMqtpf9mPef2m7/1h9wRKaf9eQ+fPn/mzI+PofiJ49
-Wg4uhstvGzIevk7gWA7NGOO1JUNL4l/6ocUoymTGp/kCO4vT898NGWH8YdMQRF2kuwwCXYYM/wY2
-8/u+OYk8tBV9AX4KCREG9tc47m+6Iq6FJSH3HG/XxH22reH8robISQKsid6qK6fDr78OP+ByuJ4F
-EoxeEp8I4qU308tUjCE9Jt/dGVkb7SKRpV8s06pvB6MkgG4aVFCE0C3ZN/2Foj0Nnr9KY7t/N4Mw
-Xiv0dY/ZEHpD8Jvf623XZvm9gIp5FloqOmcuDbBvu0PLnBj0EepKJfKPXcnvwYTMW+Gg2IvOOvrE
-ue2q3IT4keQQGqcrG1vq8de/xNKB+rY5tvwOEMCErnOcokX25nfIPFj6Y9p7O5mM9S7M2vDoGUn1
-8Our/OSJW9wqswsT2RL9vu/v1OVDJpcg9XZmhWYjU+9BTSR7leSIpRWinl9f7Sf3ZJs6dwOvQjBm
-fDMpaURj6JBv/J1fus529JZJfC/Fb66yLOJvPjkosq+IEKA7tAC+vycoiUat7NDd2fGC4SC+aFXm
-/d1QJC+/vp2ffHhQNxYKCffD0PTNhYDt84kur2+YIBYFIw7VHgtPZpY3Zppd/hsXc2Cf+FTGuq2/
-udjYAz13W8vdVaalr3N2NwbbAqnSDBdpTJ39ry8nlmfx9lMkQ5gePysC7cs3zyqBxjU3bgR+m0RF
-2JKVf1ZuqN/l1PDYMOIskFikt3DSxX6u0moLMSH85ORmidRjrO/SzGvIlC+GgP5JaNBeqyUYVy9n
-CjHPN52QhQy8uPTrA+fcZG0WhdetGjlTuVeUOGvZzUbQ2ymlvp46tw0Bq7/Zjl9nO2/vkSkhmjxQ
-hj++j4oMHmVPibuLylgcUkIrD9Ng62t3sB81SBmYqdpD2URfXTOWGwtdzAPGOu83H/XP3lefldvy
-DYoyc0EmfrvaNCknIDx0/i7Pe+swWsmlhMq4WpCuv5kN/3gluvrsH8IzPQQqb58pUBh6Lqnv7dww
-KdbjEhKFR/9ji7Bj8+vXB1/oj9+OpanPjMGkdwtD8s3SUheGqbmidXeWP4hNNmjJomMfb7BwjXeO
-xosg6u4hwtSJ3LJDdNd5er1G6iQpbyusz34r6dK5VIqrtrede7x89rM91N5e4RrN12bdT/doFa1z
-1w3VKUOQtyubGJuhNMjr3eb0Non0NTDVFW5/wJrg7WVsOVu/KaedVrd10DS12Jg29EH+oE6OiE0S
-V7hTnajXUWGEVz1Nq2soWmO6BhbobKJhFMHgesl1qBfp81SnBRBdX2303J/3k89wuxpq95D9J3tn
-shw7kl7pd9EebRgc00KbQMycZ/JuYLzkJQDH4HDHjKfXFyWTrJRSK633vahNlmWSjAB8OP8539F9
-+F54q7jjPl4c1w7yh5XC4/GpoD4z2EtvHMi7cdl7uypt61PuF0zKayCMTEXbZ+Ga9t0dmvYzymy6
-OXJ6wdBIdZo06pLgbcZlDyatOhZ2L58su9V3UIVRFGfEKbJP82o28+Tp95Yq7hsz5ulrHq/FYax1
-9EUGeKbdyPY+Sku+NRXkJiYvKriSvYH/b5D663yraT31hFUfm9HxWlaAzH0kJwa03aP/5coWXne3
-cl+jOEQHh06b8sCfQ23OyDUZ6bDYIjgNFTpIQRSJVWq5jgeyldwahnoA55AOYTJwYzlU6Et/ODLx
-mUxec53nTbtR1eDc6j5lauB7WGq1Et2b0zXjBYCLVlmTcAo2SBHxK8c2gF0+iZqXqKoFnZ32mEwa
-Si69YoJSngCSl7a5XxTEllJgKGz9F4A1oTJZCTVsyzEqjm4Wm30T8X273cjHN1odoicBEjr3yEls
-7JGyBAGe+wMQ2HKFq1t8QOa2x01EqcfdmGkbhwrjWfSCwQbzzOJBB7QRiwGXXU/x69T5ffWKxRO8
-g23LL+0TI9iEqc8THzOdeKoEByG6r6Z2l3PEOdedSSq6JH/WzFuYUNCgkW3t3kvlIXJbjF4SF+e1
-S+sdqLM+ULD5J7DRAeJGns7BwV054GxYD+rfIDnHmFE69WnxJTpk0Jzw6JXDcSTPeEMUkupgKbL4
-oJS1msQuazDkTXpbDjPtGJ5Ci5gbh983nwzBGPrUgiKp3SCHwWcVkIonQ4GPo8957JurrG/qJ6+h
-lr0slv3chvmza8czjbFtv+/43Y6TpbJ9rPv4GPl2zfc70/sYzDwf1cpciDHREOxDlTmvoxeFV96i
-/yjH17tioNnC0IL1K04hhHFA9fTJcuAfUyrkMv8ZLzjL1Z8OFjrZFoMNnz75o5toaOIEbTc/5Y2J
-+FtpccIbUn/aJpO3krY1kvUm/S691U/pZpjgZkhmaBVf8VMaevaRsvNqN+GnPlgzuzBHUfM1+nX/
-4MbdcownqyZGMkQ7TfRmj8gFLYFxyTxyQJxXR1ylgGJ3c0hUxwySdFp7Rr+PrjoVaSTCdSJm0GW4
-YmX6ki2juNKGjkiLCNKVMX38WUSB9wI+u99VWeZRepKagVO5SY+u7Sv8yH2xAwXGqxBZ2bkgS7cN
-Wg7HEAvyq6wd36PIdOdI2VC9fYqWMIEOR5OuzU1f+Zf6LTGtW0VcFD4D9eeMiSqZiEHiHUZc3hDk
-vSUIle9GGa5PIBa6m3aFNT3TM7yxLReOXuoUGIfL+b6DtUeQD+JES+vuZijX+CXQAk6Sod+2oWHv
-Jovl+wDj7aA6AOO0E1ExE9ynVf1o28RE67wOTvhDS0jvcputNPJVQ2TtlRdMfxg99EzV2rJeedcs
-532OtXcjqu4GKDDCbUvV8DzZS+KKxbmuek9kIETyam+qsNz6lZr2Cr8Xsn/PhcIJGIIaMz6mHQH8
-vREhzMF+pRapsX7mgKnDFPrPHJLWw6BRYHzFqxw49sHB+7WbJuXciKZ/aAtz7cmG8Ro+fOrwXOhf
-afPpKEW5IH/5BbbFfIiOUwG3Bql0S2c6zb7QvnAxTt6tnob0sbHTegcvZ7nCkX4j1NhsY/x+G9pG
-5/00DfoX3ShREtKCngTLeh/4ZBYkES7Q9/MUvDdhjhhXZcuenFLpobVmKY0DNNVzrFqa9oVz2fzg
-NoV3ZLSbHkwxIYqx2NwWNXkLR1vxU87f+0EifcTiO1eGT4PqwZnlXEsk3GpQ4TbUKrUZwRiasgPF
-J7JhgBDeV34D34TCaPM25qb7DXEd15tGcRpOmWQotA8a+I19t/7QV8+sqiBNOIXDZ71W6sR/jkx4
-NHd7KeClOH6syfhXj6z9W5vF55aXUB9WyaTT9eLyg6SIPrsZaTwGTyvS2sQcsMryfVEA26E1l9d4
-MlfMiOikqcTriFdlm8UWoauppTrL1feBRXKxW1NZJiWxNVTCYOLJpZc7WUOhnyBsPYVFp4+qxX/E
-2MI+EiGT53kBOVrrgeY3plys8kPDFBDN5zBq1z1kqoLlQWJyl6KRbqi+qYAq1+49xTDFtrHz5kNF
-ottp4QPNWCQTfVaLuYvVDxsS8mszVUcsWOMLCUOnSYrZn/6YavXFRlHCs2XmjGi9xjZnRn/ZWxaQ
-tahS9YlarR/luuo8T6nz5DkxMRB7uS/MWJ6X1Ue9iz06rRzHGl8xL2c//lqaXc53c6ejxT4xcU/3
-VhObx9WvYELV6bfBr33rNIBTq4IkdRDJSxeaHMrjPNrzYZJQdYZUg7ev7Qe9ighze+7ukbPm/Zr6
-AgOXyJqz9HkSotm194439JvZletezQWQYWYTFYy0AZDkXBIrGNAJv8CRVFf44Mt+3/R8InEgq0Pa
-gIkWuQJYkAdXpRjeFzMrCKXz7Vyp7hvswcAcxqMm16Fvnrvh7YBrfhenXffpdYF/qG09nmp/OZTK
-em3SpSwvRWfZTgNLO6u0lrscMh2dCUH9gkWjv43xMR9sNsHj3BKVYpryItocRkweuVsdj+ZbN9PK
-zn2hg7oFbYpqyKZt67I2lyrIbkMaeh4ozmySzm4ph4BaWG4Ao6gtQsZ4P+fmrb2MopQ1XOcuKNF6
-mXZQN8YtmISW+etM19MMNH9U64Go70jYYiTr2YY37kpeiob24oGDvW82mUy3dEEhmzZe5AIBbF47
-aRX7NqTGtsRWEhRHxrn9iYQtsyTGhkdPhdkuomOAvW/GL1n466Gyms0Qh/tO+eF+CUi6btrWis6x
-mrHD0/F4pNxrnK16qwlsI1H624bC1QNH+XIXZQxLg1ymB2zXBHv4+RtT+1+99tP3sA4oTYMGYk9L
-QC0u3t5Wvyw9dSQdVPXeGl4j6V6q0MlEj+Yj7i326Nz6igr16nrlDVOOJ0gfAkeac0eR15+s/GOm
-aDzogkE74/dnhhj5hqL1c+uH14Xv3FguExDKHjoK761rwxN0DaK3PKSTF32pOZT7zK2ZBWcJdX3j
-wQt0/bZ630hx1T5ytZM4k6yTiqwEw9DF4gvsimfaXCCHd82LWaPXQEv+pz/LNv01K/86d6oP4fr9
-VceEJxkqI/dNnb/kbkwVU/1MqOCjcfWpJZ1AzLS59YKS390d1SZoR7o0xwUwmKSwxrUIytAwRhuZ
-dk9NM4GTDqpHyVt1qmROOaF9CqZla0XaB2frECQDnKtlnh6BaI53AMt8CmrD7g+IsRjRzD9BloCW
-X/iXade0Huop/V2CP0gCrvvPvRbMVLnk88pCCvrKV6fd1zDws7T299RFQ1wt8Rm66ZRfjlKB3gmP
-gWBeQbvs5kZu4cybDbaYG1dgte6ambNKm1JTWE+CvAVXhG4iBzP4FmcY/mDpUok3u0NKsZtotqvi
-++beqqhqC59we98JbyqSwDW/RnwoXc85vwk4fdalO2z8lDW/zTjQe/Fjvno3nkzfoMnf1kEK2Xfm
-e4efY29kWJlTnq8tm37zYvd4lczokY6R7bt0RlD3OD9B0/wOLfEWVHafrIY9e2k7vjQAwq3rDdAw
-xvp1RgzFGe9XBEIy5yiINe9anAKwETr5WYwDxCGRA79GEDmHjU2lWgjuXtewSrLQ/GrIIx9EEPCX
-YgvDzTDe+Y5emA95areSi/oJcSncFWrmdBd41X6hTXhvxYTIFkw2DXeWveT+c56alMMRTAHfNfem
-54Lht5F+z8meA9BJhwMSy5MeMrVPW534Y3YbcTy867Q17GbWjp2IU+iVsYvVS87cmzFa6NvVZfRu
-cIru7YDLcXTxgJRy3Q2YUfcu3vFdhjkhCadgfnbJy2/CBnDeZOibw5Oivmb+qHNowmobzHylrjO0
-Rze3hgP7rX3banKImSobfNhHKlUkpiXl3tiLrqiYG+RNSXz2lRqC4DWa/T/0CjL+cBuamCvPfqvG
-qj82jrSe2nY0v4HXZPe9iYIbcvjMQ0HfHXCxjgcSdzmR/LiDTdIB/UbGYbiUQ63TBO42E6d5ICtO
-F77Q100JaNZ7exvWCPQjND6wP11NnX3eDqeuxuNLRe3HojkqZiheX2mW07utHXBPhqNQzxX5EEvf
-Q6uWnJWkPeD1b3ycHUFwbk2/fAwE+7kwBbuK13dvd1TFXmxqu0n6E+mqbL4vbJpcV1ES0KUaYNt0
-wUOOEJWMNd84wZP46I6+s5/RUsqNnAaMXB2J3tmYEzURuyae5n3Mi85dqjZX5BrGnSxII5H3q29i
-AoocYyHe+6Uzbcc1zU/tOprDMLvBoa56nCf0u+8GEEiH1XfHY1pO0TmNiPFB1Ndbr+A0zwXsaepc
-71fZSCcJ5v6b5l0GUmX2qwnX6kbPOcPEYv3mOm4eY0ZWJGqMBQGY/uW9U5rxyrK7F9f13/ix3bkx
-2MmDgbbunONwJxb8kJipXty5Kzq+KJPfuraFNtQYmGf1YKMF1ZaD6lgE9CI3PD5KtXs/VykhfOmK
-tyED+cEj2L6Nkm06LS9kkmYYaUQCTpYsMmge0Cqal9aaYgKOeftJjaz3WDCKv3e19nY5hQjLJlgL
-c1+68W+mbvEjetzF8ewx1xatSiYKVJM+DqlQbIeQQG5jrvFplbsgnssT8B4kUZ0GO22p+mBZeZO0
-XdRA+3OK85IvOFp9o8JN5KgJOtn6C5uMfcywar7nIIA3lZQGhSP4HZKN4XAQLwkDgmzX1V57CRIr
-poNLcU0/Hn3JsSdPPH4PUEdbsm9Npo9z5uXX2dhQA65UceWO+FkhB6OoXlUgXUKqd73xYQHo9D3K
-Sbtnay2XwziFXpR4wRq+k0q1wWdN4ezvzJAXP4qHLEy8dpHtdZ71CwiyGIhEZVsm3UU08gmqvwx8
-qcAfqJGcuOmt/fpMSkwcgKKzOy6l2DI1eZLBwJoZm/KrTsEXyMiZtxEFFOSTgy4pu9Z/SUvc8z3Y
-qdoxZ+rqCVaX7B28q9V605g63slLAG4jwrUbNnmjsXaGlXrlB5mXumrUe3lZOx1V36qmL/eyacNr
-P4+dPVhSuE34dJqPVrXeGSCXC4c/VMtWKJ3S1ZSOLxO1Zk9lOurnosS9apOvJriHOcNuqEZaLInK
-3lVtdXTaGBhKHxYDoB/49Zt+cVgTa+zNOE6qqN7QmDUmWThZO0LfWmxEbsmElo10r0ETl7AewZeX
-kE6GTTgMWPsC3VV7oD7tZ0B3l3/5TsrnkPXndqij4Q9oUIv+US6Th4GPOrpm/87LfeGax5SuTtsp
-H2FS14d4zAFToV+CgLMz0JnDvcgcn54Bfh9q1oPNOlq3CO4kGSAIdWPKwsscYW/5Ew0sZQvkBOzE
-hbCYDIFIYsuiHHYufShhgPNufMBIm1J3r6EuZL7NSwLFXU17NWFg9xiPkZsYQ+5lgkTErKwfHrlS
-prz/tTzQrhnsZt3yW2E0ogmX041PAZeFg/VCKvteOxdY3jyuG7VOZDvzo5766YBSS6AwSm06osh3
-UkZEzHWwyHwW4FubvqkSikH12YuKx6AHvU76+ZwKm1QwTwshfFThHarOcBN20v09K6Ie21rWtcMZ
-fAkPPchWHym07a9EaIZDCE+eelpDc20gcScPi9u+IX+0D03U9Y/ZFPXvGO3lHZ8892Kku70zmvCO
-s9wE7ieLQIgqmEuj+6fPgazFqzPf+StuvI0dV+lvNFhO+OjldGR5GTguwZpn078QhuEefqSFZSPT
-rUxKFff9D+4gZ97ZTrraAOZmxo6139Af3Hlt/MJeOkDg8SrULH8ZuAbjTjQ0O8QL3RumthmpRj10
-GRXWNz2J8pcyGFPckZG+7jKKOFP7MnFJabFeAIjOVUEZDFl0Vv6pe/SnVhzq1rHvkEVC/tMd2Jms
-Q9Hzw3BGROcsG8PH1G51B4FsV+d465j0gLkzuK1aMd6lVbXFZdzB55Q7bkBpghn5Z1jNS9PP8Qsh
-eNq5u2wB9ZQ1Xb0NnZUU7vy2dnh0RV+6+3wsttbF/R+1xJTVUhTnTKEJMdA5ZVVhvXYTPU0xDsOL
-7F4mRb4WuGvmbV3nYt8rbl068+UR2D+XWeAzCC+0Rp04wYKELAyeo73dsyuSCqUlA2kHWmViop7C
-7m4i9R5Z+UBw2LatW4WJXO1ti5pI8ur0Unuh59OyQfEM5i61I6PfPgUjLFQYNoEDMKvumFIjeATp
-ZoVefN9RV+WwgHnBs521+mjKjEuk4bYCNJ9mxLMFPxpwqr3M+zLqiMVnyJr2FAbv/F3rHoIiNbd6
-wJborWPvXW4s1X1qZ7j4AYN634urOfRaLfVCbdw4BLMj3b7Ab2axLOFpyk3ppd6PCMpLqzqdOgfJ
-DIHtDb3kzZ/L8L1f8vCaiZS6qbAIPDL4DE+Bi2XX9rOs3Qb+P3qxLYEpjja7+INQkOIgY9XNyWaH
-I+FIlRJyWoBoN/jwGDdyVNizLUc4lAsK7wVEnA2vWLY/ZUgZ86aPu/qu0bbLiEFLWJM6FuW3tnwb
-Y9gyw0uAhFsAWM3I6lod+44KfsFuDu/8Vla/K0K7KKZZdjfMSrwDg6RCtxuy+lP68Xpu8TSOm2aK
-kSEqiwtTMtcGhlSr/KdYwcy7VFU6nx0958cJlGi96aI8uC9tAvVJpLvsHhMx2m5u7V1YVa92F/c/
-qqHimiFS+lZntfqwePd3VscnL/k4y1PASfK4NMX6li4qf4ebd+FFESf+cI0VfKICi180AXbJ2OKC
-Tb0i42HjCL96Y7hreETOrSVoksA0tcPnN//AxJ0SC90maUjv4oCPqLlfgJm9Wn6dn7zZXm7MNMUf
-0nHLxA4pfreXqDgHyMxQiKweM78y6eeKyMILoCr9ETV9el45a3OoXqFslhwAoa3WXU7jgP/M5tX8
-GZtB3QdArQ8MGyzv4svPdhzzJNZV61eB3EP4DBsF2o2d0q+UVYcRu+0tPg6QuCz7eueptr5nXIZj
-eM7Qu/yi4lDSuHX7tHQTIKtyqSiXx+xcJcLt5A3st+okpiU6zWnenwuh2m9c2QwGldN7OpFOWEGK
-igp88vFk29u+rNUNC0YE1qbgm3MB1qoD12QY5qOruUWr2pdY9iHScc4m7/TlSDM9IFhP9xRj6Cd/
-DNUfXw/VTQMB8bwOafATCz+C29K215kILRrenNH78Yde/SndchIba1TDR4P15F0a04VE7EITYMfT
-eAiXSdB2vTRecORRjbeUVIvnztfAJSOAEhR6pZ39SGRUvGZhXX83mXl1qIjEj8+JZFxgbW3CKnNm
-FHddko+els+6i3NyGWinA+cp/Hgh0vt67CgvO/sUTtZ7rgF8yEM7csCwgna1zzLXoiYC7djMG+a0
-uF3mnvo6n6kra0TWRHsvy/urXLJ/YWj1+/20ah6duhnrKnEjNhsogAyi28iyb0YtoFPySLi39hAi
-2IU9oFI/CLPPwbQpCUnTvQtnaeUWn3h+GmujHnO+qGgvok68dAwIl51d65CCIXzbG8CpyxeFexPi
-StWG8tiG9SWY5HbLsudplh2Vb+yZm950c5CEcRP8GlSM67vlyH+Vpd4EDvGys8XBdMjWC6zaapz4
-nIXLb0PTxobJ8TRvuFrznnBG4i9gmOC4QQKyDiMmyhpznPAjq9bq22RTimTZ42YOFqwijnNN+glH
-nomECQ6eCAQmRRRsd1P4hoGHx//x7GDRHTYt3KJm12YXhvbghKrfibxAOusc+ZVS6X4KReG7SZX1
-xEhC2y52dZXqL7OEkK1nAe9+ZHSzXJWlVV34r8H7iv18wxCDy1tt0vrSxVR637LC5rwYqlxpZV2c
-wzLWzcErxyCpZL/sA9LBDPOi5kTvFYOykGHaPcWmlKkaMbCb0D72tcrW4YjnWuZNhnm9nUZOE/CE
-f7zRia98S8Rnidvqflo9GID82d15MZ25WZbB2jKr5Y6/ELAh2A4MbXQO3G3IgnJrpr43Gj2yUZUs
-7vPIv6uY+x7cTGfPeV17eFDhxx4lztZxz9w+31N2/+kre3m0YHB/WXBI6M+wrxfXUd8gAeSLF+YV
-GeRJxYi/Qr/H7ObXVqac24rA7WNGxOJvjBgXo8V/tYPE9iWUyMYN3kv81R2al3aI51tHlzs9w1Nu
-zPdhQPa46tuCfZuj6t3oWPKFeiq20v/dMCH+J7sEFhSmoIS7MN78xd8DKokugniODguQg7uYymlS
-ZR1TBJuxvTeRV0m5kzEYt+X4Pa1sKWYY6n07ls5m4Jst285PoqhG7CRHmFQNA6ZmDrz9xDGeebPr
-3MOm9ZBlavyxCKg+WJNAqPMk5HoDaPu2c4EATz7aoIdTi7K1qST7NXECZq8nL6SG0j3Uc2ltCtxB
-2yBlLRvMQF/t5D/PA5cDf1qce10EX7KhCskKx/6oLRZ8enmh53EZwyo1R97ffHTuhWjwl+8tRrOF
-iE1mlmHwX5wmNY8SH5/gtI6HknuDfS8ExbN4YBf421iWpgVvhhczd3eWC42/G5Z9XJGw5GHSGJi2
-KbmNMKnzkVTMUAc7GXvjyVaAetRsUcgwcN+tSg7AngQLI0lv/O/f/sVI+t/+BJ+BFsFUBz9DdHHO
-/ZPzsmAvacfYxAfbtPIfJJ+VLnL6xa5Wq3/ExB5sRzZnACBdfnZse/jDxGs4Gfvi1kNw8x3Av24H
-BAg+YvE378V/t+1dikjoM3JdihL8v5oEMzS8wAlAfgKbZA2dvSy+ttPG/M2P+UsU/2I/vdSa4Hjk
-FWBp/0cv2T99CC0DY9GlbXxg/LmUbN8hWc3JDNt5roLfLhd41siSag4nbbbpMAaPBYfQeYswXl7h
-2YnvqiUqsc3wsrR+U9/13mADX0xXyE+F/dz2Zff6N1/cXz8b1mvb8f1LVFpQfuH9xaapK70iSPDs
-jZ3LorC6jQ8iCnFQpiVYda4hr3F5p+xCfVQr6hnzHzvJR9gmi1gCMqDF8u3LeP53JsX/D80/Ly3R
-98/vumi2Rdeb4qv/Z7M1kGiX1///Hpq/+cw/zWeX9+bzf/j3/jM1j3WNSx2xzUuAO8IfjPei/9d/
-Cd3/wxCX98vB74n30+Zn/YdJm1Jkl38QRZSqxjzM/EsdlLH8X/+Fyh44PnT2wIRigWKU8v9i0iYn
-cHmo/suCh1tRhA7rXRTY+H/+suC5wxLNvWvNu6Vv0WyDAo76PHYM19Zc/GSUBQ5JX7PTbef4YmWK
-slGz9mW2cxVbxKZ2UShxQDWdr97p5ozj23EgDMkG3LlfnsbbsC1WCLqzsOuNCZHiNxV5GroJLFm1
-D74pijfoMkX2ZC9gBB/Iq1UdfWdFTxZbNFgNTBMA5uNiZMxW5i1Y8J47YbkJaJqkvqx2aUWNXXiz
-EL5h+ZI1b7L7ps+cH0cqsZMzps2EZGt80qW2Hl2ufsxyy3Wst04OhI55jaPLu8m007WNWAthu8Ii
-7jRmOhMJ8yO4RWpMb9N6CYtNE9FF/hiV7juZDk5Ok2UzBNchVF1U3YC6niInXbfOMGyvxeiBeUPu
-yUkGlnNmtmqEI4+QIPNnioBIimHHyQEauiZccaHLQt6BZ2E6UswuNhcaPyzbo5tw7aKxOlpRNpVn
-CiwZTMLG5vBOSzJWi6WLK/L82Dwe3J4wYMJgdNhYpJsoNuVSBKDTxbbQqWvHRPnDTKT9o3OsL9/0
-3BCwll2Ma3HtIz9PABvVEEDsE1Xxxn8t4BaXmfuUQQK2iqqdUIGaasV+YWfisVxIc900VMDBrMNz
-Gm9mq/Nwui6rhcmEtCwGPjij643oQ2NxonbagJPpKqyj8WP5BoGeQcTA7G28SQ0AbUD5Reduo8n1
-75t5dqakiNKuuY5sqipRDysuhGqkm8TvY+6uHbnA+GSLkpAy/k/8BFibIOBS23RBbkXUrDmeYriW
-wervtz3SxYLmlRfpnon9WKE1qG7Z5bQQO7s8bAN3I7J2fu7y3KIMavbE7zZI9UudK6goiCjfqkud
-+cxTR/4On/JidqPp+5l9E+tKbmzsKVXXZ5vLao75zYpQAqwoDc40S3m/29jBAJA7Q0TEfM46hqyM
-zpZkATZ59qa+heHXmvKa5Sp/MEV4H0JE48ozgOXtU22dssEBZjVNoY2eXbdvEYOUR2vIu18rFMCr
-2C+PI2WjyKv8aPfpgoZGkqKIyX1mahUGmIFJvyeD3S5PReOt39ij1husymZK8OPkzp0ZshD3pyrd
-aec2azseVztjACRj0x9noUq95eBYf/TWqu9iGdqYX+MWIHzKMFwlFr7kZ73kVKLaHBDhRlmR1+9Q
-qf1r0Te5DysTo/RGgk9yrgaPNQHlrhY3Bq+t2JKNXLguyLr41cfKnXfAt3nanQxSmdPC0N4qnZNQ
-jez01VqrlAz8SOXWrJrvqrWw/Jm8AHMo5jdE7DphmhoRCtGm/liqjPeGtt7+DmuuSYSo1VVjV+Mz
-Eqak/GYhqlBU8YxWILx7E19Q5YLxyHEY1eXa75Cfkuix9ZFmI/ECfrkjFjllv/zSzePd2tPM+1DO
-RThhlMxHOrgXCiEGN8t/z63FcFbi9Bg3q+0gB7LdPxeB7cFS5FK3EYwdwHcGE6XKaRhU362fm7Nn
-yAUkHHTX1wH4/5cmCQw1ofLm7IA5EqWiLkNyX9U07sSYTbe5VhZjQdeTuBlVNT21U5FiGvOXWWxz
-Yp8dI6taO+fATdvzGLTVcJgXeCPYQGwu3AwsgGBgYpJ24tu6Ywi2hHekRRUZQ9RdJ0vD5iWSnWVv
-p5kXBQB3bJMTVP6lcoM97au2Fm+DtuMdfEMIpMmpfLXs36TlnB3IUcn5qTSAIHK9zbsIcHrMpW6r
-GJzaicgKfQxEB/O9IxDBsg+36ayXJW6eMTN7OLlEu+5GodPHerHs52zBpbkJ3AtaE291Me0qIeUD
-p+xQbAbbxWoKTVlYVxzr5SeatRqPWWEP5Y3wiIVHGUsOSpBX71ocXQhn3ELu06LMnp2IZW47ZrPT
-s14UlJFiGeVJjH0gtqRj4+klJsq5sl45lMl1fPLFBSEePFQzuE1Ikk2t6SBrWrTO5ZK/xTvZPhaa
-0jJ8wyF8yrwtAp3kFieIUxG5giA2Y0kgoKKMEycsZqZYMPN5mFfrNDROdppnBVR05HzQHTGDm3SP
-GSY+NtyUv7mj67dmMOrBGvui3sy6WL9KYdFQrcjQUDtJBEht+RE9LQSDXE9OIy7QSb+6OKkLCnYS
-RGxXbDB38iGQcOQ6xsTlvivXhQOC8bzPSK9sdBG0kudFRd2NsttJMBqZKYcSJUsrxC2PqFeY1bcz
-mI5HL8rH12lR8ZmgdMyAnA6FR1nbEaVd0dCNNyWMx+dxtSOznQAT0OhVGt0e52CI/qDuLEfgKs4t
-NhH4VPCRVcVUp5yA6xJQVtsIRXDjFEyN78Qi5+WIybSN7+FLodVaU5jfWJ6JPwJ/8R+4E1xpCp5n
-BKf6cajjguqrFVZ1SrPSwWOR26bZaOHNZVofDfNv2VKKV7Ssma7dld4v31CAkGRoqG99MXg/XQvw
-Mxez+iyt1eGCp8fyZM8TQ4XLBoCHSD4tQnKNngZJ8t/UMsH0XzxaugnPjg5t9zB6mB/qLED5qCTk
-ZicDcQBjgQaklezyRujchRHmc1eCKHq2GBSi42du8Cgqqy5/5U6fMcgtGRmpfD3OtY3S08ZMPfJ2
-8pyk4pc+yExNEdNitz8wSpqurJzsSWLTM7RrAKqGO7oaQzi1FibkSmTfJNDzj7xbntHaEXNdmYmC
-JAudc8XcClzlRO85eoCv3BjWIrwp3uqOJ6yrwW8NlR8/K1EA6zxKeXLE4h9cGsEfYL1QJ1wWzvOF
-BPTLd2CH33pSjz/cF5uJs0Hp1ndBT7Z6m8vJCvbUoXIVXaK2ZnCFOfaoRDn/zrDXf0+iKcZXlRK8
-OQQKoUcTFzMPU+qG4c5F26VdgbFVf13EDh9jlsXDAtYgbb+9rIJDxuUxH0/EKETA7ly6C5WTqo7P
-TeONT7A513FLJLl+uvD/vJOag3p9pInmcezaUp19o8dl46FoPCyh19iJt+Y3DtDfY+EvHbey2fQ4
-y9my+qqv2yQU+awSFxstkYco6O+L1eSnGkzPucHWdkxjcP4I8jlOnn5iADSj0KcK2BNOqYy9nDPI
-txEg5HxcuaBCEBowtAP1xXT6alnYDzcTNIYexnMVNJ+4AGPYRhyNnpdCiu9h1OQuMmGauyHu9OvA
-LRinyzI5Zw/d/LpzVUh/rs6cN/JNzmvAWe226/3s8G/sndly20japm+lbwAdSACJ5XBIEKQkSpZk
-2ZZ9gjBtCzuQ2Jer/x+wemZsyiNFn89BRbiqLGHL/PJb3sXLhwinrgIR4L0sbCvf6WgBbybGfPXW
-RJnjBwdk7nNkuWBgMG380oXtd6OpQwxWhpwOOz189aKyuv4iEontn6D/jM9A2JNwaMlcfkaqJnoa
-ET9Q5G5uvNHJFz+C/Jgk4EyvNp6X0aq3Xr3k4w88RsqNpVlE4xCIOjn5dzEt9pY24Mc0M8SVhn8S
-Ui1AVrzr2kQn8qAvYliOmcgzhBDyEm3npBpMwwdk76QbDSgDhA0YIEvAn2AyMCQb4i1QWTcK6MKr
-oHVqc7rpaek+tXVLUZ4YkfERnI9IfMPiKI/nTD02cxs9svaXw4LEgNhkLse8Xy59f5+4UKvRw0dG
-B/GrwNDICpLc+gV8y2i3CsAueSNskSsGnHP8hSFezFzJAA62WYXlyRhMXdwqs2YKP06+VoAxm/o+
-2dV2PF2DL6jQQAL8MLTDt6wfkzroMfAIAdM5zEXwVpF3CKJ0j0izLlBjjQQqj3RBAU5NBl6jzKpD
-onmazXjfQsdYt2Mz2yJwoX2Fyt9r16mmUCLpzcL5hD0iZkHIGgsTvdqh+qHnrjNtQg7auwiXKVze
-nDZj7ut5uErg25gHVQI8fxnl8tVM4vGbwV3YfjrGOh0M3jfDFlO1e8tspm+wHdDgSERmfUhiU38i
-wSXCpstAst438XVoVhM6WzUd6tnJrxqG2clhwErulqLBDa/rVBmnFGCGnzMGkT5JxgKmcPEQK1iy
-afo2GatQh1FCZOUrhnTPayQwoOSAqHEyEGo7NrOoNyO8kRPb1z62GS1bbEh0TvfBKqNDGMc5SvAw
-AEa0WczNHMrig6GTDO1CQFzimvlKaCOv1Oq47iVaSlVFeWNvKXKXPQNJ45vsOMC2oBqoX61Ih1Ew
-9zno9RAOw/wJGTlhHbTO9NIgaaHvD3Ujr4a4F1+B4aLUFcvmkCnC/GLgMsW83ibWZF21awCr+IV0
-o5TOLGX6Ft/ulCkMQKlvloYEdgQbcW+jyoTJjItHXYQUUYapeG4/LOiOttd1Bcjeb0H04e4VlfbO
-LVDS2fRjlJJQGjTKtzIupw+ucj30nrrE+5mgIPvRbKNPsec1MKxSxjxViV1voRYnMJ2EmR+kmeu5
-FSPQzLq8UlOi7p2h1n3V2Ej2cTbn+W5O+vYRgRDQFE3vzH5SJu2PtIvtLvAMrL4xZSzztWTvfkLn
-HD5MDXqTPJvu4PVTRRGH9DTr360Osd6c7/BiZdbyiHYKwm15Yh+tPrYfQHSh7BOH4201LDcR1qjd
-hlmHmrd1MRwyy/7R9iQ8yB4AbDHK8QaNs4+JUev7NkXUDu0i88uyxD9ZbhPvOJGb3k5+onpRXLUh
-Yi55AuC0SMmQ0ZW5swpNXRey5YaGSt1jEssB2jXRN3IKRvsEP/ujlX3XDSl3mMVJEv3S9JNZljth
-VfIqw5/mI85O+r5xh2ZL4PQroAN7kZTOzz7XBMJ8jXVlquywlNh8IZrErFxNqgzSojE/NkJALoOi
-dvIY9dwA9xrPEzbfCgHyBF4369MhX6HlO4Lk+GPBPgyCM5xnMD7Sve4yhPI2iMyjxzGMWv1dZraL
-NA4ixEc0VTH5ncjpM8yB92mqxoNiSM0yUdn96JrzHYw5kOTMY+fjOA1khe7YLb/mFNIDDaNSIWBU
-uE+ztG1GNeBU7FWENp5ydzsqLMMMMvlfuTY1+6arz4fJc+21vQCEIvvb1iaIdnZapTj+SYiWReVF
-h07Me2QHsn3ZIQQnTEXzI7NV94l0F6PRHBmd7XSuOYDg+3UrsxfXjD1cGarlESjR8hW+i/1YVjPT
-bT1OWyT2rbndoMsvtkzr8EBJ472s8qvRAKYe58L+0GcW89hscpnt4hJPsqMVVmD2VQhyq5PHAb37
-be8wdhob/cYRM0gVXTryEfl8hhqIsT3kukXjSI8Ld5uV2XMNSvUZUiiEsb5p7kZzFDsLJ9lAybV9
-BpdeMdrHsAHVp7iW9k46oFmUjqSPOfcHc3LA6Ebj1qod62aWhiCR8hYfk/J6VxqdpEZGp6VpI203
-cBgHtseUx7Gj4kiggrawdO4XJM8V2O2mrvGaREHHENETkmLesE/0YXqybag1Y1t1rA+vlx8w5HZt
-WAP2fIt5x7gj4s7YDJTgjrsISuESKeNmEik+InTTrma4VV+11NWfpF130FXqpf20DB7ZXpSZX+op
-1fcOqFW+KjQZZfP9ASZ2O6fN0+i6nkbSkDEGhYrqMHnOkjmnqcy/2xoPMlWCfkG3FL+G2Qn3xIfq
-ER+qkXQo1O6wVHV3Vjh+6VIO1l4UJZzMWFV7Oclhm+bTY1zlzp2SIbiujnIA/5KY8mYTjjK50bFd
-uXL0xv0FdfJeA+G6bScNWLMTzvc2XfjdpDHLxv5V26yNk3TSMF6Z0u7KnnBt2MzVYn+2jUJ+lZm2
-1duYkyRCz9HBUWwPNjIH+0hiexdOcj6B70KUIpv0FwYX2McsnrzvmeCltly6O6XN2XgbD0jO87vi
-A7QnWKDCwLnAbKcDqff8ErtpcZ+10jjUw1DvGr3o5gc9AyrWQ0kf3E6ALmAMRCa1yMggHcYiapul
-yQJihaLlQTcLlO5kKTj0/hm1/f+xwjtjBccTQljMHf/fg4X/Vf78Xnwv//W9/Pmvu+RHdfre/Ouq
-zfnX9vdBw//5Tf/RgzH/7aHlAFHV1AECM8T836MGz/i3ocOad1b9BUeehxD/V6CX/4KSEDK8FvXm
-Ok38z6jB/jeNkVXHxVmlQ/gb4r8aNfwpYc/u15Ek4M4YeSASi/nCn2NJQBv0qxOieTwW5iaVxalU
-brbDSg4TTsRlA3SnXyACw3f0slMlWsCayLShFIYqW1KheOaWrR9OI8fkmHweKgS0f3vJ9/8MPd7w
-pTjfIs0J3QNqwhtBPOfPW8QiSIKAjZq9W9CTBK2F8F2MBukce8cBVg71153dwk+JDGww4eq8M32+
-1JRa3xE3YNHY4lWRfFxI/AITUO6IbB9TS24AJcFhq0RubswkxC1aGZDjQkxxPCwK4rqHbsp9vP0O
-LobH5zuw4WAIhEFsncHUn6+gtRLG9WTFe5rANHOE89TH8i6py/eE7i8Em/9zIZvLAJPwKMr+vBCi
-jFBw5qrelxUyw13UeYHTqeeqLrwAY8dkO9vA1AGvmJsBPNoWKhGQjcl4IBihaBiiW2tqZvi9hf2w
-a+ACPpqwlLfrvtivjVv6ZdW8bwor22kK544M3badtBXQwH7gIFHRguOTcU+7Imf98SLn2v4KruVK
-b5DDtZI6vI5KlHrwgZn3raS+n8NPVKKs1mJ5qoQrA2saYQu22Yswl2zXDvmp1JAEzWHALq73i/bz
-o7k4X97+QhfIEl4cW0JnligQ47IY8v/54pyFjjVdUrWXZujukmn+moahD7QIE1BKuy1Gvt7GqWkT
-v33dS8ExLmxJ07Yd9H0YPRJG/rxwoTxHteCV94yz8h1oYCxc3aU7GAayO5GJ9XDiLMO2agx5g+Kk
-ApYD+ttxSz4oEDrwwFHQuy0DHuppXAgRnPFCundVPc77PA07qAgGmAB0yd6TEDEuppzrvUM7WxEH
-DGLxC7lY1vTELJKBON+j9lP6IELlDYLMEHcHqBljX+0yBxnfLuyKOzW5mKGKq9XOrof8swlhj/8T
-gKwpgJNng4bauG2PGTNWor4z8zRo1ZB4mMuPt9/5629tgYg1bAmOB9iEx6nxO5QDZURNbyg1mTLS
-IwALyIWZsfzzohsbm9m6h0UFatR4b3/ym38bC59fGMKTnq2vTONX6nK9gRBkTz23D2l40S2msPcS
-LLjffr4LxMP5KuZqMbhqdtGiuAAqlTni31qd5/t4dsq909QMN8P49PZFkNr6y8NYHpATsCA4iBgX
-X5/mFXwojHjgO+UvoRNSptotYucRWtwblMp4Nm3kbBlWx2ixYKsi8xcRWcsDAEomiTixgh+mJY88
-y7bAdYQUOdIPecsiR9wBroKuoTpUuk+arc0w3pw7atHmKhl7F9p7T00kci/QGO/t6C0bmBjLvT4R
-31CDoRGBLfGuSvhrlPbiiMljiZYV5aYX8vNW7SKvyzQVK1r+VE8THeqV+8/AwgsgMJSb2FNWYBjt
-56lDoNxQmFSFXXoqluQkU/OBQjy8DhUKbJaZvjRGXx0wl0Va1isP2uTpMDR0L8hRY26iENASJSaF
-BLqPaGew4ATru4xaMLAqPzFBmWj0R58wf1wYRHlPMYsDIfqM+zYfygSH5RExqZ1pdLCA2O3jGr3B
-4LRfaDoxJNAaFxBOibyGxcVyL7W+C9ykN42BnkI+Jqc2mlwfY3gDEYecCYohv5UNRKWoL4xHxCBI
-HhIk7O3F1nZOnr5AQgCUtoogwiLAp6LrHhsj+8VMAukWPPCiEVWEAYo8KhWq3WUcID7i8chkNNqz
-gx015XDjbb3YdH3pmuG2t4AuE8vKfSaTk2nxOWSNQonWcgLnc4evpVUcGYV/TIX3VLcFU8a+6fws
-dOM9yY/JwTJY8P/4NGXbPNrJgqSX6j+QYOwZn50w922u2p4BqcZQfudNfM2C7H8Lat0m8baDus5f
-YM7j9lwPaBUPN0uRveRO6e0n0N64nPOg7VhI6BC3oFcNJjKD69MLucvCytiKmjOAUV7mGz1tllCx
-zqv1yJwr8quMMmw7D9mLFmmsWL7s7MDeFxX/S6/l5yGDs1BG8M0Mq2j9KYxeqtXNs4yJ1miGur4W
-VxiJI3SPhDn4wKU4YQ+e01rGw9geNPcjbnLBAq0YxwjURGa9ubFD50nvcp6R9PRopz251fphyAzu
-WrthPiw4PM5rdx5ZNrrymEmGMApUnJzckJxRRuYDol/evpvzk6sPFN2scNGxNc4Lt1m477CcAsAm
-dFAKe8+0+El5JDJo62T/bIGCFSaE+QAeCNH4geQTL0RYYdPKVE/WbEPj91WFMjduzAoyBZ+/1dku
-qq9wf6TReRwZYu3EiBiGclm0VZeczjfO7ZLF4HgTpBpnGhYxzQ3UpPZL741e0Hc68Vph5Jc7sYIx
-66FAM/DtHFzDdwtKT4Ki2odRBiqy89JtOg1HJIQxCM1QCp+6sKTdlb9o7RqwHMnP8Bws3eyfD1zo
-8sHI6+dKsa/sKX2hO+zhzJeezuGid7KXDq0ZdIWIBGUacYEWbDADCm+rbABnjehaWn28RIoB8iH6
-5kiues5mwDgMOdL0mFdu5mc1UYlABVlxUc/SqI7n0wmeGFwB9I0CKazw2rDTl1kPw3sDPbeCJGmb
-2EiUNG0J2xLhK+LpzzInmJgGKxd+M84KbQLQgX1safzegVib2RUvZJJ7iMCnjvxqDWcz+gqr88Pd
-OSj1kvASd+1zOnFvSW8j7ozLXp3LB+odVLQFWwWhidOsrYNLs0nxH+TjnquJeE1Y7MTU8O5gsVbO
-3fkJUS1/WbdEnciH9ShwbOOhU9zY+Rsow0PgRBuh8yHCm41H+q1yi6oFy6aEsxcaEpEo0TzrdMmP
-sklfMhXlu2ZhqTRIV/8T6VyLYCJxxaxmSURFNGlHNBk/tO7c0URg/6bsTHiDCz/lgpbJV9nGbv06
-E+STrVyq4xKVuo/wE/9JLdP1ORIj5k8iZke5Pya4LHDGZwg5uE9Ojk/Ehp+wuRN3ClokE8li+ACo
-OKsgqXCD0LIC91NPz3xXovbP5IveuM4bO58rZsZNYS7NVrXlg4C3CV1u3sMmZSPOvMh1hU0LwRj9
-igdJpAkgCSPhV7HoGo/AkyuWVQGtFmEvPo3pkVCsX7dNm+ekZIc7MVGfKqjc1xG/sB6oCs7xN1+j
-I3TPck930txoXlUd6rTtkJlPTo3HBaKYVQ0NkIRsyY60lemB14QbQOqZf06H+yTNd/3YZLdamM+f
-dAb2B6dgd5vQuDb6lJ3Oa6XsilPqxi/lMj3BLZo5MBrciQZe9XrahB5xMevYAiE+CZiz25mPMb3O
-bDEHOtTB6JIGAhI9koaBMywQcuwmuRtBjYEQWvNz4PxpXccHoOcceMjm3xEl65vEijvoKiWWF8zZ
-QMbGk9+LxQuY6Li7qvLQ+q87RFvaERWHMJb406olOsXO1Dek01YSDIKWVucm7d5zYlKNCd5tXT2H
-zAWCicrqh+Zly0czTxlEldnkR6r7mKK3safOYZQVCvHM8A8H42IuyYjNxGfoEPomo/FDlNeBXCiT
-hipaUwM1VFeNjJ170RfdSiIwttaIxW4219WVuxZwWUyeXC/NnSkg0DkorV9DnTv1GjqnqcPgC30z
-c4uGcRtkqM7fIByEt21JsF/LPIwpMj8WKDxwvLeBlGN88LSivktknuH0miZbsADdjh6yvm1BPWym
-nJn2oOqBAi3j5J15Y4PR/EoXErZuAOcnalTudBrqO8Ox4DbWz/kqXeb1yLYPiEHdDmiTMbgz270S
-Tbplchpy+ZRf1vHLLCQXkPwvAUsI0QdNL6/zavgW5dH4K8M6AREfNwQVw+STAuqHcsZdGs0/+onk
-WRMxQQvqOjy6AVpNjeggq6FBdq1MQDfpwya0KvC8oZEwyUBSSUvjdGsCw96tA1iS53sNC264PqSJ
-OgbAcwP2MuKbRmAckCZKKuIvuv2fIOlcNzZS4UzXFKFc+6VsFh8j4wwbWYF+Yq99lx1RN62FedUt
-1gNUKySqGv3YaGbmlxEhU0977HISoR3qBIBiOzHFdtfKZ8kQh9dR/SfYJi9iqrwgjsmfREikqcp4
-/mR2Vr1+YQCNOSeQBX7zZUw15t/CzT+XdW+BxtGfB4NQoYn2uQxpcRRZ3fyIFs8ivMG9hV3VIaxD
-EhzTGw7GjIxJp4ZDt0AzCFxrHLe07GjqnHMRwQGYbbeDSwVyXzX81FrRS4/kzjHZpiAIoDDo4sGc
-3GaTl3gJIAKKL9G6RCmY99Y4nrwBidysHB7gnKC25BUNLCBYxAtHwXqfg6s/CLoP+3alZKJlPqHi
-lJ7A450y0K8o+5AjS/2hXaZ00wGn345xO10LAS8m0R3UyB2Aqfl4VDP2LW1fB/qAvl2rG80neMhf
-GcPdRR0qqcbsXY8NQQ2Rt+w2Hbkbl6yKoWpHdr2GU+h3y23Wc+LRxFXBKN0n5BVOai6OJBjT/eJM
-zIsQMlMNeQ3ODkcQHjZ1I8ZNnTFCYJyKjx74vsGIIYMaOc+aNEysxjS+1xuhviY67x7hk24nMucq
-t1hhKmc19MBASbB4pwVKHH5sOe5n+vzI9GnJ+FTUGhy+huVmrM2rJMIfOMvgGrjEtbAlz8EvabrT
-YKf2G9tbg3RBtTIMity77RYelhzTWAa1L5N0U1dNdYC/tg/1vr0SXvpSavFLxGnfNJxDzOLvIpP7
-PJ/oOFAknBHpqV7XKqNKrCktfIoicgKKa2OXmrO207hhnBo4M8u5As+3Vi3LRIPIsSVqMlHzXGFd
-wrirHz9Eii2F4xgfG3r4vuvn8HqmMwmJN58+ZHaXPdb9gHShLnZahFLk5MRkd1T0u/Mpx0i1PCaD
-SRplzUxbXU8cI8VlcoM1PMXm8q2AmvQTnRRvS9dioAPSY8SN7BNqlqwmD2n97/kI+hV+8Yu+6Pqp
-QL7/mHPqnVc/9eauc9LkmmL1hSYET5Xbj+4EJsYzHkosDA5tyMmVKu3X2qiS1lIf+sgbbiWcz82c
-rWdgxPrsKwNiPzkUQSFSD1iBFRxmntri1ZhuDT2+Q1oLpFVuZhBJIb5lsrvWmEYQcdXNbCxYHYCt
-2qwczG1qkWAlmvGBORMKNhZ4SBBHwscv3gtY7RxxPZ9oKK2H89nrTezT2Aqf3i785d/aC/bKgxI4
-K6/Ywz/bJ0M6IEKQztleQ6URaCMNW9l1z7WiKZjqqAAtkPl4Cr5yt+BQFRtFT6hRn2X9Bbbzk+4m
-gj1MobumGb2jaztAT0/ZEN0DglmQIoJVYuSwSuJRR6JjHO7tAqED6CUkwF0EQJBz8FwjOcL4Ce4u
-frEnZLdkZz/g61D62MaJo2HP07WtpuK4erxRlKxJqUMN1DE9p17KcIfuJLmXpot/irBemO5jjyOL
-FjY3ZVt7ACfXLDBOQIRT8/oycsOrTIjpv2+RMxEwGRTALKcrYF50pLBeiAGrSTSvWmpK1xnDa6DJ
-2sE2SLpw+P6cnAPvKuiJnuhaJZE0vv1Z/9IUQ5OELhsYE2Ypl708pIhrmRhZv0+dFgazscSHtiFP
-im0EMlChBe1qDzpOJYn5TrtK/KWNSPm+qqmbBAx6SX8uKHa2QN7G6/dujReIJKj7CHmKx2S0C99a
-lPrWYw69C/UFrKJM76uhGD56ytjP5iSe334Na7v1skNn645AUwVBByBRf95Lb4Dgjqsx21trEFgb
-BoCrSaFRmmPEaj0kEdH17Uu+7tmjK22szgAgeQWJ95+XNMtOp9xEEgqsg7vL6xl90og/ibx6mtpm
-2AyxNkKhatASjobi8PbV/7KbmRNwAzgLnEdZf1694KWaXal1+xpJIT+jobMtKSjeWeF/ea10mQ1p
-Y+rxlzEVpyn6+eQS+0UA2uoRzvPRZ/qmze0dJIuvc4f5yNvPJf72YKsWu0t/W9DdX1fdb1y1GlVw
-0pKiw4YwbW+wCscPqrOaK0ICrZzRfcLQDsdpne6ZYUenYsrR2pkEGLCoBls6JD+X/PPb97Syfi4W
-1zpHtHHTdC2awBeLC7++JvF0xR7L0m+VkvOvf5LfDGe5CnzzO4L0l5xFGsES3wAHESLE9tdB5J+v
-oIeeZ4dl1u5dcKiNYXh+qYGCqUJwpzpZ80YM9ncrTz8p9H1z3fnUJADHh2S87Y3sZ+eupBTgVe8Y
-+q5T2YvXIHHJkJKlzta2zyOR376M6U5qjpyo3RfojoOyJ3m2a0INNoEcmYZxha7VMaZJ9sXsFEDB
-ik+kxQUtXa16Fs1EY4o8Do9qA653teq52uYdqomI/qTpD7uFw6JP/mKRgnTOldmaDwY5Th/FePRF
-fbrTughOCp0aZ4nibQf4C5Nyqm2oN0CSV0ndokNN3Fxrax34Rx6WeOeiy8eroZW1ju3OB1u66M3V
-2yvkkinLJ1snyXA5TbiWOBZcDEs9MUwdhSFajSHlwixraAjgJTb5WNAXA9CwnWMzoXVQAMccBv38
-mLRWt1ZeY8O4ogajkJNuSRtcjPRe20mdKdGw5s1LRlba4gN4S0sCRVSXTmhUvBvPLkX7z8/gYoph
-mRKMC8zLi2U3dMT5hmSTpBTLINRxfXpqQKCc5rkHzAMfozgi/d4AkIYSo+VI+o7wrd5+la9nrg6A
-fZaXweRed6yLN1mki6kAzNd79CauYTLQtWElwOO137mQ8TrSMDrERx29InyqnctIwxQkRGMnU6if
-0hUEjrYRM8TsGmjdS76AUwPSzeJdu8v11FdAwRATM3rkw3DUjfxRxScE3k/o/GKoWlDv4ST3wvvN
-dtVaM5YU7/S3j43JbN7MacNp0MZ2b7+tv300BngMQCUWB/LV5LikcjXwsgN9hcb9ihJDFbSc8Btt
-yTrR7EMqZOx/rvXSnNF+Qmf5ZS7cdyLW6wDpAItgnghD03qNZsiNvnWUEGqvW9UvE57PltfAxfLG
-2CI58s7VjNcTLMcxwawz9zUFLNLLkxfFEle3DcX8clyNWFH3WMeSKF3htyciSQOXhHrB4BdBEyv6
-gHLUcwWD69aGt7ax9OikXDHf5la9HAYK700GxWRjYbXoayEkjNQcP7z9mV6fo9wxljckxDYR/RJI
-0MjJwcuNreVoM57irep8DcGTXa9TP9HK1v1Bz98ZWv4l4edqrAiMUlbQ5OVOwn3AHavaqPDxpLFZ
-V6ZFIT7hmFpZcO6Kjn5qVBZUtP0VSlCQ5UwalWvPkH67tiuMCrJqSQshZFCEHMyA/rc0xTWtFRHU
-ZLPKpMTEsSDzTdk9Gwv51rknUgoKp5XwHkByJJolkn7tOn6xjD55yKiosG00Y1Q+HQttW8j3uMR/
-ymsD1VGNoZ5CYBpYY6GC2FmT+XDEzHidUOIM8DCN9EnOs40qR0SOmduPtRK2k47LTVAPRPjN1KZp
-q1Q7BsvCMnz7U/41bNhYwQheLrTkSzEL5S5J3CAruY/mLr7Hf4CmAOVLYEgL2DR9TM5AitzEM060
-zelmSz40THrXH3sDXUkbJq0z0yM6x/rCGBmNzvjJolWkpN91xtfzaNNSwgPzUzTXBePuuzjlI7z9
-JK8TWJf4SvIK4kQ3MEj5M943kcUItnHafelwGPeIhq0KM2wJKx5uosYrtp67FF8tN3R8E1rhO2em
-9Tr+wuJyIKLAs9aFuIRQeO6UoSNTogKdM0WrjGa6h63bIQhBJ9xErepzqWSxTcw4u+qRMPGBMNNV
-0OhjJ+ufZIb+Va87SMAuLFPOLiZKDgMge7a+6aKHY1U9ay1F53n+QGsDcW461ROgzjBunqVapwGS
-JntKU3KvF2uPb1rbuYtKHpp6tD7rOfxM3Ts2A6BPaS8yQISIrn3kvfAPQ49c039ZIIL3pQvAJnMY
-N779kf6SWbgG2TcCv57FqWyvb/G3rAtgOOKg0ED3NUOK84CgsNaRsGAipBK24dLlsMey5QqRSexA
-EjIG9LQYHigobYxhFr0HONXAnOS0fsjX+FbbT2iTJMzF1deSiT7Qd2YRjl7M+7fv/nXccw2bjIJ9
-r1OmXtZIPf7KbUHjBcsIay9C5otrqMhm2pHnblQeFu9EvVfJs8OaIj+lKEM6iIN9vaXf3lcscH5t
-MipBWttwwVUHdn2d3J9nMe358/YMheCwrkgOQCPImzHn7Gp3A5+i3zX4rewkYBZAvsSct9/H5UF5
-vjlJXst+W1FD6///7ebs2U1TDVDzPonBEXQN9wDpgCkA3ylf38p/fbl1i4NUMgXFxKtjJ1PA7VEz
-3I9yXbVOcZw1EiqrZe1QO75XEbuXFYJDjCOigOgEyCaoHP98vBgKjL1A1d7HcSxR0xwsYiEiWJPl
-BYyaPESwMzISzFY4M0hD4YeNyIQKrbyzKsv5MlqFd58OiP2a/YfWdvH2tDt7Y43AdUf2qE93pb3J
-XVXuIZvZG9WVybE0Uw+0CpJNydKVQZvwy5OhWfXZtIeEdvhV2pciqFKUl7XKQOPfddWBGsaKt1qV
-jL6FkOFWh6KMNNoIqjwDGxzVaDQakXkNlkNjopJ9aGfd2q52b3vHMHmHokmOdq2lPhYH0YeSOjlY
-Bm3w89LFgBJlUvTJtJNY0XZirPsHPPYMGFdhimoylRrUW1wpyejoCDa01RPm1H6ZFeY1AFUJDizz
-Ut8u6jIolZVc92kzwIazkMKFMWTuTad2D17CPWgqjOjvflSd9SGKE8PX6A7fgOpfaP8s4ls/4jnd
-OZl8Z6OZl4k6JqokYVh8Ua4Cw7v0vPKiuvG0nFMeBIULLZc9ZuagRqD6MNkml0qNQv+g6rrch9Bi
-IQXO1s5Q6wfENtZ3mw6ST4rYzMZpnBSHnfhHbqRm4AI93HAyIL3NAtrNmov8OQHSt9C/DBgiWNu1
-KxG45qJBux2to7f++rTqPnSx8SQd0CYj7iI7T/bmrm8KlA/S1n2n4XR5eAH7Y0Oxg8ljCDT6xVIn
-ciI3VGcuhq4L3MZ5Q4vond17GTzPl3BAGEpPt4XU19bfb8GCKkzSCFiVTxFURyuD9uuA3YSfqQUw
-CKJ9vBvtvaroMingosROi+SGeoKwcRGhIrx9UjtunKCuHPgRkdds0byrGbtlMNRMRnqaKdurqtHD
-rYXszzttLXGZ22OXuCbIqBvSWTXpuPz50HNd4J1bVGi22goV3AnSCTLxiw8FnwuG0rtSXoerojCe
-aDtkexirw6e3o+YZAfd7v+d8D7TI0SpzAf2uKjW/v3i2TeOsipJBameaP8x1eyhg5FGI67iDwBbx
-tgjwtt8nfQnveJHWXTWBOsU6x/2Iq/Dix4OD5xiSGEFfLJhYtwavEn6N38Xo/mdxA7tmbuHZODxO
-hzBoXVv20VFj/dlAt7pcDaGSPXK/96YTwbcbtPyd5EsaPMMfz0gCC6PSNk2TxjVn85/POCcd0m8c
-oUHPrjqO8A0DXUXQaNBUuD4/BHTB/F4fI2e1IBdbBo8h3EB9gU0IdmQhBfPR6mu2ZhxGBy+KXTi4
-qca+1ltUHIwXBRbjoA02EDIX24kkMh9gNJs71SQDFJi4PeS1je6EXNy9PTkDU23YGjJNQXNggJBD
-WgHhU60z9lILCmUsfhPKTaRiRFybur2b+MlAIXyziePocdakhlHSmN/Pi8KSAS14zFavJWRzVOAx
-iIvqeLg1Eqd71lDHeHvJmK8Odl4nTXgwlQ6tYPOy1lKeFyYLdVMAX5/eSa81Wycdjkk0fiwKK8SH
-yBLB0gkMNuwZlx06XtsUa4FD5iIgjpQbwsTMl7e5xzZLyyG+qbNI/16vEr764i03/Bb7OKCOyUTY
-Kg80kvoNL93eZ/qwig96N1R5+hYiTshApbWC2oDyWKA3t9Xs6nOfz32AtchTQUPaz5bmvczGehWt
-LEHNzY41JRpKtEv/XFBIFM027RSJbDOHN74i5jcDo7yUQ4sl0PausesrjNi7cdICUys0gDh1jOZA
-5x5mK1GoGYX9psBr5xOaccA7ErZdtkBK27gyRSV2VCxMO9L8BnCcrzeskbmD8CYSN0XAxRVoMqzy
-HTHOIob1cRzMZ0sT+Wb2nI9hnPyk1kFSkvnUTdFpziECtHEblYl735FP7rDaqHfekFOOl/CQClQ/
-9za9gb3FyC9gMMlCH7jk5OXmOz2cv60dJhcWTW9i36ukcEYjiRkla2fI5QtsA/d+3StNDwlwFNHw
-ThvXeXVyWXwiE4QanVzDcy6tsoueXpXed0RY4FQ+XnreM8Cy+EYtpdjqSzEFph6md1BN4xvDbQh4
-DemXGHnp01CvjH3UjZgmfhm88DhG9m24IJYuQPlM9vUc4WpWz+zrIQXyyt/dKnJCX/NYl03K8WGM
-7GbS9peqrZcHowLMJ+pl+IWdV3uAcy6YHE7lMW11e5dFZhTEQOI/jYjRPzLwD32BUgGWYMmCri04
-DeiGtLjspd5FGqUNYC7vionsQwc/5uBlM5EDwvNtYZfIL8OuuB11wnKrsixACyf0mZiuSqjF8EnO
-rK124JjR4sEtttLAwgaTA3Zhp6UYJ1S6RW9N/2aGq1TuIBhnx3GlBd6qZNEOkRbUvMhN7Ah7F9ML
-IgNlQyzvZAV/WS0sEnoxKx59PSX/3GetbedZEYGKdRtAOZg/pUGjJIdThQyAI9kQb4e219djqggi
-nRSLQl1eVul2VoIMhmQa5Gi7M99mNwCb867AHLmHeEEP9e3rideJJWUbWohUvMDU0ZJd7+i3vMcF
-3gb1PbICcEwmVGCQoUK49jEpGESVix7fTKhOY21io77cN4cGhjaiK3hN4J4rcFEpGQXgtoPpFX/y
-eg4qfeBT6xWuQZMjur3CQxUEZtU8YgQJMqZcD3f5P8yd2XLc2Jl1X6VfABWYh4iOvsgEcmQOZHLU
-DYKkRMzDAQ7Gp+8F2r9dVf7b3b7paNtRDlmyRCWBM+xv77UhA0ERzq9WWb1PyzIS0R6L45qHztby
-d/yLIkhtXKFplSh+hDb5WLlsdrPtnvJ+KQ5ojS9RwcYh3w+EO3+HgyQCRZXjZnLD+YiupQcArxBW
-quaxnXnWtaUK8HtrrTOOWo0bxa84yozAKzDca5h88YjwNtGM7W5jHsFjBbwVJqMpt5W97KYF9OWo
-5lySJewzFIDOK3V5V79DxE3RTR/lzPoGzZapkOARzwAr73DFs/dkLLttVotnet2UDZ8bnakNX1Dt
-OCAlSvZ6T4mZAkwCetn3z+Y87wnI2k3jLFzgCmeI3+nk90esBatp2XXTWG/3wDYcXhaWi0QbOA/I
-ceZDHNt9LFX3pAkG+F3ODz0ZubuWJtpTGfNL1IgTRBl60m8rzN94vgnzR21zTiiKxXcWVuwL/DUV
-S0vPvTLPft1rbdBNlb0lo+TtSaHz2dG6uM1n+8menE9Q6do6y019z9vZ35GpMQJWMJ5ia3K3vcg5
-siQco79fd8/m48Npyp8AvMKHHJOu6UtkiO4Zkks7347vp/1/Lfe5/EGfJPKbBKR0+x///tc/2H+X
-73/4QVBKNuD77lczPfxqu1z+vzL75Vf+T3/y3359/y7/TaRTU/m3vdhL/kmmk9q+98/4Pf+3a/P+
-81cb/z7J+fff4K9RTuc3k9Alcj9t7ZqHxvy3KKf2GzkgMIqWpjkkmqy/QyO939hPbX61TlrTZLzz
-tySnboOaVKGt8tuhxJBu/FeSnFwsWI5+f5LGAoG/nMQoQTDXQvz443IloqKekgWfA7wxgo42t9nF
-aWGa+0bYSZLsdMSkO1grNbUkdRPLVUKDjqBVh2psdDHqmjS92c9xadknTSUhs+rHhH/iKUne5gTo
-C3AoEjQBDQnRYa5sgi5Wo6sBep4RnWGNFclOMaf6zc4pQFzgYSXMRQhZ3KOjonUD8p0OjQ4sqZp0
-FpRt3QfqNOjY3FyIfjPsP3AdJhogR2OZ+6UeufN6HrzhHkBfmuzGCo1ircOoJjw9pkAIsIXhPO4J
-WlwNXcAlMeua6MdkaQAQVcO855xHyUwmegA0WjrUNEYrok04PhTqV5yo1YxdwuVNNwHYPNCtZZJH
-C4voVZDfwlPihtOnYSvyShlBuDguy27twlXoIGKY/Ts0gnFvuVaBrlXbyRu+j5bOVZONe6hUlTmB
-DUIL2Mde02AkUhAB2gjzqm6vDMIKj9LWp1fGRxR1lLMeSibIFeQb1+G6YMwN3bYQtGBA1q1jnPRC
-G060hChHo8ixJM5mMp/B43TaTWePoifInES0ofnU8F56WYr9JOJWC3JPxZMwU1QgttOo0WKzAlbe
-JHvRtpZ6cZfPJQvEbLTeJiUH4QJanLiqSLZ2+Cd1/crskyzl1C8fVrwHigr3kB5vSt6keSQ8K3Zu
-5hbTRSNEFK0LJ+41uCZgSQnT0PiYDjQ6A/UVZNzV8QF+2lcK2SwoM2xUA+vcnnbEnmKLUF81QtPJ
-6rTTup/CmX5GB+COAdRjmk25STJtwj2IQR0Ogg3lzPA654awuh9qRSPZqITeQcm7IjDT8MbRKjob
-ef+i1wY3G5spKM8Hhj7rp1YU+7Jv9sMYlVslVwEptZ6+XjzMgYGAd4p0gzJMHpuHwqgVUAEAI1ID
-HFwuIIgTNlqi0PWhszEbRIpJGSUxyTl0T1xQ2pNrwkEBtC/u8nhw+K6a8U+zb/Ota5bFSyKt8twb
-mQXEcAlRedWEfT6m8q5vowvMJScwwD4+OI1ZnZmjMp/PrDmYmbAthjKV/uB8vGWUK64mmUX7qRvo
-1XCc5lCDCVrBxQt9Z6Rx1KxSUtupcROVlnFgigjjUlexscPchF4BFA0/FR3LVPglmuxOgvmwwMeO
-0pJOVvcIhOHa1w3OFnUeVh35Ek7PsbyEcd5ySpkkZxUcXVaRYq2CmyaaNc3GD9xSc0ycyg2gyC+Y
-SNcMfwV9fsRTcinlukxbKnUkb1nkKhj1+Blm21lJwYBXsxgZj2bP8z8VysqioTTX4q1GuzNdHbP6
-q0mBtTdVfaxth6bTASqu6lHq02Tjl1PKY8cAdS0Ghe98bRRreGyzgjGY7qq8k9gbLJLcBigII+Hy
-MQMavUtjxSEURisCF/1xPTggZfPJml8Vvu5NmoYz9zJTbA0jHU5unOEId5Xhhr/4ZsswPeRW4ZDJ
-yHtuh40TuOZoBpkxlvcNfWcBjRbRilHwfMa3BEtzKkYL1mhoEOVT+s63U90AsgjGyJ9yoVBEHurT
-c5JC8YCdO5w9j5pQO3OywAMaRdFm81ULw/DVzhWH0Q6NTawNXsClnibFrC+uFshREnetfhhxhn5U
-dVluKKEDmhENVnk1JUy9vFcRS/WQlVBi5QmsSbgvg6dHP+usx4r8u131+pdd6Pchfvt7iPeH3QkI
-wuLoUJkBL9eGP+mUdCSLOI3VeO/qbS/9UBsK25dJNV1aMiZPQyVN1riKZMFgCIh0ZdOXj6VQJtST
-XPvZRcJL71BZNdA2ErK9otsEE5rlu495X2ObGtSBnsvYCblAM+Cl5a90tXhvUbE1XEby+xAXM6qn
-WtvIHiZSSEaOvGv31rFOZvcEbT27xi71z6aoQ1rqqByU2LJl+4EvejmYxfZL1kKd78sMlqbjkFde
-qYLffQVnbTh5YOT2EGCnbcf6fpwjULt5TPyE2pdxx+TdO3gT4rmrc7YzchJkyAvy2YPj5dsD9Mqm
-Q0jnKJs3a8k5hCG0lWLqZt+SboUSj5VxbQ+AGXeu3VBBx9WP6ygNDTqllSPRu12jTlZxB7jUDbzG
-jlZM3JRfOLymQ9vSvpVHFWTMxlSVhwz+TjBW0roUU2tcQe9GNxLfwUyJNe3KtQVpeV4isqlWXQqo
-XWsXj/kFi6wFhAaUV2+4AoyeYDguy3YVqQxMazWWdI64t9hyacMlIZpORxpt3yupbalcxFeOJn+u
-04++5xataO4dVBhtbSF0+kyk2odYhbEZV3xwnDfWZafiq0JZV3agfpJ3jut4uHMmGZ3TH6RSPuhD
-l5zjsIgxfxv2tU/inYM4u2dboSdH2vlz49QVHFA08v3sdNw9aP3sA8DGC+G0KV9p/Gh9Va8/RliW
-66aBlWzNRHA1ns2LcIR2SyLr08Gq8FDFvHm4WLqFwddSTOjGrQLDn5rSvdtpJu3BfeQBvJ3M+hU9
-GI3MzRzPBC/WW+d6rnvwgKNljS/ePEKh8wq1fp/w6bzJkFvWzQoVveTrc8S0thlrvGn0t5wpxjLO
-SVzaH0MaUtNV90wTIstQPrjqtdjc7X4AmC+trQdnh6GOQ2CzSO0bjZny08B9saLvsLjp5djFgcOA
-dmvlLiXD1EydHNqJT13VeT2z2hJkLvDDB9WU5ilPWW+EGNjn4Yz5tjkmgW0r7qNA6ViZiWG/c6oF
-7I21gKZUqGv5IRkWxKpFqgYKcq5kD0MpBpg1bm3Ar2syypmyfPHGgWYa2oDFrhYbAHC0ObNi4Zxs
-5m6BXE3RuZAR1Ef2RrZ9Bxs7E2TxAMeqeFn05F9dZXc7jl6UxE8GTRRGLUCqkZcBsOp25a6evJnV
-j3KaMRiY2T/bFpmNbMqMc2UW/UOUet5r13JzTgoTvaQJo4dZyTjyGGpT3vgyskdtnvnuioStaTZz
-9WC7Q3+kcsciIO62zl2c5T1VYp4AJRfSQa03+ttEUuqA8EJ6ghqV9C2XifM6hcNXX3eKuta0vt9p
-arnRQS2zYlmptc2yafyBN2uBr4/YolYtccV3sq39Tatz8zUcHbvmOwokcxW19O2sEgJsO5Qh48ec
-kSNmU1LebJmkD4kWeu91K8ZHjS6fuxTRHUBpScnPcgq3diaY5DxAgwZKptEtt0mM2f7sbJNuHqWT
-6Ffo5WNgdVnHvlohGq/NUU4/VBfuJA47soBlmIIM08swOypmKk5m5wy+Cmb0p1o05A5U2bov3Ngb
-iXFPV4wjvOqIm4auRtQ2DFOI7XJMinWtNExGJZvFG/pRcbMGN9sPIdEzM8KzSA7HRAQzwxIwhcdJ
-bDX0Xntg0QP0ok79mPtVKAogSOOg/5BOPVFWbg7xx5TCylsXYd6faiiyYNJCQjR55rTz0eWMrWp1
-Fh0nsE/1BtcJXUUxXv8wsbtDnOrUFzOXmp+Jjel1oEkNL2g0Kk9w9OOrtEv3oxo1eSPRh8i4PJJc
-nrIx5yGIeAmp80J8dAXPyLpBm7ojMKPtE7LK3H/GYqD0WUZFDm7PjK5EB+ZHqSbKBUAui72jxljm
-xjlXvmRnlsTJCh1Catuq1nn2EkQ8hpr9SRB0e5tjw/hAZpzI6KW6+AXMK9trwg6B8zNofi1HlOtN
-hkcV3oppfukJrdEkBHIR0ENE0F4kzkgtfZ/B8U8z8azhdgT7WY5FgJEEWB6bKLSwzAV4KxVI9DSz
-zdRdN6l3Qaz0Hvh8yvMgNU6ddtu8FQIWmhsaZekzj9OhuYFCeStkBfC8cGXXrEMlsQItGsZ9YyrD
-1ihYAfzUQj5Zp5hVolVaj9WF0Hdy6QB50ipj0Bk+mJGxa8rEain4znsGu2km9XWc0O3pl430ngmN
-UZFuVc6TpmjTB/cYyqPTMTHNlSgnG3ZymDTnZhonhDZJBmtqhlddVW8gxMQjOEaRBB3enwtkB7W6
-9tkY7wCFWu9Efx1+asrlOYn0cS+sIQuwfrevnTDarzFS3cIHfOzeKpXU1mym0fM05OxEWe8AkW3o
-mlnPjhsfI8Jp2YaDsHKKKGS2Nl2tlPsYhYmRgRE/Nb2tH2gTk80hg0ORbr1OAYUbNe5Al2fcXByX
-WEMeixlmQTGuSAK0e8fu3TewOuOt4bg1+hrx4z1XJTvaaKOR7/HgF81Giqnw546nk+zjVDkXoTF/
-8YkRqGu6r6atKgbjndrcZg+RoDqrWjauBs+ZiBk15uBxnwRoFsSIk9HKE8p4VZqhgMZuDZ8O7ZY/
-ozqnPLVL3aIheNgvJ1bWiXeus1DcuMI7wPds4felAsp3tAaHY1E6PUdDmmt08SoeVRFenXKXrmNY
-H0WfcfwVvNjTOupnw1ccV+zTuZOPppWnGkyIEWVbzY2S6kvS/CssIOLkKua4ZYi35Me78bWuaJy4
-FPQ48Aw3y7pZJ+pk+KznBtgGRlbXmulYH9D1RIXVKMBZl6pTzXAvOBVhhKGYAPc2tYdq7s2rWsjo
-c25m49i6bqYGxExmQoZFlEV+weTxiO9KqCtjCKfpMOS9Eu2B3jRxQHZ0+lF7HNvULi2eRuGJX1Y2
-uHtV8coXy8riZ6/su2nV6+qwHdSlAVlDUAXj1+2nMnbXM6nLL2qqoAyG2CYJvxZlPq4FvRP+pIUt
-VkNL2bIlCZ8ZA/c4lctYoTtc82GwZxjEHOvTxCu/5Ppq63H2NJx/OpfIyLMPDr6GzZQzSAIJMt96
-SJ3nHHXG1xVgsV7YQmFPxrR6aG0v/Kzm+rsbTdxyFdCwH7Vtt+kqqXBflEbyMCNKMSiP8xfTU/pz
-npnjY1U7JX6wmRgUn7V6AcLv+l5Zh6c2V61Dzwv/OEmO/o2ST7vIGSFMJWP5VYGevlh6Yz3y2HMS
-Ts2Dhqq9H7VQvkayN4+Frc1QNDUcpJbR7XHnw2GQRrnVM7Gin/HGmRzwtDOKI6AF/D+dUe0yO7Hf
-VL5zH6GRRoQ0VGvTJ2bjh7OW3dVdmVxbZ1ojU5krfMzUvdF3kQC80KMv14yfQkx/O9OqgwLANi47
-b1hX3DODybCaO1gEb5SxkJLP2mHrxV4TMDIitW/jN0I2f6GowUNeroe91SafmsNkALUC2FoDORjP
-O+cBvTssLZQ7GsLyY+imus8UMFnTFZj/wA1cnmZTwKOnEZYvMm93GFjkjhmu4yvSTTf8fdqNk5iA
-++FtVWye//wa9w+uCJXuedzwGE2o89Q0+0/DVYXltwQb7+z1PtE5di6nNNeoonM9lOawtniEpjVO
-BG1VdwYYnqlz9oDl6Iz9b76Qfxh04zO3sXct2ir/Zfy5Ta3pQgKlmjPuJ9r70r6VH0jjA2yg3vTa
-i+uW2lLySVw+AIQyPPRTxf0P4oRkPEtvQhCb/fMw6hY6GTUv0aagEQzIbWwV4h2So0PzdatYL4IU
-7pWhOp+8beSvrgAebnwLcsXQax9OOdJAq3NrfEH+UMCBSOOm94Py2cQhB+/OjZ4c1egcWCdR8ioT
-YwnD9eYJtieiAMCFF7eJeFCSeLwXlZ1CcSH6E0yzmh1BDzQ+lbQGBwkjugzEbtcSu9KD4xTTEW+x
-ceryiO2wtPKNMeavulGp91KPDs6guWt9ES2dRb6sv5VMkiGskAp+7zhAcrUe6m/ZM/qWQDF7qV+0
-YSAH6ABKf4Llc6+jlTUPVBtrLxgJhVgJQDTIX8uBnabJDr5Y5MJWZ4DyBKeH5zT/Pt1r3yd97/vU
-P37fAJI+mz4tikYDbqnuJf2+J2iyMnYh0YCVJCupYyVbrhOoSfY7FgaYxZnn7pVQf2JA0oEnbiJc
-8Sih1B5YKyX1aFpXljsLXgSuL+5ykymWOw0he3643HPCeJRxQMlacUurCXaHNnAjWu5G7nJLiuMh
-8Zu6gA0roJ6niyK6ZjVRPvLvS9a43LfS5eblLXcwfbmNTQrytoBSMa3Rcriu1V6szzfbarM3S8/r
-d8vB5+qX8IjGF2JBfEhwaa2znLlfbgfTRgtHSK9fm7C2y59KbAMMj60u+pKwacX1n78m+j/EMpBb
-IBYSD9SZT1Cd9SfvVldScg2zotsnnLVOtTJGwGsS4beNke1LCh/2wm2KgerBKgzGprq4eRXegcUn
-s6rYAwlYQLGoabMS+SgA5dJ4lg0P3Hqq0jfRSV8ZWdf9KkoMcTMHMA+1nppogHR+2M54wWh4GchK
-gxIYtP5OI1C3FHeM4Se+T2MDWNLe27HI7iGtjUj6dnowbO1WGzFWxvAKoo5wdhhhyDAoGlejG++4
-cSYlfOJiRjybAveeFU+1FMJOc8eWLVx7FyfCgrlhc0Bl71B3fe3kV9tO1atRaXj5KtOiSsSxy20E
-dieIxk6JVpVRDWhvMLHOLC7i6jYtQBZOMtK30JaHFeuqR4XRmNMhK1RqRDoNogMX8Lr86XQtto3M
-7ThIWvKqU9n6PFM56ldG2i/eotz3SKcWZLWd8C1mqvA2WhOdsENRUREss3ibENOnoyI0HWYWqdyk
-zhTtStfilTPtwebv18A2mAraIYvQ89i+OjXcchMu6QZrvWkxemIyXDld7+1stQnvQzjCHwXcH3yX
-URLQL688jCgjKAWJSyWW1R/yFGeEDpj7jLQ481Ry6MxpqztiklV+0B1dB/x2kvmwWz5kSerq6Ly1
-eFKnkDeAmOmqHySaGZOceGN3HVvabPWbiaTZW69ryaMSt/qzSDE/kr9VaePoBUvTOKT3M20cPihI
-42ixSq1Nx5FBxayBNAgAEyfW0qdSbQnEZLGH6514qXlIDJWug0La4R0RKXVrO7HKe+2lxl1dVDfP
-G8Db5AgU9vdOhLnLvLeVJjoN85gXyDtU0KxSIrPutcxCYIH1MkTSvudJmhy7eR1+z5nUZeTUoOrO
-zLSXSVTY5kylvGRKASyV+of2PbXymF/p35OsFqvLhgG085x/T7pKXVGsFa7eBeHA6l36rG71W4S6
-l+xo89GiM8FkTQ2Wfeyn2Q1jw+1bdwUHAaZt6TLQXtXNyD+5GRj2CWpds29oGAyGwdL2uKok52ph
-crnuvBmpCTZVlu5S126ZfyNgWH6TaNXR6AzOE+Jb0x0XeTeztFfh1lh7ZfQIKOw1aZYXRE+ZDDnJ
-QYQzDv7ecza1Rv8YXzWYFyalxzFmRNTSKLSrs6l9/+cLFQPSP84uQQC6BJNMEyIuxrVltvk7q4WK
-Mp8hiTp7LwIe4V1E1tzV/f33H/IvzbhPyWdTtdWX/J5Q/21i/T2F/vuPHquC//z5l/wfnXFjfcaZ
-8l/PuE/JXDXvxZ8n23/5v/0NUmyScCbti/fL4ZvzlzLEhVC8uKt59cgm6hhJ/j7XNn8zDWw//AuT
-jOZYbCx/JRTr2m8ejk7Mwlh1+P/a9r8y1/6HHcyCpoozlPQGI22Lm+kfH41Ra2foUvQAlL1JxWxW
-1tvBEsW2SbWzgeVmn4Q97wtt2lbU/dLpSDhFFkrV7z6y/88Aw/sO8/1+gLF8HczwidcSiDaRzv74
-dRhepFBoE1LGmLX5TjraxjQy8Mhru8N+dWQCKuxrCKqrS1D/JgTilR6Fp5QzyEo0xmMnQOrpu5l9
-ITkbank0UuKRCY3UXJ/IZNnOsdao7hnwkZqWvJ+6iaRKS+cuoCBmPU9DywAErO4YlkFatNcxGy9D
-BtLCQI3CJBy2iKNFdFHSmkI0K3vsEqMJWiN6N4Gt+yrqt2+xLtbw4BrEf/4gv3Mxw7NMvbZt/WhM
-GFrDCY6lcaVgZ0GbUjPEB9syCXmlBC1bRYDfNwwQV1Tv3PVlAcM+jtaTfqqUamMLA6Lji5LN6Kvp
-DUrwAWrkTjecQ8m8mHgCI0FxG0frDU6ts5rG7IwHu6Nto7fWVNi5O8NKXsianekfPNij9auKk52r
-/lBa9QnlmpmWc2qs5sEOta1OtQaqhz/ouljpDl8GcJX11GXBAiKs8v5nImho72ZDI89gf8HaD/et
-paPNzAZdcRnWh9GZj5wRTopL5AriSr4aNJ3zvX0r8oju3Ye2dNZkDmxi0sNNjNEVbxq6IWrVo+Fl
-IIumAICPtAdKToynAgjGSlVMNLGbKMevvnD3Y6u+zRAxJuJbq3ioX6Mh2UxA63VhWDjqkRBCmoUc
-74nHa5VZcEq5I+CLLzhj98Gk9udICV/Dej5Sc/GAUxtXttM9UZ/oa9rPqijOrdofu35EVu8ivxqZ
-0zINwHWsl+ss5NwxSu6Ocq2bGJlVrgkOj6aI7SdGZOoKgPPPCv0bnHbhV21aMKomdJnKT1UCsQ/V
-EPbvdED8DJC1ueHFL3R8P5rFi9M08yUl4fTSz8Wxzcz7cOz7rTstupEdDXtTt33iekcAmb4typ2M
-s1e7C39lSnWa5kttPbVmQdaSBmnwqOo9OymHzmHeU3fwYmrlsDT8+X0aX+fQuetH4cM42fSWcTGn
-+8atTyRO120Ts8+aU3XHvW/XdZSfdzZiLR03QZRK9lq8zhKZhAwpJYxufO0j7Y4mFETbfVsa5Rr8
-9Irl4JosrFcI3y81+OQ5sz+osQnSoWRKqGjNSXjaUvGV5Rj2jGAasYa5kFxzdyOyKyP/9VBr90VB
-F0plbnJ1fkYg3PV6vqJKdFgRAH1REk45Sr7l0XB8FazN3qg6kymeSqtUb5+rTjvEOr1++vyU9Lrl
-i855Q/l11hniKaE/gK0cMorx4ujtFljRupxd59iXQ4Cn/NPuzasWoqWZ1Ip6Kp0hgvFe4tFPl3k/
-ykzsk876WWXaPsXwSooICJ5eFZssL3dWqQ53zJ4xmjqE+sCsPSw+LyoH1UsE7yYotWtjz2u1Vfnk
-GcpFqrJ36+REi+/gM4LGXtv0G3NigKnY1tXi9FnkKe4EKumwGW17fDVUdcQainb9UVmeTy3Dc4F2
-a/M/+HqabXIs1v40VjgLmydKOi9hKd+6qaiXXs4YL6D7PA/TzRkYR40ejD95rKJw1RfNI3raZTbE
-m8ytH7rUUaXCO3Xq3sSUvWSTU2xlzd8DNsWk0MfTM+Z0Ev1hMpUHz+XjKTBUIjgdEN6TdQc1cSWg
-vmGgbdKd4w77gVG5rhvbuam/jKzY0lb17kbkFplnoLTG+kkwdF6Voh7XmnB/4c5/Hi2MgsgzAVPV
-jTAWZpMJVRYjS7ZqtXLnzt673gGcEq3H8yfVbW5jW9BT5Unnxr8AZQPesLOctBfhlUR4icGYRVeu
-1aJ9TzOHFwMHSiyHN/zPV1iBj8rg3qm9PM+62q9arg/bFqyiXkX7OTJ/YblkXN2AoERJu5v5WJUw
-PHEu3GAyovGoQsufFgexopjuOm6IrzdjSIVVduTV20v8FwFDmWtTY7ia4iiDvqCcTNUqAYolP/Fj
-bNs5f4AmC6RUie5bOiyFw/PQuHySWdDYzqnzKG2bzcPQ4hxqDnYs1xnws12FNYEbxcG23jojewqL
-Nkhks0U+WuGiXYuKRUitqFWMw23d2H5d/Yjb8lx4zkvfaPsx93yZm8ehlbuhr5FKS1/DQ8/k0d6r
-yYj9K5WrzLmJcPChNe6m5Cwq+TKh1g9DvoN4Cd9Xe8WueNEHGodmL1o53jaRIXjINtzNSryYzptH
-O5TvTcYdIjbH7GA3L67X+FaOugoAufT03ZB3d5pzN6Jd4xBKQNU198psnKaRlase7ZWX8sorlnO1
-xvhXPR2j3gkqR73E41fRz2cibvhN8LqrxhcuU0ZyXerT0Xnk/Ab+LPmi/+hnHJkXw5Znw252Sykm
-FrpA7eJoZTXeq5sCcuy+JG5T6l6vM3fM1mrOlhh5CatXXpFnMVkHJ//Ru9Dt+vJHREaQ9p+7Tu0u
-Dm5XA2DKVg/jE/mXF3CzuFgqJKXx3IG/neriIqziRxEpuT8p5ofnCMqldVqHphO3zIJuY2Odetqu
-MFpyA917N3evYECDHNcGET2U9PKD/pJjrAAADFflqBOsqKyVDX63hRxU5LQzpwx/kpteHAwWBSpl
-KI6tOwJNlGSasqOJr9gOxmlO3f2g5xfVS371bo9nKkqYEbB/VqjoIyaXXEBDVk/QMZk8euIuMrN7
-qqtBY9oPXYEGhEMtKeRbfCrzO719SsEDGELZ1G2KT6HdYRquVkZPjjlxUJ1mPShj/lrplXRV2Tnb
-fBx2DCV/Auc4xglDSMEH2Oh3ZkHZnD3me48BU9TmR3MkRunYz83YfHiiCwNpmgXQ2xismYKVKpPz
-elyGBBQM3A/o9Gs7bkG7qSoHm4oxBe14a5C+h4zaJ4ZgYEBM61rH9hsDlU897F5oOtgCRCpWjtk8
-N1m9q4b0OXVo8rKoodT7bTRymJkfe4bmHQsvYOy1YRUPogZPE7bbSbMCp6cuKTr1gwUiPB7vUD6p
-YaBldvjK42INNkEKKIikY0OZXFImssnk27mzHh/GOd5ULbyv8iIYh/sKOXrGhjH7R4L3vHvo2Ir8
-iZtqOmxn7yly9JdoUB+STmU9cLcJt9Ek26KD77rEvM5EGuumuxvV4r7XroXBAwScdE5+KGpMM5GW
-UYiNOSD9GAa5swf9joLmCITneBi9FkCcsL+88jnm3Zyq6ECABZRmRaUjFwlcBwkVlNoUrXL30Ybd
-4ZryPYFKqKpe51uhitzA+aFTnJdMMlCcxLOYI2jQFL7qR4A0QEhZskyOpCMV0qKwb1rx2FtBVFGX
-vu7aTMB4dmyA2UXxFGGEW5e0iB88ks+dw45MNm0+OLCVTrVrQwu1KCouoQfsmYA3nCEbT74ycKye
-hZwpGkysDnKanL5KiXLhpVjXm8zof/b0MwYwQ9StZVGitprtECNHh8DiWmOAIVf9tMs8vneNwj6q
-IrJoBs3sYkeLYfZckSgNcq3wHpCX+SQVGf8oOA3vcjLACJ942wMJa/EAgUfv1lhz4oDBGy9snuy1
-RZzCnaj+4o90PwmizB8M3NRdYU0SMGSq3Sq7MTaaE8mLG4PQUcu0OKqK09y473E+5mA2rvqmbO9F
-kRmPLl/xWvEEe0saD3tVa+tj1ZtMsBWGX04TscfNyuiHk+buI3wmDLeAbqB/1eJUVmkUsNcweGas
-vlcgjJ700gkPpKzag4dbCCS0wtVrbDw+d1SmkyQ+vi716VS5OszyaFLTG7Ew51ltVBTzqmRuhMy0
-iWhSv5jjXL1RJOGd0Y7EExcd3h+XeuwPN7W7VyU3rAHrZpxezF5aj5aXxg+eoU737eDVZ21AbO/N
-dLw0lRcfJ/O5x83KCK/ZerMcH0KGfk+KaU79qkwm/c3CW7gZKfoCXjfm903vdJCKZ+duYsP8EVuJ
-syuqziWyNtKG28zltcsHebUAhV/yTkv3RQK5H1v6ksxbKmcrt9vgmmVkyrl+ZRs1foR+xlEQ6tq6
-MtOCaVVUb4vlgo23LYHMHmHEzfKBYAgjkReD8dp6ZHn6kVq5fq7HzsBM4mhH/Jh4lTAWE5hLrhVV
-jnG3ThOcVL3MpwtDZ3bSupj6W8uTOVHN2U7Ftqq00u/E/MlMF+F1aDvoFmH/GCr2k1vOF1tkb3ay
-TNqKfQzJwpy7nGUfc7k9HkWSBsxml3o1a41ZIfJNxcO+yP6rOq/04e37ic5q/Fg/bepUDQqmTUgK
-eIfWZIc3EtIMbN+BjcG0RvR7ykjPbmSq2zJsXka9eqSHcp+o7jk3O9/U5nWcGnzF3bbPyF41z5om
-vaBW2leio/FqihJOlIX9n+ydyXLcSNalX+W33kPmcAAOYNG9iDkYQTI4k9rASA1wzPP49P1BqbRU
-5l9VXbnrtq5VLpiURIYP1+895zuPvd0/BYZ5W05ozOg4riKdnKeRZHhvwoUY9sfSrOyNY8j0kOWL
-e3qWt5OHXkTa6bqI861faZraQwMhgKK8iaJVJ+1dX7e7vDHkptw23QsiuhWJkCdfe4h8vV2Y5t/L
-vHn6180O64d5649mB0Zyh4kO6C0FaQu/lf+XpgtzMiomRw0Hlb7wzI9O89iNt+PABBgr43QlVF7d
-jEU433E+6fshUs6jCb71tg4qNawalfevHlLUD/fHVkmWXUMasX/jLDtJL3sqWXYXU4TqZP7Yccve
-K+YweRisnAZKwdbslj3qLbsVTM18lS47OPixmcfQasiBSYyrMGCvT8uu95b9D3U83GbZXF1nfuPv
-4cUigSK3yTvGQTJtcrOGfU8jcsecMESSzylDIsJwDANOHtEyqKzswXp0yQu+q8yG+jzUun0QcdE8
-iKLJTnBGEFnPNWn1M68xfznpZIAhDPKT4NfFOegsJ6IRFuY3uZyS9dRGR7LsVn5Z6S1DLQ5TEv0K
-7s4QOeOPw5ZIm+EwJZ7+nJfUGaWY/Hs7TvyttmTyzASHBwN9XxooelCnahr0ne0X5pfAN8ZtBpzI
-KmMu+R+XQNEl5n5YbgbSsfuvwXJbFMu9EUf+9F0sd0m93Cr0c4pnc7lpADlw6fBpFseQdIItI5Ts
-i7fcTs1yT2Ez1MdxLM7Fcofp5TZDPP8UBQh1Vt7czF9pEp6QPPg1eiuzeR7qTLx6U9fCPYlS+TI5
-Lk2trJPT20CsBrvGYlhdhjSgEtbmtlN9Ad6cAk5CK1ohnL4hUjC/gd4RQWqQ+qakQY0AqtqVPNoO
-ytA+ivjaDd7tzCE4BfvbzOMGmekOP4OLFqX98TdaNe98N0Otxz1tuDmLKdd63RRFeinyWBGcLuUp
-izkk9mrweK8yc6ZSwJibDytYp8mHJcq73kpx9pVCOtVOI7cua14L645xDQ2vDEhUjAJtJZxy3CIo
-ute8Ng+DYb/VOa2cTvS8JGbqypnlO+FM4LIZt74RPMZx9Zi2OtsaQ1xv0HpkqOxywEM82L/xiHkx
-POFcW53vb5vSfkLdSgVkSGsrEMpwwiIQQe6V3nuDMs5eNCZbLnoSc0QSPbqChFXVNvGVVuoxMuNH
-pIz6FFd+cshdyuwuE1ehZZKt0+uR2c3YU/S0UNxhrn+O8P8cPDP6Pk1GglR01lTFSbeV5nSuqT9W
-Q8b/PrAwkG/1r05nFlc5luxdrkYbB3kh99WU1huz97NVM9t7TxdAMfPBWGEtcHY0U2mriPqdGdYd
-daFcCTUy+zCHp7IYn6Gj5A+DUfIc81K9t7uu9yBGJyCt3FJv0gSSDzlljIoM09xbsSp3HipRlHV9
-s+sle63w6GsG6MlXRji5q3BsPg957x4nM2HiMeefHZKnV5mDtSF1cYNnvoUrgDEEyypqVlWWjeva
-XMTxJfYCfCig5Mg+WbexgzQk9DNKi1LwnL84AFcJ2qJimoiUXGkvKAhAb/mEJ16tkK/VuvH7R77P
-OYaWk3LtAq97ajyVn9BfB0dZ+oRpcu1eF4H71QRU9JhI0iu9kQPFyNAT9+n32FKPGADBH5gRbhIj
-REZdYMwmJRbApK+/gpciQZTskFVSNdmGqgB7yhR9TJN8HdI35P/XwOpYEYQdTLl7mc1CbqYk/66a
-+X4yC0Up3AElT1uw74bnSsINovCmqWW/IQ3e4iWy5M3mHpcV/lU0kFI8QU5teL2aX8ZCWFunip9c
-KLPM/33iLr2Bl3GJ6CI09Tl0rdPkDqhbLfbXWHNJECMYbWhI3xDwJ8nPc4vqELUEGGhJcGY4hPNr
-7C2PzNCadvMI33k1NnDB1nHbz5+DKMnw/sDOccncXTPQlbcu6aHvsZ6sY2gocdKDHx/T1m5ug8Jt
-Lz3M7Qsa6/Ej4Pw5mbJyD+NSUfVLbYU/rLuxlnpr+FF5LTWYNOB/ovEzNsGP6owT137ylpJtSf7d
-d/zGf1y8f2tC9Y9nT7/aK//XvzfE2n8rbt6zb83/G2MsemKLxuefj7Fu3sP3JWzzL3Osn9/3c47l
-fJJIdiCdCFcS0KaYI/4cZVmfLEuqhRgrfAfJzS+jLPUJ1SUJZP7C0WPvYU35fZTlfDJh3gBSlZZy
-+CPdvzPKkkvW55/HnCRVWZ6CKEy4GoZP/hG/jjlnr6E1h3roOEUW5jf3PXQjfxVFdXaj7Sk4RymV
-MGmFT0WZMKwhEmJf0bF/H23HvY49wjdHXsqxA0wQGdmFybAmyMF7CuFVEXDow9TqFu7aBNx/SOz+
-rmeGjYbNwoJYdulDo4FIxX5d0we36f00a9mo66lBKO056FBg1kOFDe46MGAKW86WVFpSTOLgadSB
-t0Opmq7czDnTvlHvbmSmFMXcTQVmxsTz5+s0m7N1O7Q0NjDPYx6hI294w25oevLdY283U23y6O4y
-a1Nl+EFG091A9zfQqw13lbYPfIJfB+muhjI7Y2vcTo28x29/KuoyXOPqWXeF/O6Y0Xhl6GDpkyXe
-vJe6foj43d4WUVYQb2OUe0bZT0Q3r5QxnDuHX6bfltY5nviRIyu5sXOA1QbKfnoB15bT0f8TRbaP
-xvZLKaf5JnhufAvhX0VwEpmeV7apU7Q/LT6CaYNzYpti46oyu1qbXv69teHK+AqABLOm0VOEGMSP
-Fc98XWZyU7s0rOHxrwSlxcaY44MxdXeGdHoaQ8341EWzc7TcbFvSDt5ESYEClUnE6FYh77xQPwA+
-uNdW/xE4y03W2OluHCcP0FRm3zqIB8lKn/G1BBgbJ3p5e6/FmY713Dky85oeray4t5LKZpRn8aSJ
-Mz09iDSYOYsb8o1hSoS3o7rG4/NEbgeI7Vjll6E2jDWA4OtQ2LealiKGoZcwnRCHlAg/utHex0N9
-DuvmaJCmI+bwZQhJo8AlMjlTxEfV3NR1+z3JH9CMkaeMJezguGW6nshUw6u2tcd+LbC9k1RtGWSs
-z8TMyOpm6sU5cRDikD248jwP8sW0DNFoCj+jrxoJHgPZMqrl746PlTBWdVqKJ0JborU39Q7uSFxG
-OwaOdBK9wdxX2MRyx3y3kaCfZtP/jrzl2krmlS0yWjDVxWo97rV4g1Phvp61+dajYReQoaOt3fne
-g69gnwXEHK3kxJPTAkNxiwLfuaB+x4/q403MwZx8Ke2qO5E0FLXrhvj0S1pZ5ZUVNNMptmvv3cEA
-BwQiD08G0YtHXiLdkXzN9CW2SH7AXtVEZy21OOo4rA8THY/HxkVpx1JtGBSJ6Q1lEojmaiguWln9
-0XXz9HMyBS7icygkqUiSNVIkddKq8E8lnoGdqQbi2E1z6aLM4zUP/OxxbqPxkeSV7ioWZfaU1bgI
-qh4J5Kou/fq9DXp3U5m6J3XEd66J6CjPSe8Nd/T/rRvHnLurliiSNzNOu60bYtUia4YnSaqSY619
-53auC/3Nskfa3A2Bo18BQ2Rc9uisrtFnRddx6Q9nJ0jbUxp4Jv2HvhcXzxvF/WD11Q2BNeY5Swr9
-RNKZz9QNZS1LxT1bxiDOGY3dBl0MxAqyKty9mcr0xucHpDMMdiBOtcgPv9wy/2Dyb4nlVP71MezB
-JaW9zi3goWqAq/TnUztJmEtazYyqOwzTm9Kui/4YN31zUy2Ghy4AFl6aw7CaJKYuc0jmzYA7B6EY
-ymCa1U+qb4xdak3oddx4KSkbsyALIhI7HlsNc6EoxAHWwcYFaetcVC7iUyuyGzdQYJoqf76UysxX
-BDOm11OIbJSV9OSghEee7zsHeL7ZGvqEs9KT81jXdCW6bshuVRdCrBumLngsh0EaBPBOVE+NO1f5
-Ruf8wSs5EFK5Vthn4JmAPVo3iCnGvcjI7dr2yNff8HJV0abqw2LrzGb+RDCK9wbf+KpJW6LJJIEX
-rkEqTJuvJ8bkZT7hr2/dfBOJFBRGRjqwFTJwyUx0Sp11X47tWZf1Q0DgIEQe0a760cGvHY3Y04OI
-vEHmYxYRJmt3iIls10yWZ7s/BXVxdiO2fxRNTFJw3w15BDC1q6dt5mTk3Q8q/KJ7Z8A1Ntg7A3sF
-wHDl3BRItjhjzHTn6iS+L2cVbsouzG66eXAXpz9LaXZZVbNQ4gwfgD5bFzdnaMH+decI/aRFKM9h
-pKqbBNHLfWEqcdEJXL41ZMn2xGc9nvFbRNeDQOCNaJr17sEH/OqGaFZWlmvpb/Ck8vVYB+OuXnbK
-tOwZb9k9ctlH3bKj0sbDhBSM1k2CE+eurKLqbIuc+1k3PQJrrkqYvQ0srowBPtm5uH+WHewve1ks
-uzpwk/wRGsl4Db4iPDKoG3bVcg6AmPFP00zroLQLXo5VvqyDyntg6pl+Zp7dH+flXJmXE8Zezhpn
-OXXa5fyZl5MoWs4k3yjFMeFVeM5DxZE1git6QanRHeMkWwByQ3hKW0a1fau89ziV06kMjJJmUeJe
-dEZS7QLy7U4UIOoLicZ6P4KxYSwWqQv/t3HbVaFam7TQt1EEFhAxx7TMO4OaULxm9qlQEt/kx/b8
-BPuIdNx4QPsJR3fD5FVlazO06glEns76m9yNvbVwKgfajOs380b69IaZ5/j4tfO5CcsXoFQ1cgcn
-KVtQZ1bSHoqw7sOzTEVIamCDMWDVtV7fMVfKSXerqwjxhQgNFAWe1lO48aexot00OzP3NfpJgbmW
-vBW2QVyQRtJat5bRy2svHJ270UAylPpWs60h+Nw3c+0kEB6CTOyJhEzTrVGbaDGDuPCZG5fBx4L5
-Gjaej4p4VbuzNrZdllIB9fhh0rXLsfk6p8SprCF2mJwtUxz7LDGzMkG9t/I+QSDIbKe6c4MJiEYc
-MyRsphJLc35oHE8gMG2f2v6smJxvw0Bcu55fXtvkiq0kgCuMGBZmphrRAtIhhKsBCmpiO8dNVpTD
-CuHXsCLt8zO8oGE3xcMXM7eqtVdb0BUmeQmwFt2QwSnXGMQ+IvcDdYF/NUlCEpU7yQ0hgsPZKgiH
-iV2xd3VBQ8u8jxlKbMbUQ8gAkFVnrlqHGbLxrrLdU6tGdUCeDIo5sq4ITr3Hw8idF5nW2eD+34q5
-/JI2hbF8Rox7ppKEQz1cuM6fZrOMvjs4BI9NR+9rSIv5hJlhWI04z59NT0yb2Kym7zzxWINkD5UW
-0pJWxJDwIjf8zzvv30Xy8Iay6Sb/83fe5luqo//+yFu+6bdHnuvylEPT7nAdQ5Djv78/8lz1yTPt
-BYMD89dC7P7LI8/75MHE/YHiMRGZSkSOvz/yvE/Ls4/cV6SnJn/i3+Lw+H+RstrCQzOJbI1z3l5e
-lX9pnaMyKjP+edU+qvU8cS9V7WPXh8Or7tv+1hqHx86ojXvebthyNXwNBkIMSZzShBfsYIx7y5K6
-f6+rIjoGpBptyQ5z1jPwOFAdLQVnGnGYKCgq/PHU8FgeL4zd02+xUh9D16gN02Oih2IychQstgv1
-VvAIyKxA9WU2L9ils/fCIyATTx46kSBJLlPh3BPr159SE1DiaKnhmaaa2Ip4DmiAMxP1k7Z4IO7y
-dTSQ98OrWSZF1bhVBm5OkY/1apSS6U5Dw6ebqgeRWRrfIDWKVbY+175BjBsW4wcbv/W2CeOMoOGG
-yX/dQl8OkmpPDu/wItFJHBoZpN/9oMzPCKf1B81o9OUTDp8u95rHuJPZPg4C1SOLt9AR9eiTeNWQ
-0rXCAmt+TugArcHld1tBJtF5MMcBS9fc0QpucP99xgASlfTMHPy2ld2Lt4KIB5gboMhWXmiSDFP3
-zrXT9j+854n3TBOqwfhtoqSwPFz8q9kvUFf9p/Xzb1K6liOBnfovjoT37D3/L3o//4WJ9B8cDXzz
-z6NBfvJNiRodiKXCq7bMtX7r/7jiE9sfwTJuMdcmI43WTF4gvfuf/0OKT3wFnTOsMFjKxP39cTSI
-TxZKX7he6G5AbkAt+Z1X9vPlAOqM1lz4rfgHLwmf7tMvDwn+TR5aaglFa5kieGiZ//yQKGsDln9u
-2iinou+dq27c2tmXyn+MgxKBUwyoaaKF0zMaYDREzL16o/jad/5nPXQpDsrwFOj5OenUnjCLnUne
-dXwmveGqHdDPuggeg/6a0LvnCrFa0oa7cnb28VwfRLkudLC105Jh21p13k4NfC9BRGlcH7AUHhNl
-3anauWEuuB8q+84OTFDoK0myFQOb3VT6xCFUD55RPsyowgKFUV8X6wTKStp+zOnDFEIMymBLjGrn
-2sO1W3qYMrOzWdo3uT0+lxa47Da/gETbltO0TzOFIKMFDxg8zuQTbrzAfmwU47Ihvs0CGx+LXmYH
-Tn2YA9oBcZjetaF7sFDmICTsP7e1TxRg/Rrb/MroUhB5rI6MZLZYjL7gLaL2yc424cK/rLx/8CH+
-VY/+24e4uKrwHIId95Ye3y9WhQmUbaMR+ZK0hiA1Vz9w9uFQ3TrTdOvW8Pq1TtbJ7G4NUiNR0vwf
-rI9/Bdwyt+chQo4B7U2uUmu5/n79B/Bu87CRR8GWDFE8JNHZ6+rdKKiI+8nBHqflrR0kat8F8wWl
-53OfR9aZa9Q4Zoqelrv6NuE1382qVoT9WtHONYNsGxTzeUzrA+QLSiovNI6iZUBC/BC99TTb7PF9
-YsVhJsLbJt0OpOuQ7atWRRE4qGqsUzXSiYK+Q7HWyC8TZujVMM53nYj2c8N7nb33YlXyFLjjtRd3
-pxxOwlVRleHp7x+k/16D/J/+X/93Gj2WY5LWwz8/JteaIzIK3+u/Ugx/fufPM5IiiXQtHwgTxYmt
-Fl7+zzNSfQJeCPxAYcX5zQfy84i0OCJ9ZADciTSwAc3/0SLnS8qj3vIU8G5evoDa/3Ik/qsj0uQv
-/9MRKXhk+MJljbPIbdIc/7y4O63cTGTxxDi2rp4y4O+vlQvKz0OPuCBF6vENXNVHkJj1N94a+Wcq
-Hm77XutuazdDgYKtqLcub/fX2uyLqz4rw43pRelXJw27l7+/1P6/HNdwfyFLEbAs/9Vq1O9tGzX/
-bT3+8c2/LUgPKxGWcmIdPYtPn9r89wXpiU94knzmObTGBYU+X/n90rY/mYKbnsVCGA1W8D+4mqb7
-ybVZRZ6yIatgXbL+zopknf9lSSq4BSxEX3rSX14Jy5L95cCHQU0ketyPXGuFljsMSTXIwlha68kH
-2UiBC95gCww8xwwZBsw9XHfRqtqjHI3FhEoMBKOncz780CxCY1t1AVxAjEbpQxINxqNjBvoYjsUS
-VJvrU525ItzVDrp10Cv+1rWoDpq80V976k+ayFyXGoQ/0VXBCOIKUD/exoDAj1No5jaoF6k8avRg
-ulNjkUFUnB/CzpqgSRyAJ3feSvb4qLuork/a8+lLUavI3VR0vKaDMYTP56YTdX0uB5Ldi6lZItRm
-8RA4UfpqjWP4UEjsv0pIYp29KbyG5ATXZjL6+SMsfAcVmO1iuujq9wEgHlloydGJJbCPmvw5xE4m
-1EdomvllbJr0tpyTeJsT+rvK5XgK8Z1szUyTeGfVEs9vGmJsARAMcNT8WIhOwOGKDn1a60XJGSNL
-8jEoiFowRlP/a1gY4ZNUsbUoE7CMQksypLkJZZ9vWkdABLESeyWsaFwRtSevYj4ANP8wpFqs0icA
-o89TRLt/48oRGN3c5OM6jXNRrOexysEGzIm15L4jZldD/B7ldvZNyED4e3wFpQF1poeBLPwJjb3P
-ZVk6jYH5OZsB4Pt9G45rlYeA+AwLCKdEe8pYfvDRrOblm26Cpl1nMPIZ1I9RUdE7JNQZ1pt+zdIM
-wwZ5PvpgNfw95mTlPQzlwfPXSdhWgMOcGh1eQRYsDgpiAA40w7uvZZ0PemfJYkRWa/h7t3Np0cpQ
-TShreBOtXMsDL4jPunlqbUteMPna50B1zaPOdfEeEkgTIxvIK/9E/WVB2PTG8kuFzvOt8XVhbtAj
-0rP147r8bHZAQVezuUQRx3FeP5CT6194K4OunsvBP8dJ0VwyXQET8HKN18on+f0OKcT43NhgZVe0
-w4xvEOcdZ8NwoH7FupZ9KIjJe8izfL2Q/vDY5LmFiqbN6AvWLc+9AyNDTfKoofMTGgCkTakc9kaL
-pCTUw/Dsq6G8d9piPlp0qdi3SYWxQxs4s0tFb0swBd4gjx2rdSBk8hGyuZZvDSiq7DpNq4OImrje
-2r3yjr1DvzIl5YHeoZ2O4iWsJvGKu5yRrqiKeekp8wF6OLOLvTV5zsqzKqJBG1EP5oqua4gJUIPM
-C9S3IJXz2xCOWxORNX1j60vR+6TBiySuPxx3hEiJf2l8G/s4xw6kRxJ2muERW3B51p4VHBISka9y
-Qt9z7I8tX3ajdFvBtHuZG9fWQFqAq0jy94Aitaj4xYychektcD1YZQA6LNWATAsOgMaRsE3ztmBc
-R9mKKh8TPiKHioiGWbrBsy/jbJ23DEqAnPtqbZgUeuBH67JaD2FWbfSck+xnz5Ew19kwZsVWBomd
-rSUjhG9xV+qn2dX6JBIzCbc0R/FGGbYcXg02Ckl+TKk7xCtV95ZZsa7ZIi1P+iSa2dpz5lQX8MbZ
-tMN8UxDmMJdAj1AIrVqKCaSSnepuqiqZMD/nRXFss6Z5bQSIFWYQXxOC34Ey1JzTfZoyIfMTDbCq
-MwBvzT5u9lbGIPvlnK98PfYvdhDWZyvQ+s1kZJMyP8zmbScNOFT+SOMRwG0monVVze4XcG3pIeTN
-IarIBi2bU3VwldDcDcECfbWNkEapUSN35Zc3DNdR14U0wp1wcjaNCfRwbRBKodf2EAN55OdU7qHz
-UwSeTRya1iYRfvNtspuiXQ+ju4LCwy1j99mhzurqKlBRDuqImojkJqjxm2xIk3YvYTZrjAl4oexI
-tciy55xRE87OMAJBoJwKNgmEWX56YTcblmb1nTaJxxwBWZDZgPZB2TdyOPlp/pAbbDcw8RGOiqGq
-3iIXjCO9YM+7a8taPk9uAWQJ1a48C/S6T0CXqldCWLwrL05Di1dBCz/TK0PrtiQP4VbReX+qJqYV
-HBuK5ePiXbB4ZJpoepqov57cFrMZFNXwGe6zwAqJyOi7qEhRPfEv1NZG9QiREVtN3lsL+pLc31Q2
-1+xbJzsEtnSWjF9HPXI21ec+8+ObISjkzvIYooyBRJ88GjWCsdSIDL1O59TcGTTcEAgE7ssUi2GV
-FmN2m8S+WKeywqA1FNGFx2C+1rNp8q5SBZMKXT13oUieSt8qNyaGs1K41mOLtvSSEKO26ZLYOlRO
-Jh6haxnfZEw+z0qGstuAKbOOsYjRUkIzCx4zEboXt4gei0IYl6CYyNJGplUR3h0nFyOWpADYpAys
-hyl30HD7qI+3kcgJTGz5ten15Mb4SYKUQSorIbXKd2x3AcPZLmRe5ibM9uZiwErnu0e4DVDO0mH+
-kmo0WMZcEc+ed4W+LVTanLMSTxIK6+gzJqw3Cuh5P3b+uA8ipjGuyqL3oJvsTeENyb2HP2tvVFh7
-kL/nuwoPmsJ2JY3fkianTuOwlNBH62vXybLPqe7RKnimHL2tSBOmclBhFjJpyeHSWJ597HTUPlbz
-UBxyo9bXPirBbdtMLnsuRJ6SFEhYRGNbJKyb3RqlYP/ocLXc4ay0QsKOsERj+fHUthBD8z7Dmbv2
-GiuIt5wI+tgXgb4JRS8fhN2VFxNLE6CQkKGfCHuYmY4mNDa1FwVtY8l97I3eDTCesD3lzWIL8YVO
-r1VMpgKIyQB7YpLc4wX3v9dVarncypQS9FpK/LdmtcwXzKk2yjXW9Dy9RCO5aSuHYT73d8aAo27a
-CHcqmLAXORNFgAqwvCQlaJSVzXwOSHljWu+qp2jGVhXqZ2U3ut4NdAAMYodqbOdhPG8a0uuCvaVd
-OpQgCKfh6BNxWBzaKVYvPVlzT0i4+3vCjGmzJpl5O0gtobc6TYvuzuB4IJUk3Kssbd/AhhV3NToS
-fyPDjsC3SlQnpRP26ox94OxOFhJQJlPQupnT3lHADpCB/F6/arNFRZAOfUssXaKtRxGP1Qva2vLi
-N3AzEG3MN16nsFxxbdnjxqlAOa/qOoL3O2Xu18K2sa4TnjbdGH2QX/llLvb17KMUqYfW2LqNq77M
-s9eaGw/S+XuL0nZaE+xobO2p7D9iCc5kx4it2w1AQw4xI967PsG6+NtPyRApXyPT6OF0uY9WjBFq
-ICLjhc2JULeK8vLiDdnCasqenCS9x/IEWiUNm7OfaZs9S/A5QS89A+/MAcACC6jd5Mg53RX9aP+l
-NJFdrmgkh7RQbCIgVgtd4TlWQXX2yZW594tC3aMYLq95vKTnJpzSV8MLiP1T4PG/4DzV+zkxSFEZ
-iXy7QUrU06FPaVp70SSmq2K0+unAELRPrnQuzRRxZTgd8Ew5X4I0RMGaCyRaOZpFcqZK0LcrWXv+
-TV6F88Hk5vpmmI36FoZB3W37OGFs2c000TaKYHOCRXsrkntZ+NETtE25gxMfv86GMd8LP0P3DETL
-527T/bMJHuaeMV56A79uvsyR1X6zfly+dRAvuVMzmOQhDO4nPTUfY+E11y4ExMcahKpZhUCQmNGq
-dw2uEkCr7WmkZgEZQWup8Hz2s7RuQecOG2K/kIvraIK31KSLo0XkdpLg844XSglKV3r6BfDxtJPO
-qwjNCgVc1TY4taMaA7QQ5RfbqLCFFjX6WoJc7qJsqF6wEyCZrRgIp8AlnrFgMyIdpzE8+n3XtDtz
-gIC0zuCbYSayZ+OY5JU4SDcCjAOr1Vw502LFWbwbiFnb7hxpKyv3ifJaUpxNSA08CcC41YM8lKOo
-EsKVsUCajqYOnfqen6nLy3JjlVgV1nHgzEQeuWiic5J7rrIsDgjtQcOWbmRgFhdguvOhQ0JCdYMh
-dO+IJj54Tg40GgW0vEd+bB8GU+UfXjFnn5dXdsvfQEjAprMt40F0dXfBV1m/EHs5HRPTyihVufDX
-jhXM6xLxCF/pBSWGIYtTI6byXPhhqlfMgItgXaRF/J4Vaa0Pso3CW2zj/AhJUsKmTsAS3nV+9r1u
-6aWzXXBm1ml8MZYYihV692Jdz45zCvVogrGcDIEWGoToKON5a3uztNcwKVWCNL2nIMHmCDYicjy5
-UbNtTwjeVHloWiBUvZNHBk9Tjb0nlVHmHOq24aOhjBeZD2naGWiFcyO9Rwmj4nUeBU2wzKUIiMmB
-sNuLSCjomfgThDMPbUzCbqP0wkCFqLsSidqSaaZPjWQIVuOQ+pp5pkJ6PGbtUkZm5dbtdO2tUXBE
-Rz+hLhvDpLgOa/yY6MwDH8uIK54yZ3lTtJ6TEvHJLb4mE6y+tTvG1JlqgwMa0PzQg6Q95t2kK6j8
-2fjM3ECKPWyy4mgQY0F724uq9azm9Dr37UoeLXAL4YvbjbgqeneA8vOfZta/NYD62Y+irfPPm1lP
-Lb7u92RpsP5p/vTH9/7sZZmfhC09j/YYmYZLy+r3XhZTa8cltIUB1J8TYizzk830CUWwbZmWr2z+
-IX9MpvnCkvzowrWizer8nU6Wcv/ayTLJWISh49KdoEFGx+3PnSwdTGXtWEruw9jJAMenagDp4BRI
-wwLXeW+mQN6ZE8V0VSZiDUGP3odIJkXhbHMoDo47nOHCROukp0IGNVGtdfnUzfkm74llcQl33WjF
-NMmlBP7QUdceRRxZDHrakIh2n2R2RMGeg0Nzyrxk7bmRuOeNjW2kreZbyWyHcA2IljHk92LFnEqv
-8FeOyJCHA+y5+ltIk2XdUs0G8FcjNM++6d2ItovOIfOF7SRjylm3q3aZZP5st1m0bdrYO8VAmNe+
-nut1BbVgj6XP/xpjpwAdzON9R1azvS+mTjy4vHJuk1JV+0UNvsmskfwoux3mK9wKcsNbrNnJ2c2h
-xEDTj1Yg195TQmEBCYRpvM+8iio87KdkWGu7h1zqdN7dkMYQ1KsSvrBnlx+CbL0bOxFne1afW19c
-z0UUc46mBwZhZCsCyXWmO22QAOPY3cXFh0WlUW9G2wWvXzNPUSG5JRj9211hqDSlKZCVOInHod3o
-JFCPLR1TFExpH4gNqRCk28Un0jGItPcyexPwgqD/srhCdTYxZGv9GmJE3sninZpuwm1XB5/9eHRA
-73rlZW5MDvGZDITHFOb3VR1PDc4JQ1yPWqcYY1oLY7fXkvotl1afykb30DfYK2i59089Iyx4oKGT
-AGefMYJZhnlmDmAcC1kZXxqrJS4scaS3YqU1qy4f3JchVfKUAwyHYKtROAE/mcDpZtHXiMHAVrAq
-DzSfkAgXjs73onDyz70j1a2LFWyV4lX5qMvirfUm9833Z3dPaZzcZ9RuF54S6hkwWwoVWIszOkj3
-jAYvRPSq9Abm3zkooCT2Ysx3dWUZB18Q4h2EtrzjguYJAL68wF6bsKKdBLu9GXQ3NLOS63S06ZSm
-CWAW8D3meUIKC6HcjN3n1qXixgeE/qiooukBQPd4zIbGvFDEdTY8/7J/txxv+N/kndly21gWZX8l
-ox76qVEBXMzRURXRnEVqoObhBUFbEubpYsbX9wJtZVpOp6sqldFdEa032zJIgsDFPefsvfaWyZ2B
-LKyKkNaP9VOXet2pR+2+IfpFv6lURwkYwOUdyrJIPiVsLeU8jsaqnJOqaZbnrhon/czrUkUuoAiR
-ph7HCmEkHakYXkfgNEHSPWpPhZch6Knbt5aV3hk5YOdZpfBVlHFvByg0mEaRX6PnEJtBHepVi1o6
-Ekwd8cZesFwggotDEZ5HAYWLAyF/39VjfdparrrnSU9rTuCivIZNp22NuK4oaUot/6zCoLtQ6wHW
-ktAigb+1BPbR2yo+A81WdilaEKpcrcs1XjSLLsSoZ2deO8b7SnaQH7w+W9aJBsbEMfqNbXfAjmul
-Ky6dovMuHBu9cpDST2kLGECzCrDZysHNKWeulYSnIvJwk+eDdaqhTtmpKATWqi7q00wturOALuuT
-WVAZs1+bgAtiuC2QwQKhZ/N/o8kU8p8Y87XX4bmMh1JemxmNqNCguxySR7vGFMG9NXRpfO75SXdJ
-LkR/yVi2w2GBHGFewOimsrcIhak3SqnKjZ23AYp3TyUlEiBjbSvlXrPcdB9icL4rgXBCElLzl06n
-EJ+NfS423ugo1/bQiIu2Euad5pWKOdfQr+wAR5J0V9vRjkRjLulM118BHTpkcXXFnZmr2kKBpHoX
-BmBHYz1u6hlg9XGpawPcERR4a0g8wUqtgg7Wgl/hhpUUyAqK32vDTr1VEDg1yTlON5zkcaaf+mk4
-rofUMteOWzsIG+S48LUIxhBpJg9U8AQ4V6K5Kl2Mt/zRm2Si9kPYaek69WWwQo1Ynguras4xl0yY
-mxqMkCbSJ8we7pPrpOm+sdpwzSyFWmxkcBBHVr1MW6nTaFBsccJOjWBGHHvEoidxsI3Zc25pwZSL
-rnHkiTFq6b4o+xwAWfgZKIVDB77aFoFkjeepBn7rqdDHskdual/5JbTltB9OIMT6N2WUtC9ZpYI4
-knq/ruVEg7IbUWpLaxipFFX0WwEybGT2yqBb/ryWenFa2Eo9Hw0o27Ih5iVxJHekiuzSJKtylmIb
-M/QHCRPBpCV/puXtJvUdBA+hf0ZbSm5YqpfaQDGfRmm5Qd9LB0Qi3IACnRVLbBU49DVSs5NtjIpM
-pQ2G4yYgXR7wQ9AAcauj5CRooumzaH62lD2K5EDKJ8ZprMwNidpzp9MhwY2q2V3LahyoE8S4FGVn
-rjI3ba90BefQEh2ku+m1Ao01fiZ2870766Ire6RBkaRNtacRU3wqYPYgASBDhWFQuu0LTg86cJOm
-Fhy+sS+Ms6AiMmagS0hvMRt2WifWtT6OG3B0I8oCkTxQnT6za+ew3iHo7WrTpehZnEzZ4HenReLP
-SzMHca8ZOag4Rb+CFoUvJ8rVa8AJkFKkAmAhsCHvzqBfgPY0A9VYMFnQVimRArg3VOW196S11QRD
-Hu6P8tR2imajk8rEY6bJn9MazKAjCntbi2Jkzk7mL0F2+2naPDmaxqXfpt41X0DKORVOChEZZ4cj
-yL4xqjI413y0yPyiTt+919aFOuZ7kBnqKW7+9KFrVZjzkBaIR1ZaOEUdefAbYdW07FwkS6+pousk
-JSgu7YvYQPWrS2sW+k4XLrEZWcYa1GtwkhlgXKHhQXQNegOcSd83Kk3kzIL/4mb5FfuLMDtLfKIj
-F0qa4AdgGZgHJ2qljc5ClGXUXbh9L7edK5PLid3+krLiQH0wrG6e9CWtZ90Kb3Xq0GXEdnfuxJqG
-G6XFeSSysebPtr5JCTNe6ZEAw5yH6lIHaT0vHRFu1DQkY9lm5EI37mIKKspQ4vKC1YnM+3zRkKQ2
-c9SeopitBQV87M9l1fXPXdj3rzAGnqn/5BOBDweraFU6ZoafX7iKP9H8GthsdhjOs1zvTm1d4h8q
-4N+NhpBEgtAmtCtANV3C46lSG32rl86NGDtsBIIAB4EdbeEBHVkEFZDypKh8TKpmtgqqJtxFWdZd
-1JqnrD2w7te0yup1Z2rW3BDI8C2aw8+McvQV96i/zoJR52to0pvQzOGz6o6/V9Ogh4LV1isFOBcE
-n8S69u1plpDx6JxHYowWplEnmOFa198OCmnjlU2TQeL2+qQxZF6isPL2aUh/Ru1yey5ZopCiR+Z5
-QzbWXEk8wn9KYMxeoqMF75wMqiCNeXM5Jsi4TRLF8rkIO3sZeGqwimrb89lddYh/3NzY2Y5sl5rs
-jU3aW9q1V7vBUhaYzBtFeBtzMGKgW51GAAoCz4IpAsj8tjsJEy/f211C46OxmGRO+LfwwQxlvSm7
-uLhSAUQuekFnwAgze4YX27jjQUfFbUmH6iC0xNIg4WVLWIezsT0ITg1c3Vcni50zqzKT25Z43zVT
-RnVZYu0Ev4db2i0HY2WTJk5OX0H2Q+y5PGqGLKNBxBCW7nd/Wqn1Jd2QFftUfGM2eFwnkfcK+axI
-7YLzdlAe8YMEM93PsbchpZ1ZjoQPkFO0FJZdzQuh9tvCDOql9DDazXoDcnUzTVso4gmV48Kgo5bW
-SXelxkwUVGM0sSTXHp+AcYykxbD9prL8gcJM/E7h9X2d9p3CS3GcMepUsqyY8zEjmxBYCkRehsRO
-uBImydYRTvrb0hX9jaNp7sPgtMWFCEZ/5wyifPQgkDKrZIMPaUz466AZipted8eVapJZQ5IccyLp
-KnvyD0XATRtC0zH4BtS5a7CVALoePhiWqyhsajKIQqLO1gwFpsTAmBidUPnsW7m/0BUyW5SIHIJU
-WndNWWknSl2YRHi62oNoGiT7mom3oiSKGHsVN21smudGQuZ1gnHRXKSlM57IwLaf2Kn7a3Mi8dCw
-P+StuW/q5hrCKvimOIsXWLSGhTkGw2XbZOT1xOMpUHlw8eTWB8xvSeChKg0Ca5X0cmTZ9qX5LOqS
-FpQCI5mHe8qmcNkqWn4/ijSBpxI6JEXIwGpPPdseTgIm9zqjAGFdkgDeXlSwliegv+ZhwInFi4mS
-7bnwxnZRGIq9hHotrvIxRhSnBCW5j5auLvOhtXZYvpSNKWLCQqMxL2Ex4fCEP6P2L23VP1TBWDLE
-NMOVIdNkZfZlsgJMw8SfocFMJ0TpzOtM8j3KVNb2rDEZUzV5Wy1h0YQXY5zxhKb3u/WoX/chmG9S
-cWA3XHGjuye923cnIjfw8zComGnhUL0WQc1WMO26HoJAZ6J2YL9AKlcJv2zuEMsB94x9dnvccifH
-7beYduI8hdmURwVJXZxIsVKp5Ql17EB66dNOHsMMa5Mz7e/hA7PTV+GGsz6w/+8Upz51p5ognqqD
-ZKoTmqQV5Jb7pMihWdeIzHYrAngoMOSx1rDYmbEYTSWIfqxGmqkwoZfW7dNjtQIkvae1GPCwtjox
-BypFqLUOhWPpB6gu3WPJ4xzLH82WWbGpS7vHkGJp216aZCoYBYAPGXPhEqhI6CZY4wMTBgH9k1ag
-yNp6byBiXA+IzWFJTPXWWI7XBZ6eRaIUV4oIw02hcMJ0pcivsCcb5C2xU4a6htInZyu8tXuANm1A
-kWZIr7aIxmkgPyIrh5TC9wBvTtXuRWma8wal3d51IIaXfAcDaFxKRnLr+nl8rCNRAMRnQVzTKaDI
-JBEqmnfHytM6VqHuVJAWmh6vy6lIbaZytdEs/7Skgi2mUjacitp0Km95k1OhS8krp+KXZJZ2Uhox
-vZtKY1PxncfMKB97hjSfrKmAbqZSmqz17CmbymvgHVTaRFIMm2Aqv92pEB+ONXkylefpVKi3U8lO
-Ooh9309lfH2s6DEieVC2KPPHqeCPWKRTD69djfE3nTXHzkA8NQnA59sbc2ociLpxFz9fUY/48N8c
-nKjLDYHimzBo2m+gqZ3vs+pdRD+QWZT1UDvGNqN7WwvPARoFOUpMaTgov8y9akyCA83Fs2SCSl23
-wtYeK5xepLzltv88tE23JX6Q7A1Hq/bAr90HNgb5ne4Up02Ykf+tEvbD5qm7kgRtEVqgFDHfaaRP
-duYh3sBkqSgF6ogxtOUr9rZy/Az678C70l3RsrPyxuxADB54Kij3IB3HaSGLj2tadFzfxuNaZxzX
-vWBaAt1pMfz5CTtaWt+dsGOnkM00XhZh2+Z3ImeXvKfBwGS+Rh90PT7oD+VBeSivuvPqEld8dqEk
-5z9/RWP6Cr57RU01cO4YhstSaX/3ih0NFprjobdGYuN9SnDf1ZjpouE87sNRzNlJFzs5lDUGQT8O
-PmnmSN4kOufXUTN7oHFD6K2yqEN9J2x21MvR03mGCwKI1DUJjco9XnfrxrJdHnVWlkM2iw3bARYd
-DxJqY16eYuwG6ZmN/Qk7GdYn2ikzXIpXTT8665btJ82GNFqRLlCuhqord05ujk+IwMBKd15y0pam
-A5UmUW7TsJOnSKHiS6Zc/k4kDVlF9OyL68C1xoPRhVGMkqInAa0P5R0hZ9P6lYrk/7I+9b9RB/21
-487l88fd+m0AhPWPevX8z6+9evvvrumgEf2dENrRcZiphmHo+nsdtIAv4tgO/8FAioB7mJ3ZW68e
-6j33ChJpWPi4Raz/yCpiI5t+fz9Y+At0JglooR3MLBMb5Z3qNFUjMkqHcU1+B21rOEl5xtoEjg8O
-nNlAljQ9657bVE0WlbRC7oYqdtq5P0hfw4clcFB4Rdled2rnklZr1uaqTpT0zOmbab4Z1Fc5WhIG
-YznRN+ibUB8MZFMExLbteEMp/Fr0Ip2LzBG+mtP1p1auyh3gsiy8MBExuRSthP5Q70Y2olXbrsQy
-CvLkCmKBOSDZGsiCIg5HF8u+VDN3TdD8qM8ISUSshiqFgTOZr85GdTMT5m7rRVdtY5abkrIoJtAu
-ezCzvHfnDZEcz3w47lin8qaRt97c2JUF1VQoXuLNulTz1p1Z2LCLOwupWwe6ZGUaVouKVi/tfBWO
-nZGT3e6F52GtMbuIA/r0C98uRnXLTm1ixHU9bQDmdZ69gWyoqxtjpB5cetIIWWOtzurnpLAqT0hP
-XRy6yRCe5h5j0ZLuwilcF4M04jy3w10vUNktnGTAE5/qNrjiWEoIZHnrOdDf8+YxEXEHJL6p8xdB
-Jt1rYNjQNtg6F6cwx4ezvsPgPqtNF/p/Q7ILTeSijzeaIjoSsJX2MtJl+llPA4VM8yjwkyVUCOWh
-IsgOVBHc/XxtlJW1hzFCx0UYUAJnY0U/b05TM7nJCURnv1GrhHczgihyRuuO9moVqjuNErTkET88
-cTuNAn0BjOkYrUHUYDTGuA8onmBYHLSNp7g7LSyKlVYgRBWymgR6SrEPWjpYep3DQYsc9bwkZkaZ
-RWOUdovENJ1lbKbFQa3q/hz3sN4AtBjEnGU63iqyFkuYawUiuwJRWkhVMxuHbFjXRpmvclMbVnCn
-+3ub8Jkz1c9cfMxxddcXeUjmXMT0SB+xUDuq4zywzRivtbzv95jVSVSoEZHEmttdRBqrfhKbIdrP
-Mj5rNBAvDcdiHEYSsKehZ4KL4tAQy9RJPimW3SjFclDC8UyhITYpbL0tFMh8I9LAXWU6MUJgAtI7
-qaH/yx39FmcomlILeODE9i7bHTsJrnwmVgOyNFRTbmvqJwAii3nXqM4idMJqV3pSXUDVpePsZ0AZ
-mqbf6nU2qefGdl6qFhNfCw4i7D2D8x8Lz99r8DguddE6iyGj+8W1rq9JcrGLRcDm7dXpjPqy8QoB
-ENrUrskjGu8Q2WKitp2BJlNU2i3FQ5HdJVQU92TFF3dxXjevTLmjO1szT4DiNRsj5tiRSlU5r6A2
-7geRlo+lSKvLLDW0A456InFLYbvXApjvPAsSgn6jlBIH5OEAZq2PdGJr9IHWMNPHQzdG9TADoWnc
-ClHSM2ihzskOWmTvR/YFtg7riUT2ahmkpgc6x6roRzo2GtUiJE8VHcKzXXn0q/JSFfAwFXO4iOwM
-XRklSPEqwlK7my6EG320x9fA7rpi4XRqcktqk305pP0ktCNnsocmLedMMjo+J0P3RYKj+FHHc6qs
-GwJ0zYWbJN65rtvNdmCNuPIY27ykQYyrlcblcB+Tj0SaFUvzRrfIuSVZyNNfod+hq4EfNGX5xsK6
-adwMpXNDFTgfE9Nnb+hnB0sa3P0UswWsuiLZq6HVCsYDGcB0zelPqdtrNH9jOK56HLQLPM3U6MAO
-UPNSljERQ7fAhmhFHYDYA+i13NLNLYuFTCh5IF024yZBfVzSiw2aabeagGGJuUkKC+vr3KlFdeWL
-BKNy3gf5rA2b6hoi4RTzTFg2xZy1063Eu/ITw3ikZxZvM3X0npSuugY70Z9GfgP0HFRldAnQIU7h
-TcfhDPW7QIeo+80Ju1ZSPzX4vYA2B/3Uip36LCnjAAkqmYgXsdm756C5qMCiUWk4EYkxXnZW5Xcb
-Edb1NRKa5CZofaD+kdIt29a3d4xa1Uvaad02ZCN5mgjmUmHcpKixgKMu47h3L9JsGDZtDliEIkrB
-rdHAMJ0lahcqSAlrS1mhrQjNObaBEurBIG6toMov/TJis1a31hZpX3roSaU7ICoEY4/qD9qhrstn
-ra5tRJWhuGk1UtZHI7OXJP460Ihk8dn3/O5AnikNCFB/cIVihWnWbGw7ubEGmNHMZhJEnVr2CptQ
-xnSqbQdEFkloLVXcsBBmZZ4w4spPoy7WYR9NZ3TQgfjanZmv6nGgUcGu/1KxDQVngOqkxQrwI89b
-p3CZ/qF2h3aimSnRAF3bMc9NaBAEqfDAUg7Nq96aaXOhxQ1ldO4YBAAjeGO+FhoRTYlwuJTgmXiy
-y0peZrmdErBBnY5aMbLhOtIkPUXwVfLwaq34vKp6H6pKmm8Ds0qIKaMb/GwjbKxmCiWhOvd0PdyB
-nenclRCtemvZSXjHMzsO5zIsamYpbt5SYyrmLkmcYu1apkuUIMZEKnjEpg5cZ0JMRKPsktAb1ZOw
-rbIbYLI6iMa6inZjqajGLsgG/T4vVIjviCJPwsqyiplZZdi/pn16ndviqlcdsTXcICYnRwVg6viA
-QfKx249ZxQlxWXRnil3X9ybRdq+B0473aietdYK14qQaHbQ8IxForlcap7aEysq0urLuayEDsrc6
-GE4I8A1wjvgg6AZDLj1PvDK+zzHNgZHhnK09Oi5IJSs3OXWHxnl0R0wofWg9kGlWrAcr7gleNbic
-fQOcmCyMGyUipS9Al0ncLOIIBrJIIG+Zf5HFUACmWDOhSB4zX+3uBEtnMYuELIADa4Bj65F0FyDD
-/Ub0SbC1wrw5gebpTM0ca+15yipsdDpXShSFtDG69mkQA8keYWxYc7Ss8aMzyOwoI3M20gOIrKPm
-FYzJ1fbFMyuwrUTOAHK0lmoRwofUq0MWFs6m67j8G+r/nVY7N2Dt5Lpz22vNbot7aSRy3RqyJl+h
-dVixotZU171S5axNiZ9ch1wm92WvAvph5rvBnNOmS7Bq4ZUY3bbfItknhCBvitpforw0HtyqHj4V
-NnMHOO8hc6kucVnVo9SrGnwWhRfMSTKRc9VP6PbyNY+gYBuzYtkuksewtDpOoovMchA8PtfepLQe
-gybeR0f5tTspsfNBUfYW4mzAMDawBfTa4VG6TWSgftIYHdino7S7mFTexaT3rifldzRpwCOgMiuf
-dO95QhDcTWeceJxySHgeYOzKPKtSlaaI2hnLLpWMSVyVmjsL0pOUoPi5jSZxXzl1sVAs7dxOQ+3c
-YqtMopTaXXqTZD2exOuIEdCx1xrP2Fl31LfbZUdEyCR6byb5u8b45dQvU2YgSjWJ5FNMQ2dyZLNI
-1oRp3ZlHQf14FNeLIVNAerFBRN4uLWehT0r8krWOJ9hgXhU2k6uF3rBLXGlllrQzT3FcZWZOun4m
-wO55h51k79uT7B+jA2zulsj1LcOH8qGyNOvWSazhlNwAbANG1lp3lZWblyx2TG1S0jUfuYHVlT50
-hKsyFMN8MNkQ7MmQUMQmNhHep1jQa3G2gg/+6lptivSl82262+w3T7IuxeiQHE0PqGYqAKuTF0Kv
-JltEmhR6xqo5aMqiqZi8z3w0/ojtGN9gA/N9vO1NRegN2gFToF40lAOhKNV15nujPq/Zsy8K5IAX
-o500j7ltEYZcEqJ91jg2A3PHAgBHPABaTaNVL5zKSh4ruhg15rEoSi+qLFBJqi7LxFyYgYGTAhaw
-h5ul7TtYO+RL6Ju+YM7JHeHiZmiFe+8BOSXqxvZQ68Tobum50W4HIZ0YgDWgbqn4L0btvqrodq9r
-S3V27kDHl5GTH97mipMOlwRNDs2KianxWkkmauuCDvOw8tQavg16HL9eMDOsgotaNyg5kgQyPE1L
-beShB56aZ9VwxT0D6B7IcD+vg5G9Bqv/rg7ajWzSbNeDP7hnWTKvrJzHQRh57i5rh/q6B11HDz8Z
-77vRtxVMNmEPcCuP6PEEaoLaorTg0R9r/qkp8Rtv4Yu5+Nfkvu/++M//H925cCZcLNyaEMaErCD8
-FR3gHzdLFodneTjCNSbCqvxlc2hfkvCX/z3RNv6Iu/HDl/jSVbF1EKy2QCpCODNXjfarm/eI4NAg
-adgQz74az9/cvPjLUT+yPGBgFAaz7t/6KiqKSvKm4XrQxuWQzn+igdT07/E8XxgcKo8MFPgmU6f3
-fZXSi7qITAcDMdRtM+Rn7o228lc0sWXII2fuTHAJ9C9X+m3GQ7eBm3VbleEqTO89Ir9CT5k7rYEq
-Mn1yPfyXAZAqNGvKisnqui0cmNNkFjifhh61MTlm8Fjvm+6J7exSGZjmq+O1jnuzE8OFjpNDV7aF
-8yqxmG6Q7bXi3H8OkJhk5ulANyLrznJJNpj1mhJZE0sMT+wgNQszLYIPV9XO2zRbDBhYk2BYp1aM
-UbNvkEdEK1NZq1YkV5FW+zwuk/MetDxZ9lbWfaLhclvV6mU6Yb1D33a4o2FpV/RPjOxznVxYTgut
-D+MEwzhqah83FBsFCdDBFnssa9d+gpNSlyt1EJtpxxLjOsDCcKr3WjSviuKiatjclr5cNDBKptxd
-BFuzvogippn5i0ltPc9K41FFi8nXtGyB9qM3n0VetzKqeDUYw1zW5BhZEth3daaH9b62dOCQ+ufY
-tvZ9znvlGQMpXxN3PTVzrowrkRLla7BoRXT9ZhNJgG0qR/WDcO+nhCSWqDdnhhOelxU9r/7sm9vm
-B3Nb7Xdd8y9kDlW1NQA0NnOG99cWqtgK1y4zhX5Mb2XNJN4wqn3fmhuo/UsStstFYlvbOs7WSXHB
-tGNtasYOG2uzGFRmBGnV0rTz3JMp/CJWVHZopHNFGJoaT9/rbQ741bzWDZOxXFQtSjbXZbZTG2Mt
-i2xHd4SUXqq9AmXjeGkmwQYt/FJq7nnNV4h78tWQ5pUZPyqcZvZAc7jDK5/kNQDdc0QtjMwJjgd9
-6Lj2QiDU8KWyoUO2l6ZctbqxH1T31DIQKeHRcHsEXEF9ExVYLDWLRJ+toT1ZJqSWsdmynJ+rOX0+
-JfdL/PB9MHO5KhHDr4oWYkl2ZpeoVYALm6nzKa2HTZKoML8nsCFhj/O4GU/HHhK+4x2GwlzlGcMU
-DghNHzq7og2IeIx7IfzzKLsRUp5JDBCV1t1k/dMYmf2uEAOCL1T/j6WnMwYPMNpE+jIotLUVcYl0
-lrGiCN2U1HRqz3ts0+HCh5VJ8E9O4V/rzQ50F7Xy+PTzy0RMk4xvJx3TVYJJVqcLBWvDPU7/v+EJ
-jLnqYNvOvKWVxy++0tx7nD5Pak+lDOZjK5mmyqvSi8/Hpr3wK3kSEb0V4hPT4qpcMdRELehGi6gq
-TthqXQSCKMOwvqocF6xnzcY1aF8LM/sXVze97+/eN0AllOMqCzgPGA3N4furuyowBrda5C1LW9pU
-GiD48B2O9H76ht6LTOgVYltdY7FYFGh1FORUlKLNQVAxF9m6DJJhZisENcgS3XkBv3ankYCRIxmy
-m0jghoexHLbXLKxrPen3YdRcF4p2OyIvhrrzjD/7OjUqmgtOvSAksJ6hA+CFLZJAe8dhaWzFKzlo
-DdbwWmGeg+gyGrEIJ0V3FbTtnmbWrrA8slms7Cyg4byyLPeptEdtxnzwxtKSC8KjGbebxSvemmBp
-6sVNVyuvbqATJhdar8xerysrekjHcC3bivG99lok1GG9P3cz3oFfnkjqtBFXPl7UO1rTa8SS7syW
-n7pAgfvtMCfulpC8KdrgHwfzMDbvswInGnoPg/ZOatZnqGv2pGNHdFcoIBx3o2gYB4OmuY9kfUvX
-i3XceBjj8tYP+wti6MdF2yA5VMi7jMp56asbs8yuzaDbqBQ8WR199tTiOgnqbSMwzyL6kJG5sCJn
-72fqCTzHfWcgDUuc61QTNHdTa8Esc+mimg/xj/qBuuKrP1U1yD9tN8EJ7tGJbWDmL2sbeyPt2Py0
-9sYl5OMVnuF5YtPkqR6i8XpCRcWhswianVvEJ1Hm3UtO4XogLA7nE8ZvlD9OPC4D2vZI3mBGE9HR
-02ds0O/hEHwsU/jkOAizjQDNOR91pHGRZdf3UWpf5jA/Sf0qcXd3Hf3GFt1s9LlMDFSr4jV0Usot
-996oEmqU/Bmu0Qo2B7JxEiIzbsOZ2+b7uow3+C9XUV5cp511FfvRzhBDt0DVMSuRnqO70vj/9cLN
-mxXqhYXnVxlPpodIdBu97zdpEwBHykI6X3V6S1zLg1+Zp73U75LaIbXYejDH8qZPm3rJVX1Sevbr
-KPSdB+9m2aEwQrLu7wZMfxTOw7CQvpMsTWM8ZTY+w2p8gVBGrm2pHgwyFpcwNa5yfTjEZYCFqakf
-1ARUp8Yoek7Ey14a9W07OtuWrAyIEeFSiU9idMIYRjJqxH4ugugGH+BDI5qdSoZU2jP9UTIk1Ym+
-UTq6KKq6T+HkIku+SzGxOjJmGOteWY1y5sePqCJoHjVzFy9t1YaXOu74gavdoPs6hjABOGN977Lt
-19E6EF1Xo/LRyitP+dTGzqs7qk89hFVf9CutcT9HhliEqc3syjSvPPclpUNmu0tDOZfOeaGdE/ia
-NVdRG+6lki4anVJHv2oHACCRc5v2FX19WgLIEjOLQhM5tohe4hCkcce0oXqw3ZvOxMnWg+KFKxgG
-C008Nv617aM4cyShIZc0xfGZdVd5I7hclLNIxZ4WFrNgPFWZONlkiYCX3oSWcYKg2TTSJVF1k3ed
-58OF1n12zQJ7sv5Qw1axBu7rWDyQKJv2HXa1S3XyVrJW3peeiMnQMxd++KnDSJI2r32Uz9PC/dTr
-erJy2+qTUlibUPobauHntqNAatyAmi934c0ToGy63YI2zax2cyKNAswpKMOqheOndyGpm8teDMaz
-IgkfdFA65gB3Vh2oU9AgN4Ff2osx0m7cWHnMh+E+j8ebsY9I163JlgSqPdcJrDnx6zgBOukQ+Gtl
-zaLtss95M66d0d7UzKnxf9NNQTjLvqq/VowSHrVKEgt1bIp0q6ah0GiSjroHWLlm8GTZn9K23eJ9
-eCET6AbQSTEvI7GJIgi6Oc3eGd3WeOnZkw4DUEjU1jeJPrK1Swm9NU5Bsb7GajKPtLVfW1uDSZ6W
-y7O4K1h9kRaX5vlA5hzKTEH2o87Mz4CLaaB0WqDSD6G+SGVeGW7N1EcZZv8zGD2R2A3btMJ097Eg
-zYYdGB2d9AGHXTZLc3qjfuVd6YG25dyES2YNuAYLiGa5bQPHyRp8qAqeHyQL139V0fqBYfzXknlx
-qA/LoyXusnmRw9VLRaDpr3Su6V/3eZjVN/mf+6U37NePD/TLvweIdXG5fbOf+vVYx3f8s2Mkhzqs
-m+cXeI76380J5MAwUT3+UP5C1/a//rPtMMMn60PH8nX8+cJU++Yc/dFZ+PkH/HI6f/47P/sAX87P
-yfM//qZT7n7vRjy+p//kJEyhJpN8ioDQH5wEyFpIFOheORCtpp//VyeBpSOrp2uRnLzsnbVyqq7e
-dS3+4BR8d4RvrgPx9+kD2upE7Tr+vL8O3IntCVcMuOfxh0YFr/dfdB0IpJL/5kk4PBO0vQirWoaf
-az7mrzcDeD7HgGkKwez9pzf/TnfIsPW3k/Plgvtv+vQ0kT766YX196N6xsJ3+/Ydf7sU6JycifvM
-Pvb4Q7Po370E/o0z9evSCsIleT4uquFL9aO1949+4W01+f2/f11JpuVi6kO8+8WboXj58tq/rbn/
-fHeFHK/yb/7x7ao/vs7X//71A/7+pd+91tunevvLTfgiD/JzQHoR6/Hw9W1OOVT/+BstxYBW414e
-nl+q4N3Nbk6k3t/e0D/+9u7tfrMQ/PT4VXVI3w4znRmhTcX1Rw9LUudBvh3muD67gpvpo4fdHORw
-yA5vBzp+kzg80Xl9+MhhevgcHJIfnmmIsRNJ/Y+d8b+uuT871dsDnMBf/schLf7XL7sDjprw3RnS
-TNaVj7/K7iAzdiXx+5NkoT7/C47NdZp8d2BjokJ/9NScHuIqODx3Ly/F28GO363N1ubtL6Zb7M9d
-42eH52D48T30Zev00bd/8Rzy9t/e6PEuot3zF3yZ++a5+Ry8oEl5d/CJuf/2F3/+tOybLDp8ejvO
-8V1/eXh+9HRcHaJDVaMlfXfsL4+mjx77Oozj8N2CRU/Q/Auu7ZtDGia/nB+em2/fNfF3Fg+4j77r
-IwrjR0vL123rR49//1LVv8xeMtL+3t7s9H3qbGX/gnd/dmAxZ8Gq5btr3IB7/BesvOsm4uhswL6c
-hOl92+zhhP4XPC/W+bt3PB0XO8PbS/35W4en8q9jvvPwc/6JGeBJNSUtVm8H//I5NI1sjbe/+sDr
-Idz548eTqqnYNP6KhTIcc/l+O8Ch8Q66f8H3fIM6CXjt28mYzs/Xg/8Fd++PB7K/ey2GqG9/9+e/
-jH8RqvnBXcLZJPhp3u8MVObSDIA//tbPXnz2OIfh+29hOvxfsJn8WQzNB0/LH47VuYZ491MWxkcX
-0X+Jgv/gR5gH/xru/cGXOD5nfo5c+uAr/EubyAePf/PCKup/v8e3NHwd5jRd++iXfHp45vy8Hee4
-SBsYEwTyCUFrAyUF0uS3f/7za8SP16M/IxD56fn8Ub35azvm91XoW7vtR//tfYk9/cbn5OUg//l/
-AAAA//8=</cx:binary>
+                <cx:binary>nFnZctw4lv0Vh56HNkACINjRrgeQuUupzZblekGoJBkESQAEAS7g1w/kqq6tezwTk5ERKRL7vbj3
+nHv0z+flH8/d69PwblGddv94Xj5e1N73//jwwT3Xr+rJvVfyeTDOfPPvn436YL59k8+vH16Gp1lq
+8SEFEH14rp8G/7pc/PTPOJt4NZfm+clLo2/H1yHcvbqx8+4Hbf+x6d3Ti5K6ks4P8tnDjxf9qJun
+Xy7evWovffgU+tePF3/pc/Huw99n+rdV33VxY358iWMz8J6ilBY5Si/edUaL397n+D2CGOVZkRXf
+P/Rfa56fVBx387/u4/sunl5ehlfn4jG+//4x7i97jq/ZxbtnM2r/ZikRjfbx4qBf5NPFO+lM+WtD
+ad42fDh/P+GHv9r4p3/+7UU889/e/MkNP2r73VjVk3/afLfyn0b+uPVfhv/b0B8561c/Hl4+XqSk
+ANmfvPc2yW8j/5PJ/zTk9cn5jxc5eR99hTKQZoRCggC5eDe/fm/J3lOKs4JSgnJEQIEu3mkz+Dq6
+P32PIczzIqcYYpLii3fOjG8tafEeoxSCOBDnhBCQ/n6xb0wXhNG/2+K353d6VDdGau8+XhQUXLzr
+f+33ttMcgRwTnGZpkSIcvyjep/756S5GT+wO/0sI0RKpU70bx8ntB9iOT1qSngma8ZusS9xptiBU
+XYLMSU+0ZlhpcRgW2pwKoGE5YkwfqA74pRiALi3Kk20OAarSuVlOSavrzYoSwgaM+REpKZhY1icy
+ohvTyCob08DIok5J0qFqLmjOcsNHNhTynAU3lNMqH1KDXjgay2zC6ti63u5S1cGVZaBdtrYf8zKk
+VG5kk8PPHZYJZbatu2O2In3Vt2G91jBXz2NrQEkoIb8Emdb7uN583Rch2aYoEZb1BImHFEy4HJKp
+L1EYZTUUvP0Zq7GrxBpX5SoTirWy618mkE0HZI34gpSbD4k2WZUTOFVWq9tetuapDbU/NjCowzzQ
+5XpMKN2ZGi8Zc87AhbVmGW/qbln2SUv0yYh5vAvK4aUkOq1Z7Zv0c4CKiWFZ7mWTibOr0cxSPpld
+ovKbFOnpsy+AeLWdHB4lmdGtAmBmBtDiRlKblctg+o0iXN5PjUoPRRoemnyyNzWW8D5rLT6M0dYn
+r7i8nGqqH2a+gJ0EIGOLE7KKV6McrG2eZtvLc13TemZWQlgwM+fTPSoadc77+pUjTstVtmPpRmIf
+iQy8TFDon8nKv4Um0LXKi+VLnfb7tsbHcUzbjewhvJ1oCzaSNu1Nk8/FIyJLfwlDj06ZGrLDOK7d
+C2rBxFw7GMVcU+Nz0Fly1mtPHQOowM89Hu2up0Id3FIH1tbDfFQA8fPcabvPO6RKDyk8QJ2kVzbk
+r3w4wfQxa+LKABbFvUuUOXbYuWrlOscsbcZ+s4ogRKmSXq8sOkHdCGLac1Gvblcka/icrh281t04
+lAIZ+wW6NZy7UPBKgAlchtROlbBqKLN8mqsRRgcxSNLiSs3jYFhtercHNc+qUU+edQn5Ns6Inv2Y
++41NbbEl3i5lbdLl4GMwn0mRfxZI2qposd9KmdOtC0P+qWiTadt3qnsidWIZcTKTJSYJZ7wVcNMM
+xDG7hrBddZKUSxhNmQRgKzIasEGrHJmQwV4pYsI+tWO+6xqgDmrNr/Uy7FSme5bTtb/ilKMKN7TE
+nrA8LP1uFRPrlWVDw8swBV3OqfkF12EHUSdPAi+U9SNob/uFyG2fuGHXupQh2KItgQPZpVzqE00B
+/drKJUxMAD3dQmnnO6L7r4ioX/QqNnh1l07nz82kyc3KW7rvkwFtB6h4TD5vM6qBZuUM567s17vZ
+oTsKZWCqG3xlLQ/3opCeZXOrGZfKlotULxk250Guy4b4VJdwJMmdIf34pTZzygBs193QEnCdm8aX
+Jmh4Ao3wR+MytBl9n7962vItMSS7GsYsBhPI4YbLvLjP8jRadUFpTB7FUrppsqXBZt3Ge6w3FIZZ
+s2btly9CcXrI8qbedK1z2xTk5rjkiSzzdnK7yTTh0Bq8CAadIwe3inXHR77eULHircgzx3gmchZ4
+WCoxRG+HFtclXnXBYFL7XVvYbpPw3LA+jGiXjpgChkj2S9/A2sbeJlz6AcBSAb8cQWv4l6CTtZxM
+21/6Yp6OwC76qLuZ7mtV6F9mrP1prlNQ0qIFdzHI+5rJOuesmy2R5ZLO2WciTZ6WPnT9ptXLODGO
+anp2Iia+TS1ptm2mpmMLJ+JlKdTnbLZ20we5SzoYWDTEvkMmryJg4MdJJ7ejm89BxpPzpqwnqcth
+CliwlZLmcRBq3aiONmUTvN8a09CKD10RWJNivMmG2jFXjDH+fcClk1DuvMbgxuXdpgVjx2pRlInm
+E2uK/HJs8FiOWS3KNkOnZjWOoYLe63VaTthE7GZYI39fJ0RWapxfWpq1+9kIWHE+XdVa3jYZQVXb
+JMt2pdNQSgfQ1pt53WUj73cZjhkcw2YtF57ZzajW6bUQ/rae8s8N6X3BpjhBCds+PPZNTBtMcNXg
+/UQ4Kt2KeAk8qFzHh50HbmUr4OFn2RX4DpBuOsXZy45Oez6Jr76NWb+Tn7IsP6dKbEzi5lJ1Qm2c
+TwDDHU/KenH15ZCA5riYFh3yhtiSx5N/warIvrqsmStpaXuIKLHXnvf3okuGXbAjxyWcplkwVev+
+cVlzcbIk+Otchf5kkty/qgIlLN7cNxgMMjpV6a3DpKjy1RV3jkjI1DJuCBgfx3Q680adxrlZz1CJ
+KzPUaYTZTpfcaD+zwkoDKt7EpLpAcEysFWzO3GW2hFIt6cTS2kOGmmxnumY3QAiYt03Ws6RVbQVX
+fxjUzJaF9pcpooLFXq/QhQJviW6jFTuXDveZmO1lT1/zJZu/yTzws11aymaO0xP2A9W7aZaeVMbM
+/mmNMPTarIBW/QK6G9jW/cQCWWyEt2ZaPylN/acWFFlSFaFVaTl30t6GCfgq9Hi4SoKrK+zVgJlM
+A3iIqaepbM+XnbPasTkN8w6kGlYr7Wg1zkNTBliT+6Stl4OiYVU7IgKvq6x2n/o6iSBt6TVN8Ngz
+RZOHIPO17E2kKAL0r12/LJ96lXdl4nKyHVEX0TvLVHFLkXlY8unG6ElttK7PXg5bMtKe+Wx8hH74
+PKzKsUy32S3EhdnqQodthL3iSnNVy00AXf7YYNcxE2mFwO1zU6NdZsR+dfLkZb6f/TxW84y0qFak
+hIqRZdRGTDFhuGZjGmy2ENi9weNNSMBdC+rnCGgP8zC9OIx2dpnxuRfCbgVERUmaPt7dsMKIu5GF
+8XqDNcmrhqzhqncIlNwpVGUB2TPH9bbDXNTVvOSuKmo0ngVAK8t7O0OWuKavGgyyTzH90suwulEy
+PyVoEym8PkAYWSeqz8C08pQsLqnkNGd7uzpwG1lcuDdNt27RNOMbSFVkws0LEpHAqgWNpzE6urTd
+eEUaZ45JbRLmMO4YdqmrQJ8VR55KX8EMLvssmUBphuSpCaTfB9t1lzMNEaK5JRufm4FZR5bKrDW+
+dDOHN5F+2yPNp3Tfm1kcLW9OKlns17FZ8oeJx/yXTrLOWBuSmeXe07vB0v664BDu5sY80U7H/RZD
+v5kj+rAlJwebyFA66x8tGZ7sZHAlU49YUHZHfNscOYDJFywVfdRqTjbS1slnjYZKkV6M0R1yLLto
+utcl4WoTGSW5nUMQ5dJogFmhBncktu323tp9LC3IPps9iUZV4pKLpL/JaQQpYboq83r80tfeXmJJ
+h69GGli12GrKBmKTmHiyukzn1m0ht0O8O5KXdVC8nEWRbEneFuWKEd7108g/61DbWyBSWtna8rts
+6LMzkaI/RA4235m0018GMbgyUzNiCcbhLk0UYJP03YtRMN9ZSfS3ou/5bpl7VFIbGXSfN+gyhWjt
+2Jpo9SRTWV/iaW0wgzNNTwYEeS9EZHksIVY+ONBFyOh6V6UjF2fYAbATmQJnmIcY15PIGKmdO/BV
+wT3ItfhZoxUynuZpNSezekF2LM4J7fFDgDBho58JI9novhbOirvWNt29mZf0OFNqI+RBOUXTp6Ts
+YyWwiRHTlM69gauub12DtuuA60jYnHsYa472iVvmc55NvCSz1WfkvDspgPPNyvnrrOcBsrWvyVZ3
+IVK3JePbdiX0K1yG7CS0yu7mlbjN4qE9CdeQyD8J3geP8c+xZLWbVYnitfc8rYpYAB7qQM01EVKe
+J1jLPUY+EnKk7dFkBYiogYrtoi2FZSpv2mTWm1FEZk5lAY8ygViXadGc03W4VqBOmV+wY1Pu1ZGu
+rZesT4uDz2F2ieeh/RYPaje86PNTm9doYJ03nM1d+Ib5+uxVGxgFgyj7mYoKDgtkcRXJ0CRi/uw0
+P/FanKe2jcwRFldpH9qKUDyVrsXyi0yaUM1r99XQaS2laPKrfmyYwmuz1UCF0qRuPr0V+TXz+tXO
+/Q5TVZyML8KGD3VR9cE2D3WdJhnLFyiqOsZc1U3EM2JrXY3jAC9RpGClTVP9WUQCz2MtNz0IgAlL
+LLhvguBbxLd05jvY2vbI1XTbzKTKxRyTS4iUHIBtImA4B77arRfpwrKwXDfI/RKv58KaRTXn0Uxr
+hcPgKuttHmtugnbDCjPNWqD7EmfxonZcMT805Hrs6q9rDc4i5s9NB1Lwxg3k1tgk2Ux9km5incf3
+tFFd1SI53E59JytQO7ufXLFuEtyofUSK5ginXjM7KXo9rgHt3JrbUmNxNeUZEHEtII5yGeHMujSm
+9rpt0rSChjvO1iL9kqaRPCFaIts1bOpMJ0rTJ20Zie++NpctpTMbxTRfqpgKW0aTZbp3uNFfFU9j
+8GQ15M8D12vCeJ0vHQO1XUAJpuZWDTC5WxBWXh0GNFFGfQ18pJl4OhvV6nPjG/hzRMDh3CddLHPr
+IW68aS1lq4SLKGFSPI7Zyh9SOKKNnWLdwrwMsT5VegkHPbRwR1Thd3kvyN2gl/YYPBkPOBh8ly0I
+7cYpHZ7J0BSgIvUovxpT+OdFqZW5vo/BOMXkGU1TnLiF5uDjJvdFOgc2EdSW0jhfxQnQY6yl54dp
+lOre2xmd2zw1uxpqszIChuss+vQ2VWnczEr9g0jn175r0k2shOSxBhO8DjD+NS68KFGWTVE3wLZj
+TifwOqIt3Cg0tbHkqBULIblMGtCytkNim0diwQpoE9Z1sGhYKnHUeNYmhi3oi/w+75ZkU6h0joTb
+qCugwCYdVloCgWPGmoTckzC1x2LIhrLw5tNC2qehn6/WIBPWzPKlbVFzyO1wpaYhK0FYbM+y5YuL
+xQ+NMZxnMFyNRfjZWJ0cZVPXt38WKv+imT2bPgxS1L/pwb8//vTJqPj9rlz+8fJNTv7jafdq3uRA
+9/dOb2rn773+UD/fVMTf5c6/6ZK/atI/bv1d5Hsb+13d+2R+rIr+T53+LI7+e5//v0b6fa7vEu2P
+5vj/Kd5RSv9NRf7R8f9PnX5zyff/Mvz03wAAAP//</cx:binary>
               </cx:geoCache>
             </cx:geography>
           </cx:layoutPr>
@@ -6252,7 +3753,7 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>87751</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -6368,7 +3869,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="4591050" y="95250"/>
-              <a:ext cx="3562350" cy="2486025"/>
+              <a:ext cx="3562350" cy="3248025"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6437,6 +3938,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_state" xr10:uid="{28B91DC0-80C8-45CD-95E4-2D6F4E97AB19}" sourceName="state">
   <extLst>
@@ -6454,45 +3959,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F5150032-0159-4CA8-893D-099E996638F2}" name="Table5" displayName="Table5" ref="A1:P21" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F5150032-0159-4CA8-893D-099E996638F2}" name="Table5" displayName="Table5" ref="A1:P21" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
   <autoFilter ref="A1:P21" xr:uid="{F5150032-0159-4CA8-893D-099E996638F2}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{C5CBFC98-8E7D-4C21-89E4-FAF15EA36526}" name="roll no" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{90E1E575-36AE-4B57-9554-F810D22C4069}" name="name" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{41CE8180-A4B3-4981-A46A-5797578CAEBC}" name="class" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{4F43BF84-4F85-45AF-A5B7-BFD0B0B34915}" name="age" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{723CA5DE-548C-4380-AD3E-C06E34485EB9}" name="math" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{37F8BA1F-733A-4691-BF51-B91D7018745E}" name="science" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{C5CBFC98-8E7D-4C21-89E4-FAF15EA36526}" name="roll no" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{90E1E575-36AE-4B57-9554-F810D22C4069}" name="name" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{41CE8180-A4B3-4981-A46A-5797578CAEBC}" name="class" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{4F43BF84-4F85-45AF-A5B7-BFD0B0B34915}" name="age" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{723CA5DE-548C-4380-AD3E-C06E34485EB9}" name="math" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{37F8BA1F-733A-4691-BF51-B91D7018745E}" name="science" dataDxfId="18">
       <calculatedColumnFormula>E2-5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{CDC30C63-68AB-41E4-A290-A45A3E040F06}" name="marathi" dataDxfId="18">
+    <tableColumn id="7" xr3:uid="{CDC30C63-68AB-41E4-A290-A45A3E040F06}" name="marathi" dataDxfId="17">
       <calculatedColumnFormula>F2+10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BEE1DACA-0144-458E-B4DB-2E8FA27BD48F}" name="hindi" dataDxfId="17">
+    <tableColumn id="8" xr3:uid="{BEE1DACA-0144-458E-B4DB-2E8FA27BD48F}" name="hindi" dataDxfId="16">
       <calculatedColumnFormula>G2-15</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{BBBCAECC-4D66-4109-B234-FD85295AFE78}" name="english" dataDxfId="16">
+    <tableColumn id="9" xr3:uid="{BBBCAECC-4D66-4109-B234-FD85295AFE78}" name="english" dataDxfId="15">
       <calculatedColumnFormula>E2+10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B96932F1-5DF6-40E6-82DD-186EBF3F6BDB}" name="total " dataDxfId="15">
+    <tableColumn id="10" xr3:uid="{B96932F1-5DF6-40E6-82DD-186EBF3F6BDB}" name="total " dataDxfId="14">
       <calculatedColumnFormula>E2+F2+G2+H2+I2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{ACBC5DBF-7793-4B03-BAEE-DA459C59102B}" name="percentage" dataDxfId="14">
+    <tableColumn id="11" xr3:uid="{ACBC5DBF-7793-4B03-BAEE-DA459C59102B}" name="percentage" dataDxfId="13">
       <calculatedColumnFormula>J2/5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{86B97156-9599-4332-9136-4948BFDC7CA4}" name="max mark" dataDxfId="13">
+    <tableColumn id="12" xr3:uid="{86B97156-9599-4332-9136-4948BFDC7CA4}" name="max mark" dataDxfId="12">
       <calculatedColumnFormula>MAX(E2:I2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{59256C59-67E2-4019-929E-7A2B13AA2E2D}" name="min mark" dataDxfId="12">
+    <tableColumn id="13" xr3:uid="{59256C59-67E2-4019-929E-7A2B13AA2E2D}" name="min mark" dataDxfId="11">
       <calculatedColumnFormula>MIN(E2:I2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{87E2380E-FA60-4C28-B452-18BA6BEEB07B}" name="grade" dataDxfId="11">
+    <tableColumn id="14" xr3:uid="{87E2380E-FA60-4C28-B452-18BA6BEEB07B}" name="grade" dataDxfId="10">
       <calculatedColumnFormula>IF(K2&gt;=75,"A grade",IF(K2&gt;=60,"B grade",IF(K2&gt;=50,"C grade","Fail")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{AC83FF28-CE7B-48BB-BB92-5021D9540420}" name="pass/fail" dataDxfId="10">
+    <tableColumn id="15" xr3:uid="{AC83FF28-CE7B-48BB-BB92-5021D9540420}" name="pass/fail" dataDxfId="9">
       <calculatedColumnFormula>IF(K2&gt;=35,"pass","fail")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D4F53D51-E319-4A77-BCBF-62DC45AD5BB4}" name="rank" dataDxfId="9">
+    <tableColumn id="16" xr3:uid="{D4F53D51-E319-4A77-BCBF-62DC45AD5BB4}" name="rank" dataDxfId="8">
       <calculatedColumnFormula>RANK(K2,$K$2:$K$20,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6504,7 +4009,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C9B4D063-B7D8-4E47-8C86-D164EA8A7EDA}" name="Table6" displayName="Table6" ref="A1:E5" totalsRowShown="0">
   <autoFilter ref="A1:E5" xr:uid="{C9B4D063-B7D8-4E47-8C86-D164EA8A7EDA}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{49C51BA5-B62E-40F7-85F4-4331E95A2AC7}" name="Timeline" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{49C51BA5-B62E-40F7-85F4-4331E95A2AC7}" name="Timeline" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{B8340230-C8E7-4489-9FB7-8C38F220FDCA}" name="Values"/>
     <tableColumn id="3" xr3:uid="{CA2197FD-54B9-44BE-ABAB-9BCC80299CC5}" name="Forecast"/>
     <tableColumn id="4" xr3:uid="{BE0ED526-ABE0-4DA3-B130-5A3417BAF8EE}" name="Lower Confidence Bound"/>
@@ -6519,10 +4024,7 @@
   <autoFilter ref="A1:B9" xr:uid="{C6AA5265-49D3-4EB4-80BD-70DACE080A45}">
     <filterColumn colId="0">
       <filters>
-        <filter val="mp"/>
         <filter val="punjab"/>
-        <filter val="rajasthan"/>
-        <filter val="up"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -8539,7 +6041,7 @@
         <v>61</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>62</v>
@@ -8692,7 +6194,7 @@
         <v>61</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -8702,21 +6204,14 @@
       <c r="G13" s="4">
         <v>70</v>
       </c>
-      <c r="H13" s="4">
-        <f>G13/J13</f>
-        <v>0.7</v>
-      </c>
-      <c r="J13" s="4">
-        <v>100</v>
+      <c r="H13" s="4" t="e">
+        <f>G13/J131</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G14" s="4">
         <v>60</v>
-      </c>
-      <c r="H14" s="4" t="e">
-        <f>G14/J14</f>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -8758,7 +6253,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="9">
-        <v>2000000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8766,7 +6261,7 @@
         <v>71</v>
       </c>
       <c r="B3" s="9">
-        <v>600000</v>
+        <v>410000</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -8777,7 +6272,7 @@
         <v>750000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
         <v>73</v>
       </c>
@@ -8801,20 +6296,20 @@
         <v>545222</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>76</v>
       </c>
       <c r="B8" s="9">
-        <v>54820000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>77</v>
       </c>
       <c r="B9" s="12">
-        <v>5486555</v>
+        <v>450000</v>
       </c>
     </row>
   </sheetData>
@@ -8835,80 +6330,801 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD3DE508-F655-476C-BEE4-DB9C4CE70159}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="24">
+        <v>2021</v>
+      </c>
+      <c r="B2" s="24">
+        <v>96</v>
+      </c>
+      <c r="C2" s="24">
+        <v>100</v>
+      </c>
+      <c r="D2" s="24">
+        <v>89</v>
+      </c>
+      <c r="E2" s="24">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="24">
+        <v>2022</v>
+      </c>
+      <c r="B3" s="24">
+        <v>53</v>
+      </c>
+      <c r="C3" s="24">
         <v>86</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D3" s="24">
+        <v>66</v>
+      </c>
+      <c r="E3" s="24">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="24">
+        <v>2023</v>
+      </c>
+      <c r="B4" s="24">
+        <v>77</v>
+      </c>
+      <c r="C4" s="24">
+        <v>92</v>
+      </c>
+      <c r="D4" s="24">
+        <v>93</v>
+      </c>
+      <c r="E4" s="24">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="24">
+        <v>2024</v>
+      </c>
+      <c r="B5" s="24">
+        <v>84</v>
+      </c>
+      <c r="C5" s="24">
+        <v>61</v>
+      </c>
+      <c r="D5" s="24">
         <v>81</v>
       </c>
-      <c r="C2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E5" s="24">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="24">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="24">
+        <v>76</v>
+      </c>
+      <c r="C6" s="24">
+        <v>76</v>
+      </c>
+      <c r="D6" s="24">
+        <v>74</v>
+      </c>
+      <c r="E6" s="24">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90ACC145-3951-4C66-A2C2-E39A59494BFE}">
+  <dimension ref="A2:E7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C2" s="24" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="D2" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="24">
+        <v>2021</v>
+      </c>
+      <c r="B3" s="24">
+        <v>94</v>
+      </c>
+      <c r="C3" s="24">
+        <v>83</v>
+      </c>
+      <c r="D3" s="24">
+        <v>70</v>
+      </c>
+      <c r="E3" s="24">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="24">
+        <v>2022</v>
+      </c>
+      <c r="B4" s="24">
+        <v>97</v>
+      </c>
+      <c r="C4" s="24">
+        <v>98</v>
+      </c>
+      <c r="D4" s="24">
         <v>82</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="E4" s="24">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="24">
+        <v>2023</v>
+      </c>
+      <c r="B5" s="24">
+        <v>65</v>
+      </c>
+      <c r="C5" s="24">
+        <v>66</v>
+      </c>
+      <c r="D5" s="24">
+        <v>60</v>
+      </c>
+      <c r="E5" s="24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="24">
+        <v>2024</v>
+      </c>
+      <c r="B6" s="24">
+        <v>85</v>
+      </c>
+      <c r="C6" s="24">
+        <v>86</v>
+      </c>
+      <c r="D6" s="24">
+        <v>72</v>
+      </c>
+      <c r="E6" s="24">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="24">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="24">
+        <v>78</v>
+      </c>
+      <c r="C7" s="24">
+        <v>74</v>
+      </c>
+      <c r="D7" s="24">
+        <v>72</v>
+      </c>
+      <c r="E7" s="24">
         <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EDCDC6A-CBE2-4379-961A-3E4F40848BBE}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="24">
+        <v>2021</v>
+      </c>
+      <c r="B2" s="24">
+        <v>77</v>
+      </c>
+      <c r="C2" s="24">
+        <v>73</v>
+      </c>
+      <c r="D2" s="24">
+        <v>99</v>
+      </c>
+      <c r="E2" s="24">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="24">
+        <v>2022</v>
+      </c>
+      <c r="B3" s="24">
+        <v>99</v>
+      </c>
+      <c r="C3" s="24">
+        <v>88</v>
+      </c>
+      <c r="D3" s="24">
+        <v>63</v>
+      </c>
+      <c r="E3" s="24">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="24">
+        <v>2023</v>
+      </c>
+      <c r="B4" s="24">
+        <v>52</v>
+      </c>
+      <c r="C4" s="24">
+        <v>69</v>
+      </c>
+      <c r="D4" s="24">
+        <v>98</v>
+      </c>
+      <c r="E4" s="24">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="24">
+        <v>2024</v>
+      </c>
+      <c r="B5" s="24">
+        <v>69</v>
+      </c>
+      <c r="C5" s="24">
+        <v>93</v>
+      </c>
+      <c r="D5" s="24">
+        <v>98</v>
+      </c>
+      <c r="E5" s="24">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="24">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="24">
+        <v>94</v>
+      </c>
+      <c r="C6" s="24">
+        <v>93</v>
+      </c>
+      <c r="D6" s="24">
+        <v>85</v>
+      </c>
+      <c r="E6" s="24">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B06C24-1B82-4D73-8D73-10AB5BEFC0D3}">
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2">
+        <f>Sheet6!$B$2</f>
+        <v>96</v>
+      </c>
+      <c r="D2">
+        <f>Sheet6!$C$2</f>
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <f>Sheet6!$D$2</f>
+        <v>89</v>
+      </c>
+      <c r="F2">
+        <f>Sheet6!$E$2</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3">
+        <f>Sheet7!$B$3</f>
+        <v>94</v>
+      </c>
+      <c r="D3">
+        <f>Sheet7!$C$3</f>
+        <v>83</v>
+      </c>
+      <c r="E3">
+        <f>Sheet7!$D$3</f>
+        <v>70</v>
+      </c>
+      <c r="F3">
+        <f>Sheet7!$E$3</f>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4">
+        <f>Sheet8!$B$2</f>
+        <v>77</v>
+      </c>
+      <c r="D4">
+        <f>Sheet8!$C$2</f>
+        <v>73</v>
+      </c>
+      <c r="E4">
+        <f>Sheet8!$D$2</f>
+        <v>99</v>
+      </c>
+      <c r="F4">
+        <f>Sheet8!$E$2</f>
+        <v>71</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="25"/>
+    </row>
+    <row r="5" spans="1:10" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2021</v>
+      </c>
+      <c r="C5">
+        <f>SUM(C2:C4)</f>
+        <v>267</v>
+      </c>
+      <c r="D5">
+        <f>SUM(D2:D4)</f>
+        <v>256</v>
+      </c>
+      <c r="E5">
+        <f>SUM(E2:E4)</f>
+        <v>258</v>
+      </c>
+      <c r="F5">
+        <f>SUM(F2:F4)</f>
+        <v>193</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="J5" s="25"/>
+    </row>
+    <row r="6" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6">
+        <f>Sheet6!$B$3</f>
+        <v>53</v>
+      </c>
+      <c r="D6">
+        <f>Sheet6!$C$3</f>
+        <v>86</v>
+      </c>
+      <c r="E6">
+        <f>Sheet6!$D$3</f>
+        <v>66</v>
+      </c>
+      <c r="F6">
+        <f>Sheet6!$E$3</f>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7">
+        <f>Sheet7!$B$4</f>
+        <v>97</v>
+      </c>
+      <c r="D7">
+        <f>Sheet7!$C$4</f>
+        <v>98</v>
+      </c>
+      <c r="E7">
+        <f>Sheet7!$D$4</f>
+        <v>82</v>
+      </c>
+      <c r="F7">
+        <f>Sheet7!$E$4</f>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8">
+        <f>Sheet8!$B$3</f>
+        <v>99</v>
+      </c>
+      <c r="D8">
+        <f>Sheet8!$C$3</f>
+        <v>88</v>
+      </c>
+      <c r="E8">
+        <f>Sheet8!$D$3</f>
+        <v>63</v>
+      </c>
+      <c r="F8">
+        <f>Sheet8!$E$3</f>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2022</v>
+      </c>
+      <c r="C9">
+        <f>SUM(C6:C8)</f>
+        <v>249</v>
+      </c>
+      <c r="D9">
+        <f>SUM(D6:D8)</f>
+        <v>272</v>
+      </c>
+      <c r="E9">
+        <f>SUM(E6:E8)</f>
+        <v>211</v>
+      </c>
+      <c r="F9">
+        <f>SUM(F6:F8)</f>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10">
+        <f>Sheet6!$B$4</f>
+        <v>77</v>
+      </c>
+      <c r="D10">
+        <f>Sheet6!$C$4</f>
+        <v>92</v>
+      </c>
+      <c r="E10">
+        <f>Sheet6!$D$4</f>
+        <v>93</v>
+      </c>
+      <c r="F10">
+        <f>Sheet6!$E$4</f>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11">
+        <f>Sheet7!$B$5</f>
+        <v>65</v>
+      </c>
+      <c r="D11">
+        <f>Sheet7!$C$5</f>
+        <v>66</v>
+      </c>
+      <c r="E11">
+        <f>Sheet7!$D$5</f>
+        <v>60</v>
+      </c>
+      <c r="F11">
+        <f>Sheet7!$E$5</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12">
+        <f>Sheet8!$B$4</f>
+        <v>52</v>
+      </c>
+      <c r="D12">
+        <f>Sheet8!$C$4</f>
+        <v>69</v>
+      </c>
+      <c r="E12">
+        <f>Sheet8!$D$4</f>
+        <v>98</v>
+      </c>
+      <c r="F12">
+        <f>Sheet8!$E$4</f>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2023</v>
+      </c>
+      <c r="C13">
+        <f>SUM(C10:C12)</f>
+        <v>194</v>
+      </c>
+      <c r="D13">
+        <f>SUM(D10:D12)</f>
+        <v>227</v>
+      </c>
+      <c r="E13">
+        <f>SUM(E10:E12)</f>
+        <v>251</v>
+      </c>
+      <c r="F13">
+        <f>SUM(F10:F12)</f>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14">
+        <f>Sheet6!$B$5</f>
+        <v>84</v>
+      </c>
+      <c r="D14">
+        <f>Sheet6!$C$5</f>
+        <v>61</v>
+      </c>
+      <c r="E14">
+        <f>Sheet6!$D$5</f>
+        <v>81</v>
+      </c>
+      <c r="F14">
+        <f>Sheet6!$E$5</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15">
+        <f>Sheet7!$B$6</f>
+        <v>85</v>
+      </c>
+      <c r="D15">
+        <f>Sheet7!$C$6</f>
+        <v>86</v>
+      </c>
+      <c r="E15">
+        <f>Sheet7!$D$6</f>
+        <v>72</v>
+      </c>
+      <c r="F15">
+        <f>Sheet7!$E$6</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16">
+        <f>Sheet8!$B$5</f>
+        <v>69</v>
+      </c>
+      <c r="D16">
+        <f>Sheet8!$C$5</f>
+        <v>93</v>
+      </c>
+      <c r="E16">
+        <f>Sheet8!$D$5</f>
+        <v>98</v>
+      </c>
+      <c r="F16">
+        <f>Sheet8!$E$5</f>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2024</v>
+      </c>
+      <c r="C17">
+        <f>SUM(C14:C16)</f>
+        <v>238</v>
+      </c>
+      <c r="D17">
+        <f>SUM(D14:D16)</f>
+        <v>240</v>
+      </c>
+      <c r="E17">
+        <f>SUM(E14:E16)</f>
+        <v>251</v>
+      </c>
+      <c r="F17">
+        <f>SUM(F14:F16)</f>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18">
+        <f>Sheet6!$B$6</f>
+        <v>76</v>
+      </c>
+      <c r="D18">
+        <f>Sheet6!$C$6</f>
+        <v>76</v>
+      </c>
+      <c r="E18">
+        <f>Sheet6!$D$6</f>
+        <v>74</v>
+      </c>
+      <c r="F18">
+        <f>Sheet6!$E$6</f>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19">
+        <f>Sheet7!$B$7</f>
+        <v>78</v>
+      </c>
+      <c r="D19">
+        <f>Sheet7!$C$7</f>
+        <v>74</v>
+      </c>
+      <c r="E19">
+        <f>Sheet7!$D$7</f>
+        <v>72</v>
+      </c>
+      <c r="F19">
+        <f>Sheet7!$E$7</f>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20">
+        <f>Sheet8!$B$6</f>
+        <v>94</v>
+      </c>
+      <c r="D20">
+        <f>Sheet8!$C$6</f>
+        <v>93</v>
+      </c>
+      <c r="E20">
+        <f>Sheet8!$D$6</f>
+        <v>85</v>
+      </c>
+      <c r="F20">
+        <f>Sheet8!$E$6</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2025</v>
+      </c>
+      <c r="C21">
+        <f>SUM(C18:C20)</f>
+        <v>248</v>
+      </c>
+      <c r="D21">
+        <f>SUM(D18:D20)</f>
+        <v>243</v>
+      </c>
+      <c r="E21">
+        <f>SUM(E18:E20)</f>
+        <v>231</v>
+      </c>
+      <c r="F21">
+        <f>SUM(F18:F20)</f>
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataConsolidate leftLabels="1" topLabels="1" link="1">
+    <dataRefs count="3">
+      <dataRef ref="A1:E6" sheet="Sheet6"/>
+      <dataRef ref="A2:E7" sheet="Sheet7"/>
+      <dataRef ref="A1:E6" sheet="Sheet8"/>
+    </dataRefs>
+  </dataConsolidate>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>